--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -436,10 +436,10 @@
     <t>2021-04-26</t>
   </si>
   <si>
+    <t>2021-03-12</t>
+  </si>
+  <si>
     <t>2021-04-23</t>
-  </si>
-  <si>
-    <t>2021-03-12</t>
   </si>
   <si>
     <t>2021-03-16</t>
@@ -29256,10 +29256,10 @@
         <v>3.032663136583086</v>
       </c>
       <c r="D557" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E557">
-        <v>2.50374318641956</v>
+        <v>2.455046721694439</v>
       </c>
       <c r="F557">
         <v>-1</v>
@@ -29268,10 +29268,10 @@
         <v>0.003207336863416915</v>
       </c>
       <c r="H557">
-        <v>0.00265625681358044</v>
+        <v>0.002604953278305561</v>
       </c>
       <c r="I557">
-        <v>0.5289199501635258</v>
+        <v>0.5776164148886465</v>
       </c>
       <c r="J557">
         <v>0.06517676374396589</v>
@@ -29283,10 +29283,10 @@
         <v>3.12</v>
       </c>
       <c r="M557">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="N557">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="O557">
         <v>1</v>
@@ -29306,10 +29306,10 @@
         <v>2.917225510045163</v>
       </c>
       <c r="D558" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E558">
-        <v>2.50374318641956</v>
+        <v>2.455046721694439</v>
       </c>
       <c r="F558">
         <v>-1</v>
@@ -29318,10 +29318,10 @@
         <v>0.003082774489954837</v>
       </c>
       <c r="H558">
-        <v>0.00265625681358044</v>
+        <v>0.002604953278305561</v>
       </c>
       <c r="I558">
-        <v>0.4134823236256033</v>
+        <v>0.462178788350724</v>
       </c>
       <c r="J558">
         <v>0.06517676374396589</v>
@@ -29333,10 +29333,10 @@
         <v>3</v>
       </c>
       <c r="M558">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="N558">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="O558">
         <v>1</v>
@@ -29356,7 +29356,7 @@
         <v>2.104641124313295</v>
       </c>
       <c r="D559" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E559">
         <v>2.474273209118076</v>
@@ -29406,7 +29406,7 @@
         <v>2.995940880174577</v>
       </c>
       <c r="D560" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E560">
         <v>2.471679723734519</v>
@@ -29456,7 +29456,7 @@
         <v>2.882421580463965</v>
       </c>
       <c r="D561" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E561">
         <v>2.471679723734519</v>
@@ -29556,7 +29556,7 @@
         <v>2.986590337413564</v>
       </c>
       <c r="D563" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E563">
         <v>2.463515443861097</v>
@@ -29606,7 +29606,7 @@
         <v>2.87355949889196</v>
       </c>
       <c r="D564" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E564">
         <v>2.463515443861097</v>
@@ -29706,7 +29706,7 @@
         <v>2.975995462698301</v>
       </c>
       <c r="D566" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E566">
         <v>2.454264695042546</v>
@@ -29756,7 +29756,7 @@
         <v>2.863518087781226</v>
       </c>
       <c r="D567" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E567">
         <v>2.454264695042546</v>
@@ -29856,7 +29856,7 @@
         <v>2.982237358539935</v>
       </c>
       <c r="D569" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E569">
         <v>2.459714708575913</v>
@@ -29906,7 +29906,7 @@
         <v>2.869433914437102</v>
       </c>
       <c r="D570" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E570">
         <v>2.459714708575913</v>
@@ -30006,7 +30006,7 @@
         <v>2.970054254577281</v>
       </c>
       <c r="D572" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E572">
         <v>2.449077222280164</v>
@@ -30056,7 +30056,7 @@
         <v>2.857887241278468</v>
       </c>
       <c r="D573" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E573">
         <v>2.449077222280164</v>
@@ -30106,7 +30106,7 @@
         <v>2.944089643772313</v>
       </c>
       <c r="D574" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E574">
         <v>2.426406629263886</v>
@@ -30156,7 +30156,7 @@
         <v>2.833278990739431</v>
       </c>
       <c r="D575" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E575">
         <v>2.426406629263886</v>
@@ -30256,7 +30256,7 @@
         <v>2.897401147650162</v>
       </c>
       <c r="D577" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E577">
         <v>2.385641300560216</v>
@@ -30306,7 +30306,7 @@
         <v>2.789029445907243</v>
       </c>
       <c r="D578" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E578">
         <v>2.385641300560216</v>
@@ -30406,7 +30406,7 @@
         <v>2.834385584744631</v>
       </c>
       <c r="D580" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E580">
         <v>2.330620249366581</v>
@@ -30456,7 +30456,7 @@
         <v>2.729305740765434</v>
       </c>
       <c r="D581" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E581">
         <v>2.330620249366581</v>
@@ -30506,7 +30506,7 @@
         <v>2.710585509297514</v>
       </c>
       <c r="D582" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E582">
         <v>2.222526153640366</v>
@@ -30556,7 +30556,7 @@
         <v>2.611972833438688</v>
       </c>
       <c r="D583" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E583">
         <v>2.222526153640366</v>
@@ -30606,7 +30606,7 @@
         <v>2.647551728558422</v>
       </c>
       <c r="D584" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E584">
         <v>2.167489195830861</v>
@@ -30656,7 +30656,7 @@
         <v>2.552231862141191</v>
       </c>
       <c r="D585" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E585">
         <v>2.167489195830861</v>
@@ -30706,7 +30706,7 @@
         <v>2.59897387935353</v>
       </c>
       <c r="D586" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E586">
         <v>2.125074208092261</v>
@@ -30756,7 +30756,7 @@
         <v>2.50619166177536</v>
       </c>
       <c r="D587" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E587">
         <v>2.125074208092261</v>
@@ -30806,7 +30806,7 @@
         <v>2.575095597538799</v>
       </c>
       <c r="D588" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E588">
         <v>2.104225260537608</v>
@@ -30856,7 +30856,7 @@
         <v>2.483560752891249</v>
       </c>
       <c r="D589" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E589">
         <v>2.104225260537608</v>
@@ -30906,7 +30906,7 @@
         <v>2.513392232045375</v>
       </c>
       <c r="D590" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E590">
         <v>2.050349933950066</v>
@@ -30956,7 +30956,7 @@
         <v>2.425080697535542</v>
       </c>
       <c r="D591" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E591">
         <v>2.050349933950066</v>
@@ -31006,7 +31006,7 @@
         <v>2.46037019732591</v>
       </c>
       <c r="D592" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E592">
         <v>2.004054575277101</v>
@@ -31056,7 +31056,7 @@
         <v>2.37482847059993</v>
       </c>
       <c r="D593" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E593">
         <v>2.004054575277101</v>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="349">
   <si>
     <t>trade_time</t>
   </si>
@@ -1418,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P569"/>
+  <dimension ref="A1:P572"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24429,10 +24429,10 @@
         <v>3.450555570267193</v>
       </c>
       <c r="D461" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E461">
-        <v>2.781218917988507</v>
+        <v>2.813685750602441</v>
       </c>
       <c r="F461">
         <v>-1</v>
@@ -24441,10 +24441,10 @@
         <v>0.002789444429732808</v>
       </c>
       <c r="H461">
-        <v>0.002218781082011493</v>
+        <v>0.002246314249397559</v>
       </c>
       <c r="I461">
-        <v>0.6693366522786857</v>
+        <v>0.6368698196647515</v>
       </c>
       <c r="J461">
         <v>-0.2466832613934271</v>
@@ -24456,10 +24456,10 @@
         <v>3.12</v>
       </c>
       <c r="M461">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N461">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O461">
         <v>1</v>
@@ -24479,10 +24479,10 @@
         <v>3.313287741969653</v>
       </c>
       <c r="D462" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E462">
-        <v>2.781218917988507</v>
+        <v>2.813685750602441</v>
       </c>
       <c r="F462">
         <v>-1</v>
@@ -24491,10 +24491,10 @@
         <v>0.002686712258030347</v>
       </c>
       <c r="H462">
-        <v>0.002218781082011493</v>
+        <v>0.002246314249397559</v>
       </c>
       <c r="I462">
-        <v>0.5320688239811457</v>
+        <v>0.4996019913672116</v>
       </c>
       <c r="J462">
         <v>-0.2466832613934271</v>
@@ -24506,10 +24506,10 @@
         <v>3</v>
       </c>
       <c r="M462">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N462">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O462">
         <v>1</v>
@@ -26623,43 +26623,43 @@
         <v>0</v>
       </c>
       <c r="B505" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C505">
-        <v>3.49154204736155</v>
+        <v>2.485588290136117</v>
       </c>
       <c r="D505" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E505">
-        <v>2.848860712287897</v>
+        <v>2.936587730747715</v>
       </c>
       <c r="F505">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G505">
-        <v>0.00274845795263845</v>
+        <v>0.001914411709863883</v>
       </c>
       <c r="H505">
-        <v>0.002211139287712102</v>
+        <v>0.002243412269252285</v>
       </c>
       <c r="I505">
-        <v>0.6426813350736529</v>
+        <v>0.4509994406115978</v>
       </c>
       <c r="J505">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K505">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L505">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M505">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N505">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O505">
         <v>1</v>
@@ -26673,10 +26673,10 @@
         <v>1</v>
       </c>
       <c r="B506" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C506">
-        <v>3.352133134439678</v>
+        <v>3.49154204736155</v>
       </c>
       <c r="D506" t="s">
         <v>133</v>
@@ -26688,22 +26688,22 @@
         <v>-1</v>
       </c>
       <c r="G506">
-        <v>0.002647866865560322</v>
+        <v>0.00274845795263845</v>
       </c>
       <c r="H506">
         <v>0.002211139287712102</v>
       </c>
       <c r="I506">
-        <v>0.503272422151781</v>
+        <v>0.6426813350736529</v>
       </c>
       <c r="J506">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K506">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L506">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M506">
         <v>1.15</v>
@@ -26720,96 +26720,96 @@
     </row>
     <row r="507" spans="1:16">
       <c r="A507" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B507" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C507">
-        <v>2.483803138304734</v>
+        <v>3.352133134439678</v>
       </c>
       <c r="D507" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E507">
-        <v>2.934421284350405</v>
+        <v>2.848860712287897</v>
       </c>
       <c r="F507">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G507">
-        <v>0.001916196861695266</v>
+        <v>0.002647866865560322</v>
       </c>
       <c r="H507">
-        <v>0.002245578715649595</v>
+        <v>0.002211139287712102</v>
       </c>
       <c r="I507">
-        <v>0.4506181460456711</v>
+        <v>0.503272422151781</v>
       </c>
       <c r="J507">
-        <v>-0.2755370274803244</v>
+        <v>-0.2772701845981717</v>
       </c>
       <c r="K507">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L507">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M507">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N507">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O507">
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="508" spans="1:16">
       <c r="A508" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B508" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C508">
-        <v>3.489219616823635</v>
+        <v>2.483803138304734</v>
       </c>
       <c r="D508" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E508">
-        <v>2.846867581602373</v>
+        <v>2.934421284350405</v>
       </c>
       <c r="F508">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G508">
-        <v>0.002750780383176366</v>
+        <v>0.001916196861695266</v>
       </c>
       <c r="H508">
-        <v>0.002213132418397626</v>
+        <v>0.002245578715649595</v>
       </c>
       <c r="I508">
-        <v>0.6423520352212617</v>
+        <v>0.4506181460456711</v>
       </c>
       <c r="J508">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K508">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L508">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M508">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N508">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O508">
         <v>1</v>
@@ -26820,13 +26820,13 @@
     </row>
     <row r="509" spans="1:16">
       <c r="A509" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B509" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C509">
-        <v>3.349932024900012</v>
+        <v>3.489219616823635</v>
       </c>
       <c r="D509" t="s">
         <v>133</v>
@@ -26838,22 +26838,22 @@
         <v>-1</v>
       </c>
       <c r="G509">
-        <v>0.002650067975099988</v>
+        <v>0.002750780383176366</v>
       </c>
       <c r="H509">
         <v>0.002213132418397626</v>
       </c>
       <c r="I509">
-        <v>0.5030644432976388</v>
+        <v>0.6423520352212617</v>
       </c>
       <c r="J509">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K509">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L509">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M509">
         <v>1.15</v>
@@ -26870,96 +26870,96 @@
     </row>
     <row r="510" spans="1:16">
       <c r="A510" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B510" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C510">
-        <v>2.455324757264537</v>
+        <v>3.349932024900012</v>
       </c>
       <c r="D510" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E510">
-        <v>2.899860142311331</v>
+        <v>2.846867581602373</v>
       </c>
       <c r="F510">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G510">
-        <v>0.001944675242735464</v>
+        <v>0.002650067975099988</v>
       </c>
       <c r="H510">
-        <v>0.002280139857688669</v>
+        <v>0.002213132418397626</v>
       </c>
       <c r="I510">
-        <v>0.4445353850467941</v>
+        <v>0.5030644432976388</v>
       </c>
       <c r="J510">
-        <v>-0.2478881138490649</v>
+        <v>-0.2755370274803244</v>
       </c>
       <c r="K510">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L510">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M510">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N510">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O510">
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="511" spans="1:16">
       <c r="A511" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B511" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C511">
-        <v>3.452170072557747</v>
+        <v>2.455324757264537</v>
       </c>
       <c r="D511" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E511">
-        <v>2.815071330926425</v>
+        <v>2.899860142311331</v>
       </c>
       <c r="F511">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G511">
-        <v>0.002787829927442253</v>
+        <v>0.001944675242735464</v>
       </c>
       <c r="H511">
-        <v>0.002244928669073575</v>
+        <v>0.002280139857688669</v>
       </c>
       <c r="I511">
-        <v>0.6370987416313225</v>
+        <v>0.4445353850467941</v>
       </c>
       <c r="J511">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K511">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L511">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M511">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N511">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O511">
         <v>1</v>
@@ -26970,13 +26970,13 @@
     </row>
     <row r="512" spans="1:16">
       <c r="A512" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B512" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C512">
-        <v>3.314817904588312</v>
+        <v>3.452170072557747</v>
       </c>
       <c r="D512" t="s">
         <v>133</v>
@@ -26988,22 +26988,22 @@
         <v>-1</v>
       </c>
       <c r="G512">
-        <v>0.002685182095411688</v>
+        <v>0.002787829927442253</v>
       </c>
       <c r="H512">
         <v>0.002244928669073575</v>
       </c>
       <c r="I512">
-        <v>0.4997465736618878</v>
+        <v>0.6370987416313225</v>
       </c>
       <c r="J512">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K512">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L512">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M512">
         <v>1.15</v>
@@ -27020,96 +27020,96 @@
     </row>
     <row r="513" spans="1:16">
       <c r="A513" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B513" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C513">
-        <v>2.38683909149</v>
+        <v>3.314817904588312</v>
       </c>
       <c r="D513" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E513">
-        <v>2.816746470254853</v>
+        <v>2.815071330926425</v>
       </c>
       <c r="F513">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G513">
-        <v>0.002013160908510001</v>
+        <v>0.002685182095411688</v>
       </c>
       <c r="H513">
-        <v>0.002363253529745146</v>
+        <v>0.002244928669073575</v>
       </c>
       <c r="I513">
-        <v>0.4299073787648537</v>
+        <v>0.4997465736618878</v>
       </c>
       <c r="J513">
-        <v>-0.181397176203883</v>
+        <v>-0.2478881138490649</v>
       </c>
       <c r="K513">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L513">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M513">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N513">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O513">
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="514" spans="1:16">
       <c r="A514" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B514" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C514">
-        <v>3.363072216113203</v>
+        <v>2.38683909149</v>
       </c>
       <c r="D514" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E514">
-        <v>2.738606752634465</v>
+        <v>2.816746470254853</v>
       </c>
       <c r="F514">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G514">
-        <v>0.002876927783886797</v>
+        <v>0.002013160908510001</v>
       </c>
       <c r="H514">
-        <v>0.002321393247365534</v>
+        <v>0.002363253529745146</v>
       </c>
       <c r="I514">
-        <v>0.6244654634787379</v>
+        <v>0.4299073787648537</v>
       </c>
       <c r="J514">
         <v>-0.181397176203883</v>
       </c>
       <c r="K514">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L514">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M514">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N514">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O514">
         <v>1</v>
@@ -27120,13 +27120,13 @@
     </row>
     <row r="515" spans="1:16">
       <c r="A515" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B515" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C515">
-        <v>3.230374413778931</v>
+        <v>3.363072216113203</v>
       </c>
       <c r="D515" t="s">
         <v>133</v>
@@ -27138,22 +27138,22 @@
         <v>-1</v>
       </c>
       <c r="G515">
-        <v>0.002769625586221069</v>
+        <v>0.002876927783886797</v>
       </c>
       <c r="H515">
         <v>0.002321393247365534</v>
       </c>
       <c r="I515">
-        <v>0.4917676611444661</v>
+        <v>0.6244654634787379</v>
       </c>
       <c r="J515">
         <v>-0.181397176203883</v>
       </c>
       <c r="K515">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L515">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M515">
         <v>1.15</v>
@@ -27170,40 +27170,40 @@
     </row>
     <row r="516" spans="1:16">
       <c r="A516" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B516" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C516">
-        <v>3.29280938304307</v>
+        <v>3.230374413778931</v>
       </c>
       <c r="D516" t="s">
         <v>133</v>
       </c>
       <c r="E516">
-        <v>2.678306560074276</v>
+        <v>2.738606752634465</v>
       </c>
       <c r="F516">
         <v>-1</v>
       </c>
       <c r="G516">
-        <v>0.00294719061695693</v>
+        <v>0.002769625586221069</v>
       </c>
       <c r="H516">
-        <v>0.002381693439925723</v>
+        <v>0.002321393247365534</v>
       </c>
       <c r="I516">
-        <v>0.6145028229687939</v>
+        <v>0.4917676611444661</v>
       </c>
       <c r="J516">
-        <v>-0.1289622261515449</v>
+        <v>-0.181397176203883</v>
       </c>
       <c r="K516">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L516">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M516">
         <v>1.15</v>
@@ -27215,51 +27215,51 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="517" spans="1:16">
       <c r="A517" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B517" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C517">
-        <v>3.163782027212462</v>
+        <v>2.332831092936091</v>
       </c>
       <c r="D517" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E517">
-        <v>2.678306560074276</v>
+        <v>2.751202782689431</v>
       </c>
       <c r="F517">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G517">
-        <v>0.002836217972787538</v>
+        <v>0.002067168907063909</v>
       </c>
       <c r="H517">
-        <v>0.002381693439925723</v>
+        <v>0.002428797217310569</v>
       </c>
       <c r="I517">
-        <v>0.4854754671381856</v>
+        <v>0.4183716897533394</v>
       </c>
       <c r="J517">
         <v>-0.1289622261515449</v>
       </c>
       <c r="K517">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L517">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M517">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N517">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O517">
         <v>1</v>
@@ -27270,34 +27270,34 @@
     </row>
     <row r="518" spans="1:16">
       <c r="A518" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B518" t="s">
         <v>53</v>
       </c>
       <c r="C518">
-        <v>3.240624211223998</v>
+        <v>3.29280938304307</v>
       </c>
       <c r="D518" t="s">
         <v>133</v>
       </c>
       <c r="E518">
-        <v>2.633520778289252</v>
+        <v>2.678306560074276</v>
       </c>
       <c r="F518">
         <v>-1</v>
       </c>
       <c r="G518">
-        <v>0.002999375788776002</v>
+        <v>0.00294719061695693</v>
       </c>
       <c r="H518">
-        <v>0.002426479221710748</v>
+        <v>0.002381693439925723</v>
       </c>
       <c r="I518">
-        <v>0.6071034329347462</v>
+        <v>0.6145028229687939</v>
       </c>
       <c r="J518">
-        <v>-0.09001806807761016</v>
+        <v>-0.1289622261515449</v>
       </c>
       <c r="K518">
         <v>1.34</v>
@@ -27315,39 +27315,39 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="519" spans="1:16">
       <c r="A519" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B519" t="s">
         <v>54</v>
       </c>
       <c r="C519">
-        <v>3.114322946458565</v>
+        <v>3.163782027212462</v>
       </c>
       <c r="D519" t="s">
         <v>133</v>
       </c>
       <c r="E519">
-        <v>2.633520778289252</v>
+        <v>2.678306560074276</v>
       </c>
       <c r="F519">
         <v>-1</v>
       </c>
       <c r="G519">
-        <v>0.002885677053541435</v>
+        <v>0.002836217972787538</v>
       </c>
       <c r="H519">
-        <v>0.002426479221710748</v>
+        <v>0.002381693439925723</v>
       </c>
       <c r="I519">
-        <v>0.4808021681693133</v>
+        <v>0.4854754671381856</v>
       </c>
       <c r="J519">
-        <v>-0.09001806807761016</v>
+        <v>-0.1289622261515449</v>
       </c>
       <c r="K519">
         <v>1.27</v>
@@ -27365,7 +27365,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27373,49 +27373,49 @@
         <v>0</v>
       </c>
       <c r="B520" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C520">
-        <v>3.108090425020327</v>
+        <v>2.292718610119939</v>
       </c>
       <c r="D520" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E520">
-        <v>2.519779096099534</v>
+        <v>2.702522585097013</v>
       </c>
       <c r="F520">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G520">
-        <v>0.003131909574979673</v>
+        <v>0.002107281389880062</v>
       </c>
       <c r="H520">
-        <v>0.002540220903900465</v>
+        <v>0.002477477414902987</v>
       </c>
       <c r="I520">
-        <v>0.5883113289207929</v>
+        <v>0.4098039749770739</v>
       </c>
       <c r="J520">
-        <v>0.008887742522143843</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K520">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L520">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M520">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N520">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O520">
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27423,37 +27423,37 @@
         <v>1</v>
       </c>
       <c r="B521" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C521">
-        <v>2.988712566996877</v>
+        <v>3.240624211223998</v>
       </c>
       <c r="D521" t="s">
         <v>133</v>
       </c>
       <c r="E521">
-        <v>2.519779096099534</v>
+        <v>2.633520778289252</v>
       </c>
       <c r="F521">
         <v>-1</v>
       </c>
       <c r="G521">
-        <v>0.003011287433003123</v>
+        <v>0.002999375788776002</v>
       </c>
       <c r="H521">
-        <v>0.002540220903900465</v>
+        <v>0.002426479221710748</v>
       </c>
       <c r="I521">
-        <v>0.4689334708973432</v>
+        <v>0.6071034329347462</v>
       </c>
       <c r="J521">
-        <v>0.008887742522143843</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K521">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L521">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M521">
         <v>1.15</v>
@@ -27465,45 +27465,45 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="522" spans="1:16">
       <c r="A522" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B522" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C522">
-        <v>3.056640151974971</v>
+        <v>3.114322946458565</v>
       </c>
       <c r="D522" t="s">
         <v>133</v>
       </c>
       <c r="E522">
-        <v>2.475624011023295</v>
+        <v>2.633520778289252</v>
       </c>
       <c r="F522">
         <v>-1</v>
       </c>
       <c r="G522">
-        <v>0.00318335984802503</v>
+        <v>0.002885677053541435</v>
       </c>
       <c r="H522">
-        <v>0.002584375988976704</v>
+        <v>0.002426479221710748</v>
       </c>
       <c r="I522">
-        <v>0.5810161409516752</v>
+        <v>0.4808021681693133</v>
       </c>
       <c r="J522">
-        <v>0.04728346867539508</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K522">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L522">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M522">
         <v>1.15</v>
@@ -27515,45 +27515,45 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="523" spans="1:16">
       <c r="A523" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B523" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C523">
-        <v>2.939949994782248</v>
+        <v>3.108090425020327</v>
       </c>
       <c r="D523" t="s">
         <v>133</v>
       </c>
       <c r="E523">
-        <v>2.475624011023295</v>
+        <v>2.519779096099534</v>
       </c>
       <c r="F523">
         <v>-1</v>
       </c>
       <c r="G523">
-        <v>0.003060050005217752</v>
+        <v>0.003131909574979673</v>
       </c>
       <c r="H523">
-        <v>0.002584375988976704</v>
+        <v>0.002540220903900465</v>
       </c>
       <c r="I523">
-        <v>0.4643259837589526</v>
+        <v>0.5883113289207929</v>
       </c>
       <c r="J523">
-        <v>0.04728346867539508</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K523">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L523">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M523">
         <v>1.15</v>
@@ -27565,45 +27565,45 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="524" spans="1:16">
       <c r="A524" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B524" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C524">
-        <v>3.02860014354532</v>
+        <v>2.988712566996877</v>
       </c>
       <c r="D524" t="s">
         <v>133</v>
       </c>
       <c r="E524">
-        <v>2.451559824684416</v>
+        <v>2.519779096099534</v>
       </c>
       <c r="F524">
         <v>-1</v>
       </c>
       <c r="G524">
-        <v>0.00321139985645468</v>
+        <v>0.003011287433003123</v>
       </c>
       <c r="H524">
-        <v>0.002608440175315583</v>
+        <v>0.002540220903900465</v>
       </c>
       <c r="I524">
-        <v>0.5770403188609037</v>
+        <v>0.4689334708973432</v>
       </c>
       <c r="J524">
-        <v>0.06820884810050738</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K524">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L524">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M524">
         <v>1.15</v>
@@ -27615,45 +27615,45 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="525" spans="1:16">
       <c r="A525" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B525" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C525">
-        <v>2.913374762912356</v>
+        <v>3.056640151974971</v>
       </c>
       <c r="D525" t="s">
         <v>133</v>
       </c>
       <c r="E525">
-        <v>2.451559824684416</v>
+        <v>2.475624011023295</v>
       </c>
       <c r="F525">
         <v>-1</v>
       </c>
       <c r="G525">
-        <v>0.003086625237087645</v>
+        <v>0.00318335984802503</v>
       </c>
       <c r="H525">
-        <v>0.002608440175315583</v>
+        <v>0.002584375988976704</v>
       </c>
       <c r="I525">
-        <v>0.4618149382279393</v>
+        <v>0.5810161409516752</v>
       </c>
       <c r="J525">
-        <v>0.06820884810050738</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K525">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L525">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M525">
         <v>1.15</v>
@@ -27665,45 +27665,45 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="526" spans="1:16">
       <c r="A526" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B526" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C526">
-        <v>3.020596707186351</v>
+        <v>2.939949994782248</v>
       </c>
       <c r="D526" t="s">
         <v>133</v>
       </c>
       <c r="E526">
-        <v>2.444691203928584</v>
+        <v>2.475624011023295</v>
       </c>
       <c r="F526">
         <v>-1</v>
       </c>
       <c r="G526">
-        <v>0.00321940329281365</v>
+        <v>0.003060050005217752</v>
       </c>
       <c r="H526">
-        <v>0.002615308796071415</v>
+        <v>0.002584375988976704</v>
       </c>
       <c r="I526">
-        <v>0.5759055032577662</v>
+        <v>0.4643259837589526</v>
       </c>
       <c r="J526">
-        <v>0.07418156180123091</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K526">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L526">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M526">
         <v>1.15</v>
@@ -27715,45 +27715,45 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="527" spans="1:16">
       <c r="A527" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B527" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C527">
-        <v>2.905789416512437</v>
+        <v>3.02860014354532</v>
       </c>
       <c r="D527" t="s">
         <v>133</v>
       </c>
       <c r="E527">
-        <v>2.444691203928584</v>
+        <v>2.451559824684416</v>
       </c>
       <c r="F527">
         <v>-1</v>
       </c>
       <c r="G527">
-        <v>0.003094210583487563</v>
+        <v>0.00321139985645468</v>
       </c>
       <c r="H527">
-        <v>0.002615308796071415</v>
+        <v>0.002608440175315583</v>
       </c>
       <c r="I527">
-        <v>0.4610982125838525</v>
+        <v>0.5770403188609037</v>
       </c>
       <c r="J527">
-        <v>0.07418156180123091</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K527">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L527">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M527">
         <v>1.15</v>
@@ -27765,45 +27765,45 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="528" spans="1:16">
       <c r="A528" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B528" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C528">
-        <v>3.071861218252691</v>
+        <v>2.913374762912356</v>
       </c>
       <c r="D528" t="s">
         <v>133</v>
       </c>
       <c r="E528">
-        <v>2.488686866410891</v>
+        <v>2.451559824684416</v>
       </c>
       <c r="F528">
         <v>-1</v>
       </c>
       <c r="G528">
-        <v>0.00316813878174731</v>
+        <v>0.003086625237087645</v>
       </c>
       <c r="H528">
-        <v>0.002571313133589109</v>
+        <v>0.002608440175315583</v>
       </c>
       <c r="I528">
-        <v>0.5831743518417998</v>
+        <v>0.4618149382279393</v>
       </c>
       <c r="J528">
-        <v>0.03592446399052947</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K528">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L528">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M528">
         <v>1.15</v>
@@ -27815,45 +27815,45 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="529" spans="1:16">
       <c r="A529" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B529" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C529">
-        <v>2.954375930732028</v>
+        <v>3.020596707186351</v>
       </c>
       <c r="D529" t="s">
         <v>133</v>
       </c>
       <c r="E529">
-        <v>2.488686866410891</v>
+        <v>2.444691203928584</v>
       </c>
       <c r="F529">
         <v>-1</v>
       </c>
       <c r="G529">
-        <v>0.003045624069267972</v>
+        <v>0.00321940329281365</v>
       </c>
       <c r="H529">
-        <v>0.002571313133589109</v>
+        <v>0.002615308796071415</v>
       </c>
       <c r="I529">
-        <v>0.4656890643211367</v>
+        <v>0.5759055032577662</v>
       </c>
       <c r="J529">
-        <v>0.03592446399052947</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K529">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L529">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M529">
         <v>1.15</v>
@@ -27865,45 +27865,45 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="530" spans="1:16">
       <c r="A530" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B530" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C530">
-        <v>3.057789944024353</v>
+        <v>2.905789416512437</v>
       </c>
       <c r="D530" t="s">
         <v>133</v>
       </c>
       <c r="E530">
-        <v>2.47661077285672</v>
+        <v>2.444691203928584</v>
       </c>
       <c r="F530">
         <v>-1</v>
       </c>
       <c r="G530">
-        <v>0.003182210055975647</v>
+        <v>0.003094210583487563</v>
       </c>
       <c r="H530">
-        <v>0.002583389227143279</v>
+        <v>0.002615308796071415</v>
       </c>
       <c r="I530">
-        <v>0.5811791711676326</v>
+        <v>0.4610982125838525</v>
       </c>
       <c r="J530">
-        <v>0.04642541490719935</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K530">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L530">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M530">
         <v>1.15</v>
@@ -27915,45 +27915,45 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="531" spans="1:16">
       <c r="A531" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B531" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C531">
-        <v>2.941039723067857</v>
+        <v>3.071861218252691</v>
       </c>
       <c r="D531" t="s">
         <v>133</v>
       </c>
       <c r="E531">
-        <v>2.47661077285672</v>
+        <v>2.488686866410891</v>
       </c>
       <c r="F531">
         <v>-1</v>
       </c>
       <c r="G531">
-        <v>0.003058960276932143</v>
+        <v>0.00316813878174731</v>
       </c>
       <c r="H531">
-        <v>0.002583389227143279</v>
+        <v>0.002571313133589109</v>
       </c>
       <c r="I531">
-        <v>0.4644289502111363</v>
+        <v>0.5831743518417998</v>
       </c>
       <c r="J531">
-        <v>0.04642541490719935</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K531">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L531">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M531">
         <v>1.15</v>
@@ -27965,89 +27965,89 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="532" spans="1:16">
       <c r="A532" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B532" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C532">
-        <v>2.132867933343715</v>
+        <v>2.954375930732028</v>
       </c>
       <c r="D532" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E532">
-        <v>2.508529045320043</v>
+        <v>2.488686866410891</v>
       </c>
       <c r="F532">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G532">
-        <v>0.002267132066656285</v>
+        <v>0.003045624069267972</v>
       </c>
       <c r="H532">
-        <v>0.002671470954679957</v>
+        <v>0.002571313133589109</v>
       </c>
       <c r="I532">
-        <v>0.3756611119763273</v>
+        <v>0.4656890643211367</v>
       </c>
       <c r="J532">
-        <v>0.06517676374396589</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K532">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L532">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M532">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N532">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O532">
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="533" spans="1:16">
       <c r="A533" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B533" t="s">
         <v>53</v>
       </c>
       <c r="C533">
-        <v>3.032663136583086</v>
+        <v>3.057789944024353</v>
       </c>
       <c r="D533" t="s">
         <v>133</v>
       </c>
       <c r="E533">
-        <v>2.455046721694439</v>
+        <v>2.47661077285672</v>
       </c>
       <c r="F533">
         <v>-1</v>
       </c>
       <c r="G533">
-        <v>0.003207336863416915</v>
+        <v>0.003182210055975647</v>
       </c>
       <c r="H533">
-        <v>0.002604953278305561</v>
+        <v>0.002583389227143279</v>
       </c>
       <c r="I533">
-        <v>0.5776164148886465</v>
+        <v>0.5811791711676326</v>
       </c>
       <c r="J533">
-        <v>0.06517676374396589</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K533">
         <v>1.34</v>
@@ -28065,39 +28065,39 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="534" spans="1:16">
       <c r="A534" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B534" t="s">
         <v>54</v>
       </c>
       <c r="C534">
-        <v>2.917225510045163</v>
+        <v>2.941039723067857</v>
       </c>
       <c r="D534" t="s">
         <v>133</v>
       </c>
       <c r="E534">
-        <v>2.455046721694439</v>
+        <v>2.47661077285672</v>
       </c>
       <c r="F534">
         <v>-1</v>
       </c>
       <c r="G534">
-        <v>0.003082774489954837</v>
+        <v>0.003058960276932143</v>
       </c>
       <c r="H534">
-        <v>0.002604953278305561</v>
+        <v>0.002583389227143279</v>
       </c>
       <c r="I534">
-        <v>0.462178788350724</v>
+        <v>0.4644289502111363</v>
       </c>
       <c r="J534">
-        <v>0.06517676374396589</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K534">
         <v>1.27</v>
@@ -28115,7 +28115,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28126,28 +28126,28 @@
         <v>55</v>
       </c>
       <c r="C535">
-        <v>2.104641124313295</v>
+        <v>2.132867933343715</v>
       </c>
       <c r="D535" t="s">
         <v>134</v>
       </c>
       <c r="E535">
-        <v>2.474273209118076</v>
+        <v>2.508529045320043</v>
       </c>
       <c r="F535">
         <v>1</v>
       </c>
       <c r="G535">
-        <v>0.002295358875686706</v>
+        <v>0.002267132066656285</v>
       </c>
       <c r="H535">
-        <v>0.002705726790881924</v>
+        <v>0.002671470954679957</v>
       </c>
       <c r="I535">
-        <v>0.3696320848047812</v>
+        <v>0.3756611119763273</v>
       </c>
       <c r="J535">
-        <v>0.09258143270553931</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K535">
         <v>1.03</v>
@@ -28165,7 +28165,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28176,28 +28176,28 @@
         <v>53</v>
       </c>
       <c r="C536">
-        <v>2.995940880174577</v>
+        <v>3.032663136583086</v>
       </c>
       <c r="D536" t="s">
         <v>133</v>
       </c>
       <c r="E536">
-        <v>2.423531352388629</v>
+        <v>2.455046721694439</v>
       </c>
       <c r="F536">
         <v>-1</v>
       </c>
       <c r="G536">
-        <v>0.003244059119825423</v>
+        <v>0.003207336863416915</v>
       </c>
       <c r="H536">
-        <v>0.00263646864761137</v>
+        <v>0.002604953278305561</v>
       </c>
       <c r="I536">
-        <v>0.5724095277859478</v>
+        <v>0.5776164148886465</v>
       </c>
       <c r="J536">
-        <v>0.09258143270553931</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K536">
         <v>1.34</v>
@@ -28215,7 +28215,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28226,28 +28226,28 @@
         <v>54</v>
       </c>
       <c r="C537">
-        <v>2.882421580463965</v>
+        <v>2.917225510045163</v>
       </c>
       <c r="D537" t="s">
         <v>133</v>
       </c>
       <c r="E537">
-        <v>2.423531352388629</v>
+        <v>2.455046721694439</v>
       </c>
       <c r="F537">
         <v>-1</v>
       </c>
       <c r="G537">
-        <v>0.003117578419536035</v>
+        <v>0.003082774489954837</v>
       </c>
       <c r="H537">
-        <v>0.00263646864761137</v>
+        <v>0.002604953278305561</v>
       </c>
       <c r="I537">
-        <v>0.4588902280753357</v>
+        <v>0.462178788350724</v>
       </c>
       <c r="J537">
-        <v>0.09258143270553931</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K537">
         <v>1.27</v>
@@ -28265,7 +28265,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28276,28 +28276,28 @@
         <v>55</v>
       </c>
       <c r="C538">
-        <v>2.097453766817889</v>
+        <v>2.104641124313295</v>
       </c>
       <c r="D538" t="s">
         <v>134</v>
       </c>
       <c r="E538">
-        <v>2.465550687885787</v>
+        <v>2.474273209118076</v>
       </c>
       <c r="F538">
         <v>1</v>
       </c>
       <c r="G538">
-        <v>0.002302546233182111</v>
+        <v>0.002295358875686706</v>
       </c>
       <c r="H538">
-        <v>0.002714449312114212</v>
+        <v>0.002705726790881924</v>
       </c>
       <c r="I538">
-        <v>0.3680969210678979</v>
+        <v>0.3696320848047812</v>
       </c>
       <c r="J538">
-        <v>0.09955944969136986</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K538">
         <v>1.03</v>
@@ -28315,7 +28315,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28326,28 +28326,28 @@
         <v>53</v>
       </c>
       <c r="C539">
-        <v>2.986590337413564</v>
+        <v>2.995940880174577</v>
       </c>
       <c r="D539" t="s">
         <v>133</v>
       </c>
       <c r="E539">
-        <v>2.415506632854925</v>
+        <v>2.423531352388629</v>
       </c>
       <c r="F539">
         <v>-1</v>
       </c>
       <c r="G539">
-        <v>0.003253409662586436</v>
+        <v>0.003244059119825423</v>
       </c>
       <c r="H539">
-        <v>0.002644493367145075</v>
+        <v>0.00263646864761137</v>
       </c>
       <c r="I539">
-        <v>0.5710837045586397</v>
+        <v>0.5724095277859478</v>
       </c>
       <c r="J539">
-        <v>0.09955944969136986</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K539">
         <v>1.34</v>
@@ -28365,7 +28365,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28376,28 +28376,28 @@
         <v>54</v>
       </c>
       <c r="C540">
-        <v>2.87355949889196</v>
+        <v>2.882421580463965</v>
       </c>
       <c r="D540" t="s">
         <v>133</v>
       </c>
       <c r="E540">
-        <v>2.415506632854925</v>
+        <v>2.423531352388629</v>
       </c>
       <c r="F540">
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.003126440501108039</v>
+        <v>0.003117578419536035</v>
       </c>
       <c r="H540">
-        <v>0.002644493367145075</v>
+        <v>0.00263646864761137</v>
       </c>
       <c r="I540">
-        <v>0.4580528660370358</v>
+        <v>0.4588902280753357</v>
       </c>
       <c r="J540">
-        <v>0.09955944969136986</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K540">
         <v>1.27</v>
@@ -28415,7 +28415,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28426,28 +28426,28 @@
         <v>55</v>
       </c>
       <c r="C541">
-        <v>2.089309945208396</v>
+        <v>2.097453766817889</v>
       </c>
       <c r="D541" t="s">
         <v>134</v>
       </c>
       <c r="E541">
-        <v>2.45566740923349</v>
+        <v>2.465550687885787</v>
       </c>
       <c r="F541">
         <v>1</v>
       </c>
       <c r="G541">
-        <v>0.002310690054791604</v>
+        <v>0.002302546233182111</v>
       </c>
       <c r="H541">
-        <v>0.00272433259076651</v>
+        <v>0.002714449312114212</v>
       </c>
       <c r="I541">
-        <v>0.3663574640250937</v>
+        <v>0.3680969210678979</v>
       </c>
       <c r="J541">
-        <v>0.1074660726132081</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K541">
         <v>1.03</v>
@@ -28465,7 +28465,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28476,28 +28476,28 @@
         <v>53</v>
       </c>
       <c r="C542">
-        <v>2.975995462698301</v>
+        <v>2.986590337413564</v>
       </c>
       <c r="D542" t="s">
         <v>133</v>
       </c>
       <c r="E542">
-        <v>2.406414016494811</v>
+        <v>2.415506632854925</v>
       </c>
       <c r="F542">
         <v>-1</v>
       </c>
       <c r="G542">
-        <v>0.003264004537301699</v>
+        <v>0.003253409662586436</v>
       </c>
       <c r="H542">
-        <v>0.002653585983505189</v>
+        <v>0.002644493367145075</v>
       </c>
       <c r="I542">
-        <v>0.5695814462034905</v>
+        <v>0.5710837045586397</v>
       </c>
       <c r="J542">
-        <v>0.1074660726132081</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K542">
         <v>1.34</v>
@@ -28515,7 +28515,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28526,28 +28526,28 @@
         <v>54</v>
       </c>
       <c r="C543">
-        <v>2.863518087781226</v>
+        <v>2.87355949889196</v>
       </c>
       <c r="D543" t="s">
         <v>133</v>
       </c>
       <c r="E543">
-        <v>2.406414016494811</v>
+        <v>2.415506632854925</v>
       </c>
       <c r="F543">
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.003136481912218774</v>
+        <v>0.003126440501108039</v>
       </c>
       <c r="H543">
-        <v>0.002653585983505189</v>
+        <v>0.002644493367145075</v>
       </c>
       <c r="I543">
-        <v>0.4571040712864152</v>
+        <v>0.4580528660370358</v>
       </c>
       <c r="J543">
-        <v>0.1074660726132081</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K543">
         <v>1.27</v>
@@ -28565,7 +28565,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28576,28 +28576,28 @@
         <v>55</v>
       </c>
       <c r="C544">
-        <v>2.094107820370248</v>
+        <v>2.089309945208396</v>
       </c>
       <c r="D544" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E544">
-        <v>2.514574311506508</v>
+        <v>2.45566740923349</v>
       </c>
       <c r="F544">
         <v>1</v>
       </c>
       <c r="G544">
-        <v>0.002305892179629752</v>
+        <v>0.002310690054791604</v>
       </c>
       <c r="H544">
-        <v>0.002765425688493492</v>
+        <v>0.00272433259076651</v>
       </c>
       <c r="I544">
-        <v>0.4204664911362594</v>
+        <v>0.3663574640250937</v>
       </c>
       <c r="J544">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K544">
         <v>1.03</v>
@@ -28606,16 +28606,16 @@
         <v>2.2</v>
       </c>
       <c r="M544">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="N544">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28626,28 +28626,28 @@
         <v>53</v>
       </c>
       <c r="C545">
-        <v>2.982237358539935</v>
+        <v>2.975995462698301</v>
       </c>
       <c r="D545" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E545">
-        <v>2.459714708575913</v>
+        <v>2.406414016494811</v>
       </c>
       <c r="F545">
         <v>-1</v>
       </c>
       <c r="G545">
-        <v>0.003257762641460066</v>
+        <v>0.003264004537301699</v>
       </c>
       <c r="H545">
-        <v>0.002700285291424087</v>
+        <v>0.002653585983505189</v>
       </c>
       <c r="I545">
-        <v>0.5225226499640216</v>
+        <v>0.5695814462034905</v>
       </c>
       <c r="J545">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K545">
         <v>1.34</v>
@@ -28656,16 +28656,16 @@
         <v>3.12</v>
       </c>
       <c r="M545">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="N545">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28676,28 +28676,28 @@
         <v>54</v>
       </c>
       <c r="C546">
-        <v>2.869433914437102</v>
+        <v>2.863518087781226</v>
       </c>
       <c r="D546" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E546">
-        <v>2.459714708575913</v>
+        <v>2.406414016494811</v>
       </c>
       <c r="F546">
         <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.003130566085562898</v>
+        <v>0.003136481912218774</v>
       </c>
       <c r="H546">
-        <v>0.002700285291424087</v>
+        <v>0.002653585983505189</v>
       </c>
       <c r="I546">
-        <v>0.4097192058611889</v>
+        <v>0.4571040712864152</v>
       </c>
       <c r="J546">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K546">
         <v>1.27</v>
@@ -28706,16 +28706,16 @@
         <v>3</v>
       </c>
       <c r="M546">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="N546">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="O546">
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28726,28 +28726,28 @@
         <v>55</v>
       </c>
       <c r="C547">
-        <v>2.084743195682537</v>
+        <v>2.094107820370248</v>
       </c>
       <c r="D547" t="s">
         <v>135</v>
       </c>
       <c r="E547">
-        <v>2.503482231779316</v>
+        <v>2.514574311506508</v>
       </c>
       <c r="F547">
         <v>1</v>
       </c>
       <c r="G547">
-        <v>0.002315256804317463</v>
+        <v>0.002305892179629752</v>
       </c>
       <c r="H547">
-        <v>0.002776517768220685</v>
+        <v>0.002765425688493492</v>
       </c>
       <c r="I547">
-        <v>0.4187390360967784</v>
+        <v>0.4204664911362594</v>
       </c>
       <c r="J547">
-        <v>0.1118998100169543</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K547">
         <v>1.03</v>
@@ -28765,7 +28765,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28776,28 +28776,28 @@
         <v>53</v>
       </c>
       <c r="C548">
-        <v>2.970054254577281</v>
+        <v>2.982237358539935</v>
       </c>
       <c r="D548" t="s">
         <v>136</v>
       </c>
       <c r="E548">
-        <v>2.449077222280164</v>
+        <v>2.459714708575913</v>
       </c>
       <c r="F548">
         <v>-1</v>
       </c>
       <c r="G548">
-        <v>0.003269945745422719</v>
+        <v>0.003257762641460066</v>
       </c>
       <c r="H548">
-        <v>0.002710922777719837</v>
+        <v>0.002700285291424087</v>
       </c>
       <c r="I548">
-        <v>0.5209770322971177</v>
+        <v>0.5225226499640216</v>
       </c>
       <c r="J548">
-        <v>0.1118998100169543</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K548">
         <v>1.34</v>
@@ -28815,7 +28815,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28826,28 +28826,28 @@
         <v>54</v>
       </c>
       <c r="C549">
-        <v>2.857887241278468</v>
+        <v>2.869433914437102</v>
       </c>
       <c r="D549" t="s">
         <v>136</v>
       </c>
       <c r="E549">
-        <v>2.449077222280164</v>
+        <v>2.459714708575913</v>
       </c>
       <c r="F549">
         <v>-1</v>
       </c>
       <c r="G549">
-        <v>0.003142112758721532</v>
+        <v>0.003130566085562898</v>
       </c>
       <c r="H549">
-        <v>0.002710922777719837</v>
+        <v>0.002700285291424087</v>
       </c>
       <c r="I549">
-        <v>0.4088100189983046</v>
+        <v>0.4097192058611889</v>
       </c>
       <c r="J549">
-        <v>0.1118998100169543</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K549">
         <v>1.27</v>
@@ -28865,7 +28865,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28873,49 +28873,49 @@
         <v>0</v>
       </c>
       <c r="B550" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C550">
-        <v>2.944089643772313</v>
+        <v>2.084743195682537</v>
       </c>
       <c r="D550" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E550">
-        <v>2.426406629263886</v>
+        <v>2.503482231779316</v>
       </c>
       <c r="F550">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G550">
-        <v>0.003295910356227687</v>
+        <v>0.002315256804317463</v>
       </c>
       <c r="H550">
-        <v>0.002733593370736115</v>
+        <v>0.002776517768220685</v>
       </c>
       <c r="I550">
-        <v>0.5176830145084277</v>
+        <v>0.4187390360967784</v>
       </c>
       <c r="J550">
-        <v>0.1312763852445424</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K550">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L550">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M550">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N550">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O550">
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>55</v>
+        <v>341</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28923,37 +28923,37 @@
         <v>1</v>
       </c>
       <c r="B551" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C551">
-        <v>2.833278990739431</v>
+        <v>2.970054254577281</v>
       </c>
       <c r="D551" t="s">
         <v>136</v>
       </c>
       <c r="E551">
-        <v>2.426406629263886</v>
+        <v>2.449077222280164</v>
       </c>
       <c r="F551">
         <v>-1</v>
       </c>
       <c r="G551">
-        <v>0.003166721009260569</v>
+        <v>0.003269945745422719</v>
       </c>
       <c r="H551">
-        <v>0.002733593370736115</v>
+        <v>0.002710922777719837</v>
       </c>
       <c r="I551">
-        <v>0.4068723614755454</v>
+        <v>0.5209770322971177</v>
       </c>
       <c r="J551">
-        <v>0.1312763852445424</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K551">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L551">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M551">
         <v>1.17</v>
@@ -28965,89 +28965,89 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>55</v>
+        <v>341</v>
       </c>
     </row>
     <row r="552" spans="1:16">
       <c r="A552" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B552" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C552">
-        <v>2.063914340678486</v>
+        <v>2.857887241278468</v>
       </c>
       <c r="D552" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E552">
-        <v>2.437335373233729</v>
+        <v>2.449077222280164</v>
       </c>
       <c r="F552">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G552">
-        <v>0.002416085659321514</v>
+        <v>0.003142112758721532</v>
       </c>
       <c r="H552">
-        <v>0.002842664626766271</v>
+        <v>0.002710922777719837</v>
       </c>
       <c r="I552">
-        <v>0.3734210325552429</v>
+        <v>0.4088100189983046</v>
       </c>
       <c r="J552">
-        <v>0.16611854652973</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K552">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="L552">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="M552">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N552">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O552">
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="553" spans="1:16">
       <c r="A553" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B553" t="s">
         <v>53</v>
       </c>
       <c r="C553">
-        <v>2.897401147650162</v>
+        <v>2.944089643772313</v>
       </c>
       <c r="D553" t="s">
         <v>136</v>
       </c>
       <c r="E553">
-        <v>2.385641300560216</v>
+        <v>2.426406629263886</v>
       </c>
       <c r="F553">
         <v>-1</v>
       </c>
       <c r="G553">
-        <v>0.003342598852349839</v>
+        <v>0.003295910356227687</v>
       </c>
       <c r="H553">
-        <v>0.002774358699439784</v>
+        <v>0.002733593370736115</v>
       </c>
       <c r="I553">
-        <v>0.5117598470899458</v>
+        <v>0.5176830145084277</v>
       </c>
       <c r="J553">
-        <v>0.16611854652973</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K553">
         <v>1.34</v>
@@ -29065,39 +29065,39 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>342</v>
+        <v>55</v>
       </c>
     </row>
     <row r="554" spans="1:16">
       <c r="A554" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B554" t="s">
         <v>54</v>
       </c>
       <c r="C554">
-        <v>2.789029445907243</v>
+        <v>2.833278990739431</v>
       </c>
       <c r="D554" t="s">
         <v>136</v>
       </c>
       <c r="E554">
-        <v>2.385641300560216</v>
+        <v>2.426406629263886</v>
       </c>
       <c r="F554">
         <v>-1</v>
       </c>
       <c r="G554">
-        <v>0.003210970554092757</v>
+        <v>0.003166721009260569</v>
       </c>
       <c r="H554">
-        <v>0.002774358699439784</v>
+        <v>0.002733593370736115</v>
       </c>
       <c r="I554">
-        <v>0.4033881453470269</v>
+        <v>0.4068723614755454</v>
       </c>
       <c r="J554">
-        <v>0.16611854652973</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K554">
         <v>1.27</v>
@@ -29115,7 +29115,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>342</v>
+        <v>55</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29126,28 +29126,28 @@
         <v>56</v>
       </c>
       <c r="C555">
-        <v>2.014066208827843</v>
+        <v>2.063914340678486</v>
       </c>
       <c r="D555" t="s">
         <v>135</v>
       </c>
       <c r="E555">
-        <v>2.379962995066008</v>
+        <v>2.437335373233729</v>
       </c>
       <c r="F555">
         <v>1</v>
       </c>
       <c r="G555">
-        <v>0.002465933791172158</v>
+        <v>0.002416085659321514</v>
       </c>
       <c r="H555">
-        <v>0.002900037004933993</v>
+        <v>0.002842664626766271</v>
       </c>
       <c r="I555">
-        <v>0.365896786238165</v>
+        <v>0.3734210325552429</v>
       </c>
       <c r="J555">
-        <v>0.2131450860114693</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K555">
         <v>1.06</v>
@@ -29165,7 +29165,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29176,28 +29176,28 @@
         <v>53</v>
       </c>
       <c r="C556">
-        <v>2.834385584744631</v>
+        <v>2.897401147650162</v>
       </c>
       <c r="D556" t="s">
         <v>136</v>
       </c>
       <c r="E556">
-        <v>2.330620249366581</v>
+        <v>2.385641300560216</v>
       </c>
       <c r="F556">
         <v>-1</v>
       </c>
       <c r="G556">
-        <v>0.003405614415255369</v>
+        <v>0.003342598852349839</v>
       </c>
       <c r="H556">
-        <v>0.002829379750633419</v>
+        <v>0.002774358699439784</v>
       </c>
       <c r="I556">
-        <v>0.5037653353780502</v>
+        <v>0.5117598470899458</v>
       </c>
       <c r="J556">
-        <v>0.2131450860114693</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K556">
         <v>1.34</v>
@@ -29215,7 +29215,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29226,28 +29226,28 @@
         <v>54</v>
       </c>
       <c r="C557">
-        <v>2.729305740765434</v>
+        <v>2.789029445907243</v>
       </c>
       <c r="D557" t="s">
         <v>136</v>
       </c>
       <c r="E557">
-        <v>2.330620249366581</v>
+        <v>2.385641300560216</v>
       </c>
       <c r="F557">
         <v>-1</v>
       </c>
       <c r="G557">
-        <v>0.003270694259234566</v>
+        <v>0.003210970554092757</v>
       </c>
       <c r="H557">
-        <v>0.002829379750633419</v>
+        <v>0.002774358699439784</v>
       </c>
       <c r="I557">
-        <v>0.3986854913988531</v>
+        <v>0.4033881453470269</v>
       </c>
       <c r="J557">
-        <v>0.2131450860114693</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K557">
         <v>1.27</v>
@@ -29265,7 +29265,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29273,49 +29273,49 @@
         <v>0</v>
       </c>
       <c r="B558" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C558">
-        <v>2.710585509297514</v>
+        <v>2.014066208827843</v>
       </c>
       <c r="D558" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E558">
-        <v>2.222526153640366</v>
+        <v>2.379962995066008</v>
       </c>
       <c r="F558">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G558">
-        <v>0.003529414490702487</v>
+        <v>0.002465933791172158</v>
       </c>
       <c r="H558">
-        <v>0.002937473846359634</v>
+        <v>0.002900037004933993</v>
       </c>
       <c r="I558">
-        <v>0.4880593556571475</v>
+        <v>0.365896786238165</v>
       </c>
       <c r="J558">
-        <v>0.3055332020167811</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K558">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="L558">
-        <v>3.12</v>
+        <v>2.24</v>
       </c>
       <c r="M558">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N558">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O558">
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>56</v>
+        <v>343</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29323,37 +29323,37 @@
         <v>1</v>
       </c>
       <c r="B559" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C559">
-        <v>2.611972833438688</v>
+        <v>2.834385584744631</v>
       </c>
       <c r="D559" t="s">
         <v>136</v>
       </c>
       <c r="E559">
-        <v>2.222526153640366</v>
+        <v>2.330620249366581</v>
       </c>
       <c r="F559">
         <v>-1</v>
       </c>
       <c r="G559">
-        <v>0.003388027166561312</v>
+        <v>0.003405614415255369</v>
       </c>
       <c r="H559">
-        <v>0.002937473846359634</v>
+        <v>0.002829379750633419</v>
       </c>
       <c r="I559">
-        <v>0.389446679798322</v>
+        <v>0.5037653353780502</v>
       </c>
       <c r="J559">
-        <v>0.3055332020167811</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K559">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L559">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M559">
         <v>1.17</v>
@@ -29365,45 +29365,45 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>56</v>
+        <v>343</v>
       </c>
     </row>
     <row r="560" spans="1:16">
       <c r="A560" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B560" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C560">
-        <v>2.647551728558422</v>
+        <v>2.729305740765434</v>
       </c>
       <c r="D560" t="s">
         <v>136</v>
       </c>
       <c r="E560">
-        <v>2.167489195830861</v>
+        <v>2.330620249366581</v>
       </c>
       <c r="F560">
         <v>-1</v>
       </c>
       <c r="G560">
-        <v>0.003592448271441579</v>
+        <v>0.003270694259234566</v>
       </c>
       <c r="H560">
-        <v>0.00299251080416914</v>
+        <v>0.002829379750633419</v>
       </c>
       <c r="I560">
-        <v>0.4800625327275609</v>
+        <v>0.3986854913988531</v>
       </c>
       <c r="J560">
-        <v>0.3525733368967002</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K560">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L560">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M560">
         <v>1.17</v>
@@ -29415,45 +29415,45 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="561" spans="1:16">
       <c r="A561" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B561" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C561">
-        <v>2.552231862141191</v>
+        <v>2.710585509297514</v>
       </c>
       <c r="D561" t="s">
         <v>136</v>
       </c>
       <c r="E561">
-        <v>2.167489195830861</v>
+        <v>2.222526153640366</v>
       </c>
       <c r="F561">
         <v>-1</v>
       </c>
       <c r="G561">
-        <v>0.003447768137858809</v>
+        <v>0.003529414490702487</v>
       </c>
       <c r="H561">
-        <v>0.00299251080416914</v>
+        <v>0.002937473846359634</v>
       </c>
       <c r="I561">
-        <v>0.3847426663103302</v>
+        <v>0.4880593556571475</v>
       </c>
       <c r="J561">
-        <v>0.3525733368967002</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K561">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L561">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M561">
         <v>1.17</v>
@@ -29465,45 +29465,45 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>344</v>
+        <v>56</v>
       </c>
     </row>
     <row r="562" spans="1:16">
       <c r="A562" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B562" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C562">
-        <v>2.59897387935353</v>
+        <v>2.611972833438688</v>
       </c>
       <c r="D562" t="s">
         <v>136</v>
       </c>
       <c r="E562">
-        <v>2.125074208092261</v>
+        <v>2.222526153640366</v>
       </c>
       <c r="F562">
         <v>-1</v>
       </c>
       <c r="G562">
-        <v>0.003641026120646471</v>
+        <v>0.003388027166561312</v>
       </c>
       <c r="H562">
-        <v>0.003034925791907739</v>
+        <v>0.002937473846359634</v>
       </c>
       <c r="I562">
-        <v>0.4738996712612686</v>
+        <v>0.389446679798322</v>
       </c>
       <c r="J562">
-        <v>0.3888254631690077</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K562">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L562">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M562">
         <v>1.17</v>
@@ -29515,45 +29515,45 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>345</v>
+        <v>56</v>
       </c>
     </row>
     <row r="563" spans="1:16">
       <c r="A563" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B563" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C563">
-        <v>2.50619166177536</v>
+        <v>2.647551728558422</v>
       </c>
       <c r="D563" t="s">
         <v>136</v>
       </c>
       <c r="E563">
-        <v>2.125074208092261</v>
+        <v>2.167489195830861</v>
       </c>
       <c r="F563">
         <v>-1</v>
       </c>
       <c r="G563">
-        <v>0.00349380833822464</v>
+        <v>0.003592448271441579</v>
       </c>
       <c r="H563">
-        <v>0.003034925791907739</v>
+        <v>0.00299251080416914</v>
       </c>
       <c r="I563">
-        <v>0.3811174536830992</v>
+        <v>0.4800625327275609</v>
       </c>
       <c r="J563">
-        <v>0.3888254631690077</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K563">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L563">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M563">
         <v>1.17</v>
@@ -29565,306 +29565,456 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="564" spans="1:16">
       <c r="A564" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B564" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C564">
-        <v>2.575095597538799</v>
+        <v>2.552231862141191</v>
       </c>
       <c r="D564" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E564">
-        <v>2.633560752891249</v>
+        <v>2.167489195830861</v>
       </c>
       <c r="F564">
         <v>-1</v>
       </c>
       <c r="G564">
-        <v>0.003664904402461202</v>
+        <v>0.003447768137858809</v>
       </c>
       <c r="H564">
-        <v>0.003666439247108751</v>
+        <v>0.00299251080416914</v>
       </c>
       <c r="I564">
-        <v>-0.05846515535245045</v>
+        <v>0.3847426663103302</v>
       </c>
       <c r="J564">
-        <v>0.4066450764635833</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K564">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L564">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M564">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N564">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O564">
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="565" spans="1:16">
       <c r="A565" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B565" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C565">
-        <v>2.483560752891249</v>
+        <v>2.59897387935353</v>
       </c>
       <c r="D565" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E565">
-        <v>2.104225260537608</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="F565">
         <v>-1</v>
       </c>
       <c r="G565">
-        <v>0.003516439247108751</v>
+        <v>0.003641026120646471</v>
       </c>
       <c r="H565">
-        <v>0.003055774739462393</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="I565">
-        <v>0.3793354923536416</v>
+        <v>-0.05721778242183051</v>
       </c>
       <c r="J565">
-        <v>0.4066450764635833</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K565">
+        <v>1.34</v>
+      </c>
+      <c r="L565">
+        <v>3.12</v>
+      </c>
+      <c r="M565">
         <v>1.27</v>
       </c>
-      <c r="L565">
-        <v>3</v>
-      </c>
-      <c r="M565">
-        <v>1.17</v>
-      </c>
       <c r="N565">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O565">
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="566" spans="1:16">
       <c r="A566" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B566" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C566">
-        <v>2.513392232045375</v>
+        <v>2.50619166177536</v>
       </c>
       <c r="D566" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E566">
-        <v>2.575080697535542</v>
+        <v>2.125074208092261</v>
       </c>
       <c r="F566">
         <v>-1</v>
       </c>
       <c r="G566">
-        <v>0.003726607767954625</v>
+        <v>0.00349380833822464</v>
       </c>
       <c r="H566">
-        <v>0.003724919302464458</v>
+        <v>0.003034925791907739</v>
       </c>
       <c r="I566">
-        <v>-0.0616884654901666</v>
+        <v>0.3811174536830992</v>
       </c>
       <c r="J566">
-        <v>0.4526923641452424</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K566">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L566">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M566">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N566">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O566">
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="567" spans="1:16">
       <c r="A567" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B567" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C567">
-        <v>2.425080697535542</v>
+        <v>2.575095597538799</v>
       </c>
       <c r="D567" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E567">
-        <v>2.050349933950066</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="F567">
         <v>-1</v>
       </c>
       <c r="G567">
-        <v>0.003574919302464458</v>
+        <v>0.003664904402461202</v>
       </c>
       <c r="H567">
-        <v>0.003109650066049934</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="I567">
-        <v>0.3747307635854757</v>
+        <v>-0.05846515535245045</v>
       </c>
       <c r="J567">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K567">
+        <v>1.34</v>
+      </c>
+      <c r="L567">
+        <v>3.12</v>
+      </c>
+      <c r="M567">
         <v>1.27</v>
       </c>
-      <c r="L567">
-        <v>3</v>
-      </c>
-      <c r="M567">
-        <v>1.17</v>
-      </c>
       <c r="N567">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O567">
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="568" spans="1:16">
       <c r="A568" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B568" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C568">
-        <v>2.46037019732591</v>
+        <v>2.483560752891249</v>
       </c>
       <c r="D568" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E568">
-        <v>2.524828470599929</v>
+        <v>2.104225260537608</v>
       </c>
       <c r="F568">
         <v>-1</v>
       </c>
       <c r="G568">
-        <v>0.00377962980267409</v>
+        <v>0.003516439247108751</v>
       </c>
       <c r="H568">
-        <v>0.003775171529400071</v>
+        <v>0.003055774739462393</v>
       </c>
       <c r="I568">
-        <v>-0.0644582732740191</v>
+        <v>0.3793354923536416</v>
       </c>
       <c r="J568">
-        <v>0.4922610467717091</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K568">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L568">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M568">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N568">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O568">
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="569" spans="1:16">
       <c r="A569" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B569" t="s">
+        <v>53</v>
+      </c>
+      <c r="C569">
+        <v>2.513392232045375</v>
+      </c>
+      <c r="D569" t="s">
+        <v>137</v>
+      </c>
+      <c r="E569">
+        <v>2.575080697535542</v>
+      </c>
+      <c r="F569">
+        <v>-1</v>
+      </c>
+      <c r="G569">
+        <v>0.003726607767954625</v>
+      </c>
+      <c r="H569">
+        <v>0.003724919302464458</v>
+      </c>
+      <c r="I569">
+        <v>-0.0616884654901666</v>
+      </c>
+      <c r="J569">
+        <v>0.4526923641452424</v>
+      </c>
+      <c r="K569">
+        <v>1.34</v>
+      </c>
+      <c r="L569">
+        <v>3.12</v>
+      </c>
+      <c r="M569">
+        <v>1.27</v>
+      </c>
+      <c r="N569">
+        <v>3.15</v>
+      </c>
+      <c r="O569">
+        <v>1</v>
+      </c>
+      <c r="P569" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="570" spans="1:16">
+      <c r="A570" s="1">
+        <v>1</v>
+      </c>
+      <c r="B570" t="s">
         <v>54</v>
       </c>
-      <c r="C569">
+      <c r="C570">
+        <v>2.425080697535542</v>
+      </c>
+      <c r="D570" t="s">
+        <v>136</v>
+      </c>
+      <c r="E570">
+        <v>2.050349933950066</v>
+      </c>
+      <c r="F570">
+        <v>-1</v>
+      </c>
+      <c r="G570">
+        <v>0.003574919302464458</v>
+      </c>
+      <c r="H570">
+        <v>0.003109650066049934</v>
+      </c>
+      <c r="I570">
+        <v>0.3747307635854757</v>
+      </c>
+      <c r="J570">
+        <v>0.4526923641452424</v>
+      </c>
+      <c r="K570">
+        <v>1.27</v>
+      </c>
+      <c r="L570">
+        <v>3</v>
+      </c>
+      <c r="M570">
+        <v>1.17</v>
+      </c>
+      <c r="N570">
+        <v>2.58</v>
+      </c>
+      <c r="O570">
+        <v>1</v>
+      </c>
+      <c r="P570" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="571" spans="1:16">
+      <c r="A571" s="1">
+        <v>0</v>
+      </c>
+      <c r="B571" t="s">
+        <v>53</v>
+      </c>
+      <c r="C571">
+        <v>2.46037019732591</v>
+      </c>
+      <c r="D571" t="s">
+        <v>137</v>
+      </c>
+      <c r="E571">
+        <v>2.524828470599929</v>
+      </c>
+      <c r="F571">
+        <v>-1</v>
+      </c>
+      <c r="G571">
+        <v>0.00377962980267409</v>
+      </c>
+      <c r="H571">
+        <v>0.003775171529400071</v>
+      </c>
+      <c r="I571">
+        <v>-0.0644582732740191</v>
+      </c>
+      <c r="J571">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K571">
+        <v>1.34</v>
+      </c>
+      <c r="L571">
+        <v>3.12</v>
+      </c>
+      <c r="M571">
+        <v>1.27</v>
+      </c>
+      <c r="N571">
+        <v>3.15</v>
+      </c>
+      <c r="O571">
+        <v>1</v>
+      </c>
+      <c r="P571" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="572" spans="1:16">
+      <c r="A572" s="1">
+        <v>1</v>
+      </c>
+      <c r="B572" t="s">
+        <v>54</v>
+      </c>
+      <c r="C572">
         <v>2.37482847059993</v>
       </c>
-      <c r="D569" t="s">
+      <c r="D572" t="s">
         <v>136</v>
       </c>
-      <c r="E569">
+      <c r="E572">
         <v>2.004054575277101</v>
       </c>
-      <c r="F569">
-        <v>-1</v>
-      </c>
-      <c r="G569">
+      <c r="F572">
+        <v>-1</v>
+      </c>
+      <c r="G572">
         <v>0.003625171529400071</v>
       </c>
-      <c r="H569">
+      <c r="H572">
         <v>0.003155945424722899</v>
       </c>
-      <c r="I569">
+      <c r="I572">
         <v>0.370773895322829</v>
       </c>
-      <c r="J569">
+      <c r="J572">
         <v>0.4922610467717091</v>
       </c>
-      <c r="K569">
+      <c r="K572">
         <v>1.27</v>
       </c>
-      <c r="L569">
+      <c r="L572">
         <v>3</v>
       </c>
-      <c r="M569">
+      <c r="M572">
         <v>1.17</v>
       </c>
-      <c r="N569">
+      <c r="N572">
         <v>2.58</v>
       </c>
-      <c r="O569">
-        <v>1</v>
-      </c>
-      <c r="P569" t="s">
+      <c r="O572">
+        <v>1</v>
+      </c>
+      <c r="P572" t="s">
         <v>348</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="349">
   <si>
     <t>trade_time</t>
   </si>
@@ -421,10 +421,10 @@
     <t>2021-03-12</t>
   </si>
   <si>
+    <t>2021-04-23</t>
+  </si>
+  <si>
     <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>2021-04-23</t>
   </si>
   <si>
     <t>2021-03-23</t>
@@ -1418,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P572"/>
+  <dimension ref="A1:P576"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24329,10 +24329,10 @@
         <v>3.467968230829165</v>
       </c>
       <c r="D459" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E459">
-        <v>2.796032673988991</v>
+        <v>2.828629451830999</v>
       </c>
       <c r="F459">
         <v>-1</v>
@@ -24341,10 +24341,10 @@
         <v>0.002772031769170836</v>
       </c>
       <c r="H459">
-        <v>0.002203967326011009</v>
+        <v>0.002231370548169001</v>
       </c>
       <c r="I459">
-        <v>0.6719355568401739</v>
+        <v>0.6393387789981655</v>
       </c>
       <c r="J459">
         <v>-0.259677784200869</v>
@@ -24356,10 +24356,10 @@
         <v>3.12</v>
       </c>
       <c r="M459">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N459">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O459">
         <v>1</v>
@@ -24379,10 +24379,10 @@
         <v>3.329790785935104</v>
       </c>
       <c r="D460" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E460">
-        <v>2.796032673988991</v>
+        <v>2.828629451830999</v>
       </c>
       <c r="F460">
         <v>-1</v>
@@ -24391,10 +24391,10 @@
         <v>0.002670209214064896</v>
       </c>
       <c r="H460">
-        <v>0.002203967326011009</v>
+        <v>0.002231370548169001</v>
       </c>
       <c r="I460">
-        <v>0.533758111946113</v>
+        <v>0.5011613341041046</v>
       </c>
       <c r="J460">
         <v>-0.259677784200869</v>
@@ -24406,10 +24406,10 @@
         <v>3</v>
       </c>
       <c r="M460">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N460">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O460">
         <v>1</v>
@@ -26423,43 +26423,43 @@
         <v>0</v>
       </c>
       <c r="B501" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C501">
-        <v>3.482393153074574</v>
+        <v>2.478555931094635</v>
       </c>
       <c r="D501" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E501">
-        <v>2.841009049280418</v>
+        <v>2.928053314435237</v>
       </c>
       <c r="F501">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G501">
-        <v>0.002757606846925426</v>
+        <v>0.001921444068905365</v>
       </c>
       <c r="H501">
-        <v>0.002218990950719582</v>
+        <v>0.002251946685564763</v>
       </c>
       <c r="I501">
-        <v>0.6413841037941563</v>
+        <v>0.4494973833406015</v>
       </c>
       <c r="J501">
         <v>-0.2704426515481894</v>
       </c>
       <c r="K501">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L501">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M501">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N501">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O501">
         <v>1</v>
@@ -26473,10 +26473,10 @@
         <v>1</v>
       </c>
       <c r="B502" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C502">
-        <v>3.343462167466201</v>
+        <v>3.482393153074574</v>
       </c>
       <c r="D502" t="s">
         <v>133</v>
@@ -26488,22 +26488,22 @@
         <v>-1</v>
       </c>
       <c r="G502">
-        <v>0.002656537832533799</v>
+        <v>0.002757606846925426</v>
       </c>
       <c r="H502">
         <v>0.002218990950719582</v>
       </c>
       <c r="I502">
-        <v>0.502453118185783</v>
+        <v>0.6413841037941563</v>
       </c>
       <c r="J502">
         <v>-0.2704426515481894</v>
       </c>
       <c r="K502">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L502">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M502">
         <v>1.15</v>
@@ -26520,40 +26520,40 @@
     </row>
     <row r="503" spans="1:16">
       <c r="A503" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B503" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C503">
-        <v>3.500469067562396</v>
+        <v>3.343462167466201</v>
       </c>
       <c r="D503" t="s">
         <v>133</v>
       </c>
       <c r="E503">
-        <v>2.856521960967727</v>
+        <v>2.841009049280418</v>
       </c>
       <c r="F503">
         <v>-1</v>
       </c>
       <c r="G503">
-        <v>0.002739530932437605</v>
+        <v>0.002656537832533799</v>
       </c>
       <c r="H503">
-        <v>0.002203478039032273</v>
+        <v>0.002218990950719582</v>
       </c>
       <c r="I503">
-        <v>0.6439471065946685</v>
+        <v>0.502453118185783</v>
       </c>
       <c r="J503">
-        <v>-0.2839321399719367</v>
+        <v>-0.2704426515481894</v>
       </c>
       <c r="K503">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L503">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M503">
         <v>1.15</v>
@@ -26565,51 +26565,51 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="504" spans="1:16">
       <c r="A504" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B504" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C504">
-        <v>3.36059381776436</v>
+        <v>2.492450104171095</v>
       </c>
       <c r="D504" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E504">
-        <v>2.856521960967727</v>
+        <v>2.944915174964921</v>
       </c>
       <c r="F504">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G504">
-        <v>0.002639406182235641</v>
+        <v>0.001907549895828906</v>
       </c>
       <c r="H504">
-        <v>0.002203478039032273</v>
+        <v>0.002235084825035079</v>
       </c>
       <c r="I504">
-        <v>0.5040718567966325</v>
+        <v>0.4524650707938256</v>
       </c>
       <c r="J504">
         <v>-0.2839321399719367</v>
       </c>
       <c r="K504">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L504">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M504">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N504">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O504">
         <v>1</v>
@@ -26620,90 +26620,90 @@
     </row>
     <row r="505" spans="1:16">
       <c r="A505" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B505" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C505">
-        <v>2.485588290136117</v>
+        <v>3.500469067562396</v>
       </c>
       <c r="D505" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E505">
-        <v>2.936587730747715</v>
+        <v>2.856521960967727</v>
       </c>
       <c r="F505">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G505">
-        <v>0.001914411709863883</v>
+        <v>0.002739530932437605</v>
       </c>
       <c r="H505">
-        <v>0.002243412269252285</v>
+        <v>0.002203478039032273</v>
       </c>
       <c r="I505">
-        <v>0.4509994406115978</v>
+        <v>0.6439471065946685</v>
       </c>
       <c r="J505">
-        <v>-0.2772701845981717</v>
+        <v>-0.2839321399719367</v>
       </c>
       <c r="K505">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L505">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M505">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N505">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O505">
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="506" spans="1:16">
       <c r="A506" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B506" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C506">
-        <v>3.49154204736155</v>
+        <v>3.36059381776436</v>
       </c>
       <c r="D506" t="s">
         <v>133</v>
       </c>
       <c r="E506">
-        <v>2.848860712287897</v>
+        <v>2.856521960967727</v>
       </c>
       <c r="F506">
         <v>-1</v>
       </c>
       <c r="G506">
-        <v>0.00274845795263845</v>
+        <v>0.002639406182235641</v>
       </c>
       <c r="H506">
-        <v>0.002211139287712102</v>
+        <v>0.002203478039032273</v>
       </c>
       <c r="I506">
-        <v>0.6426813350736529</v>
+        <v>0.5040718567966325</v>
       </c>
       <c r="J506">
-        <v>-0.2772701845981717</v>
+        <v>-0.2839321399719367</v>
       </c>
       <c r="K506">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L506">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M506">
         <v>1.15</v>
@@ -26715,51 +26715,51 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="507" spans="1:16">
       <c r="A507" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B507" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C507">
-        <v>3.352133134439678</v>
+        <v>2.485588290136117</v>
       </c>
       <c r="D507" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E507">
-        <v>2.848860712287897</v>
+        <v>2.936587730747715</v>
       </c>
       <c r="F507">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G507">
-        <v>0.002647866865560322</v>
+        <v>0.001914411709863883</v>
       </c>
       <c r="H507">
-        <v>0.002211139287712102</v>
+        <v>0.002243412269252285</v>
       </c>
       <c r="I507">
-        <v>0.503272422151781</v>
+        <v>0.4509994406115978</v>
       </c>
       <c r="J507">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K507">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L507">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M507">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N507">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O507">
         <v>1</v>
@@ -26770,90 +26770,90 @@
     </row>
     <row r="508" spans="1:16">
       <c r="A508" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B508" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C508">
-        <v>2.483803138304734</v>
+        <v>3.49154204736155</v>
       </c>
       <c r="D508" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E508">
-        <v>2.934421284350405</v>
+        <v>2.848860712287897</v>
       </c>
       <c r="F508">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G508">
-        <v>0.001916196861695266</v>
+        <v>0.00274845795263845</v>
       </c>
       <c r="H508">
-        <v>0.002245578715649595</v>
+        <v>0.002211139287712102</v>
       </c>
       <c r="I508">
-        <v>0.4506181460456711</v>
+        <v>0.6426813350736529</v>
       </c>
       <c r="J508">
-        <v>-0.2755370274803244</v>
+        <v>-0.2772701845981717</v>
       </c>
       <c r="K508">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L508">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M508">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N508">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O508">
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="509" spans="1:16">
       <c r="A509" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B509" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C509">
-        <v>3.489219616823635</v>
+        <v>3.352133134439678</v>
       </c>
       <c r="D509" t="s">
         <v>133</v>
       </c>
       <c r="E509">
-        <v>2.846867581602373</v>
+        <v>2.848860712287897</v>
       </c>
       <c r="F509">
         <v>-1</v>
       </c>
       <c r="G509">
-        <v>0.002750780383176366</v>
+        <v>0.002647866865560322</v>
       </c>
       <c r="H509">
-        <v>0.002213132418397626</v>
+        <v>0.002211139287712102</v>
       </c>
       <c r="I509">
-        <v>0.6423520352212617</v>
+        <v>0.503272422151781</v>
       </c>
       <c r="J509">
-        <v>-0.2755370274803244</v>
+        <v>-0.2772701845981717</v>
       </c>
       <c r="K509">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L509">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M509">
         <v>1.15</v>
@@ -26865,51 +26865,51 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="510" spans="1:16">
       <c r="A510" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B510" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C510">
-        <v>3.349932024900012</v>
+        <v>2.483803138304734</v>
       </c>
       <c r="D510" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E510">
-        <v>2.846867581602373</v>
+        <v>2.934421284350405</v>
       </c>
       <c r="F510">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G510">
-        <v>0.002650067975099988</v>
+        <v>0.001916196861695266</v>
       </c>
       <c r="H510">
-        <v>0.002213132418397626</v>
+        <v>0.002245578715649595</v>
       </c>
       <c r="I510">
-        <v>0.5030644432976388</v>
+        <v>0.4506181460456711</v>
       </c>
       <c r="J510">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K510">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L510">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M510">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N510">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O510">
         <v>1</v>
@@ -26920,90 +26920,90 @@
     </row>
     <row r="511" spans="1:16">
       <c r="A511" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B511" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C511">
-        <v>2.455324757264537</v>
+        <v>3.489219616823635</v>
       </c>
       <c r="D511" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E511">
-        <v>2.899860142311331</v>
+        <v>2.846867581602373</v>
       </c>
       <c r="F511">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G511">
-        <v>0.001944675242735464</v>
+        <v>0.002750780383176366</v>
       </c>
       <c r="H511">
-        <v>0.002280139857688669</v>
+        <v>0.002213132418397626</v>
       </c>
       <c r="I511">
-        <v>0.4445353850467941</v>
+        <v>0.6423520352212617</v>
       </c>
       <c r="J511">
-        <v>-0.2478881138490649</v>
+        <v>-0.2755370274803244</v>
       </c>
       <c r="K511">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L511">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M511">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N511">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O511">
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="512" spans="1:16">
       <c r="A512" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B512" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C512">
-        <v>3.452170072557747</v>
+        <v>3.349932024900012</v>
       </c>
       <c r="D512" t="s">
         <v>133</v>
       </c>
       <c r="E512">
-        <v>2.815071330926425</v>
+        <v>2.846867581602373</v>
       </c>
       <c r="F512">
         <v>-1</v>
       </c>
       <c r="G512">
-        <v>0.002787829927442253</v>
+        <v>0.002650067975099988</v>
       </c>
       <c r="H512">
-        <v>0.002244928669073575</v>
+        <v>0.002213132418397626</v>
       </c>
       <c r="I512">
-        <v>0.6370987416313225</v>
+        <v>0.5030644432976388</v>
       </c>
       <c r="J512">
-        <v>-0.2478881138490649</v>
+        <v>-0.2755370274803244</v>
       </c>
       <c r="K512">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L512">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M512">
         <v>1.15</v>
@@ -27015,51 +27015,51 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="513" spans="1:16">
       <c r="A513" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B513" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C513">
-        <v>3.314817904588312</v>
+        <v>2.455324757264537</v>
       </c>
       <c r="D513" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E513">
-        <v>2.815071330926425</v>
+        <v>2.899860142311331</v>
       </c>
       <c r="F513">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G513">
-        <v>0.002685182095411688</v>
+        <v>0.001944675242735464</v>
       </c>
       <c r="H513">
-        <v>0.002244928669073575</v>
+        <v>0.002280139857688669</v>
       </c>
       <c r="I513">
-        <v>0.4997465736618878</v>
+        <v>0.4445353850467941</v>
       </c>
       <c r="J513">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K513">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L513">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M513">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N513">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O513">
         <v>1</v>
@@ -27070,90 +27070,90 @@
     </row>
     <row r="514" spans="1:16">
       <c r="A514" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B514" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C514">
-        <v>2.38683909149</v>
+        <v>3.452170072557747</v>
       </c>
       <c r="D514" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E514">
-        <v>2.816746470254853</v>
+        <v>2.815071330926425</v>
       </c>
       <c r="F514">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G514">
-        <v>0.002013160908510001</v>
+        <v>0.002787829927442253</v>
       </c>
       <c r="H514">
-        <v>0.002363253529745146</v>
+        <v>0.002244928669073575</v>
       </c>
       <c r="I514">
-        <v>0.4299073787648537</v>
+        <v>0.6370987416313225</v>
       </c>
       <c r="J514">
-        <v>-0.181397176203883</v>
+        <v>-0.2478881138490649</v>
       </c>
       <c r="K514">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L514">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M514">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N514">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O514">
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="515" spans="1:16">
       <c r="A515" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B515" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C515">
-        <v>3.363072216113203</v>
+        <v>3.314817904588312</v>
       </c>
       <c r="D515" t="s">
         <v>133</v>
       </c>
       <c r="E515">
-        <v>2.738606752634465</v>
+        <v>2.815071330926425</v>
       </c>
       <c r="F515">
         <v>-1</v>
       </c>
       <c r="G515">
-        <v>0.002876927783886797</v>
+        <v>0.002685182095411688</v>
       </c>
       <c r="H515">
-        <v>0.002321393247365534</v>
+        <v>0.002244928669073575</v>
       </c>
       <c r="I515">
-        <v>0.6244654634787379</v>
+        <v>0.4997465736618878</v>
       </c>
       <c r="J515">
-        <v>-0.181397176203883</v>
+        <v>-0.2478881138490649</v>
       </c>
       <c r="K515">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L515">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M515">
         <v>1.15</v>
@@ -27165,51 +27165,51 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="516" spans="1:16">
       <c r="A516" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B516" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C516">
-        <v>3.230374413778931</v>
+        <v>2.38683909149</v>
       </c>
       <c r="D516" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E516">
-        <v>2.738606752634465</v>
+        <v>2.816746470254853</v>
       </c>
       <c r="F516">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G516">
-        <v>0.002769625586221069</v>
+        <v>0.002013160908510001</v>
       </c>
       <c r="H516">
-        <v>0.002321393247365534</v>
+        <v>0.002363253529745146</v>
       </c>
       <c r="I516">
-        <v>0.4917676611444661</v>
+        <v>0.4299073787648537</v>
       </c>
       <c r="J516">
         <v>-0.181397176203883</v>
       </c>
       <c r="K516">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L516">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M516">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N516">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O516">
         <v>1</v>
@@ -27220,90 +27220,90 @@
     </row>
     <row r="517" spans="1:16">
       <c r="A517" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B517" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C517">
-        <v>2.332831092936091</v>
+        <v>3.363072216113203</v>
       </c>
       <c r="D517" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E517">
-        <v>2.751202782689431</v>
+        <v>2.738606752634465</v>
       </c>
       <c r="F517">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G517">
-        <v>0.002067168907063909</v>
+        <v>0.002876927783886797</v>
       </c>
       <c r="H517">
-        <v>0.002428797217310569</v>
+        <v>0.002321393247365534</v>
       </c>
       <c r="I517">
-        <v>0.4183716897533394</v>
+        <v>0.6244654634787379</v>
       </c>
       <c r="J517">
-        <v>-0.1289622261515449</v>
+        <v>-0.181397176203883</v>
       </c>
       <c r="K517">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L517">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M517">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N517">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O517">
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="518" spans="1:16">
       <c r="A518" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B518" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C518">
-        <v>3.29280938304307</v>
+        <v>3.230374413778931</v>
       </c>
       <c r="D518" t="s">
         <v>133</v>
       </c>
       <c r="E518">
-        <v>2.678306560074276</v>
+        <v>2.738606752634465</v>
       </c>
       <c r="F518">
         <v>-1</v>
       </c>
       <c r="G518">
-        <v>0.00294719061695693</v>
+        <v>0.002769625586221069</v>
       </c>
       <c r="H518">
-        <v>0.002381693439925723</v>
+        <v>0.002321393247365534</v>
       </c>
       <c r="I518">
-        <v>0.6145028229687939</v>
+        <v>0.4917676611444661</v>
       </c>
       <c r="J518">
-        <v>-0.1289622261515449</v>
+        <v>-0.181397176203883</v>
       </c>
       <c r="K518">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L518">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M518">
         <v>1.15</v>
@@ -27315,51 +27315,51 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="519" spans="1:16">
       <c r="A519" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B519" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C519">
-        <v>3.163782027212462</v>
+        <v>2.332831092936091</v>
       </c>
       <c r="D519" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E519">
-        <v>2.678306560074276</v>
+        <v>2.751202782689431</v>
       </c>
       <c r="F519">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G519">
-        <v>0.002836217972787538</v>
+        <v>0.002067168907063909</v>
       </c>
       <c r="H519">
-        <v>0.002381693439925723</v>
+        <v>0.002428797217310569</v>
       </c>
       <c r="I519">
-        <v>0.4854754671381856</v>
+        <v>0.4183716897533394</v>
       </c>
       <c r="J519">
         <v>-0.1289622261515449</v>
       </c>
       <c r="K519">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L519">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M519">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N519">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O519">
         <v>1</v>
@@ -27370,90 +27370,90 @@
     </row>
     <row r="520" spans="1:16">
       <c r="A520" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B520" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C520">
-        <v>2.292718610119939</v>
+        <v>3.29280938304307</v>
       </c>
       <c r="D520" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E520">
-        <v>2.702522585097013</v>
+        <v>2.678306560074276</v>
       </c>
       <c r="F520">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G520">
-        <v>0.002107281389880062</v>
+        <v>0.00294719061695693</v>
       </c>
       <c r="H520">
-        <v>0.002477477414902987</v>
+        <v>0.002381693439925723</v>
       </c>
       <c r="I520">
-        <v>0.4098039749770739</v>
+        <v>0.6145028229687939</v>
       </c>
       <c r="J520">
-        <v>-0.09001806807761016</v>
+        <v>-0.1289622261515449</v>
       </c>
       <c r="K520">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L520">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M520">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N520">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O520">
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="521" spans="1:16">
       <c r="A521" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B521" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C521">
-        <v>3.240624211223998</v>
+        <v>3.163782027212462</v>
       </c>
       <c r="D521" t="s">
         <v>133</v>
       </c>
       <c r="E521">
-        <v>2.633520778289252</v>
+        <v>2.678306560074276</v>
       </c>
       <c r="F521">
         <v>-1</v>
       </c>
       <c r="G521">
-        <v>0.002999375788776002</v>
+        <v>0.002836217972787538</v>
       </c>
       <c r="H521">
-        <v>0.002426479221710748</v>
+        <v>0.002381693439925723</v>
       </c>
       <c r="I521">
-        <v>0.6071034329347462</v>
+        <v>0.4854754671381856</v>
       </c>
       <c r="J521">
-        <v>-0.09001806807761016</v>
+        <v>-0.1289622261515449</v>
       </c>
       <c r="K521">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L521">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M521">
         <v>1.15</v>
@@ -27465,51 +27465,51 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="522" spans="1:16">
       <c r="A522" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B522" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C522">
-        <v>3.114322946458565</v>
+        <v>2.292718610119939</v>
       </c>
       <c r="D522" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E522">
-        <v>2.633520778289252</v>
+        <v>2.702522585097013</v>
       </c>
       <c r="F522">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G522">
-        <v>0.002885677053541435</v>
+        <v>0.002107281389880062</v>
       </c>
       <c r="H522">
-        <v>0.002426479221710748</v>
+        <v>0.002477477414902987</v>
       </c>
       <c r="I522">
-        <v>0.4808021681693133</v>
+        <v>0.4098039749770739</v>
       </c>
       <c r="J522">
         <v>-0.09001806807761016</v>
       </c>
       <c r="K522">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L522">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M522">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N522">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27520,34 +27520,34 @@
     </row>
     <row r="523" spans="1:16">
       <c r="A523" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B523" t="s">
         <v>53</v>
       </c>
       <c r="C523">
-        <v>3.108090425020327</v>
+        <v>3.240624211223998</v>
       </c>
       <c r="D523" t="s">
         <v>133</v>
       </c>
       <c r="E523">
-        <v>2.519779096099534</v>
+        <v>2.633520778289252</v>
       </c>
       <c r="F523">
         <v>-1</v>
       </c>
       <c r="G523">
-        <v>0.003131909574979673</v>
+        <v>0.002999375788776002</v>
       </c>
       <c r="H523">
-        <v>0.002540220903900465</v>
+        <v>0.002426479221710748</v>
       </c>
       <c r="I523">
-        <v>0.5883113289207929</v>
+        <v>0.6071034329347462</v>
       </c>
       <c r="J523">
-        <v>0.008887742522143843</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K523">
         <v>1.34</v>
@@ -27565,39 +27565,39 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="524" spans="1:16">
       <c r="A524" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B524" t="s">
         <v>54</v>
       </c>
       <c r="C524">
-        <v>2.988712566996877</v>
+        <v>3.114322946458565</v>
       </c>
       <c r="D524" t="s">
         <v>133</v>
       </c>
       <c r="E524">
-        <v>2.519779096099534</v>
+        <v>2.633520778289252</v>
       </c>
       <c r="F524">
         <v>-1</v>
       </c>
       <c r="G524">
-        <v>0.003011287433003123</v>
+        <v>0.002885677053541435</v>
       </c>
       <c r="H524">
-        <v>0.002540220903900465</v>
+        <v>0.002426479221710748</v>
       </c>
       <c r="I524">
-        <v>0.4689334708973432</v>
+        <v>0.4808021681693133</v>
       </c>
       <c r="J524">
-        <v>0.008887742522143843</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K524">
         <v>1.27</v>
@@ -27615,7 +27615,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27626,28 +27626,28 @@
         <v>53</v>
       </c>
       <c r="C525">
-        <v>3.056640151974971</v>
+        <v>3.108090425020327</v>
       </c>
       <c r="D525" t="s">
         <v>133</v>
       </c>
       <c r="E525">
-        <v>2.475624011023295</v>
+        <v>2.519779096099534</v>
       </c>
       <c r="F525">
         <v>-1</v>
       </c>
       <c r="G525">
-        <v>0.00318335984802503</v>
+        <v>0.003131909574979673</v>
       </c>
       <c r="H525">
-        <v>0.002584375988976704</v>
+        <v>0.002540220903900465</v>
       </c>
       <c r="I525">
-        <v>0.5810161409516752</v>
+        <v>0.5883113289207929</v>
       </c>
       <c r="J525">
-        <v>0.04728346867539508</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K525">
         <v>1.34</v>
@@ -27665,7 +27665,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27676,28 +27676,28 @@
         <v>54</v>
       </c>
       <c r="C526">
-        <v>2.939949994782248</v>
+        <v>2.988712566996877</v>
       </c>
       <c r="D526" t="s">
         <v>133</v>
       </c>
       <c r="E526">
-        <v>2.475624011023295</v>
+        <v>2.519779096099534</v>
       </c>
       <c r="F526">
         <v>-1</v>
       </c>
       <c r="G526">
-        <v>0.003060050005217752</v>
+        <v>0.003011287433003123</v>
       </c>
       <c r="H526">
-        <v>0.002584375988976704</v>
+        <v>0.002540220903900465</v>
       </c>
       <c r="I526">
-        <v>0.4643259837589526</v>
+        <v>0.4689334708973432</v>
       </c>
       <c r="J526">
-        <v>0.04728346867539508</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K526">
         <v>1.27</v>
@@ -27715,7 +27715,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27726,28 +27726,28 @@
         <v>53</v>
       </c>
       <c r="C527">
-        <v>3.02860014354532</v>
+        <v>3.056640151974971</v>
       </c>
       <c r="D527" t="s">
         <v>133</v>
       </c>
       <c r="E527">
-        <v>2.451559824684416</v>
+        <v>2.475624011023295</v>
       </c>
       <c r="F527">
         <v>-1</v>
       </c>
       <c r="G527">
-        <v>0.00321139985645468</v>
+        <v>0.00318335984802503</v>
       </c>
       <c r="H527">
-        <v>0.002608440175315583</v>
+        <v>0.002584375988976704</v>
       </c>
       <c r="I527">
-        <v>0.5770403188609037</v>
+        <v>0.5810161409516752</v>
       </c>
       <c r="J527">
-        <v>0.06820884810050738</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K527">
         <v>1.34</v>
@@ -27765,7 +27765,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27776,28 +27776,28 @@
         <v>54</v>
       </c>
       <c r="C528">
-        <v>2.913374762912356</v>
+        <v>2.939949994782248</v>
       </c>
       <c r="D528" t="s">
         <v>133</v>
       </c>
       <c r="E528">
-        <v>2.451559824684416</v>
+        <v>2.475624011023295</v>
       </c>
       <c r="F528">
         <v>-1</v>
       </c>
       <c r="G528">
-        <v>0.003086625237087645</v>
+        <v>0.003060050005217752</v>
       </c>
       <c r="H528">
-        <v>0.002608440175315583</v>
+        <v>0.002584375988976704</v>
       </c>
       <c r="I528">
-        <v>0.4618149382279393</v>
+        <v>0.4643259837589526</v>
       </c>
       <c r="J528">
-        <v>0.06820884810050738</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K528">
         <v>1.27</v>
@@ -27815,7 +27815,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27826,28 +27826,28 @@
         <v>53</v>
       </c>
       <c r="C529">
-        <v>3.020596707186351</v>
+        <v>3.02860014354532</v>
       </c>
       <c r="D529" t="s">
         <v>133</v>
       </c>
       <c r="E529">
-        <v>2.444691203928584</v>
+        <v>2.451559824684416</v>
       </c>
       <c r="F529">
         <v>-1</v>
       </c>
       <c r="G529">
-        <v>0.00321940329281365</v>
+        <v>0.00321139985645468</v>
       </c>
       <c r="H529">
-        <v>0.002615308796071415</v>
+        <v>0.002608440175315583</v>
       </c>
       <c r="I529">
-        <v>0.5759055032577662</v>
+        <v>0.5770403188609037</v>
       </c>
       <c r="J529">
-        <v>0.07418156180123091</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K529">
         <v>1.34</v>
@@ -27865,7 +27865,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27876,28 +27876,28 @@
         <v>54</v>
       </c>
       <c r="C530">
-        <v>2.905789416512437</v>
+        <v>2.913374762912356</v>
       </c>
       <c r="D530" t="s">
         <v>133</v>
       </c>
       <c r="E530">
-        <v>2.444691203928584</v>
+        <v>2.451559824684416</v>
       </c>
       <c r="F530">
         <v>-1</v>
       </c>
       <c r="G530">
-        <v>0.003094210583487563</v>
+        <v>0.003086625237087645</v>
       </c>
       <c r="H530">
-        <v>0.002615308796071415</v>
+        <v>0.002608440175315583</v>
       </c>
       <c r="I530">
-        <v>0.4610982125838525</v>
+        <v>0.4618149382279393</v>
       </c>
       <c r="J530">
-        <v>0.07418156180123091</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K530">
         <v>1.27</v>
@@ -27915,7 +27915,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27926,28 +27926,28 @@
         <v>53</v>
       </c>
       <c r="C531">
-        <v>3.071861218252691</v>
+        <v>3.020596707186351</v>
       </c>
       <c r="D531" t="s">
         <v>133</v>
       </c>
       <c r="E531">
-        <v>2.488686866410891</v>
+        <v>2.444691203928584</v>
       </c>
       <c r="F531">
         <v>-1</v>
       </c>
       <c r="G531">
-        <v>0.00316813878174731</v>
+        <v>0.00321940329281365</v>
       </c>
       <c r="H531">
-        <v>0.002571313133589109</v>
+        <v>0.002615308796071415</v>
       </c>
       <c r="I531">
-        <v>0.5831743518417998</v>
+        <v>0.5759055032577662</v>
       </c>
       <c r="J531">
-        <v>0.03592446399052947</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K531">
         <v>1.34</v>
@@ -27965,7 +27965,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -27976,28 +27976,28 @@
         <v>54</v>
       </c>
       <c r="C532">
-        <v>2.954375930732028</v>
+        <v>2.905789416512437</v>
       </c>
       <c r="D532" t="s">
         <v>133</v>
       </c>
       <c r="E532">
-        <v>2.488686866410891</v>
+        <v>2.444691203928584</v>
       </c>
       <c r="F532">
         <v>-1</v>
       </c>
       <c r="G532">
-        <v>0.003045624069267972</v>
+        <v>0.003094210583487563</v>
       </c>
       <c r="H532">
-        <v>0.002571313133589109</v>
+        <v>0.002615308796071415</v>
       </c>
       <c r="I532">
-        <v>0.4656890643211367</v>
+        <v>0.4610982125838525</v>
       </c>
       <c r="J532">
-        <v>0.03592446399052947</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K532">
         <v>1.27</v>
@@ -28015,7 +28015,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28023,49 +28023,49 @@
         <v>0</v>
       </c>
       <c r="B533" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C533">
-        <v>3.057789944024353</v>
+        <v>2.162997802089755</v>
       </c>
       <c r="D533" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E533">
-        <v>2.47661077285672</v>
+        <v>2.545094420011838</v>
       </c>
       <c r="F533">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G533">
-        <v>0.003182210055975647</v>
+        <v>0.002237002197910246</v>
       </c>
       <c r="H533">
-        <v>0.002583389227143279</v>
+        <v>0.002634905579988162</v>
       </c>
       <c r="I533">
-        <v>0.5811791711676326</v>
+        <v>0.382096617922083</v>
       </c>
       <c r="J533">
-        <v>0.04642541490719935</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K533">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L533">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M533">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N533">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O533">
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28073,37 +28073,37 @@
         <v>1</v>
       </c>
       <c r="B534" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C534">
-        <v>2.941039723067857</v>
+        <v>3.071861218252691</v>
       </c>
       <c r="D534" t="s">
         <v>133</v>
       </c>
       <c r="E534">
-        <v>2.47661077285672</v>
+        <v>2.488686866410891</v>
       </c>
       <c r="F534">
         <v>-1</v>
       </c>
       <c r="G534">
-        <v>0.003058960276932143</v>
+        <v>0.00316813878174731</v>
       </c>
       <c r="H534">
-        <v>0.002583389227143279</v>
+        <v>0.002571313133589109</v>
       </c>
       <c r="I534">
-        <v>0.4644289502111363</v>
+        <v>0.5831743518417998</v>
       </c>
       <c r="J534">
-        <v>0.04642541490719935</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K534">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L534">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M534">
         <v>1.15</v>
@@ -28115,145 +28115,145 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="535" spans="1:16">
       <c r="A535" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B535" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C535">
-        <v>2.132867933343715</v>
+        <v>2.954375930732028</v>
       </c>
       <c r="D535" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E535">
-        <v>2.508529045320043</v>
+        <v>2.488686866410891</v>
       </c>
       <c r="F535">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G535">
-        <v>0.002267132066656285</v>
+        <v>0.003045624069267972</v>
       </c>
       <c r="H535">
-        <v>0.002671470954679957</v>
+        <v>0.002571313133589109</v>
       </c>
       <c r="I535">
-        <v>0.3756611119763273</v>
+        <v>0.4656890643211367</v>
       </c>
       <c r="J535">
-        <v>0.06517676374396589</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K535">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L535">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M535">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N535">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O535">
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="536" spans="1:16">
       <c r="A536" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B536" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C536">
-        <v>3.032663136583086</v>
+        <v>2.152181822645585</v>
       </c>
       <c r="D536" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E536">
-        <v>2.455046721694439</v>
+        <v>2.531968231366001</v>
       </c>
       <c r="F536">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G536">
-        <v>0.003207336863416915</v>
+        <v>0.002247818177354416</v>
       </c>
       <c r="H536">
-        <v>0.002604953278305561</v>
+        <v>0.002648031768633999</v>
       </c>
       <c r="I536">
-        <v>0.5776164148886465</v>
+        <v>0.3797864087204159</v>
       </c>
       <c r="J536">
-        <v>0.06517676374396589</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K536">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L536">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M536">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N536">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O536">
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="537" spans="1:16">
       <c r="A537" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B537" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C537">
-        <v>2.917225510045163</v>
+        <v>3.057789944024353</v>
       </c>
       <c r="D537" t="s">
         <v>133</v>
       </c>
       <c r="E537">
-        <v>2.455046721694439</v>
+        <v>2.47661077285672</v>
       </c>
       <c r="F537">
         <v>-1</v>
       </c>
       <c r="G537">
-        <v>0.003082774489954837</v>
+        <v>0.003182210055975647</v>
       </c>
       <c r="H537">
-        <v>0.002604953278305561</v>
+        <v>0.002583389227143279</v>
       </c>
       <c r="I537">
-        <v>0.462178788350724</v>
+        <v>0.5811791711676326</v>
       </c>
       <c r="J537">
-        <v>0.06517676374396589</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K537">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L537">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M537">
         <v>1.15</v>
@@ -28265,145 +28265,145 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B538" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C538">
-        <v>2.104641124313295</v>
+        <v>2.941039723067857</v>
       </c>
       <c r="D538" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E538">
-        <v>2.474273209118076</v>
+        <v>2.47661077285672</v>
       </c>
       <c r="F538">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G538">
-        <v>0.002295358875686706</v>
+        <v>0.003058960276932143</v>
       </c>
       <c r="H538">
-        <v>0.002705726790881924</v>
+        <v>0.002583389227143279</v>
       </c>
       <c r="I538">
-        <v>0.3696320848047812</v>
+        <v>0.4644289502111363</v>
       </c>
       <c r="J538">
-        <v>0.09258143270553931</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K538">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L538">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M538">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N538">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O538">
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B539" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C539">
-        <v>2.995940880174577</v>
+        <v>2.132867933343715</v>
       </c>
       <c r="D539" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E539">
-        <v>2.423531352388629</v>
+        <v>2.508529045320043</v>
       </c>
       <c r="F539">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G539">
-        <v>0.003244059119825423</v>
+        <v>0.002267132066656285</v>
       </c>
       <c r="H539">
-        <v>0.00263646864761137</v>
+        <v>0.002671470954679957</v>
       </c>
       <c r="I539">
-        <v>0.5724095277859478</v>
+        <v>0.3756611119763273</v>
       </c>
       <c r="J539">
-        <v>0.09258143270553931</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K539">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L539">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M539">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N539">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O539">
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="540" spans="1:16">
       <c r="A540" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B540" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C540">
-        <v>2.882421580463965</v>
+        <v>3.032663136583086</v>
       </c>
       <c r="D540" t="s">
         <v>133</v>
       </c>
       <c r="E540">
-        <v>2.423531352388629</v>
+        <v>2.455046721694439</v>
       </c>
       <c r="F540">
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.003117578419536035</v>
+        <v>0.003207336863416915</v>
       </c>
       <c r="H540">
-        <v>0.00263646864761137</v>
+        <v>0.002604953278305561</v>
       </c>
       <c r="I540">
-        <v>0.4588902280753357</v>
+        <v>0.5776164148886465</v>
       </c>
       <c r="J540">
-        <v>0.09258143270553931</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K540">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L540">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M540">
         <v>1.15</v>
@@ -28415,145 +28415,145 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="541" spans="1:16">
       <c r="A541" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B541" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C541">
-        <v>2.097453766817889</v>
+        <v>2.917225510045163</v>
       </c>
       <c r="D541" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E541">
-        <v>2.465550687885787</v>
+        <v>2.455046721694439</v>
       </c>
       <c r="F541">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.002302546233182111</v>
+        <v>0.003082774489954837</v>
       </c>
       <c r="H541">
-        <v>0.002714449312114212</v>
+        <v>0.002604953278305561</v>
       </c>
       <c r="I541">
-        <v>0.3680969210678979</v>
+        <v>0.462178788350724</v>
       </c>
       <c r="J541">
-        <v>0.09955944969136986</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K541">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L541">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M541">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N541">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="542" spans="1:16">
       <c r="A542" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B542" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C542">
-        <v>2.986590337413564</v>
+        <v>2.104641124313295</v>
       </c>
       <c r="D542" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E542">
-        <v>2.415506632854925</v>
+        <v>2.474273209118076</v>
       </c>
       <c r="F542">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G542">
-        <v>0.003253409662586436</v>
+        <v>0.002295358875686706</v>
       </c>
       <c r="H542">
-        <v>0.002644493367145075</v>
+        <v>0.002705726790881924</v>
       </c>
       <c r="I542">
-        <v>0.5710837045586397</v>
+        <v>0.3696320848047812</v>
       </c>
       <c r="J542">
-        <v>0.09955944969136986</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K542">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L542">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M542">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N542">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O542">
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="543" spans="1:16">
       <c r="A543" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B543" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C543">
-        <v>2.87355949889196</v>
+        <v>2.995940880174577</v>
       </c>
       <c r="D543" t="s">
         <v>133</v>
       </c>
       <c r="E543">
-        <v>2.415506632854925</v>
+        <v>2.423531352388629</v>
       </c>
       <c r="F543">
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.003126440501108039</v>
+        <v>0.003244059119825423</v>
       </c>
       <c r="H543">
-        <v>0.002644493367145075</v>
+        <v>0.00263646864761137</v>
       </c>
       <c r="I543">
-        <v>0.4580528660370358</v>
+        <v>0.5724095277859478</v>
       </c>
       <c r="J543">
-        <v>0.09955944969136986</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K543">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L543">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M543">
         <v>1.15</v>
@@ -28565,145 +28565,145 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="544" spans="1:16">
       <c r="A544" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B544" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C544">
-        <v>2.089309945208396</v>
+        <v>2.882421580463965</v>
       </c>
       <c r="D544" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E544">
-        <v>2.45566740923349</v>
+        <v>2.423531352388629</v>
       </c>
       <c r="F544">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.002310690054791604</v>
+        <v>0.003117578419536035</v>
       </c>
       <c r="H544">
-        <v>0.00272433259076651</v>
+        <v>0.00263646864761137</v>
       </c>
       <c r="I544">
-        <v>0.3663574640250937</v>
+        <v>0.4588902280753357</v>
       </c>
       <c r="J544">
-        <v>0.1074660726132081</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K544">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L544">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M544">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N544">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="545" spans="1:16">
       <c r="A545" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B545" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C545">
-        <v>2.975995462698301</v>
+        <v>2.097453766817889</v>
       </c>
       <c r="D545" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E545">
-        <v>2.406414016494811</v>
+        <v>2.465550687885787</v>
       </c>
       <c r="F545">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G545">
-        <v>0.003264004537301699</v>
+        <v>0.002302546233182111</v>
       </c>
       <c r="H545">
-        <v>0.002653585983505189</v>
+        <v>0.002714449312114212</v>
       </c>
       <c r="I545">
-        <v>0.5695814462034905</v>
+        <v>0.3680969210678979</v>
       </c>
       <c r="J545">
-        <v>0.1074660726132081</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K545">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L545">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M545">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N545">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="546" spans="1:16">
       <c r="A546" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B546" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C546">
-        <v>2.863518087781226</v>
+        <v>2.986590337413564</v>
       </c>
       <c r="D546" t="s">
         <v>133</v>
       </c>
       <c r="E546">
-        <v>2.406414016494811</v>
+        <v>2.415506632854925</v>
       </c>
       <c r="F546">
         <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.003136481912218774</v>
+        <v>0.003253409662586436</v>
       </c>
       <c r="H546">
-        <v>0.002653585983505189</v>
+        <v>0.002644493367145075</v>
       </c>
       <c r="I546">
-        <v>0.4571040712864152</v>
+        <v>0.5710837045586397</v>
       </c>
       <c r="J546">
-        <v>0.1074660726132081</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K546">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L546">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M546">
         <v>1.15</v>
@@ -28715,145 +28715,145 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="547" spans="1:16">
       <c r="A547" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B547" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C547">
-        <v>2.094107820370248</v>
+        <v>2.87355949889196</v>
       </c>
       <c r="D547" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E547">
-        <v>2.514574311506508</v>
+        <v>2.415506632854925</v>
       </c>
       <c r="F547">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G547">
-        <v>0.002305892179629752</v>
+        <v>0.003126440501108039</v>
       </c>
       <c r="H547">
-        <v>0.002765425688493492</v>
+        <v>0.002644493367145075</v>
       </c>
       <c r="I547">
-        <v>0.4204664911362594</v>
+        <v>0.4580528660370358</v>
       </c>
       <c r="J547">
-        <v>0.1028079413881086</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K547">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L547">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M547">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="N547">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="548" spans="1:16">
       <c r="A548" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B548" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C548">
-        <v>2.982237358539935</v>
+        <v>2.089309945208396</v>
       </c>
       <c r="D548" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E548">
-        <v>2.459714708575913</v>
+        <v>2.45566740923349</v>
       </c>
       <c r="F548">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G548">
-        <v>0.003257762641460066</v>
+        <v>0.002310690054791604</v>
       </c>
       <c r="H548">
-        <v>0.002700285291424087</v>
+        <v>0.00272433259076651</v>
       </c>
       <c r="I548">
-        <v>0.5225226499640216</v>
+        <v>0.3663574640250937</v>
       </c>
       <c r="J548">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K548">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L548">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M548">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N548">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="549" spans="1:16">
       <c r="A549" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B549" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C549">
-        <v>2.869433914437102</v>
+        <v>2.975995462698301</v>
       </c>
       <c r="D549" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E549">
-        <v>2.459714708575913</v>
+        <v>2.454264695042546</v>
       </c>
       <c r="F549">
         <v>-1</v>
       </c>
       <c r="G549">
-        <v>0.003130566085562898</v>
+        <v>0.003264004537301699</v>
       </c>
       <c r="H549">
-        <v>0.002700285291424087</v>
+        <v>0.002705735304957454</v>
       </c>
       <c r="I549">
-        <v>0.4097192058611889</v>
+        <v>0.5217307676557548</v>
       </c>
       <c r="J549">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K549">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L549">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M549">
         <v>1.17</v>
@@ -28865,145 +28865,145 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="550" spans="1:16">
       <c r="A550" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B550" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C550">
-        <v>2.084743195682537</v>
+        <v>2.863518087781226</v>
       </c>
       <c r="D550" t="s">
         <v>135</v>
       </c>
       <c r="E550">
-        <v>2.503482231779316</v>
+        <v>2.454264695042546</v>
       </c>
       <c r="F550">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G550">
-        <v>0.002315256804317463</v>
+        <v>0.003136481912218774</v>
       </c>
       <c r="H550">
-        <v>0.002776517768220685</v>
+        <v>0.002705735304957454</v>
       </c>
       <c r="I550">
-        <v>0.4187390360967784</v>
+        <v>0.4092533927386794</v>
       </c>
       <c r="J550">
-        <v>0.1118998100169543</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K550">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L550">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M550">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N550">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O550">
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="551" spans="1:16">
       <c r="A551" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B551" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C551">
-        <v>2.970054254577281</v>
+        <v>2.094107820370248</v>
       </c>
       <c r="D551" t="s">
         <v>136</v>
       </c>
       <c r="E551">
-        <v>2.449077222280164</v>
+        <v>2.514574311506508</v>
       </c>
       <c r="F551">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G551">
-        <v>0.003269945745422719</v>
+        <v>0.002305892179629752</v>
       </c>
       <c r="H551">
-        <v>0.002710922777719837</v>
+        <v>0.002765425688493492</v>
       </c>
       <c r="I551">
-        <v>0.5209770322971177</v>
+        <v>0.4204664911362594</v>
       </c>
       <c r="J551">
-        <v>0.1118998100169543</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K551">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L551">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M551">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N551">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="552" spans="1:16">
       <c r="A552" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B552" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C552">
-        <v>2.857887241278468</v>
+        <v>2.982237358539935</v>
       </c>
       <c r="D552" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E552">
-        <v>2.449077222280164</v>
+        <v>2.459714708575913</v>
       </c>
       <c r="F552">
         <v>-1</v>
       </c>
       <c r="G552">
-        <v>0.003142112758721532</v>
+        <v>0.003257762641460066</v>
       </c>
       <c r="H552">
-        <v>0.002710922777719837</v>
+        <v>0.002700285291424087</v>
       </c>
       <c r="I552">
-        <v>0.4088100189983046</v>
+        <v>0.5225226499640216</v>
       </c>
       <c r="J552">
-        <v>0.1118998100169543</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K552">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L552">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M552">
         <v>1.17</v>
@@ -29015,45 +29015,45 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="553" spans="1:16">
       <c r="A553" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B553" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C553">
-        <v>2.944089643772313</v>
+        <v>2.869433914437102</v>
       </c>
       <c r="D553" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E553">
-        <v>2.426406629263886</v>
+        <v>2.459714708575913</v>
       </c>
       <c r="F553">
         <v>-1</v>
       </c>
       <c r="G553">
-        <v>0.003295910356227687</v>
+        <v>0.003130566085562898</v>
       </c>
       <c r="H553">
-        <v>0.002733593370736115</v>
+        <v>0.002700285291424087</v>
       </c>
       <c r="I553">
-        <v>0.5176830145084277</v>
+        <v>0.4097192058611889</v>
       </c>
       <c r="J553">
-        <v>0.1312763852445424</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K553">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L553">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M553">
         <v>1.17</v>
@@ -29065,45 +29065,45 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>55</v>
+        <v>340</v>
       </c>
     </row>
     <row r="554" spans="1:16">
       <c r="A554" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B554" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C554">
-        <v>2.833278990739431</v>
+        <v>2.970054254577281</v>
       </c>
       <c r="D554" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E554">
-        <v>2.426406629263886</v>
+        <v>2.449077222280164</v>
       </c>
       <c r="F554">
         <v>-1</v>
       </c>
       <c r="G554">
-        <v>0.003166721009260569</v>
+        <v>0.003269945745422719</v>
       </c>
       <c r="H554">
-        <v>0.002733593370736115</v>
+        <v>0.002710922777719837</v>
       </c>
       <c r="I554">
-        <v>0.4068723614755454</v>
+        <v>0.5209770322971177</v>
       </c>
       <c r="J554">
-        <v>0.1312763852445424</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K554">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L554">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M554">
         <v>1.17</v>
@@ -29115,145 +29115,145 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>55</v>
+        <v>341</v>
       </c>
     </row>
     <row r="555" spans="1:16">
       <c r="A555" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B555" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C555">
-        <v>2.063914340678486</v>
+        <v>2.857887241278468</v>
       </c>
       <c r="D555" t="s">
         <v>135</v>
       </c>
       <c r="E555">
-        <v>2.437335373233729</v>
+        <v>2.449077222280164</v>
       </c>
       <c r="F555">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G555">
-        <v>0.002416085659321514</v>
+        <v>0.003142112758721532</v>
       </c>
       <c r="H555">
-        <v>0.002842664626766271</v>
+        <v>0.002710922777719837</v>
       </c>
       <c r="I555">
-        <v>0.3734210325552429</v>
+        <v>0.4088100189983046</v>
       </c>
       <c r="J555">
-        <v>0.16611854652973</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K555">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="L555">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="M555">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N555">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O555">
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="556" spans="1:16">
       <c r="A556" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B556" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C556">
-        <v>2.897401147650162</v>
+        <v>2.100847031640785</v>
       </c>
       <c r="D556" t="s">
         <v>136</v>
       </c>
       <c r="E556">
-        <v>2.385641300560216</v>
+        <v>2.479842810001658</v>
       </c>
       <c r="F556">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G556">
-        <v>0.003342598852349839</v>
+        <v>0.002379152968359215</v>
       </c>
       <c r="H556">
-        <v>0.002774358699439784</v>
+        <v>0.002800157189998342</v>
       </c>
       <c r="I556">
-        <v>0.5117598470899458</v>
+        <v>0.3789957783608728</v>
       </c>
       <c r="J556">
-        <v>0.16611854652973</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K556">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="L556">
-        <v>3.12</v>
+        <v>2.24</v>
       </c>
       <c r="M556">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N556">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O556">
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>342</v>
+        <v>55</v>
       </c>
     </row>
     <row r="557" spans="1:16">
       <c r="A557" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B557" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C557">
-        <v>2.789029445907243</v>
+        <v>2.944089643772313</v>
       </c>
       <c r="D557" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E557">
-        <v>2.385641300560216</v>
+        <v>2.426406629263886</v>
       </c>
       <c r="F557">
         <v>-1</v>
       </c>
       <c r="G557">
-        <v>0.003210970554092757</v>
+        <v>0.003295910356227687</v>
       </c>
       <c r="H557">
-        <v>0.002774358699439784</v>
+        <v>0.002733593370736115</v>
       </c>
       <c r="I557">
-        <v>0.4033881453470269</v>
+        <v>0.5176830145084277</v>
       </c>
       <c r="J557">
-        <v>0.16611854652973</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K557">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L557">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M557">
         <v>1.17</v>
@@ -29265,145 +29265,145 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>342</v>
+        <v>55</v>
       </c>
     </row>
     <row r="558" spans="1:16">
       <c r="A558" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B558" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C558">
-        <v>2.014066208827843</v>
+        <v>2.833278990739431</v>
       </c>
       <c r="D558" t="s">
         <v>135</v>
       </c>
       <c r="E558">
-        <v>2.379962995066008</v>
+        <v>2.426406629263886</v>
       </c>
       <c r="F558">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G558">
-        <v>0.002465933791172158</v>
+        <v>0.003166721009260569</v>
       </c>
       <c r="H558">
-        <v>0.002900037004933993</v>
+        <v>0.002733593370736115</v>
       </c>
       <c r="I558">
-        <v>0.365896786238165</v>
+        <v>0.4068723614755454</v>
       </c>
       <c r="J558">
-        <v>0.2131450860114693</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K558">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="L558">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="M558">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N558">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O558">
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>343</v>
+        <v>55</v>
       </c>
     </row>
     <row r="559" spans="1:16">
       <c r="A559" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B559" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C559">
-        <v>2.834385584744631</v>
+        <v>2.063914340678486</v>
       </c>
       <c r="D559" t="s">
         <v>136</v>
       </c>
       <c r="E559">
-        <v>2.330620249366581</v>
+        <v>2.437335373233729</v>
       </c>
       <c r="F559">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G559">
-        <v>0.003405614415255369</v>
+        <v>0.002416085659321514</v>
       </c>
       <c r="H559">
-        <v>0.002829379750633419</v>
+        <v>0.002842664626766271</v>
       </c>
       <c r="I559">
-        <v>0.5037653353780502</v>
+        <v>0.3734210325552429</v>
       </c>
       <c r="J559">
-        <v>0.2131450860114693</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K559">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="L559">
-        <v>3.12</v>
+        <v>2.24</v>
       </c>
       <c r="M559">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N559">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O559">
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="560" spans="1:16">
       <c r="A560" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B560" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C560">
-        <v>2.729305740765434</v>
+        <v>2.897401147650162</v>
       </c>
       <c r="D560" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E560">
-        <v>2.330620249366581</v>
+        <v>2.385641300560216</v>
       </c>
       <c r="F560">
         <v>-1</v>
       </c>
       <c r="G560">
-        <v>0.003270694259234566</v>
+        <v>0.003342598852349839</v>
       </c>
       <c r="H560">
-        <v>0.002829379750633419</v>
+        <v>0.002774358699439784</v>
       </c>
       <c r="I560">
-        <v>0.3986854913988531</v>
+        <v>0.5117598470899458</v>
       </c>
       <c r="J560">
-        <v>0.2131450860114693</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K560">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L560">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M560">
         <v>1.17</v>
@@ -29415,45 +29415,45 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="561" spans="1:16">
       <c r="A561" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B561" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C561">
-        <v>2.710585509297514</v>
+        <v>2.789029445907243</v>
       </c>
       <c r="D561" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E561">
-        <v>2.222526153640366</v>
+        <v>2.385641300560216</v>
       </c>
       <c r="F561">
         <v>-1</v>
       </c>
       <c r="G561">
-        <v>0.003529414490702487</v>
+        <v>0.003210970554092757</v>
       </c>
       <c r="H561">
-        <v>0.002937473846359634</v>
+        <v>0.002774358699439784</v>
       </c>
       <c r="I561">
-        <v>0.4880593556571475</v>
+        <v>0.4033881453470269</v>
       </c>
       <c r="J561">
-        <v>0.3055332020167811</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K561">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L561">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M561">
         <v>1.17</v>
@@ -29465,89 +29465,89 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>56</v>
+        <v>342</v>
       </c>
     </row>
     <row r="562" spans="1:16">
       <c r="A562" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B562" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C562">
-        <v>2.611972833438688</v>
+        <v>2.014066208827843</v>
       </c>
       <c r="D562" t="s">
         <v>136</v>
       </c>
       <c r="E562">
-        <v>2.222526153640366</v>
+        <v>2.379962995066008</v>
       </c>
       <c r="F562">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G562">
-        <v>0.003388027166561312</v>
+        <v>0.002465933791172158</v>
       </c>
       <c r="H562">
-        <v>0.002937473846359634</v>
+        <v>0.002900037004933993</v>
       </c>
       <c r="I562">
-        <v>0.389446679798322</v>
+        <v>0.365896786238165</v>
       </c>
       <c r="J562">
-        <v>0.3055332020167811</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K562">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="L562">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="M562">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N562">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O562">
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>56</v>
+        <v>343</v>
       </c>
     </row>
     <row r="563" spans="1:16">
       <c r="A563" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B563" t="s">
         <v>53</v>
       </c>
       <c r="C563">
-        <v>2.647551728558422</v>
+        <v>2.834385584744631</v>
       </c>
       <c r="D563" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E563">
-        <v>2.167489195830861</v>
+        <v>2.330620249366581</v>
       </c>
       <c r="F563">
         <v>-1</v>
       </c>
       <c r="G563">
-        <v>0.003592448271441579</v>
+        <v>0.003405614415255369</v>
       </c>
       <c r="H563">
-        <v>0.00299251080416914</v>
+        <v>0.002829379750633419</v>
       </c>
       <c r="I563">
-        <v>0.4800625327275609</v>
+        <v>0.5037653353780502</v>
       </c>
       <c r="J563">
-        <v>0.3525733368967002</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K563">
         <v>1.34</v>
@@ -29565,39 +29565,39 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="564" spans="1:16">
       <c r="A564" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B564" t="s">
         <v>54</v>
       </c>
       <c r="C564">
-        <v>2.552231862141191</v>
+        <v>2.729305740765434</v>
       </c>
       <c r="D564" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E564">
-        <v>2.167489195830861</v>
+        <v>2.330620249366581</v>
       </c>
       <c r="F564">
         <v>-1</v>
       </c>
       <c r="G564">
-        <v>0.003447768137858809</v>
+        <v>0.003270694259234566</v>
       </c>
       <c r="H564">
-        <v>0.00299251080416914</v>
+        <v>0.002829379750633419</v>
       </c>
       <c r="I564">
-        <v>0.3847426663103302</v>
+        <v>0.3986854913988531</v>
       </c>
       <c r="J564">
-        <v>0.3525733368967002</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K564">
         <v>1.27</v>
@@ -29615,7 +29615,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29626,28 +29626,28 @@
         <v>53</v>
       </c>
       <c r="C565">
-        <v>2.59897387935353</v>
+        <v>2.710585509297514</v>
       </c>
       <c r="D565" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E565">
-        <v>2.65619166177536</v>
+        <v>2.222526153640366</v>
       </c>
       <c r="F565">
         <v>-1</v>
       </c>
       <c r="G565">
-        <v>0.003641026120646471</v>
+        <v>0.003529414490702487</v>
       </c>
       <c r="H565">
-        <v>0.00364380833822464</v>
+        <v>0.002937473846359634</v>
       </c>
       <c r="I565">
-        <v>-0.05721778242183051</v>
+        <v>0.4880593556571475</v>
       </c>
       <c r="J565">
-        <v>0.3888254631690077</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K565">
         <v>1.34</v>
@@ -29656,16 +29656,16 @@
         <v>3.12</v>
       </c>
       <c r="M565">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N565">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O565">
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>345</v>
+        <v>56</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29676,28 +29676,28 @@
         <v>54</v>
       </c>
       <c r="C566">
-        <v>2.50619166177536</v>
+        <v>2.611972833438688</v>
       </c>
       <c r="D566" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E566">
-        <v>2.125074208092261</v>
+        <v>2.222526153640366</v>
       </c>
       <c r="F566">
         <v>-1</v>
       </c>
       <c r="G566">
-        <v>0.00349380833822464</v>
+        <v>0.003388027166561312</v>
       </c>
       <c r="H566">
-        <v>0.003034925791907739</v>
+        <v>0.002937473846359634</v>
       </c>
       <c r="I566">
-        <v>0.3811174536830992</v>
+        <v>0.389446679798322</v>
       </c>
       <c r="J566">
-        <v>0.3888254631690077</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K566">
         <v>1.27</v>
@@ -29715,7 +29715,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>345</v>
+        <v>56</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29726,28 +29726,28 @@
         <v>53</v>
       </c>
       <c r="C567">
-        <v>2.575095597538799</v>
+        <v>2.647551728558422</v>
       </c>
       <c r="D567" t="s">
         <v>137</v>
       </c>
       <c r="E567">
-        <v>2.633560752891249</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="F567">
         <v>-1</v>
       </c>
       <c r="G567">
-        <v>0.003664904402461202</v>
+        <v>0.003592448271441579</v>
       </c>
       <c r="H567">
-        <v>0.003666439247108751</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="I567">
-        <v>-0.05846515535245045</v>
+        <v>-0.05468013358276913</v>
       </c>
       <c r="J567">
-        <v>0.4066450764635833</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K567">
         <v>1.34</v>
@@ -29765,7 +29765,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29776,28 +29776,28 @@
         <v>54</v>
       </c>
       <c r="C568">
-        <v>2.483560752891249</v>
+        <v>2.552231862141191</v>
       </c>
       <c r="D568" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E568">
-        <v>2.104225260537608</v>
+        <v>2.167489195830861</v>
       </c>
       <c r="F568">
         <v>-1</v>
       </c>
       <c r="G568">
-        <v>0.003516439247108751</v>
+        <v>0.003447768137858809</v>
       </c>
       <c r="H568">
-        <v>0.003055774739462393</v>
+        <v>0.00299251080416914</v>
       </c>
       <c r="I568">
-        <v>0.3793354923536416</v>
+        <v>0.3847426663103302</v>
       </c>
       <c r="J568">
-        <v>0.4066450764635833</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K568">
         <v>1.27</v>
@@ -29815,7 +29815,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -29826,28 +29826,28 @@
         <v>53</v>
       </c>
       <c r="C569">
-        <v>2.513392232045375</v>
+        <v>2.59897387935353</v>
       </c>
       <c r="D569" t="s">
         <v>137</v>
       </c>
       <c r="E569">
-        <v>2.575080697535542</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="F569">
         <v>-1</v>
       </c>
       <c r="G569">
-        <v>0.003726607767954625</v>
+        <v>0.003641026120646471</v>
       </c>
       <c r="H569">
-        <v>0.003724919302464458</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="I569">
-        <v>-0.0616884654901666</v>
+        <v>-0.05721778242183051</v>
       </c>
       <c r="J569">
-        <v>0.4526923641452424</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K569">
         <v>1.34</v>
@@ -29865,7 +29865,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -29876,28 +29876,28 @@
         <v>54</v>
       </c>
       <c r="C570">
-        <v>2.425080697535542</v>
+        <v>2.50619166177536</v>
       </c>
       <c r="D570" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E570">
-        <v>2.050349933950066</v>
+        <v>2.125074208092261</v>
       </c>
       <c r="F570">
         <v>-1</v>
       </c>
       <c r="G570">
-        <v>0.003574919302464458</v>
+        <v>0.00349380833822464</v>
       </c>
       <c r="H570">
-        <v>0.003109650066049934</v>
+        <v>0.003034925791907739</v>
       </c>
       <c r="I570">
-        <v>0.3747307635854757</v>
+        <v>0.3811174536830992</v>
       </c>
       <c r="J570">
-        <v>0.4526923641452424</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K570">
         <v>1.27</v>
@@ -29915,7 +29915,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29926,28 +29926,28 @@
         <v>53</v>
       </c>
       <c r="C571">
-        <v>2.46037019732591</v>
+        <v>2.575095597538799</v>
       </c>
       <c r="D571" t="s">
         <v>137</v>
       </c>
       <c r="E571">
-        <v>2.524828470599929</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="F571">
         <v>-1</v>
       </c>
       <c r="G571">
-        <v>0.00377962980267409</v>
+        <v>0.003664904402461202</v>
       </c>
       <c r="H571">
-        <v>0.003775171529400071</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="I571">
-        <v>-0.0644582732740191</v>
+        <v>-0.05846515535245045</v>
       </c>
       <c r="J571">
-        <v>0.4922610467717091</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K571">
         <v>1.34</v>
@@ -29965,7 +29965,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -29976,28 +29976,28 @@
         <v>54</v>
       </c>
       <c r="C572">
-        <v>2.37482847059993</v>
+        <v>2.483560752891249</v>
       </c>
       <c r="D572" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E572">
-        <v>2.004054575277101</v>
+        <v>2.104225260537608</v>
       </c>
       <c r="F572">
         <v>-1</v>
       </c>
       <c r="G572">
-        <v>0.003625171529400071</v>
+        <v>0.003516439247108751</v>
       </c>
       <c r="H572">
-        <v>0.003155945424722899</v>
+        <v>0.003055774739462393</v>
       </c>
       <c r="I572">
-        <v>0.370773895322829</v>
+        <v>0.3793354923536416</v>
       </c>
       <c r="J572">
-        <v>0.4922610467717091</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K572">
         <v>1.27</v>
@@ -30015,6 +30015,206 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="573" spans="1:16">
+      <c r="A573" s="1">
+        <v>0</v>
+      </c>
+      <c r="B573" t="s">
+        <v>53</v>
+      </c>
+      <c r="C573">
+        <v>2.513392232045375</v>
+      </c>
+      <c r="D573" t="s">
+        <v>137</v>
+      </c>
+      <c r="E573">
+        <v>2.575080697535542</v>
+      </c>
+      <c r="F573">
+        <v>-1</v>
+      </c>
+      <c r="G573">
+        <v>0.003726607767954625</v>
+      </c>
+      <c r="H573">
+        <v>0.003724919302464458</v>
+      </c>
+      <c r="I573">
+        <v>-0.0616884654901666</v>
+      </c>
+      <c r="J573">
+        <v>0.4526923641452424</v>
+      </c>
+      <c r="K573">
+        <v>1.34</v>
+      </c>
+      <c r="L573">
+        <v>3.12</v>
+      </c>
+      <c r="M573">
+        <v>1.27</v>
+      </c>
+      <c r="N573">
+        <v>3.15</v>
+      </c>
+      <c r="O573">
+        <v>1</v>
+      </c>
+      <c r="P573" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="574" spans="1:16">
+      <c r="A574" s="1">
+        <v>1</v>
+      </c>
+      <c r="B574" t="s">
+        <v>54</v>
+      </c>
+      <c r="C574">
+        <v>2.425080697535542</v>
+      </c>
+      <c r="D574" t="s">
+        <v>135</v>
+      </c>
+      <c r="E574">
+        <v>2.050349933950066</v>
+      </c>
+      <c r="F574">
+        <v>-1</v>
+      </c>
+      <c r="G574">
+        <v>0.003574919302464458</v>
+      </c>
+      <c r="H574">
+        <v>0.003109650066049934</v>
+      </c>
+      <c r="I574">
+        <v>0.3747307635854757</v>
+      </c>
+      <c r="J574">
+        <v>0.4526923641452424</v>
+      </c>
+      <c r="K574">
+        <v>1.27</v>
+      </c>
+      <c r="L574">
+        <v>3</v>
+      </c>
+      <c r="M574">
+        <v>1.17</v>
+      </c>
+      <c r="N574">
+        <v>2.58</v>
+      </c>
+      <c r="O574">
+        <v>1</v>
+      </c>
+      <c r="P574" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="575" spans="1:16">
+      <c r="A575" s="1">
+        <v>0</v>
+      </c>
+      <c r="B575" t="s">
+        <v>53</v>
+      </c>
+      <c r="C575">
+        <v>2.46037019732591</v>
+      </c>
+      <c r="D575" t="s">
+        <v>137</v>
+      </c>
+      <c r="E575">
+        <v>2.524828470599929</v>
+      </c>
+      <c r="F575">
+        <v>-1</v>
+      </c>
+      <c r="G575">
+        <v>0.00377962980267409</v>
+      </c>
+      <c r="H575">
+        <v>0.003775171529400071</v>
+      </c>
+      <c r="I575">
+        <v>-0.0644582732740191</v>
+      </c>
+      <c r="J575">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K575">
+        <v>1.34</v>
+      </c>
+      <c r="L575">
+        <v>3.12</v>
+      </c>
+      <c r="M575">
+        <v>1.27</v>
+      </c>
+      <c r="N575">
+        <v>3.15</v>
+      </c>
+      <c r="O575">
+        <v>1</v>
+      </c>
+      <c r="P575" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="576" spans="1:16">
+      <c r="A576" s="1">
+        <v>1</v>
+      </c>
+      <c r="B576" t="s">
+        <v>54</v>
+      </c>
+      <c r="C576">
+        <v>2.37482847059993</v>
+      </c>
+      <c r="D576" t="s">
+        <v>135</v>
+      </c>
+      <c r="E576">
+        <v>2.004054575277101</v>
+      </c>
+      <c r="F576">
+        <v>-1</v>
+      </c>
+      <c r="G576">
+        <v>0.003625171529400071</v>
+      </c>
+      <c r="H576">
+        <v>0.003155945424722899</v>
+      </c>
+      <c r="I576">
+        <v>0.370773895322829</v>
+      </c>
+      <c r="J576">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K576">
+        <v>1.27</v>
+      </c>
+      <c r="L576">
+        <v>3</v>
+      </c>
+      <c r="M576">
+        <v>1.17</v>
+      </c>
+      <c r="N576">
+        <v>2.58</v>
+      </c>
+      <c r="O576">
+        <v>1</v>
+      </c>
+      <c r="P576" t="s">
         <v>348</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="342">
   <si>
     <t>trade_time</t>
   </si>
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P572"/>
+  <dimension ref="A1:P573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -25502,43 +25502,43 @@
         <v>0</v>
       </c>
       <c r="B483" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C483">
-        <v>3.381419347879684</v>
+        <v>2.400941737549309</v>
       </c>
       <c r="D483" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E483">
-        <v>2.754352425419131</v>
+        <v>2.833861331977317</v>
       </c>
       <c r="F483">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G483">
-        <v>0.002858580652120316</v>
+        <v>0.001999058262450691</v>
       </c>
       <c r="H483">
-        <v>0.002305647574580868</v>
+        <v>0.002346138668022683</v>
       </c>
       <c r="I483">
-        <v>0.6270669224605525</v>
+        <v>0.4329195944280078</v>
       </c>
       <c r="J483">
         <v>-0.1950890655818535</v>
       </c>
       <c r="K483">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L483">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M483">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N483">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O483">
         <v>1</v>
@@ -25552,10 +25552,10 @@
         <v>1</v>
       </c>
       <c r="B484" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C484">
-        <v>3.247763113288954</v>
+        <v>3.381419347879684</v>
       </c>
       <c r="D484" t="s">
         <v>130</v>
@@ -25567,22 +25567,22 @@
         <v>-1</v>
       </c>
       <c r="G484">
-        <v>0.002752236886711046</v>
+        <v>0.002858580652120316</v>
       </c>
       <c r="H484">
         <v>0.002305647574580868</v>
       </c>
       <c r="I484">
-        <v>0.4934106878698228</v>
+        <v>0.6270669224605525</v>
       </c>
       <c r="J484">
         <v>-0.1950890655818535</v>
       </c>
       <c r="K484">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L484">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M484">
         <v>1.15</v>
@@ -25599,96 +25599,96 @@
     </row>
     <row r="485" spans="1:16">
       <c r="A485" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B485" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C485">
-        <v>2.416869377367424</v>
+        <v>3.247763113288954</v>
       </c>
       <c r="D485" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E485">
-        <v>2.853190991950757</v>
+        <v>2.754352425419131</v>
       </c>
       <c r="F485">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G485">
-        <v>0.001983130622632577</v>
+        <v>0.002752236886711046</v>
       </c>
       <c r="H485">
-        <v>0.002326809008049243</v>
+        <v>0.002305647574580868</v>
       </c>
       <c r="I485">
-        <v>0.4363216145833326</v>
+        <v>0.4934106878698228</v>
       </c>
       <c r="J485">
-        <v>-0.2105527935606056</v>
+        <v>-0.1950890655818535</v>
       </c>
       <c r="K485">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L485">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M485">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N485">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O485">
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="486" spans="1:16">
       <c r="A486" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B486" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C486">
-        <v>3.402140743371211</v>
+        <v>2.416869377367424</v>
       </c>
       <c r="D486" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E486">
-        <v>2.772135712594696</v>
+        <v>2.853190991950757</v>
       </c>
       <c r="F486">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G486">
-        <v>0.002837859256628789</v>
+        <v>0.001983130622632577</v>
       </c>
       <c r="H486">
-        <v>0.002287864287405304</v>
+        <v>0.002326809008049243</v>
       </c>
       <c r="I486">
-        <v>0.6300050307765153</v>
+        <v>0.4363216145833326</v>
       </c>
       <c r="J486">
         <v>-0.2105527935606056</v>
       </c>
       <c r="K486">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L486">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M486">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N486">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O486">
         <v>1</v>
@@ -25699,13 +25699,13 @@
     </row>
     <row r="487" spans="1:16">
       <c r="A487" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B487" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C487">
-        <v>3.267402047821969</v>
+        <v>3.402140743371211</v>
       </c>
       <c r="D487" t="s">
         <v>130</v>
@@ -25717,22 +25717,22 @@
         <v>-1</v>
       </c>
       <c r="G487">
-        <v>0.002732597952178031</v>
+        <v>0.002837859256628789</v>
       </c>
       <c r="H487">
         <v>0.002287864287405304</v>
       </c>
       <c r="I487">
-        <v>0.495266335227273</v>
+        <v>0.6300050307765153</v>
       </c>
       <c r="J487">
         <v>-0.2105527935606056</v>
       </c>
       <c r="K487">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L487">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M487">
         <v>1.15</v>
@@ -25749,96 +25749,96 @@
     </row>
     <row r="488" spans="1:16">
       <c r="A488" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B488" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C488">
-        <v>2.427926332334885</v>
+        <v>3.267402047821969</v>
       </c>
       <c r="D488" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E488">
-        <v>2.866609626620006</v>
+        <v>2.772135712594696</v>
       </c>
       <c r="F488">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G488">
-        <v>0.001972073667665115</v>
+        <v>0.002732597952178031</v>
       </c>
       <c r="H488">
-        <v>0.002313390373379994</v>
+        <v>0.002287864287405304</v>
       </c>
       <c r="I488">
-        <v>0.4386832942851204</v>
+        <v>0.495266335227273</v>
       </c>
       <c r="J488">
-        <v>-0.2212877012960047</v>
+        <v>-0.2105527935606056</v>
       </c>
       <c r="K488">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L488">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M488">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N488">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O488">
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="489" spans="1:16">
       <c r="A489" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B489" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C489">
-        <v>3.416525519736647</v>
+        <v>2.427926332334885</v>
       </c>
       <c r="D489" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E489">
-        <v>2.784480856490405</v>
+        <v>2.866609626620006</v>
       </c>
       <c r="F489">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G489">
-        <v>0.002823474480263354</v>
+        <v>0.001972073667665115</v>
       </c>
       <c r="H489">
-        <v>0.002275519143509595</v>
+        <v>0.002313390373379994</v>
       </c>
       <c r="I489">
-        <v>0.6320446632462415</v>
+        <v>0.4386832942851204</v>
       </c>
       <c r="J489">
         <v>-0.2212877012960047</v>
       </c>
       <c r="K489">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L489">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M489">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N489">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O489">
         <v>1</v>
@@ -25849,13 +25849,13 @@
     </row>
     <row r="490" spans="1:16">
       <c r="A490" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B490" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C490">
-        <v>3.281035380645926</v>
+        <v>3.416525519736647</v>
       </c>
       <c r="D490" t="s">
         <v>130</v>
@@ -25867,22 +25867,22 @@
         <v>-1</v>
       </c>
       <c r="G490">
-        <v>0.002718964619354074</v>
+        <v>0.002823474480263354</v>
       </c>
       <c r="H490">
         <v>0.002275519143509595</v>
       </c>
       <c r="I490">
-        <v>0.4965545241555209</v>
+        <v>0.6320446632462415</v>
       </c>
       <c r="J490">
         <v>-0.2212877012960047</v>
       </c>
       <c r="K490">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L490">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M490">
         <v>1.15</v>
@@ -25899,96 +25899,96 @@
     </row>
     <row r="491" spans="1:16">
       <c r="A491" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B491" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C491">
-        <v>2.43983969591803</v>
+        <v>3.281035380645926</v>
       </c>
       <c r="D491" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E491">
-        <v>2.88106759213353</v>
+        <v>2.784480856490405</v>
       </c>
       <c r="F491">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G491">
-        <v>0.001960160304081971</v>
+        <v>0.002718964619354074</v>
       </c>
       <c r="H491">
-        <v>0.002298932407866469</v>
+        <v>0.002275519143509595</v>
       </c>
       <c r="I491">
-        <v>0.441227896215501</v>
+        <v>0.4965545241555209</v>
       </c>
       <c r="J491">
-        <v>-0.2328540737068246</v>
+        <v>-0.2212877012960047</v>
       </c>
       <c r="K491">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L491">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M491">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N491">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O491">
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="492" spans="1:16">
       <c r="A492" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B492" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C492">
-        <v>3.432024458767145</v>
+        <v>2.43983969591803</v>
       </c>
       <c r="D492" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E492">
-        <v>2.797782184762848</v>
+        <v>2.88106759213353</v>
       </c>
       <c r="F492">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G492">
-        <v>0.002807975541232855</v>
+        <v>0.001960160304081971</v>
       </c>
       <c r="H492">
-        <v>0.002262217815237151</v>
+        <v>0.002298932407866469</v>
       </c>
       <c r="I492">
-        <v>0.634242274004297</v>
+        <v>0.441227896215501</v>
       </c>
       <c r="J492">
         <v>-0.2328540737068246</v>
       </c>
       <c r="K492">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L492">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M492">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N492">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O492">
         <v>1</v>
@@ -25999,13 +25999,13 @@
     </row>
     <row r="493" spans="1:16">
       <c r="A493" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B493" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C493">
-        <v>3.295724673607667</v>
+        <v>3.432024458767145</v>
       </c>
       <c r="D493" t="s">
         <v>130</v>
@@ -26017,22 +26017,22 @@
         <v>-1</v>
       </c>
       <c r="G493">
-        <v>0.002704275326392333</v>
+        <v>0.002807975541232855</v>
       </c>
       <c r="H493">
         <v>0.002262217815237151</v>
       </c>
       <c r="I493">
-        <v>0.497942488844819</v>
+        <v>0.634242274004297</v>
       </c>
       <c r="J493">
         <v>-0.2328540737068246</v>
       </c>
       <c r="K493">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L493">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M493">
         <v>1.15</v>
@@ -26049,96 +26049,96 @@
     </row>
     <row r="494" spans="1:16">
       <c r="A494" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B494" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C494">
-        <v>2.478555931094635</v>
+        <v>3.295724673607667</v>
       </c>
       <c r="D494" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E494">
-        <v>2.928053314435237</v>
+        <v>2.797782184762848</v>
       </c>
       <c r="F494">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G494">
-        <v>0.001921444068905365</v>
+        <v>0.002704275326392333</v>
       </c>
       <c r="H494">
-        <v>0.002251946685564763</v>
+        <v>0.002262217815237151</v>
       </c>
       <c r="I494">
-        <v>0.4494973833406015</v>
+        <v>0.497942488844819</v>
       </c>
       <c r="J494">
-        <v>-0.2704426515481894</v>
+        <v>-0.2328540737068246</v>
       </c>
       <c r="K494">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L494">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M494">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N494">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O494">
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="495" spans="1:16">
       <c r="A495" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B495" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C495">
-        <v>3.482393153074574</v>
+        <v>2.478555931094635</v>
       </c>
       <c r="D495" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E495">
-        <v>2.841009049280418</v>
+        <v>2.928053314435237</v>
       </c>
       <c r="F495">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G495">
-        <v>0.002757606846925426</v>
+        <v>0.001921444068905365</v>
       </c>
       <c r="H495">
-        <v>0.002218990950719582</v>
+        <v>0.002251946685564763</v>
       </c>
       <c r="I495">
-        <v>0.6413841037941563</v>
+        <v>0.4494973833406015</v>
       </c>
       <c r="J495">
         <v>-0.2704426515481894</v>
       </c>
       <c r="K495">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L495">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M495">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N495">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O495">
         <v>1</v>
@@ -26149,13 +26149,13 @@
     </row>
     <row r="496" spans="1:16">
       <c r="A496" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B496" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C496">
-        <v>3.343462167466201</v>
+        <v>3.482393153074574</v>
       </c>
       <c r="D496" t="s">
         <v>130</v>
@@ -26167,22 +26167,22 @@
         <v>-1</v>
       </c>
       <c r="G496">
-        <v>0.002656537832533799</v>
+        <v>0.002757606846925426</v>
       </c>
       <c r="H496">
         <v>0.002218990950719582</v>
       </c>
       <c r="I496">
-        <v>0.502453118185783</v>
+        <v>0.6413841037941563</v>
       </c>
       <c r="J496">
         <v>-0.2704426515481894</v>
       </c>
       <c r="K496">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L496">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M496">
         <v>1.15</v>
@@ -26199,96 +26199,96 @@
     </row>
     <row r="497" spans="1:16">
       <c r="A497" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B497" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C497">
-        <v>2.492450104171095</v>
+        <v>3.343462167466201</v>
       </c>
       <c r="D497" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E497">
-        <v>2.944915174964921</v>
+        <v>2.841009049280418</v>
       </c>
       <c r="F497">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G497">
-        <v>0.001907549895828906</v>
+        <v>0.002656537832533799</v>
       </c>
       <c r="H497">
-        <v>0.002235084825035079</v>
+        <v>0.002218990950719582</v>
       </c>
       <c r="I497">
-        <v>0.4524650707938256</v>
+        <v>0.502453118185783</v>
       </c>
       <c r="J497">
-        <v>-0.2839321399719367</v>
+        <v>-0.2704426515481894</v>
       </c>
       <c r="K497">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L497">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M497">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N497">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O497">
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="498" spans="1:16">
       <c r="A498" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B498" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C498">
-        <v>3.500469067562396</v>
+        <v>2.492450104171095</v>
       </c>
       <c r="D498" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E498">
-        <v>2.856521960967727</v>
+        <v>2.944915174964921</v>
       </c>
       <c r="F498">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G498">
-        <v>0.002739530932437605</v>
+        <v>0.001907549895828906</v>
       </c>
       <c r="H498">
-        <v>0.002203478039032273</v>
+        <v>0.002235084825035079</v>
       </c>
       <c r="I498">
-        <v>0.6439471065946685</v>
+        <v>0.4524650707938256</v>
       </c>
       <c r="J498">
         <v>-0.2839321399719367</v>
       </c>
       <c r="K498">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L498">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M498">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N498">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O498">
         <v>1</v>
@@ -26299,13 +26299,13 @@
     </row>
     <row r="499" spans="1:16">
       <c r="A499" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B499" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C499">
-        <v>3.36059381776436</v>
+        <v>3.500469067562396</v>
       </c>
       <c r="D499" t="s">
         <v>130</v>
@@ -26317,22 +26317,22 @@
         <v>-1</v>
       </c>
       <c r="G499">
-        <v>0.002639406182235641</v>
+        <v>0.002739530932437605</v>
       </c>
       <c r="H499">
         <v>0.002203478039032273</v>
       </c>
       <c r="I499">
-        <v>0.5040718567966325</v>
+        <v>0.6439471065946685</v>
       </c>
       <c r="J499">
         <v>-0.2839321399719367</v>
       </c>
       <c r="K499">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L499">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M499">
         <v>1.15</v>
@@ -26349,96 +26349,96 @@
     </row>
     <row r="500" spans="1:16">
       <c r="A500" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B500" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C500">
-        <v>2.485588290136117</v>
+        <v>3.36059381776436</v>
       </c>
       <c r="D500" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E500">
-        <v>2.936587730747715</v>
+        <v>2.856521960967727</v>
       </c>
       <c r="F500">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G500">
-        <v>0.001914411709863883</v>
+        <v>0.002639406182235641</v>
       </c>
       <c r="H500">
-        <v>0.002243412269252285</v>
+        <v>0.002203478039032273</v>
       </c>
       <c r="I500">
-        <v>0.4509994406115978</v>
+        <v>0.5040718567966325</v>
       </c>
       <c r="J500">
-        <v>-0.2772701845981717</v>
+        <v>-0.2839321399719367</v>
       </c>
       <c r="K500">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L500">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M500">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N500">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O500">
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="501" spans="1:16">
       <c r="A501" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B501" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C501">
-        <v>3.49154204736155</v>
+        <v>2.485588290136117</v>
       </c>
       <c r="D501" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E501">
-        <v>2.848860712287897</v>
+        <v>2.936587730747715</v>
       </c>
       <c r="F501">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G501">
-        <v>0.00274845795263845</v>
+        <v>0.001914411709863883</v>
       </c>
       <c r="H501">
-        <v>0.002211139287712102</v>
+        <v>0.002243412269252285</v>
       </c>
       <c r="I501">
-        <v>0.6426813350736529</v>
+        <v>0.4509994406115978</v>
       </c>
       <c r="J501">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K501">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L501">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M501">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N501">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O501">
         <v>1</v>
@@ -26449,13 +26449,13 @@
     </row>
     <row r="502" spans="1:16">
       <c r="A502" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B502" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C502">
-        <v>3.352133134439678</v>
+        <v>3.49154204736155</v>
       </c>
       <c r="D502" t="s">
         <v>130</v>
@@ -26467,22 +26467,22 @@
         <v>-1</v>
       </c>
       <c r="G502">
-        <v>0.002647866865560322</v>
+        <v>0.00274845795263845</v>
       </c>
       <c r="H502">
         <v>0.002211139287712102</v>
       </c>
       <c r="I502">
-        <v>0.503272422151781</v>
+        <v>0.6426813350736529</v>
       </c>
       <c r="J502">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K502">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L502">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M502">
         <v>1.15</v>
@@ -26499,96 +26499,96 @@
     </row>
     <row r="503" spans="1:16">
       <c r="A503" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B503" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C503">
-        <v>2.483803138304734</v>
+        <v>3.352133134439678</v>
       </c>
       <c r="D503" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E503">
-        <v>2.934421284350405</v>
+        <v>2.848860712287897</v>
       </c>
       <c r="F503">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G503">
-        <v>0.001916196861695266</v>
+        <v>0.002647866865560322</v>
       </c>
       <c r="H503">
-        <v>0.002245578715649595</v>
+        <v>0.002211139287712102</v>
       </c>
       <c r="I503">
-        <v>0.4506181460456711</v>
+        <v>0.503272422151781</v>
       </c>
       <c r="J503">
-        <v>-0.2755370274803244</v>
+        <v>-0.2772701845981717</v>
       </c>
       <c r="K503">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L503">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M503">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N503">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O503">
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="504" spans="1:16">
       <c r="A504" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B504" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C504">
-        <v>3.489219616823635</v>
+        <v>2.483803138304734</v>
       </c>
       <c r="D504" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E504">
-        <v>2.846867581602373</v>
+        <v>2.934421284350405</v>
       </c>
       <c r="F504">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G504">
-        <v>0.002750780383176366</v>
+        <v>0.001916196861695266</v>
       </c>
       <c r="H504">
-        <v>0.002213132418397626</v>
+        <v>0.002245578715649595</v>
       </c>
       <c r="I504">
-        <v>0.6423520352212617</v>
+        <v>0.4506181460456711</v>
       </c>
       <c r="J504">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K504">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L504">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M504">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N504">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O504">
         <v>1</v>
@@ -26599,13 +26599,13 @@
     </row>
     <row r="505" spans="1:16">
       <c r="A505" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B505" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C505">
-        <v>3.349932024900012</v>
+        <v>3.489219616823635</v>
       </c>
       <c r="D505" t="s">
         <v>130</v>
@@ -26617,22 +26617,22 @@
         <v>-1</v>
       </c>
       <c r="G505">
-        <v>0.002650067975099988</v>
+        <v>0.002750780383176366</v>
       </c>
       <c r="H505">
         <v>0.002213132418397626</v>
       </c>
       <c r="I505">
-        <v>0.5030644432976388</v>
+        <v>0.6423520352212617</v>
       </c>
       <c r="J505">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K505">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L505">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M505">
         <v>1.15</v>
@@ -26649,96 +26649,96 @@
     </row>
     <row r="506" spans="1:16">
       <c r="A506" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B506" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C506">
-        <v>2.455324757264537</v>
+        <v>3.349932024900012</v>
       </c>
       <c r="D506" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E506">
-        <v>2.899860142311331</v>
+        <v>2.846867581602373</v>
       </c>
       <c r="F506">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G506">
-        <v>0.001944675242735464</v>
+        <v>0.002650067975099988</v>
       </c>
       <c r="H506">
-        <v>0.002280139857688669</v>
+        <v>0.002213132418397626</v>
       </c>
       <c r="I506">
-        <v>0.4445353850467941</v>
+        <v>0.5030644432976388</v>
       </c>
       <c r="J506">
-        <v>-0.2478881138490649</v>
+        <v>-0.2755370274803244</v>
       </c>
       <c r="K506">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L506">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M506">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N506">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O506">
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="507" spans="1:16">
       <c r="A507" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B507" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C507">
-        <v>3.452170072557747</v>
+        <v>2.455324757264537</v>
       </c>
       <c r="D507" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E507">
-        <v>2.815071330926425</v>
+        <v>2.899860142311331</v>
       </c>
       <c r="F507">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G507">
-        <v>0.002787829927442253</v>
+        <v>0.001944675242735464</v>
       </c>
       <c r="H507">
-        <v>0.002244928669073575</v>
+        <v>0.002280139857688669</v>
       </c>
       <c r="I507">
-        <v>0.6370987416313225</v>
+        <v>0.4445353850467941</v>
       </c>
       <c r="J507">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K507">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L507">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M507">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N507">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O507">
         <v>1</v>
@@ -26749,13 +26749,13 @@
     </row>
     <row r="508" spans="1:16">
       <c r="A508" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B508" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C508">
-        <v>3.314817904588312</v>
+        <v>3.452170072557747</v>
       </c>
       <c r="D508" t="s">
         <v>130</v>
@@ -26767,22 +26767,22 @@
         <v>-1</v>
       </c>
       <c r="G508">
-        <v>0.002685182095411688</v>
+        <v>0.002787829927442253</v>
       </c>
       <c r="H508">
         <v>0.002244928669073575</v>
       </c>
       <c r="I508">
-        <v>0.4997465736618878</v>
+        <v>0.6370987416313225</v>
       </c>
       <c r="J508">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K508">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L508">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M508">
         <v>1.15</v>
@@ -26799,96 +26799,96 @@
     </row>
     <row r="509" spans="1:16">
       <c r="A509" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B509" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C509">
-        <v>2.38683909149</v>
+        <v>3.314817904588312</v>
       </c>
       <c r="D509" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E509">
-        <v>2.816746470254853</v>
+        <v>2.815071330926425</v>
       </c>
       <c r="F509">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G509">
-        <v>0.002013160908510001</v>
+        <v>0.002685182095411688</v>
       </c>
       <c r="H509">
-        <v>0.002363253529745146</v>
+        <v>0.002244928669073575</v>
       </c>
       <c r="I509">
-        <v>0.4299073787648537</v>
+        <v>0.4997465736618878</v>
       </c>
       <c r="J509">
-        <v>-0.181397176203883</v>
+        <v>-0.2478881138490649</v>
       </c>
       <c r="K509">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L509">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M509">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N509">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O509">
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="510" spans="1:16">
       <c r="A510" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B510" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C510">
-        <v>3.363072216113203</v>
+        <v>2.38683909149</v>
       </c>
       <c r="D510" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E510">
-        <v>2.738606752634465</v>
+        <v>2.816746470254853</v>
       </c>
       <c r="F510">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G510">
-        <v>0.002876927783886797</v>
+        <v>0.002013160908510001</v>
       </c>
       <c r="H510">
-        <v>0.002321393247365534</v>
+        <v>0.002363253529745146</v>
       </c>
       <c r="I510">
-        <v>0.6244654634787379</v>
+        <v>0.4299073787648537</v>
       </c>
       <c r="J510">
         <v>-0.181397176203883</v>
       </c>
       <c r="K510">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L510">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M510">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N510">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O510">
         <v>1</v>
@@ -26899,13 +26899,13 @@
     </row>
     <row r="511" spans="1:16">
       <c r="A511" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B511" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C511">
-        <v>3.230374413778931</v>
+        <v>3.363072216113203</v>
       </c>
       <c r="D511" t="s">
         <v>130</v>
@@ -26917,22 +26917,22 @@
         <v>-1</v>
       </c>
       <c r="G511">
-        <v>0.002769625586221069</v>
+        <v>0.002876927783886797</v>
       </c>
       <c r="H511">
         <v>0.002321393247365534</v>
       </c>
       <c r="I511">
-        <v>0.4917676611444661</v>
+        <v>0.6244654634787379</v>
       </c>
       <c r="J511">
         <v>-0.181397176203883</v>
       </c>
       <c r="K511">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L511">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M511">
         <v>1.15</v>
@@ -26949,96 +26949,96 @@
     </row>
     <row r="512" spans="1:16">
       <c r="A512" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B512" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C512">
-        <v>2.332831092936091</v>
+        <v>3.230374413778931</v>
       </c>
       <c r="D512" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E512">
-        <v>2.751202782689431</v>
+        <v>2.738606752634465</v>
       </c>
       <c r="F512">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G512">
-        <v>0.002067168907063909</v>
+        <v>0.002769625586221069</v>
       </c>
       <c r="H512">
-        <v>0.002428797217310569</v>
+        <v>0.002321393247365534</v>
       </c>
       <c r="I512">
-        <v>0.4183716897533394</v>
+        <v>0.4917676611444661</v>
       </c>
       <c r="J512">
-        <v>-0.1289622261515449</v>
+        <v>-0.181397176203883</v>
       </c>
       <c r="K512">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L512">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M512">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N512">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O512">
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="513" spans="1:16">
       <c r="A513" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B513" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C513">
-        <v>3.29280938304307</v>
+        <v>2.332831092936091</v>
       </c>
       <c r="D513" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E513">
-        <v>2.678306560074276</v>
+        <v>2.751202782689431</v>
       </c>
       <c r="F513">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G513">
-        <v>0.00294719061695693</v>
+        <v>0.002067168907063909</v>
       </c>
       <c r="H513">
-        <v>0.002381693439925723</v>
+        <v>0.002428797217310569</v>
       </c>
       <c r="I513">
-        <v>0.6145028229687939</v>
+        <v>0.4183716897533394</v>
       </c>
       <c r="J513">
         <v>-0.1289622261515449</v>
       </c>
       <c r="K513">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L513">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M513">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N513">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O513">
         <v>1</v>
@@ -27049,13 +27049,13 @@
     </row>
     <row r="514" spans="1:16">
       <c r="A514" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B514" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C514">
-        <v>3.163782027212462</v>
+        <v>3.29280938304307</v>
       </c>
       <c r="D514" t="s">
         <v>130</v>
@@ -27067,22 +27067,22 @@
         <v>-1</v>
       </c>
       <c r="G514">
-        <v>0.002836217972787538</v>
+        <v>0.00294719061695693</v>
       </c>
       <c r="H514">
         <v>0.002381693439925723</v>
       </c>
       <c r="I514">
-        <v>0.4854754671381856</v>
+        <v>0.6145028229687939</v>
       </c>
       <c r="J514">
         <v>-0.1289622261515449</v>
       </c>
       <c r="K514">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L514">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M514">
         <v>1.15</v>
@@ -27099,96 +27099,96 @@
     </row>
     <row r="515" spans="1:16">
       <c r="A515" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B515" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C515">
-        <v>2.292718610119939</v>
+        <v>3.163782027212462</v>
       </c>
       <c r="D515" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E515">
-        <v>2.702522585097013</v>
+        <v>2.678306560074276</v>
       </c>
       <c r="F515">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G515">
-        <v>0.002107281389880062</v>
+        <v>0.002836217972787538</v>
       </c>
       <c r="H515">
-        <v>0.002477477414902987</v>
+        <v>0.002381693439925723</v>
       </c>
       <c r="I515">
-        <v>0.4098039749770739</v>
+        <v>0.4854754671381856</v>
       </c>
       <c r="J515">
-        <v>-0.09001806807761016</v>
+        <v>-0.1289622261515449</v>
       </c>
       <c r="K515">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L515">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M515">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N515">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O515">
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="516" spans="1:16">
       <c r="A516" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B516" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C516">
-        <v>3.240624211223998</v>
+        <v>2.292718610119939</v>
       </c>
       <c r="D516" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E516">
-        <v>2.633520778289252</v>
+        <v>2.702522585097013</v>
       </c>
       <c r="F516">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G516">
-        <v>0.002999375788776002</v>
+        <v>0.002107281389880062</v>
       </c>
       <c r="H516">
-        <v>0.002426479221710748</v>
+        <v>0.002477477414902987</v>
       </c>
       <c r="I516">
-        <v>0.6071034329347462</v>
+        <v>0.4098039749770739</v>
       </c>
       <c r="J516">
         <v>-0.09001806807761016</v>
       </c>
       <c r="K516">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L516">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M516">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N516">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O516">
         <v>1</v>
@@ -27199,13 +27199,13 @@
     </row>
     <row r="517" spans="1:16">
       <c r="A517" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B517" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C517">
-        <v>3.114322946458565</v>
+        <v>3.240624211223998</v>
       </c>
       <c r="D517" t="s">
         <v>130</v>
@@ -27217,22 +27217,22 @@
         <v>-1</v>
       </c>
       <c r="G517">
-        <v>0.002885677053541435</v>
+        <v>0.002999375788776002</v>
       </c>
       <c r="H517">
         <v>0.002426479221710748</v>
       </c>
       <c r="I517">
-        <v>0.4808021681693133</v>
+        <v>0.6071034329347462</v>
       </c>
       <c r="J517">
         <v>-0.09001806807761016</v>
       </c>
       <c r="K517">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L517">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M517">
         <v>1.15</v>
@@ -27249,96 +27249,96 @@
     </row>
     <row r="518" spans="1:16">
       <c r="A518" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B518" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C518">
-        <v>2.190845625202192</v>
+        <v>3.114322946458565</v>
       </c>
       <c r="D518" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E518">
-        <v>2.57889032184732</v>
+        <v>2.633520778289252</v>
       </c>
       <c r="F518">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G518">
-        <v>0.002209154374797808</v>
+        <v>0.002885677053541435</v>
       </c>
       <c r="H518">
-        <v>0.00260110967815268</v>
+        <v>0.002426479221710748</v>
       </c>
       <c r="I518">
-        <v>0.3880446966451281</v>
+        <v>0.4808021681693133</v>
       </c>
       <c r="J518">
-        <v>0.008887742522143843</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K518">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L518">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M518">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N518">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O518">
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="519" spans="1:16">
       <c r="A519" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B519" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C519">
-        <v>3.108090425020327</v>
+        <v>2.190845625202192</v>
       </c>
       <c r="D519" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E519">
-        <v>2.519779096099534</v>
+        <v>2.57889032184732</v>
       </c>
       <c r="F519">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G519">
-        <v>0.003131909574979673</v>
+        <v>0.002209154374797808</v>
       </c>
       <c r="H519">
-        <v>0.002540220903900465</v>
+        <v>0.00260110967815268</v>
       </c>
       <c r="I519">
-        <v>0.5883113289207929</v>
+        <v>0.3880446966451281</v>
       </c>
       <c r="J519">
         <v>0.008887742522143843</v>
       </c>
       <c r="K519">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L519">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M519">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N519">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O519">
         <v>1</v>
@@ -27349,13 +27349,13 @@
     </row>
     <row r="520" spans="1:16">
       <c r="A520" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B520" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C520">
-        <v>2.988712566996877</v>
+        <v>3.108090425020327</v>
       </c>
       <c r="D520" t="s">
         <v>130</v>
@@ -27367,22 +27367,22 @@
         <v>-1</v>
       </c>
       <c r="G520">
-        <v>0.003011287433003123</v>
+        <v>0.003131909574979673</v>
       </c>
       <c r="H520">
         <v>0.002540220903900465</v>
       </c>
       <c r="I520">
-        <v>0.4689334708973432</v>
+        <v>0.5883113289207929</v>
       </c>
       <c r="J520">
         <v>0.008887742522143843</v>
       </c>
       <c r="K520">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L520">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M520">
         <v>1.15</v>
@@ -27399,96 +27399,96 @@
     </row>
     <row r="521" spans="1:16">
       <c r="A521" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B521" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C521">
-        <v>2.151298027264343</v>
+        <v>2.988712566996877</v>
       </c>
       <c r="D521" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E521">
-        <v>2.530895664155756</v>
+        <v>2.519779096099534</v>
       </c>
       <c r="F521">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G521">
-        <v>0.002248701972735657</v>
+        <v>0.003011287433003123</v>
       </c>
       <c r="H521">
-        <v>0.002649104335844244</v>
+        <v>0.002540220903900465</v>
       </c>
       <c r="I521">
-        <v>0.3795976368914125</v>
+        <v>0.4689334708973432</v>
       </c>
       <c r="J521">
-        <v>0.04728346867539508</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K521">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L521">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M521">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N521">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O521">
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="522" spans="1:16">
       <c r="A522" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B522" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C522">
-        <v>3.056640151974971</v>
+        <v>2.151298027264343</v>
       </c>
       <c r="D522" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E522">
-        <v>2.475624011023295</v>
+        <v>2.530895664155756</v>
       </c>
       <c r="F522">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G522">
-        <v>0.00318335984802503</v>
+        <v>0.002248701972735657</v>
       </c>
       <c r="H522">
-        <v>0.002584375988976704</v>
+        <v>0.002649104335844244</v>
       </c>
       <c r="I522">
-        <v>0.5810161409516752</v>
+        <v>0.3795976368914125</v>
       </c>
       <c r="J522">
         <v>0.04728346867539508</v>
       </c>
       <c r="K522">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L522">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M522">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N522">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27499,13 +27499,13 @@
     </row>
     <row r="523" spans="1:16">
       <c r="A523" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B523" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C523">
-        <v>2.939949994782248</v>
+        <v>3.056640151974971</v>
       </c>
       <c r="D523" t="s">
         <v>130</v>
@@ -27517,22 +27517,22 @@
         <v>-1</v>
       </c>
       <c r="G523">
-        <v>0.003060050005217752</v>
+        <v>0.00318335984802503</v>
       </c>
       <c r="H523">
         <v>0.002584375988976704</v>
       </c>
       <c r="I523">
-        <v>0.4643259837589526</v>
+        <v>0.5810161409516752</v>
       </c>
       <c r="J523">
         <v>0.04728346867539508</v>
       </c>
       <c r="K523">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L523">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M523">
         <v>1.15</v>
@@ -27549,96 +27549,96 @@
     </row>
     <row r="524" spans="1:16">
       <c r="A524" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B524" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C524">
-        <v>2.129744886456478</v>
+        <v>2.939949994782248</v>
       </c>
       <c r="D524" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E524">
-        <v>2.504738939874366</v>
+        <v>2.475624011023295</v>
       </c>
       <c r="F524">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G524">
-        <v>0.002270255113543523</v>
+        <v>0.003060050005217752</v>
       </c>
       <c r="H524">
-        <v>0.002675261060125634</v>
+        <v>0.002584375988976704</v>
       </c>
       <c r="I524">
-        <v>0.3749940534178879</v>
+        <v>0.4643259837589526</v>
       </c>
       <c r="J524">
-        <v>0.06820884810050738</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K524">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L524">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M524">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N524">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O524">
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="525" spans="1:16">
       <c r="A525" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B525" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C525">
-        <v>3.02860014354532</v>
+        <v>2.129744886456478</v>
       </c>
       <c r="D525" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E525">
-        <v>2.451559824684416</v>
+        <v>2.504738939874366</v>
       </c>
       <c r="F525">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G525">
-        <v>0.00321139985645468</v>
+        <v>0.002270255113543523</v>
       </c>
       <c r="H525">
-        <v>0.002608440175315583</v>
+        <v>0.002675261060125634</v>
       </c>
       <c r="I525">
-        <v>0.5770403188609037</v>
+        <v>0.3749940534178879</v>
       </c>
       <c r="J525">
         <v>0.06820884810050738</v>
       </c>
       <c r="K525">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L525">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M525">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N525">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O525">
         <v>1</v>
@@ -27649,13 +27649,13 @@
     </row>
     <row r="526" spans="1:16">
       <c r="A526" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B526" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C526">
-        <v>2.913374762912356</v>
+        <v>3.02860014354532</v>
       </c>
       <c r="D526" t="s">
         <v>130</v>
@@ -27667,22 +27667,22 @@
         <v>-1</v>
       </c>
       <c r="G526">
-        <v>0.003086625237087645</v>
+        <v>0.00321139985645468</v>
       </c>
       <c r="H526">
         <v>0.002608440175315583</v>
       </c>
       <c r="I526">
-        <v>0.4618149382279393</v>
+        <v>0.5770403188609037</v>
       </c>
       <c r="J526">
         <v>0.06820884810050738</v>
       </c>
       <c r="K526">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L526">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M526">
         <v>1.15</v>
@@ -27699,96 +27699,96 @@
     </row>
     <row r="527" spans="1:16">
       <c r="A527" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B527" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C527">
-        <v>2.123592991344732</v>
+        <v>2.913374762912356</v>
       </c>
       <c r="D527" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E527">
-        <v>2.497273047748461</v>
+        <v>2.451559824684416</v>
       </c>
       <c r="F527">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G527">
-        <v>0.002276407008655268</v>
+        <v>0.003086625237087645</v>
       </c>
       <c r="H527">
-        <v>0.002682726952251539</v>
+        <v>0.002608440175315583</v>
       </c>
       <c r="I527">
-        <v>0.3736800564037286</v>
+        <v>0.4618149382279393</v>
       </c>
       <c r="J527">
-        <v>0.07418156180123091</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K527">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L527">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M527">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N527">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O527">
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="528" spans="1:16">
       <c r="A528" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B528" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C528">
-        <v>3.020596707186351</v>
+        <v>2.123592991344732</v>
       </c>
       <c r="D528" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E528">
-        <v>2.444691203928584</v>
+        <v>2.497273047748461</v>
       </c>
       <c r="F528">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G528">
-        <v>0.00321940329281365</v>
+        <v>0.002276407008655268</v>
       </c>
       <c r="H528">
-        <v>0.002615308796071415</v>
+        <v>0.002682726952251539</v>
       </c>
       <c r="I528">
-        <v>0.5759055032577662</v>
+        <v>0.3736800564037286</v>
       </c>
       <c r="J528">
         <v>0.07418156180123091</v>
       </c>
       <c r="K528">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L528">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M528">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N528">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -27799,13 +27799,13 @@
     </row>
     <row r="529" spans="1:16">
       <c r="A529" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B529" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C529">
-        <v>2.905789416512437</v>
+        <v>3.020596707186351</v>
       </c>
       <c r="D529" t="s">
         <v>130</v>
@@ -27817,22 +27817,22 @@
         <v>-1</v>
       </c>
       <c r="G529">
-        <v>0.003094210583487563</v>
+        <v>0.00321940329281365</v>
       </c>
       <c r="H529">
         <v>0.002615308796071415</v>
       </c>
       <c r="I529">
-        <v>0.4610982125838525</v>
+        <v>0.5759055032577662</v>
       </c>
       <c r="J529">
         <v>0.07418156180123091</v>
       </c>
       <c r="K529">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L529">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M529">
         <v>1.15</v>
@@ -27849,96 +27849,96 @@
     </row>
     <row r="530" spans="1:16">
       <c r="A530" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B530" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C530">
-        <v>2.162997802089755</v>
+        <v>2.905789416512437</v>
       </c>
       <c r="D530" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E530">
-        <v>2.545094420011838</v>
+        <v>2.444691203928584</v>
       </c>
       <c r="F530">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G530">
-        <v>0.002237002197910246</v>
+        <v>0.003094210583487563</v>
       </c>
       <c r="H530">
-        <v>0.002634905579988162</v>
+        <v>0.002615308796071415</v>
       </c>
       <c r="I530">
-        <v>0.382096617922083</v>
+        <v>0.4610982125838525</v>
       </c>
       <c r="J530">
-        <v>0.03592446399052947</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K530">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L530">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M530">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N530">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O530">
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="531" spans="1:16">
       <c r="A531" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B531" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C531">
-        <v>3.071861218252691</v>
+        <v>2.162997802089755</v>
       </c>
       <c r="D531" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E531">
-        <v>2.488686866410891</v>
+        <v>2.545094420011838</v>
       </c>
       <c r="F531">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G531">
-        <v>0.00316813878174731</v>
+        <v>0.002237002197910246</v>
       </c>
       <c r="H531">
-        <v>0.002571313133589109</v>
+        <v>0.002634905579988162</v>
       </c>
       <c r="I531">
-        <v>0.5831743518417998</v>
+        <v>0.382096617922083</v>
       </c>
       <c r="J531">
         <v>0.03592446399052947</v>
       </c>
       <c r="K531">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L531">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M531">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N531">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -27949,13 +27949,13 @@
     </row>
     <row r="532" spans="1:16">
       <c r="A532" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B532" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C532">
-        <v>2.954375930732028</v>
+        <v>3.071861218252691</v>
       </c>
       <c r="D532" t="s">
         <v>130</v>
@@ -27967,22 +27967,22 @@
         <v>-1</v>
       </c>
       <c r="G532">
-        <v>0.003045624069267972</v>
+        <v>0.00316813878174731</v>
       </c>
       <c r="H532">
         <v>0.002571313133589109</v>
       </c>
       <c r="I532">
-        <v>0.4656890643211367</v>
+        <v>0.5831743518417998</v>
       </c>
       <c r="J532">
         <v>0.03592446399052947</v>
       </c>
       <c r="K532">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L532">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M532">
         <v>1.15</v>
@@ -27999,96 +27999,96 @@
     </row>
     <row r="533" spans="1:16">
       <c r="A533" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B533" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C533">
-        <v>2.152181822645585</v>
+        <v>2.954375930732028</v>
       </c>
       <c r="D533" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E533">
-        <v>2.531968231366001</v>
+        <v>2.488686866410891</v>
       </c>
       <c r="F533">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G533">
-        <v>0.002247818177354416</v>
+        <v>0.003045624069267972</v>
       </c>
       <c r="H533">
-        <v>0.002648031768633999</v>
+        <v>0.002571313133589109</v>
       </c>
       <c r="I533">
-        <v>0.3797864087204159</v>
+        <v>0.4656890643211367</v>
       </c>
       <c r="J533">
-        <v>0.04642541490719935</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K533">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L533">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M533">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N533">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O533">
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="534" spans="1:16">
       <c r="A534" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B534" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C534">
-        <v>3.057789944024353</v>
+        <v>2.152181822645585</v>
       </c>
       <c r="D534" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E534">
-        <v>2.47661077285672</v>
+        <v>2.531968231366001</v>
       </c>
       <c r="F534">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G534">
-        <v>0.003182210055975647</v>
+        <v>0.002247818177354416</v>
       </c>
       <c r="H534">
-        <v>0.002583389227143279</v>
+        <v>0.002648031768633999</v>
       </c>
       <c r="I534">
-        <v>0.5811791711676326</v>
+        <v>0.3797864087204159</v>
       </c>
       <c r="J534">
         <v>0.04642541490719935</v>
       </c>
       <c r="K534">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L534">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M534">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N534">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O534">
         <v>1</v>
@@ -28099,13 +28099,13 @@
     </row>
     <row r="535" spans="1:16">
       <c r="A535" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B535" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C535">
-        <v>2.941039723067857</v>
+        <v>3.057789944024353</v>
       </c>
       <c r="D535" t="s">
         <v>130</v>
@@ -28117,22 +28117,22 @@
         <v>-1</v>
       </c>
       <c r="G535">
-        <v>0.003058960276932143</v>
+        <v>0.003182210055975647</v>
       </c>
       <c r="H535">
         <v>0.002583389227143279</v>
       </c>
       <c r="I535">
-        <v>0.4644289502111363</v>
+        <v>0.5811791711676326</v>
       </c>
       <c r="J535">
         <v>0.04642541490719935</v>
       </c>
       <c r="K535">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L535">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M535">
         <v>1.15</v>
@@ -28149,96 +28149,96 @@
     </row>
     <row r="536" spans="1:16">
       <c r="A536" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B536" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C536">
-        <v>2.132867933343715</v>
+        <v>2.941039723067857</v>
       </c>
       <c r="D536" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E536">
-        <v>2.508529045320043</v>
+        <v>2.47661077285672</v>
       </c>
       <c r="F536">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G536">
-        <v>0.002267132066656285</v>
+        <v>0.003058960276932143</v>
       </c>
       <c r="H536">
-        <v>0.002671470954679957</v>
+        <v>0.002583389227143279</v>
       </c>
       <c r="I536">
-        <v>0.3756611119763273</v>
+        <v>0.4644289502111363</v>
       </c>
       <c r="J536">
-        <v>0.06517676374396589</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K536">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L536">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M536">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N536">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O536">
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="537" spans="1:16">
       <c r="A537" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B537" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C537">
-        <v>3.032663136583086</v>
+        <v>2.132867933343715</v>
       </c>
       <c r="D537" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E537">
-        <v>2.455046721694439</v>
+        <v>2.508529045320043</v>
       </c>
       <c r="F537">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G537">
-        <v>0.003207336863416915</v>
+        <v>0.002267132066656285</v>
       </c>
       <c r="H537">
-        <v>0.002604953278305561</v>
+        <v>0.002671470954679957</v>
       </c>
       <c r="I537">
-        <v>0.5776164148886465</v>
+        <v>0.3756611119763273</v>
       </c>
       <c r="J537">
         <v>0.06517676374396589</v>
       </c>
       <c r="K537">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L537">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M537">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N537">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O537">
         <v>1</v>
@@ -28249,13 +28249,13 @@
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B538" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C538">
-        <v>2.917225510045163</v>
+        <v>3.032663136583086</v>
       </c>
       <c r="D538" t="s">
         <v>130</v>
@@ -28267,22 +28267,22 @@
         <v>-1</v>
       </c>
       <c r="G538">
-        <v>0.003082774489954837</v>
+        <v>0.003207336863416915</v>
       </c>
       <c r="H538">
         <v>0.002604953278305561</v>
       </c>
       <c r="I538">
-        <v>0.462178788350724</v>
+        <v>0.5776164148886465</v>
       </c>
       <c r="J538">
         <v>0.06517676374396589</v>
       </c>
       <c r="K538">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L538">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M538">
         <v>1.15</v>
@@ -28299,96 +28299,96 @@
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B539" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C539">
-        <v>2.104641124313295</v>
+        <v>2.917225510045163</v>
       </c>
       <c r="D539" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E539">
-        <v>2.474273209118076</v>
+        <v>2.455046721694439</v>
       </c>
       <c r="F539">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G539">
-        <v>0.002295358875686706</v>
+        <v>0.003082774489954837</v>
       </c>
       <c r="H539">
-        <v>0.002705726790881924</v>
+        <v>0.002604953278305561</v>
       </c>
       <c r="I539">
-        <v>0.3696320848047812</v>
+        <v>0.462178788350724</v>
       </c>
       <c r="J539">
-        <v>0.09258143270553931</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K539">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L539">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M539">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N539">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O539">
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="540" spans="1:16">
       <c r="A540" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B540" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C540">
-        <v>2.995940880174577</v>
+        <v>2.104641124313295</v>
       </c>
       <c r="D540" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E540">
-        <v>2.423531352388629</v>
+        <v>2.474273209118076</v>
       </c>
       <c r="F540">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G540">
-        <v>0.003244059119825423</v>
+        <v>0.002295358875686706</v>
       </c>
       <c r="H540">
-        <v>0.00263646864761137</v>
+        <v>0.002705726790881924</v>
       </c>
       <c r="I540">
-        <v>0.5724095277859478</v>
+        <v>0.3696320848047812</v>
       </c>
       <c r="J540">
         <v>0.09258143270553931</v>
       </c>
       <c r="K540">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L540">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M540">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N540">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28399,46 +28399,46 @@
     </row>
     <row r="541" spans="1:16">
       <c r="A541" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B541" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C541">
-        <v>2.882421580463965</v>
+        <v>2.995940880174577</v>
       </c>
       <c r="D541" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E541">
-        <v>2.423531352388629</v>
+        <v>2.471679723734519</v>
       </c>
       <c r="F541">
         <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.003117578419536035</v>
+        <v>0.003244059119825423</v>
       </c>
       <c r="H541">
-        <v>0.00263646864761137</v>
+        <v>0.002688320276265481</v>
       </c>
       <c r="I541">
-        <v>0.4588902280753357</v>
+        <v>0.5242611564400583</v>
       </c>
       <c r="J541">
         <v>0.09258143270553931</v>
       </c>
       <c r="K541">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L541">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M541">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N541">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28449,96 +28449,96 @@
     </row>
     <row r="542" spans="1:16">
       <c r="A542" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B542" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C542">
-        <v>2.097453766817889</v>
+        <v>2.882421580463965</v>
       </c>
       <c r="D542" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E542">
-        <v>2.465550687885787</v>
+        <v>2.471679723734519</v>
       </c>
       <c r="F542">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G542">
-        <v>0.002302546233182111</v>
+        <v>0.003117578419536035</v>
       </c>
       <c r="H542">
-        <v>0.002714449312114212</v>
+        <v>0.002688320276265481</v>
       </c>
       <c r="I542">
-        <v>0.3680969210678979</v>
+        <v>0.4107418567294463</v>
       </c>
       <c r="J542">
-        <v>0.09955944969136986</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K542">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L542">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M542">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N542">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O542">
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="543" spans="1:16">
       <c r="A543" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B543" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C543">
-        <v>2.986590337413564</v>
+        <v>2.097453766817889</v>
       </c>
       <c r="D543" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E543">
-        <v>2.463515443861097</v>
+        <v>2.518537471376529</v>
       </c>
       <c r="F543">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G543">
-        <v>0.003253409662586436</v>
+        <v>0.002302546233182111</v>
       </c>
       <c r="H543">
-        <v>0.002696484556138903</v>
+        <v>0.002761462528623472</v>
       </c>
       <c r="I543">
-        <v>0.5230748935524669</v>
+        <v>0.4210837045586393</v>
       </c>
       <c r="J543">
         <v>0.09955944969136986</v>
       </c>
       <c r="K543">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L543">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M543">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N543">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28549,13 +28549,13 @@
     </row>
     <row r="544" spans="1:16">
       <c r="A544" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B544" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C544">
-        <v>2.87355949889196</v>
+        <v>2.986590337413564</v>
       </c>
       <c r="D544" t="s">
         <v>132</v>
@@ -28567,22 +28567,22 @@
         <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.003126440501108039</v>
+        <v>0.003253409662586436</v>
       </c>
       <c r="H544">
         <v>0.002696484556138903</v>
       </c>
       <c r="I544">
-        <v>0.4100440550308631</v>
+        <v>0.5230748935524669</v>
       </c>
       <c r="J544">
         <v>0.09955944969136986</v>
       </c>
       <c r="K544">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L544">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M544">
         <v>1.17</v>
@@ -28599,96 +28599,96 @@
     </row>
     <row r="545" spans="1:16">
       <c r="A545" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B545" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C545">
-        <v>2.089309945208396</v>
+        <v>2.87355949889196</v>
       </c>
       <c r="D545" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E545">
-        <v>2.508891391411886</v>
+        <v>2.463515443861097</v>
       </c>
       <c r="F545">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G545">
-        <v>0.002310690054791604</v>
+        <v>0.003126440501108039</v>
       </c>
       <c r="H545">
-        <v>0.002771108608588114</v>
+        <v>0.002696484556138903</v>
       </c>
       <c r="I545">
-        <v>0.4195814462034901</v>
+        <v>0.4100440550308631</v>
       </c>
       <c r="J545">
-        <v>0.1074660726132081</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K545">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L545">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M545">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N545">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="546" spans="1:16">
       <c r="A546" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B546" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C546">
-        <v>2.975995462698301</v>
+        <v>2.089309945208396</v>
       </c>
       <c r="D546" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E546">
-        <v>2.454264695042546</v>
+        <v>2.508891391411886</v>
       </c>
       <c r="F546">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G546">
-        <v>0.003264004537301699</v>
+        <v>0.002310690054791604</v>
       </c>
       <c r="H546">
-        <v>0.002705735304957454</v>
+        <v>0.002771108608588114</v>
       </c>
       <c r="I546">
-        <v>0.5217307676557548</v>
+        <v>0.4195814462034901</v>
       </c>
       <c r="J546">
         <v>0.1074660726132081</v>
       </c>
       <c r="K546">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L546">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M546">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N546">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28699,13 +28699,13 @@
     </row>
     <row r="547" spans="1:16">
       <c r="A547" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B547" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C547">
-        <v>2.863518087781226</v>
+        <v>2.975995462698301</v>
       </c>
       <c r="D547" t="s">
         <v>132</v>
@@ -28717,22 +28717,22 @@
         <v>-1</v>
       </c>
       <c r="G547">
-        <v>0.003136481912218774</v>
+        <v>0.003264004537301699</v>
       </c>
       <c r="H547">
         <v>0.002705735304957454</v>
       </c>
       <c r="I547">
-        <v>0.4092533927386794</v>
+        <v>0.5217307676557548</v>
       </c>
       <c r="J547">
         <v>0.1074660726132081</v>
       </c>
       <c r="K547">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L547">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M547">
         <v>1.17</v>
@@ -28749,96 +28749,96 @@
     </row>
     <row r="548" spans="1:16">
       <c r="A548" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B548" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C548">
-        <v>2.124107820370248</v>
+        <v>2.863518087781226</v>
       </c>
       <c r="D548" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E548">
-        <v>2.514574311506508</v>
+        <v>2.454264695042546</v>
       </c>
       <c r="F548">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G548">
-        <v>0.002335892179629752</v>
+        <v>0.003136481912218774</v>
       </c>
       <c r="H548">
-        <v>0.002765425688493492</v>
+        <v>0.002705735304957454</v>
       </c>
       <c r="I548">
-        <v>0.3904664911362596</v>
+        <v>0.4092533927386794</v>
       </c>
       <c r="J548">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K548">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L548">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="M548">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N548">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="549" spans="1:16">
       <c r="A549" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B549" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C549">
-        <v>2.982237358539935</v>
+        <v>2.124107820370248</v>
       </c>
       <c r="D549" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E549">
-        <v>2.459714708575913</v>
+        <v>2.514574311506508</v>
       </c>
       <c r="F549">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G549">
-        <v>0.003257762641460066</v>
+        <v>0.002335892179629752</v>
       </c>
       <c r="H549">
-        <v>0.002700285291424087</v>
+        <v>0.002765425688493492</v>
       </c>
       <c r="I549">
-        <v>0.5225226499640216</v>
+        <v>0.3904664911362596</v>
       </c>
       <c r="J549">
         <v>0.1028079413881086</v>
       </c>
       <c r="K549">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L549">
-        <v>3.12</v>
+        <v>2.23</v>
       </c>
       <c r="M549">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N549">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O549">
         <v>1</v>
@@ -28849,13 +28849,13 @@
     </row>
     <row r="550" spans="1:16">
       <c r="A550" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B550" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C550">
-        <v>2.869433914437102</v>
+        <v>2.982237358539935</v>
       </c>
       <c r="D550" t="s">
         <v>132</v>
@@ -28867,22 +28867,22 @@
         <v>-1</v>
       </c>
       <c r="G550">
-        <v>0.003130566085562898</v>
+        <v>0.003257762641460066</v>
       </c>
       <c r="H550">
         <v>0.002700285291424087</v>
       </c>
       <c r="I550">
-        <v>0.4097192058611889</v>
+        <v>0.5225226499640216</v>
       </c>
       <c r="J550">
         <v>0.1028079413881086</v>
       </c>
       <c r="K550">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L550">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M550">
         <v>1.17</v>
@@ -28899,96 +28899,96 @@
     </row>
     <row r="551" spans="1:16">
       <c r="A551" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B551" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C551">
-        <v>2.121386201382029</v>
+        <v>2.869433914437102</v>
       </c>
       <c r="D551" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E551">
-        <v>2.503482231779316</v>
+        <v>2.459714708575913</v>
       </c>
       <c r="F551">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G551">
-        <v>0.002358613798617972</v>
+        <v>0.003130566085562898</v>
       </c>
       <c r="H551">
-        <v>0.002776517768220685</v>
+        <v>0.002700285291424087</v>
       </c>
       <c r="I551">
-        <v>0.3820960303972871</v>
+        <v>0.4097192058611889</v>
       </c>
       <c r="J551">
-        <v>0.1118998100169543</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K551">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="L551">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="M551">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N551">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>55</v>
+        <v>334</v>
       </c>
     </row>
     <row r="552" spans="1:16">
       <c r="A552" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B552" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C552">
-        <v>2.970054254577281</v>
+        <v>2.121386201382029</v>
       </c>
       <c r="D552" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E552">
-        <v>2.449077222280164</v>
+        <v>2.503482231779316</v>
       </c>
       <c r="F552">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G552">
-        <v>0.003269945745422719</v>
+        <v>0.002358613798617972</v>
       </c>
       <c r="H552">
-        <v>0.002710922777719837</v>
+        <v>0.002776517768220685</v>
       </c>
       <c r="I552">
-        <v>0.5209770322971177</v>
+        <v>0.3820960303972871</v>
       </c>
       <c r="J552">
         <v>0.1118998100169543</v>
       </c>
       <c r="K552">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="L552">
-        <v>3.12</v>
+        <v>2.24</v>
       </c>
       <c r="M552">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N552">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O552">
         <v>1</v>
@@ -28999,13 +28999,13 @@
     </row>
     <row r="553" spans="1:16">
       <c r="A553" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B553" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C553">
-        <v>2.857887241278468</v>
+        <v>2.970054254577281</v>
       </c>
       <c r="D553" t="s">
         <v>132</v>
@@ -29017,22 +29017,22 @@
         <v>-1</v>
       </c>
       <c r="G553">
-        <v>0.003142112758721532</v>
+        <v>0.003269945745422719</v>
       </c>
       <c r="H553">
         <v>0.002710922777719837</v>
       </c>
       <c r="I553">
-        <v>0.4088100189983046</v>
+        <v>0.5209770322971177</v>
       </c>
       <c r="J553">
         <v>0.1118998100169543</v>
       </c>
       <c r="K553">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L553">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M553">
         <v>1.17</v>
@@ -29049,96 +29049,96 @@
     </row>
     <row r="554" spans="1:16">
       <c r="A554" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B554" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C554">
-        <v>2.100847031640785</v>
+        <v>2.857887241278468</v>
       </c>
       <c r="D554" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E554">
-        <v>2.479842810001658</v>
+        <v>2.449077222280164</v>
       </c>
       <c r="F554">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G554">
-        <v>0.002379152968359215</v>
+        <v>0.003142112758721532</v>
       </c>
       <c r="H554">
-        <v>0.002800157189998342</v>
+        <v>0.002710922777719837</v>
       </c>
       <c r="I554">
-        <v>0.3789957783608728</v>
+        <v>0.4088100189983046</v>
       </c>
       <c r="J554">
-        <v>0.1312763852445424</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K554">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="L554">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="M554">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N554">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O554">
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="555" spans="1:16">
       <c r="A555" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B555" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C555">
-        <v>2.944089643772313</v>
+        <v>2.100847031640785</v>
       </c>
       <c r="D555" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E555">
-        <v>2.426406629263886</v>
+        <v>2.479842810001658</v>
       </c>
       <c r="F555">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G555">
-        <v>0.003295910356227687</v>
+        <v>0.002379152968359215</v>
       </c>
       <c r="H555">
-        <v>0.002733593370736115</v>
+        <v>0.002800157189998342</v>
       </c>
       <c r="I555">
-        <v>0.5176830145084277</v>
+        <v>0.3789957783608728</v>
       </c>
       <c r="J555">
         <v>0.1312763852445424</v>
       </c>
       <c r="K555">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="L555">
-        <v>3.12</v>
+        <v>2.24</v>
       </c>
       <c r="M555">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N555">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O555">
         <v>1</v>
@@ -29149,13 +29149,13 @@
     </row>
     <row r="556" spans="1:16">
       <c r="A556" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B556" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C556">
-        <v>2.833278990739431</v>
+        <v>2.944089643772313</v>
       </c>
       <c r="D556" t="s">
         <v>132</v>
@@ -29167,22 +29167,22 @@
         <v>-1</v>
       </c>
       <c r="G556">
-        <v>0.003166721009260569</v>
+        <v>0.003295910356227687</v>
       </c>
       <c r="H556">
         <v>0.002733593370736115</v>
       </c>
       <c r="I556">
-        <v>0.4068723614755454</v>
+        <v>0.5176830145084277</v>
       </c>
       <c r="J556">
         <v>0.1312763852445424</v>
       </c>
       <c r="K556">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L556">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M556">
         <v>1.17</v>
@@ -29199,40 +29199,40 @@
     </row>
     <row r="557" spans="1:16">
       <c r="A557" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B557" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C557">
-        <v>2.897401147650162</v>
+        <v>2.833278990739431</v>
       </c>
       <c r="D557" t="s">
         <v>132</v>
       </c>
       <c r="E557">
-        <v>2.385641300560216</v>
+        <v>2.426406629263886</v>
       </c>
       <c r="F557">
         <v>-1</v>
       </c>
       <c r="G557">
-        <v>0.003342598852349839</v>
+        <v>0.003166721009260569</v>
       </c>
       <c r="H557">
-        <v>0.002774358699439784</v>
+        <v>0.002733593370736115</v>
       </c>
       <c r="I557">
-        <v>0.5117598470899458</v>
+        <v>0.4068723614755454</v>
       </c>
       <c r="J557">
-        <v>0.16611854652973</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K557">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L557">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M557">
         <v>1.17</v>
@@ -29244,18 +29244,18 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>335</v>
+        <v>54</v>
       </c>
     </row>
     <row r="558" spans="1:16">
       <c r="A558" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B558" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C558">
-        <v>2.789029445907243</v>
+        <v>2.897401147650162</v>
       </c>
       <c r="D558" t="s">
         <v>132</v>
@@ -29267,22 +29267,22 @@
         <v>-1</v>
       </c>
       <c r="G558">
-        <v>0.003210970554092757</v>
+        <v>0.003342598852349839</v>
       </c>
       <c r="H558">
         <v>0.002774358699439784</v>
       </c>
       <c r="I558">
-        <v>0.4033881453470269</v>
+        <v>0.5117598470899458</v>
       </c>
       <c r="J558">
         <v>0.16611854652973</v>
       </c>
       <c r="K558">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L558">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M558">
         <v>1.17</v>
@@ -29299,40 +29299,40 @@
     </row>
     <row r="559" spans="1:16">
       <c r="A559" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B559" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C559">
-        <v>2.834385584744631</v>
+        <v>2.789029445907243</v>
       </c>
       <c r="D559" t="s">
         <v>132</v>
       </c>
       <c r="E559">
-        <v>2.330620249366581</v>
+        <v>2.385641300560216</v>
       </c>
       <c r="F559">
         <v>-1</v>
       </c>
       <c r="G559">
-        <v>0.003405614415255369</v>
+        <v>0.003210970554092757</v>
       </c>
       <c r="H559">
-        <v>0.002829379750633419</v>
+        <v>0.002774358699439784</v>
       </c>
       <c r="I559">
-        <v>0.5037653353780502</v>
+        <v>0.4033881453470269</v>
       </c>
       <c r="J559">
-        <v>0.2131450860114693</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K559">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L559">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M559">
         <v>1.17</v>
@@ -29344,18 +29344,18 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="560" spans="1:16">
       <c r="A560" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B560" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C560">
-        <v>2.729305740765434</v>
+        <v>2.834385584744631</v>
       </c>
       <c r="D560" t="s">
         <v>132</v>
@@ -29367,22 +29367,22 @@
         <v>-1</v>
       </c>
       <c r="G560">
-        <v>0.003270694259234566</v>
+        <v>0.003405614415255369</v>
       </c>
       <c r="H560">
         <v>0.002829379750633419</v>
       </c>
       <c r="I560">
-        <v>0.3986854913988531</v>
+        <v>0.5037653353780502</v>
       </c>
       <c r="J560">
         <v>0.2131450860114693</v>
       </c>
       <c r="K560">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L560">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M560">
         <v>1.17</v>
@@ -29399,96 +29399,96 @@
     </row>
     <row r="561" spans="1:16">
       <c r="A561" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B561" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C561">
-        <v>2.710585509297514</v>
+        <v>2.729305740765434</v>
       </c>
       <c r="D561" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E561">
-        <v>2.761972833438688</v>
+        <v>2.330620249366581</v>
       </c>
       <c r="F561">
         <v>-1</v>
       </c>
       <c r="G561">
-        <v>0.003529414490702487</v>
+        <v>0.003270694259234566</v>
       </c>
       <c r="H561">
-        <v>0.003538027166561312</v>
+        <v>0.002829379750633419</v>
       </c>
       <c r="I561">
-        <v>-0.05138732414117442</v>
+        <v>0.3986854913988531</v>
       </c>
       <c r="J561">
-        <v>0.3055332020167811</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K561">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L561">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M561">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N561">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O561">
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>56</v>
+        <v>336</v>
       </c>
     </row>
     <row r="562" spans="1:16">
       <c r="A562" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B562" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C562">
-        <v>2.611972833438688</v>
+        <v>2.710585509297514</v>
       </c>
       <c r="D562" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E562">
-        <v>2.222526153640366</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="F562">
         <v>-1</v>
       </c>
       <c r="G562">
-        <v>0.003388027166561312</v>
+        <v>0.003529414490702487</v>
       </c>
       <c r="H562">
-        <v>0.002937473846359634</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="I562">
-        <v>0.389446679798322</v>
+        <v>-0.05138732414117442</v>
       </c>
       <c r="J562">
         <v>0.3055332020167811</v>
       </c>
       <c r="K562">
+        <v>1.34</v>
+      </c>
+      <c r="L562">
+        <v>3.12</v>
+      </c>
+      <c r="M562">
         <v>1.27</v>
       </c>
-      <c r="L562">
-        <v>3</v>
-      </c>
-      <c r="M562">
-        <v>1.17</v>
-      </c>
       <c r="N562">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O562">
         <v>1</v>
@@ -29499,96 +29499,96 @@
     </row>
     <row r="563" spans="1:16">
       <c r="A563" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B563" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C563">
-        <v>2.647551728558422</v>
+        <v>2.611972833438688</v>
       </c>
       <c r="D563" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E563">
-        <v>2.702231862141191</v>
+        <v>2.222526153640366</v>
       </c>
       <c r="F563">
         <v>-1</v>
       </c>
       <c r="G563">
-        <v>0.003592448271441579</v>
+        <v>0.003388027166561312</v>
       </c>
       <c r="H563">
-        <v>0.003597768137858809</v>
+        <v>0.002937473846359634</v>
       </c>
       <c r="I563">
-        <v>-0.05468013358276913</v>
+        <v>0.389446679798322</v>
       </c>
       <c r="J563">
-        <v>0.3525733368967002</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K563">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L563">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M563">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N563">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O563">
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>337</v>
+        <v>56</v>
       </c>
     </row>
     <row r="564" spans="1:16">
       <c r="A564" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B564" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C564">
-        <v>2.552231862141191</v>
+        <v>2.647551728558422</v>
       </c>
       <c r="D564" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E564">
-        <v>2.167489195830861</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="F564">
         <v>-1</v>
       </c>
       <c r="G564">
-        <v>0.003447768137858809</v>
+        <v>0.003592448271441579</v>
       </c>
       <c r="H564">
-        <v>0.00299251080416914</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="I564">
-        <v>0.3847426663103302</v>
+        <v>-0.05468013358276913</v>
       </c>
       <c r="J564">
         <v>0.3525733368967002</v>
       </c>
       <c r="K564">
+        <v>1.34</v>
+      </c>
+      <c r="L564">
+        <v>3.12</v>
+      </c>
+      <c r="M564">
         <v>1.27</v>
       </c>
-      <c r="L564">
-        <v>3</v>
-      </c>
-      <c r="M564">
-        <v>1.17</v>
-      </c>
       <c r="N564">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O564">
         <v>1</v>
@@ -29599,96 +29599,96 @@
     </row>
     <row r="565" spans="1:16">
       <c r="A565" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B565" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C565">
-        <v>2.59897387935353</v>
+        <v>2.552231862141191</v>
       </c>
       <c r="D565" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E565">
-        <v>2.65619166177536</v>
+        <v>2.167489195830861</v>
       </c>
       <c r="F565">
         <v>-1</v>
       </c>
       <c r="G565">
-        <v>0.003641026120646471</v>
+        <v>0.003447768137858809</v>
       </c>
       <c r="H565">
-        <v>0.00364380833822464</v>
+        <v>0.00299251080416914</v>
       </c>
       <c r="I565">
-        <v>-0.05721778242183051</v>
+        <v>0.3847426663103302</v>
       </c>
       <c r="J565">
-        <v>0.3888254631690077</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K565">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L565">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M565">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N565">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O565">
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="566" spans="1:16">
       <c r="A566" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B566" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C566">
-        <v>2.50619166177536</v>
+        <v>2.59897387935353</v>
       </c>
       <c r="D566" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E566">
-        <v>2.125074208092261</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="F566">
         <v>-1</v>
       </c>
       <c r="G566">
-        <v>0.00349380833822464</v>
+        <v>0.003641026120646471</v>
       </c>
       <c r="H566">
-        <v>0.003034925791907739</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="I566">
-        <v>0.3811174536830992</v>
+        <v>-0.05721778242183051</v>
       </c>
       <c r="J566">
         <v>0.3888254631690077</v>
       </c>
       <c r="K566">
+        <v>1.34</v>
+      </c>
+      <c r="L566">
+        <v>3.12</v>
+      </c>
+      <c r="M566">
         <v>1.27</v>
       </c>
-      <c r="L566">
-        <v>3</v>
-      </c>
-      <c r="M566">
-        <v>1.17</v>
-      </c>
       <c r="N566">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O566">
         <v>1</v>
@@ -29699,96 +29699,96 @@
     </row>
     <row r="567" spans="1:16">
       <c r="A567" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B567" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C567">
-        <v>2.575095597538799</v>
+        <v>2.50619166177536</v>
       </c>
       <c r="D567" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E567">
-        <v>2.633560752891249</v>
+        <v>2.125074208092261</v>
       </c>
       <c r="F567">
         <v>-1</v>
       </c>
       <c r="G567">
-        <v>0.003664904402461202</v>
+        <v>0.00349380833822464</v>
       </c>
       <c r="H567">
-        <v>0.003666439247108751</v>
+        <v>0.003034925791907739</v>
       </c>
       <c r="I567">
-        <v>-0.05846515535245045</v>
+        <v>0.3811174536830992</v>
       </c>
       <c r="J567">
-        <v>0.4066450764635833</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K567">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L567">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M567">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N567">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O567">
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="568" spans="1:16">
       <c r="A568" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B568" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C568">
-        <v>2.483560752891249</v>
+        <v>2.575095597538799</v>
       </c>
       <c r="D568" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E568">
-        <v>2.104225260537608</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="F568">
         <v>-1</v>
       </c>
       <c r="G568">
-        <v>0.003516439247108751</v>
+        <v>0.003664904402461202</v>
       </c>
       <c r="H568">
-        <v>0.003055774739462393</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="I568">
-        <v>0.3793354923536416</v>
+        <v>-0.05846515535245045</v>
       </c>
       <c r="J568">
         <v>0.4066450764635833</v>
       </c>
       <c r="K568">
+        <v>1.34</v>
+      </c>
+      <c r="L568">
+        <v>3.12</v>
+      </c>
+      <c r="M568">
         <v>1.27</v>
       </c>
-      <c r="L568">
-        <v>3</v>
-      </c>
-      <c r="M568">
-        <v>1.17</v>
-      </c>
       <c r="N568">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O568">
         <v>1</v>
@@ -29799,96 +29799,96 @@
     </row>
     <row r="569" spans="1:16">
       <c r="A569" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B569" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C569">
-        <v>2.513392232045375</v>
+        <v>2.483560752891249</v>
       </c>
       <c r="D569" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E569">
-        <v>2.575080697535542</v>
+        <v>2.104225260537608</v>
       </c>
       <c r="F569">
         <v>-1</v>
       </c>
       <c r="G569">
-        <v>0.003726607767954625</v>
+        <v>0.003516439247108751</v>
       </c>
       <c r="H569">
-        <v>0.003724919302464458</v>
+        <v>0.003055774739462393</v>
       </c>
       <c r="I569">
-        <v>-0.0616884654901666</v>
+        <v>0.3793354923536416</v>
       </c>
       <c r="J569">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K569">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L569">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M569">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N569">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O569">
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="570" spans="1:16">
       <c r="A570" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B570" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C570">
-        <v>2.425080697535542</v>
+        <v>2.513392232045375</v>
       </c>
       <c r="D570" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E570">
-        <v>2.050349933950066</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="F570">
         <v>-1</v>
       </c>
       <c r="G570">
-        <v>0.003574919302464458</v>
+        <v>0.003726607767954625</v>
       </c>
       <c r="H570">
-        <v>0.003109650066049934</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="I570">
-        <v>0.3747307635854757</v>
+        <v>-0.0616884654901666</v>
       </c>
       <c r="J570">
         <v>0.4526923641452424</v>
       </c>
       <c r="K570">
+        <v>1.34</v>
+      </c>
+      <c r="L570">
+        <v>3.12</v>
+      </c>
+      <c r="M570">
         <v>1.27</v>
       </c>
-      <c r="L570">
-        <v>3</v>
-      </c>
-      <c r="M570">
-        <v>1.17</v>
-      </c>
       <c r="N570">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O570">
         <v>1</v>
@@ -29899,101 +29899,151 @@
     </row>
     <row r="571" spans="1:16">
       <c r="A571" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B571" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C571">
-        <v>2.46037019732591</v>
+        <v>2.425080697535542</v>
       </c>
       <c r="D571" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E571">
-        <v>2.524828470599929</v>
+        <v>2.050349933950066</v>
       </c>
       <c r="F571">
         <v>-1</v>
       </c>
       <c r="G571">
-        <v>0.00377962980267409</v>
+        <v>0.003574919302464458</v>
       </c>
       <c r="H571">
-        <v>0.003775171529400071</v>
+        <v>0.003109650066049934</v>
       </c>
       <c r="I571">
-        <v>-0.0644582732740191</v>
+        <v>0.3747307635854757</v>
       </c>
       <c r="J571">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K571">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L571">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M571">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N571">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O571">
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="572" spans="1:16">
       <c r="A572" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B572" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C572">
-        <v>2.37482847059993</v>
+        <v>2.46037019732591</v>
       </c>
       <c r="D572" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E572">
-        <v>2.004054575277101</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="F572">
         <v>-1</v>
       </c>
       <c r="G572">
-        <v>0.003625171529400071</v>
+        <v>0.00377962980267409</v>
       </c>
       <c r="H572">
-        <v>0.003155945424722899</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="I572">
-        <v>0.370773895322829</v>
+        <v>-0.0644582732740191</v>
       </c>
       <c r="J572">
         <v>0.4922610467717091</v>
       </c>
       <c r="K572">
+        <v>1.34</v>
+      </c>
+      <c r="L572">
+        <v>3.12</v>
+      </c>
+      <c r="M572">
         <v>1.27</v>
       </c>
-      <c r="L572">
+      <c r="N572">
+        <v>3.15</v>
+      </c>
+      <c r="O572">
+        <v>1</v>
+      </c>
+      <c r="P572" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="573" spans="1:16">
+      <c r="A573" s="1">
+        <v>1</v>
+      </c>
+      <c r="B573" t="s">
+        <v>53</v>
+      </c>
+      <c r="C573">
+        <v>2.37482847059993</v>
+      </c>
+      <c r="D573" t="s">
+        <v>132</v>
+      </c>
+      <c r="E573">
+        <v>2.004054575277101</v>
+      </c>
+      <c r="F573">
+        <v>-1</v>
+      </c>
+      <c r="G573">
+        <v>0.003625171529400071</v>
+      </c>
+      <c r="H573">
+        <v>0.003155945424722899</v>
+      </c>
+      <c r="I573">
+        <v>0.370773895322829</v>
+      </c>
+      <c r="J573">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K573">
+        <v>1.27</v>
+      </c>
+      <c r="L573">
         <v>3</v>
       </c>
-      <c r="M572">
+      <c r="M573">
         <v>1.17</v>
       </c>
-      <c r="N572">
+      <c r="N573">
         <v>2.58</v>
       </c>
-      <c r="O572">
-        <v>1</v>
-      </c>
-      <c r="P572" t="s">
+      <c r="O573">
+        <v>1</v>
+      </c>
+      <c r="P573" t="s">
         <v>341</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -23152,10 +23152,10 @@
         <v>3.290901329475496</v>
       </c>
       <c r="D436" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E436">
-        <v>2.64539366835975</v>
+        <v>2.676669051415537</v>
       </c>
       <c r="F436">
         <v>-1</v>
@@ -23164,10 +23164,10 @@
         <v>0.002949098670524505</v>
       </c>
       <c r="H436">
-        <v>0.00235460633164025</v>
+        <v>0.002383330948584463</v>
       </c>
       <c r="I436">
-        <v>0.6455076611157455</v>
+        <v>0.6142322780599585</v>
       </c>
       <c r="J436">
         <v>-0.1275383055787282</v>
@@ -23179,10 +23179,10 @@
         <v>3.12</v>
       </c>
       <c r="M436">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N436">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O436">
         <v>1</v>
@@ -23202,10 +23202,10 @@
         <v>3.161973648084985</v>
       </c>
       <c r="D437" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E437">
-        <v>2.64539366835975</v>
+        <v>2.676669051415537</v>
       </c>
       <c r="F437">
         <v>-1</v>
@@ -23214,10 +23214,10 @@
         <v>0.002838026351915015</v>
       </c>
       <c r="H437">
-        <v>0.00235460633164025</v>
+        <v>0.002383330948584463</v>
       </c>
       <c r="I437">
-        <v>0.5165799797252348</v>
+        <v>0.4853045966694478</v>
       </c>
       <c r="J437">
         <v>-0.1275383055787282</v>
@@ -23229,10 +23229,10 @@
         <v>3</v>
       </c>
       <c r="M437">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N437">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O437">
         <v>1</v>
@@ -25146,43 +25146,43 @@
         <v>0</v>
       </c>
       <c r="B476" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C476">
-        <v>3.394803884930561</v>
+        <v>2.41122985184961</v>
       </c>
       <c r="D476" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E476">
-        <v>2.76583915497772</v>
+        <v>2.846346907584478</v>
       </c>
       <c r="F476">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G476">
-        <v>0.00284519611506944</v>
+        <v>0.00198877014815039</v>
       </c>
       <c r="H476">
-        <v>0.00229416084502228</v>
+        <v>0.002333653092415522</v>
       </c>
       <c r="I476">
-        <v>0.6289647299528411</v>
+        <v>0.4351170557348678</v>
       </c>
       <c r="J476">
         <v>-0.2050775260675825</v>
       </c>
       <c r="K476">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L476">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M476">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N476">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O476">
         <v>1</v>
@@ -25196,10 +25196,10 @@
         <v>1</v>
       </c>
       <c r="B477" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C477">
-        <v>3.26044845810583</v>
+        <v>3.394803884930561</v>
       </c>
       <c r="D477" t="s">
         <v>130</v>
@@ -25211,22 +25211,22 @@
         <v>-1</v>
       </c>
       <c r="G477">
-        <v>0.00273955154189417</v>
+        <v>0.00284519611506944</v>
       </c>
       <c r="H477">
         <v>0.00229416084502228</v>
       </c>
       <c r="I477">
-        <v>0.4946093031281102</v>
+        <v>0.6289647299528411</v>
       </c>
       <c r="J477">
         <v>-0.2050775260675825</v>
       </c>
       <c r="K477">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L477">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M477">
         <v>1.15</v>
@@ -25243,96 +25243,96 @@
     </row>
     <row r="478" spans="1:16">
       <c r="A478" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B478" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C478">
-        <v>2.414401903996001</v>
+        <v>3.26044845810583</v>
       </c>
       <c r="D478" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E478">
-        <v>2.850196485432039</v>
+        <v>2.76583915497772</v>
       </c>
       <c r="F478">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G478">
-        <v>0.001985598096004</v>
+        <v>0.00273955154189417</v>
       </c>
       <c r="H478">
-        <v>0.00232980351456796</v>
+        <v>0.00229416084502228</v>
       </c>
       <c r="I478">
-        <v>0.4357945814360389</v>
+        <v>0.4946093031281102</v>
       </c>
       <c r="J478">
-        <v>-0.2081571883456315</v>
+        <v>-0.2050775260675825</v>
       </c>
       <c r="K478">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L478">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M478">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N478">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O478">
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="479" spans="1:16">
       <c r="A479" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B479" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C479">
-        <v>3.398930632383146</v>
+        <v>2.414401903996001</v>
       </c>
       <c r="D479" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E479">
-        <v>2.769380766597476</v>
+        <v>2.850196485432039</v>
       </c>
       <c r="F479">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G479">
-        <v>0.002841069367616854</v>
+        <v>0.001985598096004</v>
       </c>
       <c r="H479">
-        <v>0.002290619233402524</v>
+        <v>0.00232980351456796</v>
       </c>
       <c r="I479">
-        <v>0.6295498657856702</v>
+        <v>0.4357945814360389</v>
       </c>
       <c r="J479">
         <v>-0.2081571883456315</v>
       </c>
       <c r="K479">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L479">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M479">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N479">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O479">
         <v>1</v>
@@ -25343,13 +25343,13 @@
     </row>
     <row r="480" spans="1:16">
       <c r="A480" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B480" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C480">
-        <v>3.264359629198952</v>
+        <v>3.398930632383146</v>
       </c>
       <c r="D480" t="s">
         <v>130</v>
@@ -25361,22 +25361,22 @@
         <v>-1</v>
       </c>
       <c r="G480">
-        <v>0.002735640370801048</v>
+        <v>0.002841069367616854</v>
       </c>
       <c r="H480">
         <v>0.002290619233402524</v>
       </c>
       <c r="I480">
-        <v>0.4949788626014757</v>
+        <v>0.6295498657856702</v>
       </c>
       <c r="J480">
         <v>-0.2081571883456315</v>
       </c>
       <c r="K480">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L480">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M480">
         <v>1.15</v>
@@ -25393,96 +25393,96 @@
     </row>
     <row r="481" spans="1:16">
       <c r="A481" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B481" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C481">
-        <v>2.400941737549309</v>
+        <v>3.264359629198952</v>
       </c>
       <c r="D481" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E481">
-        <v>2.833861331977317</v>
+        <v>2.769380766597476</v>
       </c>
       <c r="F481">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G481">
-        <v>0.001999058262450691</v>
+        <v>0.002735640370801048</v>
       </c>
       <c r="H481">
-        <v>0.002346138668022683</v>
+        <v>0.002290619233402524</v>
       </c>
       <c r="I481">
-        <v>0.4329195944280078</v>
+        <v>0.4949788626014757</v>
       </c>
       <c r="J481">
-        <v>-0.1950890655818535</v>
+        <v>-0.2081571883456315</v>
       </c>
       <c r="K481">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L481">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M481">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N481">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O481">
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="482" spans="1:16">
       <c r="A482" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B482" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C482">
-        <v>3.381419347879684</v>
+        <v>2.400941737549309</v>
       </c>
       <c r="D482" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E482">
-        <v>2.754352425419131</v>
+        <v>2.833861331977317</v>
       </c>
       <c r="F482">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G482">
-        <v>0.002858580652120316</v>
+        <v>0.001999058262450691</v>
       </c>
       <c r="H482">
-        <v>0.002305647574580868</v>
+        <v>0.002346138668022683</v>
       </c>
       <c r="I482">
-        <v>0.6270669224605525</v>
+        <v>0.4329195944280078</v>
       </c>
       <c r="J482">
         <v>-0.1950890655818535</v>
       </c>
       <c r="K482">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L482">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M482">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N482">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O482">
         <v>1</v>
@@ -25493,13 +25493,13 @@
     </row>
     <row r="483" spans="1:16">
       <c r="A483" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B483" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C483">
-        <v>3.247763113288954</v>
+        <v>3.381419347879684</v>
       </c>
       <c r="D483" t="s">
         <v>130</v>
@@ -25511,22 +25511,22 @@
         <v>-1</v>
       </c>
       <c r="G483">
-        <v>0.002752236886711046</v>
+        <v>0.002858580652120316</v>
       </c>
       <c r="H483">
         <v>0.002305647574580868</v>
       </c>
       <c r="I483">
-        <v>0.4934106878698228</v>
+        <v>0.6270669224605525</v>
       </c>
       <c r="J483">
         <v>-0.1950890655818535</v>
       </c>
       <c r="K483">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L483">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M483">
         <v>1.15</v>
@@ -25543,96 +25543,96 @@
     </row>
     <row r="484" spans="1:16">
       <c r="A484" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B484" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C484">
-        <v>2.416869377367424</v>
+        <v>3.247763113288954</v>
       </c>
       <c r="D484" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E484">
-        <v>2.853190991950757</v>
+        <v>2.754352425419131</v>
       </c>
       <c r="F484">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G484">
-        <v>0.001983130622632577</v>
+        <v>0.002752236886711046</v>
       </c>
       <c r="H484">
-        <v>0.002326809008049243</v>
+        <v>0.002305647574580868</v>
       </c>
       <c r="I484">
-        <v>0.4363216145833326</v>
+        <v>0.4934106878698228</v>
       </c>
       <c r="J484">
-        <v>-0.2105527935606056</v>
+        <v>-0.1950890655818535</v>
       </c>
       <c r="K484">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L484">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M484">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N484">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O484">
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="485" spans="1:16">
       <c r="A485" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B485" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C485">
-        <v>3.402140743371211</v>
+        <v>2.416869377367424</v>
       </c>
       <c r="D485" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E485">
-        <v>2.772135712594696</v>
+        <v>2.853190991950757</v>
       </c>
       <c r="F485">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G485">
-        <v>0.002837859256628789</v>
+        <v>0.001983130622632577</v>
       </c>
       <c r="H485">
-        <v>0.002287864287405304</v>
+        <v>0.002326809008049243</v>
       </c>
       <c r="I485">
-        <v>0.6300050307765153</v>
+        <v>0.4363216145833326</v>
       </c>
       <c r="J485">
         <v>-0.2105527935606056</v>
       </c>
       <c r="K485">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L485">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M485">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N485">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O485">
         <v>1</v>
@@ -25643,13 +25643,13 @@
     </row>
     <row r="486" spans="1:16">
       <c r="A486" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B486" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C486">
-        <v>3.267402047821969</v>
+        <v>3.402140743371211</v>
       </c>
       <c r="D486" t="s">
         <v>130</v>
@@ -25661,22 +25661,22 @@
         <v>-1</v>
       </c>
       <c r="G486">
-        <v>0.002732597952178031</v>
+        <v>0.002837859256628789</v>
       </c>
       <c r="H486">
         <v>0.002287864287405304</v>
       </c>
       <c r="I486">
-        <v>0.495266335227273</v>
+        <v>0.6300050307765153</v>
       </c>
       <c r="J486">
         <v>-0.2105527935606056</v>
       </c>
       <c r="K486">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L486">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M486">
         <v>1.15</v>
@@ -25693,96 +25693,96 @@
     </row>
     <row r="487" spans="1:16">
       <c r="A487" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B487" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C487">
-        <v>2.427926332334885</v>
+        <v>3.267402047821969</v>
       </c>
       <c r="D487" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E487">
-        <v>2.866609626620006</v>
+        <v>2.772135712594696</v>
       </c>
       <c r="F487">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G487">
-        <v>0.001972073667665115</v>
+        <v>0.002732597952178031</v>
       </c>
       <c r="H487">
-        <v>0.002313390373379994</v>
+        <v>0.002287864287405304</v>
       </c>
       <c r="I487">
-        <v>0.4386832942851204</v>
+        <v>0.495266335227273</v>
       </c>
       <c r="J487">
-        <v>-0.2212877012960047</v>
+        <v>-0.2105527935606056</v>
       </c>
       <c r="K487">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L487">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M487">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N487">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O487">
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="488" spans="1:16">
       <c r="A488" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B488" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C488">
-        <v>3.416525519736647</v>
+        <v>2.427926332334885</v>
       </c>
       <c r="D488" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E488">
-        <v>2.784480856490405</v>
+        <v>2.866609626620006</v>
       </c>
       <c r="F488">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G488">
-        <v>0.002823474480263354</v>
+        <v>0.001972073667665115</v>
       </c>
       <c r="H488">
-        <v>0.002275519143509595</v>
+        <v>0.002313390373379994</v>
       </c>
       <c r="I488">
-        <v>0.6320446632462415</v>
+        <v>0.4386832942851204</v>
       </c>
       <c r="J488">
         <v>-0.2212877012960047</v>
       </c>
       <c r="K488">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L488">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M488">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N488">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O488">
         <v>1</v>
@@ -25793,13 +25793,13 @@
     </row>
     <row r="489" spans="1:16">
       <c r="A489" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B489" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C489">
-        <v>3.281035380645926</v>
+        <v>3.416525519736647</v>
       </c>
       <c r="D489" t="s">
         <v>130</v>
@@ -25811,22 +25811,22 @@
         <v>-1</v>
       </c>
       <c r="G489">
-        <v>0.002718964619354074</v>
+        <v>0.002823474480263354</v>
       </c>
       <c r="H489">
         <v>0.002275519143509595</v>
       </c>
       <c r="I489">
-        <v>0.4965545241555209</v>
+        <v>0.6320446632462415</v>
       </c>
       <c r="J489">
         <v>-0.2212877012960047</v>
       </c>
       <c r="K489">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L489">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M489">
         <v>1.15</v>
@@ -25843,96 +25843,96 @@
     </row>
     <row r="490" spans="1:16">
       <c r="A490" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B490" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C490">
-        <v>2.43983969591803</v>
+        <v>3.281035380645926</v>
       </c>
       <c r="D490" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E490">
-        <v>2.88106759213353</v>
+        <v>2.784480856490405</v>
       </c>
       <c r="F490">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G490">
-        <v>0.001960160304081971</v>
+        <v>0.002718964619354074</v>
       </c>
       <c r="H490">
-        <v>0.002298932407866469</v>
+        <v>0.002275519143509595</v>
       </c>
       <c r="I490">
-        <v>0.441227896215501</v>
+        <v>0.4965545241555209</v>
       </c>
       <c r="J490">
-        <v>-0.2328540737068246</v>
+        <v>-0.2212877012960047</v>
       </c>
       <c r="K490">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L490">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M490">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N490">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O490">
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="491" spans="1:16">
       <c r="A491" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B491" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C491">
-        <v>3.432024458767145</v>
+        <v>2.43983969591803</v>
       </c>
       <c r="D491" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E491">
-        <v>2.797782184762848</v>
+        <v>2.88106759213353</v>
       </c>
       <c r="F491">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G491">
-        <v>0.002807975541232855</v>
+        <v>0.001960160304081971</v>
       </c>
       <c r="H491">
-        <v>0.002262217815237151</v>
+        <v>0.002298932407866469</v>
       </c>
       <c r="I491">
-        <v>0.634242274004297</v>
+        <v>0.441227896215501</v>
       </c>
       <c r="J491">
         <v>-0.2328540737068246</v>
       </c>
       <c r="K491">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L491">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M491">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N491">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O491">
         <v>1</v>
@@ -25943,13 +25943,13 @@
     </row>
     <row r="492" spans="1:16">
       <c r="A492" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B492" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C492">
-        <v>3.295724673607667</v>
+        <v>3.432024458767145</v>
       </c>
       <c r="D492" t="s">
         <v>130</v>
@@ -25961,22 +25961,22 @@
         <v>-1</v>
       </c>
       <c r="G492">
-        <v>0.002704275326392333</v>
+        <v>0.002807975541232855</v>
       </c>
       <c r="H492">
         <v>0.002262217815237151</v>
       </c>
       <c r="I492">
-        <v>0.497942488844819</v>
+        <v>0.634242274004297</v>
       </c>
       <c r="J492">
         <v>-0.2328540737068246</v>
       </c>
       <c r="K492">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L492">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M492">
         <v>1.15</v>
@@ -25993,96 +25993,96 @@
     </row>
     <row r="493" spans="1:16">
       <c r="A493" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B493" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C493">
-        <v>2.478555931094635</v>
+        <v>3.295724673607667</v>
       </c>
       <c r="D493" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E493">
-        <v>2.928053314435237</v>
+        <v>2.797782184762848</v>
       </c>
       <c r="F493">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G493">
-        <v>0.001921444068905365</v>
+        <v>0.002704275326392333</v>
       </c>
       <c r="H493">
-        <v>0.002251946685564763</v>
+        <v>0.002262217815237151</v>
       </c>
       <c r="I493">
-        <v>0.4494973833406015</v>
+        <v>0.497942488844819</v>
       </c>
       <c r="J493">
-        <v>-0.2704426515481894</v>
+        <v>-0.2328540737068246</v>
       </c>
       <c r="K493">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L493">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M493">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N493">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O493">
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="494" spans="1:16">
       <c r="A494" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B494" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C494">
-        <v>3.482393153074574</v>
+        <v>2.478555931094635</v>
       </c>
       <c r="D494" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E494">
-        <v>2.841009049280418</v>
+        <v>2.928053314435237</v>
       </c>
       <c r="F494">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G494">
-        <v>0.002757606846925426</v>
+        <v>0.001921444068905365</v>
       </c>
       <c r="H494">
-        <v>0.002218990950719582</v>
+        <v>0.002251946685564763</v>
       </c>
       <c r="I494">
-        <v>0.6413841037941563</v>
+        <v>0.4494973833406015</v>
       </c>
       <c r="J494">
         <v>-0.2704426515481894</v>
       </c>
       <c r="K494">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L494">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M494">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N494">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O494">
         <v>1</v>
@@ -26093,13 +26093,13 @@
     </row>
     <row r="495" spans="1:16">
       <c r="A495" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B495" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C495">
-        <v>3.343462167466201</v>
+        <v>3.482393153074574</v>
       </c>
       <c r="D495" t="s">
         <v>130</v>
@@ -26111,22 +26111,22 @@
         <v>-1</v>
       </c>
       <c r="G495">
-        <v>0.002656537832533799</v>
+        <v>0.002757606846925426</v>
       </c>
       <c r="H495">
         <v>0.002218990950719582</v>
       </c>
       <c r="I495">
-        <v>0.502453118185783</v>
+        <v>0.6413841037941563</v>
       </c>
       <c r="J495">
         <v>-0.2704426515481894</v>
       </c>
       <c r="K495">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L495">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M495">
         <v>1.15</v>
@@ -26143,96 +26143,96 @@
     </row>
     <row r="496" spans="1:16">
       <c r="A496" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B496" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C496">
-        <v>2.492450104171095</v>
+        <v>3.343462167466201</v>
       </c>
       <c r="D496" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E496">
-        <v>2.944915174964921</v>
+        <v>2.841009049280418</v>
       </c>
       <c r="F496">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G496">
-        <v>0.001907549895828906</v>
+        <v>0.002656537832533799</v>
       </c>
       <c r="H496">
-        <v>0.002235084825035079</v>
+        <v>0.002218990950719582</v>
       </c>
       <c r="I496">
-        <v>0.4524650707938256</v>
+        <v>0.502453118185783</v>
       </c>
       <c r="J496">
-        <v>-0.2839321399719367</v>
+        <v>-0.2704426515481894</v>
       </c>
       <c r="K496">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L496">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M496">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N496">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O496">
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="497" spans="1:16">
       <c r="A497" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B497" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C497">
-        <v>3.500469067562396</v>
+        <v>2.492450104171095</v>
       </c>
       <c r="D497" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E497">
-        <v>2.856521960967727</v>
+        <v>2.944915174964921</v>
       </c>
       <c r="F497">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G497">
-        <v>0.002739530932437605</v>
+        <v>0.001907549895828906</v>
       </c>
       <c r="H497">
-        <v>0.002203478039032273</v>
+        <v>0.002235084825035079</v>
       </c>
       <c r="I497">
-        <v>0.6439471065946685</v>
+        <v>0.4524650707938256</v>
       </c>
       <c r="J497">
         <v>-0.2839321399719367</v>
       </c>
       <c r="K497">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L497">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M497">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N497">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O497">
         <v>1</v>
@@ -26243,13 +26243,13 @@
     </row>
     <row r="498" spans="1:16">
       <c r="A498" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B498" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C498">
-        <v>3.36059381776436</v>
+        <v>3.500469067562396</v>
       </c>
       <c r="D498" t="s">
         <v>130</v>
@@ -26261,22 +26261,22 @@
         <v>-1</v>
       </c>
       <c r="G498">
-        <v>0.002639406182235641</v>
+        <v>0.002739530932437605</v>
       </c>
       <c r="H498">
         <v>0.002203478039032273</v>
       </c>
       <c r="I498">
-        <v>0.5040718567966325</v>
+        <v>0.6439471065946685</v>
       </c>
       <c r="J498">
         <v>-0.2839321399719367</v>
       </c>
       <c r="K498">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L498">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M498">
         <v>1.15</v>
@@ -26293,96 +26293,96 @@
     </row>
     <row r="499" spans="1:16">
       <c r="A499" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B499" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C499">
-        <v>2.485588290136117</v>
+        <v>3.36059381776436</v>
       </c>
       <c r="D499" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E499">
-        <v>2.936587730747715</v>
+        <v>2.856521960967727</v>
       </c>
       <c r="F499">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G499">
-        <v>0.001914411709863883</v>
+        <v>0.002639406182235641</v>
       </c>
       <c r="H499">
-        <v>0.002243412269252285</v>
+        <v>0.002203478039032273</v>
       </c>
       <c r="I499">
-        <v>0.4509994406115978</v>
+        <v>0.5040718567966325</v>
       </c>
       <c r="J499">
-        <v>-0.2772701845981717</v>
+        <v>-0.2839321399719367</v>
       </c>
       <c r="K499">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L499">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M499">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N499">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O499">
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="500" spans="1:16">
       <c r="A500" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B500" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C500">
-        <v>3.49154204736155</v>
+        <v>2.485588290136117</v>
       </c>
       <c r="D500" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E500">
-        <v>2.848860712287897</v>
+        <v>2.936587730747715</v>
       </c>
       <c r="F500">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G500">
-        <v>0.00274845795263845</v>
+        <v>0.001914411709863883</v>
       </c>
       <c r="H500">
-        <v>0.002211139287712102</v>
+        <v>0.002243412269252285</v>
       </c>
       <c r="I500">
-        <v>0.6426813350736529</v>
+        <v>0.4509994406115978</v>
       </c>
       <c r="J500">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K500">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L500">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M500">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N500">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O500">
         <v>1</v>
@@ -26393,13 +26393,13 @@
     </row>
     <row r="501" spans="1:16">
       <c r="A501" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B501" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C501">
-        <v>3.352133134439678</v>
+        <v>3.49154204736155</v>
       </c>
       <c r="D501" t="s">
         <v>130</v>
@@ -26411,22 +26411,22 @@
         <v>-1</v>
       </c>
       <c r="G501">
-        <v>0.002647866865560322</v>
+        <v>0.00274845795263845</v>
       </c>
       <c r="H501">
         <v>0.002211139287712102</v>
       </c>
       <c r="I501">
-        <v>0.503272422151781</v>
+        <v>0.6426813350736529</v>
       </c>
       <c r="J501">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K501">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L501">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M501">
         <v>1.15</v>
@@ -26443,96 +26443,96 @@
     </row>
     <row r="502" spans="1:16">
       <c r="A502" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B502" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C502">
-        <v>2.483803138304734</v>
+        <v>3.352133134439678</v>
       </c>
       <c r="D502" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E502">
-        <v>2.934421284350405</v>
+        <v>2.848860712287897</v>
       </c>
       <c r="F502">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G502">
-        <v>0.001916196861695266</v>
+        <v>0.002647866865560322</v>
       </c>
       <c r="H502">
-        <v>0.002245578715649595</v>
+        <v>0.002211139287712102</v>
       </c>
       <c r="I502">
-        <v>0.4506181460456711</v>
+        <v>0.503272422151781</v>
       </c>
       <c r="J502">
-        <v>-0.2755370274803244</v>
+        <v>-0.2772701845981717</v>
       </c>
       <c r="K502">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L502">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M502">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N502">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O502">
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="503" spans="1:16">
       <c r="A503" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B503" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C503">
-        <v>3.489219616823635</v>
+        <v>2.483803138304734</v>
       </c>
       <c r="D503" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E503">
-        <v>2.846867581602373</v>
+        <v>2.934421284350405</v>
       </c>
       <c r="F503">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G503">
-        <v>0.002750780383176366</v>
+        <v>0.001916196861695266</v>
       </c>
       <c r="H503">
-        <v>0.002213132418397626</v>
+        <v>0.002245578715649595</v>
       </c>
       <c r="I503">
-        <v>0.6423520352212617</v>
+        <v>0.4506181460456711</v>
       </c>
       <c r="J503">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K503">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L503">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M503">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N503">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O503">
         <v>1</v>
@@ -26543,13 +26543,13 @@
     </row>
     <row r="504" spans="1:16">
       <c r="A504" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B504" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C504">
-        <v>3.349932024900012</v>
+        <v>3.489219616823635</v>
       </c>
       <c r="D504" t="s">
         <v>130</v>
@@ -26561,22 +26561,22 @@
         <v>-1</v>
       </c>
       <c r="G504">
-        <v>0.002650067975099988</v>
+        <v>0.002750780383176366</v>
       </c>
       <c r="H504">
         <v>0.002213132418397626</v>
       </c>
       <c r="I504">
-        <v>0.5030644432976388</v>
+        <v>0.6423520352212617</v>
       </c>
       <c r="J504">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K504">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L504">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M504">
         <v>1.15</v>
@@ -26593,96 +26593,96 @@
     </row>
     <row r="505" spans="1:16">
       <c r="A505" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B505" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C505">
-        <v>2.455324757264537</v>
+        <v>3.349932024900012</v>
       </c>
       <c r="D505" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E505">
-        <v>2.899860142311331</v>
+        <v>2.846867581602373</v>
       </c>
       <c r="F505">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G505">
-        <v>0.001944675242735464</v>
+        <v>0.002650067975099988</v>
       </c>
       <c r="H505">
-        <v>0.002280139857688669</v>
+        <v>0.002213132418397626</v>
       </c>
       <c r="I505">
-        <v>0.4445353850467941</v>
+        <v>0.5030644432976388</v>
       </c>
       <c r="J505">
-        <v>-0.2478881138490649</v>
+        <v>-0.2755370274803244</v>
       </c>
       <c r="K505">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L505">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M505">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N505">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O505">
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="506" spans="1:16">
       <c r="A506" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B506" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C506">
-        <v>3.452170072557747</v>
+        <v>2.455324757264537</v>
       </c>
       <c r="D506" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E506">
-        <v>2.815071330926425</v>
+        <v>2.899860142311331</v>
       </c>
       <c r="F506">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G506">
-        <v>0.002787829927442253</v>
+        <v>0.001944675242735464</v>
       </c>
       <c r="H506">
-        <v>0.002244928669073575</v>
+        <v>0.002280139857688669</v>
       </c>
       <c r="I506">
-        <v>0.6370987416313225</v>
+        <v>0.4445353850467941</v>
       </c>
       <c r="J506">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K506">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L506">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M506">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N506">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O506">
         <v>1</v>
@@ -26693,13 +26693,13 @@
     </row>
     <row r="507" spans="1:16">
       <c r="A507" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B507" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C507">
-        <v>3.314817904588312</v>
+        <v>3.452170072557747</v>
       </c>
       <c r="D507" t="s">
         <v>130</v>
@@ -26711,22 +26711,22 @@
         <v>-1</v>
       </c>
       <c r="G507">
-        <v>0.002685182095411688</v>
+        <v>0.002787829927442253</v>
       </c>
       <c r="H507">
         <v>0.002244928669073575</v>
       </c>
       <c r="I507">
-        <v>0.4997465736618878</v>
+        <v>0.6370987416313225</v>
       </c>
       <c r="J507">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K507">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L507">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M507">
         <v>1.15</v>
@@ -26743,96 +26743,96 @@
     </row>
     <row r="508" spans="1:16">
       <c r="A508" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B508" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C508">
-        <v>2.38683909149</v>
+        <v>3.314817904588312</v>
       </c>
       <c r="D508" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E508">
-        <v>2.816746470254853</v>
+        <v>2.815071330926425</v>
       </c>
       <c r="F508">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G508">
-        <v>0.002013160908510001</v>
+        <v>0.002685182095411688</v>
       </c>
       <c r="H508">
-        <v>0.002363253529745146</v>
+        <v>0.002244928669073575</v>
       </c>
       <c r="I508">
-        <v>0.4299073787648537</v>
+        <v>0.4997465736618878</v>
       </c>
       <c r="J508">
-        <v>-0.181397176203883</v>
+        <v>-0.2478881138490649</v>
       </c>
       <c r="K508">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L508">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M508">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N508">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O508">
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="509" spans="1:16">
       <c r="A509" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B509" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C509">
-        <v>3.363072216113203</v>
+        <v>2.38683909149</v>
       </c>
       <c r="D509" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E509">
-        <v>2.738606752634465</v>
+        <v>2.816746470254853</v>
       </c>
       <c r="F509">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G509">
-        <v>0.002876927783886797</v>
+        <v>0.002013160908510001</v>
       </c>
       <c r="H509">
-        <v>0.002321393247365534</v>
+        <v>0.002363253529745146</v>
       </c>
       <c r="I509">
-        <v>0.6244654634787379</v>
+        <v>0.4299073787648537</v>
       </c>
       <c r="J509">
         <v>-0.181397176203883</v>
       </c>
       <c r="K509">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L509">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M509">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N509">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O509">
         <v>1</v>
@@ -26843,13 +26843,13 @@
     </row>
     <row r="510" spans="1:16">
       <c r="A510" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B510" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C510">
-        <v>3.230374413778931</v>
+        <v>3.363072216113203</v>
       </c>
       <c r="D510" t="s">
         <v>130</v>
@@ -26861,22 +26861,22 @@
         <v>-1</v>
       </c>
       <c r="G510">
-        <v>0.002769625586221069</v>
+        <v>0.002876927783886797</v>
       </c>
       <c r="H510">
         <v>0.002321393247365534</v>
       </c>
       <c r="I510">
-        <v>0.4917676611444661</v>
+        <v>0.6244654634787379</v>
       </c>
       <c r="J510">
         <v>-0.181397176203883</v>
       </c>
       <c r="K510">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L510">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M510">
         <v>1.15</v>
@@ -26893,96 +26893,96 @@
     </row>
     <row r="511" spans="1:16">
       <c r="A511" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B511" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C511">
-        <v>2.332831092936091</v>
+        <v>3.230374413778931</v>
       </c>
       <c r="D511" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E511">
-        <v>2.751202782689431</v>
+        <v>2.738606752634465</v>
       </c>
       <c r="F511">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G511">
-        <v>0.002067168907063909</v>
+        <v>0.002769625586221069</v>
       </c>
       <c r="H511">
-        <v>0.002428797217310569</v>
+        <v>0.002321393247365534</v>
       </c>
       <c r="I511">
-        <v>0.4183716897533394</v>
+        <v>0.4917676611444661</v>
       </c>
       <c r="J511">
-        <v>-0.1289622261515449</v>
+        <v>-0.181397176203883</v>
       </c>
       <c r="K511">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L511">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M511">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N511">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O511">
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="512" spans="1:16">
       <c r="A512" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B512" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C512">
-        <v>3.29280938304307</v>
+        <v>2.332831092936091</v>
       </c>
       <c r="D512" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E512">
-        <v>2.678306560074276</v>
+        <v>2.751202782689431</v>
       </c>
       <c r="F512">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G512">
-        <v>0.00294719061695693</v>
+        <v>0.002067168907063909</v>
       </c>
       <c r="H512">
-        <v>0.002381693439925723</v>
+        <v>0.002428797217310569</v>
       </c>
       <c r="I512">
-        <v>0.6145028229687939</v>
+        <v>0.4183716897533394</v>
       </c>
       <c r="J512">
         <v>-0.1289622261515449</v>
       </c>
       <c r="K512">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L512">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M512">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N512">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O512">
         <v>1</v>
@@ -26993,13 +26993,13 @@
     </row>
     <row r="513" spans="1:16">
       <c r="A513" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B513" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C513">
-        <v>3.163782027212462</v>
+        <v>3.29280938304307</v>
       </c>
       <c r="D513" t="s">
         <v>130</v>
@@ -27011,22 +27011,22 @@
         <v>-1</v>
       </c>
       <c r="G513">
-        <v>0.002836217972787538</v>
+        <v>0.00294719061695693</v>
       </c>
       <c r="H513">
         <v>0.002381693439925723</v>
       </c>
       <c r="I513">
-        <v>0.4854754671381856</v>
+        <v>0.6145028229687939</v>
       </c>
       <c r="J513">
         <v>-0.1289622261515449</v>
       </c>
       <c r="K513">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L513">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M513">
         <v>1.15</v>
@@ -27043,96 +27043,96 @@
     </row>
     <row r="514" spans="1:16">
       <c r="A514" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B514" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C514">
-        <v>2.292718610119939</v>
+        <v>3.163782027212462</v>
       </c>
       <c r="D514" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E514">
-        <v>2.702522585097013</v>
+        <v>2.678306560074276</v>
       </c>
       <c r="F514">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G514">
-        <v>0.002107281389880062</v>
+        <v>0.002836217972787538</v>
       </c>
       <c r="H514">
-        <v>0.002477477414902987</v>
+        <v>0.002381693439925723</v>
       </c>
       <c r="I514">
-        <v>0.4098039749770739</v>
+        <v>0.4854754671381856</v>
       </c>
       <c r="J514">
-        <v>-0.09001806807761016</v>
+        <v>-0.1289622261515449</v>
       </c>
       <c r="K514">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L514">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M514">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N514">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O514">
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="515" spans="1:16">
       <c r="A515" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B515" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C515">
-        <v>3.240624211223998</v>
+        <v>2.292718610119939</v>
       </c>
       <c r="D515" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E515">
-        <v>2.633520778289252</v>
+        <v>2.702522585097013</v>
       </c>
       <c r="F515">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G515">
-        <v>0.002999375788776002</v>
+        <v>0.002107281389880062</v>
       </c>
       <c r="H515">
-        <v>0.002426479221710748</v>
+        <v>0.002477477414902987</v>
       </c>
       <c r="I515">
-        <v>0.6071034329347462</v>
+        <v>0.4098039749770739</v>
       </c>
       <c r="J515">
         <v>-0.09001806807761016</v>
       </c>
       <c r="K515">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L515">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M515">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N515">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O515">
         <v>1</v>
@@ -27143,13 +27143,13 @@
     </row>
     <row r="516" spans="1:16">
       <c r="A516" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B516" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C516">
-        <v>3.114322946458565</v>
+        <v>3.240624211223998</v>
       </c>
       <c r="D516" t="s">
         <v>130</v>
@@ -27161,22 +27161,22 @@
         <v>-1</v>
       </c>
       <c r="G516">
-        <v>0.002885677053541435</v>
+        <v>0.002999375788776002</v>
       </c>
       <c r="H516">
         <v>0.002426479221710748</v>
       </c>
       <c r="I516">
-        <v>0.4808021681693133</v>
+        <v>0.6071034329347462</v>
       </c>
       <c r="J516">
         <v>-0.09001806807761016</v>
       </c>
       <c r="K516">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L516">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M516">
         <v>1.15</v>
@@ -27193,96 +27193,96 @@
     </row>
     <row r="517" spans="1:16">
       <c r="A517" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B517" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C517">
-        <v>2.190845625202192</v>
+        <v>3.114322946458565</v>
       </c>
       <c r="D517" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E517">
-        <v>2.57889032184732</v>
+        <v>2.633520778289252</v>
       </c>
       <c r="F517">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G517">
-        <v>0.002209154374797808</v>
+        <v>0.002885677053541435</v>
       </c>
       <c r="H517">
-        <v>0.00260110967815268</v>
+        <v>0.002426479221710748</v>
       </c>
       <c r="I517">
-        <v>0.3880446966451281</v>
+        <v>0.4808021681693133</v>
       </c>
       <c r="J517">
-        <v>0.008887742522143843</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K517">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L517">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M517">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N517">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O517">
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="518" spans="1:16">
       <c r="A518" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B518" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C518">
-        <v>3.108090425020327</v>
+        <v>2.190845625202192</v>
       </c>
       <c r="D518" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E518">
-        <v>2.519779096099534</v>
+        <v>2.57889032184732</v>
       </c>
       <c r="F518">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G518">
-        <v>0.003131909574979673</v>
+        <v>0.002209154374797808</v>
       </c>
       <c r="H518">
-        <v>0.002540220903900465</v>
+        <v>0.00260110967815268</v>
       </c>
       <c r="I518">
-        <v>0.5883113289207929</v>
+        <v>0.3880446966451281</v>
       </c>
       <c r="J518">
         <v>0.008887742522143843</v>
       </c>
       <c r="K518">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L518">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M518">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N518">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O518">
         <v>1</v>
@@ -27293,13 +27293,13 @@
     </row>
     <row r="519" spans="1:16">
       <c r="A519" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B519" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C519">
-        <v>2.988712566996877</v>
+        <v>3.108090425020327</v>
       </c>
       <c r="D519" t="s">
         <v>130</v>
@@ -27311,22 +27311,22 @@
         <v>-1</v>
       </c>
       <c r="G519">
-        <v>0.003011287433003123</v>
+        <v>0.003131909574979673</v>
       </c>
       <c r="H519">
         <v>0.002540220903900465</v>
       </c>
       <c r="I519">
-        <v>0.4689334708973432</v>
+        <v>0.5883113289207929</v>
       </c>
       <c r="J519">
         <v>0.008887742522143843</v>
       </c>
       <c r="K519">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L519">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M519">
         <v>1.15</v>
@@ -27343,96 +27343,96 @@
     </row>
     <row r="520" spans="1:16">
       <c r="A520" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B520" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C520">
-        <v>2.151298027264343</v>
+        <v>2.988712566996877</v>
       </c>
       <c r="D520" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E520">
-        <v>2.530895664155756</v>
+        <v>2.519779096099534</v>
       </c>
       <c r="F520">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G520">
-        <v>0.002248701972735657</v>
+        <v>0.003011287433003123</v>
       </c>
       <c r="H520">
-        <v>0.002649104335844244</v>
+        <v>0.002540220903900465</v>
       </c>
       <c r="I520">
-        <v>0.3795976368914125</v>
+        <v>0.4689334708973432</v>
       </c>
       <c r="J520">
-        <v>0.04728346867539508</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K520">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L520">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M520">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N520">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O520">
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="521" spans="1:16">
       <c r="A521" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B521" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C521">
-        <v>3.056640151974971</v>
+        <v>2.151298027264343</v>
       </c>
       <c r="D521" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E521">
-        <v>2.475624011023295</v>
+        <v>2.530895664155756</v>
       </c>
       <c r="F521">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G521">
-        <v>0.00318335984802503</v>
+        <v>0.002248701972735657</v>
       </c>
       <c r="H521">
-        <v>0.002584375988976704</v>
+        <v>0.002649104335844244</v>
       </c>
       <c r="I521">
-        <v>0.5810161409516752</v>
+        <v>0.3795976368914125</v>
       </c>
       <c r="J521">
         <v>0.04728346867539508</v>
       </c>
       <c r="K521">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L521">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M521">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N521">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O521">
         <v>1</v>
@@ -27443,13 +27443,13 @@
     </row>
     <row r="522" spans="1:16">
       <c r="A522" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B522" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C522">
-        <v>2.939949994782248</v>
+        <v>3.056640151974971</v>
       </c>
       <c r="D522" t="s">
         <v>130</v>
@@ -27461,22 +27461,22 @@
         <v>-1</v>
       </c>
       <c r="G522">
-        <v>0.003060050005217752</v>
+        <v>0.00318335984802503</v>
       </c>
       <c r="H522">
         <v>0.002584375988976704</v>
       </c>
       <c r="I522">
-        <v>0.4643259837589526</v>
+        <v>0.5810161409516752</v>
       </c>
       <c r="J522">
         <v>0.04728346867539508</v>
       </c>
       <c r="K522">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L522">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M522">
         <v>1.15</v>
@@ -27493,96 +27493,96 @@
     </row>
     <row r="523" spans="1:16">
       <c r="A523" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B523" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C523">
-        <v>2.129744886456478</v>
+        <v>2.939949994782248</v>
       </c>
       <c r="D523" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E523">
-        <v>2.504738939874366</v>
+        <v>2.475624011023295</v>
       </c>
       <c r="F523">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G523">
-        <v>0.002270255113543523</v>
+        <v>0.003060050005217752</v>
       </c>
       <c r="H523">
-        <v>0.002675261060125634</v>
+        <v>0.002584375988976704</v>
       </c>
       <c r="I523">
-        <v>0.3749940534178879</v>
+        <v>0.4643259837589526</v>
       </c>
       <c r="J523">
-        <v>0.06820884810050738</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K523">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L523">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M523">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N523">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O523">
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="524" spans="1:16">
       <c r="A524" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B524" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C524">
-        <v>3.02860014354532</v>
+        <v>2.129744886456478</v>
       </c>
       <c r="D524" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E524">
-        <v>2.451559824684416</v>
+        <v>2.504738939874366</v>
       </c>
       <c r="F524">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G524">
-        <v>0.00321139985645468</v>
+        <v>0.002270255113543523</v>
       </c>
       <c r="H524">
-        <v>0.002608440175315583</v>
+        <v>0.002675261060125634</v>
       </c>
       <c r="I524">
-        <v>0.5770403188609037</v>
+        <v>0.3749940534178879</v>
       </c>
       <c r="J524">
         <v>0.06820884810050738</v>
       </c>
       <c r="K524">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L524">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M524">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N524">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27593,13 +27593,13 @@
     </row>
     <row r="525" spans="1:16">
       <c r="A525" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B525" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C525">
-        <v>2.913374762912356</v>
+        <v>3.02860014354532</v>
       </c>
       <c r="D525" t="s">
         <v>130</v>
@@ -27611,22 +27611,22 @@
         <v>-1</v>
       </c>
       <c r="G525">
-        <v>0.003086625237087645</v>
+        <v>0.00321139985645468</v>
       </c>
       <c r="H525">
         <v>0.002608440175315583</v>
       </c>
       <c r="I525">
-        <v>0.4618149382279393</v>
+        <v>0.5770403188609037</v>
       </c>
       <c r="J525">
         <v>0.06820884810050738</v>
       </c>
       <c r="K525">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L525">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M525">
         <v>1.15</v>
@@ -27643,96 +27643,96 @@
     </row>
     <row r="526" spans="1:16">
       <c r="A526" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B526" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C526">
-        <v>2.123592991344732</v>
+        <v>2.913374762912356</v>
       </c>
       <c r="D526" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E526">
-        <v>2.497273047748461</v>
+        <v>2.451559824684416</v>
       </c>
       <c r="F526">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G526">
-        <v>0.002276407008655268</v>
+        <v>0.003086625237087645</v>
       </c>
       <c r="H526">
-        <v>0.002682726952251539</v>
+        <v>0.002608440175315583</v>
       </c>
       <c r="I526">
-        <v>0.3736800564037286</v>
+        <v>0.4618149382279393</v>
       </c>
       <c r="J526">
-        <v>0.07418156180123091</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K526">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L526">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M526">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N526">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O526">
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="527" spans="1:16">
       <c r="A527" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B527" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C527">
-        <v>3.020596707186351</v>
+        <v>2.123592991344732</v>
       </c>
       <c r="D527" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E527">
-        <v>2.444691203928584</v>
+        <v>2.497273047748461</v>
       </c>
       <c r="F527">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G527">
-        <v>0.00321940329281365</v>
+        <v>0.002276407008655268</v>
       </c>
       <c r="H527">
-        <v>0.002615308796071415</v>
+        <v>0.002682726952251539</v>
       </c>
       <c r="I527">
-        <v>0.5759055032577662</v>
+        <v>0.3736800564037286</v>
       </c>
       <c r="J527">
         <v>0.07418156180123091</v>
       </c>
       <c r="K527">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L527">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M527">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N527">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27743,13 +27743,13 @@
     </row>
     <row r="528" spans="1:16">
       <c r="A528" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B528" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C528">
-        <v>2.905789416512437</v>
+        <v>3.020596707186351</v>
       </c>
       <c r="D528" t="s">
         <v>130</v>
@@ -27761,22 +27761,22 @@
         <v>-1</v>
       </c>
       <c r="G528">
-        <v>0.003094210583487563</v>
+        <v>0.00321940329281365</v>
       </c>
       <c r="H528">
         <v>0.002615308796071415</v>
       </c>
       <c r="I528">
-        <v>0.4610982125838525</v>
+        <v>0.5759055032577662</v>
       </c>
       <c r="J528">
         <v>0.07418156180123091</v>
       </c>
       <c r="K528">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L528">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M528">
         <v>1.15</v>
@@ -27793,96 +27793,96 @@
     </row>
     <row r="529" spans="1:16">
       <c r="A529" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B529" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C529">
-        <v>2.162997802089755</v>
+        <v>2.905789416512437</v>
       </c>
       <c r="D529" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E529">
-        <v>2.545094420011838</v>
+        <v>2.444691203928584</v>
       </c>
       <c r="F529">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G529">
-        <v>0.002237002197910246</v>
+        <v>0.003094210583487563</v>
       </c>
       <c r="H529">
-        <v>0.002634905579988162</v>
+        <v>0.002615308796071415</v>
       </c>
       <c r="I529">
-        <v>0.382096617922083</v>
+        <v>0.4610982125838525</v>
       </c>
       <c r="J529">
-        <v>0.03592446399052947</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K529">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L529">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M529">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N529">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O529">
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="530" spans="1:16">
       <c r="A530" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B530" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C530">
-        <v>3.071861218252691</v>
+        <v>2.162997802089755</v>
       </c>
       <c r="D530" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E530">
-        <v>2.488686866410891</v>
+        <v>2.545094420011838</v>
       </c>
       <c r="F530">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G530">
-        <v>0.00316813878174731</v>
+        <v>0.002237002197910246</v>
       </c>
       <c r="H530">
-        <v>0.002571313133589109</v>
+        <v>0.002634905579988162</v>
       </c>
       <c r="I530">
-        <v>0.5831743518417998</v>
+        <v>0.382096617922083</v>
       </c>
       <c r="J530">
         <v>0.03592446399052947</v>
       </c>
       <c r="K530">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L530">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M530">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N530">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -27893,13 +27893,13 @@
     </row>
     <row r="531" spans="1:16">
       <c r="A531" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B531" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C531">
-        <v>2.954375930732028</v>
+        <v>3.071861218252691</v>
       </c>
       <c r="D531" t="s">
         <v>130</v>
@@ -27911,22 +27911,22 @@
         <v>-1</v>
       </c>
       <c r="G531">
-        <v>0.003045624069267972</v>
+        <v>0.00316813878174731</v>
       </c>
       <c r="H531">
         <v>0.002571313133589109</v>
       </c>
       <c r="I531">
-        <v>0.4656890643211367</v>
+        <v>0.5831743518417998</v>
       </c>
       <c r="J531">
         <v>0.03592446399052947</v>
       </c>
       <c r="K531">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L531">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M531">
         <v>1.15</v>
@@ -27943,96 +27943,96 @@
     </row>
     <row r="532" spans="1:16">
       <c r="A532" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B532" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C532">
-        <v>2.152181822645585</v>
+        <v>2.954375930732028</v>
       </c>
       <c r="D532" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E532">
-        <v>2.531968231366001</v>
+        <v>2.488686866410891</v>
       </c>
       <c r="F532">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G532">
-        <v>0.002247818177354416</v>
+        <v>0.003045624069267972</v>
       </c>
       <c r="H532">
-        <v>0.002648031768633999</v>
+        <v>0.002571313133589109</v>
       </c>
       <c r="I532">
-        <v>0.3797864087204159</v>
+        <v>0.4656890643211367</v>
       </c>
       <c r="J532">
-        <v>0.04642541490719935</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K532">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L532">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M532">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N532">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O532">
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="533" spans="1:16">
       <c r="A533" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B533" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C533">
-        <v>3.057789944024353</v>
+        <v>2.152181822645585</v>
       </c>
       <c r="D533" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E533">
-        <v>2.47661077285672</v>
+        <v>2.531968231366001</v>
       </c>
       <c r="F533">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G533">
-        <v>0.003182210055975647</v>
+        <v>0.002247818177354416</v>
       </c>
       <c r="H533">
-        <v>0.002583389227143279</v>
+        <v>0.002648031768633999</v>
       </c>
       <c r="I533">
-        <v>0.5811791711676326</v>
+        <v>0.3797864087204159</v>
       </c>
       <c r="J533">
         <v>0.04642541490719935</v>
       </c>
       <c r="K533">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L533">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M533">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N533">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28043,46 +28043,46 @@
     </row>
     <row r="534" spans="1:16">
       <c r="A534" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B534" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C534">
-        <v>2.941039723067857</v>
+        <v>3.057789944024353</v>
       </c>
       <c r="D534" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E534">
-        <v>2.47661077285672</v>
+        <v>2.525682264558577</v>
       </c>
       <c r="F534">
         <v>-1</v>
       </c>
       <c r="G534">
-        <v>0.003058960276932143</v>
+        <v>0.003182210055975647</v>
       </c>
       <c r="H534">
-        <v>0.002583389227143279</v>
+        <v>0.002634317735441423</v>
       </c>
       <c r="I534">
-        <v>0.4644289502111363</v>
+        <v>0.532107679465776</v>
       </c>
       <c r="J534">
         <v>0.04642541490719935</v>
       </c>
       <c r="K534">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L534">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M534">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N534">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O534">
         <v>1</v>
@@ -28093,96 +28093,96 @@
     </row>
     <row r="535" spans="1:16">
       <c r="A535" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B535" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C535">
-        <v>2.132867933343715</v>
+        <v>2.941039723067857</v>
       </c>
       <c r="D535" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E535">
-        <v>2.508529045320043</v>
+        <v>2.525682264558577</v>
       </c>
       <c r="F535">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G535">
-        <v>0.002267132066656285</v>
+        <v>0.003058960276932143</v>
       </c>
       <c r="H535">
-        <v>0.002671470954679957</v>
+        <v>0.002634317735441423</v>
       </c>
       <c r="I535">
-        <v>0.3756611119763273</v>
+        <v>0.4153574585092796</v>
       </c>
       <c r="J535">
-        <v>0.06517676374396589</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K535">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L535">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M535">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N535">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O535">
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="536" spans="1:16">
       <c r="A536" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B536" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C536">
-        <v>3.032663136583086</v>
+        <v>2.132867933343715</v>
       </c>
       <c r="D536" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E536">
-        <v>2.50374318641956</v>
+        <v>2.508529045320043</v>
       </c>
       <c r="F536">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G536">
-        <v>0.003207336863416915</v>
+        <v>0.002267132066656285</v>
       </c>
       <c r="H536">
-        <v>0.00265625681358044</v>
+        <v>0.002671470954679957</v>
       </c>
       <c r="I536">
-        <v>0.5289199501635258</v>
+        <v>0.3756611119763273</v>
       </c>
       <c r="J536">
         <v>0.06517676374396589</v>
       </c>
       <c r="K536">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L536">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M536">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N536">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28193,13 +28193,13 @@
     </row>
     <row r="537" spans="1:16">
       <c r="A537" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B537" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C537">
-        <v>2.917225510045163</v>
+        <v>3.032663136583086</v>
       </c>
       <c r="D537" t="s">
         <v>132</v>
@@ -28211,22 +28211,22 @@
         <v>-1</v>
       </c>
       <c r="G537">
-        <v>0.003082774489954837</v>
+        <v>0.003207336863416915</v>
       </c>
       <c r="H537">
         <v>0.00265625681358044</v>
       </c>
       <c r="I537">
-        <v>0.4134823236256033</v>
+        <v>0.5289199501635258</v>
       </c>
       <c r="J537">
         <v>0.06517676374396589</v>
       </c>
       <c r="K537">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L537">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M537">
         <v>1.17</v>
@@ -28243,96 +28243,96 @@
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B538" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C538">
-        <v>2.104641124313295</v>
+        <v>2.917225510045163</v>
       </c>
       <c r="D538" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E538">
-        <v>2.474273209118076</v>
+        <v>2.50374318641956</v>
       </c>
       <c r="F538">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G538">
-        <v>0.002295358875686706</v>
+        <v>0.003082774489954837</v>
       </c>
       <c r="H538">
-        <v>0.002705726790881924</v>
+        <v>0.00265625681358044</v>
       </c>
       <c r="I538">
-        <v>0.3696320848047812</v>
+        <v>0.4134823236256033</v>
       </c>
       <c r="J538">
-        <v>0.09258143270553931</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K538">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L538">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M538">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N538">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O538">
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B539" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C539">
-        <v>2.995940880174577</v>
+        <v>2.104641124313295</v>
       </c>
       <c r="D539" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E539">
-        <v>2.471679723734519</v>
+        <v>2.527050652099242</v>
       </c>
       <c r="F539">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G539">
-        <v>0.003244059119825423</v>
+        <v>0.002295358875686706</v>
       </c>
       <c r="H539">
-        <v>0.002688320276265481</v>
+        <v>0.002752949347900758</v>
       </c>
       <c r="I539">
-        <v>0.5242611564400583</v>
+        <v>0.4224095277859474</v>
       </c>
       <c r="J539">
         <v>0.09258143270553931</v>
       </c>
       <c r="K539">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L539">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M539">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N539">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28343,13 +28343,13 @@
     </row>
     <row r="540" spans="1:16">
       <c r="A540" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B540" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C540">
-        <v>2.882421580463965</v>
+        <v>2.995940880174577</v>
       </c>
       <c r="D540" t="s">
         <v>132</v>
@@ -28361,22 +28361,22 @@
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.003117578419536035</v>
+        <v>0.003244059119825423</v>
       </c>
       <c r="H540">
         <v>0.002688320276265481</v>
       </c>
       <c r="I540">
-        <v>0.4107418567294463</v>
+        <v>0.5242611564400583</v>
       </c>
       <c r="J540">
         <v>0.09258143270553931</v>
       </c>
       <c r="K540">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L540">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M540">
         <v>1.17</v>
@@ -28393,96 +28393,96 @@
     </row>
     <row r="541" spans="1:16">
       <c r="A541" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B541" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C541">
-        <v>2.097453766817889</v>
+        <v>2.882421580463965</v>
       </c>
       <c r="D541" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E541">
-        <v>2.518537471376529</v>
+        <v>2.471679723734519</v>
       </c>
       <c r="F541">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.002302546233182111</v>
+        <v>0.003117578419536035</v>
       </c>
       <c r="H541">
-        <v>0.002761462528623472</v>
+        <v>0.002688320276265481</v>
       </c>
       <c r="I541">
-        <v>0.4210837045586393</v>
+        <v>0.4107418567294463</v>
       </c>
       <c r="J541">
-        <v>0.09955944969136986</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K541">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L541">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M541">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N541">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="542" spans="1:16">
       <c r="A542" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B542" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C542">
-        <v>2.986590337413564</v>
+        <v>2.097453766817889</v>
       </c>
       <c r="D542" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E542">
-        <v>2.463515443861097</v>
+        <v>2.518537471376529</v>
       </c>
       <c r="F542">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G542">
-        <v>0.003253409662586436</v>
+        <v>0.002302546233182111</v>
       </c>
       <c r="H542">
-        <v>0.002696484556138903</v>
+        <v>0.002761462528623472</v>
       </c>
       <c r="I542">
-        <v>0.5230748935524669</v>
+        <v>0.4210837045586393</v>
       </c>
       <c r="J542">
         <v>0.09955944969136986</v>
       </c>
       <c r="K542">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L542">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M542">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N542">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28493,13 +28493,13 @@
     </row>
     <row r="543" spans="1:16">
       <c r="A543" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B543" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C543">
-        <v>2.87355949889196</v>
+        <v>2.986590337413564</v>
       </c>
       <c r="D543" t="s">
         <v>132</v>
@@ -28511,22 +28511,22 @@
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.003126440501108039</v>
+        <v>0.003253409662586436</v>
       </c>
       <c r="H543">
         <v>0.002696484556138903</v>
       </c>
       <c r="I543">
-        <v>0.4100440550308631</v>
+        <v>0.5230748935524669</v>
       </c>
       <c r="J543">
         <v>0.09955944969136986</v>
       </c>
       <c r="K543">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L543">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M543">
         <v>1.17</v>
@@ -28543,96 +28543,96 @@
     </row>
     <row r="544" spans="1:16">
       <c r="A544" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B544" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C544">
-        <v>2.119309945208395</v>
+        <v>2.87355949889196</v>
       </c>
       <c r="D544" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E544">
-        <v>2.508891391411886</v>
+        <v>2.463515443861097</v>
       </c>
       <c r="F544">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.002340690054791605</v>
+        <v>0.003126440501108039</v>
       </c>
       <c r="H544">
-        <v>0.002771108608588114</v>
+        <v>0.002696484556138903</v>
       </c>
       <c r="I544">
-        <v>0.3895814462034908</v>
+        <v>0.4100440550308631</v>
       </c>
       <c r="J544">
-        <v>0.1074660726132081</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K544">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L544">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="M544">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N544">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="545" spans="1:16">
       <c r="A545" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B545" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C545">
-        <v>2.975995462698301</v>
+        <v>2.119309945208395</v>
       </c>
       <c r="D545" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E545">
-        <v>2.454264695042546</v>
+        <v>2.508891391411886</v>
       </c>
       <c r="F545">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G545">
-        <v>0.003264004537301699</v>
+        <v>0.002340690054791605</v>
       </c>
       <c r="H545">
-        <v>0.002705735304957454</v>
+        <v>0.002771108608588114</v>
       </c>
       <c r="I545">
-        <v>0.5217307676557548</v>
+        <v>0.3895814462034908</v>
       </c>
       <c r="J545">
         <v>0.1074660726132081</v>
       </c>
       <c r="K545">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L545">
-        <v>3.12</v>
+        <v>2.23</v>
       </c>
       <c r="M545">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N545">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28643,13 +28643,13 @@
     </row>
     <row r="546" spans="1:16">
       <c r="A546" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B546" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C546">
-        <v>2.863518087781226</v>
+        <v>2.975995462698301</v>
       </c>
       <c r="D546" t="s">
         <v>132</v>
@@ -28661,22 +28661,22 @@
         <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.003136481912218774</v>
+        <v>0.003264004537301699</v>
       </c>
       <c r="H546">
         <v>0.002705735304957454</v>
       </c>
       <c r="I546">
-        <v>0.4092533927386794</v>
+        <v>0.5217307676557548</v>
       </c>
       <c r="J546">
         <v>0.1074660726132081</v>
       </c>
       <c r="K546">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L546">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M546">
         <v>1.17</v>
@@ -28693,57 +28693,57 @@
     </row>
     <row r="547" spans="1:16">
       <c r="A547" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B547" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C547">
-        <v>2.124107820370248</v>
+        <v>2.863518087781226</v>
       </c>
       <c r="D547" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E547">
-        <v>2.514574311506508</v>
+        <v>2.454264695042546</v>
       </c>
       <c r="F547">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G547">
-        <v>0.002335892179629752</v>
+        <v>0.003136481912218774</v>
       </c>
       <c r="H547">
-        <v>0.002765425688493492</v>
+        <v>0.002705735304957454</v>
       </c>
       <c r="I547">
-        <v>0.3904664911362596</v>
+        <v>0.4092533927386794</v>
       </c>
       <c r="J547">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K547">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L547">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="M547">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N547">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="548" spans="1:16">
       <c r="A548" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B548" t="s">
         <v>56</v>
@@ -28793,7 +28793,7 @@
     </row>
     <row r="549" spans="1:16">
       <c r="A549" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B549" t="s">
         <v>52</v>
@@ -28843,7 +28843,7 @@
     </row>
     <row r="550" spans="1:16">
       <c r="A550" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B550" t="s">
         <v>53</v>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="340">
   <si>
     <t>trade_time</t>
   </si>
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P572"/>
+  <dimension ref="A1:P573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -23052,10 +23052,10 @@
         <v>3.259685052120739</v>
       </c>
       <c r="D434" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E434">
-        <v>2.618836536878837</v>
+        <v>2.649878962640932</v>
       </c>
       <c r="F434">
         <v>-1</v>
@@ -23064,10 +23064,10 @@
         <v>0.002980314947879261</v>
       </c>
       <c r="H434">
-        <v>0.002381163463121163</v>
+        <v>0.002410121037359067</v>
       </c>
       <c r="I434">
-        <v>0.6408485152419017</v>
+        <v>0.6098060894798065</v>
       </c>
       <c r="J434">
         <v>-0.1042425762095065</v>
@@ -23079,10 +23079,10 @@
         <v>3.12</v>
       </c>
       <c r="M434">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N434">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O434">
         <v>1</v>
@@ -23102,10 +23102,10 @@
         <v>3.132388071786073</v>
       </c>
       <c r="D435" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E435">
-        <v>2.618836536878837</v>
+        <v>2.649878962640932</v>
       </c>
       <c r="F435">
         <v>-1</v>
@@ -23114,10 +23114,10 @@
         <v>0.002867611928213927</v>
       </c>
       <c r="H435">
-        <v>0.002381163463121163</v>
+        <v>0.002410121037359067</v>
       </c>
       <c r="I435">
-        <v>0.5135515349072359</v>
+        <v>0.4825091091451408</v>
       </c>
       <c r="J435">
         <v>-0.1042425762095065</v>
@@ -23129,10 +23129,10 @@
         <v>3</v>
       </c>
       <c r="M435">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N435">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O435">
         <v>1</v>
@@ -26702,10 +26702,10 @@
         <v>3.452170072557747</v>
       </c>
       <c r="D507" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E507">
-        <v>2.815071330926425</v>
+        <v>2.870029093203406</v>
       </c>
       <c r="F507">
         <v>-1</v>
@@ -26714,10 +26714,10 @@
         <v>0.002787829927442253</v>
       </c>
       <c r="H507">
-        <v>0.002244928669073575</v>
+        <v>0.002289970906796594</v>
       </c>
       <c r="I507">
-        <v>0.6370987416313225</v>
+        <v>0.5821409793543411</v>
       </c>
       <c r="J507">
         <v>-0.2478881138490649</v>
@@ -26729,10 +26729,10 @@
         <v>3.12</v>
       </c>
       <c r="M507">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N507">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O507">
         <v>1</v>
@@ -26752,10 +26752,10 @@
         <v>3.314817904588312</v>
       </c>
       <c r="D508" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E508">
-        <v>2.815071330926425</v>
+        <v>2.870029093203406</v>
       </c>
       <c r="F508">
         <v>-1</v>
@@ -26764,10 +26764,10 @@
         <v>0.002685182095411688</v>
       </c>
       <c r="H508">
-        <v>0.002244928669073575</v>
+        <v>0.002289970906796594</v>
       </c>
       <c r="I508">
-        <v>0.4997465736618878</v>
+        <v>0.4447888113849063</v>
       </c>
       <c r="J508">
         <v>-0.2478881138490649</v>
@@ -26779,10 +26779,10 @@
         <v>3</v>
       </c>
       <c r="M508">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N508">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O508">
         <v>1</v>
@@ -27902,10 +27902,10 @@
         <v>3.071861218252691</v>
       </c>
       <c r="D531" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E531">
-        <v>2.488686866410891</v>
+        <v>2.537968377131081</v>
       </c>
       <c r="F531">
         <v>-1</v>
@@ -27914,10 +27914,10 @@
         <v>0.00316813878174731</v>
       </c>
       <c r="H531">
-        <v>0.002571313133589109</v>
+        <v>0.00262203162286892</v>
       </c>
       <c r="I531">
-        <v>0.5831743518417998</v>
+        <v>0.53389284112161</v>
       </c>
       <c r="J531">
         <v>0.03592446399052947</v>
@@ -27929,10 +27929,10 @@
         <v>3.12</v>
       </c>
       <c r="M531">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N531">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -27952,10 +27952,10 @@
         <v>2.954375930732028</v>
       </c>
       <c r="D532" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E532">
-        <v>2.488686866410891</v>
+        <v>2.537968377131081</v>
       </c>
       <c r="F532">
         <v>-1</v>
@@ -27964,10 +27964,10 @@
         <v>0.003045624069267972</v>
       </c>
       <c r="H532">
-        <v>0.002571313133589109</v>
+        <v>0.00262203162286892</v>
       </c>
       <c r="I532">
-        <v>0.4656890643211367</v>
+        <v>0.4164075536009468</v>
       </c>
       <c r="J532">
         <v>0.03592446399052947</v>
@@ -27979,10 +27979,10 @@
         <v>3</v>
       </c>
       <c r="M532">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N532">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O532">
         <v>1</v>
@@ -28446,10 +28446,10 @@
         <v>0</v>
       </c>
       <c r="B542" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C542">
-        <v>2.097453766817889</v>
+        <v>2.127453766817889</v>
       </c>
       <c r="D542" t="s">
         <v>133</v>
@@ -28461,13 +28461,13 @@
         <v>1</v>
       </c>
       <c r="G542">
-        <v>0.002302546233182111</v>
+        <v>0.002332546233182111</v>
       </c>
       <c r="H542">
         <v>0.002761462528623472</v>
       </c>
       <c r="I542">
-        <v>0.4210837045586393</v>
+        <v>0.3910837045586395</v>
       </c>
       <c r="J542">
         <v>0.09955944969136986</v>
@@ -28476,7 +28476,7 @@
         <v>1.03</v>
       </c>
       <c r="L542">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="M542">
         <v>1.22</v>
@@ -29646,43 +29646,43 @@
         <v>0</v>
       </c>
       <c r="B566" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C566">
-        <v>2.575095597538799</v>
+        <v>1.838291711302243</v>
       </c>
       <c r="D566" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E566">
-        <v>2.633560752891249</v>
+        <v>2.143893006714428</v>
       </c>
       <c r="F566">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G566">
-        <v>0.003664904402461202</v>
+        <v>0.002781708288697757</v>
       </c>
       <c r="H566">
-        <v>0.003666439247108751</v>
+        <v>0.003136106993285572</v>
       </c>
       <c r="I566">
-        <v>-0.05846515535245045</v>
+        <v>0.3056012954121849</v>
       </c>
       <c r="J566">
         <v>0.4066450764635833</v>
       </c>
       <c r="K566">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="L566">
-        <v>3.12</v>
+        <v>2.31</v>
       </c>
       <c r="M566">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="N566">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="O566">
         <v>1</v>
@@ -29696,43 +29696,43 @@
         <v>1</v>
       </c>
       <c r="B567" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C567">
-        <v>2.483560752891249</v>
+        <v>2.575095597538799</v>
       </c>
       <c r="D567" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E567">
-        <v>2.104225260537608</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="F567">
         <v>-1</v>
       </c>
       <c r="G567">
-        <v>0.003516439247108751</v>
+        <v>0.003664904402461202</v>
       </c>
       <c r="H567">
-        <v>0.003055774739462393</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="I567">
-        <v>0.3793354923536416</v>
+        <v>-0.05846515535245045</v>
       </c>
       <c r="J567">
         <v>0.4066450764635833</v>
       </c>
       <c r="K567">
+        <v>1.34</v>
+      </c>
+      <c r="L567">
+        <v>3.12</v>
+      </c>
+      <c r="M567">
         <v>1.27</v>
       </c>
-      <c r="L567">
-        <v>3</v>
-      </c>
-      <c r="M567">
-        <v>1.17</v>
-      </c>
       <c r="N567">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O567">
         <v>1</v>
@@ -29743,96 +29743,96 @@
     </row>
     <row r="568" spans="1:16">
       <c r="A568" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B568" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C568">
-        <v>1.784876857591519</v>
+        <v>2.483560752891249</v>
       </c>
       <c r="D568" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E568">
-        <v>2.087715315742805</v>
+        <v>2.104225260537608</v>
       </c>
       <c r="F568">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G568">
-        <v>0.002835123142408481</v>
+        <v>0.003516439247108751</v>
       </c>
       <c r="H568">
-        <v>0.003192284684257196</v>
+        <v>0.003055774739462393</v>
       </c>
       <c r="I568">
-        <v>0.3028384581512857</v>
+        <v>0.3793354923536416</v>
       </c>
       <c r="J568">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K568">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="L568">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="M568">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N568">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O568">
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="569" spans="1:16">
       <c r="A569" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B569" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C569">
-        <v>2.513392232045375</v>
+        <v>1.784876857591519</v>
       </c>
       <c r="D569" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E569">
-        <v>2.575080697535542</v>
+        <v>2.087715315742805</v>
       </c>
       <c r="F569">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G569">
-        <v>0.003726607767954625</v>
+        <v>0.002835123142408481</v>
       </c>
       <c r="H569">
-        <v>0.003724919302464458</v>
+        <v>0.003192284684257196</v>
       </c>
       <c r="I569">
-        <v>-0.0616884654901666</v>
+        <v>0.3028384581512857</v>
       </c>
       <c r="J569">
         <v>0.4526923641452424</v>
       </c>
       <c r="K569">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="L569">
-        <v>3.12</v>
+        <v>2.31</v>
       </c>
       <c r="M569">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="N569">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="O569">
         <v>1</v>
@@ -29843,46 +29843,46 @@
     </row>
     <row r="570" spans="1:16">
       <c r="A570" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B570" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C570">
-        <v>2.425080697535542</v>
+        <v>2.513392232045375</v>
       </c>
       <c r="D570" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E570">
-        <v>2.050349933950066</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="F570">
         <v>-1</v>
       </c>
       <c r="G570">
-        <v>0.003574919302464458</v>
+        <v>0.003726607767954625</v>
       </c>
       <c r="H570">
-        <v>0.003109650066049934</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="I570">
-        <v>0.3747307635854757</v>
+        <v>-0.0616884654901666</v>
       </c>
       <c r="J570">
         <v>0.4526923641452424</v>
       </c>
       <c r="K570">
+        <v>1.34</v>
+      </c>
+      <c r="L570">
+        <v>3.12</v>
+      </c>
+      <c r="M570">
         <v>1.27</v>
       </c>
-      <c r="L570">
-        <v>3</v>
-      </c>
-      <c r="M570">
-        <v>1.17</v>
-      </c>
       <c r="N570">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O570">
         <v>1</v>
@@ -29893,101 +29893,151 @@
     </row>
     <row r="571" spans="1:16">
       <c r="A571" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B571" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C571">
-        <v>2.46037019732591</v>
+        <v>2.425080697535542</v>
       </c>
       <c r="D571" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E571">
-        <v>2.524828470599929</v>
+        <v>2.050349933950066</v>
       </c>
       <c r="F571">
         <v>-1</v>
       </c>
       <c r="G571">
-        <v>0.00377962980267409</v>
+        <v>0.003574919302464458</v>
       </c>
       <c r="H571">
-        <v>0.003775171529400071</v>
+        <v>0.003109650066049934</v>
       </c>
       <c r="I571">
-        <v>-0.0644582732740191</v>
+        <v>0.3747307635854757</v>
       </c>
       <c r="J571">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K571">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L571">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M571">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N571">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O571">
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>57</v>
+        <v>339</v>
       </c>
     </row>
     <row r="572" spans="1:16">
       <c r="A572" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B572" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C572">
-        <v>2.37482847059993</v>
+        <v>2.46037019732591</v>
       </c>
       <c r="D572" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E572">
-        <v>2.004054575277101</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="F572">
         <v>-1</v>
       </c>
       <c r="G572">
-        <v>0.003625171529400071</v>
+        <v>0.00377962980267409</v>
       </c>
       <c r="H572">
-        <v>0.003155945424722899</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="I572">
-        <v>0.370773895322829</v>
+        <v>-0.0644582732740191</v>
       </c>
       <c r="J572">
         <v>0.4922610467717091</v>
       </c>
       <c r="K572">
+        <v>1.34</v>
+      </c>
+      <c r="L572">
+        <v>3.12</v>
+      </c>
+      <c r="M572">
         <v>1.27</v>
       </c>
-      <c r="L572">
+      <c r="N572">
+        <v>3.15</v>
+      </c>
+      <c r="O572">
+        <v>1</v>
+      </c>
+      <c r="P572" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="573" spans="1:16">
+      <c r="A573" s="1">
+        <v>1</v>
+      </c>
+      <c r="B573" t="s">
+        <v>53</v>
+      </c>
+      <c r="C573">
+        <v>2.37482847059993</v>
+      </c>
+      <c r="D573" t="s">
+        <v>132</v>
+      </c>
+      <c r="E573">
+        <v>2.004054575277101</v>
+      </c>
+      <c r="F573">
+        <v>-1</v>
+      </c>
+      <c r="G573">
+        <v>0.003625171529400071</v>
+      </c>
+      <c r="H573">
+        <v>0.003155945424722899</v>
+      </c>
+      <c r="I573">
+        <v>0.370773895322829</v>
+      </c>
+      <c r="J573">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K573">
+        <v>1.27</v>
+      </c>
+      <c r="L573">
         <v>3</v>
       </c>
-      <c r="M572">
+      <c r="M573">
         <v>1.17</v>
       </c>
-      <c r="N572">
+      <c r="N573">
         <v>2.58</v>
       </c>
-      <c r="O572">
-        <v>1</v>
-      </c>
-      <c r="P572" t="s">
+      <c r="O573">
+        <v>1</v>
+      </c>
+      <c r="P573" t="s">
         <v>57</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -22952,10 +22952,10 @@
         <v>3.22654267572782</v>
       </c>
       <c r="D432" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E432">
-        <v>2.590640783828145</v>
+        <v>2.621435878423129</v>
       </c>
       <c r="F432">
         <v>-1</v>
@@ -22964,10 +22964,10 @@
         <v>0.00301345732427218</v>
       </c>
       <c r="H432">
-        <v>0.002409359216171855</v>
+        <v>0.002438564121576871</v>
       </c>
       <c r="I432">
-        <v>0.6359018918996746</v>
+        <v>0.6051067973046909</v>
       </c>
       <c r="J432">
         <v>-0.0795094594983729</v>
@@ -22979,10 +22979,10 @@
         <v>3.12</v>
       </c>
       <c r="M432">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N432">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O432">
         <v>1</v>
@@ -23002,10 +23002,10 @@
         <v>3.100977013562934</v>
       </c>
       <c r="D433" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E433">
-        <v>2.590640783828145</v>
+        <v>2.621435878423129</v>
       </c>
       <c r="F433">
         <v>-1</v>
@@ -23014,10 +23014,10 @@
         <v>0.002899022986437066</v>
       </c>
       <c r="H433">
-        <v>0.002409359216171855</v>
+        <v>0.002438564121576871</v>
       </c>
       <c r="I433">
-        <v>0.5103362297347886</v>
+        <v>0.4795411351398049</v>
       </c>
       <c r="J433">
         <v>-0.0795094594983729</v>
@@ -23029,10 +23029,10 @@
         <v>3</v>
       </c>
       <c r="M433">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N433">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O433">
         <v>1</v>
@@ -26402,10 +26402,10 @@
         <v>3.49154204736155</v>
       </c>
       <c r="D501" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E501">
-        <v>2.848860712287897</v>
+        <v>2.904406115979861</v>
       </c>
       <c r="F501">
         <v>-1</v>
@@ -26414,10 +26414,10 @@
         <v>0.00274845795263845</v>
       </c>
       <c r="H501">
-        <v>0.002211139287712102</v>
+        <v>0.002255593884020139</v>
       </c>
       <c r="I501">
-        <v>0.6426813350736529</v>
+        <v>0.5871359313816891</v>
       </c>
       <c r="J501">
         <v>-0.2772701845981717</v>
@@ -26429,10 +26429,10 @@
         <v>3.12</v>
       </c>
       <c r="M501">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N501">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O501">
         <v>1</v>
@@ -26452,10 +26452,10 @@
         <v>3.352133134439678</v>
       </c>
       <c r="D502" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E502">
-        <v>2.848860712287897</v>
+        <v>2.904406115979861</v>
       </c>
       <c r="F502">
         <v>-1</v>
@@ -26464,10 +26464,10 @@
         <v>0.002647866865560322</v>
       </c>
       <c r="H502">
-        <v>0.002211139287712102</v>
+        <v>0.002255593884020139</v>
       </c>
       <c r="I502">
-        <v>0.503272422151781</v>
+        <v>0.4477270184598172</v>
       </c>
       <c r="J502">
         <v>-0.2772701845981717</v>
@@ -26479,10 +26479,10 @@
         <v>3</v>
       </c>
       <c r="M502">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N502">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O502">
         <v>1</v>
@@ -26552,10 +26552,10 @@
         <v>3.489219616823635</v>
       </c>
       <c r="D504" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E504">
-        <v>2.846867581602373</v>
+        <v>2.902378322151979</v>
       </c>
       <c r="F504">
         <v>-1</v>
@@ -26564,10 +26564,10 @@
         <v>0.002750780383176366</v>
       </c>
       <c r="H504">
-        <v>0.002213132418397626</v>
+        <v>0.002257621677848021</v>
       </c>
       <c r="I504">
-        <v>0.6423520352212617</v>
+        <v>0.5868412946716552</v>
       </c>
       <c r="J504">
         <v>-0.2755370274803244</v>
@@ -26579,10 +26579,10 @@
         <v>3.12</v>
       </c>
       <c r="M504">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N504">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O504">
         <v>1</v>
@@ -26602,10 +26602,10 @@
         <v>3.349932024900012</v>
       </c>
       <c r="D505" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E505">
-        <v>2.846867581602373</v>
+        <v>2.902378322151979</v>
       </c>
       <c r="F505">
         <v>-1</v>
@@ -26614,10 +26614,10 @@
         <v>0.002650067975099988</v>
       </c>
       <c r="H505">
-        <v>0.002213132418397626</v>
+        <v>0.002257621677848021</v>
       </c>
       <c r="I505">
-        <v>0.5030644432976388</v>
+        <v>0.4475537027480323</v>
       </c>
       <c r="J505">
         <v>-0.2755370274803244</v>
@@ -26629,10 +26629,10 @@
         <v>3</v>
       </c>
       <c r="M505">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N505">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O505">
         <v>1</v>
@@ -26852,10 +26852,10 @@
         <v>3.363072216113203</v>
       </c>
       <c r="D510" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E510">
-        <v>2.738606752634465</v>
+        <v>2.792234696158543</v>
       </c>
       <c r="F510">
         <v>-1</v>
@@ -26864,10 +26864,10 @@
         <v>0.002876927783886797</v>
       </c>
       <c r="H510">
-        <v>0.002321393247365534</v>
+        <v>0.002367765303841457</v>
       </c>
       <c r="I510">
-        <v>0.6244654634787379</v>
+        <v>0.5708375199546598</v>
       </c>
       <c r="J510">
         <v>-0.181397176203883</v>
@@ -26879,10 +26879,10 @@
         <v>3.12</v>
       </c>
       <c r="M510">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N510">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O510">
         <v>1</v>
@@ -26902,10 +26902,10 @@
         <v>3.230374413778931</v>
       </c>
       <c r="D511" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E511">
-        <v>2.738606752634465</v>
+        <v>2.792234696158543</v>
       </c>
       <c r="F511">
         <v>-1</v>
@@ -26914,10 +26914,10 @@
         <v>0.002769625586221069</v>
       </c>
       <c r="H511">
-        <v>0.002321393247365534</v>
+        <v>0.002367765303841457</v>
       </c>
       <c r="I511">
-        <v>0.4917676611444661</v>
+        <v>0.4381397176203881</v>
       </c>
       <c r="J511">
         <v>-0.181397176203883</v>
@@ -26929,10 +26929,10 @@
         <v>3</v>
       </c>
       <c r="M511">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N511">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O511">
         <v>1</v>
@@ -27002,10 +27002,10 @@
         <v>3.29280938304307</v>
       </c>
       <c r="D513" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E513">
-        <v>2.678306560074276</v>
+        <v>2.730885804597308</v>
       </c>
       <c r="F513">
         <v>-1</v>
@@ -27014,10 +27014,10 @@
         <v>0.00294719061695693</v>
       </c>
       <c r="H513">
-        <v>0.002381693439925723</v>
+        <v>0.002429114195402692</v>
       </c>
       <c r="I513">
-        <v>0.6145028229687939</v>
+        <v>0.5619235784457626</v>
       </c>
       <c r="J513">
         <v>-0.1289622261515449</v>
@@ -27029,10 +27029,10 @@
         <v>3.12</v>
       </c>
       <c r="M513">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N513">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O513">
         <v>1</v>
@@ -27052,10 +27052,10 @@
         <v>3.163782027212462</v>
       </c>
       <c r="D514" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E514">
-        <v>2.678306560074276</v>
+        <v>2.730885804597308</v>
       </c>
       <c r="F514">
         <v>-1</v>
@@ -27064,10 +27064,10 @@
         <v>0.002836217972787538</v>
       </c>
       <c r="H514">
-        <v>0.002381693439925723</v>
+        <v>0.002429114195402692</v>
       </c>
       <c r="I514">
-        <v>0.4854754671381856</v>
+        <v>0.4328962226151543</v>
       </c>
       <c r="J514">
         <v>-0.1289622261515449</v>
@@ -27079,10 +27079,10 @@
         <v>3</v>
       </c>
       <c r="M514">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N514">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O514">
         <v>1</v>
@@ -27152,10 +27152,10 @@
         <v>3.240624211223998</v>
       </c>
       <c r="D516" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E516">
-        <v>2.633520778289252</v>
+        <v>2.685321139650804</v>
       </c>
       <c r="F516">
         <v>-1</v>
@@ -27164,10 +27164,10 @@
         <v>0.002999375788776002</v>
       </c>
       <c r="H516">
-        <v>0.002426479221710748</v>
+        <v>0.002474678860349197</v>
       </c>
       <c r="I516">
-        <v>0.6071034329347462</v>
+        <v>0.5553030715731939</v>
       </c>
       <c r="J516">
         <v>-0.09001806807761016</v>
@@ -27179,10 +27179,10 @@
         <v>3.12</v>
       </c>
       <c r="M516">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N516">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O516">
         <v>1</v>
@@ -27202,10 +27202,10 @@
         <v>3.114322946458565</v>
       </c>
       <c r="D517" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E517">
-        <v>2.633520778289252</v>
+        <v>2.685321139650804</v>
       </c>
       <c r="F517">
         <v>-1</v>
@@ -27214,10 +27214,10 @@
         <v>0.002885677053541435</v>
       </c>
       <c r="H517">
-        <v>0.002426479221710748</v>
+        <v>0.002474678860349197</v>
       </c>
       <c r="I517">
-        <v>0.4808021681693133</v>
+        <v>0.429001806807761</v>
       </c>
       <c r="J517">
         <v>-0.09001806807761016</v>
@@ -27229,10 +27229,10 @@
         <v>3</v>
       </c>
       <c r="M517">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N517">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O517">
         <v>1</v>
@@ -28152,10 +28152,10 @@
         <v>2.132867933343715</v>
       </c>
       <c r="D536" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E536">
-        <v>2.508529045320043</v>
+        <v>2.560484348232362</v>
       </c>
       <c r="F536">
         <v>1</v>
@@ -28164,10 +28164,10 @@
         <v>0.002267132066656285</v>
       </c>
       <c r="H536">
-        <v>0.002671470954679957</v>
+        <v>0.002719515651767639</v>
       </c>
       <c r="I536">
-        <v>0.3756611119763273</v>
+        <v>0.4276164148886465</v>
       </c>
       <c r="J536">
         <v>0.06517676374396589</v>
@@ -28179,10 +28179,10 @@
         <v>2.2</v>
       </c>
       <c r="M536">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="N536">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="O536">
         <v>1</v>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="340">
   <si>
     <t>trade_time</t>
   </si>
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P573"/>
+  <dimension ref="A1:P576"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -22852,10 +22852,10 @@
         <v>3.185945174511515</v>
       </c>
       <c r="D430" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E430">
-        <v>2.556102611151587</v>
+        <v>2.586594739319583</v>
       </c>
       <c r="F430">
         <v>-1</v>
@@ -22864,10 +22864,10 @@
         <v>0.003054054825488485</v>
       </c>
       <c r="H430">
-        <v>0.002443897388848413</v>
+        <v>0.002473405260680417</v>
       </c>
       <c r="I430">
-        <v>0.6298425633599281</v>
+        <v>0.5993504351919317</v>
       </c>
       <c r="J430">
         <v>-0.0492128167996377</v>
@@ -22879,10 +22879,10 @@
         <v>3.12</v>
       </c>
       <c r="M430">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N430">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O430">
         <v>1</v>
@@ -22902,10 +22902,10 @@
         <v>3.06250027733554</v>
       </c>
       <c r="D431" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E431">
-        <v>2.556102611151587</v>
+        <v>2.586594739319583</v>
       </c>
       <c r="F431">
         <v>-1</v>
@@ -22914,10 +22914,10 @@
         <v>0.00293749972266446</v>
       </c>
       <c r="H431">
-        <v>0.002443897388848413</v>
+        <v>0.002473405260680417</v>
       </c>
       <c r="I431">
-        <v>0.5063976661839531</v>
+        <v>0.4759055380159567</v>
       </c>
       <c r="J431">
         <v>-0.0492128167996377</v>
@@ -22929,10 +22929,10 @@
         <v>3</v>
       </c>
       <c r="M431">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N431">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O431">
         <v>1</v>
@@ -24946,43 +24946,43 @@
         <v>0</v>
       </c>
       <c r="B472" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C472">
-        <v>3.389468548537006</v>
+        <v>2.407128809696355</v>
       </c>
       <c r="D472" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E472">
-        <v>2.761260321505639</v>
+        <v>2.841369914680043</v>
       </c>
       <c r="F472">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G472">
-        <v>0.002850531451462994</v>
+        <v>0.001992871190303645</v>
       </c>
       <c r="H472">
-        <v>0.002298739678494361</v>
+        <v>0.002338630085319957</v>
       </c>
       <c r="I472">
-        <v>0.6282082270313669</v>
+        <v>0.4342411049836872</v>
       </c>
       <c r="J472">
         <v>-0.2010959317440343</v>
       </c>
       <c r="K472">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L472">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M472">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N472">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O472">
         <v>1</v>
@@ -24996,10 +24996,10 @@
         <v>1</v>
       </c>
       <c r="B473" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C473">
-        <v>3.255391833314924</v>
+        <v>3.389468548537006</v>
       </c>
       <c r="D473" t="s">
         <v>130</v>
@@ -25011,22 +25011,22 @@
         <v>-1</v>
       </c>
       <c r="G473">
-        <v>0.002744608166685076</v>
+        <v>0.002850531451462994</v>
       </c>
       <c r="H473">
         <v>0.002298739678494361</v>
       </c>
       <c r="I473">
-        <v>0.4941315118092846</v>
+        <v>0.6282082270313669</v>
       </c>
       <c r="J473">
         <v>-0.2010959317440343</v>
       </c>
       <c r="K473">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L473">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M473">
         <v>1.15</v>
@@ -25043,40 +25043,40 @@
     </row>
     <row r="474" spans="1:16">
       <c r="A474" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B474" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C474">
-        <v>3.389721924935656</v>
+        <v>3.255391833314924</v>
       </c>
       <c r="D474" t="s">
         <v>130</v>
       </c>
       <c r="E474">
-        <v>2.761477771400003</v>
+        <v>2.761260321505639</v>
       </c>
       <c r="F474">
         <v>-1</v>
       </c>
       <c r="G474">
-        <v>0.002850278075064344</v>
+        <v>0.002744608166685076</v>
       </c>
       <c r="H474">
-        <v>0.002298522228599997</v>
+        <v>0.002298739678494361</v>
       </c>
       <c r="I474">
-        <v>0.6282441535356531</v>
+        <v>0.4941315118092846</v>
       </c>
       <c r="J474">
-        <v>-0.2012850186086983</v>
+        <v>-0.2010959317440343</v>
       </c>
       <c r="K474">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L474">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M474">
         <v>1.15</v>
@@ -25088,51 +25088,51 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="475" spans="1:16">
       <c r="A475" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B475" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C475">
-        <v>3.255631973633047</v>
+        <v>2.407323569166959</v>
       </c>
       <c r="D475" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E475">
-        <v>2.761477771400003</v>
+        <v>2.841606273260873</v>
       </c>
       <c r="F475">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G475">
-        <v>0.002744368026366953</v>
+        <v>0.001992676430833041</v>
       </c>
       <c r="H475">
-        <v>0.002298522228599997</v>
+        <v>0.002338393726739127</v>
       </c>
       <c r="I475">
-        <v>0.4941542022330441</v>
+        <v>0.4342827040939135</v>
       </c>
       <c r="J475">
         <v>-0.2012850186086983</v>
       </c>
       <c r="K475">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L475">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M475">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N475">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O475">
         <v>1</v>
@@ -25143,90 +25143,90 @@
     </row>
     <row r="476" spans="1:16">
       <c r="A476" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B476" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C476">
-        <v>2.41122985184961</v>
+        <v>3.389721924935656</v>
       </c>
       <c r="D476" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E476">
-        <v>2.846346907584478</v>
+        <v>2.761477771400003</v>
       </c>
       <c r="F476">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G476">
-        <v>0.00198877014815039</v>
+        <v>0.002850278075064344</v>
       </c>
       <c r="H476">
-        <v>0.002333653092415522</v>
+        <v>0.002298522228599997</v>
       </c>
       <c r="I476">
-        <v>0.4351170557348678</v>
+        <v>0.6282441535356531</v>
       </c>
       <c r="J476">
-        <v>-0.2050775260675825</v>
+        <v>-0.2012850186086983</v>
       </c>
       <c r="K476">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L476">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M476">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N476">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O476">
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="477" spans="1:16">
       <c r="A477" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B477" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C477">
-        <v>3.394803884930561</v>
+        <v>3.255631973633047</v>
       </c>
       <c r="D477" t="s">
         <v>130</v>
       </c>
       <c r="E477">
-        <v>2.76583915497772</v>
+        <v>2.761477771400003</v>
       </c>
       <c r="F477">
         <v>-1</v>
       </c>
       <c r="G477">
-        <v>0.00284519611506944</v>
+        <v>0.002744368026366953</v>
       </c>
       <c r="H477">
-        <v>0.00229416084502228</v>
+        <v>0.002298522228599997</v>
       </c>
       <c r="I477">
-        <v>0.6289647299528411</v>
+        <v>0.4941542022330441</v>
       </c>
       <c r="J477">
-        <v>-0.2050775260675825</v>
+        <v>-0.2012850186086983</v>
       </c>
       <c r="K477">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L477">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M477">
         <v>1.15</v>
@@ -25238,51 +25238,51 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="478" spans="1:16">
       <c r="A478" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B478" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C478">
-        <v>3.26044845810583</v>
+        <v>2.41122985184961</v>
       </c>
       <c r="D478" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E478">
-        <v>2.76583915497772</v>
+        <v>2.846346907584478</v>
       </c>
       <c r="F478">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G478">
-        <v>0.00273955154189417</v>
+        <v>0.00198877014815039</v>
       </c>
       <c r="H478">
-        <v>0.00229416084502228</v>
+        <v>0.002333653092415522</v>
       </c>
       <c r="I478">
-        <v>0.4946093031281102</v>
+        <v>0.4351170557348678</v>
       </c>
       <c r="J478">
         <v>-0.2050775260675825</v>
       </c>
       <c r="K478">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L478">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M478">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N478">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O478">
         <v>1</v>
@@ -25293,90 +25293,90 @@
     </row>
     <row r="479" spans="1:16">
       <c r="A479" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B479" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C479">
-        <v>2.414401903996001</v>
+        <v>3.394803884930561</v>
       </c>
       <c r="D479" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E479">
-        <v>2.850196485432039</v>
+        <v>2.76583915497772</v>
       </c>
       <c r="F479">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G479">
-        <v>0.001985598096004</v>
+        <v>0.00284519611506944</v>
       </c>
       <c r="H479">
-        <v>0.00232980351456796</v>
+        <v>0.00229416084502228</v>
       </c>
       <c r="I479">
-        <v>0.4357945814360389</v>
+        <v>0.6289647299528411</v>
       </c>
       <c r="J479">
-        <v>-0.2081571883456315</v>
+        <v>-0.2050775260675825</v>
       </c>
       <c r="K479">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L479">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M479">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N479">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O479">
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="480" spans="1:16">
       <c r="A480" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B480" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C480">
-        <v>3.398930632383146</v>
+        <v>3.26044845810583</v>
       </c>
       <c r="D480" t="s">
         <v>130</v>
       </c>
       <c r="E480">
-        <v>2.769380766597476</v>
+        <v>2.76583915497772</v>
       </c>
       <c r="F480">
         <v>-1</v>
       </c>
       <c r="G480">
-        <v>0.002841069367616854</v>
+        <v>0.00273955154189417</v>
       </c>
       <c r="H480">
-        <v>0.002290619233402524</v>
+        <v>0.00229416084502228</v>
       </c>
       <c r="I480">
-        <v>0.6295498657856702</v>
+        <v>0.4946093031281102</v>
       </c>
       <c r="J480">
-        <v>-0.2081571883456315</v>
+        <v>-0.2050775260675825</v>
       </c>
       <c r="K480">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L480">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M480">
         <v>1.15</v>
@@ -25388,51 +25388,51 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="481" spans="1:16">
       <c r="A481" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B481" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C481">
-        <v>3.264359629198952</v>
+        <v>2.414401903996001</v>
       </c>
       <c r="D481" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E481">
-        <v>2.769380766597476</v>
+        <v>2.850196485432039</v>
       </c>
       <c r="F481">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G481">
-        <v>0.002735640370801048</v>
+        <v>0.001985598096004</v>
       </c>
       <c r="H481">
-        <v>0.002290619233402524</v>
+        <v>0.00232980351456796</v>
       </c>
       <c r="I481">
-        <v>0.4949788626014757</v>
+        <v>0.4357945814360389</v>
       </c>
       <c r="J481">
         <v>-0.2081571883456315</v>
       </c>
       <c r="K481">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L481">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M481">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N481">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O481">
         <v>1</v>
@@ -25443,90 +25443,90 @@
     </row>
     <row r="482" spans="1:16">
       <c r="A482" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B482" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C482">
-        <v>2.400941737549309</v>
+        <v>3.398930632383146</v>
       </c>
       <c r="D482" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E482">
-        <v>2.833861331977317</v>
+        <v>2.769380766597476</v>
       </c>
       <c r="F482">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G482">
-        <v>0.001999058262450691</v>
+        <v>0.002841069367616854</v>
       </c>
       <c r="H482">
-        <v>0.002346138668022683</v>
+        <v>0.002290619233402524</v>
       </c>
       <c r="I482">
-        <v>0.4329195944280078</v>
+        <v>0.6295498657856702</v>
       </c>
       <c r="J482">
-        <v>-0.1950890655818535</v>
+        <v>-0.2081571883456315</v>
       </c>
       <c r="K482">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L482">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M482">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N482">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O482">
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="483" spans="1:16">
       <c r="A483" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B483" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C483">
-        <v>3.381419347879684</v>
+        <v>3.264359629198952</v>
       </c>
       <c r="D483" t="s">
         <v>130</v>
       </c>
       <c r="E483">
-        <v>2.754352425419131</v>
+        <v>2.769380766597476</v>
       </c>
       <c r="F483">
         <v>-1</v>
       </c>
       <c r="G483">
-        <v>0.002858580652120316</v>
+        <v>0.002735640370801048</v>
       </c>
       <c r="H483">
-        <v>0.002305647574580868</v>
+        <v>0.002290619233402524</v>
       </c>
       <c r="I483">
-        <v>0.6270669224605525</v>
+        <v>0.4949788626014757</v>
       </c>
       <c r="J483">
-        <v>-0.1950890655818535</v>
+        <v>-0.2081571883456315</v>
       </c>
       <c r="K483">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L483">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M483">
         <v>1.15</v>
@@ -25538,51 +25538,51 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="484" spans="1:16">
       <c r="A484" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B484" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C484">
-        <v>3.247763113288954</v>
+        <v>2.400941737549309</v>
       </c>
       <c r="D484" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E484">
-        <v>2.754352425419131</v>
+        <v>2.833861331977317</v>
       </c>
       <c r="F484">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G484">
-        <v>0.002752236886711046</v>
+        <v>0.001999058262450691</v>
       </c>
       <c r="H484">
-        <v>0.002305647574580868</v>
+        <v>0.002346138668022683</v>
       </c>
       <c r="I484">
-        <v>0.4934106878698228</v>
+        <v>0.4329195944280078</v>
       </c>
       <c r="J484">
         <v>-0.1950890655818535</v>
       </c>
       <c r="K484">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L484">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M484">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N484">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O484">
         <v>1</v>
@@ -25593,90 +25593,90 @@
     </row>
     <row r="485" spans="1:16">
       <c r="A485" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B485" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C485">
-        <v>2.416869377367424</v>
+        <v>3.381419347879684</v>
       </c>
       <c r="D485" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E485">
-        <v>2.853190991950757</v>
+        <v>2.754352425419131</v>
       </c>
       <c r="F485">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G485">
-        <v>0.001983130622632577</v>
+        <v>0.002858580652120316</v>
       </c>
       <c r="H485">
-        <v>0.002326809008049243</v>
+        <v>0.002305647574580868</v>
       </c>
       <c r="I485">
-        <v>0.4363216145833326</v>
+        <v>0.6270669224605525</v>
       </c>
       <c r="J485">
-        <v>-0.2105527935606056</v>
+        <v>-0.1950890655818535</v>
       </c>
       <c r="K485">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L485">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M485">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N485">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O485">
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="486" spans="1:16">
       <c r="A486" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B486" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C486">
-        <v>3.402140743371211</v>
+        <v>3.247763113288954</v>
       </c>
       <c r="D486" t="s">
         <v>130</v>
       </c>
       <c r="E486">
-        <v>2.772135712594696</v>
+        <v>2.754352425419131</v>
       </c>
       <c r="F486">
         <v>-1</v>
       </c>
       <c r="G486">
-        <v>0.002837859256628789</v>
+        <v>0.002752236886711046</v>
       </c>
       <c r="H486">
-        <v>0.002287864287405304</v>
+        <v>0.002305647574580868</v>
       </c>
       <c r="I486">
-        <v>0.6300050307765153</v>
+        <v>0.4934106878698228</v>
       </c>
       <c r="J486">
-        <v>-0.2105527935606056</v>
+        <v>-0.1950890655818535</v>
       </c>
       <c r="K486">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L486">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M486">
         <v>1.15</v>
@@ -25688,51 +25688,51 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="487" spans="1:16">
       <c r="A487" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B487" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C487">
-        <v>3.267402047821969</v>
+        <v>2.416869377367424</v>
       </c>
       <c r="D487" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E487">
-        <v>2.772135712594696</v>
+        <v>2.853190991950757</v>
       </c>
       <c r="F487">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G487">
-        <v>0.002732597952178031</v>
+        <v>0.001983130622632577</v>
       </c>
       <c r="H487">
-        <v>0.002287864287405304</v>
+        <v>0.002326809008049243</v>
       </c>
       <c r="I487">
-        <v>0.495266335227273</v>
+        <v>0.4363216145833326</v>
       </c>
       <c r="J487">
         <v>-0.2105527935606056</v>
       </c>
       <c r="K487">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L487">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M487">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N487">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O487">
         <v>1</v>
@@ -25743,90 +25743,90 @@
     </row>
     <row r="488" spans="1:16">
       <c r="A488" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B488" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C488">
-        <v>2.427926332334885</v>
+        <v>3.402140743371211</v>
       </c>
       <c r="D488" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E488">
-        <v>2.866609626620006</v>
+        <v>2.772135712594696</v>
       </c>
       <c r="F488">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G488">
-        <v>0.001972073667665115</v>
+        <v>0.002837859256628789</v>
       </c>
       <c r="H488">
-        <v>0.002313390373379994</v>
+        <v>0.002287864287405304</v>
       </c>
       <c r="I488">
-        <v>0.4386832942851204</v>
+        <v>0.6300050307765153</v>
       </c>
       <c r="J488">
-        <v>-0.2212877012960047</v>
+        <v>-0.2105527935606056</v>
       </c>
       <c r="K488">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L488">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M488">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N488">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O488">
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="489" spans="1:16">
       <c r="A489" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B489" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C489">
-        <v>3.416525519736647</v>
+        <v>3.267402047821969</v>
       </c>
       <c r="D489" t="s">
         <v>130</v>
       </c>
       <c r="E489">
-        <v>2.784480856490405</v>
+        <v>2.772135712594696</v>
       </c>
       <c r="F489">
         <v>-1</v>
       </c>
       <c r="G489">
-        <v>0.002823474480263354</v>
+        <v>0.002732597952178031</v>
       </c>
       <c r="H489">
-        <v>0.002275519143509595</v>
+        <v>0.002287864287405304</v>
       </c>
       <c r="I489">
-        <v>0.6320446632462415</v>
+        <v>0.495266335227273</v>
       </c>
       <c r="J489">
-        <v>-0.2212877012960047</v>
+        <v>-0.2105527935606056</v>
       </c>
       <c r="K489">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L489">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M489">
         <v>1.15</v>
@@ -25838,51 +25838,51 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="490" spans="1:16">
       <c r="A490" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B490" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C490">
-        <v>3.281035380645926</v>
+        <v>2.427926332334885</v>
       </c>
       <c r="D490" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E490">
-        <v>2.784480856490405</v>
+        <v>2.866609626620006</v>
       </c>
       <c r="F490">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G490">
-        <v>0.002718964619354074</v>
+        <v>0.001972073667665115</v>
       </c>
       <c r="H490">
-        <v>0.002275519143509595</v>
+        <v>0.002313390373379994</v>
       </c>
       <c r="I490">
-        <v>0.4965545241555209</v>
+        <v>0.4386832942851204</v>
       </c>
       <c r="J490">
         <v>-0.2212877012960047</v>
       </c>
       <c r="K490">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L490">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M490">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N490">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O490">
         <v>1</v>
@@ -25893,90 +25893,90 @@
     </row>
     <row r="491" spans="1:16">
       <c r="A491" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B491" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C491">
-        <v>2.43983969591803</v>
+        <v>3.416525519736647</v>
       </c>
       <c r="D491" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E491">
-        <v>2.88106759213353</v>
+        <v>2.784480856490405</v>
       </c>
       <c r="F491">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G491">
-        <v>0.001960160304081971</v>
+        <v>0.002823474480263354</v>
       </c>
       <c r="H491">
-        <v>0.002298932407866469</v>
+        <v>0.002275519143509595</v>
       </c>
       <c r="I491">
-        <v>0.441227896215501</v>
+        <v>0.6320446632462415</v>
       </c>
       <c r="J491">
-        <v>-0.2328540737068246</v>
+        <v>-0.2212877012960047</v>
       </c>
       <c r="K491">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L491">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M491">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N491">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O491">
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="492" spans="1:16">
       <c r="A492" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B492" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C492">
-        <v>3.432024458767145</v>
+        <v>3.281035380645926</v>
       </c>
       <c r="D492" t="s">
         <v>130</v>
       </c>
       <c r="E492">
-        <v>2.797782184762848</v>
+        <v>2.784480856490405</v>
       </c>
       <c r="F492">
         <v>-1</v>
       </c>
       <c r="G492">
-        <v>0.002807975541232855</v>
+        <v>0.002718964619354074</v>
       </c>
       <c r="H492">
-        <v>0.002262217815237151</v>
+        <v>0.002275519143509595</v>
       </c>
       <c r="I492">
-        <v>0.634242274004297</v>
+        <v>0.4965545241555209</v>
       </c>
       <c r="J492">
-        <v>-0.2328540737068246</v>
+        <v>-0.2212877012960047</v>
       </c>
       <c r="K492">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L492">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M492">
         <v>1.15</v>
@@ -25988,51 +25988,51 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="493" spans="1:16">
       <c r="A493" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B493" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C493">
-        <v>3.295724673607667</v>
+        <v>2.43983969591803</v>
       </c>
       <c r="D493" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E493">
-        <v>2.797782184762848</v>
+        <v>2.88106759213353</v>
       </c>
       <c r="F493">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G493">
-        <v>0.002704275326392333</v>
+        <v>0.001960160304081971</v>
       </c>
       <c r="H493">
-        <v>0.002262217815237151</v>
+        <v>0.002298932407866469</v>
       </c>
       <c r="I493">
-        <v>0.497942488844819</v>
+        <v>0.441227896215501</v>
       </c>
       <c r="J493">
         <v>-0.2328540737068246</v>
       </c>
       <c r="K493">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L493">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M493">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N493">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O493">
         <v>1</v>
@@ -26043,90 +26043,90 @@
     </row>
     <row r="494" spans="1:16">
       <c r="A494" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B494" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C494">
-        <v>2.478555931094635</v>
+        <v>3.432024458767145</v>
       </c>
       <c r="D494" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E494">
-        <v>2.928053314435237</v>
+        <v>2.797782184762848</v>
       </c>
       <c r="F494">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G494">
-        <v>0.001921444068905365</v>
+        <v>0.002807975541232855</v>
       </c>
       <c r="H494">
-        <v>0.002251946685564763</v>
+        <v>0.002262217815237151</v>
       </c>
       <c r="I494">
-        <v>0.4494973833406015</v>
+        <v>0.634242274004297</v>
       </c>
       <c r="J494">
-        <v>-0.2704426515481894</v>
+        <v>-0.2328540737068246</v>
       </c>
       <c r="K494">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L494">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M494">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N494">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O494">
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="495" spans="1:16">
       <c r="A495" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B495" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C495">
-        <v>3.482393153074574</v>
+        <v>3.295724673607667</v>
       </c>
       <c r="D495" t="s">
         <v>130</v>
       </c>
       <c r="E495">
-        <v>2.841009049280418</v>
+        <v>2.797782184762848</v>
       </c>
       <c r="F495">
         <v>-1</v>
       </c>
       <c r="G495">
-        <v>0.002757606846925426</v>
+        <v>0.002704275326392333</v>
       </c>
       <c r="H495">
-        <v>0.002218990950719582</v>
+        <v>0.002262217815237151</v>
       </c>
       <c r="I495">
-        <v>0.6413841037941563</v>
+        <v>0.497942488844819</v>
       </c>
       <c r="J495">
-        <v>-0.2704426515481894</v>
+        <v>-0.2328540737068246</v>
       </c>
       <c r="K495">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L495">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M495">
         <v>1.15</v>
@@ -26138,51 +26138,51 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="496" spans="1:16">
       <c r="A496" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B496" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C496">
-        <v>3.343462167466201</v>
+        <v>2.478555931094635</v>
       </c>
       <c r="D496" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E496">
-        <v>2.841009049280418</v>
+        <v>2.928053314435237</v>
       </c>
       <c r="F496">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G496">
-        <v>0.002656537832533799</v>
+        <v>0.001921444068905365</v>
       </c>
       <c r="H496">
-        <v>0.002218990950719582</v>
+        <v>0.002251946685564763</v>
       </c>
       <c r="I496">
-        <v>0.502453118185783</v>
+        <v>0.4494973833406015</v>
       </c>
       <c r="J496">
         <v>-0.2704426515481894</v>
       </c>
       <c r="K496">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L496">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M496">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N496">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O496">
         <v>1</v>
@@ -26193,90 +26193,90 @@
     </row>
     <row r="497" spans="1:16">
       <c r="A497" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B497" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C497">
-        <v>2.492450104171095</v>
+        <v>3.482393153074574</v>
       </c>
       <c r="D497" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E497">
-        <v>2.944915174964921</v>
+        <v>2.841009049280418</v>
       </c>
       <c r="F497">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G497">
-        <v>0.001907549895828906</v>
+        <v>0.002757606846925426</v>
       </c>
       <c r="H497">
-        <v>0.002235084825035079</v>
+        <v>0.002218990950719582</v>
       </c>
       <c r="I497">
-        <v>0.4524650707938256</v>
+        <v>0.6413841037941563</v>
       </c>
       <c r="J497">
-        <v>-0.2839321399719367</v>
+        <v>-0.2704426515481894</v>
       </c>
       <c r="K497">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L497">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M497">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N497">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O497">
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="498" spans="1:16">
       <c r="A498" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B498" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C498">
-        <v>3.500469067562396</v>
+        <v>3.343462167466201</v>
       </c>
       <c r="D498" t="s">
         <v>130</v>
       </c>
       <c r="E498">
-        <v>2.856521960967727</v>
+        <v>2.841009049280418</v>
       </c>
       <c r="F498">
         <v>-1</v>
       </c>
       <c r="G498">
-        <v>0.002739530932437605</v>
+        <v>0.002656537832533799</v>
       </c>
       <c r="H498">
-        <v>0.002203478039032273</v>
+        <v>0.002218990950719582</v>
       </c>
       <c r="I498">
-        <v>0.6439471065946685</v>
+        <v>0.502453118185783</v>
       </c>
       <c r="J498">
-        <v>-0.2839321399719367</v>
+        <v>-0.2704426515481894</v>
       </c>
       <c r="K498">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L498">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M498">
         <v>1.15</v>
@@ -26288,51 +26288,51 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="499" spans="1:16">
       <c r="A499" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B499" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C499">
-        <v>3.36059381776436</v>
+        <v>2.492450104171095</v>
       </c>
       <c r="D499" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E499">
-        <v>2.856521960967727</v>
+        <v>2.944915174964921</v>
       </c>
       <c r="F499">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G499">
-        <v>0.002639406182235641</v>
+        <v>0.001907549895828906</v>
       </c>
       <c r="H499">
-        <v>0.002203478039032273</v>
+        <v>0.002235084825035079</v>
       </c>
       <c r="I499">
-        <v>0.5040718567966325</v>
+        <v>0.4524650707938256</v>
       </c>
       <c r="J499">
         <v>-0.2839321399719367</v>
       </c>
       <c r="K499">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L499">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M499">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N499">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O499">
         <v>1</v>
@@ -26343,90 +26343,90 @@
     </row>
     <row r="500" spans="1:16">
       <c r="A500" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B500" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C500">
-        <v>2.485588290136117</v>
+        <v>3.500469067562396</v>
       </c>
       <c r="D500" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E500">
-        <v>2.936587730747715</v>
+        <v>2.912200603767166</v>
       </c>
       <c r="F500">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G500">
-        <v>0.001914411709863883</v>
+        <v>0.002739530932437605</v>
       </c>
       <c r="H500">
-        <v>0.002243412269252285</v>
+        <v>0.002247799396232834</v>
       </c>
       <c r="I500">
-        <v>0.4509994406115978</v>
+        <v>0.5882684637952296</v>
       </c>
       <c r="J500">
-        <v>-0.2772701845981717</v>
+        <v>-0.2839321399719367</v>
       </c>
       <c r="K500">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L500">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M500">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N500">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O500">
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="501" spans="1:16">
       <c r="A501" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B501" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C501">
-        <v>3.49154204736155</v>
+        <v>3.36059381776436</v>
       </c>
       <c r="D501" t="s">
         <v>132</v>
       </c>
       <c r="E501">
-        <v>2.904406115979861</v>
+        <v>2.912200603767166</v>
       </c>
       <c r="F501">
         <v>-1</v>
       </c>
       <c r="G501">
-        <v>0.00274845795263845</v>
+        <v>0.002639406182235641</v>
       </c>
       <c r="H501">
-        <v>0.002255593884020139</v>
+        <v>0.002247799396232834</v>
       </c>
       <c r="I501">
-        <v>0.5871359313816891</v>
+        <v>0.4483932139971936</v>
       </c>
       <c r="J501">
-        <v>-0.2772701845981717</v>
+        <v>-0.2839321399719367</v>
       </c>
       <c r="K501">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L501">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M501">
         <v>1.17</v>
@@ -26438,51 +26438,51 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="502" spans="1:16">
       <c r="A502" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B502" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C502">
-        <v>3.352133134439678</v>
+        <v>2.485588290136117</v>
       </c>
       <c r="D502" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E502">
-        <v>2.904406115979861</v>
+        <v>2.936587730747715</v>
       </c>
       <c r="F502">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G502">
-        <v>0.002647866865560322</v>
+        <v>0.001914411709863883</v>
       </c>
       <c r="H502">
-        <v>0.002255593884020139</v>
+        <v>0.002243412269252285</v>
       </c>
       <c r="I502">
-        <v>0.4477270184598172</v>
+        <v>0.4509994406115978</v>
       </c>
       <c r="J502">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K502">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L502">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M502">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N502">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O502">
         <v>1</v>
@@ -26493,90 +26493,90 @@
     </row>
     <row r="503" spans="1:16">
       <c r="A503" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B503" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C503">
-        <v>2.483803138304734</v>
+        <v>3.49154204736155</v>
       </c>
       <c r="D503" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E503">
-        <v>2.934421284350405</v>
+        <v>2.904406115979861</v>
       </c>
       <c r="F503">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G503">
-        <v>0.001916196861695266</v>
+        <v>0.00274845795263845</v>
       </c>
       <c r="H503">
-        <v>0.002245578715649595</v>
+        <v>0.002255593884020139</v>
       </c>
       <c r="I503">
-        <v>0.4506181460456711</v>
+        <v>0.5871359313816891</v>
       </c>
       <c r="J503">
-        <v>-0.2755370274803244</v>
+        <v>-0.2772701845981717</v>
       </c>
       <c r="K503">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L503">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M503">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N503">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O503">
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="504" spans="1:16">
       <c r="A504" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B504" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C504">
-        <v>3.489219616823635</v>
+        <v>3.352133134439678</v>
       </c>
       <c r="D504" t="s">
         <v>132</v>
       </c>
       <c r="E504">
-        <v>2.902378322151979</v>
+        <v>2.904406115979861</v>
       </c>
       <c r="F504">
         <v>-1</v>
       </c>
       <c r="G504">
-        <v>0.002750780383176366</v>
+        <v>0.002647866865560322</v>
       </c>
       <c r="H504">
-        <v>0.002257621677848021</v>
+        <v>0.002255593884020139</v>
       </c>
       <c r="I504">
-        <v>0.5868412946716552</v>
+        <v>0.4477270184598172</v>
       </c>
       <c r="J504">
-        <v>-0.2755370274803244</v>
+        <v>-0.2772701845981717</v>
       </c>
       <c r="K504">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L504">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M504">
         <v>1.17</v>
@@ -26588,51 +26588,51 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="505" spans="1:16">
       <c r="A505" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B505" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C505">
-        <v>3.349932024900012</v>
+        <v>2.483803138304734</v>
       </c>
       <c r="D505" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E505">
-        <v>2.902378322151979</v>
+        <v>2.934421284350405</v>
       </c>
       <c r="F505">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G505">
-        <v>0.002650067975099988</v>
+        <v>0.001916196861695266</v>
       </c>
       <c r="H505">
-        <v>0.002257621677848021</v>
+        <v>0.002245578715649595</v>
       </c>
       <c r="I505">
-        <v>0.4475537027480323</v>
+        <v>0.4506181460456711</v>
       </c>
       <c r="J505">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K505">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L505">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M505">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N505">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O505">
         <v>1</v>
@@ -26643,90 +26643,90 @@
     </row>
     <row r="506" spans="1:16">
       <c r="A506" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B506" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C506">
-        <v>2.455324757264537</v>
+        <v>3.489219616823635</v>
       </c>
       <c r="D506" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E506">
-        <v>2.899860142311331</v>
+        <v>2.902378322151979</v>
       </c>
       <c r="F506">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G506">
-        <v>0.001944675242735464</v>
+        <v>0.002750780383176366</v>
       </c>
       <c r="H506">
-        <v>0.002280139857688669</v>
+        <v>0.002257621677848021</v>
       </c>
       <c r="I506">
-        <v>0.4445353850467941</v>
+        <v>0.5868412946716552</v>
       </c>
       <c r="J506">
-        <v>-0.2478881138490649</v>
+        <v>-0.2755370274803244</v>
       </c>
       <c r="K506">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L506">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M506">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N506">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O506">
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="507" spans="1:16">
       <c r="A507" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B507" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C507">
-        <v>3.452170072557747</v>
+        <v>3.349932024900012</v>
       </c>
       <c r="D507" t="s">
         <v>132</v>
       </c>
       <c r="E507">
-        <v>2.870029093203406</v>
+        <v>2.902378322151979</v>
       </c>
       <c r="F507">
         <v>-1</v>
       </c>
       <c r="G507">
-        <v>0.002787829927442253</v>
+        <v>0.002650067975099988</v>
       </c>
       <c r="H507">
-        <v>0.002289970906796594</v>
+        <v>0.002257621677848021</v>
       </c>
       <c r="I507">
-        <v>0.5821409793543411</v>
+        <v>0.4475537027480323</v>
       </c>
       <c r="J507">
-        <v>-0.2478881138490649</v>
+        <v>-0.2755370274803244</v>
       </c>
       <c r="K507">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L507">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M507">
         <v>1.17</v>
@@ -26738,51 +26738,51 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="508" spans="1:16">
       <c r="A508" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B508" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C508">
-        <v>3.314817904588312</v>
+        <v>2.455324757264537</v>
       </c>
       <c r="D508" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E508">
-        <v>2.870029093203406</v>
+        <v>2.899860142311331</v>
       </c>
       <c r="F508">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G508">
-        <v>0.002685182095411688</v>
+        <v>0.001944675242735464</v>
       </c>
       <c r="H508">
-        <v>0.002289970906796594</v>
+        <v>0.002280139857688669</v>
       </c>
       <c r="I508">
-        <v>0.4447888113849063</v>
+        <v>0.4445353850467941</v>
       </c>
       <c r="J508">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K508">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L508">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M508">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N508">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O508">
         <v>1</v>
@@ -26793,90 +26793,90 @@
     </row>
     <row r="509" spans="1:16">
       <c r="A509" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B509" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C509">
-        <v>2.38683909149</v>
+        <v>3.452170072557747</v>
       </c>
       <c r="D509" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E509">
-        <v>2.816746470254853</v>
+        <v>2.870029093203406</v>
       </c>
       <c r="F509">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G509">
-        <v>0.002013160908510001</v>
+        <v>0.002787829927442253</v>
       </c>
       <c r="H509">
-        <v>0.002363253529745146</v>
+        <v>0.002289970906796594</v>
       </c>
       <c r="I509">
-        <v>0.4299073787648537</v>
+        <v>0.5821409793543411</v>
       </c>
       <c r="J509">
-        <v>-0.181397176203883</v>
+        <v>-0.2478881138490649</v>
       </c>
       <c r="K509">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L509">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M509">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N509">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O509">
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="510" spans="1:16">
       <c r="A510" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B510" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C510">
-        <v>3.363072216113203</v>
+        <v>3.314817904588312</v>
       </c>
       <c r="D510" t="s">
         <v>132</v>
       </c>
       <c r="E510">
-        <v>2.792234696158543</v>
+        <v>2.870029093203406</v>
       </c>
       <c r="F510">
         <v>-1</v>
       </c>
       <c r="G510">
-        <v>0.002876927783886797</v>
+        <v>0.002685182095411688</v>
       </c>
       <c r="H510">
-        <v>0.002367765303841457</v>
+        <v>0.002289970906796594</v>
       </c>
       <c r="I510">
-        <v>0.5708375199546598</v>
+        <v>0.4447888113849063</v>
       </c>
       <c r="J510">
-        <v>-0.181397176203883</v>
+        <v>-0.2478881138490649</v>
       </c>
       <c r="K510">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L510">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M510">
         <v>1.17</v>
@@ -26888,51 +26888,51 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="511" spans="1:16">
       <c r="A511" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B511" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C511">
-        <v>3.230374413778931</v>
+        <v>2.38683909149</v>
       </c>
       <c r="D511" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E511">
-        <v>2.792234696158543</v>
+        <v>2.816746470254853</v>
       </c>
       <c r="F511">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G511">
-        <v>0.002769625586221069</v>
+        <v>0.002013160908510001</v>
       </c>
       <c r="H511">
-        <v>0.002367765303841457</v>
+        <v>0.002363253529745146</v>
       </c>
       <c r="I511">
-        <v>0.4381397176203881</v>
+        <v>0.4299073787648537</v>
       </c>
       <c r="J511">
         <v>-0.181397176203883</v>
       </c>
       <c r="K511">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L511">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M511">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N511">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O511">
         <v>1</v>
@@ -26943,90 +26943,90 @@
     </row>
     <row r="512" spans="1:16">
       <c r="A512" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B512" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C512">
-        <v>2.332831092936091</v>
+        <v>3.363072216113203</v>
       </c>
       <c r="D512" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E512">
-        <v>2.751202782689431</v>
+        <v>2.792234696158543</v>
       </c>
       <c r="F512">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G512">
-        <v>0.002067168907063909</v>
+        <v>0.002876927783886797</v>
       </c>
       <c r="H512">
-        <v>0.002428797217310569</v>
+        <v>0.002367765303841457</v>
       </c>
       <c r="I512">
-        <v>0.4183716897533394</v>
+        <v>0.5708375199546598</v>
       </c>
       <c r="J512">
-        <v>-0.1289622261515449</v>
+        <v>-0.181397176203883</v>
       </c>
       <c r="K512">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L512">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M512">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N512">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O512">
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="513" spans="1:16">
       <c r="A513" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B513" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C513">
-        <v>3.29280938304307</v>
+        <v>3.230374413778931</v>
       </c>
       <c r="D513" t="s">
         <v>132</v>
       </c>
       <c r="E513">
-        <v>2.730885804597308</v>
+        <v>2.792234696158543</v>
       </c>
       <c r="F513">
         <v>-1</v>
       </c>
       <c r="G513">
-        <v>0.00294719061695693</v>
+        <v>0.002769625586221069</v>
       </c>
       <c r="H513">
-        <v>0.002429114195402692</v>
+        <v>0.002367765303841457</v>
       </c>
       <c r="I513">
-        <v>0.5619235784457626</v>
+        <v>0.4381397176203881</v>
       </c>
       <c r="J513">
-        <v>-0.1289622261515449</v>
+        <v>-0.181397176203883</v>
       </c>
       <c r="K513">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L513">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M513">
         <v>1.17</v>
@@ -27038,51 +27038,51 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="514" spans="1:16">
       <c r="A514" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B514" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C514">
-        <v>3.163782027212462</v>
+        <v>2.332831092936091</v>
       </c>
       <c r="D514" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E514">
-        <v>2.730885804597308</v>
+        <v>2.751202782689431</v>
       </c>
       <c r="F514">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G514">
-        <v>0.002836217972787538</v>
+        <v>0.002067168907063909</v>
       </c>
       <c r="H514">
-        <v>0.002429114195402692</v>
+        <v>0.002428797217310569</v>
       </c>
       <c r="I514">
-        <v>0.4328962226151543</v>
+        <v>0.4183716897533394</v>
       </c>
       <c r="J514">
         <v>-0.1289622261515449</v>
       </c>
       <c r="K514">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L514">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M514">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N514">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O514">
         <v>1</v>
@@ -27093,90 +27093,90 @@
     </row>
     <row r="515" spans="1:16">
       <c r="A515" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B515" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C515">
-        <v>2.292718610119939</v>
+        <v>3.29280938304307</v>
       </c>
       <c r="D515" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E515">
-        <v>2.702522585097013</v>
+        <v>2.730885804597308</v>
       </c>
       <c r="F515">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G515">
-        <v>0.002107281389880062</v>
+        <v>0.00294719061695693</v>
       </c>
       <c r="H515">
-        <v>0.002477477414902987</v>
+        <v>0.002429114195402692</v>
       </c>
       <c r="I515">
-        <v>0.4098039749770739</v>
+        <v>0.5619235784457626</v>
       </c>
       <c r="J515">
-        <v>-0.09001806807761016</v>
+        <v>-0.1289622261515449</v>
       </c>
       <c r="K515">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L515">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M515">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N515">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O515">
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="516" spans="1:16">
       <c r="A516" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B516" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C516">
-        <v>3.240624211223998</v>
+        <v>3.163782027212462</v>
       </c>
       <c r="D516" t="s">
         <v>132</v>
       </c>
       <c r="E516">
-        <v>2.685321139650804</v>
+        <v>2.730885804597308</v>
       </c>
       <c r="F516">
         <v>-1</v>
       </c>
       <c r="G516">
-        <v>0.002999375788776002</v>
+        <v>0.002836217972787538</v>
       </c>
       <c r="H516">
-        <v>0.002474678860349197</v>
+        <v>0.002429114195402692</v>
       </c>
       <c r="I516">
-        <v>0.5553030715731939</v>
+        <v>0.4328962226151543</v>
       </c>
       <c r="J516">
-        <v>-0.09001806807761016</v>
+        <v>-0.1289622261515449</v>
       </c>
       <c r="K516">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L516">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M516">
         <v>1.17</v>
@@ -27188,51 +27188,51 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="517" spans="1:16">
       <c r="A517" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B517" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C517">
-        <v>3.114322946458565</v>
+        <v>2.292718610119939</v>
       </c>
       <c r="D517" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E517">
-        <v>2.685321139650804</v>
+        <v>2.702522585097013</v>
       </c>
       <c r="F517">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G517">
-        <v>0.002885677053541435</v>
+        <v>0.002107281389880062</v>
       </c>
       <c r="H517">
-        <v>0.002474678860349197</v>
+        <v>0.002477477414902987</v>
       </c>
       <c r="I517">
-        <v>0.429001806807761</v>
+        <v>0.4098039749770739</v>
       </c>
       <c r="J517">
         <v>-0.09001806807761016</v>
       </c>
       <c r="K517">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L517">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M517">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N517">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O517">
         <v>1</v>
@@ -27243,146 +27243,146 @@
     </row>
     <row r="518" spans="1:16">
       <c r="A518" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B518" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C518">
-        <v>2.190845625202192</v>
+        <v>3.240624211223998</v>
       </c>
       <c r="D518" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E518">
-        <v>2.57889032184732</v>
+        <v>2.685321139650804</v>
       </c>
       <c r="F518">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G518">
-        <v>0.002209154374797808</v>
+        <v>0.002999375788776002</v>
       </c>
       <c r="H518">
-        <v>0.00260110967815268</v>
+        <v>0.002474678860349197</v>
       </c>
       <c r="I518">
-        <v>0.3880446966451281</v>
+        <v>0.5553030715731939</v>
       </c>
       <c r="J518">
-        <v>0.008887742522143843</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K518">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L518">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M518">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N518">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O518">
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="519" spans="1:16">
       <c r="A519" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B519" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C519">
-        <v>3.108090425020327</v>
+        <v>3.114322946458565</v>
       </c>
       <c r="D519" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E519">
-        <v>2.519779096099534</v>
+        <v>2.685321139650804</v>
       </c>
       <c r="F519">
         <v>-1</v>
       </c>
       <c r="G519">
-        <v>0.003131909574979673</v>
+        <v>0.002885677053541435</v>
       </c>
       <c r="H519">
-        <v>0.002540220903900465</v>
+        <v>0.002474678860349197</v>
       </c>
       <c r="I519">
-        <v>0.5883113289207929</v>
+        <v>0.429001806807761</v>
       </c>
       <c r="J519">
-        <v>0.008887742522143843</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K519">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L519">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M519">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N519">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O519">
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="520" spans="1:16">
       <c r="A520" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B520" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C520">
-        <v>2.988712566996877</v>
+        <v>2.190845625202192</v>
       </c>
       <c r="D520" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E520">
-        <v>2.519779096099534</v>
+        <v>2.57889032184732</v>
       </c>
       <c r="F520">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G520">
-        <v>0.003011287433003123</v>
+        <v>0.002209154374797808</v>
       </c>
       <c r="H520">
-        <v>0.002540220903900465</v>
+        <v>0.00260110967815268</v>
       </c>
       <c r="I520">
-        <v>0.4689334708973432</v>
+        <v>0.3880446966451281</v>
       </c>
       <c r="J520">
         <v>0.008887742522143843</v>
       </c>
       <c r="K520">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L520">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M520">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N520">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O520">
         <v>1</v>
@@ -27393,146 +27393,146 @@
     </row>
     <row r="521" spans="1:16">
       <c r="A521" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B521" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C521">
-        <v>2.151298027264343</v>
+        <v>3.108090425020327</v>
       </c>
       <c r="D521" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E521">
-        <v>2.530895664155756</v>
+        <v>2.569601341249092</v>
       </c>
       <c r="F521">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G521">
-        <v>0.002248701972735657</v>
+        <v>0.003131909574979673</v>
       </c>
       <c r="H521">
-        <v>0.002649104335844244</v>
+        <v>0.002590398658750909</v>
       </c>
       <c r="I521">
-        <v>0.3795976368914125</v>
+        <v>0.5384890837712355</v>
       </c>
       <c r="J521">
-        <v>0.04728346867539508</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K521">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L521">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M521">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N521">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O521">
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="522" spans="1:16">
       <c r="A522" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B522" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C522">
-        <v>3.056640151974971</v>
+        <v>2.988712566996877</v>
       </c>
       <c r="D522" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E522">
-        <v>2.475624011023295</v>
+        <v>2.569601341249092</v>
       </c>
       <c r="F522">
         <v>-1</v>
       </c>
       <c r="G522">
-        <v>0.00318335984802503</v>
+        <v>0.003011287433003123</v>
       </c>
       <c r="H522">
-        <v>0.002584375988976704</v>
+        <v>0.002590398658750909</v>
       </c>
       <c r="I522">
-        <v>0.5810161409516752</v>
+        <v>0.4191112257477858</v>
       </c>
       <c r="J522">
-        <v>0.04728346867539508</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K522">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L522">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M522">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N522">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O522">
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="523" spans="1:16">
       <c r="A523" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B523" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C523">
-        <v>2.939949994782248</v>
+        <v>2.151298027264343</v>
       </c>
       <c r="D523" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E523">
-        <v>2.475624011023295</v>
+        <v>2.530895664155756</v>
       </c>
       <c r="F523">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G523">
-        <v>0.003060050005217752</v>
+        <v>0.002248701972735657</v>
       </c>
       <c r="H523">
-        <v>0.002584375988976704</v>
+        <v>0.002649104335844244</v>
       </c>
       <c r="I523">
-        <v>0.4643259837589526</v>
+        <v>0.3795976368914125</v>
       </c>
       <c r="J523">
         <v>0.04728346867539508</v>
       </c>
       <c r="K523">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L523">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M523">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N523">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27543,90 +27543,90 @@
     </row>
     <row r="524" spans="1:16">
       <c r="A524" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B524" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C524">
-        <v>2.129744886456478</v>
+        <v>3.056640151974971</v>
       </c>
       <c r="D524" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E524">
-        <v>2.504738939874366</v>
+        <v>2.475624011023295</v>
       </c>
       <c r="F524">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G524">
-        <v>0.002270255113543523</v>
+        <v>0.00318335984802503</v>
       </c>
       <c r="H524">
-        <v>0.002675261060125634</v>
+        <v>0.002584375988976704</v>
       </c>
       <c r="I524">
-        <v>0.3749940534178879</v>
+        <v>0.5810161409516752</v>
       </c>
       <c r="J524">
-        <v>0.06820884810050738</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K524">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L524">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M524">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N524">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O524">
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="525" spans="1:16">
       <c r="A525" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B525" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C525">
-        <v>3.02860014354532</v>
+        <v>2.939949994782248</v>
       </c>
       <c r="D525" t="s">
         <v>130</v>
       </c>
       <c r="E525">
-        <v>2.451559824684416</v>
+        <v>2.475624011023295</v>
       </c>
       <c r="F525">
         <v>-1</v>
       </c>
       <c r="G525">
-        <v>0.00321139985645468</v>
+        <v>0.003060050005217752</v>
       </c>
       <c r="H525">
-        <v>0.002608440175315583</v>
+        <v>0.002584375988976704</v>
       </c>
       <c r="I525">
-        <v>0.5770403188609037</v>
+        <v>0.4643259837589526</v>
       </c>
       <c r="J525">
-        <v>0.06820884810050738</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K525">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L525">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M525">
         <v>1.15</v>
@@ -27638,51 +27638,51 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="526" spans="1:16">
       <c r="A526" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B526" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C526">
-        <v>2.913374762912356</v>
+        <v>2.129744886456478</v>
       </c>
       <c r="D526" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E526">
-        <v>2.451559824684416</v>
+        <v>2.504738939874366</v>
       </c>
       <c r="F526">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G526">
-        <v>0.003086625237087645</v>
+        <v>0.002270255113543523</v>
       </c>
       <c r="H526">
-        <v>0.002608440175315583</v>
+        <v>0.002675261060125634</v>
       </c>
       <c r="I526">
-        <v>0.4618149382279393</v>
+        <v>0.3749940534178879</v>
       </c>
       <c r="J526">
         <v>0.06820884810050738</v>
       </c>
       <c r="K526">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L526">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M526">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N526">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27693,90 +27693,90 @@
     </row>
     <row r="527" spans="1:16">
       <c r="A527" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B527" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C527">
-        <v>2.123592991344732</v>
+        <v>3.02860014354532</v>
       </c>
       <c r="D527" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E527">
-        <v>2.497273047748461</v>
+        <v>2.451559824684416</v>
       </c>
       <c r="F527">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G527">
-        <v>0.002276407008655268</v>
+        <v>0.00321139985645468</v>
       </c>
       <c r="H527">
-        <v>0.002682726952251539</v>
+        <v>0.002608440175315583</v>
       </c>
       <c r="I527">
-        <v>0.3736800564037286</v>
+        <v>0.5770403188609037</v>
       </c>
       <c r="J527">
-        <v>0.07418156180123091</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K527">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L527">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M527">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N527">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O527">
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="528" spans="1:16">
       <c r="A528" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B528" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C528">
-        <v>3.020596707186351</v>
+        <v>2.913374762912356</v>
       </c>
       <c r="D528" t="s">
         <v>130</v>
       </c>
       <c r="E528">
-        <v>2.444691203928584</v>
+        <v>2.451559824684416</v>
       </c>
       <c r="F528">
         <v>-1</v>
       </c>
       <c r="G528">
-        <v>0.00321940329281365</v>
+        <v>0.003086625237087645</v>
       </c>
       <c r="H528">
-        <v>0.002615308796071415</v>
+        <v>0.002608440175315583</v>
       </c>
       <c r="I528">
-        <v>0.5759055032577662</v>
+        <v>0.4618149382279393</v>
       </c>
       <c r="J528">
-        <v>0.07418156180123091</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K528">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L528">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M528">
         <v>1.15</v>
@@ -27788,51 +27788,51 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="529" spans="1:16">
       <c r="A529" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B529" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C529">
-        <v>2.905789416512437</v>
+        <v>2.123592991344732</v>
       </c>
       <c r="D529" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E529">
-        <v>2.444691203928584</v>
+        <v>2.497273047748461</v>
       </c>
       <c r="F529">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G529">
-        <v>0.003094210583487563</v>
+        <v>0.002276407008655268</v>
       </c>
       <c r="H529">
-        <v>0.002615308796071415</v>
+        <v>0.002682726952251539</v>
       </c>
       <c r="I529">
-        <v>0.4610982125838525</v>
+        <v>0.3736800564037286</v>
       </c>
       <c r="J529">
         <v>0.07418156180123091</v>
       </c>
       <c r="K529">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L529">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M529">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N529">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -27843,90 +27843,90 @@
     </row>
     <row r="530" spans="1:16">
       <c r="A530" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B530" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C530">
-        <v>2.162997802089755</v>
+        <v>3.020596707186351</v>
       </c>
       <c r="D530" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E530">
-        <v>2.545094420011838</v>
+        <v>2.49320757269256</v>
       </c>
       <c r="F530">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G530">
-        <v>0.002237002197910246</v>
+        <v>0.00321940329281365</v>
       </c>
       <c r="H530">
-        <v>0.002634905579988162</v>
+        <v>0.00266679242730744</v>
       </c>
       <c r="I530">
-        <v>0.382096617922083</v>
+        <v>0.5273891344937907</v>
       </c>
       <c r="J530">
-        <v>0.03592446399052947</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K530">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L530">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M530">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N530">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O530">
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="531" spans="1:16">
       <c r="A531" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B531" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C531">
-        <v>3.071861218252691</v>
+        <v>2.905789416512437</v>
       </c>
       <c r="D531" t="s">
         <v>132</v>
       </c>
       <c r="E531">
-        <v>2.537968377131081</v>
+        <v>2.49320757269256</v>
       </c>
       <c r="F531">
         <v>-1</v>
       </c>
       <c r="G531">
-        <v>0.00316813878174731</v>
+        <v>0.003094210583487563</v>
       </c>
       <c r="H531">
-        <v>0.00262203162286892</v>
+        <v>0.00266679242730744</v>
       </c>
       <c r="I531">
-        <v>0.53389284112161</v>
+        <v>0.4125818438198769</v>
       </c>
       <c r="J531">
-        <v>0.03592446399052947</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K531">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L531">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M531">
         <v>1.17</v>
@@ -27938,51 +27938,51 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="532" spans="1:16">
       <c r="A532" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B532" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C532">
-        <v>2.954375930732028</v>
+        <v>2.162997802089755</v>
       </c>
       <c r="D532" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E532">
-        <v>2.537968377131081</v>
+        <v>2.545094420011838</v>
       </c>
       <c r="F532">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G532">
-        <v>0.003045624069267972</v>
+        <v>0.002237002197910246</v>
       </c>
       <c r="H532">
-        <v>0.00262203162286892</v>
+        <v>0.002634905579988162</v>
       </c>
       <c r="I532">
-        <v>0.4164075536009468</v>
+        <v>0.382096617922083</v>
       </c>
       <c r="J532">
         <v>0.03592446399052947</v>
       </c>
       <c r="K532">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L532">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M532">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N532">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O532">
         <v>1</v>
@@ -27993,90 +27993,90 @@
     </row>
     <row r="533" spans="1:16">
       <c r="A533" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B533" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C533">
-        <v>2.152181822645585</v>
+        <v>3.071861218252691</v>
       </c>
       <c r="D533" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E533">
-        <v>2.531968231366001</v>
+        <v>2.537968377131081</v>
       </c>
       <c r="F533">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G533">
-        <v>0.002247818177354416</v>
+        <v>0.00316813878174731</v>
       </c>
       <c r="H533">
-        <v>0.002648031768633999</v>
+        <v>0.00262203162286892</v>
       </c>
       <c r="I533">
-        <v>0.3797864087204159</v>
+        <v>0.53389284112161</v>
       </c>
       <c r="J533">
-        <v>0.04642541490719935</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K533">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L533">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M533">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N533">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O533">
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="534" spans="1:16">
       <c r="A534" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B534" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C534">
-        <v>3.057789944024353</v>
+        <v>2.954375930732028</v>
       </c>
       <c r="D534" t="s">
         <v>132</v>
       </c>
       <c r="E534">
-        <v>2.525682264558577</v>
+        <v>2.537968377131081</v>
       </c>
       <c r="F534">
         <v>-1</v>
       </c>
       <c r="G534">
-        <v>0.003182210055975647</v>
+        <v>0.003045624069267972</v>
       </c>
       <c r="H534">
-        <v>0.002634317735441423</v>
+        <v>0.00262203162286892</v>
       </c>
       <c r="I534">
-        <v>0.532107679465776</v>
+        <v>0.4164075536009468</v>
       </c>
       <c r="J534">
-        <v>0.04642541490719935</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K534">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L534">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M534">
         <v>1.17</v>
@@ -28088,51 +28088,51 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="535" spans="1:16">
       <c r="A535" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B535" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C535">
-        <v>2.941039723067857</v>
+        <v>2.152181822645585</v>
       </c>
       <c r="D535" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E535">
-        <v>2.525682264558577</v>
+        <v>2.531968231366001</v>
       </c>
       <c r="F535">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G535">
-        <v>0.003058960276932143</v>
+        <v>0.002247818177354416</v>
       </c>
       <c r="H535">
-        <v>0.002634317735441423</v>
+        <v>0.002648031768633999</v>
       </c>
       <c r="I535">
-        <v>0.4153574585092796</v>
+        <v>0.3797864087204159</v>
       </c>
       <c r="J535">
         <v>0.04642541490719935</v>
       </c>
       <c r="K535">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L535">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M535">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N535">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O535">
         <v>1</v>
@@ -28143,90 +28143,90 @@
     </row>
     <row r="536" spans="1:16">
       <c r="A536" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B536" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C536">
-        <v>2.132867933343715</v>
+        <v>3.057789944024353</v>
       </c>
       <c r="D536" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E536">
-        <v>2.560484348232362</v>
+        <v>2.525682264558577</v>
       </c>
       <c r="F536">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G536">
-        <v>0.002267132066656285</v>
+        <v>0.003182210055975647</v>
       </c>
       <c r="H536">
-        <v>0.002719515651767639</v>
+        <v>0.002634317735441423</v>
       </c>
       <c r="I536">
-        <v>0.4276164148886465</v>
+        <v>0.532107679465776</v>
       </c>
       <c r="J536">
-        <v>0.06517676374396589</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K536">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L536">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M536">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N536">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O536">
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="537" spans="1:16">
       <c r="A537" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B537" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C537">
-        <v>3.032663136583086</v>
+        <v>2.941039723067857</v>
       </c>
       <c r="D537" t="s">
         <v>132</v>
       </c>
       <c r="E537">
-        <v>2.50374318641956</v>
+        <v>2.525682264558577</v>
       </c>
       <c r="F537">
         <v>-1</v>
       </c>
       <c r="G537">
-        <v>0.003207336863416915</v>
+        <v>0.003058960276932143</v>
       </c>
       <c r="H537">
-        <v>0.00265625681358044</v>
+        <v>0.002634317735441423</v>
       </c>
       <c r="I537">
-        <v>0.5289199501635258</v>
+        <v>0.4153574585092796</v>
       </c>
       <c r="J537">
-        <v>0.06517676374396589</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K537">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L537">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M537">
         <v>1.17</v>
@@ -28238,51 +28238,51 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B538" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C538">
-        <v>2.917225510045163</v>
+        <v>2.132867933343715</v>
       </c>
       <c r="D538" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E538">
-        <v>2.50374318641956</v>
+        <v>2.560484348232362</v>
       </c>
       <c r="F538">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G538">
-        <v>0.003082774489954837</v>
+        <v>0.002267132066656285</v>
       </c>
       <c r="H538">
-        <v>0.00265625681358044</v>
+        <v>0.002719515651767639</v>
       </c>
       <c r="I538">
-        <v>0.4134823236256033</v>
+        <v>0.4276164148886465</v>
       </c>
       <c r="J538">
         <v>0.06517676374396589</v>
       </c>
       <c r="K538">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L538">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M538">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N538">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28293,90 +28293,90 @@
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B539" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C539">
-        <v>2.104641124313295</v>
+        <v>3.032663136583086</v>
       </c>
       <c r="D539" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E539">
-        <v>2.527050652099242</v>
+        <v>2.50374318641956</v>
       </c>
       <c r="F539">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G539">
-        <v>0.002295358875686706</v>
+        <v>0.003207336863416915</v>
       </c>
       <c r="H539">
-        <v>0.002752949347900758</v>
+        <v>0.00265625681358044</v>
       </c>
       <c r="I539">
-        <v>0.4224095277859474</v>
+        <v>0.5289199501635258</v>
       </c>
       <c r="J539">
-        <v>0.09258143270553931</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K539">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L539">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M539">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N539">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O539">
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="540" spans="1:16">
       <c r="A540" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B540" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C540">
-        <v>2.995940880174577</v>
+        <v>2.917225510045163</v>
       </c>
       <c r="D540" t="s">
         <v>132</v>
       </c>
       <c r="E540">
-        <v>2.471679723734519</v>
+        <v>2.50374318641956</v>
       </c>
       <c r="F540">
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.003244059119825423</v>
+        <v>0.003082774489954837</v>
       </c>
       <c r="H540">
-        <v>0.002688320276265481</v>
+        <v>0.00265625681358044</v>
       </c>
       <c r="I540">
-        <v>0.5242611564400583</v>
+        <v>0.4134823236256033</v>
       </c>
       <c r="J540">
-        <v>0.09258143270553931</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K540">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L540">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M540">
         <v>1.17</v>
@@ -28388,51 +28388,51 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="541" spans="1:16">
       <c r="A541" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B541" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C541">
-        <v>2.882421580463965</v>
+        <v>2.104641124313295</v>
       </c>
       <c r="D541" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E541">
-        <v>2.471679723734519</v>
+        <v>2.527050652099242</v>
       </c>
       <c r="F541">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G541">
-        <v>0.003117578419536035</v>
+        <v>0.002295358875686706</v>
       </c>
       <c r="H541">
-        <v>0.002688320276265481</v>
+        <v>0.002752949347900758</v>
       </c>
       <c r="I541">
-        <v>0.4107418567294463</v>
+        <v>0.4224095277859474</v>
       </c>
       <c r="J541">
         <v>0.09258143270553931</v>
       </c>
       <c r="K541">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L541">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M541">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N541">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28443,90 +28443,90 @@
     </row>
     <row r="542" spans="1:16">
       <c r="A542" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B542" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C542">
-        <v>2.127453766817889</v>
+        <v>2.995940880174577</v>
       </c>
       <c r="D542" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E542">
-        <v>2.518537471376529</v>
+        <v>2.471679723734519</v>
       </c>
       <c r="F542">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G542">
-        <v>0.002332546233182111</v>
+        <v>0.003244059119825423</v>
       </c>
       <c r="H542">
-        <v>0.002761462528623472</v>
+        <v>0.002688320276265481</v>
       </c>
       <c r="I542">
-        <v>0.3910837045586395</v>
+        <v>0.5242611564400583</v>
       </c>
       <c r="J542">
-        <v>0.09955944969136986</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K542">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L542">
-        <v>2.23</v>
+        <v>3.12</v>
       </c>
       <c r="M542">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N542">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O542">
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="543" spans="1:16">
       <c r="A543" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B543" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C543">
-        <v>2.986590337413564</v>
+        <v>2.882421580463965</v>
       </c>
       <c r="D543" t="s">
         <v>132</v>
       </c>
       <c r="E543">
-        <v>2.463515443861097</v>
+        <v>2.471679723734519</v>
       </c>
       <c r="F543">
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.003253409662586436</v>
+        <v>0.003117578419536035</v>
       </c>
       <c r="H543">
-        <v>0.002696484556138903</v>
+        <v>0.002688320276265481</v>
       </c>
       <c r="I543">
-        <v>0.5230748935524669</v>
+        <v>0.4107418567294463</v>
       </c>
       <c r="J543">
-        <v>0.09955944969136986</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K543">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L543">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M543">
         <v>1.17</v>
@@ -28538,51 +28538,51 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="544" spans="1:16">
       <c r="A544" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B544" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C544">
-        <v>2.87355949889196</v>
+        <v>2.127453766817889</v>
       </c>
       <c r="D544" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E544">
-        <v>2.463515443861097</v>
+        <v>2.518537471376529</v>
       </c>
       <c r="F544">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G544">
-        <v>0.003126440501108039</v>
+        <v>0.002332546233182111</v>
       </c>
       <c r="H544">
-        <v>0.002696484556138903</v>
+        <v>0.002761462528623472</v>
       </c>
       <c r="I544">
-        <v>0.4100440550308631</v>
+        <v>0.3910837045586395</v>
       </c>
       <c r="J544">
         <v>0.09955944969136986</v>
       </c>
       <c r="K544">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L544">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="M544">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N544">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28593,90 +28593,90 @@
     </row>
     <row r="545" spans="1:16">
       <c r="A545" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B545" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C545">
-        <v>2.119309945208395</v>
+        <v>2.986590337413564</v>
       </c>
       <c r="D545" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E545">
-        <v>2.508891391411886</v>
+        <v>2.463515443861097</v>
       </c>
       <c r="F545">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G545">
-        <v>0.002340690054791605</v>
+        <v>0.003253409662586436</v>
       </c>
       <c r="H545">
-        <v>0.002771108608588114</v>
+        <v>0.002696484556138903</v>
       </c>
       <c r="I545">
-        <v>0.3895814462034908</v>
+        <v>0.5230748935524669</v>
       </c>
       <c r="J545">
-        <v>0.1074660726132081</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K545">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L545">
-        <v>2.23</v>
+        <v>3.12</v>
       </c>
       <c r="M545">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N545">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="546" spans="1:16">
       <c r="A546" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B546" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C546">
-        <v>2.975995462698301</v>
+        <v>2.87355949889196</v>
       </c>
       <c r="D546" t="s">
         <v>132</v>
       </c>
       <c r="E546">
-        <v>2.454264695042546</v>
+        <v>2.463515443861097</v>
       </c>
       <c r="F546">
         <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.003264004537301699</v>
+        <v>0.003126440501108039</v>
       </c>
       <c r="H546">
-        <v>0.002705735304957454</v>
+        <v>0.002696484556138903</v>
       </c>
       <c r="I546">
-        <v>0.5217307676557548</v>
+        <v>0.4100440550308631</v>
       </c>
       <c r="J546">
-        <v>0.1074660726132081</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K546">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L546">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M546">
         <v>1.17</v>
@@ -28688,51 +28688,51 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="547" spans="1:16">
       <c r="A547" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B547" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C547">
-        <v>2.863518087781226</v>
+        <v>2.119309945208395</v>
       </c>
       <c r="D547" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E547">
-        <v>2.454264695042546</v>
+        <v>2.508891391411886</v>
       </c>
       <c r="F547">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G547">
-        <v>0.003136481912218774</v>
+        <v>0.002340690054791605</v>
       </c>
       <c r="H547">
-        <v>0.002705735304957454</v>
+        <v>0.002771108608588114</v>
       </c>
       <c r="I547">
-        <v>0.4092533927386794</v>
+        <v>0.3895814462034908</v>
       </c>
       <c r="J547">
         <v>0.1074660726132081</v>
       </c>
       <c r="K547">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L547">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="M547">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N547">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O547">
         <v>1</v>
@@ -28743,34 +28743,34 @@
     </row>
     <row r="548" spans="1:16">
       <c r="A548" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B548" t="s">
         <v>56</v>
       </c>
       <c r="C548">
-        <v>2.131023582128605</v>
+        <v>2.12608596303</v>
       </c>
       <c r="D548" t="s">
         <v>133</v>
       </c>
       <c r="E548">
-        <v>2.514574311506508</v>
+        <v>2.508891391411886</v>
       </c>
       <c r="F548">
         <v>1</v>
       </c>
       <c r="G548">
-        <v>0.002348976417871395</v>
+        <v>0.002353914036970001</v>
       </c>
       <c r="H548">
-        <v>0.002765425688493492</v>
+        <v>0.002771108608588114</v>
       </c>
       <c r="I548">
-        <v>0.3835507293779026</v>
+        <v>0.3828054283818867</v>
       </c>
       <c r="J548">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K548">
         <v>1.06</v>
@@ -28788,39 +28788,39 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="549" spans="1:16">
       <c r="A549" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B549" t="s">
         <v>52</v>
       </c>
       <c r="C549">
-        <v>2.982237358539935</v>
+        <v>2.975995462698301</v>
       </c>
       <c r="D549" t="s">
         <v>132</v>
       </c>
       <c r="E549">
-        <v>2.459714708575913</v>
+        <v>2.454264695042546</v>
       </c>
       <c r="F549">
         <v>-1</v>
       </c>
       <c r="G549">
-        <v>0.003257762641460066</v>
+        <v>0.003264004537301699</v>
       </c>
       <c r="H549">
-        <v>0.002700285291424087</v>
+        <v>0.002705735304957454</v>
       </c>
       <c r="I549">
-        <v>0.5225226499640216</v>
+        <v>0.5217307676557548</v>
       </c>
       <c r="J549">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K549">
         <v>1.34</v>
@@ -28838,39 +28838,39 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="550" spans="1:16">
       <c r="A550" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B550" t="s">
         <v>53</v>
       </c>
       <c r="C550">
-        <v>2.869433914437102</v>
+        <v>2.863518087781226</v>
       </c>
       <c r="D550" t="s">
         <v>132</v>
       </c>
       <c r="E550">
-        <v>2.459714708575913</v>
+        <v>2.454264695042546</v>
       </c>
       <c r="F550">
         <v>-1</v>
       </c>
       <c r="G550">
-        <v>0.003130566085562898</v>
+        <v>0.003136481912218774</v>
       </c>
       <c r="H550">
-        <v>0.002700285291424087</v>
+        <v>0.002705735304957454</v>
       </c>
       <c r="I550">
-        <v>0.4097192058611889</v>
+        <v>0.4092533927386794</v>
       </c>
       <c r="J550">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K550">
         <v>1.27</v>
@@ -28888,7 +28888,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28899,28 +28899,28 @@
         <v>56</v>
       </c>
       <c r="C551">
-        <v>2.121386201382029</v>
+        <v>2.131023582128605</v>
       </c>
       <c r="D551" t="s">
         <v>133</v>
       </c>
       <c r="E551">
-        <v>2.503482231779316</v>
+        <v>2.514574311506508</v>
       </c>
       <c r="F551">
         <v>1</v>
       </c>
       <c r="G551">
-        <v>0.002358613798617972</v>
+        <v>0.002348976417871395</v>
       </c>
       <c r="H551">
-        <v>0.002776517768220685</v>
+        <v>0.002765425688493492</v>
       </c>
       <c r="I551">
-        <v>0.3820960303972871</v>
+        <v>0.3835507293779026</v>
       </c>
       <c r="J551">
-        <v>0.1118998100169543</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K551">
         <v>1.06</v>
@@ -28938,7 +28938,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>55</v>
+        <v>333</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28949,28 +28949,28 @@
         <v>52</v>
       </c>
       <c r="C552">
-        <v>2.970054254577281</v>
+        <v>2.982237358539935</v>
       </c>
       <c r="D552" t="s">
         <v>132</v>
       </c>
       <c r="E552">
-        <v>2.449077222280164</v>
+        <v>2.459714708575913</v>
       </c>
       <c r="F552">
         <v>-1</v>
       </c>
       <c r="G552">
-        <v>0.003269945745422719</v>
+        <v>0.003257762641460066</v>
       </c>
       <c r="H552">
-        <v>0.002710922777719837</v>
+        <v>0.002700285291424087</v>
       </c>
       <c r="I552">
-        <v>0.5209770322971177</v>
+        <v>0.5225226499640216</v>
       </c>
       <c r="J552">
-        <v>0.1118998100169543</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K552">
         <v>1.34</v>
@@ -28988,7 +28988,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>55</v>
+        <v>333</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -28999,28 +28999,28 @@
         <v>53</v>
       </c>
       <c r="C553">
-        <v>2.857887241278468</v>
+        <v>2.869433914437102</v>
       </c>
       <c r="D553" t="s">
         <v>132</v>
       </c>
       <c r="E553">
-        <v>2.449077222280164</v>
+        <v>2.459714708575913</v>
       </c>
       <c r="F553">
         <v>-1</v>
       </c>
       <c r="G553">
-        <v>0.003142112758721532</v>
+        <v>0.003130566085562898</v>
       </c>
       <c r="H553">
-        <v>0.002710922777719837</v>
+        <v>0.002700285291424087</v>
       </c>
       <c r="I553">
-        <v>0.4088100189983046</v>
+        <v>0.4097192058611889</v>
       </c>
       <c r="J553">
-        <v>0.1118998100169543</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K553">
         <v>1.27</v>
@@ -29038,7 +29038,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>55</v>
+        <v>333</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29049,28 +29049,28 @@
         <v>52</v>
       </c>
       <c r="C554">
-        <v>2.944089643772313</v>
+        <v>2.970054254577281</v>
       </c>
       <c r="D554" t="s">
         <v>132</v>
       </c>
       <c r="E554">
-        <v>2.426406629263886</v>
+        <v>2.449077222280164</v>
       </c>
       <c r="F554">
         <v>-1</v>
       </c>
       <c r="G554">
-        <v>0.003295910356227687</v>
+        <v>0.003269945745422719</v>
       </c>
       <c r="H554">
-        <v>0.002733593370736115</v>
+        <v>0.002710922777719837</v>
       </c>
       <c r="I554">
-        <v>0.5176830145084277</v>
+        <v>0.5209770322971177</v>
       </c>
       <c r="J554">
-        <v>0.1312763852445424</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K554">
         <v>1.34</v>
@@ -29088,7 +29088,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29099,28 +29099,28 @@
         <v>53</v>
       </c>
       <c r="C555">
-        <v>2.833278990739431</v>
+        <v>2.857887241278468</v>
       </c>
       <c r="D555" t="s">
         <v>132</v>
       </c>
       <c r="E555">
-        <v>2.426406629263886</v>
+        <v>2.449077222280164</v>
       </c>
       <c r="F555">
         <v>-1</v>
       </c>
       <c r="G555">
-        <v>0.003166721009260569</v>
+        <v>0.003142112758721532</v>
       </c>
       <c r="H555">
-        <v>0.002733593370736115</v>
+        <v>0.002710922777719837</v>
       </c>
       <c r="I555">
-        <v>0.4068723614755454</v>
+        <v>0.4088100189983046</v>
       </c>
       <c r="J555">
-        <v>0.1312763852445424</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K555">
         <v>1.27</v>
@@ -29138,7 +29138,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29149,28 +29149,28 @@
         <v>52</v>
       </c>
       <c r="C556">
-        <v>2.897401147650162</v>
+        <v>2.944089643772313</v>
       </c>
       <c r="D556" t="s">
         <v>132</v>
       </c>
       <c r="E556">
-        <v>2.385641300560216</v>
+        <v>2.426406629263886</v>
       </c>
       <c r="F556">
         <v>-1</v>
       </c>
       <c r="G556">
-        <v>0.003342598852349839</v>
+        <v>0.003295910356227687</v>
       </c>
       <c r="H556">
-        <v>0.002774358699439784</v>
+        <v>0.002733593370736115</v>
       </c>
       <c r="I556">
-        <v>0.5117598470899458</v>
+        <v>0.5176830145084277</v>
       </c>
       <c r="J556">
-        <v>0.16611854652973</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K556">
         <v>1.34</v>
@@ -29188,7 +29188,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>334</v>
+        <v>54</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29199,28 +29199,28 @@
         <v>53</v>
       </c>
       <c r="C557">
-        <v>2.789029445907243</v>
+        <v>2.833278990739431</v>
       </c>
       <c r="D557" t="s">
         <v>132</v>
       </c>
       <c r="E557">
-        <v>2.385641300560216</v>
+        <v>2.426406629263886</v>
       </c>
       <c r="F557">
         <v>-1</v>
       </c>
       <c r="G557">
-        <v>0.003210970554092757</v>
+        <v>0.003166721009260569</v>
       </c>
       <c r="H557">
-        <v>0.002774358699439784</v>
+        <v>0.002733593370736115</v>
       </c>
       <c r="I557">
-        <v>0.4033881453470269</v>
+        <v>0.4068723614755454</v>
       </c>
       <c r="J557">
-        <v>0.16611854652973</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K557">
         <v>1.27</v>
@@ -29238,7 +29238,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>334</v>
+        <v>54</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29249,28 +29249,28 @@
         <v>52</v>
       </c>
       <c r="C558">
-        <v>2.834385584744631</v>
+        <v>2.897401147650162</v>
       </c>
       <c r="D558" t="s">
         <v>132</v>
       </c>
       <c r="E558">
-        <v>2.330620249366581</v>
+        <v>2.385641300560216</v>
       </c>
       <c r="F558">
         <v>-1</v>
       </c>
       <c r="G558">
-        <v>0.003405614415255369</v>
+        <v>0.003342598852349839</v>
       </c>
       <c r="H558">
-        <v>0.002829379750633419</v>
+        <v>0.002774358699439784</v>
       </c>
       <c r="I558">
-        <v>0.5037653353780502</v>
+        <v>0.5117598470899458</v>
       </c>
       <c r="J558">
-        <v>0.2131450860114693</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K558">
         <v>1.34</v>
@@ -29288,7 +29288,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29299,28 +29299,28 @@
         <v>53</v>
       </c>
       <c r="C559">
-        <v>2.729305740765434</v>
+        <v>2.789029445907243</v>
       </c>
       <c r="D559" t="s">
         <v>132</v>
       </c>
       <c r="E559">
-        <v>2.330620249366581</v>
+        <v>2.385641300560216</v>
       </c>
       <c r="F559">
         <v>-1</v>
       </c>
       <c r="G559">
-        <v>0.003270694259234566</v>
+        <v>0.003210970554092757</v>
       </c>
       <c r="H559">
-        <v>0.002829379750633419</v>
+        <v>0.002774358699439784</v>
       </c>
       <c r="I559">
-        <v>0.3986854913988531</v>
+        <v>0.4033881453470269</v>
       </c>
       <c r="J559">
-        <v>0.2131450860114693</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K559">
         <v>1.27</v>
@@ -29338,7 +29338,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29349,28 +29349,28 @@
         <v>52</v>
       </c>
       <c r="C560">
-        <v>2.710585509297514</v>
+        <v>2.834385584744631</v>
       </c>
       <c r="D560" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E560">
-        <v>2.761972833438688</v>
+        <v>2.330620249366581</v>
       </c>
       <c r="F560">
         <v>-1</v>
       </c>
       <c r="G560">
-        <v>0.003529414490702487</v>
+        <v>0.003405614415255369</v>
       </c>
       <c r="H560">
-        <v>0.003538027166561312</v>
+        <v>0.002829379750633419</v>
       </c>
       <c r="I560">
-        <v>-0.05138732414117442</v>
+        <v>0.5037653353780502</v>
       </c>
       <c r="J560">
-        <v>0.3055332020167811</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K560">
         <v>1.34</v>
@@ -29379,16 +29379,16 @@
         <v>3.12</v>
       </c>
       <c r="M560">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N560">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O560">
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>56</v>
+        <v>335</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29399,28 +29399,28 @@
         <v>53</v>
       </c>
       <c r="C561">
-        <v>2.611972833438688</v>
+        <v>2.729305740765434</v>
       </c>
       <c r="D561" t="s">
         <v>132</v>
       </c>
       <c r="E561">
-        <v>2.222526153640366</v>
+        <v>2.330620249366581</v>
       </c>
       <c r="F561">
         <v>-1</v>
       </c>
       <c r="G561">
-        <v>0.003388027166561312</v>
+        <v>0.003270694259234566</v>
       </c>
       <c r="H561">
-        <v>0.002937473846359634</v>
+        <v>0.002829379750633419</v>
       </c>
       <c r="I561">
-        <v>0.389446679798322</v>
+        <v>0.3986854913988531</v>
       </c>
       <c r="J561">
-        <v>0.3055332020167811</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K561">
         <v>1.27</v>
@@ -29438,7 +29438,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>56</v>
+        <v>335</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29449,28 +29449,28 @@
         <v>52</v>
       </c>
       <c r="C562">
-        <v>2.647551728558422</v>
+        <v>2.710585509297514</v>
       </c>
       <c r="D562" t="s">
         <v>134</v>
       </c>
       <c r="E562">
-        <v>2.702231862141191</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="F562">
         <v>-1</v>
       </c>
       <c r="G562">
-        <v>0.003592448271441579</v>
+        <v>0.003529414490702487</v>
       </c>
       <c r="H562">
-        <v>0.003597768137858809</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="I562">
-        <v>-0.05468013358276913</v>
+        <v>-0.05138732414117442</v>
       </c>
       <c r="J562">
-        <v>0.3525733368967002</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K562">
         <v>1.34</v>
@@ -29488,7 +29488,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>336</v>
+        <v>56</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29499,28 +29499,28 @@
         <v>53</v>
       </c>
       <c r="C563">
-        <v>2.552231862141191</v>
+        <v>2.611972833438688</v>
       </c>
       <c r="D563" t="s">
         <v>132</v>
       </c>
       <c r="E563">
-        <v>2.167489195830861</v>
+        <v>2.222526153640366</v>
       </c>
       <c r="F563">
         <v>-1</v>
       </c>
       <c r="G563">
-        <v>0.003447768137858809</v>
+        <v>0.003388027166561312</v>
       </c>
       <c r="H563">
-        <v>0.00299251080416914</v>
+        <v>0.002937473846359634</v>
       </c>
       <c r="I563">
-        <v>0.3847426663103302</v>
+        <v>0.389446679798322</v>
       </c>
       <c r="J563">
-        <v>0.3525733368967002</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K563">
         <v>1.27</v>
@@ -29538,7 +29538,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>336</v>
+        <v>56</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29549,28 +29549,28 @@
         <v>52</v>
       </c>
       <c r="C564">
-        <v>2.59897387935353</v>
+        <v>2.647551728558422</v>
       </c>
       <c r="D564" t="s">
         <v>134</v>
       </c>
       <c r="E564">
-        <v>2.65619166177536</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="F564">
         <v>-1</v>
       </c>
       <c r="G564">
-        <v>0.003641026120646471</v>
+        <v>0.003592448271441579</v>
       </c>
       <c r="H564">
-        <v>0.00364380833822464</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="I564">
-        <v>-0.05721778242183051</v>
+        <v>-0.05468013358276913</v>
       </c>
       <c r="J564">
-        <v>0.3888254631690077</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K564">
         <v>1.34</v>
@@ -29588,7 +29588,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29599,28 +29599,28 @@
         <v>53</v>
       </c>
       <c r="C565">
-        <v>2.50619166177536</v>
+        <v>2.552231862141191</v>
       </c>
       <c r="D565" t="s">
         <v>132</v>
       </c>
       <c r="E565">
-        <v>2.125074208092261</v>
+        <v>2.167489195830861</v>
       </c>
       <c r="F565">
         <v>-1</v>
       </c>
       <c r="G565">
-        <v>0.00349380833822464</v>
+        <v>0.003447768137858809</v>
       </c>
       <c r="H565">
-        <v>0.003034925791907739</v>
+        <v>0.00299251080416914</v>
       </c>
       <c r="I565">
-        <v>0.3811174536830992</v>
+        <v>0.3847426663103302</v>
       </c>
       <c r="J565">
-        <v>0.3888254631690077</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K565">
         <v>1.27</v>
@@ -29638,7 +29638,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29649,28 +29649,28 @@
         <v>57</v>
       </c>
       <c r="C566">
-        <v>1.838291711302243</v>
+        <v>1.858962462723951</v>
       </c>
       <c r="D566" t="s">
         <v>133</v>
       </c>
       <c r="E566">
-        <v>2.143893006714428</v>
+        <v>2.165632934933811</v>
       </c>
       <c r="F566">
         <v>1</v>
       </c>
       <c r="G566">
-        <v>0.002781708288697757</v>
+        <v>0.002761037537276049</v>
       </c>
       <c r="H566">
-        <v>0.003136106993285572</v>
+        <v>0.00311436706506619</v>
       </c>
       <c r="I566">
-        <v>0.3056012954121849</v>
+        <v>0.3066704722098597</v>
       </c>
       <c r="J566">
-        <v>0.4066450764635833</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K566">
         <v>1.16</v>
@@ -29688,7 +29688,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29699,28 +29699,28 @@
         <v>52</v>
       </c>
       <c r="C567">
-        <v>2.575095597538799</v>
+        <v>2.59897387935353</v>
       </c>
       <c r="D567" t="s">
         <v>134</v>
       </c>
       <c r="E567">
-        <v>2.633560752891249</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="F567">
         <v>-1</v>
       </c>
       <c r="G567">
-        <v>0.003664904402461202</v>
+        <v>0.003641026120646471</v>
       </c>
       <c r="H567">
-        <v>0.003666439247108751</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="I567">
-        <v>-0.05846515535245045</v>
+        <v>-0.05721778242183051</v>
       </c>
       <c r="J567">
-        <v>0.4066450764635833</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K567">
         <v>1.34</v>
@@ -29738,7 +29738,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29749,28 +29749,28 @@
         <v>53</v>
       </c>
       <c r="C568">
-        <v>2.483560752891249</v>
+        <v>2.50619166177536</v>
       </c>
       <c r="D568" t="s">
         <v>132</v>
       </c>
       <c r="E568">
-        <v>2.104225260537608</v>
+        <v>2.125074208092261</v>
       </c>
       <c r="F568">
         <v>-1</v>
       </c>
       <c r="G568">
-        <v>0.003516439247108751</v>
+        <v>0.00349380833822464</v>
       </c>
       <c r="H568">
-        <v>0.003055774739462393</v>
+        <v>0.003034925791907739</v>
       </c>
       <c r="I568">
-        <v>0.3793354923536416</v>
+        <v>0.3811174536830992</v>
       </c>
       <c r="J568">
-        <v>0.4066450764635833</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K568">
         <v>1.27</v>
@@ -29788,7 +29788,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -29799,28 +29799,28 @@
         <v>57</v>
       </c>
       <c r="C569">
-        <v>1.784876857591519</v>
+        <v>1.838291711302243</v>
       </c>
       <c r="D569" t="s">
         <v>133</v>
       </c>
       <c r="E569">
-        <v>2.087715315742805</v>
+        <v>2.143893006714428</v>
       </c>
       <c r="F569">
         <v>1</v>
       </c>
       <c r="G569">
-        <v>0.002835123142408481</v>
+        <v>0.002781708288697757</v>
       </c>
       <c r="H569">
-        <v>0.003192284684257196</v>
+        <v>0.003136106993285572</v>
       </c>
       <c r="I569">
-        <v>0.3028384581512857</v>
+        <v>0.3056012954121849</v>
       </c>
       <c r="J569">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K569">
         <v>1.16</v>
@@ -29838,7 +29838,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -29849,28 +29849,28 @@
         <v>52</v>
       </c>
       <c r="C570">
-        <v>2.513392232045375</v>
+        <v>2.575095597538799</v>
       </c>
       <c r="D570" t="s">
         <v>134</v>
       </c>
       <c r="E570">
-        <v>2.575080697535542</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="F570">
         <v>-1</v>
       </c>
       <c r="G570">
-        <v>0.003726607767954625</v>
+        <v>0.003664904402461202</v>
       </c>
       <c r="H570">
-        <v>0.003724919302464458</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="I570">
-        <v>-0.0616884654901666</v>
+        <v>-0.05846515535245045</v>
       </c>
       <c r="J570">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K570">
         <v>1.34</v>
@@ -29888,7 +29888,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29899,28 +29899,28 @@
         <v>53</v>
       </c>
       <c r="C571">
-        <v>2.425080697535542</v>
+        <v>2.483560752891249</v>
       </c>
       <c r="D571" t="s">
         <v>132</v>
       </c>
       <c r="E571">
-        <v>2.050349933950066</v>
+        <v>2.104225260537608</v>
       </c>
       <c r="F571">
         <v>-1</v>
       </c>
       <c r="G571">
-        <v>0.003574919302464458</v>
+        <v>0.003516439247108751</v>
       </c>
       <c r="H571">
-        <v>0.003109650066049934</v>
+        <v>0.003055774739462393</v>
       </c>
       <c r="I571">
-        <v>0.3747307635854757</v>
+        <v>0.3793354923536416</v>
       </c>
       <c r="J571">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K571">
         <v>1.27</v>
@@ -29938,7 +29938,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -29946,49 +29946,49 @@
         <v>0</v>
       </c>
       <c r="B572" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C572">
-        <v>2.46037019732591</v>
+        <v>1.784876857591519</v>
       </c>
       <c r="D572" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E572">
-        <v>2.524828470599929</v>
+        <v>2.087715315742805</v>
       </c>
       <c r="F572">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G572">
-        <v>0.00377962980267409</v>
+        <v>0.002835123142408481</v>
       </c>
       <c r="H572">
-        <v>0.003775171529400071</v>
+        <v>0.003192284684257196</v>
       </c>
       <c r="I572">
-        <v>-0.0644582732740191</v>
+        <v>0.3028384581512857</v>
       </c>
       <c r="J572">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K572">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="L572">
-        <v>3.12</v>
+        <v>2.31</v>
       </c>
       <c r="M572">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="N572">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="O572">
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>57</v>
+        <v>339</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -29996,48 +29996,198 @@
         <v>1</v>
       </c>
       <c r="B573" t="s">
+        <v>52</v>
+      </c>
+      <c r="C573">
+        <v>2.513392232045375</v>
+      </c>
+      <c r="D573" t="s">
+        <v>134</v>
+      </c>
+      <c r="E573">
+        <v>2.575080697535542</v>
+      </c>
+      <c r="F573">
+        <v>-1</v>
+      </c>
+      <c r="G573">
+        <v>0.003726607767954625</v>
+      </c>
+      <c r="H573">
+        <v>0.003724919302464458</v>
+      </c>
+      <c r="I573">
+        <v>-0.0616884654901666</v>
+      </c>
+      <c r="J573">
+        <v>0.4526923641452424</v>
+      </c>
+      <c r="K573">
+        <v>1.34</v>
+      </c>
+      <c r="L573">
+        <v>3.12</v>
+      </c>
+      <c r="M573">
+        <v>1.27</v>
+      </c>
+      <c r="N573">
+        <v>3.15</v>
+      </c>
+      <c r="O573">
+        <v>1</v>
+      </c>
+      <c r="P573" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="574" spans="1:16">
+      <c r="A574" s="1">
+        <v>2</v>
+      </c>
+      <c r="B574" t="s">
         <v>53</v>
       </c>
-      <c r="C573">
+      <c r="C574">
+        <v>2.425080697535542</v>
+      </c>
+      <c r="D574" t="s">
+        <v>132</v>
+      </c>
+      <c r="E574">
+        <v>2.050349933950066</v>
+      </c>
+      <c r="F574">
+        <v>-1</v>
+      </c>
+      <c r="G574">
+        <v>0.003574919302464458</v>
+      </c>
+      <c r="H574">
+        <v>0.003109650066049934</v>
+      </c>
+      <c r="I574">
+        <v>0.3747307635854757</v>
+      </c>
+      <c r="J574">
+        <v>0.4526923641452424</v>
+      </c>
+      <c r="K574">
+        <v>1.27</v>
+      </c>
+      <c r="L574">
+        <v>3</v>
+      </c>
+      <c r="M574">
+        <v>1.17</v>
+      </c>
+      <c r="N574">
+        <v>2.58</v>
+      </c>
+      <c r="O574">
+        <v>1</v>
+      </c>
+      <c r="P574" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="575" spans="1:16">
+      <c r="A575" s="1">
+        <v>0</v>
+      </c>
+      <c r="B575" t="s">
+        <v>52</v>
+      </c>
+      <c r="C575">
+        <v>2.46037019732591</v>
+      </c>
+      <c r="D575" t="s">
+        <v>134</v>
+      </c>
+      <c r="E575">
+        <v>2.524828470599929</v>
+      </c>
+      <c r="F575">
+        <v>-1</v>
+      </c>
+      <c r="G575">
+        <v>0.00377962980267409</v>
+      </c>
+      <c r="H575">
+        <v>0.003775171529400071</v>
+      </c>
+      <c r="I575">
+        <v>-0.0644582732740191</v>
+      </c>
+      <c r="J575">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K575">
+        <v>1.34</v>
+      </c>
+      <c r="L575">
+        <v>3.12</v>
+      </c>
+      <c r="M575">
+        <v>1.27</v>
+      </c>
+      <c r="N575">
+        <v>3.15</v>
+      </c>
+      <c r="O575">
+        <v>1</v>
+      </c>
+      <c r="P575" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="576" spans="1:16">
+      <c r="A576" s="1">
+        <v>1</v>
+      </c>
+      <c r="B576" t="s">
+        <v>53</v>
+      </c>
+      <c r="C576">
         <v>2.37482847059993</v>
       </c>
-      <c r="D573" t="s">
+      <c r="D576" t="s">
         <v>132</v>
       </c>
-      <c r="E573">
+      <c r="E576">
         <v>2.004054575277101</v>
       </c>
-      <c r="F573">
-        <v>-1</v>
-      </c>
-      <c r="G573">
+      <c r="F576">
+        <v>-1</v>
+      </c>
+      <c r="G576">
         <v>0.003625171529400071</v>
       </c>
-      <c r="H573">
+      <c r="H576">
         <v>0.003155945424722899</v>
       </c>
-      <c r="I573">
+      <c r="I576">
         <v>0.370773895322829</v>
       </c>
-      <c r="J573">
+      <c r="J576">
         <v>0.4922610467717091</v>
       </c>
-      <c r="K573">
+      <c r="K576">
         <v>1.27</v>
       </c>
-      <c r="L573">
+      <c r="L576">
         <v>3</v>
       </c>
-      <c r="M573">
+      <c r="M576">
         <v>1.17</v>
       </c>
-      <c r="N573">
+      <c r="N576">
         <v>2.58</v>
       </c>
-      <c r="O573">
-        <v>1</v>
-      </c>
-      <c r="P573" t="s">
+      <c r="O576">
+        <v>1</v>
+      </c>
+      <c r="P576" t="s">
         <v>57</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="339">
   <si>
     <t>trade_time</t>
   </si>
@@ -401,9 +401,6 @@
   </si>
   <si>
     <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
   </si>
   <si>
     <t>2021-04-26</t>
@@ -1391,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P576"/>
+  <dimension ref="A1:P575"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1488,7 +1485,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1538,7 +1535,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1588,7 +1585,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1638,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1688,7 +1685,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1738,7 +1735,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1788,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1838,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1888,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1938,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1988,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2038,7 +2035,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2088,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2138,7 +2135,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2188,7 +2185,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2238,7 +2235,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2288,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2338,7 +2335,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2388,7 +2385,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2438,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2488,7 +2485,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2538,7 +2535,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2588,7 +2585,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2638,7 +2635,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2688,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2738,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2788,7 +2785,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2838,7 +2835,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2888,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2938,7 +2935,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2988,7 +2985,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3038,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3088,7 +3085,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3138,7 +3135,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3188,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3238,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3288,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3338,7 +3335,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3388,7 +3385,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3438,7 +3435,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3488,7 +3485,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3538,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3588,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3638,7 +3635,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3688,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3738,7 +3735,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3788,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3838,7 +3835,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3888,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3938,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3988,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4038,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4088,7 +4085,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4138,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4188,7 +4185,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4238,7 +4235,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4288,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4338,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4388,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4438,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4488,7 +4485,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4538,7 +4535,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4588,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4638,7 +4635,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4688,7 +4685,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4738,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4788,7 +4785,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4838,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4888,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4938,7 +4935,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4988,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5038,7 +5035,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5088,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5138,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5188,7 +5185,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5238,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5288,7 +5285,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5338,7 +5335,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5388,7 +5385,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5438,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5488,7 +5485,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5538,7 +5535,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5588,7 +5585,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5638,7 +5635,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5688,7 +5685,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5738,7 +5735,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5788,7 +5785,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5838,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5888,7 +5885,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5938,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5988,7 +5985,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6038,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6088,7 +6085,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6138,7 +6135,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6188,7 +6185,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6238,7 +6235,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6288,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6338,7 +6335,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6388,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6438,7 +6435,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6488,7 +6485,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6538,7 +6535,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6588,7 +6585,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6638,7 +6635,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6688,7 +6685,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6738,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6788,7 +6785,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6838,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6888,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6938,7 +6935,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6988,7 +6985,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7038,7 +7035,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7088,7 +7085,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7138,7 +7135,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7188,7 +7185,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7238,7 +7235,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7288,7 +7285,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7338,7 +7335,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7388,7 +7385,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7438,7 +7435,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7488,7 +7485,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7538,7 +7535,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7588,7 +7585,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7638,7 +7635,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7688,7 +7685,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7738,7 +7735,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7788,7 +7785,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7838,7 +7835,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7888,7 +7885,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7938,7 +7935,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7988,7 +7985,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8038,7 +8035,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8088,7 +8085,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8138,7 +8135,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8188,7 +8185,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8238,7 +8235,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8288,7 +8285,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8338,7 +8335,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8388,7 +8385,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8438,7 +8435,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8488,7 +8485,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8538,7 +8535,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8588,7 +8585,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8638,7 +8635,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8688,7 +8685,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8738,7 +8735,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8788,7 +8785,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8838,7 +8835,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9088,7 +9085,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9138,7 +9135,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9188,7 +9185,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9238,7 +9235,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9288,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9338,7 +9335,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9388,7 +9385,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9438,7 +9435,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9488,7 +9485,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9538,7 +9535,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9588,7 +9585,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9638,7 +9635,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9688,7 +9685,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9738,7 +9735,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9788,7 +9785,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9838,7 +9835,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9888,7 +9885,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9938,7 +9935,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9988,7 +9985,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10038,7 +10035,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10088,7 +10085,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10138,7 +10135,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10188,7 +10185,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10238,7 +10235,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10288,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10338,7 +10335,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10388,7 +10385,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10438,7 +10435,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10488,7 +10485,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10538,7 +10535,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11338,7 +11335,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11388,7 +11385,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11438,7 +11435,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11488,7 +11485,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11538,7 +11535,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11588,7 +11585,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11638,7 +11635,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11688,7 +11685,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11738,7 +11735,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11788,7 +11785,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11838,7 +11835,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11888,7 +11885,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11938,7 +11935,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11988,7 +11985,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12038,7 +12035,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12088,7 +12085,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12388,7 +12385,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12438,7 +12435,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12488,7 +12485,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12538,7 +12535,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12588,7 +12585,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12938,7 +12935,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12988,7 +12985,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13038,7 +13035,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13088,7 +13085,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13138,7 +13135,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13188,7 +13185,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13238,7 +13235,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13288,7 +13285,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13338,7 +13335,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13388,7 +13385,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13438,7 +13435,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13488,7 +13485,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13538,7 +13535,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13988,7 +13985,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14038,7 +14035,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14088,7 +14085,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14138,7 +14135,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14188,7 +14185,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14238,7 +14235,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14288,7 +14285,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14638,7 +14635,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14688,7 +14685,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14738,7 +14735,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14788,7 +14785,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14838,7 +14835,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14888,7 +14885,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14938,7 +14935,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15288,7 +15285,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15338,7 +15335,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15388,7 +15385,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15438,7 +15435,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15488,7 +15485,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15538,7 +15535,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15838,7 +15835,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15888,7 +15885,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15938,7 +15935,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15988,7 +15985,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16038,7 +16035,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16288,7 +16285,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16338,7 +16335,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16388,7 +16385,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16438,7 +16435,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16938,7 +16935,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -16988,7 +16985,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17038,7 +17035,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17088,7 +17085,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17138,7 +17135,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17188,7 +17185,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17238,7 +17235,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17288,7 +17285,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17338,7 +17335,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17388,7 +17385,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17588,7 +17585,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17638,7 +17635,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17688,7 +17685,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17888,7 +17885,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17938,7 +17935,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17988,7 +17985,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18038,7 +18035,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18088,7 +18085,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18138,7 +18135,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18188,7 +18185,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18238,7 +18235,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18288,7 +18285,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18338,7 +18335,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18388,7 +18385,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18438,7 +18435,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18488,7 +18485,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18538,7 +18535,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18588,7 +18585,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18638,7 +18635,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18688,7 +18685,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18738,7 +18735,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18788,7 +18785,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18838,7 +18835,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18888,7 +18885,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18938,7 +18935,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18988,7 +18985,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19038,7 +19035,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19088,7 +19085,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19138,7 +19135,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19188,7 +19185,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19238,7 +19235,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19288,7 +19285,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19338,7 +19335,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19388,7 +19385,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19438,7 +19435,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19488,7 +19485,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19538,7 +19535,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19588,7 +19585,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19638,7 +19635,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19688,7 +19685,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19738,7 +19735,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19788,7 +19785,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19838,7 +19835,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19888,7 +19885,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19938,7 +19935,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19988,7 +19985,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20038,7 +20035,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20088,7 +20085,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20138,7 +20135,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20188,7 +20185,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20238,7 +20235,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20288,7 +20285,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20338,7 +20335,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20388,7 +20385,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20438,7 +20435,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20488,7 +20485,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20538,7 +20535,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20588,7 +20585,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20638,7 +20635,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20688,7 +20685,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20738,7 +20735,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20788,7 +20785,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20838,7 +20835,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20888,7 +20885,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20938,7 +20935,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20988,7 +20985,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21038,7 +21035,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21088,7 +21085,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21138,7 +21135,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21188,7 +21185,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21238,7 +21235,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21288,7 +21285,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21438,7 +21435,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21488,7 +21485,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21538,7 +21535,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21588,7 +21585,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21638,7 +21635,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21788,7 +21785,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21838,7 +21835,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21888,7 +21885,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -21938,7 +21935,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -21988,7 +21985,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22038,7 +22035,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22088,7 +22085,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22138,7 +22135,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22188,7 +22185,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22238,7 +22235,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22288,7 +22285,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22338,7 +22335,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22388,7 +22385,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22438,7 +22435,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22488,7 +22485,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22538,7 +22535,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22588,7 +22585,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22638,7 +22635,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22688,7 +22685,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22738,7 +22735,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22755,7 +22752,7 @@
         <v>129</v>
       </c>
       <c r="E428">
-        <v>2.527186807308291</v>
+        <v>2.557425288074153</v>
       </c>
       <c r="F428">
         <v>-1</v>
@@ -22764,10 +22761,10 @@
         <v>0.003088043577374465</v>
       </c>
       <c r="H428">
-        <v>0.002472813192691709</v>
+        <v>0.002502574711925846</v>
       </c>
       <c r="I428">
-        <v>0.6247696153172444</v>
+        <v>0.5945311345513824</v>
       </c>
       <c r="J428">
         <v>-0.02384807658622054</v>
@@ -22779,16 +22776,16 @@
         <v>3.12</v>
       </c>
       <c r="M428">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N428">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O428">
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22805,7 +22802,7 @@
         <v>129</v>
       </c>
       <c r="E429">
-        <v>2.527186807308291</v>
+        <v>2.557425288074153</v>
       </c>
       <c r="F429">
         <v>-1</v>
@@ -22814,10 +22811,10 @@
         <v>0.0029697129427355</v>
       </c>
       <c r="H429">
-        <v>0.002472813192691709</v>
+        <v>0.002502574711925846</v>
       </c>
       <c r="I429">
-        <v>0.5031002499562089</v>
+        <v>0.4728617691903469</v>
       </c>
       <c r="J429">
         <v>-0.02384807658622054</v>
@@ -22829,16 +22826,16 @@
         <v>3</v>
       </c>
       <c r="M429">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N429">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O429">
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22852,7 +22849,7 @@
         <v>3.185945174511515</v>
       </c>
       <c r="D430" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E430">
         <v>2.586594739319583</v>
@@ -22888,7 +22885,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -22902,7 +22899,7 @@
         <v>3.06250027733554</v>
       </c>
       <c r="D431" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E431">
         <v>2.586594739319583</v>
@@ -22938,7 +22935,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22952,7 +22949,7 @@
         <v>3.22654267572782</v>
       </c>
       <c r="D432" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E432">
         <v>2.621435878423129</v>
@@ -22988,7 +22985,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23002,7 +22999,7 @@
         <v>3.100977013562934</v>
       </c>
       <c r="D433" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E433">
         <v>2.621435878423129</v>
@@ -23038,7 +23035,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23052,7 +23049,7 @@
         <v>3.259685052120739</v>
       </c>
       <c r="D434" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E434">
         <v>2.649878962640932</v>
@@ -23088,7 +23085,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23102,7 +23099,7 @@
         <v>3.132388071786073</v>
       </c>
       <c r="D435" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E435">
         <v>2.649878962640932</v>
@@ -23138,7 +23135,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23152,7 +23149,7 @@
         <v>3.290901329475496</v>
       </c>
       <c r="D436" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E436">
         <v>2.676669051415537</v>
@@ -23188,7 +23185,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23202,7 +23199,7 @@
         <v>3.161973648084985</v>
       </c>
       <c r="D437" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E437">
         <v>2.676669051415537</v>
@@ -23238,7 +23235,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23252,7 +23249,7 @@
         <v>3.324668655156648</v>
       </c>
       <c r="D438" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E438">
         <v>2.705648472709063</v>
@@ -23288,7 +23285,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23302,7 +23299,7 @@
         <v>3.193977008991748</v>
       </c>
       <c r="D439" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E439">
         <v>2.705648472709063</v>
@@ -23338,7 +23335,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23352,7 +23349,7 @@
         <v>3.514497085630696</v>
       </c>
       <c r="D440" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E440">
         <v>2.868560931697985</v>
@@ -23388,7 +23385,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23402,7 +23399,7 @@
         <v>3.373889028918645</v>
       </c>
       <c r="D441" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E441">
         <v>2.868560931697985</v>
@@ -23438,7 +23435,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23452,7 +23449,7 @@
         <v>3.504669279018375</v>
       </c>
       <c r="D442" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E442">
         <v>2.860126620053082</v>
@@ -23488,7 +23485,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23502,7 +23499,7 @@
         <v>3.364574615189056</v>
       </c>
       <c r="D443" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E443">
         <v>2.860126620053082</v>
@@ -23538,7 +23535,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23552,7 +23549,7 @@
         <v>3.484588355788175</v>
       </c>
       <c r="D444" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E444">
         <v>2.842892991907762</v>
@@ -23588,7 +23585,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23602,7 +23599,7 @@
         <v>3.345542695411181</v>
       </c>
       <c r="D445" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E445">
         <v>2.842892991907762</v>
@@ -23638,7 +23635,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23652,7 +23649,7 @@
         <v>3.467968230829165</v>
       </c>
       <c r="D446" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E446">
         <v>2.828629451830999</v>
@@ -23688,7 +23685,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23702,7 +23699,7 @@
         <v>3.329790785935104</v>
       </c>
       <c r="D447" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E447">
         <v>2.828629451830999</v>
@@ -23738,7 +23735,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23752,7 +23749,7 @@
         <v>3.450555570267193</v>
       </c>
       <c r="D448" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E448">
         <v>2.813685750602441</v>
@@ -23788,7 +23785,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23802,7 +23799,7 @@
         <v>3.313287741969653</v>
       </c>
       <c r="D449" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E449">
         <v>2.813685750602441</v>
@@ -23838,7 +23835,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23852,7 +23849,7 @@
         <v>3.43166453059071</v>
       </c>
       <c r="D450" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E450">
         <v>2.797473291178594</v>
@@ -23888,7 +23885,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23902,7 +23899,7 @@
         <v>3.295383547649404</v>
       </c>
       <c r="D451" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E451">
         <v>2.797473291178594</v>
@@ -23938,7 +23935,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23952,7 +23949,7 @@
         <v>3.41667545109858</v>
       </c>
       <c r="D452" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E452">
         <v>2.784609528927886</v>
@@ -23988,7 +23985,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24002,7 +23999,7 @@
         <v>3.281177479772535</v>
       </c>
       <c r="D453" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E453">
         <v>2.784609528927886</v>
@@ -24038,7 +24035,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24052,7 +24049,7 @@
         <v>3.40518789098997</v>
       </c>
       <c r="D454" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E454">
         <v>2.774750801969004</v>
@@ -24088,7 +24085,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24102,7 +24099,7 @@
         <v>3.270290016087509</v>
       </c>
       <c r="D455" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E455">
         <v>2.774750801969004</v>
@@ -24138,7 +24135,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24152,7 +24149,7 @@
         <v>3.394743887022124</v>
       </c>
       <c r="D456" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E456">
         <v>2.765787664235404</v>
@@ -24188,7 +24185,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24202,7 +24199,7 @@
         <v>3.260391594416491</v>
       </c>
       <c r="D457" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E457">
         <v>2.765787664235404</v>
@@ -24238,7 +24235,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24252,7 +24249,7 @@
         <v>3.371143087500839</v>
       </c>
       <c r="D458" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E458">
         <v>2.745533246735795</v>
@@ -24288,7 +24285,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24302,7 +24299,7 @@
         <v>3.238023672482139</v>
       </c>
       <c r="D459" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E459">
         <v>2.745533246735795</v>
@@ -24338,7 +24335,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24352,7 +24349,7 @@
         <v>3.347974655973466</v>
       </c>
       <c r="D460" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E460">
         <v>2.725649891320511</v>
@@ -24388,7 +24385,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24402,7 +24399,7 @@
         <v>3.216065532153956</v>
       </c>
       <c r="D461" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E461">
         <v>2.725649891320511</v>
@@ -24438,7 +24435,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24452,7 +24449,7 @@
         <v>3.340600981946587</v>
       </c>
       <c r="D462" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E462">
         <v>2.719321738237743</v>
@@ -24488,7 +24485,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24502,7 +24499,7 @@
         <v>3.209077050053855</v>
       </c>
       <c r="D463" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E463">
         <v>2.719321738237743</v>
@@ -24538,7 +24535,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24552,7 +24549,7 @@
         <v>3.338798166754803</v>
       </c>
       <c r="D464" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E464">
         <v>2.71777454609554</v>
@@ -24588,7 +24585,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24602,7 +24599,7 @@
         <v>3.207368411775074</v>
       </c>
       <c r="D465" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E465">
         <v>2.71777454609554</v>
@@ -24638,7 +24635,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24652,7 +24649,7 @@
         <v>3.330627629571408</v>
       </c>
       <c r="D466" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E466">
         <v>2.71076251791576</v>
@@ -24688,7 +24685,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24702,7 +24699,7 @@
         <v>3.199624693698275</v>
       </c>
       <c r="D467" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E467">
         <v>2.71076251791576</v>
@@ -24738,7 +24735,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24752,7 +24749,7 @@
         <v>3.339410382635936</v>
       </c>
       <c r="D468" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E468">
         <v>2.718299955247258</v>
@@ -24788,7 +24785,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24802,7 +24799,7 @@
         <v>3.207948646229581</v>
       </c>
       <c r="D469" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E469">
         <v>2.718299955247258</v>
@@ -24838,7 +24835,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24852,7 +24849,7 @@
         <v>3.366448540958179</v>
       </c>
       <c r="D470" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E470">
         <v>2.741504344852168</v>
@@ -24888,7 +24885,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24902,7 +24899,7 @@
         <v>3.233574363445438</v>
       </c>
       <c r="D471" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E471">
         <v>2.741504344852168</v>
@@ -24938,7 +24935,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24952,7 +24949,7 @@
         <v>2.407128809696355</v>
       </c>
       <c r="D472" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E472">
         <v>2.841369914680043</v>
@@ -24988,7 +24985,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25002,7 +24999,7 @@
         <v>3.389468548537006</v>
       </c>
       <c r="D473" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E473">
         <v>2.761260321505639</v>
@@ -25038,7 +25035,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25052,7 +25049,7 @@
         <v>3.255391833314924</v>
       </c>
       <c r="D474" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E474">
         <v>2.761260321505639</v>
@@ -25088,7 +25085,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25102,7 +25099,7 @@
         <v>2.407323569166959</v>
       </c>
       <c r="D475" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E475">
         <v>2.841606273260873</v>
@@ -25138,7 +25135,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25152,7 +25149,7 @@
         <v>3.389721924935656</v>
       </c>
       <c r="D476" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E476">
         <v>2.761477771400003</v>
@@ -25188,7 +25185,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25202,7 +25199,7 @@
         <v>3.255631973633047</v>
       </c>
       <c r="D477" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E477">
         <v>2.761477771400003</v>
@@ -25238,7 +25235,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25252,7 +25249,7 @@
         <v>2.41122985184961</v>
       </c>
       <c r="D478" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E478">
         <v>2.846346907584478</v>
@@ -25288,7 +25285,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25302,7 +25299,7 @@
         <v>3.394803884930561</v>
       </c>
       <c r="D479" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E479">
         <v>2.76583915497772</v>
@@ -25338,7 +25335,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25352,7 +25349,7 @@
         <v>3.26044845810583</v>
       </c>
       <c r="D480" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E480">
         <v>2.76583915497772</v>
@@ -25388,7 +25385,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25402,7 +25399,7 @@
         <v>2.414401903996001</v>
       </c>
       <c r="D481" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E481">
         <v>2.850196485432039</v>
@@ -25438,7 +25435,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25452,7 +25449,7 @@
         <v>3.398930632383146</v>
       </c>
       <c r="D482" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E482">
         <v>2.769380766597476</v>
@@ -25488,7 +25485,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25502,7 +25499,7 @@
         <v>3.264359629198952</v>
       </c>
       <c r="D483" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E483">
         <v>2.769380766597476</v>
@@ -25538,7 +25535,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25552,7 +25549,7 @@
         <v>2.400941737549309</v>
       </c>
       <c r="D484" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E484">
         <v>2.833861331977317</v>
@@ -25588,7 +25585,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25602,7 +25599,7 @@
         <v>3.381419347879684</v>
       </c>
       <c r="D485" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E485">
         <v>2.754352425419131</v>
@@ -25638,7 +25635,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25652,7 +25649,7 @@
         <v>3.247763113288954</v>
       </c>
       <c r="D486" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E486">
         <v>2.754352425419131</v>
@@ -25688,7 +25685,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25702,7 +25699,7 @@
         <v>2.416869377367424</v>
       </c>
       <c r="D487" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E487">
         <v>2.853190991950757</v>
@@ -25738,7 +25735,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25752,7 +25749,7 @@
         <v>3.402140743371211</v>
       </c>
       <c r="D488" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E488">
         <v>2.772135712594696</v>
@@ -25788,7 +25785,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25802,7 +25799,7 @@
         <v>3.267402047821969</v>
       </c>
       <c r="D489" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E489">
         <v>2.772135712594696</v>
@@ -25838,7 +25835,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25852,7 +25849,7 @@
         <v>2.427926332334885</v>
       </c>
       <c r="D490" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E490">
         <v>2.866609626620006</v>
@@ -25888,7 +25885,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25902,7 +25899,7 @@
         <v>3.416525519736647</v>
       </c>
       <c r="D491" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E491">
         <v>2.784480856490405</v>
@@ -25938,7 +25935,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25952,7 +25949,7 @@
         <v>3.281035380645926</v>
       </c>
       <c r="D492" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E492">
         <v>2.784480856490405</v>
@@ -25988,7 +25985,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26002,7 +25999,7 @@
         <v>2.43983969591803</v>
       </c>
       <c r="D493" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E493">
         <v>2.88106759213353</v>
@@ -26038,7 +26035,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26052,7 +26049,7 @@
         <v>3.432024458767145</v>
       </c>
       <c r="D494" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E494">
         <v>2.797782184762848</v>
@@ -26088,7 +26085,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26102,7 +26099,7 @@
         <v>3.295724673607667</v>
       </c>
       <c r="D495" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E495">
         <v>2.797782184762848</v>
@@ -26138,7 +26135,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26152,7 +26149,7 @@
         <v>2.478555931094635</v>
       </c>
       <c r="D496" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E496">
         <v>2.928053314435237</v>
@@ -26188,7 +26185,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26202,10 +26199,10 @@
         <v>3.482393153074574</v>
       </c>
       <c r="D497" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E497">
-        <v>2.841009049280418</v>
+        <v>2.896417902311382</v>
       </c>
       <c r="F497">
         <v>-1</v>
@@ -26214,10 +26211,10 @@
         <v>0.002757606846925426</v>
       </c>
       <c r="H497">
-        <v>0.002218990950719582</v>
+        <v>0.002263582097688619</v>
       </c>
       <c r="I497">
-        <v>0.6413841037941563</v>
+        <v>0.5859752507631923</v>
       </c>
       <c r="J497">
         <v>-0.2704426515481894</v>
@@ -26229,16 +26226,16 @@
         <v>3.12</v>
       </c>
       <c r="M497">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N497">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O497">
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26252,10 +26249,10 @@
         <v>3.343462167466201</v>
       </c>
       <c r="D498" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E498">
-        <v>2.841009049280418</v>
+        <v>2.896417902311382</v>
       </c>
       <c r="F498">
         <v>-1</v>
@@ -26264,10 +26261,10 @@
         <v>0.002656537832533799</v>
       </c>
       <c r="H498">
-        <v>0.002218990950719582</v>
+        <v>0.002263582097688619</v>
       </c>
       <c r="I498">
-        <v>0.502453118185783</v>
+        <v>0.447044265154819</v>
       </c>
       <c r="J498">
         <v>-0.2704426515481894</v>
@@ -26279,16 +26276,16 @@
         <v>3</v>
       </c>
       <c r="M498">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N498">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O498">
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26302,7 +26299,7 @@
         <v>2.492450104171095</v>
       </c>
       <c r="D499" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E499">
         <v>2.944915174964921</v>
@@ -26338,7 +26335,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26352,7 +26349,7 @@
         <v>3.500469067562396</v>
       </c>
       <c r="D500" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E500">
         <v>2.912200603767166</v>
@@ -26388,7 +26385,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26402,7 +26399,7 @@
         <v>3.36059381776436</v>
       </c>
       <c r="D501" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E501">
         <v>2.912200603767166</v>
@@ -26438,7 +26435,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26452,7 +26449,7 @@
         <v>2.485588290136117</v>
       </c>
       <c r="D502" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E502">
         <v>2.936587730747715</v>
@@ -26488,7 +26485,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26502,7 +26499,7 @@
         <v>3.49154204736155</v>
       </c>
       <c r="D503" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E503">
         <v>2.904406115979861</v>
@@ -26538,7 +26535,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26552,7 +26549,7 @@
         <v>3.352133134439678</v>
       </c>
       <c r="D504" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E504">
         <v>2.904406115979861</v>
@@ -26588,7 +26585,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26602,7 +26599,7 @@
         <v>2.483803138304734</v>
       </c>
       <c r="D505" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E505">
         <v>2.934421284350405</v>
@@ -26638,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26652,7 +26649,7 @@
         <v>3.489219616823635</v>
       </c>
       <c r="D506" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E506">
         <v>2.902378322151979</v>
@@ -26688,7 +26685,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26702,7 +26699,7 @@
         <v>3.349932024900012</v>
       </c>
       <c r="D507" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E507">
         <v>2.902378322151979</v>
@@ -26738,7 +26735,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26752,7 +26749,7 @@
         <v>2.455324757264537</v>
       </c>
       <c r="D508" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E508">
         <v>2.899860142311331</v>
@@ -26788,7 +26785,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26802,7 +26799,7 @@
         <v>3.452170072557747</v>
       </c>
       <c r="D509" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E509">
         <v>2.870029093203406</v>
@@ -26838,7 +26835,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26852,7 +26849,7 @@
         <v>3.314817904588312</v>
       </c>
       <c r="D510" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E510">
         <v>2.870029093203406</v>
@@ -26888,7 +26885,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26902,7 +26899,7 @@
         <v>2.38683909149</v>
       </c>
       <c r="D511" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E511">
         <v>2.816746470254853</v>
@@ -26938,7 +26935,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26952,7 +26949,7 @@
         <v>3.363072216113203</v>
       </c>
       <c r="D512" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E512">
         <v>2.792234696158543</v>
@@ -26988,7 +26985,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27002,7 +26999,7 @@
         <v>3.230374413778931</v>
       </c>
       <c r="D513" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E513">
         <v>2.792234696158543</v>
@@ -27038,7 +27035,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27052,7 +27049,7 @@
         <v>2.332831092936091</v>
       </c>
       <c r="D514" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E514">
         <v>2.751202782689431</v>
@@ -27088,7 +27085,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27102,7 +27099,7 @@
         <v>3.29280938304307</v>
       </c>
       <c r="D515" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E515">
         <v>2.730885804597308</v>
@@ -27138,7 +27135,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27152,7 +27149,7 @@
         <v>3.163782027212462</v>
       </c>
       <c r="D516" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E516">
         <v>2.730885804597308</v>
@@ -27188,7 +27185,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27202,7 +27199,7 @@
         <v>2.292718610119939</v>
       </c>
       <c r="D517" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E517">
         <v>2.702522585097013</v>
@@ -27238,7 +27235,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27252,7 +27249,7 @@
         <v>3.240624211223998</v>
       </c>
       <c r="D518" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E518">
         <v>2.685321139650804</v>
@@ -27288,7 +27285,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27302,7 +27299,7 @@
         <v>3.114322946458565</v>
       </c>
       <c r="D519" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E519">
         <v>2.685321139650804</v>
@@ -27338,7 +27335,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27352,7 +27349,7 @@
         <v>2.190845625202192</v>
       </c>
       <c r="D520" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E520">
         <v>2.57889032184732</v>
@@ -27388,7 +27385,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27402,7 +27399,7 @@
         <v>3.108090425020327</v>
       </c>
       <c r="D521" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E521">
         <v>2.569601341249092</v>
@@ -27438,7 +27435,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27452,7 +27449,7 @@
         <v>2.988712566996877</v>
       </c>
       <c r="D522" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E522">
         <v>2.569601341249092</v>
@@ -27488,7 +27485,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27502,7 +27499,7 @@
         <v>2.151298027264343</v>
       </c>
       <c r="D523" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E523">
         <v>2.530895664155756</v>
@@ -27538,7 +27535,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27552,10 +27549,10 @@
         <v>3.056640151974971</v>
       </c>
       <c r="D524" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E524">
-        <v>2.475624011023295</v>
+        <v>2.524678341649788</v>
       </c>
       <c r="F524">
         <v>-1</v>
@@ -27564,10 +27561,10 @@
         <v>0.00318335984802503</v>
       </c>
       <c r="H524">
-        <v>0.002584375988976704</v>
+        <v>0.002635321658350212</v>
       </c>
       <c r="I524">
-        <v>0.5810161409516752</v>
+        <v>0.5319618103251829</v>
       </c>
       <c r="J524">
         <v>0.04728346867539508</v>
@@ -27579,16 +27576,16 @@
         <v>3.12</v>
       </c>
       <c r="M524">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N524">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O524">
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27602,10 +27599,10 @@
         <v>2.939949994782248</v>
       </c>
       <c r="D525" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E525">
-        <v>2.475624011023295</v>
+        <v>2.524678341649788</v>
       </c>
       <c r="F525">
         <v>-1</v>
@@ -27614,10 +27611,10 @@
         <v>0.003060050005217752</v>
       </c>
       <c r="H525">
-        <v>0.002584375988976704</v>
+        <v>0.002635321658350212</v>
       </c>
       <c r="I525">
-        <v>0.4643259837589526</v>
+        <v>0.4152716531324603</v>
       </c>
       <c r="J525">
         <v>0.04728346867539508</v>
@@ -27629,16 +27626,16 @@
         <v>3</v>
       </c>
       <c r="M525">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N525">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O525">
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27652,7 +27649,7 @@
         <v>2.129744886456478</v>
       </c>
       <c r="D526" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E526">
         <v>2.504738939874366</v>
@@ -27688,7 +27685,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27702,10 +27699,10 @@
         <v>3.02860014354532</v>
       </c>
       <c r="D527" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E527">
-        <v>2.451559824684416</v>
+        <v>2.500195647722407</v>
       </c>
       <c r="F527">
         <v>-1</v>
@@ -27714,10 +27711,10 @@
         <v>0.00321139985645468</v>
       </c>
       <c r="H527">
-        <v>0.002608440175315583</v>
+        <v>0.002659804352277594</v>
       </c>
       <c r="I527">
-        <v>0.5770403188609037</v>
+        <v>0.5284044958229135</v>
       </c>
       <c r="J527">
         <v>0.06820884810050738</v>
@@ -27729,16 +27726,16 @@
         <v>3.12</v>
       </c>
       <c r="M527">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N527">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O527">
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27752,10 +27749,10 @@
         <v>2.913374762912356</v>
       </c>
       <c r="D528" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E528">
-        <v>2.451559824684416</v>
+        <v>2.500195647722407</v>
       </c>
       <c r="F528">
         <v>-1</v>
@@ -27764,10 +27761,10 @@
         <v>0.003086625237087645</v>
       </c>
       <c r="H528">
-        <v>0.002608440175315583</v>
+        <v>0.002659804352277594</v>
       </c>
       <c r="I528">
-        <v>0.4618149382279393</v>
+        <v>0.4131791151899491</v>
       </c>
       <c r="J528">
         <v>0.06820884810050738</v>
@@ -27779,16 +27776,16 @@
         <v>3</v>
       </c>
       <c r="M528">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N528">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O528">
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27802,7 +27799,7 @@
         <v>2.123592991344732</v>
       </c>
       <c r="D529" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E529">
         <v>2.497273047748461</v>
@@ -27838,7 +27835,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27852,7 +27849,7 @@
         <v>3.020596707186351</v>
       </c>
       <c r="D530" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E530">
         <v>2.49320757269256</v>
@@ -27888,7 +27885,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27902,7 +27899,7 @@
         <v>2.905789416512437</v>
       </c>
       <c r="D531" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E531">
         <v>2.49320757269256</v>
@@ -27938,7 +27935,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -27952,7 +27949,7 @@
         <v>2.162997802089755</v>
       </c>
       <c r="D532" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E532">
         <v>2.545094420011838</v>
@@ -27988,7 +27985,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28002,7 +27999,7 @@
         <v>3.071861218252691</v>
       </c>
       <c r="D533" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E533">
         <v>2.537968377131081</v>
@@ -28038,7 +28035,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28052,7 +28049,7 @@
         <v>2.954375930732028</v>
       </c>
       <c r="D534" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E534">
         <v>2.537968377131081</v>
@@ -28088,7 +28085,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28102,10 +28099,10 @@
         <v>2.152181822645585</v>
       </c>
       <c r="D535" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E535">
-        <v>2.531968231366001</v>
+        <v>2.583360993813217</v>
       </c>
       <c r="F535">
         <v>1</v>
@@ -28114,10 +28111,10 @@
         <v>0.002247818177354416</v>
       </c>
       <c r="H535">
-        <v>0.002648031768633999</v>
+        <v>0.002696639006186784</v>
       </c>
       <c r="I535">
-        <v>0.3797864087204159</v>
+        <v>0.4311791711676323</v>
       </c>
       <c r="J535">
         <v>0.04642541490719935</v>
@@ -28129,16 +28126,16 @@
         <v>2.2</v>
       </c>
       <c r="M535">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="N535">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="O535">
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28152,7 +28149,7 @@
         <v>3.057789944024353</v>
       </c>
       <c r="D536" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E536">
         <v>2.525682264558577</v>
@@ -28188,7 +28185,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28202,7 +28199,7 @@
         <v>2.941039723067857</v>
       </c>
       <c r="D537" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E537">
         <v>2.525682264558577</v>
@@ -28238,7 +28235,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28252,7 +28249,7 @@
         <v>2.132867933343715</v>
       </c>
       <c r="D538" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E538">
         <v>2.560484348232362</v>
@@ -28288,7 +28285,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28302,7 +28299,7 @@
         <v>3.032663136583086</v>
       </c>
       <c r="D539" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E539">
         <v>2.50374318641956</v>
@@ -28338,7 +28335,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28352,7 +28349,7 @@
         <v>2.917225510045163</v>
       </c>
       <c r="D540" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E540">
         <v>2.50374318641956</v>
@@ -28388,7 +28385,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28396,13 +28393,13 @@
         <v>0</v>
       </c>
       <c r="B541" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C541">
-        <v>2.104641124313295</v>
+        <v>2.134641124313295</v>
       </c>
       <c r="D541" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E541">
         <v>2.527050652099242</v>
@@ -28411,13 +28408,13 @@
         <v>1</v>
       </c>
       <c r="G541">
-        <v>0.002295358875686706</v>
+        <v>0.002325358875686705</v>
       </c>
       <c r="H541">
         <v>0.002752949347900758</v>
       </c>
       <c r="I541">
-        <v>0.4224095277859474</v>
+        <v>0.3924095277859476</v>
       </c>
       <c r="J541">
         <v>0.09258143270553931</v>
@@ -28426,7 +28423,7 @@
         <v>1.03</v>
       </c>
       <c r="L541">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="M541">
         <v>1.22</v>
@@ -28438,7 +28435,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28452,7 +28449,7 @@
         <v>2.995940880174577</v>
       </c>
       <c r="D542" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E542">
         <v>2.471679723734519</v>
@@ -28488,7 +28485,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28502,7 +28499,7 @@
         <v>2.882421580463965</v>
       </c>
       <c r="D543" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E543">
         <v>2.471679723734519</v>
@@ -28538,7 +28535,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28552,7 +28549,7 @@
         <v>2.127453766817889</v>
       </c>
       <c r="D544" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E544">
         <v>2.518537471376529</v>
@@ -28588,7 +28585,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28602,7 +28599,7 @@
         <v>2.986590337413564</v>
       </c>
       <c r="D545" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E545">
         <v>2.463515443861097</v>
@@ -28638,7 +28635,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28652,7 +28649,7 @@
         <v>2.87355949889196</v>
       </c>
       <c r="D546" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E546">
         <v>2.463515443861097</v>
@@ -28688,7 +28685,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28696,13 +28693,13 @@
         <v>0</v>
       </c>
       <c r="B547" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C547">
-        <v>2.119309945208395</v>
+        <v>2.12608596303</v>
       </c>
       <c r="D547" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E547">
         <v>2.508891391411886</v>
@@ -28711,22 +28708,22 @@
         <v>1</v>
       </c>
       <c r="G547">
-        <v>0.002340690054791605</v>
+        <v>0.002353914036970001</v>
       </c>
       <c r="H547">
         <v>0.002771108608588114</v>
       </c>
       <c r="I547">
-        <v>0.3895814462034908</v>
+        <v>0.3828054283818867</v>
       </c>
       <c r="J547">
         <v>0.1074660726132081</v>
       </c>
       <c r="K547">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="L547">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="M547">
         <v>1.22</v>
@@ -28738,7 +28735,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28746,49 +28743,49 @@
         <v>1</v>
       </c>
       <c r="B548" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C548">
-        <v>2.12608596303</v>
+        <v>2.975995462698301</v>
       </c>
       <c r="D548" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E548">
-        <v>2.508891391411886</v>
+        <v>2.454264695042546</v>
       </c>
       <c r="F548">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G548">
-        <v>0.002353914036970001</v>
+        <v>0.003264004537301699</v>
       </c>
       <c r="H548">
-        <v>0.002771108608588114</v>
+        <v>0.002705735304957454</v>
       </c>
       <c r="I548">
-        <v>0.3828054283818867</v>
+        <v>0.5217307676557548</v>
       </c>
       <c r="J548">
         <v>0.1074660726132081</v>
       </c>
       <c r="K548">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="L548">
-        <v>2.24</v>
+        <v>3.12</v>
       </c>
       <c r="M548">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N548">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28796,13 +28793,13 @@
         <v>2</v>
       </c>
       <c r="B549" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C549">
-        <v>2.975995462698301</v>
+        <v>2.863518087781226</v>
       </c>
       <c r="D549" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E549">
         <v>2.454264695042546</v>
@@ -28811,22 +28808,22 @@
         <v>-1</v>
       </c>
       <c r="G549">
-        <v>0.003264004537301699</v>
+        <v>0.003136481912218774</v>
       </c>
       <c r="H549">
         <v>0.002705735304957454</v>
       </c>
       <c r="I549">
-        <v>0.5217307676557548</v>
+        <v>0.4092533927386794</v>
       </c>
       <c r="J549">
         <v>0.1074660726132081</v>
       </c>
       <c r="K549">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L549">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M549">
         <v>1.17</v>
@@ -28838,51 +28835,51 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="550" spans="1:16">
       <c r="A550" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B550" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C550">
-        <v>2.863518087781226</v>
+        <v>2.131023582128605</v>
       </c>
       <c r="D550" t="s">
         <v>132</v>
       </c>
       <c r="E550">
-        <v>2.454264695042546</v>
+        <v>2.514574311506508</v>
       </c>
       <c r="F550">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G550">
-        <v>0.003136481912218774</v>
+        <v>0.002348976417871395</v>
       </c>
       <c r="H550">
-        <v>0.002705735304957454</v>
+        <v>0.002765425688493492</v>
       </c>
       <c r="I550">
-        <v>0.4092533927386794</v>
+        <v>0.3835507293779026</v>
       </c>
       <c r="J550">
-        <v>0.1074660726132081</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K550">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="L550">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="M550">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N550">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O550">
         <v>1</v>
@@ -28893,66 +28890,66 @@
     </row>
     <row r="551" spans="1:16">
       <c r="A551" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B551" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C551">
-        <v>2.131023582128605</v>
+        <v>2.982237358539935</v>
       </c>
       <c r="D551" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E551">
-        <v>2.514574311506508</v>
+        <v>2.459714708575913</v>
       </c>
       <c r="F551">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G551">
-        <v>0.002348976417871395</v>
+        <v>0.003257762641460066</v>
       </c>
       <c r="H551">
-        <v>0.002765425688493492</v>
+        <v>0.002700285291424087</v>
       </c>
       <c r="I551">
-        <v>0.3835507293779026</v>
+        <v>0.5225226499640216</v>
       </c>
       <c r="J551">
         <v>0.1028079413881086</v>
       </c>
       <c r="K551">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="L551">
-        <v>2.24</v>
+        <v>3.12</v>
       </c>
       <c r="M551">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N551">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="552" spans="1:16">
       <c r="A552" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B552" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C552">
-        <v>2.982237358539935</v>
+        <v>2.869433914437102</v>
       </c>
       <c r="D552" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E552">
         <v>2.459714708575913</v>
@@ -28961,22 +28958,22 @@
         <v>-1</v>
       </c>
       <c r="G552">
-        <v>0.003257762641460066</v>
+        <v>0.003130566085562898</v>
       </c>
       <c r="H552">
         <v>0.002700285291424087</v>
       </c>
       <c r="I552">
-        <v>0.5225226499640216</v>
+        <v>0.4097192058611889</v>
       </c>
       <c r="J552">
         <v>0.1028079413881086</v>
       </c>
       <c r="K552">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L552">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M552">
         <v>1.17</v>
@@ -28988,45 +28985,45 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="553" spans="1:16">
       <c r="A553" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B553" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C553">
-        <v>2.869433914437102</v>
+        <v>2.970054254577281</v>
       </c>
       <c r="D553" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E553">
-        <v>2.459714708575913</v>
+        <v>2.449077222280164</v>
       </c>
       <c r="F553">
         <v>-1</v>
       </c>
       <c r="G553">
-        <v>0.003130566085562898</v>
+        <v>0.003269945745422719</v>
       </c>
       <c r="H553">
-        <v>0.002700285291424087</v>
+        <v>0.002710922777719837</v>
       </c>
       <c r="I553">
-        <v>0.4097192058611889</v>
+        <v>0.5209770322971177</v>
       </c>
       <c r="J553">
-        <v>0.1028079413881086</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K553">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L553">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M553">
         <v>1.17</v>
@@ -29038,21 +29035,21 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>333</v>
+        <v>55</v>
       </c>
     </row>
     <row r="554" spans="1:16">
       <c r="A554" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B554" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C554">
-        <v>2.970054254577281</v>
+        <v>2.857887241278468</v>
       </c>
       <c r="D554" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E554">
         <v>2.449077222280164</v>
@@ -29061,22 +29058,22 @@
         <v>-1</v>
       </c>
       <c r="G554">
-        <v>0.003269945745422719</v>
+        <v>0.003142112758721532</v>
       </c>
       <c r="H554">
         <v>0.002710922777719837</v>
       </c>
       <c r="I554">
-        <v>0.5209770322971177</v>
+        <v>0.4088100189983046</v>
       </c>
       <c r="J554">
         <v>0.1118998100169543</v>
       </c>
       <c r="K554">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L554">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M554">
         <v>1.17</v>
@@ -29093,40 +29090,40 @@
     </row>
     <row r="555" spans="1:16">
       <c r="A555" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B555" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C555">
-        <v>2.857887241278468</v>
+        <v>2.944089643772313</v>
       </c>
       <c r="D555" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E555">
-        <v>2.449077222280164</v>
+        <v>2.426406629263886</v>
       </c>
       <c r="F555">
         <v>-1</v>
       </c>
       <c r="G555">
-        <v>0.003142112758721532</v>
+        <v>0.003295910356227687</v>
       </c>
       <c r="H555">
-        <v>0.002710922777719837</v>
+        <v>0.002733593370736115</v>
       </c>
       <c r="I555">
-        <v>0.4088100189983046</v>
+        <v>0.5176830145084277</v>
       </c>
       <c r="J555">
-        <v>0.1118998100169543</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K555">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L555">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M555">
         <v>1.17</v>
@@ -29138,21 +29135,21 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="556" spans="1:16">
       <c r="A556" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B556" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C556">
-        <v>2.944089643772313</v>
+        <v>2.833278990739431</v>
       </c>
       <c r="D556" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E556">
         <v>2.426406629263886</v>
@@ -29161,22 +29158,22 @@
         <v>-1</v>
       </c>
       <c r="G556">
-        <v>0.003295910356227687</v>
+        <v>0.003166721009260569</v>
       </c>
       <c r="H556">
         <v>0.002733593370736115</v>
       </c>
       <c r="I556">
-        <v>0.5176830145084277</v>
+        <v>0.4068723614755454</v>
       </c>
       <c r="J556">
         <v>0.1312763852445424</v>
       </c>
       <c r="K556">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L556">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M556">
         <v>1.17</v>
@@ -29193,40 +29190,40 @@
     </row>
     <row r="557" spans="1:16">
       <c r="A557" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B557" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C557">
-        <v>2.833278990739431</v>
+        <v>2.897401147650162</v>
       </c>
       <c r="D557" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E557">
-        <v>2.426406629263886</v>
+        <v>2.385641300560216</v>
       </c>
       <c r="F557">
         <v>-1</v>
       </c>
       <c r="G557">
-        <v>0.003166721009260569</v>
+        <v>0.003342598852349839</v>
       </c>
       <c r="H557">
-        <v>0.002733593370736115</v>
+        <v>0.002774358699439784</v>
       </c>
       <c r="I557">
-        <v>0.4068723614755454</v>
+        <v>0.5117598470899458</v>
       </c>
       <c r="J557">
-        <v>0.1312763852445424</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K557">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L557">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M557">
         <v>1.17</v>
@@ -29238,21 +29235,21 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>54</v>
+        <v>333</v>
       </c>
     </row>
     <row r="558" spans="1:16">
       <c r="A558" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B558" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C558">
-        <v>2.897401147650162</v>
+        <v>2.789029445907243</v>
       </c>
       <c r="D558" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E558">
         <v>2.385641300560216</v>
@@ -29261,22 +29258,22 @@
         <v>-1</v>
       </c>
       <c r="G558">
-        <v>0.003342598852349839</v>
+        <v>0.003210970554092757</v>
       </c>
       <c r="H558">
         <v>0.002774358699439784</v>
       </c>
       <c r="I558">
-        <v>0.5117598470899458</v>
+        <v>0.4033881453470269</v>
       </c>
       <c r="J558">
         <v>0.16611854652973</v>
       </c>
       <c r="K558">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L558">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M558">
         <v>1.17</v>
@@ -29288,45 +29285,45 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="559" spans="1:16">
       <c r="A559" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B559" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C559">
-        <v>2.789029445907243</v>
+        <v>2.834385584744631</v>
       </c>
       <c r="D559" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E559">
-        <v>2.385641300560216</v>
+        <v>2.330620249366581</v>
       </c>
       <c r="F559">
         <v>-1</v>
       </c>
       <c r="G559">
-        <v>0.003210970554092757</v>
+        <v>0.003405614415255369</v>
       </c>
       <c r="H559">
-        <v>0.002774358699439784</v>
+        <v>0.002829379750633419</v>
       </c>
       <c r="I559">
-        <v>0.4033881453470269</v>
+        <v>0.5037653353780502</v>
       </c>
       <c r="J559">
-        <v>0.16611854652973</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K559">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L559">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M559">
         <v>1.17</v>
@@ -29343,16 +29340,16 @@
     </row>
     <row r="560" spans="1:16">
       <c r="A560" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B560" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C560">
-        <v>2.834385584744631</v>
+        <v>2.729305740765434</v>
       </c>
       <c r="D560" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E560">
         <v>2.330620249366581</v>
@@ -29361,22 +29358,22 @@
         <v>-1</v>
       </c>
       <c r="G560">
-        <v>0.003405614415255369</v>
+        <v>0.003270694259234566</v>
       </c>
       <c r="H560">
         <v>0.002829379750633419</v>
       </c>
       <c r="I560">
-        <v>0.5037653353780502</v>
+        <v>0.3986854913988531</v>
       </c>
       <c r="J560">
         <v>0.2131450860114693</v>
       </c>
       <c r="K560">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L560">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M560">
         <v>1.17</v>
@@ -29388,101 +29385,101 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="561" spans="1:16">
       <c r="A561" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B561" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C561">
-        <v>2.729305740765434</v>
+        <v>2.710585509297514</v>
       </c>
       <c r="D561" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E561">
-        <v>2.330620249366581</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="F561">
         <v>-1</v>
       </c>
       <c r="G561">
-        <v>0.003270694259234566</v>
+        <v>0.003529414490702487</v>
       </c>
       <c r="H561">
-        <v>0.002829379750633419</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="I561">
-        <v>0.3986854913988531</v>
+        <v>-0.05138732414117442</v>
       </c>
       <c r="J561">
-        <v>0.2131450860114693</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K561">
+        <v>1.34</v>
+      </c>
+      <c r="L561">
+        <v>3.12</v>
+      </c>
+      <c r="M561">
         <v>1.27</v>
       </c>
-      <c r="L561">
-        <v>3</v>
-      </c>
-      <c r="M561">
-        <v>1.17</v>
-      </c>
       <c r="N561">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O561">
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>335</v>
+        <v>56</v>
       </c>
     </row>
     <row r="562" spans="1:16">
       <c r="A562" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B562" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C562">
-        <v>2.710585509297514</v>
+        <v>2.611972833438688</v>
       </c>
       <c r="D562" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E562">
-        <v>2.761972833438688</v>
+        <v>2.222526153640366</v>
       </c>
       <c r="F562">
         <v>-1</v>
       </c>
       <c r="G562">
-        <v>0.003529414490702487</v>
+        <v>0.003388027166561312</v>
       </c>
       <c r="H562">
-        <v>0.003538027166561312</v>
+        <v>0.002937473846359634</v>
       </c>
       <c r="I562">
-        <v>-0.05138732414117442</v>
+        <v>0.389446679798322</v>
       </c>
       <c r="J562">
         <v>0.3055332020167811</v>
       </c>
       <c r="K562">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L562">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M562">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N562">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O562">
         <v>1</v>
@@ -29493,146 +29490,146 @@
     </row>
     <row r="563" spans="1:16">
       <c r="A563" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B563" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C563">
-        <v>2.611972833438688</v>
+        <v>2.647551728558422</v>
       </c>
       <c r="D563" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E563">
-        <v>2.222526153640366</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="F563">
         <v>-1</v>
       </c>
       <c r="G563">
-        <v>0.003388027166561312</v>
+        <v>0.003592448271441579</v>
       </c>
       <c r="H563">
-        <v>0.002937473846359634</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="I563">
-        <v>0.389446679798322</v>
+        <v>-0.05468013358276913</v>
       </c>
       <c r="J563">
-        <v>0.3055332020167811</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K563">
+        <v>1.34</v>
+      </c>
+      <c r="L563">
+        <v>3.12</v>
+      </c>
+      <c r="M563">
         <v>1.27</v>
       </c>
-      <c r="L563">
-        <v>3</v>
-      </c>
-      <c r="M563">
-        <v>1.17</v>
-      </c>
       <c r="N563">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O563">
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>56</v>
+        <v>335</v>
       </c>
     </row>
     <row r="564" spans="1:16">
       <c r="A564" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B564" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C564">
-        <v>2.647551728558422</v>
+        <v>2.552231862141191</v>
       </c>
       <c r="D564" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E564">
-        <v>2.702231862141191</v>
+        <v>2.167489195830861</v>
       </c>
       <c r="F564">
         <v>-1</v>
       </c>
       <c r="G564">
-        <v>0.003592448271441579</v>
+        <v>0.003447768137858809</v>
       </c>
       <c r="H564">
-        <v>0.003597768137858809</v>
+        <v>0.00299251080416914</v>
       </c>
       <c r="I564">
-        <v>-0.05468013358276913</v>
+        <v>0.3847426663103302</v>
       </c>
       <c r="J564">
         <v>0.3525733368967002</v>
       </c>
       <c r="K564">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L564">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M564">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N564">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O564">
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="565" spans="1:16">
       <c r="A565" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B565" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C565">
-        <v>2.552231862141191</v>
+        <v>1.858962462723951</v>
       </c>
       <c r="D565" t="s">
         <v>132</v>
       </c>
       <c r="E565">
-        <v>2.167489195830861</v>
+        <v>2.165632934933811</v>
       </c>
       <c r="F565">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G565">
-        <v>0.003447768137858809</v>
+        <v>0.002761037537276049</v>
       </c>
       <c r="H565">
-        <v>0.00299251080416914</v>
+        <v>0.00311436706506619</v>
       </c>
       <c r="I565">
-        <v>0.3847426663103302</v>
+        <v>0.3066704722098597</v>
       </c>
       <c r="J565">
-        <v>0.3525733368967002</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K565">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="L565">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M565">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N565">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O565">
         <v>1</v>
@@ -29643,146 +29640,146 @@
     </row>
     <row r="566" spans="1:16">
       <c r="A566" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B566" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C566">
-        <v>1.858962462723951</v>
+        <v>2.59897387935353</v>
       </c>
       <c r="D566" t="s">
         <v>133</v>
       </c>
       <c r="E566">
-        <v>2.165632934933811</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="F566">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G566">
-        <v>0.002761037537276049</v>
+        <v>0.003641026120646471</v>
       </c>
       <c r="H566">
-        <v>0.00311436706506619</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="I566">
-        <v>0.3066704722098597</v>
+        <v>-0.05721778242183051</v>
       </c>
       <c r="J566">
         <v>0.3888254631690077</v>
       </c>
       <c r="K566">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="L566">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="M566">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="N566">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="O566">
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="567" spans="1:16">
       <c r="A567" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B567" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C567">
-        <v>2.59897387935353</v>
+        <v>2.50619166177536</v>
       </c>
       <c r="D567" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E567">
-        <v>2.65619166177536</v>
+        <v>2.125074208092261</v>
       </c>
       <c r="F567">
         <v>-1</v>
       </c>
       <c r="G567">
-        <v>0.003641026120646471</v>
+        <v>0.00349380833822464</v>
       </c>
       <c r="H567">
-        <v>0.00364380833822464</v>
+        <v>0.003034925791907739</v>
       </c>
       <c r="I567">
-        <v>-0.05721778242183051</v>
+        <v>0.3811174536830992</v>
       </c>
       <c r="J567">
         <v>0.3888254631690077</v>
       </c>
       <c r="K567">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L567">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M567">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N567">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O567">
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="568" spans="1:16">
       <c r="A568" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B568" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C568">
-        <v>2.50619166177536</v>
+        <v>1.838291711302243</v>
       </c>
       <c r="D568" t="s">
         <v>132</v>
       </c>
       <c r="E568">
-        <v>2.125074208092261</v>
+        <v>2.143893006714428</v>
       </c>
       <c r="F568">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G568">
-        <v>0.00349380833822464</v>
+        <v>0.002781708288697757</v>
       </c>
       <c r="H568">
-        <v>0.003034925791907739</v>
+        <v>0.003136106993285572</v>
       </c>
       <c r="I568">
-        <v>0.3811174536830992</v>
+        <v>0.3056012954121849</v>
       </c>
       <c r="J568">
-        <v>0.3888254631690077</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K568">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="L568">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M568">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N568">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O568">
         <v>1</v>
@@ -29793,146 +29790,146 @@
     </row>
     <row r="569" spans="1:16">
       <c r="A569" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B569" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C569">
-        <v>1.838291711302243</v>
+        <v>2.575095597538799</v>
       </c>
       <c r="D569" t="s">
         <v>133</v>
       </c>
       <c r="E569">
-        <v>2.143893006714428</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="F569">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G569">
-        <v>0.002781708288697757</v>
+        <v>0.003664904402461202</v>
       </c>
       <c r="H569">
-        <v>0.003136106993285572</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="I569">
-        <v>0.3056012954121849</v>
+        <v>-0.05846515535245045</v>
       </c>
       <c r="J569">
         <v>0.4066450764635833</v>
       </c>
       <c r="K569">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="L569">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="M569">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="N569">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="O569">
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="570" spans="1:16">
       <c r="A570" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B570" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C570">
-        <v>2.575095597538799</v>
+        <v>2.483560752891249</v>
       </c>
       <c r="D570" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E570">
-        <v>2.633560752891249</v>
+        <v>2.104225260537608</v>
       </c>
       <c r="F570">
         <v>-1</v>
       </c>
       <c r="G570">
-        <v>0.003664904402461202</v>
+        <v>0.003516439247108751</v>
       </c>
       <c r="H570">
-        <v>0.003666439247108751</v>
+        <v>0.003055774739462393</v>
       </c>
       <c r="I570">
-        <v>-0.05846515535245045</v>
+        <v>0.3793354923536416</v>
       </c>
       <c r="J570">
         <v>0.4066450764635833</v>
       </c>
       <c r="K570">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L570">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M570">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N570">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O570">
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="571" spans="1:16">
       <c r="A571" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B571" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C571">
-        <v>2.483560752891249</v>
+        <v>1.784876857591519</v>
       </c>
       <c r="D571" t="s">
         <v>132</v>
       </c>
       <c r="E571">
-        <v>2.104225260537608</v>
+        <v>2.087715315742805</v>
       </c>
       <c r="F571">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G571">
-        <v>0.003516439247108751</v>
+        <v>0.002835123142408481</v>
       </c>
       <c r="H571">
-        <v>0.003055774739462393</v>
+        <v>0.003192284684257196</v>
       </c>
       <c r="I571">
-        <v>0.3793354923536416</v>
+        <v>0.3028384581512857</v>
       </c>
       <c r="J571">
-        <v>0.4066450764635833</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K571">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="L571">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M571">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N571">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O571">
         <v>1</v>
@@ -29943,251 +29940,201 @@
     </row>
     <row r="572" spans="1:16">
       <c r="A572" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B572" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C572">
-        <v>1.784876857591519</v>
+        <v>2.513392232045375</v>
       </c>
       <c r="D572" t="s">
         <v>133</v>
       </c>
       <c r="E572">
-        <v>2.087715315742805</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="F572">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G572">
-        <v>0.002835123142408481</v>
+        <v>0.003726607767954625</v>
       </c>
       <c r="H572">
-        <v>0.003192284684257196</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="I572">
-        <v>0.3028384581512857</v>
+        <v>-0.0616884654901666</v>
       </c>
       <c r="J572">
         <v>0.4526923641452424</v>
       </c>
       <c r="K572">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="L572">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="M572">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="N572">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="O572">
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="573" spans="1:16">
       <c r="A573" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B573" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C573">
-        <v>2.513392232045375</v>
+        <v>2.425080697535542</v>
       </c>
       <c r="D573" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E573">
-        <v>2.575080697535542</v>
+        <v>2.050349933950066</v>
       </c>
       <c r="F573">
         <v>-1</v>
       </c>
       <c r="G573">
-        <v>0.003726607767954625</v>
+        <v>0.003574919302464458</v>
       </c>
       <c r="H573">
-        <v>0.003724919302464458</v>
+        <v>0.003109650066049934</v>
       </c>
       <c r="I573">
-        <v>-0.0616884654901666</v>
+        <v>0.3747307635854757</v>
       </c>
       <c r="J573">
         <v>0.4526923641452424</v>
       </c>
       <c r="K573">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L573">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M573">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N573">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O573">
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="574" spans="1:16">
       <c r="A574" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B574" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C574">
-        <v>2.425080697535542</v>
+        <v>2.46037019732591</v>
       </c>
       <c r="D574" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E574">
-        <v>2.050349933950066</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="F574">
         <v>-1</v>
       </c>
       <c r="G574">
-        <v>0.003574919302464458</v>
+        <v>0.00377962980267409</v>
       </c>
       <c r="H574">
-        <v>0.003109650066049934</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="I574">
-        <v>0.3747307635854757</v>
+        <v>-0.0644582732740191</v>
       </c>
       <c r="J574">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K574">
+        <v>1.34</v>
+      </c>
+      <c r="L574">
+        <v>3.12</v>
+      </c>
+      <c r="M574">
         <v>1.27</v>
       </c>
-      <c r="L574">
-        <v>3</v>
-      </c>
-      <c r="M574">
-        <v>1.17</v>
-      </c>
       <c r="N574">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O574">
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>339</v>
+        <v>57</v>
       </c>
     </row>
     <row r="575" spans="1:16">
       <c r="A575" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B575" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C575">
-        <v>2.46037019732591</v>
+        <v>2.37482847059993</v>
       </c>
       <c r="D575" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E575">
-        <v>2.524828470599929</v>
+        <v>2.004054575277101</v>
       </c>
       <c r="F575">
         <v>-1</v>
       </c>
       <c r="G575">
-        <v>0.00377962980267409</v>
+        <v>0.003625171529400071</v>
       </c>
       <c r="H575">
-        <v>0.003775171529400071</v>
+        <v>0.003155945424722899</v>
       </c>
       <c r="I575">
-        <v>-0.0644582732740191</v>
+        <v>0.370773895322829</v>
       </c>
       <c r="J575">
         <v>0.4922610467717091</v>
       </c>
       <c r="K575">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L575">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M575">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N575">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O575">
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="576" spans="1:16">
-      <c r="A576" s="1">
-        <v>1</v>
-      </c>
-      <c r="B576" t="s">
-        <v>53</v>
-      </c>
-      <c r="C576">
-        <v>2.37482847059993</v>
-      </c>
-      <c r="D576" t="s">
-        <v>132</v>
-      </c>
-      <c r="E576">
-        <v>2.004054575277101</v>
-      </c>
-      <c r="F576">
-        <v>-1</v>
-      </c>
-      <c r="G576">
-        <v>0.003625171529400071</v>
-      </c>
-      <c r="H576">
-        <v>0.003155945424722899</v>
-      </c>
-      <c r="I576">
-        <v>0.370773895322829</v>
-      </c>
-      <c r="J576">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K576">
-        <v>1.27</v>
-      </c>
-      <c r="L576">
-        <v>3</v>
-      </c>
-      <c r="M576">
-        <v>1.17</v>
-      </c>
-      <c r="N576">
-        <v>2.58</v>
-      </c>
-      <c r="O576">
-        <v>1</v>
-      </c>
-      <c r="P576" t="s">
         <v>57</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="339">
   <si>
     <t>trade_time</t>
   </si>
@@ -1388,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P575"/>
+  <dimension ref="A1:P577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24843,43 +24843,43 @@
         <v>0</v>
       </c>
       <c r="B470" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C470">
-        <v>3.366448540958179</v>
+        <v>2.389434326258899</v>
       </c>
       <c r="D470" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E470">
-        <v>2.741504344852168</v>
+        <v>2.819896027013226</v>
       </c>
       <c r="F470">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G470">
-        <v>0.002873551459041821</v>
+        <v>0.002010565673741102</v>
       </c>
       <c r="H470">
-        <v>0.002318495655147832</v>
+        <v>0.002360103972986773</v>
       </c>
       <c r="I470">
-        <v>0.6249441961060107</v>
+        <v>0.4304617007543277</v>
       </c>
       <c r="J470">
         <v>-0.1839168216105812</v>
       </c>
       <c r="K470">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L470">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M470">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N470">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O470">
         <v>1</v>
@@ -24893,10 +24893,10 @@
         <v>1</v>
       </c>
       <c r="B471" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C471">
-        <v>3.233574363445438</v>
+        <v>3.366448540958179</v>
       </c>
       <c r="D471" t="s">
         <v>129</v>
@@ -24908,22 +24908,22 @@
         <v>-1</v>
       </c>
       <c r="G471">
-        <v>0.002766425636554562</v>
+        <v>0.002873551459041821</v>
       </c>
       <c r="H471">
         <v>0.002318495655147832</v>
       </c>
       <c r="I471">
-        <v>0.49207001859327</v>
+        <v>0.6249441961060107</v>
       </c>
       <c r="J471">
         <v>-0.1839168216105812</v>
       </c>
       <c r="K471">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L471">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M471">
         <v>1.15</v>
@@ -24940,96 +24940,96 @@
     </row>
     <row r="472" spans="1:16">
       <c r="A472" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B472" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C472">
-        <v>2.407128809696355</v>
+        <v>3.233574363445438</v>
       </c>
       <c r="D472" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E472">
-        <v>2.841369914680043</v>
+        <v>2.741504344852168</v>
       </c>
       <c r="F472">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G472">
-        <v>0.001992871190303645</v>
+        <v>0.002766425636554562</v>
       </c>
       <c r="H472">
-        <v>0.002338630085319957</v>
+        <v>0.002318495655147832</v>
       </c>
       <c r="I472">
-        <v>0.4342411049836872</v>
+        <v>0.49207001859327</v>
       </c>
       <c r="J472">
-        <v>-0.2010959317440343</v>
+        <v>-0.1839168216105812</v>
       </c>
       <c r="K472">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L472">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M472">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N472">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O472">
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="473" spans="1:16">
       <c r="A473" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B473" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C473">
-        <v>3.389468548537006</v>
+        <v>2.407128809696355</v>
       </c>
       <c r="D473" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E473">
-        <v>2.761260321505639</v>
+        <v>2.841369914680043</v>
       </c>
       <c r="F473">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G473">
-        <v>0.002850531451462994</v>
+        <v>0.001992871190303645</v>
       </c>
       <c r="H473">
-        <v>0.002298739678494361</v>
+        <v>0.002338630085319957</v>
       </c>
       <c r="I473">
-        <v>0.6282082270313669</v>
+        <v>0.4342411049836872</v>
       </c>
       <c r="J473">
         <v>-0.2010959317440343</v>
       </c>
       <c r="K473">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L473">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M473">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N473">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O473">
         <v>1</v>
@@ -25040,13 +25040,13 @@
     </row>
     <row r="474" spans="1:16">
       <c r="A474" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B474" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C474">
-        <v>3.255391833314924</v>
+        <v>3.389468548537006</v>
       </c>
       <c r="D474" t="s">
         <v>129</v>
@@ -25058,22 +25058,22 @@
         <v>-1</v>
       </c>
       <c r="G474">
-        <v>0.002744608166685076</v>
+        <v>0.002850531451462994</v>
       </c>
       <c r="H474">
         <v>0.002298739678494361</v>
       </c>
       <c r="I474">
-        <v>0.4941315118092846</v>
+        <v>0.6282082270313669</v>
       </c>
       <c r="J474">
         <v>-0.2010959317440343</v>
       </c>
       <c r="K474">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L474">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M474">
         <v>1.15</v>
@@ -25090,96 +25090,96 @@
     </row>
     <row r="475" spans="1:16">
       <c r="A475" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B475" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C475">
-        <v>2.407323569166959</v>
+        <v>3.255391833314924</v>
       </c>
       <c r="D475" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E475">
-        <v>2.841606273260873</v>
+        <v>2.761260321505639</v>
       </c>
       <c r="F475">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G475">
-        <v>0.001992676430833041</v>
+        <v>0.002744608166685076</v>
       </c>
       <c r="H475">
-        <v>0.002338393726739127</v>
+        <v>0.002298739678494361</v>
       </c>
       <c r="I475">
-        <v>0.4342827040939135</v>
+        <v>0.4941315118092846</v>
       </c>
       <c r="J475">
-        <v>-0.2012850186086983</v>
+        <v>-0.2010959317440343</v>
       </c>
       <c r="K475">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L475">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M475">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N475">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O475">
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="476" spans="1:16">
       <c r="A476" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B476" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C476">
-        <v>3.389721924935656</v>
+        <v>2.407323569166959</v>
       </c>
       <c r="D476" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E476">
-        <v>2.761477771400003</v>
+        <v>2.841606273260873</v>
       </c>
       <c r="F476">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G476">
-        <v>0.002850278075064344</v>
+        <v>0.001992676430833041</v>
       </c>
       <c r="H476">
-        <v>0.002298522228599997</v>
+        <v>0.002338393726739127</v>
       </c>
       <c r="I476">
-        <v>0.6282441535356531</v>
+        <v>0.4342827040939135</v>
       </c>
       <c r="J476">
         <v>-0.2012850186086983</v>
       </c>
       <c r="K476">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L476">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M476">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N476">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O476">
         <v>1</v>
@@ -25190,13 +25190,13 @@
     </row>
     <row r="477" spans="1:16">
       <c r="A477" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B477" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C477">
-        <v>3.255631973633047</v>
+        <v>3.389721924935656</v>
       </c>
       <c r="D477" t="s">
         <v>129</v>
@@ -25208,22 +25208,22 @@
         <v>-1</v>
       </c>
       <c r="G477">
-        <v>0.002744368026366953</v>
+        <v>0.002850278075064344</v>
       </c>
       <c r="H477">
         <v>0.002298522228599997</v>
       </c>
       <c r="I477">
-        <v>0.4941542022330441</v>
+        <v>0.6282441535356531</v>
       </c>
       <c r="J477">
         <v>-0.2012850186086983</v>
       </c>
       <c r="K477">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L477">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M477">
         <v>1.15</v>
@@ -25240,96 +25240,96 @@
     </row>
     <row r="478" spans="1:16">
       <c r="A478" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B478" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C478">
-        <v>2.41122985184961</v>
+        <v>3.255631973633047</v>
       </c>
       <c r="D478" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E478">
-        <v>2.846346907584478</v>
+        <v>2.761477771400003</v>
       </c>
       <c r="F478">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G478">
-        <v>0.00198877014815039</v>
+        <v>0.002744368026366953</v>
       </c>
       <c r="H478">
-        <v>0.002333653092415522</v>
+        <v>0.002298522228599997</v>
       </c>
       <c r="I478">
-        <v>0.4351170557348678</v>
+        <v>0.4941542022330441</v>
       </c>
       <c r="J478">
-        <v>-0.2050775260675825</v>
+        <v>-0.2012850186086983</v>
       </c>
       <c r="K478">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L478">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M478">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N478">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O478">
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="479" spans="1:16">
       <c r="A479" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B479" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C479">
-        <v>3.394803884930561</v>
+        <v>2.41122985184961</v>
       </c>
       <c r="D479" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E479">
-        <v>2.76583915497772</v>
+        <v>2.846346907584478</v>
       </c>
       <c r="F479">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G479">
-        <v>0.00284519611506944</v>
+        <v>0.00198877014815039</v>
       </c>
       <c r="H479">
-        <v>0.00229416084502228</v>
+        <v>0.002333653092415522</v>
       </c>
       <c r="I479">
-        <v>0.6289647299528411</v>
+        <v>0.4351170557348678</v>
       </c>
       <c r="J479">
         <v>-0.2050775260675825</v>
       </c>
       <c r="K479">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L479">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M479">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N479">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O479">
         <v>1</v>
@@ -25340,13 +25340,13 @@
     </row>
     <row r="480" spans="1:16">
       <c r="A480" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B480" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C480">
-        <v>3.26044845810583</v>
+        <v>3.394803884930561</v>
       </c>
       <c r="D480" t="s">
         <v>129</v>
@@ -25358,22 +25358,22 @@
         <v>-1</v>
       </c>
       <c r="G480">
-        <v>0.00273955154189417</v>
+        <v>0.00284519611506944</v>
       </c>
       <c r="H480">
         <v>0.00229416084502228</v>
       </c>
       <c r="I480">
-        <v>0.4946093031281102</v>
+        <v>0.6289647299528411</v>
       </c>
       <c r="J480">
         <v>-0.2050775260675825</v>
       </c>
       <c r="K480">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L480">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M480">
         <v>1.15</v>
@@ -25390,96 +25390,96 @@
     </row>
     <row r="481" spans="1:16">
       <c r="A481" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B481" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C481">
-        <v>2.414401903996001</v>
+        <v>3.26044845810583</v>
       </c>
       <c r="D481" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E481">
-        <v>2.850196485432039</v>
+        <v>2.76583915497772</v>
       </c>
       <c r="F481">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G481">
-        <v>0.001985598096004</v>
+        <v>0.00273955154189417</v>
       </c>
       <c r="H481">
-        <v>0.00232980351456796</v>
+        <v>0.00229416084502228</v>
       </c>
       <c r="I481">
-        <v>0.4357945814360389</v>
+        <v>0.4946093031281102</v>
       </c>
       <c r="J481">
-        <v>-0.2081571883456315</v>
+        <v>-0.2050775260675825</v>
       </c>
       <c r="K481">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L481">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M481">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N481">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O481">
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="482" spans="1:16">
       <c r="A482" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B482" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C482">
-        <v>3.398930632383146</v>
+        <v>2.414401903996001</v>
       </c>
       <c r="D482" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E482">
-        <v>2.769380766597476</v>
+        <v>2.850196485432039</v>
       </c>
       <c r="F482">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G482">
-        <v>0.002841069367616854</v>
+        <v>0.001985598096004</v>
       </c>
       <c r="H482">
-        <v>0.002290619233402524</v>
+        <v>0.00232980351456796</v>
       </c>
       <c r="I482">
-        <v>0.6295498657856702</v>
+        <v>0.4357945814360389</v>
       </c>
       <c r="J482">
         <v>-0.2081571883456315</v>
       </c>
       <c r="K482">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L482">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M482">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N482">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O482">
         <v>1</v>
@@ -25490,13 +25490,13 @@
     </row>
     <row r="483" spans="1:16">
       <c r="A483" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B483" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C483">
-        <v>3.264359629198952</v>
+        <v>3.398930632383146</v>
       </c>
       <c r="D483" t="s">
         <v>129</v>
@@ -25508,22 +25508,22 @@
         <v>-1</v>
       </c>
       <c r="G483">
-        <v>0.002735640370801048</v>
+        <v>0.002841069367616854</v>
       </c>
       <c r="H483">
         <v>0.002290619233402524</v>
       </c>
       <c r="I483">
-        <v>0.4949788626014757</v>
+        <v>0.6295498657856702</v>
       </c>
       <c r="J483">
         <v>-0.2081571883456315</v>
       </c>
       <c r="K483">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L483">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M483">
         <v>1.15</v>
@@ -25540,96 +25540,96 @@
     </row>
     <row r="484" spans="1:16">
       <c r="A484" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B484" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C484">
-        <v>2.400941737549309</v>
+        <v>3.264359629198952</v>
       </c>
       <c r="D484" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E484">
-        <v>2.833861331977317</v>
+        <v>2.769380766597476</v>
       </c>
       <c r="F484">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G484">
-        <v>0.001999058262450691</v>
+        <v>0.002735640370801048</v>
       </c>
       <c r="H484">
-        <v>0.002346138668022683</v>
+        <v>0.002290619233402524</v>
       </c>
       <c r="I484">
-        <v>0.4329195944280078</v>
+        <v>0.4949788626014757</v>
       </c>
       <c r="J484">
-        <v>-0.1950890655818535</v>
+        <v>-0.2081571883456315</v>
       </c>
       <c r="K484">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L484">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M484">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N484">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O484">
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="485" spans="1:16">
       <c r="A485" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B485" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C485">
-        <v>3.381419347879684</v>
+        <v>2.400941737549309</v>
       </c>
       <c r="D485" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E485">
-        <v>2.754352425419131</v>
+        <v>2.833861331977317</v>
       </c>
       <c r="F485">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G485">
-        <v>0.002858580652120316</v>
+        <v>0.001999058262450691</v>
       </c>
       <c r="H485">
-        <v>0.002305647574580868</v>
+        <v>0.002346138668022683</v>
       </c>
       <c r="I485">
-        <v>0.6270669224605525</v>
+        <v>0.4329195944280078</v>
       </c>
       <c r="J485">
         <v>-0.1950890655818535</v>
       </c>
       <c r="K485">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L485">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M485">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N485">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O485">
         <v>1</v>
@@ -25640,13 +25640,13 @@
     </row>
     <row r="486" spans="1:16">
       <c r="A486" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B486" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C486">
-        <v>3.247763113288954</v>
+        <v>3.381419347879684</v>
       </c>
       <c r="D486" t="s">
         <v>129</v>
@@ -25658,22 +25658,22 @@
         <v>-1</v>
       </c>
       <c r="G486">
-        <v>0.002752236886711046</v>
+        <v>0.002858580652120316</v>
       </c>
       <c r="H486">
         <v>0.002305647574580868</v>
       </c>
       <c r="I486">
-        <v>0.4934106878698228</v>
+        <v>0.6270669224605525</v>
       </c>
       <c r="J486">
         <v>-0.1950890655818535</v>
       </c>
       <c r="K486">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L486">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M486">
         <v>1.15</v>
@@ -25690,96 +25690,96 @@
     </row>
     <row r="487" spans="1:16">
       <c r="A487" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B487" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C487">
-        <v>2.416869377367424</v>
+        <v>3.247763113288954</v>
       </c>
       <c r="D487" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E487">
-        <v>2.853190991950757</v>
+        <v>2.754352425419131</v>
       </c>
       <c r="F487">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G487">
-        <v>0.001983130622632577</v>
+        <v>0.002752236886711046</v>
       </c>
       <c r="H487">
-        <v>0.002326809008049243</v>
+        <v>0.002305647574580868</v>
       </c>
       <c r="I487">
-        <v>0.4363216145833326</v>
+        <v>0.4934106878698228</v>
       </c>
       <c r="J487">
-        <v>-0.2105527935606056</v>
+        <v>-0.1950890655818535</v>
       </c>
       <c r="K487">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L487">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M487">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N487">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O487">
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="488" spans="1:16">
       <c r="A488" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B488" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C488">
-        <v>3.402140743371211</v>
+        <v>2.416869377367424</v>
       </c>
       <c r="D488" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E488">
-        <v>2.772135712594696</v>
+        <v>2.853190991950757</v>
       </c>
       <c r="F488">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G488">
-        <v>0.002837859256628789</v>
+        <v>0.001983130622632577</v>
       </c>
       <c r="H488">
-        <v>0.002287864287405304</v>
+        <v>0.002326809008049243</v>
       </c>
       <c r="I488">
-        <v>0.6300050307765153</v>
+        <v>0.4363216145833326</v>
       </c>
       <c r="J488">
         <v>-0.2105527935606056</v>
       </c>
       <c r="K488">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L488">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M488">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N488">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O488">
         <v>1</v>
@@ -25790,13 +25790,13 @@
     </row>
     <row r="489" spans="1:16">
       <c r="A489" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B489" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C489">
-        <v>3.267402047821969</v>
+        <v>3.402140743371211</v>
       </c>
       <c r="D489" t="s">
         <v>129</v>
@@ -25808,22 +25808,22 @@
         <v>-1</v>
       </c>
       <c r="G489">
-        <v>0.002732597952178031</v>
+        <v>0.002837859256628789</v>
       </c>
       <c r="H489">
         <v>0.002287864287405304</v>
       </c>
       <c r="I489">
-        <v>0.495266335227273</v>
+        <v>0.6300050307765153</v>
       </c>
       <c r="J489">
         <v>-0.2105527935606056</v>
       </c>
       <c r="K489">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L489">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M489">
         <v>1.15</v>
@@ -25840,96 +25840,96 @@
     </row>
     <row r="490" spans="1:16">
       <c r="A490" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B490" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C490">
-        <v>2.427926332334885</v>
+        <v>3.267402047821969</v>
       </c>
       <c r="D490" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E490">
-        <v>2.866609626620006</v>
+        <v>2.772135712594696</v>
       </c>
       <c r="F490">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G490">
-        <v>0.001972073667665115</v>
+        <v>0.002732597952178031</v>
       </c>
       <c r="H490">
-        <v>0.002313390373379994</v>
+        <v>0.002287864287405304</v>
       </c>
       <c r="I490">
-        <v>0.4386832942851204</v>
+        <v>0.495266335227273</v>
       </c>
       <c r="J490">
-        <v>-0.2212877012960047</v>
+        <v>-0.2105527935606056</v>
       </c>
       <c r="K490">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L490">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M490">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N490">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O490">
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="491" spans="1:16">
       <c r="A491" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B491" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C491">
-        <v>3.416525519736647</v>
+        <v>2.427926332334885</v>
       </c>
       <c r="D491" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E491">
-        <v>2.784480856490405</v>
+        <v>2.866609626620006</v>
       </c>
       <c r="F491">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G491">
-        <v>0.002823474480263354</v>
+        <v>0.001972073667665115</v>
       </c>
       <c r="H491">
-        <v>0.002275519143509595</v>
+        <v>0.002313390373379994</v>
       </c>
       <c r="I491">
-        <v>0.6320446632462415</v>
+        <v>0.4386832942851204</v>
       </c>
       <c r="J491">
         <v>-0.2212877012960047</v>
       </c>
       <c r="K491">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L491">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M491">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N491">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O491">
         <v>1</v>
@@ -25940,13 +25940,13 @@
     </row>
     <row r="492" spans="1:16">
       <c r="A492" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B492" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C492">
-        <v>3.281035380645926</v>
+        <v>3.416525519736647</v>
       </c>
       <c r="D492" t="s">
         <v>129</v>
@@ -25958,22 +25958,22 @@
         <v>-1</v>
       </c>
       <c r="G492">
-        <v>0.002718964619354074</v>
+        <v>0.002823474480263354</v>
       </c>
       <c r="H492">
         <v>0.002275519143509595</v>
       </c>
       <c r="I492">
-        <v>0.4965545241555209</v>
+        <v>0.6320446632462415</v>
       </c>
       <c r="J492">
         <v>-0.2212877012960047</v>
       </c>
       <c r="K492">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L492">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M492">
         <v>1.15</v>
@@ -25990,96 +25990,96 @@
     </row>
     <row r="493" spans="1:16">
       <c r="A493" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B493" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C493">
-        <v>2.43983969591803</v>
+        <v>3.281035380645926</v>
       </c>
       <c r="D493" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E493">
-        <v>2.88106759213353</v>
+        <v>2.784480856490405</v>
       </c>
       <c r="F493">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G493">
-        <v>0.001960160304081971</v>
+        <v>0.002718964619354074</v>
       </c>
       <c r="H493">
-        <v>0.002298932407866469</v>
+        <v>0.002275519143509595</v>
       </c>
       <c r="I493">
-        <v>0.441227896215501</v>
+        <v>0.4965545241555209</v>
       </c>
       <c r="J493">
-        <v>-0.2328540737068246</v>
+        <v>-0.2212877012960047</v>
       </c>
       <c r="K493">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L493">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M493">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N493">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O493">
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="494" spans="1:16">
       <c r="A494" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B494" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C494">
-        <v>3.432024458767145</v>
+        <v>2.43983969591803</v>
       </c>
       <c r="D494" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E494">
-        <v>2.797782184762848</v>
+        <v>2.88106759213353</v>
       </c>
       <c r="F494">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G494">
-        <v>0.002807975541232855</v>
+        <v>0.001960160304081971</v>
       </c>
       <c r="H494">
-        <v>0.002262217815237151</v>
+        <v>0.002298932407866469</v>
       </c>
       <c r="I494">
-        <v>0.634242274004297</v>
+        <v>0.441227896215501</v>
       </c>
       <c r="J494">
         <v>-0.2328540737068246</v>
       </c>
       <c r="K494">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L494">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M494">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N494">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O494">
         <v>1</v>
@@ -26090,13 +26090,13 @@
     </row>
     <row r="495" spans="1:16">
       <c r="A495" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B495" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C495">
-        <v>3.295724673607667</v>
+        <v>3.432024458767145</v>
       </c>
       <c r="D495" t="s">
         <v>129</v>
@@ -26108,22 +26108,22 @@
         <v>-1</v>
       </c>
       <c r="G495">
-        <v>0.002704275326392333</v>
+        <v>0.002807975541232855</v>
       </c>
       <c r="H495">
         <v>0.002262217815237151</v>
       </c>
       <c r="I495">
-        <v>0.497942488844819</v>
+        <v>0.634242274004297</v>
       </c>
       <c r="J495">
         <v>-0.2328540737068246</v>
       </c>
       <c r="K495">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L495">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M495">
         <v>1.15</v>
@@ -26140,96 +26140,96 @@
     </row>
     <row r="496" spans="1:16">
       <c r="A496" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B496" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C496">
-        <v>2.478555931094635</v>
+        <v>3.295724673607667</v>
       </c>
       <c r="D496" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E496">
-        <v>2.928053314435237</v>
+        <v>2.797782184762848</v>
       </c>
       <c r="F496">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G496">
-        <v>0.001921444068905365</v>
+        <v>0.002704275326392333</v>
       </c>
       <c r="H496">
-        <v>0.002251946685564763</v>
+        <v>0.002262217815237151</v>
       </c>
       <c r="I496">
-        <v>0.4494973833406015</v>
+        <v>0.497942488844819</v>
       </c>
       <c r="J496">
-        <v>-0.2704426515481894</v>
+        <v>-0.2328540737068246</v>
       </c>
       <c r="K496">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L496">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M496">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N496">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O496">
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="497" spans="1:16">
       <c r="A497" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B497" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C497">
-        <v>3.482393153074574</v>
+        <v>2.478555931094635</v>
       </c>
       <c r="D497" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E497">
-        <v>2.896417902311382</v>
+        <v>2.928053314435237</v>
       </c>
       <c r="F497">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G497">
-        <v>0.002757606846925426</v>
+        <v>0.001921444068905365</v>
       </c>
       <c r="H497">
-        <v>0.002263582097688619</v>
+        <v>0.002251946685564763</v>
       </c>
       <c r="I497">
-        <v>0.5859752507631923</v>
+        <v>0.4494973833406015</v>
       </c>
       <c r="J497">
         <v>-0.2704426515481894</v>
       </c>
       <c r="K497">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L497">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M497">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N497">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O497">
         <v>1</v>
@@ -26240,13 +26240,13 @@
     </row>
     <row r="498" spans="1:16">
       <c r="A498" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B498" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C498">
-        <v>3.343462167466201</v>
+        <v>3.482393153074574</v>
       </c>
       <c r="D498" t="s">
         <v>131</v>
@@ -26258,22 +26258,22 @@
         <v>-1</v>
       </c>
       <c r="G498">
-        <v>0.002656537832533799</v>
+        <v>0.002757606846925426</v>
       </c>
       <c r="H498">
         <v>0.002263582097688619</v>
       </c>
       <c r="I498">
-        <v>0.447044265154819</v>
+        <v>0.5859752507631923</v>
       </c>
       <c r="J498">
         <v>-0.2704426515481894</v>
       </c>
       <c r="K498">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L498">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M498">
         <v>1.17</v>
@@ -26290,96 +26290,96 @@
     </row>
     <row r="499" spans="1:16">
       <c r="A499" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B499" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C499">
-        <v>2.492450104171095</v>
+        <v>3.343462167466201</v>
       </c>
       <c r="D499" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E499">
-        <v>2.944915174964921</v>
+        <v>2.896417902311382</v>
       </c>
       <c r="F499">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G499">
-        <v>0.001907549895828906</v>
+        <v>0.002656537832533799</v>
       </c>
       <c r="H499">
-        <v>0.002235084825035079</v>
+        <v>0.002263582097688619</v>
       </c>
       <c r="I499">
-        <v>0.4524650707938256</v>
+        <v>0.447044265154819</v>
       </c>
       <c r="J499">
-        <v>-0.2839321399719367</v>
+        <v>-0.2704426515481894</v>
       </c>
       <c r="K499">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L499">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M499">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N499">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O499">
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="500" spans="1:16">
       <c r="A500" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B500" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C500">
-        <v>3.500469067562396</v>
+        <v>2.492450104171095</v>
       </c>
       <c r="D500" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E500">
-        <v>2.912200603767166</v>
+        <v>2.944915174964921</v>
       </c>
       <c r="F500">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G500">
-        <v>0.002739530932437605</v>
+        <v>0.001907549895828906</v>
       </c>
       <c r="H500">
-        <v>0.002247799396232834</v>
+        <v>0.002235084825035079</v>
       </c>
       <c r="I500">
-        <v>0.5882684637952296</v>
+        <v>0.4524650707938256</v>
       </c>
       <c r="J500">
         <v>-0.2839321399719367</v>
       </c>
       <c r="K500">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L500">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M500">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N500">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O500">
         <v>1</v>
@@ -26390,13 +26390,13 @@
     </row>
     <row r="501" spans="1:16">
       <c r="A501" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B501" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C501">
-        <v>3.36059381776436</v>
+        <v>3.500469067562396</v>
       </c>
       <c r="D501" t="s">
         <v>131</v>
@@ -26408,22 +26408,22 @@
         <v>-1</v>
       </c>
       <c r="G501">
-        <v>0.002639406182235641</v>
+        <v>0.002739530932437605</v>
       </c>
       <c r="H501">
         <v>0.002247799396232834</v>
       </c>
       <c r="I501">
-        <v>0.4483932139971936</v>
+        <v>0.5882684637952296</v>
       </c>
       <c r="J501">
         <v>-0.2839321399719367</v>
       </c>
       <c r="K501">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L501">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M501">
         <v>1.17</v>
@@ -26440,96 +26440,96 @@
     </row>
     <row r="502" spans="1:16">
       <c r="A502" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B502" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C502">
-        <v>2.485588290136117</v>
+        <v>3.36059381776436</v>
       </c>
       <c r="D502" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E502">
-        <v>2.936587730747715</v>
+        <v>2.912200603767166</v>
       </c>
       <c r="F502">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G502">
-        <v>0.001914411709863883</v>
+        <v>0.002639406182235641</v>
       </c>
       <c r="H502">
-        <v>0.002243412269252285</v>
+        <v>0.002247799396232834</v>
       </c>
       <c r="I502">
-        <v>0.4509994406115978</v>
+        <v>0.4483932139971936</v>
       </c>
       <c r="J502">
-        <v>-0.2772701845981717</v>
+        <v>-0.2839321399719367</v>
       </c>
       <c r="K502">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L502">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M502">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N502">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O502">
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="503" spans="1:16">
       <c r="A503" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B503" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C503">
-        <v>3.49154204736155</v>
+        <v>2.485588290136117</v>
       </c>
       <c r="D503" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E503">
-        <v>2.904406115979861</v>
+        <v>2.936587730747715</v>
       </c>
       <c r="F503">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G503">
-        <v>0.00274845795263845</v>
+        <v>0.001914411709863883</v>
       </c>
       <c r="H503">
-        <v>0.002255593884020139</v>
+        <v>0.002243412269252285</v>
       </c>
       <c r="I503">
-        <v>0.5871359313816891</v>
+        <v>0.4509994406115978</v>
       </c>
       <c r="J503">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K503">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L503">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M503">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N503">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O503">
         <v>1</v>
@@ -26540,13 +26540,13 @@
     </row>
     <row r="504" spans="1:16">
       <c r="A504" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B504" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C504">
-        <v>3.352133134439678</v>
+        <v>3.49154204736155</v>
       </c>
       <c r="D504" t="s">
         <v>131</v>
@@ -26558,22 +26558,22 @@
         <v>-1</v>
       </c>
       <c r="G504">
-        <v>0.002647866865560322</v>
+        <v>0.00274845795263845</v>
       </c>
       <c r="H504">
         <v>0.002255593884020139</v>
       </c>
       <c r="I504">
-        <v>0.4477270184598172</v>
+        <v>0.5871359313816891</v>
       </c>
       <c r="J504">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K504">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L504">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M504">
         <v>1.17</v>
@@ -26590,96 +26590,96 @@
     </row>
     <row r="505" spans="1:16">
       <c r="A505" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B505" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C505">
-        <v>2.483803138304734</v>
+        <v>3.352133134439678</v>
       </c>
       <c r="D505" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E505">
-        <v>2.934421284350405</v>
+        <v>2.904406115979861</v>
       </c>
       <c r="F505">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G505">
-        <v>0.001916196861695266</v>
+        <v>0.002647866865560322</v>
       </c>
       <c r="H505">
-        <v>0.002245578715649595</v>
+        <v>0.002255593884020139</v>
       </c>
       <c r="I505">
-        <v>0.4506181460456711</v>
+        <v>0.4477270184598172</v>
       </c>
       <c r="J505">
-        <v>-0.2755370274803244</v>
+        <v>-0.2772701845981717</v>
       </c>
       <c r="K505">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L505">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M505">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N505">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O505">
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="506" spans="1:16">
       <c r="A506" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B506" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C506">
-        <v>3.489219616823635</v>
+        <v>2.483803138304734</v>
       </c>
       <c r="D506" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E506">
-        <v>2.902378322151979</v>
+        <v>2.934421284350405</v>
       </c>
       <c r="F506">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G506">
-        <v>0.002750780383176366</v>
+        <v>0.001916196861695266</v>
       </c>
       <c r="H506">
-        <v>0.002257621677848021</v>
+        <v>0.002245578715649595</v>
       </c>
       <c r="I506">
-        <v>0.5868412946716552</v>
+        <v>0.4506181460456711</v>
       </c>
       <c r="J506">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K506">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L506">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M506">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N506">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O506">
         <v>1</v>
@@ -26690,13 +26690,13 @@
     </row>
     <row r="507" spans="1:16">
       <c r="A507" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B507" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C507">
-        <v>3.349932024900012</v>
+        <v>3.489219616823635</v>
       </c>
       <c r="D507" t="s">
         <v>131</v>
@@ -26708,22 +26708,22 @@
         <v>-1</v>
       </c>
       <c r="G507">
-        <v>0.002650067975099988</v>
+        <v>0.002750780383176366</v>
       </c>
       <c r="H507">
         <v>0.002257621677848021</v>
       </c>
       <c r="I507">
-        <v>0.4475537027480323</v>
+        <v>0.5868412946716552</v>
       </c>
       <c r="J507">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K507">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L507">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M507">
         <v>1.17</v>
@@ -26740,96 +26740,96 @@
     </row>
     <row r="508" spans="1:16">
       <c r="A508" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B508" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C508">
-        <v>2.455324757264537</v>
+        <v>3.349932024900012</v>
       </c>
       <c r="D508" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E508">
-        <v>2.899860142311331</v>
+        <v>2.902378322151979</v>
       </c>
       <c r="F508">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G508">
-        <v>0.001944675242735464</v>
+        <v>0.002650067975099988</v>
       </c>
       <c r="H508">
-        <v>0.002280139857688669</v>
+        <v>0.002257621677848021</v>
       </c>
       <c r="I508">
-        <v>0.4445353850467941</v>
+        <v>0.4475537027480323</v>
       </c>
       <c r="J508">
-        <v>-0.2478881138490649</v>
+        <v>-0.2755370274803244</v>
       </c>
       <c r="K508">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L508">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M508">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N508">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O508">
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="509" spans="1:16">
       <c r="A509" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B509" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C509">
-        <v>3.452170072557747</v>
+        <v>2.455324757264537</v>
       </c>
       <c r="D509" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E509">
-        <v>2.870029093203406</v>
+        <v>2.899860142311331</v>
       </c>
       <c r="F509">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G509">
-        <v>0.002787829927442253</v>
+        <v>0.001944675242735464</v>
       </c>
       <c r="H509">
-        <v>0.002289970906796594</v>
+        <v>0.002280139857688669</v>
       </c>
       <c r="I509">
-        <v>0.5821409793543411</v>
+        <v>0.4445353850467941</v>
       </c>
       <c r="J509">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K509">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L509">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M509">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N509">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O509">
         <v>1</v>
@@ -26840,13 +26840,13 @@
     </row>
     <row r="510" spans="1:16">
       <c r="A510" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B510" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C510">
-        <v>3.314817904588312</v>
+        <v>3.452170072557747</v>
       </c>
       <c r="D510" t="s">
         <v>131</v>
@@ -26858,22 +26858,22 @@
         <v>-1</v>
       </c>
       <c r="G510">
-        <v>0.002685182095411688</v>
+        <v>0.002787829927442253</v>
       </c>
       <c r="H510">
         <v>0.002289970906796594</v>
       </c>
       <c r="I510">
-        <v>0.4447888113849063</v>
+        <v>0.5821409793543411</v>
       </c>
       <c r="J510">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K510">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L510">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M510">
         <v>1.17</v>
@@ -26890,96 +26890,96 @@
     </row>
     <row r="511" spans="1:16">
       <c r="A511" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B511" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C511">
-        <v>2.38683909149</v>
+        <v>3.314817904588312</v>
       </c>
       <c r="D511" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E511">
-        <v>2.816746470254853</v>
+        <v>2.870029093203406</v>
       </c>
       <c r="F511">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G511">
-        <v>0.002013160908510001</v>
+        <v>0.002685182095411688</v>
       </c>
       <c r="H511">
-        <v>0.002363253529745146</v>
+        <v>0.002289970906796594</v>
       </c>
       <c r="I511">
-        <v>0.4299073787648537</v>
+        <v>0.4447888113849063</v>
       </c>
       <c r="J511">
-        <v>-0.181397176203883</v>
+        <v>-0.2478881138490649</v>
       </c>
       <c r="K511">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L511">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M511">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N511">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O511">
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="512" spans="1:16">
       <c r="A512" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B512" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C512">
-        <v>3.363072216113203</v>
+        <v>2.38683909149</v>
       </c>
       <c r="D512" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E512">
-        <v>2.792234696158543</v>
+        <v>2.816746470254853</v>
       </c>
       <c r="F512">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G512">
-        <v>0.002876927783886797</v>
+        <v>0.002013160908510001</v>
       </c>
       <c r="H512">
-        <v>0.002367765303841457</v>
+        <v>0.002363253529745146</v>
       </c>
       <c r="I512">
-        <v>0.5708375199546598</v>
+        <v>0.4299073787648537</v>
       </c>
       <c r="J512">
         <v>-0.181397176203883</v>
       </c>
       <c r="K512">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L512">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M512">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N512">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O512">
         <v>1</v>
@@ -26990,13 +26990,13 @@
     </row>
     <row r="513" spans="1:16">
       <c r="A513" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B513" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C513">
-        <v>3.230374413778931</v>
+        <v>3.363072216113203</v>
       </c>
       <c r="D513" t="s">
         <v>131</v>
@@ -27008,22 +27008,22 @@
         <v>-1</v>
       </c>
       <c r="G513">
-        <v>0.002769625586221069</v>
+        <v>0.002876927783886797</v>
       </c>
       <c r="H513">
         <v>0.002367765303841457</v>
       </c>
       <c r="I513">
-        <v>0.4381397176203881</v>
+        <v>0.5708375199546598</v>
       </c>
       <c r="J513">
         <v>-0.181397176203883</v>
       </c>
       <c r="K513">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L513">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M513">
         <v>1.17</v>
@@ -27040,96 +27040,96 @@
     </row>
     <row r="514" spans="1:16">
       <c r="A514" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B514" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C514">
-        <v>2.332831092936091</v>
+        <v>3.230374413778931</v>
       </c>
       <c r="D514" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E514">
-        <v>2.751202782689431</v>
+        <v>2.792234696158543</v>
       </c>
       <c r="F514">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G514">
-        <v>0.002067168907063909</v>
+        <v>0.002769625586221069</v>
       </c>
       <c r="H514">
-        <v>0.002428797217310569</v>
+        <v>0.002367765303841457</v>
       </c>
       <c r="I514">
-        <v>0.4183716897533394</v>
+        <v>0.4381397176203881</v>
       </c>
       <c r="J514">
-        <v>-0.1289622261515449</v>
+        <v>-0.181397176203883</v>
       </c>
       <c r="K514">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L514">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M514">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N514">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O514">
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="515" spans="1:16">
       <c r="A515" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B515" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C515">
-        <v>3.29280938304307</v>
+        <v>2.332831092936091</v>
       </c>
       <c r="D515" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E515">
-        <v>2.730885804597308</v>
+        <v>2.751202782689431</v>
       </c>
       <c r="F515">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G515">
-        <v>0.00294719061695693</v>
+        <v>0.002067168907063909</v>
       </c>
       <c r="H515">
-        <v>0.002429114195402692</v>
+        <v>0.002428797217310569</v>
       </c>
       <c r="I515">
-        <v>0.5619235784457626</v>
+        <v>0.4183716897533394</v>
       </c>
       <c r="J515">
         <v>-0.1289622261515449</v>
       </c>
       <c r="K515">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L515">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M515">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N515">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O515">
         <v>1</v>
@@ -27140,13 +27140,13 @@
     </row>
     <row r="516" spans="1:16">
       <c r="A516" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B516" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C516">
-        <v>3.163782027212462</v>
+        <v>3.29280938304307</v>
       </c>
       <c r="D516" t="s">
         <v>131</v>
@@ -27158,22 +27158,22 @@
         <v>-1</v>
       </c>
       <c r="G516">
-        <v>0.002836217972787538</v>
+        <v>0.00294719061695693</v>
       </c>
       <c r="H516">
         <v>0.002429114195402692</v>
       </c>
       <c r="I516">
-        <v>0.4328962226151543</v>
+        <v>0.5619235784457626</v>
       </c>
       <c r="J516">
         <v>-0.1289622261515449</v>
       </c>
       <c r="K516">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L516">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M516">
         <v>1.17</v>
@@ -27190,96 +27190,96 @@
     </row>
     <row r="517" spans="1:16">
       <c r="A517" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B517" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C517">
-        <v>2.292718610119939</v>
+        <v>3.163782027212462</v>
       </c>
       <c r="D517" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E517">
-        <v>2.702522585097013</v>
+        <v>2.730885804597308</v>
       </c>
       <c r="F517">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G517">
-        <v>0.002107281389880062</v>
+        <v>0.002836217972787538</v>
       </c>
       <c r="H517">
-        <v>0.002477477414902987</v>
+        <v>0.002429114195402692</v>
       </c>
       <c r="I517">
-        <v>0.4098039749770739</v>
+        <v>0.4328962226151543</v>
       </c>
       <c r="J517">
-        <v>-0.09001806807761016</v>
+        <v>-0.1289622261515449</v>
       </c>
       <c r="K517">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L517">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M517">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N517">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O517">
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="518" spans="1:16">
       <c r="A518" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B518" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C518">
-        <v>3.240624211223998</v>
+        <v>2.292718610119939</v>
       </c>
       <c r="D518" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E518">
-        <v>2.685321139650804</v>
+        <v>2.702522585097013</v>
       </c>
       <c r="F518">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G518">
-        <v>0.002999375788776002</v>
+        <v>0.002107281389880062</v>
       </c>
       <c r="H518">
-        <v>0.002474678860349197</v>
+        <v>0.002477477414902987</v>
       </c>
       <c r="I518">
-        <v>0.5553030715731939</v>
+        <v>0.4098039749770739</v>
       </c>
       <c r="J518">
         <v>-0.09001806807761016</v>
       </c>
       <c r="K518">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L518">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M518">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N518">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O518">
         <v>1</v>
@@ -27290,13 +27290,13 @@
     </row>
     <row r="519" spans="1:16">
       <c r="A519" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B519" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C519">
-        <v>3.114322946458565</v>
+        <v>3.240624211223998</v>
       </c>
       <c r="D519" t="s">
         <v>131</v>
@@ -27308,22 +27308,22 @@
         <v>-1</v>
       </c>
       <c r="G519">
-        <v>0.002885677053541435</v>
+        <v>0.002999375788776002</v>
       </c>
       <c r="H519">
         <v>0.002474678860349197</v>
       </c>
       <c r="I519">
-        <v>0.429001806807761</v>
+        <v>0.5553030715731939</v>
       </c>
       <c r="J519">
         <v>-0.09001806807761016</v>
       </c>
       <c r="K519">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L519">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M519">
         <v>1.17</v>
@@ -27340,96 +27340,96 @@
     </row>
     <row r="520" spans="1:16">
       <c r="A520" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B520" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C520">
-        <v>2.190845625202192</v>
+        <v>3.114322946458565</v>
       </c>
       <c r="D520" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E520">
-        <v>2.57889032184732</v>
+        <v>2.685321139650804</v>
       </c>
       <c r="F520">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G520">
-        <v>0.002209154374797808</v>
+        <v>0.002885677053541435</v>
       </c>
       <c r="H520">
-        <v>0.00260110967815268</v>
+        <v>0.002474678860349197</v>
       </c>
       <c r="I520">
-        <v>0.3880446966451281</v>
+        <v>0.429001806807761</v>
       </c>
       <c r="J520">
-        <v>0.008887742522143843</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K520">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L520">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M520">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N520">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O520">
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="521" spans="1:16">
       <c r="A521" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B521" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C521">
-        <v>3.108090425020327</v>
+        <v>2.190845625202192</v>
       </c>
       <c r="D521" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E521">
-        <v>2.569601341249092</v>
+        <v>2.57889032184732</v>
       </c>
       <c r="F521">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G521">
-        <v>0.003131909574979673</v>
+        <v>0.002209154374797808</v>
       </c>
       <c r="H521">
-        <v>0.002590398658750909</v>
+        <v>0.00260110967815268</v>
       </c>
       <c r="I521">
-        <v>0.5384890837712355</v>
+        <v>0.3880446966451281</v>
       </c>
       <c r="J521">
         <v>0.008887742522143843</v>
       </c>
       <c r="K521">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L521">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M521">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N521">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O521">
         <v>1</v>
@@ -27440,13 +27440,13 @@
     </row>
     <row r="522" spans="1:16">
       <c r="A522" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B522" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C522">
-        <v>2.988712566996877</v>
+        <v>3.108090425020327</v>
       </c>
       <c r="D522" t="s">
         <v>131</v>
@@ -27458,22 +27458,22 @@
         <v>-1</v>
       </c>
       <c r="G522">
-        <v>0.003011287433003123</v>
+        <v>0.003131909574979673</v>
       </c>
       <c r="H522">
         <v>0.002590398658750909</v>
       </c>
       <c r="I522">
-        <v>0.4191112257477858</v>
+        <v>0.5384890837712355</v>
       </c>
       <c r="J522">
         <v>0.008887742522143843</v>
       </c>
       <c r="K522">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L522">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M522">
         <v>1.17</v>
@@ -27490,96 +27490,96 @@
     </row>
     <row r="523" spans="1:16">
       <c r="A523" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B523" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C523">
-        <v>2.151298027264343</v>
+        <v>2.988712566996877</v>
       </c>
       <c r="D523" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E523">
-        <v>2.530895664155756</v>
+        <v>2.569601341249092</v>
       </c>
       <c r="F523">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G523">
-        <v>0.002248701972735657</v>
+        <v>0.003011287433003123</v>
       </c>
       <c r="H523">
-        <v>0.002649104335844244</v>
+        <v>0.002590398658750909</v>
       </c>
       <c r="I523">
-        <v>0.3795976368914125</v>
+        <v>0.4191112257477858</v>
       </c>
       <c r="J523">
-        <v>0.04728346867539508</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K523">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L523">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M523">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N523">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O523">
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="524" spans="1:16">
       <c r="A524" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B524" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C524">
-        <v>3.056640151974971</v>
+        <v>2.151298027264343</v>
       </c>
       <c r="D524" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E524">
-        <v>2.524678341649788</v>
+        <v>2.530895664155756</v>
       </c>
       <c r="F524">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G524">
-        <v>0.00318335984802503</v>
+        <v>0.002248701972735657</v>
       </c>
       <c r="H524">
-        <v>0.002635321658350212</v>
+        <v>0.002649104335844244</v>
       </c>
       <c r="I524">
-        <v>0.5319618103251829</v>
+        <v>0.3795976368914125</v>
       </c>
       <c r="J524">
         <v>0.04728346867539508</v>
       </c>
       <c r="K524">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L524">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M524">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N524">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27590,13 +27590,13 @@
     </row>
     <row r="525" spans="1:16">
       <c r="A525" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B525" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C525">
-        <v>2.939949994782248</v>
+        <v>3.056640151974971</v>
       </c>
       <c r="D525" t="s">
         <v>131</v>
@@ -27608,22 +27608,22 @@
         <v>-1</v>
       </c>
       <c r="G525">
-        <v>0.003060050005217752</v>
+        <v>0.00318335984802503</v>
       </c>
       <c r="H525">
         <v>0.002635321658350212</v>
       </c>
       <c r="I525">
-        <v>0.4152716531324603</v>
+        <v>0.5319618103251829</v>
       </c>
       <c r="J525">
         <v>0.04728346867539508</v>
       </c>
       <c r="K525">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L525">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M525">
         <v>1.17</v>
@@ -27640,96 +27640,96 @@
     </row>
     <row r="526" spans="1:16">
       <c r="A526" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B526" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C526">
-        <v>2.129744886456478</v>
+        <v>2.939949994782248</v>
       </c>
       <c r="D526" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E526">
-        <v>2.504738939874366</v>
+        <v>2.524678341649788</v>
       </c>
       <c r="F526">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G526">
-        <v>0.002270255113543523</v>
+        <v>0.003060050005217752</v>
       </c>
       <c r="H526">
-        <v>0.002675261060125634</v>
+        <v>0.002635321658350212</v>
       </c>
       <c r="I526">
-        <v>0.3749940534178879</v>
+        <v>0.4152716531324603</v>
       </c>
       <c r="J526">
-        <v>0.06820884810050738</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K526">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L526">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M526">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N526">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O526">
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="527" spans="1:16">
       <c r="A527" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B527" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C527">
-        <v>3.02860014354532</v>
+        <v>2.129744886456478</v>
       </c>
       <c r="D527" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E527">
-        <v>2.500195647722407</v>
+        <v>2.504738939874366</v>
       </c>
       <c r="F527">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G527">
-        <v>0.00321139985645468</v>
+        <v>0.002270255113543523</v>
       </c>
       <c r="H527">
-        <v>0.002659804352277594</v>
+        <v>0.002675261060125634</v>
       </c>
       <c r="I527">
-        <v>0.5284044958229135</v>
+        <v>0.3749940534178879</v>
       </c>
       <c r="J527">
         <v>0.06820884810050738</v>
       </c>
       <c r="K527">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L527">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M527">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N527">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27740,13 +27740,13 @@
     </row>
     <row r="528" spans="1:16">
       <c r="A528" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B528" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C528">
-        <v>2.913374762912356</v>
+        <v>3.02860014354532</v>
       </c>
       <c r="D528" t="s">
         <v>131</v>
@@ -27758,22 +27758,22 @@
         <v>-1</v>
       </c>
       <c r="G528">
-        <v>0.003086625237087645</v>
+        <v>0.00321139985645468</v>
       </c>
       <c r="H528">
         <v>0.002659804352277594</v>
       </c>
       <c r="I528">
-        <v>0.4131791151899491</v>
+        <v>0.5284044958229135</v>
       </c>
       <c r="J528">
         <v>0.06820884810050738</v>
       </c>
       <c r="K528">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L528">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M528">
         <v>1.17</v>
@@ -27790,96 +27790,96 @@
     </row>
     <row r="529" spans="1:16">
       <c r="A529" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B529" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C529">
-        <v>2.123592991344732</v>
+        <v>2.913374762912356</v>
       </c>
       <c r="D529" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E529">
-        <v>2.497273047748461</v>
+        <v>2.500195647722407</v>
       </c>
       <c r="F529">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G529">
-        <v>0.002276407008655268</v>
+        <v>0.003086625237087645</v>
       </c>
       <c r="H529">
-        <v>0.002682726952251539</v>
+        <v>0.002659804352277594</v>
       </c>
       <c r="I529">
-        <v>0.3736800564037286</v>
+        <v>0.4131791151899491</v>
       </c>
       <c r="J529">
-        <v>0.07418156180123091</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K529">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L529">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M529">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N529">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O529">
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="530" spans="1:16">
       <c r="A530" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B530" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C530">
-        <v>3.020596707186351</v>
+        <v>2.123592991344732</v>
       </c>
       <c r="D530" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E530">
-        <v>2.49320757269256</v>
+        <v>2.497273047748461</v>
       </c>
       <c r="F530">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G530">
-        <v>0.00321940329281365</v>
+        <v>0.002276407008655268</v>
       </c>
       <c r="H530">
-        <v>0.00266679242730744</v>
+        <v>0.002682726952251539</v>
       </c>
       <c r="I530">
-        <v>0.5273891344937907</v>
+        <v>0.3736800564037286</v>
       </c>
       <c r="J530">
         <v>0.07418156180123091</v>
       </c>
       <c r="K530">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L530">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M530">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N530">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -27890,13 +27890,13 @@
     </row>
     <row r="531" spans="1:16">
       <c r="A531" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B531" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C531">
-        <v>2.905789416512437</v>
+        <v>3.020596707186351</v>
       </c>
       <c r="D531" t="s">
         <v>131</v>
@@ -27908,22 +27908,22 @@
         <v>-1</v>
       </c>
       <c r="G531">
-        <v>0.003094210583487563</v>
+        <v>0.00321940329281365</v>
       </c>
       <c r="H531">
         <v>0.00266679242730744</v>
       </c>
       <c r="I531">
-        <v>0.4125818438198769</v>
+        <v>0.5273891344937907</v>
       </c>
       <c r="J531">
         <v>0.07418156180123091</v>
       </c>
       <c r="K531">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L531">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M531">
         <v>1.17</v>
@@ -27940,96 +27940,96 @@
     </row>
     <row r="532" spans="1:16">
       <c r="A532" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B532" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C532">
-        <v>2.162997802089755</v>
+        <v>2.905789416512437</v>
       </c>
       <c r="D532" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E532">
-        <v>2.545094420011838</v>
+        <v>2.49320757269256</v>
       </c>
       <c r="F532">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G532">
-        <v>0.002237002197910246</v>
+        <v>0.003094210583487563</v>
       </c>
       <c r="H532">
-        <v>0.002634905579988162</v>
+        <v>0.00266679242730744</v>
       </c>
       <c r="I532">
-        <v>0.382096617922083</v>
+        <v>0.4125818438198769</v>
       </c>
       <c r="J532">
-        <v>0.03592446399052947</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K532">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L532">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M532">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N532">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O532">
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="533" spans="1:16">
       <c r="A533" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B533" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C533">
-        <v>3.071861218252691</v>
+        <v>2.162997802089755</v>
       </c>
       <c r="D533" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E533">
-        <v>2.537968377131081</v>
+        <v>2.545094420011838</v>
       </c>
       <c r="F533">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G533">
-        <v>0.00316813878174731</v>
+        <v>0.002237002197910246</v>
       </c>
       <c r="H533">
-        <v>0.00262203162286892</v>
+        <v>0.002634905579988162</v>
       </c>
       <c r="I533">
-        <v>0.53389284112161</v>
+        <v>0.382096617922083</v>
       </c>
       <c r="J533">
         <v>0.03592446399052947</v>
       </c>
       <c r="K533">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L533">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M533">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N533">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28040,13 +28040,13 @@
     </row>
     <row r="534" spans="1:16">
       <c r="A534" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B534" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C534">
-        <v>2.954375930732028</v>
+        <v>3.071861218252691</v>
       </c>
       <c r="D534" t="s">
         <v>131</v>
@@ -28058,22 +28058,22 @@
         <v>-1</v>
       </c>
       <c r="G534">
-        <v>0.003045624069267972</v>
+        <v>0.00316813878174731</v>
       </c>
       <c r="H534">
         <v>0.00262203162286892</v>
       </c>
       <c r="I534">
-        <v>0.4164075536009468</v>
+        <v>0.53389284112161</v>
       </c>
       <c r="J534">
         <v>0.03592446399052947</v>
       </c>
       <c r="K534">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L534">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M534">
         <v>1.17</v>
@@ -28090,96 +28090,96 @@
     </row>
     <row r="535" spans="1:16">
       <c r="A535" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B535" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C535">
-        <v>2.152181822645585</v>
+        <v>2.954375930732028</v>
       </c>
       <c r="D535" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E535">
-        <v>2.583360993813217</v>
+        <v>2.537968377131081</v>
       </c>
       <c r="F535">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G535">
-        <v>0.002247818177354416</v>
+        <v>0.003045624069267972</v>
       </c>
       <c r="H535">
-        <v>0.002696639006186784</v>
+        <v>0.00262203162286892</v>
       </c>
       <c r="I535">
-        <v>0.4311791711676323</v>
+        <v>0.4164075536009468</v>
       </c>
       <c r="J535">
-        <v>0.04642541490719935</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K535">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L535">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M535">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N535">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O535">
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="536" spans="1:16">
       <c r="A536" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B536" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C536">
-        <v>3.057789944024353</v>
+        <v>2.152181822645585</v>
       </c>
       <c r="D536" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E536">
-        <v>2.525682264558577</v>
+        <v>2.583360993813217</v>
       </c>
       <c r="F536">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G536">
-        <v>0.003182210055975647</v>
+        <v>0.002247818177354416</v>
       </c>
       <c r="H536">
-        <v>0.002634317735441423</v>
+        <v>0.002696639006186784</v>
       </c>
       <c r="I536">
-        <v>0.532107679465776</v>
+        <v>0.4311791711676323</v>
       </c>
       <c r="J536">
         <v>0.04642541490719935</v>
       </c>
       <c r="K536">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L536">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M536">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N536">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28190,13 +28190,13 @@
     </row>
     <row r="537" spans="1:16">
       <c r="A537" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B537" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C537">
-        <v>2.941039723067857</v>
+        <v>3.057789944024353</v>
       </c>
       <c r="D537" t="s">
         <v>131</v>
@@ -28208,22 +28208,22 @@
         <v>-1</v>
       </c>
       <c r="G537">
-        <v>0.003058960276932143</v>
+        <v>0.003182210055975647</v>
       </c>
       <c r="H537">
         <v>0.002634317735441423</v>
       </c>
       <c r="I537">
-        <v>0.4153574585092796</v>
+        <v>0.532107679465776</v>
       </c>
       <c r="J537">
         <v>0.04642541490719935</v>
       </c>
       <c r="K537">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L537">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M537">
         <v>1.17</v>
@@ -28240,96 +28240,96 @@
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B538" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C538">
-        <v>2.132867933343715</v>
+        <v>2.941039723067857</v>
       </c>
       <c r="D538" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E538">
-        <v>2.560484348232362</v>
+        <v>2.525682264558577</v>
       </c>
       <c r="F538">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G538">
-        <v>0.002267132066656285</v>
+        <v>0.003058960276932143</v>
       </c>
       <c r="H538">
-        <v>0.002719515651767639</v>
+        <v>0.002634317735441423</v>
       </c>
       <c r="I538">
-        <v>0.4276164148886465</v>
+        <v>0.4153574585092796</v>
       </c>
       <c r="J538">
-        <v>0.06517676374396589</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K538">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L538">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M538">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N538">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O538">
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B539" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C539">
-        <v>3.032663136583086</v>
+        <v>2.132867933343715</v>
       </c>
       <c r="D539" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E539">
-        <v>2.50374318641956</v>
+        <v>2.560484348232362</v>
       </c>
       <c r="F539">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G539">
-        <v>0.003207336863416915</v>
+        <v>0.002267132066656285</v>
       </c>
       <c r="H539">
-        <v>0.00265625681358044</v>
+        <v>0.002719515651767639</v>
       </c>
       <c r="I539">
-        <v>0.5289199501635258</v>
+        <v>0.4276164148886465</v>
       </c>
       <c r="J539">
         <v>0.06517676374396589</v>
       </c>
       <c r="K539">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L539">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="M539">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N539">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28340,13 +28340,13 @@
     </row>
     <row r="540" spans="1:16">
       <c r="A540" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B540" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C540">
-        <v>2.917225510045163</v>
+        <v>3.032663136583086</v>
       </c>
       <c r="D540" t="s">
         <v>131</v>
@@ -28358,22 +28358,22 @@
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.003082774489954837</v>
+        <v>0.003207336863416915</v>
       </c>
       <c r="H540">
         <v>0.00265625681358044</v>
       </c>
       <c r="I540">
-        <v>0.4134823236256033</v>
+        <v>0.5289199501635258</v>
       </c>
       <c r="J540">
         <v>0.06517676374396589</v>
       </c>
       <c r="K540">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L540">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M540">
         <v>1.17</v>
@@ -28390,96 +28390,96 @@
     </row>
     <row r="541" spans="1:16">
       <c r="A541" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B541" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C541">
-        <v>2.134641124313295</v>
+        <v>2.917225510045163</v>
       </c>
       <c r="D541" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E541">
-        <v>2.527050652099242</v>
+        <v>2.50374318641956</v>
       </c>
       <c r="F541">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.002325358875686705</v>
+        <v>0.003082774489954837</v>
       </c>
       <c r="H541">
-        <v>0.002752949347900758</v>
+        <v>0.00265625681358044</v>
       </c>
       <c r="I541">
-        <v>0.3924095277859476</v>
+        <v>0.4134823236256033</v>
       </c>
       <c r="J541">
-        <v>0.09258143270553931</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K541">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L541">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="M541">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N541">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="542" spans="1:16">
       <c r="A542" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B542" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C542">
-        <v>2.995940880174577</v>
+        <v>2.134641124313295</v>
       </c>
       <c r="D542" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E542">
-        <v>2.471679723734519</v>
+        <v>2.527050652099242</v>
       </c>
       <c r="F542">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G542">
-        <v>0.003244059119825423</v>
+        <v>0.002325358875686705</v>
       </c>
       <c r="H542">
-        <v>0.002688320276265481</v>
+        <v>0.002752949347900758</v>
       </c>
       <c r="I542">
-        <v>0.5242611564400583</v>
+        <v>0.3924095277859476</v>
       </c>
       <c r="J542">
         <v>0.09258143270553931</v>
       </c>
       <c r="K542">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L542">
-        <v>3.12</v>
+        <v>2.23</v>
       </c>
       <c r="M542">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N542">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28490,13 +28490,13 @@
     </row>
     <row r="543" spans="1:16">
       <c r="A543" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B543" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C543">
-        <v>2.882421580463965</v>
+        <v>2.995940880174577</v>
       </c>
       <c r="D543" t="s">
         <v>131</v>
@@ -28508,22 +28508,22 @@
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.003117578419536035</v>
+        <v>0.003244059119825423</v>
       </c>
       <c r="H543">
         <v>0.002688320276265481</v>
       </c>
       <c r="I543">
-        <v>0.4107418567294463</v>
+        <v>0.5242611564400583</v>
       </c>
       <c r="J543">
         <v>0.09258143270553931</v>
       </c>
       <c r="K543">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L543">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M543">
         <v>1.17</v>
@@ -28540,96 +28540,96 @@
     </row>
     <row r="544" spans="1:16">
       <c r="A544" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B544" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C544">
-        <v>2.127453766817889</v>
+        <v>2.882421580463965</v>
       </c>
       <c r="D544" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E544">
-        <v>2.518537471376529</v>
+        <v>2.471679723734519</v>
       </c>
       <c r="F544">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.002332546233182111</v>
+        <v>0.003117578419536035</v>
       </c>
       <c r="H544">
-        <v>0.002761462528623472</v>
+        <v>0.002688320276265481</v>
       </c>
       <c r="I544">
-        <v>0.3910837045586395</v>
+        <v>0.4107418567294463</v>
       </c>
       <c r="J544">
-        <v>0.09955944969136986</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K544">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L544">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="M544">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N544">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="545" spans="1:16">
       <c r="A545" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B545" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C545">
-        <v>2.986590337413564</v>
+        <v>2.127453766817889</v>
       </c>
       <c r="D545" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E545">
-        <v>2.463515443861097</v>
+        <v>2.518537471376529</v>
       </c>
       <c r="F545">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G545">
-        <v>0.003253409662586436</v>
+        <v>0.002332546233182111</v>
       </c>
       <c r="H545">
-        <v>0.002696484556138903</v>
+        <v>0.002761462528623472</v>
       </c>
       <c r="I545">
-        <v>0.5230748935524669</v>
+        <v>0.3910837045586395</v>
       </c>
       <c r="J545">
         <v>0.09955944969136986</v>
       </c>
       <c r="K545">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="L545">
-        <v>3.12</v>
+        <v>2.23</v>
       </c>
       <c r="M545">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N545">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28640,46 +28640,46 @@
     </row>
     <row r="546" spans="1:16">
       <c r="A546" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B546" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C546">
-        <v>2.87355949889196</v>
+        <v>2.134466983327148</v>
       </c>
       <c r="D546" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E546">
-        <v>2.463515443861097</v>
+        <v>2.518537471376529</v>
       </c>
       <c r="F546">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G546">
-        <v>0.003126440501108039</v>
+        <v>0.002345533016672852</v>
       </c>
       <c r="H546">
-        <v>0.002696484556138903</v>
+        <v>0.002761462528623472</v>
       </c>
       <c r="I546">
-        <v>0.4100440550308631</v>
+        <v>0.3840704880493804</v>
       </c>
       <c r="J546">
         <v>0.09955944969136986</v>
       </c>
       <c r="K546">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="L546">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="M546">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N546">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28690,90 +28690,90 @@
     </row>
     <row r="547" spans="1:16">
       <c r="A547" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B547" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C547">
-        <v>2.12608596303</v>
+        <v>2.986590337413564</v>
       </c>
       <c r="D547" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E547">
-        <v>2.508891391411886</v>
+        <v>2.463515443861097</v>
       </c>
       <c r="F547">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G547">
-        <v>0.002353914036970001</v>
+        <v>0.003253409662586436</v>
       </c>
       <c r="H547">
-        <v>0.002771108608588114</v>
+        <v>0.002696484556138903</v>
       </c>
       <c r="I547">
-        <v>0.3828054283818867</v>
+        <v>0.5230748935524669</v>
       </c>
       <c r="J547">
-        <v>0.1074660726132081</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K547">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="L547">
-        <v>2.24</v>
+        <v>3.12</v>
       </c>
       <c r="M547">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N547">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="548" spans="1:16">
       <c r="A548" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B548" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C548">
-        <v>2.975995462698301</v>
+        <v>2.87355949889196</v>
       </c>
       <c r="D548" t="s">
         <v>131</v>
       </c>
       <c r="E548">
-        <v>2.454264695042546</v>
+        <v>2.463515443861097</v>
       </c>
       <c r="F548">
         <v>-1</v>
       </c>
       <c r="G548">
-        <v>0.003264004537301699</v>
+        <v>0.003126440501108039</v>
       </c>
       <c r="H548">
-        <v>0.002705735304957454</v>
+        <v>0.002696484556138903</v>
       </c>
       <c r="I548">
-        <v>0.5217307676557548</v>
+        <v>0.4100440550308631</v>
       </c>
       <c r="J548">
-        <v>0.1074660726132081</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K548">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L548">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M548">
         <v>1.17</v>
@@ -28785,51 +28785,51 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="549" spans="1:16">
       <c r="A549" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B549" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C549">
-        <v>2.863518087781226</v>
+        <v>2.12608596303</v>
       </c>
       <c r="D549" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E549">
-        <v>2.454264695042546</v>
+        <v>2.508891391411886</v>
       </c>
       <c r="F549">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G549">
-        <v>0.003136481912218774</v>
+        <v>0.002353914036970001</v>
       </c>
       <c r="H549">
-        <v>0.002705735304957454</v>
+        <v>0.002771108608588114</v>
       </c>
       <c r="I549">
-        <v>0.4092533927386794</v>
+        <v>0.3828054283818867</v>
       </c>
       <c r="J549">
         <v>0.1074660726132081</v>
       </c>
       <c r="K549">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="L549">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="M549">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N549">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O549">
         <v>1</v>
@@ -28840,90 +28840,90 @@
     </row>
     <row r="550" spans="1:16">
       <c r="A550" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B550" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C550">
-        <v>2.131023582128605</v>
+        <v>2.975995462698301</v>
       </c>
       <c r="D550" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E550">
-        <v>2.514574311506508</v>
+        <v>2.454264695042546</v>
       </c>
       <c r="F550">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G550">
-        <v>0.002348976417871395</v>
+        <v>0.003264004537301699</v>
       </c>
       <c r="H550">
-        <v>0.002765425688493492</v>
+        <v>0.002705735304957454</v>
       </c>
       <c r="I550">
-        <v>0.3835507293779026</v>
+        <v>0.5217307676557548</v>
       </c>
       <c r="J550">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K550">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="L550">
-        <v>2.24</v>
+        <v>3.12</v>
       </c>
       <c r="M550">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N550">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O550">
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="551" spans="1:16">
       <c r="A551" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B551" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C551">
-        <v>2.982237358539935</v>
+        <v>2.863518087781226</v>
       </c>
       <c r="D551" t="s">
         <v>131</v>
       </c>
       <c r="E551">
-        <v>2.459714708575913</v>
+        <v>2.454264695042546</v>
       </c>
       <c r="F551">
         <v>-1</v>
       </c>
       <c r="G551">
-        <v>0.003257762641460066</v>
+        <v>0.003136481912218774</v>
       </c>
       <c r="H551">
-        <v>0.002700285291424087</v>
+        <v>0.002705735304957454</v>
       </c>
       <c r="I551">
-        <v>0.5225226499640216</v>
+        <v>0.4092533927386794</v>
       </c>
       <c r="J551">
-        <v>0.1028079413881086</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K551">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L551">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M551">
         <v>1.17</v>
@@ -28935,51 +28935,51 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="552" spans="1:16">
       <c r="A552" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B552" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C552">
-        <v>2.869433914437102</v>
+        <v>2.131023582128605</v>
       </c>
       <c r="D552" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E552">
-        <v>2.459714708575913</v>
+        <v>2.514574311506508</v>
       </c>
       <c r="F552">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G552">
-        <v>0.003130566085562898</v>
+        <v>0.002348976417871395</v>
       </c>
       <c r="H552">
-        <v>0.002700285291424087</v>
+        <v>0.002765425688493492</v>
       </c>
       <c r="I552">
-        <v>0.4097192058611889</v>
+        <v>0.3835507293779026</v>
       </c>
       <c r="J552">
         <v>0.1028079413881086</v>
       </c>
       <c r="K552">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="L552">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="M552">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N552">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O552">
         <v>1</v>
@@ -28990,34 +28990,34 @@
     </row>
     <row r="553" spans="1:16">
       <c r="A553" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B553" t="s">
         <v>52</v>
       </c>
       <c r="C553">
-        <v>2.970054254577281</v>
+        <v>2.982237358539935</v>
       </c>
       <c r="D553" t="s">
         <v>131</v>
       </c>
       <c r="E553">
-        <v>2.449077222280164</v>
+        <v>2.459714708575913</v>
       </c>
       <c r="F553">
         <v>-1</v>
       </c>
       <c r="G553">
-        <v>0.003269945745422719</v>
+        <v>0.003257762641460066</v>
       </c>
       <c r="H553">
-        <v>0.002710922777719837</v>
+        <v>0.002700285291424087</v>
       </c>
       <c r="I553">
-        <v>0.5209770322971177</v>
+        <v>0.5225226499640216</v>
       </c>
       <c r="J553">
-        <v>0.1118998100169543</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K553">
         <v>1.34</v>
@@ -29035,39 +29035,39 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>55</v>
+        <v>332</v>
       </c>
     </row>
     <row r="554" spans="1:16">
       <c r="A554" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B554" t="s">
         <v>53</v>
       </c>
       <c r="C554">
-        <v>2.857887241278468</v>
+        <v>2.869433914437102</v>
       </c>
       <c r="D554" t="s">
         <v>131</v>
       </c>
       <c r="E554">
-        <v>2.449077222280164</v>
+        <v>2.459714708575913</v>
       </c>
       <c r="F554">
         <v>-1</v>
       </c>
       <c r="G554">
-        <v>0.003142112758721532</v>
+        <v>0.003130566085562898</v>
       </c>
       <c r="H554">
-        <v>0.002710922777719837</v>
+        <v>0.002700285291424087</v>
       </c>
       <c r="I554">
-        <v>0.4088100189983046</v>
+        <v>0.4097192058611889</v>
       </c>
       <c r="J554">
-        <v>0.1118998100169543</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K554">
         <v>1.27</v>
@@ -29085,7 +29085,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>55</v>
+        <v>332</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29096,28 +29096,28 @@
         <v>52</v>
       </c>
       <c r="C555">
-        <v>2.944089643772313</v>
+        <v>2.970054254577281</v>
       </c>
       <c r="D555" t="s">
         <v>131</v>
       </c>
       <c r="E555">
-        <v>2.426406629263886</v>
+        <v>2.449077222280164</v>
       </c>
       <c r="F555">
         <v>-1</v>
       </c>
       <c r="G555">
-        <v>0.003295910356227687</v>
+        <v>0.003269945745422719</v>
       </c>
       <c r="H555">
-        <v>0.002733593370736115</v>
+        <v>0.002710922777719837</v>
       </c>
       <c r="I555">
-        <v>0.5176830145084277</v>
+        <v>0.5209770322971177</v>
       </c>
       <c r="J555">
-        <v>0.1312763852445424</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K555">
         <v>1.34</v>
@@ -29135,7 +29135,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29146,28 +29146,28 @@
         <v>53</v>
       </c>
       <c r="C556">
-        <v>2.833278990739431</v>
+        <v>2.857887241278468</v>
       </c>
       <c r="D556" t="s">
         <v>131</v>
       </c>
       <c r="E556">
-        <v>2.426406629263886</v>
+        <v>2.449077222280164</v>
       </c>
       <c r="F556">
         <v>-1</v>
       </c>
       <c r="G556">
-        <v>0.003166721009260569</v>
+        <v>0.003142112758721532</v>
       </c>
       <c r="H556">
-        <v>0.002733593370736115</v>
+        <v>0.002710922777719837</v>
       </c>
       <c r="I556">
-        <v>0.4068723614755454</v>
+        <v>0.4088100189983046</v>
       </c>
       <c r="J556">
-        <v>0.1312763852445424</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K556">
         <v>1.27</v>
@@ -29185,7 +29185,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29196,28 +29196,28 @@
         <v>52</v>
       </c>
       <c r="C557">
-        <v>2.897401147650162</v>
+        <v>2.944089643772313</v>
       </c>
       <c r="D557" t="s">
         <v>131</v>
       </c>
       <c r="E557">
-        <v>2.385641300560216</v>
+        <v>2.426406629263886</v>
       </c>
       <c r="F557">
         <v>-1</v>
       </c>
       <c r="G557">
-        <v>0.003342598852349839</v>
+        <v>0.003295910356227687</v>
       </c>
       <c r="H557">
-        <v>0.002774358699439784</v>
+        <v>0.002733593370736115</v>
       </c>
       <c r="I557">
-        <v>0.5117598470899458</v>
+        <v>0.5176830145084277</v>
       </c>
       <c r="J557">
-        <v>0.16611854652973</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K557">
         <v>1.34</v>
@@ -29235,7 +29235,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>333</v>
+        <v>54</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29246,28 +29246,28 @@
         <v>53</v>
       </c>
       <c r="C558">
-        <v>2.789029445907243</v>
+        <v>2.833278990739431</v>
       </c>
       <c r="D558" t="s">
         <v>131</v>
       </c>
       <c r="E558">
-        <v>2.385641300560216</v>
+        <v>2.426406629263886</v>
       </c>
       <c r="F558">
         <v>-1</v>
       </c>
       <c r="G558">
-        <v>0.003210970554092757</v>
+        <v>0.003166721009260569</v>
       </c>
       <c r="H558">
-        <v>0.002774358699439784</v>
+        <v>0.002733593370736115</v>
       </c>
       <c r="I558">
-        <v>0.4033881453470269</v>
+        <v>0.4068723614755454</v>
       </c>
       <c r="J558">
-        <v>0.16611854652973</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K558">
         <v>1.27</v>
@@ -29285,7 +29285,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>333</v>
+        <v>54</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29296,28 +29296,28 @@
         <v>52</v>
       </c>
       <c r="C559">
-        <v>2.834385584744631</v>
+        <v>2.897401147650162</v>
       </c>
       <c r="D559" t="s">
         <v>131</v>
       </c>
       <c r="E559">
-        <v>2.330620249366581</v>
+        <v>2.385641300560216</v>
       </c>
       <c r="F559">
         <v>-1</v>
       </c>
       <c r="G559">
-        <v>0.003405614415255369</v>
+        <v>0.003342598852349839</v>
       </c>
       <c r="H559">
-        <v>0.002829379750633419</v>
+        <v>0.002774358699439784</v>
       </c>
       <c r="I559">
-        <v>0.5037653353780502</v>
+        <v>0.5117598470899458</v>
       </c>
       <c r="J559">
-        <v>0.2131450860114693</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K559">
         <v>1.34</v>
@@ -29335,7 +29335,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29346,28 +29346,28 @@
         <v>53</v>
       </c>
       <c r="C560">
-        <v>2.729305740765434</v>
+        <v>2.789029445907243</v>
       </c>
       <c r="D560" t="s">
         <v>131</v>
       </c>
       <c r="E560">
-        <v>2.330620249366581</v>
+        <v>2.385641300560216</v>
       </c>
       <c r="F560">
         <v>-1</v>
       </c>
       <c r="G560">
-        <v>0.003270694259234566</v>
+        <v>0.003210970554092757</v>
       </c>
       <c r="H560">
-        <v>0.002829379750633419</v>
+        <v>0.002774358699439784</v>
       </c>
       <c r="I560">
-        <v>0.3986854913988531</v>
+        <v>0.4033881453470269</v>
       </c>
       <c r="J560">
-        <v>0.2131450860114693</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K560">
         <v>1.27</v>
@@ -29385,7 +29385,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29396,28 +29396,28 @@
         <v>52</v>
       </c>
       <c r="C561">
-        <v>2.710585509297514</v>
+        <v>2.834385584744631</v>
       </c>
       <c r="D561" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E561">
-        <v>2.761972833438688</v>
+        <v>2.330620249366581</v>
       </c>
       <c r="F561">
         <v>-1</v>
       </c>
       <c r="G561">
-        <v>0.003529414490702487</v>
+        <v>0.003405614415255369</v>
       </c>
       <c r="H561">
-        <v>0.003538027166561312</v>
+        <v>0.002829379750633419</v>
       </c>
       <c r="I561">
-        <v>-0.05138732414117442</v>
+        <v>0.5037653353780502</v>
       </c>
       <c r="J561">
-        <v>0.3055332020167811</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K561">
         <v>1.34</v>
@@ -29426,16 +29426,16 @@
         <v>3.12</v>
       </c>
       <c r="M561">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N561">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O561">
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>56</v>
+        <v>334</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29446,28 +29446,28 @@
         <v>53</v>
       </c>
       <c r="C562">
-        <v>2.611972833438688</v>
+        <v>2.729305740765434</v>
       </c>
       <c r="D562" t="s">
         <v>131</v>
       </c>
       <c r="E562">
-        <v>2.222526153640366</v>
+        <v>2.330620249366581</v>
       </c>
       <c r="F562">
         <v>-1</v>
       </c>
       <c r="G562">
-        <v>0.003388027166561312</v>
+        <v>0.003270694259234566</v>
       </c>
       <c r="H562">
-        <v>0.002937473846359634</v>
+        <v>0.002829379750633419</v>
       </c>
       <c r="I562">
-        <v>0.389446679798322</v>
+        <v>0.3986854913988531</v>
       </c>
       <c r="J562">
-        <v>0.3055332020167811</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K562">
         <v>1.27</v>
@@ -29485,7 +29485,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>56</v>
+        <v>334</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29496,28 +29496,28 @@
         <v>52</v>
       </c>
       <c r="C563">
-        <v>2.647551728558422</v>
+        <v>2.710585509297514</v>
       </c>
       <c r="D563" t="s">
         <v>133</v>
       </c>
       <c r="E563">
-        <v>2.702231862141191</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="F563">
         <v>-1</v>
       </c>
       <c r="G563">
-        <v>0.003592448271441579</v>
+        <v>0.003529414490702487</v>
       </c>
       <c r="H563">
-        <v>0.003597768137858809</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="I563">
-        <v>-0.05468013358276913</v>
+        <v>-0.05138732414117442</v>
       </c>
       <c r="J563">
-        <v>0.3525733368967002</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K563">
         <v>1.34</v>
@@ -29535,7 +29535,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>335</v>
+        <v>56</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29546,28 +29546,28 @@
         <v>53</v>
       </c>
       <c r="C564">
-        <v>2.552231862141191</v>
+        <v>2.611972833438688</v>
       </c>
       <c r="D564" t="s">
         <v>131</v>
       </c>
       <c r="E564">
-        <v>2.167489195830861</v>
+        <v>2.222526153640366</v>
       </c>
       <c r="F564">
         <v>-1</v>
       </c>
       <c r="G564">
-        <v>0.003447768137858809</v>
+        <v>0.003388027166561312</v>
       </c>
       <c r="H564">
-        <v>0.00299251080416914</v>
+        <v>0.002937473846359634</v>
       </c>
       <c r="I564">
-        <v>0.3847426663103302</v>
+        <v>0.389446679798322</v>
       </c>
       <c r="J564">
-        <v>0.3525733368967002</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K564">
         <v>1.27</v>
@@ -29585,7 +29585,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>335</v>
+        <v>56</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29593,49 +29593,49 @@
         <v>0</v>
       </c>
       <c r="B565" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C565">
-        <v>1.858962462723951</v>
+        <v>2.647551728558422</v>
       </c>
       <c r="D565" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E565">
-        <v>2.165632934933811</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="F565">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G565">
-        <v>0.002761037537276049</v>
+        <v>0.003592448271441579</v>
       </c>
       <c r="H565">
-        <v>0.00311436706506619</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="I565">
-        <v>0.3066704722098597</v>
+        <v>-0.05468013358276913</v>
       </c>
       <c r="J565">
-        <v>0.3888254631690077</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K565">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="L565">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="M565">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="N565">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="O565">
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29643,93 +29643,93 @@
         <v>1</v>
       </c>
       <c r="B566" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C566">
-        <v>2.59897387935353</v>
+        <v>2.552231862141191</v>
       </c>
       <c r="D566" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E566">
-        <v>2.65619166177536</v>
+        <v>2.167489195830861</v>
       </c>
       <c r="F566">
         <v>-1</v>
       </c>
       <c r="G566">
-        <v>0.003641026120646471</v>
+        <v>0.003447768137858809</v>
       </c>
       <c r="H566">
-        <v>0.00364380833822464</v>
+        <v>0.00299251080416914</v>
       </c>
       <c r="I566">
-        <v>-0.05721778242183051</v>
+        <v>0.3847426663103302</v>
       </c>
       <c r="J566">
-        <v>0.3888254631690077</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K566">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L566">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M566">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N566">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O566">
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="567" spans="1:16">
       <c r="A567" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B567" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C567">
-        <v>2.50619166177536</v>
+        <v>1.858962462723951</v>
       </c>
       <c r="D567" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E567">
-        <v>2.125074208092261</v>
+        <v>2.165632934933811</v>
       </c>
       <c r="F567">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G567">
-        <v>0.00349380833822464</v>
+        <v>0.002761037537276049</v>
       </c>
       <c r="H567">
-        <v>0.003034925791907739</v>
+        <v>0.00311436706506619</v>
       </c>
       <c r="I567">
-        <v>0.3811174536830992</v>
+        <v>0.3066704722098597</v>
       </c>
       <c r="J567">
         <v>0.3888254631690077</v>
       </c>
       <c r="K567">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="L567">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M567">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N567">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O567">
         <v>1</v>
@@ -29740,146 +29740,146 @@
     </row>
     <row r="568" spans="1:16">
       <c r="A568" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B568" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C568">
-        <v>1.838291711302243</v>
+        <v>2.59897387935353</v>
       </c>
       <c r="D568" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E568">
-        <v>2.143893006714428</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="F568">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G568">
-        <v>0.002781708288697757</v>
+        <v>0.003641026120646471</v>
       </c>
       <c r="H568">
-        <v>0.003136106993285572</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="I568">
-        <v>0.3056012954121849</v>
+        <v>-0.05721778242183051</v>
       </c>
       <c r="J568">
-        <v>0.4066450764635833</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K568">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="L568">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="M568">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="N568">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="O568">
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="569" spans="1:16">
       <c r="A569" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B569" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C569">
-        <v>2.575095597538799</v>
+        <v>2.50619166177536</v>
       </c>
       <c r="D569" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E569">
-        <v>2.633560752891249</v>
+        <v>2.125074208092261</v>
       </c>
       <c r="F569">
         <v>-1</v>
       </c>
       <c r="G569">
-        <v>0.003664904402461202</v>
+        <v>0.00349380833822464</v>
       </c>
       <c r="H569">
-        <v>0.003666439247108751</v>
+        <v>0.003034925791907739</v>
       </c>
       <c r="I569">
-        <v>-0.05846515535245045</v>
+        <v>0.3811174536830992</v>
       </c>
       <c r="J569">
-        <v>0.4066450764635833</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K569">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L569">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M569">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N569">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O569">
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="570" spans="1:16">
       <c r="A570" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B570" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C570">
-        <v>2.483560752891249</v>
+        <v>1.838291711302243</v>
       </c>
       <c r="D570" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E570">
-        <v>2.104225260537608</v>
+        <v>2.143893006714428</v>
       </c>
       <c r="F570">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G570">
-        <v>0.003516439247108751</v>
+        <v>0.002781708288697757</v>
       </c>
       <c r="H570">
-        <v>0.003055774739462393</v>
+        <v>0.003136106993285572</v>
       </c>
       <c r="I570">
-        <v>0.3793354923536416</v>
+        <v>0.3056012954121849</v>
       </c>
       <c r="J570">
         <v>0.4066450764635833</v>
       </c>
       <c r="K570">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="L570">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M570">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N570">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O570">
         <v>1</v>
@@ -29890,146 +29890,146 @@
     </row>
     <row r="571" spans="1:16">
       <c r="A571" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B571" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C571">
-        <v>1.784876857591519</v>
+        <v>2.575095597538799</v>
       </c>
       <c r="D571" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E571">
-        <v>2.087715315742805</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="F571">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G571">
-        <v>0.002835123142408481</v>
+        <v>0.003664904402461202</v>
       </c>
       <c r="H571">
-        <v>0.003192284684257196</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="I571">
-        <v>0.3028384581512857</v>
+        <v>-0.05846515535245045</v>
       </c>
       <c r="J571">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K571">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="L571">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="M571">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="N571">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="O571">
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="572" spans="1:16">
       <c r="A572" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B572" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C572">
-        <v>2.513392232045375</v>
+        <v>2.483560752891249</v>
       </c>
       <c r="D572" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E572">
-        <v>2.575080697535542</v>
+        <v>2.104225260537608</v>
       </c>
       <c r="F572">
         <v>-1</v>
       </c>
       <c r="G572">
-        <v>0.003726607767954625</v>
+        <v>0.003516439247108751</v>
       </c>
       <c r="H572">
-        <v>0.003724919302464458</v>
+        <v>0.003055774739462393</v>
       </c>
       <c r="I572">
-        <v>-0.0616884654901666</v>
+        <v>0.3793354923536416</v>
       </c>
       <c r="J572">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K572">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L572">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M572">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N572">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O572">
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="573" spans="1:16">
       <c r="A573" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B573" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C573">
-        <v>2.425080697535542</v>
+        <v>1.784876857591519</v>
       </c>
       <c r="D573" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E573">
-        <v>2.050349933950066</v>
+        <v>2.087715315742805</v>
       </c>
       <c r="F573">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G573">
-        <v>0.003574919302464458</v>
+        <v>0.002835123142408481</v>
       </c>
       <c r="H573">
-        <v>0.003109650066049934</v>
+        <v>0.003192284684257196</v>
       </c>
       <c r="I573">
-        <v>0.3747307635854757</v>
+        <v>0.3028384581512857</v>
       </c>
       <c r="J573">
         <v>0.4526923641452424</v>
       </c>
       <c r="K573">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="L573">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M573">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N573">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O573">
         <v>1</v>
@@ -30040,34 +30040,34 @@
     </row>
     <row r="574" spans="1:16">
       <c r="A574" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B574" t="s">
         <v>52</v>
       </c>
       <c r="C574">
-        <v>2.46037019732591</v>
+        <v>2.513392232045375</v>
       </c>
       <c r="D574" t="s">
         <v>133</v>
       </c>
       <c r="E574">
-        <v>2.524828470599929</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="F574">
         <v>-1</v>
       </c>
       <c r="G574">
-        <v>0.00377962980267409</v>
+        <v>0.003726607767954625</v>
       </c>
       <c r="H574">
-        <v>0.003775171529400071</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="I574">
-        <v>-0.0644582732740191</v>
+        <v>-0.0616884654901666</v>
       </c>
       <c r="J574">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K574">
         <v>1.34</v>
@@ -30085,39 +30085,39 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>57</v>
+        <v>338</v>
       </c>
     </row>
     <row r="575" spans="1:16">
       <c r="A575" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B575" t="s">
         <v>53</v>
       </c>
       <c r="C575">
-        <v>2.37482847059993</v>
+        <v>2.425080697535542</v>
       </c>
       <c r="D575" t="s">
         <v>131</v>
       </c>
       <c r="E575">
-        <v>2.004054575277101</v>
+        <v>2.050349933950066</v>
       </c>
       <c r="F575">
         <v>-1</v>
       </c>
       <c r="G575">
-        <v>0.003625171529400071</v>
+        <v>0.003574919302464458</v>
       </c>
       <c r="H575">
-        <v>0.003155945424722899</v>
+        <v>0.003109650066049934</v>
       </c>
       <c r="I575">
-        <v>0.370773895322829</v>
+        <v>0.3747307635854757</v>
       </c>
       <c r="J575">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K575">
         <v>1.27</v>
@@ -30135,6 +30135,106 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="576" spans="1:16">
+      <c r="A576" s="1">
+        <v>0</v>
+      </c>
+      <c r="B576" t="s">
+        <v>52</v>
+      </c>
+      <c r="C576">
+        <v>2.46037019732591</v>
+      </c>
+      <c r="D576" t="s">
+        <v>133</v>
+      </c>
+      <c r="E576">
+        <v>2.524828470599929</v>
+      </c>
+      <c r="F576">
+        <v>-1</v>
+      </c>
+      <c r="G576">
+        <v>0.00377962980267409</v>
+      </c>
+      <c r="H576">
+        <v>0.003775171529400071</v>
+      </c>
+      <c r="I576">
+        <v>-0.0644582732740191</v>
+      </c>
+      <c r="J576">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K576">
+        <v>1.34</v>
+      </c>
+      <c r="L576">
+        <v>3.12</v>
+      </c>
+      <c r="M576">
+        <v>1.27</v>
+      </c>
+      <c r="N576">
+        <v>3.15</v>
+      </c>
+      <c r="O576">
+        <v>1</v>
+      </c>
+      <c r="P576" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="577" spans="1:16">
+      <c r="A577" s="1">
+        <v>1</v>
+      </c>
+      <c r="B577" t="s">
+        <v>53</v>
+      </c>
+      <c r="C577">
+        <v>2.37482847059993</v>
+      </c>
+      <c r="D577" t="s">
+        <v>131</v>
+      </c>
+      <c r="E577">
+        <v>2.004054575277101</v>
+      </c>
+      <c r="F577">
+        <v>-1</v>
+      </c>
+      <c r="G577">
+        <v>0.003625171529400071</v>
+      </c>
+      <c r="H577">
+        <v>0.003155945424722899</v>
+      </c>
+      <c r="I577">
+        <v>0.370773895322829</v>
+      </c>
+      <c r="J577">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K577">
+        <v>1.27</v>
+      </c>
+      <c r="L577">
+        <v>3</v>
+      </c>
+      <c r="M577">
+        <v>1.17</v>
+      </c>
+      <c r="N577">
+        <v>2.58</v>
+      </c>
+      <c r="O577">
+        <v>1</v>
+      </c>
+      <c r="P577" t="s">
         <v>57</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="339">
   <si>
     <t>trade_time</t>
   </si>
@@ -1388,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P577"/>
+  <dimension ref="A1:P576"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24843,43 +24843,43 @@
         <v>0</v>
       </c>
       <c r="B470" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C470">
-        <v>2.389434326258899</v>
+        <v>3.366448540958179</v>
       </c>
       <c r="D470" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E470">
-        <v>2.819896027013226</v>
+        <v>2.741504344852168</v>
       </c>
       <c r="F470">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G470">
-        <v>0.002010565673741102</v>
+        <v>0.002873551459041821</v>
       </c>
       <c r="H470">
-        <v>0.002360103972986773</v>
+        <v>0.002318495655147832</v>
       </c>
       <c r="I470">
-        <v>0.4304617007543277</v>
+        <v>0.6249441961060107</v>
       </c>
       <c r="J470">
         <v>-0.1839168216105812</v>
       </c>
       <c r="K470">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L470">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M470">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N470">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O470">
         <v>1</v>
@@ -24893,10 +24893,10 @@
         <v>1</v>
       </c>
       <c r="B471" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C471">
-        <v>3.366448540958179</v>
+        <v>3.233574363445438</v>
       </c>
       <c r="D471" t="s">
         <v>129</v>
@@ -24908,22 +24908,22 @@
         <v>-1</v>
       </c>
       <c r="G471">
-        <v>0.002873551459041821</v>
+        <v>0.002766425636554562</v>
       </c>
       <c r="H471">
         <v>0.002318495655147832</v>
       </c>
       <c r="I471">
-        <v>0.6249441961060107</v>
+        <v>0.49207001859327</v>
       </c>
       <c r="J471">
         <v>-0.1839168216105812</v>
       </c>
       <c r="K471">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L471">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M471">
         <v>1.15</v>
@@ -24940,96 +24940,96 @@
     </row>
     <row r="472" spans="1:16">
       <c r="A472" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B472" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C472">
-        <v>3.233574363445438</v>
+        <v>2.407128809696355</v>
       </c>
       <c r="D472" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E472">
-        <v>2.741504344852168</v>
+        <v>2.841369914680043</v>
       </c>
       <c r="F472">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G472">
-        <v>0.002766425636554562</v>
+        <v>0.001992871190303645</v>
       </c>
       <c r="H472">
-        <v>0.002318495655147832</v>
+        <v>0.002338630085319957</v>
       </c>
       <c r="I472">
-        <v>0.49207001859327</v>
+        <v>0.4342411049836872</v>
       </c>
       <c r="J472">
-        <v>-0.1839168216105812</v>
+        <v>-0.2010959317440343</v>
       </c>
       <c r="K472">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L472">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M472">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N472">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O472">
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="473" spans="1:16">
       <c r="A473" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B473" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C473">
-        <v>2.407128809696355</v>
+        <v>3.389468548537006</v>
       </c>
       <c r="D473" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E473">
-        <v>2.841369914680043</v>
+        <v>2.761260321505639</v>
       </c>
       <c r="F473">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G473">
-        <v>0.001992871190303645</v>
+        <v>0.002850531451462994</v>
       </c>
       <c r="H473">
-        <v>0.002338630085319957</v>
+        <v>0.002298739678494361</v>
       </c>
       <c r="I473">
-        <v>0.4342411049836872</v>
+        <v>0.6282082270313669</v>
       </c>
       <c r="J473">
         <v>-0.2010959317440343</v>
       </c>
       <c r="K473">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L473">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M473">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N473">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O473">
         <v>1</v>
@@ -25040,13 +25040,13 @@
     </row>
     <row r="474" spans="1:16">
       <c r="A474" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B474" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C474">
-        <v>3.389468548537006</v>
+        <v>3.255391833314924</v>
       </c>
       <c r="D474" t="s">
         <v>129</v>
@@ -25058,22 +25058,22 @@
         <v>-1</v>
       </c>
       <c r="G474">
-        <v>0.002850531451462994</v>
+        <v>0.002744608166685076</v>
       </c>
       <c r="H474">
         <v>0.002298739678494361</v>
       </c>
       <c r="I474">
-        <v>0.6282082270313669</v>
+        <v>0.4941315118092846</v>
       </c>
       <c r="J474">
         <v>-0.2010959317440343</v>
       </c>
       <c r="K474">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L474">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M474">
         <v>1.15</v>
@@ -25090,96 +25090,96 @@
     </row>
     <row r="475" spans="1:16">
       <c r="A475" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B475" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C475">
-        <v>3.255391833314924</v>
+        <v>2.407323569166959</v>
       </c>
       <c r="D475" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E475">
-        <v>2.761260321505639</v>
+        <v>2.841606273260873</v>
       </c>
       <c r="F475">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G475">
-        <v>0.002744608166685076</v>
+        <v>0.001992676430833041</v>
       </c>
       <c r="H475">
-        <v>0.002298739678494361</v>
+        <v>0.002338393726739127</v>
       </c>
       <c r="I475">
-        <v>0.4941315118092846</v>
+        <v>0.4342827040939135</v>
       </c>
       <c r="J475">
-        <v>-0.2010959317440343</v>
+        <v>-0.2012850186086983</v>
       </c>
       <c r="K475">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L475">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M475">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N475">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O475">
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="476" spans="1:16">
       <c r="A476" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B476" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C476">
-        <v>2.407323569166959</v>
+        <v>3.389721924935656</v>
       </c>
       <c r="D476" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E476">
-        <v>2.841606273260873</v>
+        <v>2.761477771400003</v>
       </c>
       <c r="F476">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G476">
-        <v>0.001992676430833041</v>
+        <v>0.002850278075064344</v>
       </c>
       <c r="H476">
-        <v>0.002338393726739127</v>
+        <v>0.002298522228599997</v>
       </c>
       <c r="I476">
-        <v>0.4342827040939135</v>
+        <v>0.6282441535356531</v>
       </c>
       <c r="J476">
         <v>-0.2012850186086983</v>
       </c>
       <c r="K476">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L476">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M476">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N476">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O476">
         <v>1</v>
@@ -25190,13 +25190,13 @@
     </row>
     <row r="477" spans="1:16">
       <c r="A477" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B477" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C477">
-        <v>3.389721924935656</v>
+        <v>3.255631973633047</v>
       </c>
       <c r="D477" t="s">
         <v>129</v>
@@ -25208,22 +25208,22 @@
         <v>-1</v>
       </c>
       <c r="G477">
-        <v>0.002850278075064344</v>
+        <v>0.002744368026366953</v>
       </c>
       <c r="H477">
         <v>0.002298522228599997</v>
       </c>
       <c r="I477">
-        <v>0.6282441535356531</v>
+        <v>0.4941542022330441</v>
       </c>
       <c r="J477">
         <v>-0.2012850186086983</v>
       </c>
       <c r="K477">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L477">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M477">
         <v>1.15</v>
@@ -25240,96 +25240,96 @@
     </row>
     <row r="478" spans="1:16">
       <c r="A478" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B478" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C478">
-        <v>3.255631973633047</v>
+        <v>2.41122985184961</v>
       </c>
       <c r="D478" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E478">
-        <v>2.761477771400003</v>
+        <v>2.846346907584478</v>
       </c>
       <c r="F478">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G478">
-        <v>0.002744368026366953</v>
+        <v>0.00198877014815039</v>
       </c>
       <c r="H478">
-        <v>0.002298522228599997</v>
+        <v>0.002333653092415522</v>
       </c>
       <c r="I478">
-        <v>0.4941542022330441</v>
+        <v>0.4351170557348678</v>
       </c>
       <c r="J478">
-        <v>-0.2012850186086983</v>
+        <v>-0.2050775260675825</v>
       </c>
       <c r="K478">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L478">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M478">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N478">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O478">
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="479" spans="1:16">
       <c r="A479" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B479" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C479">
-        <v>2.41122985184961</v>
+        <v>3.394803884930561</v>
       </c>
       <c r="D479" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E479">
-        <v>2.846346907584478</v>
+        <v>2.76583915497772</v>
       </c>
       <c r="F479">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G479">
-        <v>0.00198877014815039</v>
+        <v>0.00284519611506944</v>
       </c>
       <c r="H479">
-        <v>0.002333653092415522</v>
+        <v>0.00229416084502228</v>
       </c>
       <c r="I479">
-        <v>0.4351170557348678</v>
+        <v>0.6289647299528411</v>
       </c>
       <c r="J479">
         <v>-0.2050775260675825</v>
       </c>
       <c r="K479">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L479">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M479">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N479">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O479">
         <v>1</v>
@@ -25340,13 +25340,13 @@
     </row>
     <row r="480" spans="1:16">
       <c r="A480" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B480" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C480">
-        <v>3.394803884930561</v>
+        <v>3.26044845810583</v>
       </c>
       <c r="D480" t="s">
         <v>129</v>
@@ -25358,22 +25358,22 @@
         <v>-1</v>
       </c>
       <c r="G480">
-        <v>0.00284519611506944</v>
+        <v>0.00273955154189417</v>
       </c>
       <c r="H480">
         <v>0.00229416084502228</v>
       </c>
       <c r="I480">
-        <v>0.6289647299528411</v>
+        <v>0.4946093031281102</v>
       </c>
       <c r="J480">
         <v>-0.2050775260675825</v>
       </c>
       <c r="K480">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L480">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M480">
         <v>1.15</v>
@@ -25390,96 +25390,96 @@
     </row>
     <row r="481" spans="1:16">
       <c r="A481" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B481" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C481">
-        <v>3.26044845810583</v>
+        <v>2.414401903996001</v>
       </c>
       <c r="D481" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E481">
-        <v>2.76583915497772</v>
+        <v>2.850196485432039</v>
       </c>
       <c r="F481">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G481">
-        <v>0.00273955154189417</v>
+        <v>0.001985598096004</v>
       </c>
       <c r="H481">
-        <v>0.00229416084502228</v>
+        <v>0.00232980351456796</v>
       </c>
       <c r="I481">
-        <v>0.4946093031281102</v>
+        <v>0.4357945814360389</v>
       </c>
       <c r="J481">
-        <v>-0.2050775260675825</v>
+        <v>-0.2081571883456315</v>
       </c>
       <c r="K481">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L481">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M481">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N481">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O481">
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="482" spans="1:16">
       <c r="A482" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B482" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C482">
-        <v>2.414401903996001</v>
+        <v>3.398930632383146</v>
       </c>
       <c r="D482" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E482">
-        <v>2.850196485432039</v>
+        <v>2.769380766597476</v>
       </c>
       <c r="F482">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G482">
-        <v>0.001985598096004</v>
+        <v>0.002841069367616854</v>
       </c>
       <c r="H482">
-        <v>0.00232980351456796</v>
+        <v>0.002290619233402524</v>
       </c>
       <c r="I482">
-        <v>0.4357945814360389</v>
+        <v>0.6295498657856702</v>
       </c>
       <c r="J482">
         <v>-0.2081571883456315</v>
       </c>
       <c r="K482">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L482">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M482">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N482">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O482">
         <v>1</v>
@@ -25490,13 +25490,13 @@
     </row>
     <row r="483" spans="1:16">
       <c r="A483" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B483" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C483">
-        <v>3.398930632383146</v>
+        <v>3.264359629198952</v>
       </c>
       <c r="D483" t="s">
         <v>129</v>
@@ -25508,22 +25508,22 @@
         <v>-1</v>
       </c>
       <c r="G483">
-        <v>0.002841069367616854</v>
+        <v>0.002735640370801048</v>
       </c>
       <c r="H483">
         <v>0.002290619233402524</v>
       </c>
       <c r="I483">
-        <v>0.6295498657856702</v>
+        <v>0.4949788626014757</v>
       </c>
       <c r="J483">
         <v>-0.2081571883456315</v>
       </c>
       <c r="K483">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L483">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M483">
         <v>1.15</v>
@@ -25540,96 +25540,96 @@
     </row>
     <row r="484" spans="1:16">
       <c r="A484" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B484" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C484">
-        <v>3.264359629198952</v>
+        <v>2.400941737549309</v>
       </c>
       <c r="D484" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E484">
-        <v>2.769380766597476</v>
+        <v>2.833861331977317</v>
       </c>
       <c r="F484">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G484">
-        <v>0.002735640370801048</v>
+        <v>0.001999058262450691</v>
       </c>
       <c r="H484">
-        <v>0.002290619233402524</v>
+        <v>0.002346138668022683</v>
       </c>
       <c r="I484">
-        <v>0.4949788626014757</v>
+        <v>0.4329195944280078</v>
       </c>
       <c r="J484">
-        <v>-0.2081571883456315</v>
+        <v>-0.1950890655818535</v>
       </c>
       <c r="K484">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L484">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M484">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N484">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O484">
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="485" spans="1:16">
       <c r="A485" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B485" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C485">
-        <v>2.400941737549309</v>
+        <v>3.381419347879684</v>
       </c>
       <c r="D485" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E485">
-        <v>2.833861331977317</v>
+        <v>2.754352425419131</v>
       </c>
       <c r="F485">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G485">
-        <v>0.001999058262450691</v>
+        <v>0.002858580652120316</v>
       </c>
       <c r="H485">
-        <v>0.002346138668022683</v>
+        <v>0.002305647574580868</v>
       </c>
       <c r="I485">
-        <v>0.4329195944280078</v>
+        <v>0.6270669224605525</v>
       </c>
       <c r="J485">
         <v>-0.1950890655818535</v>
       </c>
       <c r="K485">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L485">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M485">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N485">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O485">
         <v>1</v>
@@ -25640,13 +25640,13 @@
     </row>
     <row r="486" spans="1:16">
       <c r="A486" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B486" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C486">
-        <v>3.381419347879684</v>
+        <v>3.247763113288954</v>
       </c>
       <c r="D486" t="s">
         <v>129</v>
@@ -25658,22 +25658,22 @@
         <v>-1</v>
       </c>
       <c r="G486">
-        <v>0.002858580652120316</v>
+        <v>0.002752236886711046</v>
       </c>
       <c r="H486">
         <v>0.002305647574580868</v>
       </c>
       <c r="I486">
-        <v>0.6270669224605525</v>
+        <v>0.4934106878698228</v>
       </c>
       <c r="J486">
         <v>-0.1950890655818535</v>
       </c>
       <c r="K486">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L486">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M486">
         <v>1.15</v>
@@ -25690,96 +25690,96 @@
     </row>
     <row r="487" spans="1:16">
       <c r="A487" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B487" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C487">
-        <v>3.247763113288954</v>
+        <v>2.416869377367424</v>
       </c>
       <c r="D487" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E487">
-        <v>2.754352425419131</v>
+        <v>2.853190991950757</v>
       </c>
       <c r="F487">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G487">
-        <v>0.002752236886711046</v>
+        <v>0.001983130622632577</v>
       </c>
       <c r="H487">
-        <v>0.002305647574580868</v>
+        <v>0.002326809008049243</v>
       </c>
       <c r="I487">
-        <v>0.4934106878698228</v>
+        <v>0.4363216145833326</v>
       </c>
       <c r="J487">
-        <v>-0.1950890655818535</v>
+        <v>-0.2105527935606056</v>
       </c>
       <c r="K487">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L487">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M487">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N487">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O487">
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="488" spans="1:16">
       <c r="A488" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B488" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C488">
-        <v>2.416869377367424</v>
+        <v>3.402140743371211</v>
       </c>
       <c r="D488" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E488">
-        <v>2.853190991950757</v>
+        <v>2.772135712594696</v>
       </c>
       <c r="F488">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G488">
-        <v>0.001983130622632577</v>
+        <v>0.002837859256628789</v>
       </c>
       <c r="H488">
-        <v>0.002326809008049243</v>
+        <v>0.002287864287405304</v>
       </c>
       <c r="I488">
-        <v>0.4363216145833326</v>
+        <v>0.6300050307765153</v>
       </c>
       <c r="J488">
         <v>-0.2105527935606056</v>
       </c>
       <c r="K488">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L488">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M488">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N488">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O488">
         <v>1</v>
@@ -25790,13 +25790,13 @@
     </row>
     <row r="489" spans="1:16">
       <c r="A489" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B489" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C489">
-        <v>3.402140743371211</v>
+        <v>3.267402047821969</v>
       </c>
       <c r="D489" t="s">
         <v>129</v>
@@ -25808,22 +25808,22 @@
         <v>-1</v>
       </c>
       <c r="G489">
-        <v>0.002837859256628789</v>
+        <v>0.002732597952178031</v>
       </c>
       <c r="H489">
         <v>0.002287864287405304</v>
       </c>
       <c r="I489">
-        <v>0.6300050307765153</v>
+        <v>0.495266335227273</v>
       </c>
       <c r="J489">
         <v>-0.2105527935606056</v>
       </c>
       <c r="K489">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L489">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M489">
         <v>1.15</v>
@@ -25840,96 +25840,96 @@
     </row>
     <row r="490" spans="1:16">
       <c r="A490" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B490" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C490">
-        <v>3.267402047821969</v>
+        <v>2.427926332334885</v>
       </c>
       <c r="D490" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E490">
-        <v>2.772135712594696</v>
+        <v>2.866609626620006</v>
       </c>
       <c r="F490">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G490">
-        <v>0.002732597952178031</v>
+        <v>0.001972073667665115</v>
       </c>
       <c r="H490">
-        <v>0.002287864287405304</v>
+        <v>0.002313390373379994</v>
       </c>
       <c r="I490">
-        <v>0.495266335227273</v>
+        <v>0.4386832942851204</v>
       </c>
       <c r="J490">
-        <v>-0.2105527935606056</v>
+        <v>-0.2212877012960047</v>
       </c>
       <c r="K490">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L490">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M490">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N490">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O490">
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="491" spans="1:16">
       <c r="A491" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B491" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C491">
-        <v>2.427926332334885</v>
+        <v>3.416525519736647</v>
       </c>
       <c r="D491" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E491">
-        <v>2.866609626620006</v>
+        <v>2.838906610516326</v>
       </c>
       <c r="F491">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G491">
-        <v>0.001972073667665115</v>
+        <v>0.002823474480263354</v>
       </c>
       <c r="H491">
-        <v>0.002313390373379994</v>
+        <v>0.002321093389483675</v>
       </c>
       <c r="I491">
-        <v>0.4386832942851204</v>
+        <v>0.577618909220321</v>
       </c>
       <c r="J491">
         <v>-0.2212877012960047</v>
       </c>
       <c r="K491">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L491">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M491">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N491">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O491">
         <v>1</v>
@@ -25940,46 +25940,46 @@
     </row>
     <row r="492" spans="1:16">
       <c r="A492" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B492" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C492">
-        <v>3.416525519736647</v>
+        <v>3.281035380645926</v>
       </c>
       <c r="D492" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E492">
-        <v>2.784480856490405</v>
+        <v>2.838906610516326</v>
       </c>
       <c r="F492">
         <v>-1</v>
       </c>
       <c r="G492">
-        <v>0.002823474480263354</v>
+        <v>0.002718964619354074</v>
       </c>
       <c r="H492">
-        <v>0.002275519143509595</v>
+        <v>0.002321093389483675</v>
       </c>
       <c r="I492">
-        <v>0.6320446632462415</v>
+        <v>0.4421287701296004</v>
       </c>
       <c r="J492">
         <v>-0.2212877012960047</v>
       </c>
       <c r="K492">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L492">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M492">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N492">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O492">
         <v>1</v>
@@ -25990,96 +25990,96 @@
     </row>
     <row r="493" spans="1:16">
       <c r="A493" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B493" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C493">
-        <v>3.281035380645926</v>
+        <v>2.43983969591803</v>
       </c>
       <c r="D493" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E493">
-        <v>2.784480856490405</v>
+        <v>2.88106759213353</v>
       </c>
       <c r="F493">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G493">
-        <v>0.002718964619354074</v>
+        <v>0.001960160304081971</v>
       </c>
       <c r="H493">
-        <v>0.002275519143509595</v>
+        <v>0.002298932407866469</v>
       </c>
       <c r="I493">
-        <v>0.4965545241555209</v>
+        <v>0.441227896215501</v>
       </c>
       <c r="J493">
-        <v>-0.2212877012960047</v>
+        <v>-0.2328540737068246</v>
       </c>
       <c r="K493">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L493">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M493">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N493">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O493">
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="494" spans="1:16">
       <c r="A494" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B494" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C494">
-        <v>2.43983969591803</v>
+        <v>3.432024458767145</v>
       </c>
       <c r="D494" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E494">
-        <v>2.88106759213353</v>
+        <v>2.852439266236985</v>
       </c>
       <c r="F494">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G494">
-        <v>0.001960160304081971</v>
+        <v>0.002807975541232855</v>
       </c>
       <c r="H494">
-        <v>0.002298932407866469</v>
+        <v>0.002307560733763015</v>
       </c>
       <c r="I494">
-        <v>0.441227896215501</v>
+        <v>0.5795851925301605</v>
       </c>
       <c r="J494">
         <v>-0.2328540737068246</v>
       </c>
       <c r="K494">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L494">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M494">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N494">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O494">
         <v>1</v>
@@ -26090,46 +26090,46 @@
     </row>
     <row r="495" spans="1:16">
       <c r="A495" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B495" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C495">
-        <v>3.432024458767145</v>
+        <v>3.295724673607667</v>
       </c>
       <c r="D495" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E495">
-        <v>2.797782184762848</v>
+        <v>2.852439266236985</v>
       </c>
       <c r="F495">
         <v>-1</v>
       </c>
       <c r="G495">
-        <v>0.002807975541232855</v>
+        <v>0.002704275326392333</v>
       </c>
       <c r="H495">
-        <v>0.002262217815237151</v>
+        <v>0.002307560733763015</v>
       </c>
       <c r="I495">
-        <v>0.634242274004297</v>
+        <v>0.4432854073706824</v>
       </c>
       <c r="J495">
         <v>-0.2328540737068246</v>
       </c>
       <c r="K495">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L495">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M495">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N495">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O495">
         <v>1</v>
@@ -26140,96 +26140,96 @@
     </row>
     <row r="496" spans="1:16">
       <c r="A496" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B496" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C496">
-        <v>3.295724673607667</v>
+        <v>2.478555931094635</v>
       </c>
       <c r="D496" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E496">
-        <v>2.797782184762848</v>
+        <v>2.928053314435237</v>
       </c>
       <c r="F496">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G496">
-        <v>0.002704275326392333</v>
+        <v>0.001921444068905365</v>
       </c>
       <c r="H496">
-        <v>0.002262217815237151</v>
+        <v>0.002251946685564763</v>
       </c>
       <c r="I496">
-        <v>0.497942488844819</v>
+        <v>0.4494973833406015</v>
       </c>
       <c r="J496">
-        <v>-0.2328540737068246</v>
+        <v>-0.2704426515481894</v>
       </c>
       <c r="K496">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L496">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M496">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="N496">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="O496">
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="497" spans="1:16">
       <c r="A497" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B497" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C497">
-        <v>2.478555931094635</v>
+        <v>3.482393153074574</v>
       </c>
       <c r="D497" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E497">
-        <v>2.928053314435237</v>
+        <v>2.896417902311382</v>
       </c>
       <c r="F497">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G497">
-        <v>0.001921444068905365</v>
+        <v>0.002757606846925426</v>
       </c>
       <c r="H497">
-        <v>0.002251946685564763</v>
+        <v>0.002263582097688619</v>
       </c>
       <c r="I497">
-        <v>0.4494973833406015</v>
+        <v>0.5859752507631923</v>
       </c>
       <c r="J497">
         <v>-0.2704426515481894</v>
       </c>
       <c r="K497">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L497">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M497">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N497">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O497">
         <v>1</v>
@@ -26240,13 +26240,13 @@
     </row>
     <row r="498" spans="1:16">
       <c r="A498" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B498" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C498">
-        <v>3.482393153074574</v>
+        <v>3.343462167466201</v>
       </c>
       <c r="D498" t="s">
         <v>131</v>
@@ -26258,22 +26258,22 @@
         <v>-1</v>
       </c>
       <c r="G498">
-        <v>0.002757606846925426</v>
+        <v>0.002656537832533799</v>
       </c>
       <c r="H498">
         <v>0.002263582097688619</v>
       </c>
       <c r="I498">
-        <v>0.5859752507631923</v>
+        <v>0.447044265154819</v>
       </c>
       <c r="J498">
         <v>-0.2704426515481894</v>
       </c>
       <c r="K498">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L498">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M498">
         <v>1.17</v>
@@ -26290,96 +26290,96 @@
     </row>
     <row r="499" spans="1:16">
       <c r="A499" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B499" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C499">
-        <v>3.343462167466201</v>
+        <v>2.492450104171095</v>
       </c>
       <c r="D499" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E499">
-        <v>2.896417902311382</v>
+        <v>2.944915174964921</v>
       </c>
       <c r="F499">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G499">
-        <v>0.002656537832533799</v>
+        <v>0.001907549895828906</v>
       </c>
       <c r="H499">
-        <v>0.002263582097688619</v>
+        <v>0.002235084825035079</v>
       </c>
       <c r="I499">
-        <v>0.447044265154819</v>
+        <v>0.4524650707938256</v>
       </c>
       <c r="J499">
-        <v>-0.2704426515481894</v>
+        <v>-0.2839321399719367</v>
       </c>
       <c r="K499">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L499">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M499">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N499">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O499">
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="500" spans="1:16">
       <c r="A500" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B500" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C500">
-        <v>2.492450104171095</v>
+        <v>3.500469067562396</v>
       </c>
       <c r="D500" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E500">
-        <v>2.944915174964921</v>
+        <v>2.912200603767166</v>
       </c>
       <c r="F500">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G500">
-        <v>0.001907549895828906</v>
+        <v>0.002739530932437605</v>
       </c>
       <c r="H500">
-        <v>0.002235084825035079</v>
+        <v>0.002247799396232834</v>
       </c>
       <c r="I500">
-        <v>0.4524650707938256</v>
+        <v>0.5882684637952296</v>
       </c>
       <c r="J500">
         <v>-0.2839321399719367</v>
       </c>
       <c r="K500">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L500">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M500">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N500">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O500">
         <v>1</v>
@@ -26390,13 +26390,13 @@
     </row>
     <row r="501" spans="1:16">
       <c r="A501" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B501" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C501">
-        <v>3.500469067562396</v>
+        <v>3.36059381776436</v>
       </c>
       <c r="D501" t="s">
         <v>131</v>
@@ -26408,22 +26408,22 @@
         <v>-1</v>
       </c>
       <c r="G501">
-        <v>0.002739530932437605</v>
+        <v>0.002639406182235641</v>
       </c>
       <c r="H501">
         <v>0.002247799396232834</v>
       </c>
       <c r="I501">
-        <v>0.5882684637952296</v>
+        <v>0.4483932139971936</v>
       </c>
       <c r="J501">
         <v>-0.2839321399719367</v>
       </c>
       <c r="K501">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L501">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M501">
         <v>1.17</v>
@@ -26440,96 +26440,96 @@
     </row>
     <row r="502" spans="1:16">
       <c r="A502" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B502" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C502">
-        <v>3.36059381776436</v>
+        <v>2.485588290136117</v>
       </c>
       <c r="D502" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E502">
-        <v>2.912200603767166</v>
+        <v>2.936587730747715</v>
       </c>
       <c r="F502">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G502">
-        <v>0.002639406182235641</v>
+        <v>0.001914411709863883</v>
       </c>
       <c r="H502">
-        <v>0.002247799396232834</v>
+        <v>0.002243412269252285</v>
       </c>
       <c r="I502">
-        <v>0.4483932139971936</v>
+        <v>0.4509994406115978</v>
       </c>
       <c r="J502">
-        <v>-0.2839321399719367</v>
+        <v>-0.2772701845981717</v>
       </c>
       <c r="K502">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L502">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M502">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N502">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O502">
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="503" spans="1:16">
       <c r="A503" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B503" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C503">
-        <v>2.485588290136117</v>
+        <v>3.49154204736155</v>
       </c>
       <c r="D503" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E503">
-        <v>2.936587730747715</v>
+        <v>2.904406115979861</v>
       </c>
       <c r="F503">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G503">
-        <v>0.001914411709863883</v>
+        <v>0.00274845795263845</v>
       </c>
       <c r="H503">
-        <v>0.002243412269252285</v>
+        <v>0.002255593884020139</v>
       </c>
       <c r="I503">
-        <v>0.4509994406115978</v>
+        <v>0.5871359313816891</v>
       </c>
       <c r="J503">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K503">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L503">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M503">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N503">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O503">
         <v>1</v>
@@ -26540,13 +26540,13 @@
     </row>
     <row r="504" spans="1:16">
       <c r="A504" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B504" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C504">
-        <v>3.49154204736155</v>
+        <v>3.352133134439678</v>
       </c>
       <c r="D504" t="s">
         <v>131</v>
@@ -26558,22 +26558,22 @@
         <v>-1</v>
       </c>
       <c r="G504">
-        <v>0.00274845795263845</v>
+        <v>0.002647866865560322</v>
       </c>
       <c r="H504">
         <v>0.002255593884020139</v>
       </c>
       <c r="I504">
-        <v>0.5871359313816891</v>
+        <v>0.4477270184598172</v>
       </c>
       <c r="J504">
         <v>-0.2772701845981717</v>
       </c>
       <c r="K504">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L504">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M504">
         <v>1.17</v>
@@ -26590,96 +26590,96 @@
     </row>
     <row r="505" spans="1:16">
       <c r="A505" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B505" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C505">
-        <v>3.352133134439678</v>
+        <v>2.483803138304734</v>
       </c>
       <c r="D505" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E505">
-        <v>2.904406115979861</v>
+        <v>2.934421284350405</v>
       </c>
       <c r="F505">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G505">
-        <v>0.002647866865560322</v>
+        <v>0.001916196861695266</v>
       </c>
       <c r="H505">
-        <v>0.002255593884020139</v>
+        <v>0.002245578715649595</v>
       </c>
       <c r="I505">
-        <v>0.4477270184598172</v>
+        <v>0.4506181460456711</v>
       </c>
       <c r="J505">
-        <v>-0.2772701845981717</v>
+        <v>-0.2755370274803244</v>
       </c>
       <c r="K505">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L505">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M505">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N505">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O505">
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="506" spans="1:16">
       <c r="A506" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B506" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C506">
-        <v>2.483803138304734</v>
+        <v>3.489219616823635</v>
       </c>
       <c r="D506" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E506">
-        <v>2.934421284350405</v>
+        <v>2.902378322151979</v>
       </c>
       <c r="F506">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G506">
-        <v>0.001916196861695266</v>
+        <v>0.002750780383176366</v>
       </c>
       <c r="H506">
-        <v>0.002245578715649595</v>
+        <v>0.002257621677848021</v>
       </c>
       <c r="I506">
-        <v>0.4506181460456711</v>
+        <v>0.5868412946716552</v>
       </c>
       <c r="J506">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K506">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L506">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M506">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N506">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O506">
         <v>1</v>
@@ -26690,13 +26690,13 @@
     </row>
     <row r="507" spans="1:16">
       <c r="A507" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B507" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C507">
-        <v>3.489219616823635</v>
+        <v>3.349932024900012</v>
       </c>
       <c r="D507" t="s">
         <v>131</v>
@@ -26708,22 +26708,22 @@
         <v>-1</v>
       </c>
       <c r="G507">
-        <v>0.002750780383176366</v>
+        <v>0.002650067975099988</v>
       </c>
       <c r="H507">
         <v>0.002257621677848021</v>
       </c>
       <c r="I507">
-        <v>0.5868412946716552</v>
+        <v>0.4475537027480323</v>
       </c>
       <c r="J507">
         <v>-0.2755370274803244</v>
       </c>
       <c r="K507">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L507">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M507">
         <v>1.17</v>
@@ -26740,96 +26740,96 @@
     </row>
     <row r="508" spans="1:16">
       <c r="A508" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B508" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C508">
-        <v>3.349932024900012</v>
+        <v>2.455324757264537</v>
       </c>
       <c r="D508" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E508">
-        <v>2.902378322151979</v>
+        <v>2.899860142311331</v>
       </c>
       <c r="F508">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G508">
-        <v>0.002650067975099988</v>
+        <v>0.001944675242735464</v>
       </c>
       <c r="H508">
-        <v>0.002257621677848021</v>
+        <v>0.002280139857688669</v>
       </c>
       <c r="I508">
-        <v>0.4475537027480323</v>
+        <v>0.4445353850467941</v>
       </c>
       <c r="J508">
-        <v>-0.2755370274803244</v>
+        <v>-0.2478881138490649</v>
       </c>
       <c r="K508">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L508">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M508">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N508">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O508">
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="509" spans="1:16">
       <c r="A509" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B509" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C509">
-        <v>2.455324757264537</v>
+        <v>3.452170072557747</v>
       </c>
       <c r="D509" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E509">
-        <v>2.899860142311331</v>
+        <v>2.870029093203406</v>
       </c>
       <c r="F509">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G509">
-        <v>0.001944675242735464</v>
+        <v>0.002787829927442253</v>
       </c>
       <c r="H509">
-        <v>0.002280139857688669</v>
+        <v>0.002289970906796594</v>
       </c>
       <c r="I509">
-        <v>0.4445353850467941</v>
+        <v>0.5821409793543411</v>
       </c>
       <c r="J509">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K509">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L509">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M509">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N509">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O509">
         <v>1</v>
@@ -26840,13 +26840,13 @@
     </row>
     <row r="510" spans="1:16">
       <c r="A510" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B510" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C510">
-        <v>3.452170072557747</v>
+        <v>3.314817904588312</v>
       </c>
       <c r="D510" t="s">
         <v>131</v>
@@ -26858,22 +26858,22 @@
         <v>-1</v>
       </c>
       <c r="G510">
-        <v>0.002787829927442253</v>
+        <v>0.002685182095411688</v>
       </c>
       <c r="H510">
         <v>0.002289970906796594</v>
       </c>
       <c r="I510">
-        <v>0.5821409793543411</v>
+        <v>0.4447888113849063</v>
       </c>
       <c r="J510">
         <v>-0.2478881138490649</v>
       </c>
       <c r="K510">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L510">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M510">
         <v>1.17</v>
@@ -26890,96 +26890,96 @@
     </row>
     <row r="511" spans="1:16">
       <c r="A511" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B511" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C511">
-        <v>3.314817904588312</v>
+        <v>2.38683909149</v>
       </c>
       <c r="D511" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E511">
-        <v>2.870029093203406</v>
+        <v>2.816746470254853</v>
       </c>
       <c r="F511">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G511">
-        <v>0.002685182095411688</v>
+        <v>0.002013160908510001</v>
       </c>
       <c r="H511">
-        <v>0.002289970906796594</v>
+        <v>0.002363253529745146</v>
       </c>
       <c r="I511">
-        <v>0.4447888113849063</v>
+        <v>0.4299073787648537</v>
       </c>
       <c r="J511">
-        <v>-0.2478881138490649</v>
+        <v>-0.181397176203883</v>
       </c>
       <c r="K511">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L511">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M511">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N511">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O511">
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="512" spans="1:16">
       <c r="A512" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B512" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C512">
-        <v>2.38683909149</v>
+        <v>3.363072216113203</v>
       </c>
       <c r="D512" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E512">
-        <v>2.816746470254853</v>
+        <v>2.792234696158543</v>
       </c>
       <c r="F512">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G512">
-        <v>0.002013160908510001</v>
+        <v>0.002876927783886797</v>
       </c>
       <c r="H512">
-        <v>0.002363253529745146</v>
+        <v>0.002367765303841457</v>
       </c>
       <c r="I512">
-        <v>0.4299073787648537</v>
+        <v>0.5708375199546598</v>
       </c>
       <c r="J512">
         <v>-0.181397176203883</v>
       </c>
       <c r="K512">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L512">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M512">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N512">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O512">
         <v>1</v>
@@ -26990,13 +26990,13 @@
     </row>
     <row r="513" spans="1:16">
       <c r="A513" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B513" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C513">
-        <v>3.363072216113203</v>
+        <v>3.230374413778931</v>
       </c>
       <c r="D513" t="s">
         <v>131</v>
@@ -27008,22 +27008,22 @@
         <v>-1</v>
       </c>
       <c r="G513">
-        <v>0.002876927783886797</v>
+        <v>0.002769625586221069</v>
       </c>
       <c r="H513">
         <v>0.002367765303841457</v>
       </c>
       <c r="I513">
-        <v>0.5708375199546598</v>
+        <v>0.4381397176203881</v>
       </c>
       <c r="J513">
         <v>-0.181397176203883</v>
       </c>
       <c r="K513">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L513">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M513">
         <v>1.17</v>
@@ -27040,96 +27040,96 @@
     </row>
     <row r="514" spans="1:16">
       <c r="A514" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B514" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C514">
-        <v>3.230374413778931</v>
+        <v>2.332831092936091</v>
       </c>
       <c r="D514" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E514">
-        <v>2.792234696158543</v>
+        <v>2.751202782689431</v>
       </c>
       <c r="F514">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G514">
-        <v>0.002769625586221069</v>
+        <v>0.002067168907063909</v>
       </c>
       <c r="H514">
-        <v>0.002367765303841457</v>
+        <v>0.002428797217310569</v>
       </c>
       <c r="I514">
-        <v>0.4381397176203881</v>
+        <v>0.4183716897533394</v>
       </c>
       <c r="J514">
-        <v>-0.181397176203883</v>
+        <v>-0.1289622261515449</v>
       </c>
       <c r="K514">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L514">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M514">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N514">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O514">
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="515" spans="1:16">
       <c r="A515" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B515" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C515">
-        <v>2.332831092936091</v>
+        <v>3.29280938304307</v>
       </c>
       <c r="D515" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E515">
-        <v>2.751202782689431</v>
+        <v>2.730885804597308</v>
       </c>
       <c r="F515">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G515">
-        <v>0.002067168907063909</v>
+        <v>0.00294719061695693</v>
       </c>
       <c r="H515">
-        <v>0.002428797217310569</v>
+        <v>0.002429114195402692</v>
       </c>
       <c r="I515">
-        <v>0.4183716897533394</v>
+        <v>0.5619235784457626</v>
       </c>
       <c r="J515">
         <v>-0.1289622261515449</v>
       </c>
       <c r="K515">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L515">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M515">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N515">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O515">
         <v>1</v>
@@ -27140,13 +27140,13 @@
     </row>
     <row r="516" spans="1:16">
       <c r="A516" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B516" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C516">
-        <v>3.29280938304307</v>
+        <v>3.163782027212462</v>
       </c>
       <c r="D516" t="s">
         <v>131</v>
@@ -27158,22 +27158,22 @@
         <v>-1</v>
       </c>
       <c r="G516">
-        <v>0.00294719061695693</v>
+        <v>0.002836217972787538</v>
       </c>
       <c r="H516">
         <v>0.002429114195402692</v>
       </c>
       <c r="I516">
-        <v>0.5619235784457626</v>
+        <v>0.4328962226151543</v>
       </c>
       <c r="J516">
         <v>-0.1289622261515449</v>
       </c>
       <c r="K516">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L516">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M516">
         <v>1.17</v>
@@ -27190,96 +27190,96 @@
     </row>
     <row r="517" spans="1:16">
       <c r="A517" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B517" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C517">
-        <v>3.163782027212462</v>
+        <v>2.292718610119939</v>
       </c>
       <c r="D517" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E517">
-        <v>2.730885804597308</v>
+        <v>2.702522585097013</v>
       </c>
       <c r="F517">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G517">
-        <v>0.002836217972787538</v>
+        <v>0.002107281389880062</v>
       </c>
       <c r="H517">
-        <v>0.002429114195402692</v>
+        <v>0.002477477414902987</v>
       </c>
       <c r="I517">
-        <v>0.4328962226151543</v>
+        <v>0.4098039749770739</v>
       </c>
       <c r="J517">
-        <v>-0.1289622261515449</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K517">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L517">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M517">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N517">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O517">
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="518" spans="1:16">
       <c r="A518" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B518" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C518">
-        <v>2.292718610119939</v>
+        <v>3.240624211223998</v>
       </c>
       <c r="D518" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E518">
-        <v>2.702522585097013</v>
+        <v>2.685321139650804</v>
       </c>
       <c r="F518">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G518">
-        <v>0.002107281389880062</v>
+        <v>0.002999375788776002</v>
       </c>
       <c r="H518">
-        <v>0.002477477414902987</v>
+        <v>0.002474678860349197</v>
       </c>
       <c r="I518">
-        <v>0.4098039749770739</v>
+        <v>0.5553030715731939</v>
       </c>
       <c r="J518">
         <v>-0.09001806807761016</v>
       </c>
       <c r="K518">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L518">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M518">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N518">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O518">
         <v>1</v>
@@ -27290,13 +27290,13 @@
     </row>
     <row r="519" spans="1:16">
       <c r="A519" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B519" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C519">
-        <v>3.240624211223998</v>
+        <v>3.114322946458565</v>
       </c>
       <c r="D519" t="s">
         <v>131</v>
@@ -27308,22 +27308,22 @@
         <v>-1</v>
       </c>
       <c r="G519">
-        <v>0.002999375788776002</v>
+        <v>0.002885677053541435</v>
       </c>
       <c r="H519">
         <v>0.002474678860349197</v>
       </c>
       <c r="I519">
-        <v>0.5553030715731939</v>
+        <v>0.429001806807761</v>
       </c>
       <c r="J519">
         <v>-0.09001806807761016</v>
       </c>
       <c r="K519">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L519">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M519">
         <v>1.17</v>
@@ -27340,96 +27340,96 @@
     </row>
     <row r="520" spans="1:16">
       <c r="A520" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B520" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C520">
-        <v>3.114322946458565</v>
+        <v>2.190845625202192</v>
       </c>
       <c r="D520" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E520">
-        <v>2.685321139650804</v>
+        <v>2.57889032184732</v>
       </c>
       <c r="F520">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G520">
-        <v>0.002885677053541435</v>
+        <v>0.002209154374797808</v>
       </c>
       <c r="H520">
-        <v>0.002474678860349197</v>
+        <v>0.00260110967815268</v>
       </c>
       <c r="I520">
-        <v>0.429001806807761</v>
+        <v>0.3880446966451281</v>
       </c>
       <c r="J520">
-        <v>-0.09001806807761016</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K520">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L520">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M520">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N520">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O520">
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="521" spans="1:16">
       <c r="A521" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B521" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C521">
-        <v>2.190845625202192</v>
+        <v>3.108090425020327</v>
       </c>
       <c r="D521" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E521">
-        <v>2.57889032184732</v>
+        <v>2.569601341249092</v>
       </c>
       <c r="F521">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G521">
-        <v>0.002209154374797808</v>
+        <v>0.003131909574979673</v>
       </c>
       <c r="H521">
-        <v>0.00260110967815268</v>
+        <v>0.002590398658750909</v>
       </c>
       <c r="I521">
-        <v>0.3880446966451281</v>
+        <v>0.5384890837712355</v>
       </c>
       <c r="J521">
         <v>0.008887742522143843</v>
       </c>
       <c r="K521">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L521">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M521">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N521">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O521">
         <v>1</v>
@@ -27440,13 +27440,13 @@
     </row>
     <row r="522" spans="1:16">
       <c r="A522" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B522" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C522">
-        <v>3.108090425020327</v>
+        <v>2.988712566996877</v>
       </c>
       <c r="D522" t="s">
         <v>131</v>
@@ -27458,22 +27458,22 @@
         <v>-1</v>
       </c>
       <c r="G522">
-        <v>0.003131909574979673</v>
+        <v>0.003011287433003123</v>
       </c>
       <c r="H522">
         <v>0.002590398658750909</v>
       </c>
       <c r="I522">
-        <v>0.5384890837712355</v>
+        <v>0.4191112257477858</v>
       </c>
       <c r="J522">
         <v>0.008887742522143843</v>
       </c>
       <c r="K522">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L522">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M522">
         <v>1.17</v>
@@ -27490,96 +27490,96 @@
     </row>
     <row r="523" spans="1:16">
       <c r="A523" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B523" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C523">
-        <v>2.988712566996877</v>
+        <v>2.151298027264343</v>
       </c>
       <c r="D523" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E523">
-        <v>2.569601341249092</v>
+        <v>2.530895664155756</v>
       </c>
       <c r="F523">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G523">
-        <v>0.003011287433003123</v>
+        <v>0.002248701972735657</v>
       </c>
       <c r="H523">
-        <v>0.002590398658750909</v>
+        <v>0.002649104335844244</v>
       </c>
       <c r="I523">
-        <v>0.4191112257477858</v>
+        <v>0.3795976368914125</v>
       </c>
       <c r="J523">
-        <v>0.008887742522143843</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K523">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L523">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M523">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N523">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O523">
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="524" spans="1:16">
       <c r="A524" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B524" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C524">
-        <v>2.151298027264343</v>
+        <v>3.056640151974971</v>
       </c>
       <c r="D524" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E524">
-        <v>2.530895664155756</v>
+        <v>2.524678341649788</v>
       </c>
       <c r="F524">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G524">
-        <v>0.002248701972735657</v>
+        <v>0.00318335984802503</v>
       </c>
       <c r="H524">
-        <v>0.002649104335844244</v>
+        <v>0.002635321658350212</v>
       </c>
       <c r="I524">
-        <v>0.3795976368914125</v>
+        <v>0.5319618103251829</v>
       </c>
       <c r="J524">
         <v>0.04728346867539508</v>
       </c>
       <c r="K524">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L524">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M524">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N524">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27590,13 +27590,13 @@
     </row>
     <row r="525" spans="1:16">
       <c r="A525" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B525" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C525">
-        <v>3.056640151974971</v>
+        <v>2.939949994782248</v>
       </c>
       <c r="D525" t="s">
         <v>131</v>
@@ -27608,22 +27608,22 @@
         <v>-1</v>
       </c>
       <c r="G525">
-        <v>0.00318335984802503</v>
+        <v>0.003060050005217752</v>
       </c>
       <c r="H525">
         <v>0.002635321658350212</v>
       </c>
       <c r="I525">
-        <v>0.5319618103251829</v>
+        <v>0.4152716531324603</v>
       </c>
       <c r="J525">
         <v>0.04728346867539508</v>
       </c>
       <c r="K525">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L525">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M525">
         <v>1.17</v>
@@ -27640,96 +27640,96 @@
     </row>
     <row r="526" spans="1:16">
       <c r="A526" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B526" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C526">
-        <v>2.939949994782248</v>
+        <v>2.129744886456478</v>
       </c>
       <c r="D526" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E526">
-        <v>2.524678341649788</v>
+        <v>2.504738939874366</v>
       </c>
       <c r="F526">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G526">
-        <v>0.003060050005217752</v>
+        <v>0.002270255113543523</v>
       </c>
       <c r="H526">
-        <v>0.002635321658350212</v>
+        <v>0.002675261060125634</v>
       </c>
       <c r="I526">
-        <v>0.4152716531324603</v>
+        <v>0.3749940534178879</v>
       </c>
       <c r="J526">
-        <v>0.04728346867539508</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K526">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L526">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M526">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N526">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="O526">
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="527" spans="1:16">
       <c r="A527" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B527" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C527">
-        <v>2.129744886456478</v>
+        <v>3.02860014354532</v>
       </c>
       <c r="D527" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E527">
-        <v>2.504738939874366</v>
+        <v>2.500195647722407</v>
       </c>
       <c r="F527">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G527">
-        <v>0.002270255113543523</v>
+        <v>0.00321139985645468</v>
       </c>
       <c r="H527">
-        <v>0.002675261060125634</v>
+        <v>0.002659804352277594</v>
       </c>
       <c r="I527">
-        <v>0.3749940534178879</v>
+        <v>0.5284044958229135</v>
       </c>
       <c r="J527">
         <v>0.06820884810050738</v>
       </c>
       <c r="K527">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L527">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M527">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N527">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27740,13 +27740,13 @@
     </row>
     <row r="528" spans="1:16">
       <c r="A528" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B528" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C528">
-        <v>3.02860014354532</v>
+        <v>2.913374762912356</v>
       </c>
       <c r="D528" t="s">
         <v>131</v>
@@ -27758,22 +27758,22 @@
         <v>-1</v>
       </c>
       <c r="G528">
-        <v>0.00321139985645468</v>
+        <v>0.003086625237087645</v>
       </c>
       <c r="H528">
         <v>0.002659804352277594</v>
       </c>
       <c r="I528">
-        <v>0.5284044958229135</v>
+        <v>0.4131791151899491</v>
       </c>
       <c r="J528">
         <v>0.06820884810050738</v>
       </c>
       <c r="K528">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L528">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M528">
         <v>1.17</v>
@@ -27790,96 +27790,96 @@
     </row>
     <row r="529" spans="1:16">
       <c r="A529" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B529" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C529">
-        <v>2.913374762912356</v>
+        <v>2.123592991344732</v>
       </c>
       <c r="D529" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E529">
-        <v>2.500195647722407</v>
+        <v>2.549498494602498</v>
       </c>
       <c r="F529">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G529">
-        <v>0.003086625237087645</v>
+        <v>0.002276407008655268</v>
       </c>
       <c r="H529">
-        <v>0.002659804352277594</v>
+        <v>0.002730501505397502</v>
       </c>
       <c r="I529">
-        <v>0.4131791151899491</v>
+        <v>0.4259055032577659</v>
       </c>
       <c r="J529">
-        <v>0.06820884810050738</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K529">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L529">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M529">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N529">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O529">
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="530" spans="1:16">
       <c r="A530" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B530" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C530">
-        <v>2.123592991344732</v>
+        <v>3.020596707186351</v>
       </c>
       <c r="D530" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E530">
-        <v>2.497273047748461</v>
+        <v>2.49320757269256</v>
       </c>
       <c r="F530">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G530">
-        <v>0.002276407008655268</v>
+        <v>0.00321940329281365</v>
       </c>
       <c r="H530">
-        <v>0.002682726952251539</v>
+        <v>0.00266679242730744</v>
       </c>
       <c r="I530">
-        <v>0.3736800564037286</v>
+        <v>0.5273891344937907</v>
       </c>
       <c r="J530">
         <v>0.07418156180123091</v>
       </c>
       <c r="K530">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L530">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M530">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N530">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -27890,13 +27890,13 @@
     </row>
     <row r="531" spans="1:16">
       <c r="A531" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B531" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C531">
-        <v>3.020596707186351</v>
+        <v>2.905789416512437</v>
       </c>
       <c r="D531" t="s">
         <v>131</v>
@@ -27908,22 +27908,22 @@
         <v>-1</v>
       </c>
       <c r="G531">
-        <v>0.00321940329281365</v>
+        <v>0.003094210583487563</v>
       </c>
       <c r="H531">
         <v>0.00266679242730744</v>
       </c>
       <c r="I531">
-        <v>0.5273891344937907</v>
+        <v>0.4125818438198769</v>
       </c>
       <c r="J531">
         <v>0.07418156180123091</v>
       </c>
       <c r="K531">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L531">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M531">
         <v>1.17</v>
@@ -27940,96 +27940,96 @@
     </row>
     <row r="532" spans="1:16">
       <c r="A532" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B532" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C532">
-        <v>2.905789416512437</v>
+        <v>2.162997802089755</v>
       </c>
       <c r="D532" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E532">
-        <v>2.49320757269256</v>
+        <v>2.596172153931554</v>
       </c>
       <c r="F532">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G532">
-        <v>0.003094210583487563</v>
+        <v>0.002237002197910246</v>
       </c>
       <c r="H532">
-        <v>0.00266679242730744</v>
+        <v>0.002683827846068446</v>
       </c>
       <c r="I532">
-        <v>0.4125818438198769</v>
+        <v>0.4331743518417994</v>
       </c>
       <c r="J532">
-        <v>0.07418156180123091</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K532">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L532">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M532">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N532">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O532">
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="533" spans="1:16">
       <c r="A533" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B533" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C533">
-        <v>2.162997802089755</v>
+        <v>3.071861218252691</v>
       </c>
       <c r="D533" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E533">
-        <v>2.545094420011838</v>
+        <v>2.537968377131081</v>
       </c>
       <c r="F533">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G533">
-        <v>0.002237002197910246</v>
+        <v>0.00316813878174731</v>
       </c>
       <c r="H533">
-        <v>0.002634905579988162</v>
+        <v>0.00262203162286892</v>
       </c>
       <c r="I533">
-        <v>0.382096617922083</v>
+        <v>0.53389284112161</v>
       </c>
       <c r="J533">
         <v>0.03592446399052947</v>
       </c>
       <c r="K533">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L533">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M533">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="N533">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28040,13 +28040,13 @@
     </row>
     <row r="534" spans="1:16">
       <c r="A534" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B534" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C534">
-        <v>3.071861218252691</v>
+        <v>2.954375930732028</v>
       </c>
       <c r="D534" t="s">
         <v>131</v>
@@ -28058,22 +28058,22 @@
         <v>-1</v>
       </c>
       <c r="G534">
-        <v>0.00316813878174731</v>
+        <v>0.003045624069267972</v>
       </c>
       <c r="H534">
         <v>0.00262203162286892</v>
       </c>
       <c r="I534">
-        <v>0.53389284112161</v>
+        <v>0.4164075536009468</v>
       </c>
       <c r="J534">
         <v>0.03592446399052947</v>
       </c>
       <c r="K534">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L534">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M534">
         <v>1.17</v>
@@ -28090,96 +28090,96 @@
     </row>
     <row r="535" spans="1:16">
       <c r="A535" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B535" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C535">
-        <v>2.954375930732028</v>
+        <v>2.152181822645585</v>
       </c>
       <c r="D535" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E535">
-        <v>2.537968377131081</v>
+        <v>2.583360993813217</v>
       </c>
       <c r="F535">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G535">
-        <v>0.003045624069267972</v>
+        <v>0.002247818177354416</v>
       </c>
       <c r="H535">
-        <v>0.00262203162286892</v>
+        <v>0.002696639006186784</v>
       </c>
       <c r="I535">
-        <v>0.4164075536009468</v>
+        <v>0.4311791711676323</v>
       </c>
       <c r="J535">
-        <v>0.03592446399052947</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K535">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L535">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M535">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N535">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O535">
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="536" spans="1:16">
       <c r="A536" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B536" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C536">
-        <v>2.152181822645585</v>
+        <v>3.057789944024353</v>
       </c>
       <c r="D536" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E536">
-        <v>2.583360993813217</v>
+        <v>2.525682264558577</v>
       </c>
       <c r="F536">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G536">
-        <v>0.002247818177354416</v>
+        <v>0.003182210055975647</v>
       </c>
       <c r="H536">
-        <v>0.002696639006186784</v>
+        <v>0.002634317735441423</v>
       </c>
       <c r="I536">
-        <v>0.4311791711676323</v>
+        <v>0.532107679465776</v>
       </c>
       <c r="J536">
         <v>0.04642541490719935</v>
       </c>
       <c r="K536">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L536">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M536">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N536">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28190,13 +28190,13 @@
     </row>
     <row r="537" spans="1:16">
       <c r="A537" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B537" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C537">
-        <v>3.057789944024353</v>
+        <v>2.941039723067857</v>
       </c>
       <c r="D537" t="s">
         <v>131</v>
@@ -28208,22 +28208,22 @@
         <v>-1</v>
       </c>
       <c r="G537">
-        <v>0.003182210055975647</v>
+        <v>0.003058960276932143</v>
       </c>
       <c r="H537">
         <v>0.002634317735441423</v>
       </c>
       <c r="I537">
-        <v>0.532107679465776</v>
+        <v>0.4153574585092796</v>
       </c>
       <c r="J537">
         <v>0.04642541490719935</v>
       </c>
       <c r="K537">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L537">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M537">
         <v>1.17</v>
@@ -28240,96 +28240,96 @@
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B538" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C538">
-        <v>2.941039723067857</v>
+        <v>2.132867933343715</v>
       </c>
       <c r="D538" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E538">
-        <v>2.525682264558577</v>
+        <v>2.560484348232362</v>
       </c>
       <c r="F538">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G538">
-        <v>0.003058960276932143</v>
+        <v>0.002267132066656285</v>
       </c>
       <c r="H538">
-        <v>0.002634317735441423</v>
+        <v>0.002719515651767639</v>
       </c>
       <c r="I538">
-        <v>0.4153574585092796</v>
+        <v>0.4276164148886465</v>
       </c>
       <c r="J538">
-        <v>0.04642541490719935</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K538">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L538">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M538">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N538">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O538">
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B539" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C539">
-        <v>2.132867933343715</v>
+        <v>3.032663136583086</v>
       </c>
       <c r="D539" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E539">
-        <v>2.560484348232362</v>
+        <v>2.50374318641956</v>
       </c>
       <c r="F539">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G539">
-        <v>0.002267132066656285</v>
+        <v>0.003207336863416915</v>
       </c>
       <c r="H539">
-        <v>0.002719515651767639</v>
+        <v>0.00265625681358044</v>
       </c>
       <c r="I539">
-        <v>0.4276164148886465</v>
+        <v>0.5289199501635258</v>
       </c>
       <c r="J539">
         <v>0.06517676374396589</v>
       </c>
       <c r="K539">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L539">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="M539">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N539">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28340,13 +28340,13 @@
     </row>
     <row r="540" spans="1:16">
       <c r="A540" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B540" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C540">
-        <v>3.032663136583086</v>
+        <v>2.917225510045163</v>
       </c>
       <c r="D540" t="s">
         <v>131</v>
@@ -28358,22 +28358,22 @@
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.003207336863416915</v>
+        <v>0.003082774489954837</v>
       </c>
       <c r="H540">
         <v>0.00265625681358044</v>
       </c>
       <c r="I540">
-        <v>0.5289199501635258</v>
+        <v>0.4134823236256033</v>
       </c>
       <c r="J540">
         <v>0.06517676374396589</v>
       </c>
       <c r="K540">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L540">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M540">
         <v>1.17</v>
@@ -28390,96 +28390,96 @@
     </row>
     <row r="541" spans="1:16">
       <c r="A541" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B541" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C541">
-        <v>2.917225510045163</v>
+        <v>2.134641124313295</v>
       </c>
       <c r="D541" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E541">
-        <v>2.50374318641956</v>
+        <v>2.527050652099242</v>
       </c>
       <c r="F541">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G541">
-        <v>0.003082774489954837</v>
+        <v>0.002325358875686705</v>
       </c>
       <c r="H541">
-        <v>0.00265625681358044</v>
+        <v>0.002752949347900758</v>
       </c>
       <c r="I541">
-        <v>0.4134823236256033</v>
+        <v>0.3924095277859476</v>
       </c>
       <c r="J541">
-        <v>0.06517676374396589</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K541">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L541">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="M541">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N541">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="542" spans="1:16">
       <c r="A542" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B542" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C542">
-        <v>2.134641124313295</v>
+        <v>2.995940880174577</v>
       </c>
       <c r="D542" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E542">
-        <v>2.527050652099242</v>
+        <v>2.471679723734519</v>
       </c>
       <c r="F542">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G542">
-        <v>0.002325358875686705</v>
+        <v>0.003244059119825423</v>
       </c>
       <c r="H542">
-        <v>0.002752949347900758</v>
+        <v>0.002688320276265481</v>
       </c>
       <c r="I542">
-        <v>0.3924095277859476</v>
+        <v>0.5242611564400583</v>
       </c>
       <c r="J542">
         <v>0.09258143270553931</v>
       </c>
       <c r="K542">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="L542">
-        <v>2.23</v>
+        <v>3.12</v>
       </c>
       <c r="M542">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N542">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28490,13 +28490,13 @@
     </row>
     <row r="543" spans="1:16">
       <c r="A543" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B543" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C543">
-        <v>2.995940880174577</v>
+        <v>2.882421580463965</v>
       </c>
       <c r="D543" t="s">
         <v>131</v>
@@ -28508,22 +28508,22 @@
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.003244059119825423</v>
+        <v>0.003117578419536035</v>
       </c>
       <c r="H543">
         <v>0.002688320276265481</v>
       </c>
       <c r="I543">
-        <v>0.5242611564400583</v>
+        <v>0.4107418567294463</v>
       </c>
       <c r="J543">
         <v>0.09258143270553931</v>
       </c>
       <c r="K543">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L543">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M543">
         <v>1.17</v>
@@ -28540,63 +28540,63 @@
     </row>
     <row r="544" spans="1:16">
       <c r="A544" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B544" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C544">
-        <v>2.882421580463965</v>
+        <v>2.127453766817889</v>
       </c>
       <c r="D544" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E544">
-        <v>2.471679723734519</v>
+        <v>2.518537471376529</v>
       </c>
       <c r="F544">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G544">
-        <v>0.003117578419536035</v>
+        <v>0.002332546233182111</v>
       </c>
       <c r="H544">
-        <v>0.002688320276265481</v>
+        <v>0.002761462528623472</v>
       </c>
       <c r="I544">
-        <v>0.4107418567294463</v>
+        <v>0.3910837045586395</v>
       </c>
       <c r="J544">
-        <v>0.09258143270553931</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K544">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="L544">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="M544">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N544">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="545" spans="1:16">
       <c r="A545" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B545" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C545">
-        <v>2.127453766817889</v>
+        <v>2.134466983327148</v>
       </c>
       <c r="D545" t="s">
         <v>132</v>
@@ -28608,22 +28608,22 @@
         <v>1</v>
       </c>
       <c r="G545">
-        <v>0.002332546233182111</v>
+        <v>0.002345533016672852</v>
       </c>
       <c r="H545">
         <v>0.002761462528623472</v>
       </c>
       <c r="I545">
-        <v>0.3910837045586395</v>
+        <v>0.3840704880493804</v>
       </c>
       <c r="J545">
         <v>0.09955944969136986</v>
       </c>
       <c r="K545">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="L545">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="M545">
         <v>1.22</v>
@@ -28640,46 +28640,46 @@
     </row>
     <row r="546" spans="1:16">
       <c r="A546" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B546" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C546">
-        <v>2.134466983327148</v>
+        <v>2.986590337413564</v>
       </c>
       <c r="D546" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E546">
-        <v>2.518537471376529</v>
+        <v>2.463515443861097</v>
       </c>
       <c r="F546">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.002345533016672852</v>
+        <v>0.003253409662586436</v>
       </c>
       <c r="H546">
-        <v>0.002761462528623472</v>
+        <v>0.002696484556138903</v>
       </c>
       <c r="I546">
-        <v>0.3840704880493804</v>
+        <v>0.5230748935524669</v>
       </c>
       <c r="J546">
         <v>0.09955944969136986</v>
       </c>
       <c r="K546">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="L546">
-        <v>2.24</v>
+        <v>3.12</v>
       </c>
       <c r="M546">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N546">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28690,13 +28690,13 @@
     </row>
     <row r="547" spans="1:16">
       <c r="A547" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B547" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C547">
-        <v>2.986590337413564</v>
+        <v>2.87355949889196</v>
       </c>
       <c r="D547" t="s">
         <v>131</v>
@@ -28708,22 +28708,22 @@
         <v>-1</v>
       </c>
       <c r="G547">
-        <v>0.003253409662586436</v>
+        <v>0.003126440501108039</v>
       </c>
       <c r="H547">
         <v>0.002696484556138903</v>
       </c>
       <c r="I547">
-        <v>0.5230748935524669</v>
+        <v>0.4100440550308631</v>
       </c>
       <c r="J547">
         <v>0.09955944969136986</v>
       </c>
       <c r="K547">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L547">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M547">
         <v>1.17</v>
@@ -28740,96 +28740,96 @@
     </row>
     <row r="548" spans="1:16">
       <c r="A548" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B548" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C548">
-        <v>2.87355949889196</v>
+        <v>2.12608596303</v>
       </c>
       <c r="D548" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E548">
-        <v>2.463515443861097</v>
+        <v>2.508891391411886</v>
       </c>
       <c r="F548">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G548">
-        <v>0.003126440501108039</v>
+        <v>0.002353914036970001</v>
       </c>
       <c r="H548">
-        <v>0.002696484556138903</v>
+        <v>0.002771108608588114</v>
       </c>
       <c r="I548">
-        <v>0.4100440550308631</v>
+        <v>0.3828054283818867</v>
       </c>
       <c r="J548">
-        <v>0.09955944969136986</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K548">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="L548">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="M548">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N548">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="549" spans="1:16">
       <c r="A549" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B549" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C549">
-        <v>2.12608596303</v>
+        <v>2.975995462698301</v>
       </c>
       <c r="D549" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E549">
-        <v>2.508891391411886</v>
+        <v>2.454264695042546</v>
       </c>
       <c r="F549">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G549">
-        <v>0.002353914036970001</v>
+        <v>0.003264004537301699</v>
       </c>
       <c r="H549">
-        <v>0.002771108608588114</v>
+        <v>0.002705735304957454</v>
       </c>
       <c r="I549">
-        <v>0.3828054283818867</v>
+        <v>0.5217307676557548</v>
       </c>
       <c r="J549">
         <v>0.1074660726132081</v>
       </c>
       <c r="K549">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="L549">
-        <v>2.24</v>
+        <v>3.12</v>
       </c>
       <c r="M549">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N549">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O549">
         <v>1</v>
@@ -28840,13 +28840,13 @@
     </row>
     <row r="550" spans="1:16">
       <c r="A550" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B550" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C550">
-        <v>2.975995462698301</v>
+        <v>2.863518087781226</v>
       </c>
       <c r="D550" t="s">
         <v>131</v>
@@ -28858,22 +28858,22 @@
         <v>-1</v>
       </c>
       <c r="G550">
-        <v>0.003264004537301699</v>
+        <v>0.003136481912218774</v>
       </c>
       <c r="H550">
         <v>0.002705735304957454</v>
       </c>
       <c r="I550">
-        <v>0.5217307676557548</v>
+        <v>0.4092533927386794</v>
       </c>
       <c r="J550">
         <v>0.1074660726132081</v>
       </c>
       <c r="K550">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L550">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M550">
         <v>1.17</v>
@@ -28890,96 +28890,96 @@
     </row>
     <row r="551" spans="1:16">
       <c r="A551" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B551" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C551">
-        <v>2.863518087781226</v>
+        <v>2.131023582128605</v>
       </c>
       <c r="D551" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E551">
-        <v>2.454264695042546</v>
+        <v>2.514574311506508</v>
       </c>
       <c r="F551">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G551">
-        <v>0.003136481912218774</v>
+        <v>0.002348976417871395</v>
       </c>
       <c r="H551">
-        <v>0.002705735304957454</v>
+        <v>0.002765425688493492</v>
       </c>
       <c r="I551">
-        <v>0.4092533927386794</v>
+        <v>0.3835507293779026</v>
       </c>
       <c r="J551">
-        <v>0.1074660726132081</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K551">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="L551">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="M551">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N551">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="552" spans="1:16">
       <c r="A552" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B552" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C552">
-        <v>2.131023582128605</v>
+        <v>2.982237358539935</v>
       </c>
       <c r="D552" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E552">
-        <v>2.514574311506508</v>
+        <v>2.459714708575913</v>
       </c>
       <c r="F552">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G552">
-        <v>0.002348976417871395</v>
+        <v>0.003257762641460066</v>
       </c>
       <c r="H552">
-        <v>0.002765425688493492</v>
+        <v>0.002700285291424087</v>
       </c>
       <c r="I552">
-        <v>0.3835507293779026</v>
+        <v>0.5225226499640216</v>
       </c>
       <c r="J552">
         <v>0.1028079413881086</v>
       </c>
       <c r="K552">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="L552">
-        <v>2.24</v>
+        <v>3.12</v>
       </c>
       <c r="M552">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N552">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O552">
         <v>1</v>
@@ -28990,13 +28990,13 @@
     </row>
     <row r="553" spans="1:16">
       <c r="A553" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B553" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C553">
-        <v>2.982237358539935</v>
+        <v>2.869433914437102</v>
       </c>
       <c r="D553" t="s">
         <v>131</v>
@@ -29008,22 +29008,22 @@
         <v>-1</v>
       </c>
       <c r="G553">
-        <v>0.003257762641460066</v>
+        <v>0.003130566085562898</v>
       </c>
       <c r="H553">
         <v>0.002700285291424087</v>
       </c>
       <c r="I553">
-        <v>0.5225226499640216</v>
+        <v>0.4097192058611889</v>
       </c>
       <c r="J553">
         <v>0.1028079413881086</v>
       </c>
       <c r="K553">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L553">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M553">
         <v>1.17</v>
@@ -29040,40 +29040,40 @@
     </row>
     <row r="554" spans="1:16">
       <c r="A554" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B554" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C554">
-        <v>2.869433914437102</v>
+        <v>2.970054254577281</v>
       </c>
       <c r="D554" t="s">
         <v>131</v>
       </c>
       <c r="E554">
-        <v>2.459714708575913</v>
+        <v>2.449077222280164</v>
       </c>
       <c r="F554">
         <v>-1</v>
       </c>
       <c r="G554">
-        <v>0.003130566085562898</v>
+        <v>0.003269945745422719</v>
       </c>
       <c r="H554">
-        <v>0.002700285291424087</v>
+        <v>0.002710922777719837</v>
       </c>
       <c r="I554">
-        <v>0.4097192058611889</v>
+        <v>0.5209770322971177</v>
       </c>
       <c r="J554">
-        <v>0.1028079413881086</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K554">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L554">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M554">
         <v>1.17</v>
@@ -29085,18 +29085,18 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>332</v>
+        <v>55</v>
       </c>
     </row>
     <row r="555" spans="1:16">
       <c r="A555" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B555" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C555">
-        <v>2.970054254577281</v>
+        <v>2.857887241278468</v>
       </c>
       <c r="D555" t="s">
         <v>131</v>
@@ -29108,22 +29108,22 @@
         <v>-1</v>
       </c>
       <c r="G555">
-        <v>0.003269945745422719</v>
+        <v>0.003142112758721532</v>
       </c>
       <c r="H555">
         <v>0.002710922777719837</v>
       </c>
       <c r="I555">
-        <v>0.5209770322971177</v>
+        <v>0.4088100189983046</v>
       </c>
       <c r="J555">
         <v>0.1118998100169543</v>
       </c>
       <c r="K555">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L555">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M555">
         <v>1.17</v>
@@ -29140,40 +29140,40 @@
     </row>
     <row r="556" spans="1:16">
       <c r="A556" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B556" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C556">
-        <v>2.857887241278468</v>
+        <v>2.944089643772313</v>
       </c>
       <c r="D556" t="s">
         <v>131</v>
       </c>
       <c r="E556">
-        <v>2.449077222280164</v>
+        <v>2.426406629263886</v>
       </c>
       <c r="F556">
         <v>-1</v>
       </c>
       <c r="G556">
-        <v>0.003142112758721532</v>
+        <v>0.003295910356227687</v>
       </c>
       <c r="H556">
-        <v>0.002710922777719837</v>
+        <v>0.002733593370736115</v>
       </c>
       <c r="I556">
-        <v>0.4088100189983046</v>
+        <v>0.5176830145084277</v>
       </c>
       <c r="J556">
-        <v>0.1118998100169543</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K556">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L556">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M556">
         <v>1.17</v>
@@ -29185,18 +29185,18 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="557" spans="1:16">
       <c r="A557" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B557" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C557">
-        <v>2.944089643772313</v>
+        <v>2.833278990739431</v>
       </c>
       <c r="D557" t="s">
         <v>131</v>
@@ -29208,22 +29208,22 @@
         <v>-1</v>
       </c>
       <c r="G557">
-        <v>0.003295910356227687</v>
+        <v>0.003166721009260569</v>
       </c>
       <c r="H557">
         <v>0.002733593370736115</v>
       </c>
       <c r="I557">
-        <v>0.5176830145084277</v>
+        <v>0.4068723614755454</v>
       </c>
       <c r="J557">
         <v>0.1312763852445424</v>
       </c>
       <c r="K557">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L557">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M557">
         <v>1.17</v>
@@ -29240,40 +29240,40 @@
     </row>
     <row r="558" spans="1:16">
       <c r="A558" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B558" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C558">
-        <v>2.833278990739431</v>
+        <v>2.897401147650162</v>
       </c>
       <c r="D558" t="s">
         <v>131</v>
       </c>
       <c r="E558">
-        <v>2.426406629263886</v>
+        <v>2.385641300560216</v>
       </c>
       <c r="F558">
         <v>-1</v>
       </c>
       <c r="G558">
-        <v>0.003166721009260569</v>
+        <v>0.003342598852349839</v>
       </c>
       <c r="H558">
-        <v>0.002733593370736115</v>
+        <v>0.002774358699439784</v>
       </c>
       <c r="I558">
-        <v>0.4068723614755454</v>
+        <v>0.5117598470899458</v>
       </c>
       <c r="J558">
-        <v>0.1312763852445424</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K558">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L558">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M558">
         <v>1.17</v>
@@ -29285,18 +29285,18 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>54</v>
+        <v>333</v>
       </c>
     </row>
     <row r="559" spans="1:16">
       <c r="A559" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B559" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C559">
-        <v>2.897401147650162</v>
+        <v>2.789029445907243</v>
       </c>
       <c r="D559" t="s">
         <v>131</v>
@@ -29308,22 +29308,22 @@
         <v>-1</v>
       </c>
       <c r="G559">
-        <v>0.003342598852349839</v>
+        <v>0.003210970554092757</v>
       </c>
       <c r="H559">
         <v>0.002774358699439784</v>
       </c>
       <c r="I559">
-        <v>0.5117598470899458</v>
+        <v>0.4033881453470269</v>
       </c>
       <c r="J559">
         <v>0.16611854652973</v>
       </c>
       <c r="K559">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L559">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M559">
         <v>1.17</v>
@@ -29340,40 +29340,40 @@
     </row>
     <row r="560" spans="1:16">
       <c r="A560" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B560" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C560">
-        <v>2.789029445907243</v>
+        <v>2.834385584744631</v>
       </c>
       <c r="D560" t="s">
         <v>131</v>
       </c>
       <c r="E560">
-        <v>2.385641300560216</v>
+        <v>2.330620249366581</v>
       </c>
       <c r="F560">
         <v>-1</v>
       </c>
       <c r="G560">
-        <v>0.003210970554092757</v>
+        <v>0.003405614415255369</v>
       </c>
       <c r="H560">
-        <v>0.002774358699439784</v>
+        <v>0.002829379750633419</v>
       </c>
       <c r="I560">
-        <v>0.4033881453470269</v>
+        <v>0.5037653353780502</v>
       </c>
       <c r="J560">
-        <v>0.16611854652973</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K560">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="L560">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M560">
         <v>1.17</v>
@@ -29385,18 +29385,18 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="561" spans="1:16">
       <c r="A561" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B561" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C561">
-        <v>2.834385584744631</v>
+        <v>2.729305740765434</v>
       </c>
       <c r="D561" t="s">
         <v>131</v>
@@ -29408,22 +29408,22 @@
         <v>-1</v>
       </c>
       <c r="G561">
-        <v>0.003405614415255369</v>
+        <v>0.003270694259234566</v>
       </c>
       <c r="H561">
         <v>0.002829379750633419</v>
       </c>
       <c r="I561">
-        <v>0.5037653353780502</v>
+        <v>0.3986854913988531</v>
       </c>
       <c r="J561">
         <v>0.2131450860114693</v>
       </c>
       <c r="K561">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L561">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M561">
         <v>1.17</v>
@@ -29440,96 +29440,96 @@
     </row>
     <row r="562" spans="1:16">
       <c r="A562" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B562" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C562">
-        <v>2.729305740765434</v>
+        <v>2.710585509297514</v>
       </c>
       <c r="D562" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E562">
-        <v>2.330620249366581</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="F562">
         <v>-1</v>
       </c>
       <c r="G562">
-        <v>0.003270694259234566</v>
+        <v>0.003529414490702487</v>
       </c>
       <c r="H562">
-        <v>0.002829379750633419</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="I562">
-        <v>0.3986854913988531</v>
+        <v>-0.05138732414117442</v>
       </c>
       <c r="J562">
-        <v>0.2131450860114693</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K562">
+        <v>1.34</v>
+      </c>
+      <c r="L562">
+        <v>3.12</v>
+      </c>
+      <c r="M562">
         <v>1.27</v>
       </c>
-      <c r="L562">
-        <v>3</v>
-      </c>
-      <c r="M562">
-        <v>1.17</v>
-      </c>
       <c r="N562">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O562">
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>334</v>
+        <v>56</v>
       </c>
     </row>
     <row r="563" spans="1:16">
       <c r="A563" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B563" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C563">
-        <v>2.710585509297514</v>
+        <v>2.611972833438688</v>
       </c>
       <c r="D563" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E563">
-        <v>2.761972833438688</v>
+        <v>2.222526153640366</v>
       </c>
       <c r="F563">
         <v>-1</v>
       </c>
       <c r="G563">
-        <v>0.003529414490702487</v>
+        <v>0.003388027166561312</v>
       </c>
       <c r="H563">
-        <v>0.003538027166561312</v>
+        <v>0.002937473846359634</v>
       </c>
       <c r="I563">
-        <v>-0.05138732414117442</v>
+        <v>0.389446679798322</v>
       </c>
       <c r="J563">
         <v>0.3055332020167811</v>
       </c>
       <c r="K563">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L563">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M563">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N563">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O563">
         <v>1</v>
@@ -29540,96 +29540,96 @@
     </row>
     <row r="564" spans="1:16">
       <c r="A564" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B564" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C564">
-        <v>2.611972833438688</v>
+        <v>2.647551728558422</v>
       </c>
       <c r="D564" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E564">
-        <v>2.222526153640366</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="F564">
         <v>-1</v>
       </c>
       <c r="G564">
-        <v>0.003388027166561312</v>
+        <v>0.003592448271441579</v>
       </c>
       <c r="H564">
-        <v>0.002937473846359634</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="I564">
-        <v>0.389446679798322</v>
+        <v>-0.05468013358276913</v>
       </c>
       <c r="J564">
-        <v>0.3055332020167811</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K564">
+        <v>1.34</v>
+      </c>
+      <c r="L564">
+        <v>3.12</v>
+      </c>
+      <c r="M564">
         <v>1.27</v>
       </c>
-      <c r="L564">
-        <v>3</v>
-      </c>
-      <c r="M564">
-        <v>1.17</v>
-      </c>
       <c r="N564">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O564">
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>56</v>
+        <v>335</v>
       </c>
     </row>
     <row r="565" spans="1:16">
       <c r="A565" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B565" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C565">
-        <v>2.647551728558422</v>
+        <v>2.552231862141191</v>
       </c>
       <c r="D565" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E565">
-        <v>2.702231862141191</v>
+        <v>2.167489195830861</v>
       </c>
       <c r="F565">
         <v>-1</v>
       </c>
       <c r="G565">
-        <v>0.003592448271441579</v>
+        <v>0.003447768137858809</v>
       </c>
       <c r="H565">
-        <v>0.003597768137858809</v>
+        <v>0.00299251080416914</v>
       </c>
       <c r="I565">
-        <v>-0.05468013358276913</v>
+        <v>0.3847426663103302</v>
       </c>
       <c r="J565">
         <v>0.3525733368967002</v>
       </c>
       <c r="K565">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L565">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M565">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N565">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O565">
         <v>1</v>
@@ -29640,96 +29640,96 @@
     </row>
     <row r="566" spans="1:16">
       <c r="A566" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B566" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C566">
-        <v>2.552231862141191</v>
+        <v>1.858962462723951</v>
       </c>
       <c r="D566" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E566">
-        <v>2.167489195830861</v>
+        <v>2.165632934933811</v>
       </c>
       <c r="F566">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G566">
-        <v>0.003447768137858809</v>
+        <v>0.002761037537276049</v>
       </c>
       <c r="H566">
-        <v>0.00299251080416914</v>
+        <v>0.00311436706506619</v>
       </c>
       <c r="I566">
-        <v>0.3847426663103302</v>
+        <v>0.3066704722098597</v>
       </c>
       <c r="J566">
-        <v>0.3525733368967002</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K566">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="L566">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M566">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N566">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O566">
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="567" spans="1:16">
       <c r="A567" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B567" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C567">
-        <v>1.858962462723951</v>
+        <v>2.59897387935353</v>
       </c>
       <c r="D567" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E567">
-        <v>2.165632934933811</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="F567">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G567">
-        <v>0.002761037537276049</v>
+        <v>0.003641026120646471</v>
       </c>
       <c r="H567">
-        <v>0.00311436706506619</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="I567">
-        <v>0.3066704722098597</v>
+        <v>-0.05721778242183051</v>
       </c>
       <c r="J567">
         <v>0.3888254631690077</v>
       </c>
       <c r="K567">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="L567">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="M567">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="N567">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="O567">
         <v>1</v>
@@ -29740,46 +29740,46 @@
     </row>
     <row r="568" spans="1:16">
       <c r="A568" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B568" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C568">
-        <v>2.59897387935353</v>
+        <v>2.50619166177536</v>
       </c>
       <c r="D568" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E568">
-        <v>2.65619166177536</v>
+        <v>2.125074208092261</v>
       </c>
       <c r="F568">
         <v>-1</v>
       </c>
       <c r="G568">
-        <v>0.003641026120646471</v>
+        <v>0.00349380833822464</v>
       </c>
       <c r="H568">
-        <v>0.00364380833822464</v>
+        <v>0.003034925791907739</v>
       </c>
       <c r="I568">
-        <v>-0.05721778242183051</v>
+        <v>0.3811174536830992</v>
       </c>
       <c r="J568">
         <v>0.3888254631690077</v>
       </c>
       <c r="K568">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L568">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M568">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N568">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O568">
         <v>1</v>
@@ -29790,96 +29790,96 @@
     </row>
     <row r="569" spans="1:16">
       <c r="A569" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B569" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C569">
-        <v>2.50619166177536</v>
+        <v>1.838291711302243</v>
       </c>
       <c r="D569" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E569">
-        <v>2.125074208092261</v>
+        <v>2.143893006714428</v>
       </c>
       <c r="F569">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G569">
-        <v>0.00349380833822464</v>
+        <v>0.002781708288697757</v>
       </c>
       <c r="H569">
-        <v>0.003034925791907739</v>
+        <v>0.003136106993285572</v>
       </c>
       <c r="I569">
-        <v>0.3811174536830992</v>
+        <v>0.3056012954121849</v>
       </c>
       <c r="J569">
-        <v>0.3888254631690077</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K569">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="L569">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M569">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N569">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O569">
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="570" spans="1:16">
       <c r="A570" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B570" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C570">
-        <v>1.838291711302243</v>
+        <v>2.575095597538799</v>
       </c>
       <c r="D570" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E570">
-        <v>2.143893006714428</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="F570">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G570">
-        <v>0.002781708288697757</v>
+        <v>0.003664904402461202</v>
       </c>
       <c r="H570">
-        <v>0.003136106993285572</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="I570">
-        <v>0.3056012954121849</v>
+        <v>-0.05846515535245045</v>
       </c>
       <c r="J570">
         <v>0.4066450764635833</v>
       </c>
       <c r="K570">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="L570">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="M570">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="N570">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="O570">
         <v>1</v>
@@ -29890,46 +29890,46 @@
     </row>
     <row r="571" spans="1:16">
       <c r="A571" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B571" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C571">
-        <v>2.575095597538799</v>
+        <v>2.483560752891249</v>
       </c>
       <c r="D571" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E571">
-        <v>2.633560752891249</v>
+        <v>2.104225260537608</v>
       </c>
       <c r="F571">
         <v>-1</v>
       </c>
       <c r="G571">
-        <v>0.003664904402461202</v>
+        <v>0.003516439247108751</v>
       </c>
       <c r="H571">
-        <v>0.003666439247108751</v>
+        <v>0.003055774739462393</v>
       </c>
       <c r="I571">
-        <v>-0.05846515535245045</v>
+        <v>0.3793354923536416</v>
       </c>
       <c r="J571">
         <v>0.4066450764635833</v>
       </c>
       <c r="K571">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L571">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M571">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N571">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O571">
         <v>1</v>
@@ -29940,96 +29940,96 @@
     </row>
     <row r="572" spans="1:16">
       <c r="A572" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B572" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C572">
-        <v>2.483560752891249</v>
+        <v>1.784876857591519</v>
       </c>
       <c r="D572" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E572">
-        <v>2.104225260537608</v>
+        <v>2.087715315742805</v>
       </c>
       <c r="F572">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G572">
-        <v>0.003516439247108751</v>
+        <v>0.002835123142408481</v>
       </c>
       <c r="H572">
-        <v>0.003055774739462393</v>
+        <v>0.003192284684257196</v>
       </c>
       <c r="I572">
-        <v>0.3793354923536416</v>
+        <v>0.3028384581512857</v>
       </c>
       <c r="J572">
-        <v>0.4066450764635833</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K572">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="L572">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M572">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N572">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O572">
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="573" spans="1:16">
       <c r="A573" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B573" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C573">
-        <v>1.784876857591519</v>
+        <v>2.513392232045375</v>
       </c>
       <c r="D573" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E573">
-        <v>2.087715315742805</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="F573">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G573">
-        <v>0.002835123142408481</v>
+        <v>0.003726607767954625</v>
       </c>
       <c r="H573">
-        <v>0.003192284684257196</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="I573">
-        <v>0.3028384581512857</v>
+        <v>-0.0616884654901666</v>
       </c>
       <c r="J573">
         <v>0.4526923641452424</v>
       </c>
       <c r="K573">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="L573">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="M573">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="N573">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="O573">
         <v>1</v>
@@ -30040,46 +30040,46 @@
     </row>
     <row r="574" spans="1:16">
       <c r="A574" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B574" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C574">
-        <v>2.513392232045375</v>
+        <v>2.425080697535542</v>
       </c>
       <c r="D574" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E574">
-        <v>2.575080697535542</v>
+        <v>2.050349933950066</v>
       </c>
       <c r="F574">
         <v>-1</v>
       </c>
       <c r="G574">
-        <v>0.003726607767954625</v>
+        <v>0.003574919302464458</v>
       </c>
       <c r="H574">
-        <v>0.003724919302464458</v>
+        <v>0.003109650066049934</v>
       </c>
       <c r="I574">
-        <v>-0.0616884654901666</v>
+        <v>0.3747307635854757</v>
       </c>
       <c r="J574">
         <v>0.4526923641452424</v>
       </c>
       <c r="K574">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L574">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M574">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N574">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O574">
         <v>1</v>
@@ -30090,151 +30090,101 @@
     </row>
     <row r="575" spans="1:16">
       <c r="A575" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B575" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C575">
-        <v>2.425080697535542</v>
+        <v>2.46037019732591</v>
       </c>
       <c r="D575" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E575">
-        <v>2.050349933950066</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="F575">
         <v>-1</v>
       </c>
       <c r="G575">
-        <v>0.003574919302464458</v>
+        <v>0.00377962980267409</v>
       </c>
       <c r="H575">
-        <v>0.003109650066049934</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="I575">
-        <v>0.3747307635854757</v>
+        <v>-0.0644582732740191</v>
       </c>
       <c r="J575">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K575">
+        <v>1.34</v>
+      </c>
+      <c r="L575">
+        <v>3.12</v>
+      </c>
+      <c r="M575">
         <v>1.27</v>
       </c>
-      <c r="L575">
-        <v>3</v>
-      </c>
-      <c r="M575">
-        <v>1.17</v>
-      </c>
       <c r="N575">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O575">
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>338</v>
+        <v>57</v>
       </c>
     </row>
     <row r="576" spans="1:16">
       <c r="A576" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B576" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C576">
-        <v>2.46037019732591</v>
+        <v>2.37482847059993</v>
       </c>
       <c r="D576" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E576">
-        <v>2.524828470599929</v>
+        <v>2.004054575277101</v>
       </c>
       <c r="F576">
         <v>-1</v>
       </c>
       <c r="G576">
-        <v>0.00377962980267409</v>
+        <v>0.003625171529400071</v>
       </c>
       <c r="H576">
-        <v>0.003775171529400071</v>
+        <v>0.003155945424722899</v>
       </c>
       <c r="I576">
-        <v>-0.0644582732740191</v>
+        <v>0.370773895322829</v>
       </c>
       <c r="J576">
         <v>0.4922610467717091</v>
       </c>
       <c r="K576">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L576">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M576">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N576">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="O576">
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="577" spans="1:16">
-      <c r="A577" s="1">
-        <v>1</v>
-      </c>
-      <c r="B577" t="s">
-        <v>53</v>
-      </c>
-      <c r="C577">
-        <v>2.37482847059993</v>
-      </c>
-      <c r="D577" t="s">
-        <v>131</v>
-      </c>
-      <c r="E577">
-        <v>2.004054575277101</v>
-      </c>
-      <c r="F577">
-        <v>-1</v>
-      </c>
-      <c r="G577">
-        <v>0.003625171529400071</v>
-      </c>
-      <c r="H577">
-        <v>0.003155945424722899</v>
-      </c>
-      <c r="I577">
-        <v>0.370773895322829</v>
-      </c>
-      <c r="J577">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K577">
-        <v>1.27</v>
-      </c>
-      <c r="L577">
-        <v>3</v>
-      </c>
-      <c r="M577">
-        <v>1.17</v>
-      </c>
-      <c r="N577">
-        <v>2.58</v>
-      </c>
-      <c r="O577">
-        <v>1</v>
-      </c>
-      <c r="P577" t="s">
         <v>57</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="314">
   <si>
     <t>trade_time</t>
   </si>
@@ -868,9 +868,6 @@
     <t>2020-12-08</t>
   </si>
   <si>
-    <t>2020-12-09</t>
-  </si>
-  <si>
     <t>2020-12-10</t>
   </si>
   <si>
@@ -904,42 +901,6 @@
     <t>2020-12-24</t>
   </si>
   <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-29</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-08</t>
-  </si>
-  <si>
-    <t>2021-01-15</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>2021-01-19</t>
-  </si>
-  <si>
     <t>2021-01-20</t>
   </si>
   <si>
@@ -950,12 +911,6 @@
   </si>
   <si>
     <t>2021-01-25</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
   </si>
   <si>
     <t>2021-01-29</t>
@@ -1358,7 +1313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P499"/>
+  <dimension ref="A1:P464"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -22863,43 +22818,43 @@
         <v>0</v>
       </c>
       <c r="B431" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C431">
-        <v>3.514497085630696</v>
+        <v>3.534545223359963</v>
       </c>
       <c r="D431" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E431">
-        <v>2.924448947901429</v>
+        <v>3.997489231461685</v>
       </c>
       <c r="F431">
         <v>-1</v>
       </c>
       <c r="G431">
-        <v>0.002725502914369304</v>
+        <v>0.002645454776640036</v>
       </c>
       <c r="H431">
-        <v>0.002235551052098571</v>
+        <v>0.003102510768538314</v>
       </c>
       <c r="I431">
-        <v>0.5900481377292675</v>
+        <v>-0.4629440081017218</v>
       </c>
       <c r="J431">
         <v>-0.2944008101721614</v>
       </c>
       <c r="K431">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="L431">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="M431">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="N431">
-        <v>2.58</v>
+        <v>3.55</v>
       </c>
       <c r="O431">
         <v>1</v>
@@ -22910,34 +22865,34 @@
     </row>
     <row r="432" spans="1:16">
       <c r="A432" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B432" t="s">
         <v>52</v>
       </c>
       <c r="C432">
-        <v>3.534545223359963</v>
+        <v>3.523470605461004</v>
       </c>
       <c r="D432" t="s">
         <v>124</v>
       </c>
       <c r="E432">
-        <v>3.997489231461685</v>
+        <v>3.986341271722335</v>
       </c>
       <c r="F432">
         <v>-1</v>
       </c>
       <c r="G432">
-        <v>0.002645454776640036</v>
+        <v>0.002656529394538996</v>
       </c>
       <c r="H432">
-        <v>0.003102510768538314</v>
+        <v>0.003113658728277664</v>
       </c>
       <c r="I432">
-        <v>-0.4629440081017218</v>
+        <v>-0.4628706662613311</v>
       </c>
       <c r="J432">
-        <v>-0.2944008101721614</v>
+        <v>-0.2870666261331153</v>
       </c>
       <c r="K432">
         <v>1.51</v>
@@ -22955,7 +22910,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -22963,81 +22918,81 @@
         <v>0</v>
       </c>
       <c r="B433" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C433">
-        <v>3.504669279018375</v>
+        <v>3.500842102418018</v>
       </c>
       <c r="D433" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E433">
-        <v>2.915867952575745</v>
+        <v>3.963562911043303</v>
       </c>
       <c r="F433">
         <v>-1</v>
       </c>
       <c r="G433">
-        <v>0.002735330720981625</v>
+        <v>0.002679157897581982</v>
       </c>
       <c r="H433">
-        <v>0.002244132047424255</v>
+        <v>0.003136437088956697</v>
       </c>
       <c r="I433">
-        <v>0.5888013264426299</v>
+        <v>-0.462720808625285</v>
       </c>
       <c r="J433">
-        <v>-0.2870666261331153</v>
+        <v>-0.2720808625284886</v>
       </c>
       <c r="K433">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="L433">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="M433">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="N433">
-        <v>2.58</v>
+        <v>3.55</v>
       </c>
       <c r="O433">
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="434" spans="1:16">
       <c r="A434" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B434" t="s">
         <v>52</v>
       </c>
       <c r="C434">
-        <v>3.523470605461004</v>
+        <v>3.482113454143312</v>
       </c>
       <c r="D434" t="s">
         <v>124</v>
       </c>
       <c r="E434">
-        <v>3.986341271722335</v>
+        <v>3.944710231985321</v>
       </c>
       <c r="F434">
         <v>-1</v>
       </c>
       <c r="G434">
-        <v>0.002656529394538996</v>
+        <v>0.002697886545856688</v>
       </c>
       <c r="H434">
-        <v>0.003113658728277664</v>
+        <v>0.003155289768014679</v>
       </c>
       <c r="I434">
-        <v>-0.4628706662613311</v>
+        <v>-0.4625967778420086</v>
       </c>
       <c r="J434">
-        <v>-0.2870666261331153</v>
+        <v>-0.259677784200869</v>
       </c>
       <c r="K434">
         <v>1.51</v>
@@ -23055,7 +23010,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23063,37 +23018,37 @@
         <v>0</v>
       </c>
       <c r="B435" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C435">
-        <v>3.484588355788175</v>
+        <v>3.445383547649404</v>
       </c>
       <c r="D435" t="s">
         <v>125</v>
       </c>
       <c r="E435">
-        <v>2.898334609158332</v>
+        <v>2.852125000590396</v>
       </c>
       <c r="F435">
         <v>-1</v>
       </c>
       <c r="G435">
-        <v>0.002755411644211826</v>
+        <v>0.002854616452350596</v>
       </c>
       <c r="H435">
-        <v>0.002261665390841669</v>
+        <v>0.002307874999409604</v>
       </c>
       <c r="I435">
-        <v>0.5862537466298434</v>
+        <v>0.5932585470590079</v>
       </c>
       <c r="J435">
-        <v>-0.2720808625284886</v>
+        <v>-0.2325854705900817</v>
       </c>
       <c r="K435">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L435">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M435">
         <v>1.17</v>
@@ -23105,57 +23060,57 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="436" spans="1:16">
       <c r="A436" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B436" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C436">
-        <v>3.500842102418018</v>
+        <v>3.431177479772535</v>
       </c>
       <c r="D436" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E436">
-        <v>3.963562911043303</v>
+        <v>2.839037520735328</v>
       </c>
       <c r="F436">
         <v>-1</v>
       </c>
       <c r="G436">
-        <v>0.002679157897581982</v>
+        <v>0.002868822520227465</v>
       </c>
       <c r="H436">
-        <v>0.003136437088956697</v>
+        <v>0.002320962479264672</v>
       </c>
       <c r="I436">
-        <v>-0.462720808625285</v>
+        <v>0.5921399590372074</v>
       </c>
       <c r="J436">
-        <v>-0.2720808625284886</v>
+        <v>-0.2213995903720749</v>
       </c>
       <c r="K436">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L436">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M436">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="N436">
-        <v>3.55</v>
+        <v>2.58</v>
       </c>
       <c r="O436">
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23163,99 +23118,99 @@
         <v>0</v>
       </c>
       <c r="B437" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C437">
-        <v>3.467968230829165</v>
+        <v>3.420290016087509</v>
       </c>
       <c r="D437" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E437">
-        <v>2.883823007515017</v>
+        <v>2.859007337655421</v>
       </c>
       <c r="F437">
         <v>-1</v>
       </c>
       <c r="G437">
-        <v>0.002772031769170836</v>
+        <v>0.002879709983912491</v>
       </c>
       <c r="H437">
-        <v>0.002276176992484984</v>
+        <v>0.002360992662344579</v>
       </c>
       <c r="I437">
-        <v>0.584145223314148</v>
+        <v>0.5612826784320877</v>
       </c>
       <c r="J437">
-        <v>-0.259677784200869</v>
+        <v>-0.212826784320873</v>
       </c>
       <c r="K437">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L437">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M437">
         <v>1.17</v>
       </c>
       <c r="N437">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="O437">
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="438" spans="1:16">
       <c r="A438" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B438" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C438">
-        <v>3.482113454143312</v>
+        <v>3.41039159441649</v>
       </c>
       <c r="D438" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E438">
-        <v>3.944710231985321</v>
+        <v>2.851938646780676</v>
       </c>
       <c r="F438">
         <v>-1</v>
       </c>
       <c r="G438">
-        <v>0.002697886545856688</v>
+        <v>0.00288960840558351</v>
       </c>
       <c r="H438">
-        <v>0.003155289768014679</v>
+        <v>0.002368061353219324</v>
       </c>
       <c r="I438">
-        <v>-0.4625967778420086</v>
+        <v>0.5584529476358147</v>
       </c>
       <c r="J438">
-        <v>-0.259677784200869</v>
+        <v>-0.2050327515090475</v>
       </c>
       <c r="K438">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L438">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M438">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="N438">
-        <v>3.55</v>
+        <v>2.61</v>
       </c>
       <c r="O438">
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23263,99 +23218,99 @@
         <v>0</v>
       </c>
       <c r="B439" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C439">
-        <v>3.450555570267193</v>
+        <v>3.388023672482139</v>
       </c>
       <c r="D439" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E439">
-        <v>2.86861941583031</v>
+        <v>2.831155853172381</v>
       </c>
       <c r="F439">
         <v>-1</v>
       </c>
       <c r="G439">
-        <v>0.002789444429732808</v>
+        <v>0.002911976327517861</v>
       </c>
       <c r="H439">
-        <v>0.00229138058416969</v>
+        <v>0.002388844146827619</v>
       </c>
       <c r="I439">
-        <v>0.5819361544368826</v>
+        <v>0.5568678193097578</v>
       </c>
       <c r="J439">
-        <v>-0.2466832613934271</v>
+        <v>-0.1874202145528653</v>
       </c>
       <c r="K439">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L439">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M439">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N439">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="O439">
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="440" spans="1:16">
       <c r="A440" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B440" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C440">
-        <v>3.462491724704075</v>
+        <v>3.366065532153956</v>
       </c>
       <c r="D440" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E440">
-        <v>3.924958557318009</v>
+        <v>2.810753801528873</v>
       </c>
       <c r="F440">
         <v>-1</v>
       </c>
       <c r="G440">
-        <v>0.002717508275295925</v>
+        <v>0.002933934467846044</v>
       </c>
       <c r="H440">
-        <v>0.00317504144268199</v>
+        <v>0.002409246198471127</v>
       </c>
       <c r="I440">
-        <v>-0.4624668326139343</v>
+        <v>0.5553117306250837</v>
       </c>
       <c r="J440">
-        <v>-0.2466832613934271</v>
+        <v>-0.1701303402787057</v>
       </c>
       <c r="K440">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L440">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M440">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="N440">
-        <v>3.55</v>
+        <v>2.61</v>
       </c>
       <c r="O440">
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23363,99 +23318,99 @@
         <v>0</v>
       </c>
       <c r="B441" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C441">
-        <v>3.43166453059071</v>
+        <v>3.359077050053855</v>
       </c>
       <c r="D441" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E441">
-        <v>2.852125000590396</v>
+        <v>2.804260566191771</v>
       </c>
       <c r="F441">
         <v>-1</v>
       </c>
       <c r="G441">
-        <v>0.00280833546940929</v>
+        <v>0.002940922949946145</v>
       </c>
       <c r="H441">
-        <v>0.002307874999409604</v>
+        <v>0.002415739433808229</v>
       </c>
       <c r="I441">
-        <v>0.5795395300003139</v>
+        <v>0.5548164838620839</v>
       </c>
       <c r="J441">
-        <v>-0.2325854705900817</v>
+        <v>-0.1646275984676025</v>
       </c>
       <c r="K441">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L441">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M441">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N441">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="O441">
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="442" spans="1:16">
       <c r="A442" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B442" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C442">
-        <v>3.441204060591023</v>
+        <v>3.357368411775074</v>
       </c>
       <c r="D442" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E442">
-        <v>3.903529915296924</v>
+        <v>2.802673012515423</v>
       </c>
       <c r="F442">
         <v>-1</v>
       </c>
       <c r="G442">
-        <v>0.002738795939408976</v>
+        <v>0.002942631588224926</v>
       </c>
       <c r="H442">
-        <v>0.003196470084703076</v>
+        <v>0.002417326987484576</v>
       </c>
       <c r="I442">
-        <v>-0.4623258547059006</v>
+        <v>0.5546953992596508</v>
       </c>
       <c r="J442">
-        <v>-0.2325854705900817</v>
+        <v>-0.1632822139961216</v>
       </c>
       <c r="K442">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L442">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M442">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="N442">
-        <v>3.55</v>
+        <v>2.61</v>
       </c>
       <c r="O442">
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23463,99 +23418,99 @@
         <v>0</v>
       </c>
       <c r="B443" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C443">
-        <v>3.41667545109858</v>
+        <v>3.349624693698275</v>
       </c>
       <c r="D443" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E443">
-        <v>2.839037520735328</v>
+        <v>2.795478061861389</v>
       </c>
       <c r="F443">
         <v>-1</v>
       </c>
       <c r="G443">
-        <v>0.00282332454890142</v>
+        <v>0.002950375306301725</v>
       </c>
       <c r="H443">
-        <v>0.002320962479264672</v>
+        <v>0.002424521938138611</v>
       </c>
       <c r="I443">
-        <v>0.5776379303632528</v>
+        <v>0.5541466318368857</v>
       </c>
       <c r="J443">
-        <v>-0.2213995903720749</v>
+        <v>-0.157184798187618</v>
       </c>
       <c r="K443">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L443">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M443">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N443">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="O443">
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="444" spans="1:16">
       <c r="A444" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B444" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C444">
-        <v>3.424313381461833</v>
+        <v>3.357948646229581</v>
       </c>
       <c r="D444" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E444">
-        <v>3.886527377365554</v>
+        <v>2.803212127992839</v>
       </c>
       <c r="F444">
         <v>-1</v>
       </c>
       <c r="G444">
-        <v>0.002755686618538167</v>
+        <v>0.002942051353770419</v>
       </c>
       <c r="H444">
-        <v>0.003213472622634446</v>
+        <v>0.002416787872007161</v>
       </c>
       <c r="I444">
-        <v>-0.4622139959037206</v>
+        <v>0.5547365182367421</v>
       </c>
       <c r="J444">
-        <v>-0.2213995903720749</v>
+        <v>-0.1637390915193551</v>
       </c>
       <c r="K444">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L444">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M444">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="N444">
-        <v>3.55</v>
+        <v>2.61</v>
       </c>
       <c r="O444">
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23563,99 +23518,99 @@
         <v>0</v>
       </c>
       <c r="B445" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C445">
-        <v>3.40518789098997</v>
+        <v>3.383574363445438</v>
       </c>
       <c r="D445" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E445">
-        <v>2.829007337655421</v>
+        <v>2.827021849500486</v>
       </c>
       <c r="F445">
         <v>-1</v>
       </c>
       <c r="G445">
-        <v>0.00283481210901003</v>
+        <v>0.002916425636554562</v>
       </c>
       <c r="H445">
-        <v>0.002330992662344579</v>
+        <v>0.002392978150499514</v>
       </c>
       <c r="I445">
-        <v>0.5761805533345488</v>
+        <v>0.5565525139449523</v>
       </c>
       <c r="J445">
-        <v>-0.212826784320873</v>
+        <v>-0.1839168216105812</v>
       </c>
       <c r="K445">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L445">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M445">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N445">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="O445">
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="446" spans="1:16">
       <c r="A446" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B446" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C446">
-        <v>3.411368444324518</v>
+        <v>3.138712566996877</v>
       </c>
       <c r="D446" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E446">
-        <v>3.873496712167727</v>
+        <v>2.619423586398649</v>
       </c>
       <c r="F446">
         <v>-1</v>
       </c>
       <c r="G446">
-        <v>0.002768631555675482</v>
+        <v>0.003161287433003123</v>
       </c>
       <c r="H446">
-        <v>0.003226503287832273</v>
+        <v>0.002640576413601351</v>
       </c>
       <c r="I446">
-        <v>-0.4621282678432088</v>
+        <v>0.5192889805982288</v>
       </c>
       <c r="J446">
-        <v>-0.212826784320873</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K446">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L446">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M446">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="N446">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="O446">
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23663,99 +23618,99 @@
         <v>0</v>
       </c>
       <c r="B447" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C447">
-        <v>3.394743887022124</v>
+        <v>3.089949994782248</v>
       </c>
       <c r="D447" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E447">
-        <v>2.819888319265586</v>
+        <v>2.57373267227628</v>
       </c>
       <c r="F447">
         <v>-1</v>
       </c>
       <c r="G447">
-        <v>0.002845256112977877</v>
+        <v>0.003210050005217752</v>
       </c>
       <c r="H447">
-        <v>0.002340111680734414</v>
+        <v>0.00268626732772372</v>
       </c>
       <c r="I447">
-        <v>0.5748555677565381</v>
+        <v>0.5162173225059683</v>
       </c>
       <c r="J447">
-        <v>-0.2050327515090475</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K447">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L447">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M447">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="N447">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="O447">
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="448" spans="1:16">
       <c r="A448" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B448" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C448">
-        <v>3.399599454778662</v>
+        <v>3.063374762912356</v>
       </c>
       <c r="D448" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E448">
-        <v>3.861649782293752</v>
+        <v>2.548831470760396</v>
       </c>
       <c r="F448">
         <v>-1</v>
       </c>
       <c r="G448">
-        <v>0.002780400545221338</v>
+        <v>0.003236625237087644</v>
       </c>
       <c r="H448">
-        <v>0.003238350217706248</v>
+        <v>0.002711168529239603</v>
       </c>
       <c r="I448">
-        <v>-0.4620503275150902</v>
+        <v>0.5145432921519593</v>
       </c>
       <c r="J448">
-        <v>-0.2050327515090475</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K448">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L448">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M448">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="N448">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="O448">
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23763,99 +23718,99 @@
         <v>0</v>
       </c>
       <c r="B449" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C449">
-        <v>3.371143087500839</v>
+        <v>3.055789416512437</v>
       </c>
       <c r="D449" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E449">
-        <v>2.799281651026853</v>
+        <v>2.541723941456535</v>
       </c>
       <c r="F449">
         <v>-1</v>
       </c>
       <c r="G449">
-        <v>0.002868856912499161</v>
+        <v>0.003244210583487563</v>
       </c>
       <c r="H449">
-        <v>0.002360718348973148</v>
+        <v>0.002718276058543465</v>
       </c>
       <c r="I449">
-        <v>0.5718614364739869</v>
+        <v>0.5140654750559017</v>
       </c>
       <c r="J449">
-        <v>-0.1874202145528653</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K449">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L449">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M449">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="N449">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="O449">
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="450" spans="1:16">
       <c r="A450" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B450" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C450">
-        <v>3.373004523974827</v>
+        <v>3.067225510045163</v>
       </c>
       <c r="D450" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E450">
-        <v>3.834878726120355</v>
+        <v>2.552439651144681</v>
       </c>
       <c r="F450">
         <v>-1</v>
       </c>
       <c r="G450">
-        <v>0.002806995476025173</v>
+        <v>0.003232774489954837</v>
       </c>
       <c r="H450">
-        <v>0.003265121273879644</v>
+        <v>0.002707560348855319</v>
       </c>
       <c r="I450">
-        <v>-0.4618742021455287</v>
+        <v>0.5147858589004826</v>
       </c>
       <c r="J450">
-        <v>-0.1874202145528653</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K450">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L450">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M450">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="N450">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="O450">
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23863,99 +23818,99 @@
         <v>0</v>
       </c>
       <c r="B451" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C451">
-        <v>3.347974655973466</v>
+        <v>3.032421580463965</v>
       </c>
       <c r="D451" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E451">
-        <v>2.779052498126086</v>
+        <v>2.519828095080408</v>
       </c>
       <c r="F451">
         <v>-1</v>
       </c>
       <c r="G451">
-        <v>0.002892025344026534</v>
+        <v>0.003267578419536035</v>
       </c>
       <c r="H451">
-        <v>0.002380947501873914</v>
+        <v>0.002740171904919592</v>
       </c>
       <c r="I451">
-        <v>0.5689221578473802</v>
+        <v>0.5125934853835572</v>
       </c>
       <c r="J451">
-        <v>-0.1701303402787057</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K451">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L451">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M451">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="N451">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="O451">
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
     </row>
     <row r="452" spans="1:16">
       <c r="A452" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B452" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C452">
-        <v>3.346896813820845</v>
+        <v>3.02355949889196</v>
       </c>
       <c r="D452" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E452">
-        <v>3.808598117223633</v>
+        <v>2.51152425486727</v>
       </c>
       <c r="F452">
         <v>-1</v>
       </c>
       <c r="G452">
-        <v>0.002833103186179154</v>
+        <v>0.003276440501108039</v>
       </c>
       <c r="H452">
-        <v>0.003291401882776367</v>
+        <v>0.00274847574513273</v>
       </c>
       <c r="I452">
-        <v>-0.461701303402787</v>
+        <v>0.5120352440246907</v>
       </c>
       <c r="J452">
-        <v>-0.1701303402787057</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K452">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L452">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M452">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="N452">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="O452">
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -23963,99 +23918,99 @@
         <v>0</v>
       </c>
       <c r="B453" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C453">
-        <v>3.340600981946587</v>
+        <v>3.013518087781226</v>
       </c>
       <c r="D453" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E453">
-        <v>2.802614290207095</v>
+        <v>2.502115373590282</v>
       </c>
       <c r="F453">
         <v>-1</v>
       </c>
       <c r="G453">
-        <v>0.002899399018053413</v>
+        <v>0.003286481912218774</v>
       </c>
       <c r="H453">
-        <v>0.002417385709792905</v>
+        <v>0.002757884626409718</v>
       </c>
       <c r="I453">
-        <v>0.5379866917394924</v>
+        <v>0.5114027141909436</v>
       </c>
       <c r="J453">
-        <v>-0.1646275984676025</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K453">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L453">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M453">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="N453">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="O453">
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
     </row>
     <row r="454" spans="1:16">
       <c r="A454" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B454" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C454">
-        <v>3.33858767368608</v>
+        <v>3.019433914437102</v>
       </c>
       <c r="D454" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E454">
-        <v>3.800233949670756</v>
+        <v>2.507658549748151</v>
       </c>
       <c r="F454">
         <v>-1</v>
       </c>
       <c r="G454">
-        <v>0.00284141232631392</v>
+        <v>0.003280566085562898</v>
       </c>
       <c r="H454">
-        <v>0.003299766050329244</v>
+        <v>0.002752341450251849</v>
       </c>
       <c r="I454">
-        <v>-0.461646275984676</v>
+        <v>0.5117753646889511</v>
       </c>
       <c r="J454">
-        <v>-0.1646275984676025</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K454">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L454">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M454">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="N454">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="O454">
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24063,99 +24018,99 @@
         <v>0</v>
       </c>
       <c r="B455" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C455">
-        <v>3.338798166754803</v>
+        <v>3.007887241278468</v>
       </c>
       <c r="D455" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E455">
-        <v>2.802673012515423</v>
+        <v>2.496839226079824</v>
       </c>
       <c r="F455">
         <v>-1</v>
       </c>
       <c r="G455">
-        <v>0.002901201833245197</v>
+        <v>0.003292112758721532</v>
       </c>
       <c r="H455">
-        <v>0.002417326987484576</v>
+        <v>0.002763160773920176</v>
       </c>
       <c r="I455">
-        <v>0.5361251542393797</v>
+        <v>0.5110480151986438</v>
       </c>
       <c r="J455">
-        <v>-0.1632822139961216</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K455">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L455">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M455">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N455">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="O455">
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
     </row>
     <row r="456" spans="1:16">
       <c r="A456" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B456" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C456">
-        <v>3.336556143134144</v>
+        <v>2.983278990739431</v>
       </c>
       <c r="D456" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E456">
-        <v>3.798188965274105</v>
+        <v>2.473781101558994</v>
       </c>
       <c r="F456">
         <v>-1</v>
       </c>
       <c r="G456">
-        <v>0.002843443856865856</v>
+        <v>0.003316721009260569</v>
       </c>
       <c r="H456">
-        <v>0.003301811034725895</v>
+        <v>0.002786218898441006</v>
       </c>
       <c r="I456">
-        <v>-0.4616328221399613</v>
+        <v>0.5094978891804369</v>
       </c>
       <c r="J456">
-        <v>-0.1632822139961216</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K456">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L456">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M456">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="N456">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="O456">
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24163,99 +24118,99 @@
         <v>0</v>
       </c>
       <c r="B457" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C457">
-        <v>3.330627629571408</v>
+        <v>2.939029445907243</v>
       </c>
       <c r="D457" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E457">
-        <v>2.795478061861389</v>
+        <v>2.432318929629621</v>
       </c>
       <c r="F457">
         <v>-1</v>
       </c>
       <c r="G457">
-        <v>0.002909372370428592</v>
+        <v>0.003360970554092757</v>
       </c>
       <c r="H457">
-        <v>0.002424521938138611</v>
+        <v>0.002827681070370379</v>
       </c>
       <c r="I457">
-        <v>0.5351495677100191</v>
+        <v>0.5067105162776215</v>
       </c>
       <c r="J457">
-        <v>-0.157184798187618</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K457">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L457">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M457">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N457">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="O457">
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
     </row>
     <row r="458" spans="1:16">
       <c r="A458" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B458" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C458">
-        <v>3.327349045263303</v>
+        <v>2.879305740765434</v>
       </c>
       <c r="D458" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E458">
-        <v>3.788920893245179</v>
+        <v>2.376357347646351</v>
       </c>
       <c r="F458">
         <v>-1</v>
       </c>
       <c r="G458">
-        <v>0.002852650954736696</v>
+        <v>0.003420694259234566</v>
       </c>
       <c r="H458">
-        <v>0.00331107910675482</v>
+        <v>0.002883642652353649</v>
       </c>
       <c r="I458">
-        <v>-0.461571847981876</v>
+        <v>0.5029483931190826</v>
       </c>
       <c r="J458">
-        <v>-0.157184798187618</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K458">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L458">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M458">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="N458">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="O458">
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24263,99 +24218,99 @@
         <v>0</v>
       </c>
       <c r="B459" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C459">
-        <v>3.339410382635936</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="D459" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E459">
-        <v>2.803212127992839</v>
+        <v>2.26641548960003</v>
       </c>
       <c r="F459">
         <v>-1</v>
       </c>
       <c r="G459">
-        <v>0.002900589617364064</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="H459">
-        <v>0.002416787872007161</v>
+        <v>0.00299358451039997</v>
       </c>
       <c r="I459">
-        <v>0.536198254643097</v>
+        <v>0.4955573438386578</v>
       </c>
       <c r="J459">
-        <v>-0.1637390915193551</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K459">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L459">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M459">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N459">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="O459">
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
     </row>
     <row r="460" spans="1:16">
       <c r="A460" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B460" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C460">
-        <v>3.337246028194226</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D460" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E460">
-        <v>3.79888341910942</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F460">
         <v>-1</v>
       </c>
       <c r="G460">
-        <v>0.002842753971805774</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H460">
-        <v>0.00330111658089058</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I460">
-        <v>-0.4616373909151936</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J460">
-        <v>-0.1637390915193551</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K460">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L460">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M460">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="N460">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="O460">
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24363,99 +24318,99 @@
         <v>0</v>
       </c>
       <c r="B461" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C461">
-        <v>3.366448540958179</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D461" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E461">
-        <v>2.827021849500486</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F461">
         <v>-1</v>
       </c>
       <c r="G461">
-        <v>0.002873551459041821</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H461">
-        <v>0.002392978150499514</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I461">
-        <v>0.5394266914576931</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J461">
-        <v>-0.1839168216105812</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K461">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L461">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M461">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N461">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="O461">
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
     </row>
     <row r="462" spans="1:16">
       <c r="A462" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B462" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C462">
-        <v>3.367714400631977</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D462" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E462">
-        <v>3.829553568848083</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F462">
         <v>-1</v>
       </c>
       <c r="G462">
-        <v>0.002812285599368023</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H462">
-        <v>0.003270446431151916</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I462">
-        <v>-0.4618391682161058</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J462">
-        <v>-0.1839168216105812</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K462">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L462">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M462">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="N462">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="O462">
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24463,1849 +24418,99 @@
         <v>0</v>
       </c>
       <c r="B463" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C463">
-        <v>3.389468548537006</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D463" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E463">
-        <v>2.84729319945796</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F463">
         <v>-1</v>
       </c>
       <c r="G463">
-        <v>0.002850531451462994</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H463">
-        <v>0.002372706800542039</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I463">
-        <v>0.5421753490790455</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J463">
-        <v>-0.2010959317440343</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K463">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L463">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="M463">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N463">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="O463">
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
     </row>
     <row r="464" spans="1:16">
       <c r="A464" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B464" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C464">
-        <v>3.393654856933491</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D464" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E464">
-        <v>3.855665816250932</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F464">
         <v>-1</v>
       </c>
       <c r="G464">
-        <v>0.002786345143066508</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H464">
-        <v>0.003244334183749068</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I464">
-        <v>-0.4620109593174404</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J464">
-        <v>-0.2010959317440343</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K464">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="L464">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="M464">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="N464">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="O464">
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="465" spans="1:16">
-      <c r="A465" s="1">
-        <v>0</v>
-      </c>
-      <c r="B465" t="s">
-        <v>54</v>
-      </c>
-      <c r="C465">
-        <v>3.405631973633047</v>
-      </c>
-      <c r="D465" t="s">
-        <v>127</v>
-      </c>
-      <c r="E465">
-        <v>2.847516321958264</v>
-      </c>
-      <c r="F465">
-        <v>-1</v>
-      </c>
-      <c r="G465">
-        <v>0.002894368026366953</v>
-      </c>
-      <c r="H465">
-        <v>0.002372483678041736</v>
-      </c>
-      <c r="I465">
-        <v>0.5581156516747829</v>
-      </c>
-      <c r="J465">
-        <v>-0.2012850186086983</v>
-      </c>
-      <c r="K465">
-        <v>1.27</v>
-      </c>
-      <c r="L465">
-        <v>3.15</v>
-      </c>
-      <c r="M465">
-        <v>1.18</v>
-      </c>
-      <c r="N465">
-        <v>2.61</v>
-      </c>
-      <c r="O465">
-        <v>1</v>
-      </c>
-      <c r="P465" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="466" spans="1:16">
-      <c r="A466" s="1">
-        <v>1</v>
-      </c>
-      <c r="B466" t="s">
-        <v>52</v>
-      </c>
-      <c r="C466">
-        <v>3.393940378099134</v>
-      </c>
-      <c r="D466" t="s">
-        <v>124</v>
-      </c>
-      <c r="E466">
-        <v>3.855953228285221</v>
-      </c>
-      <c r="F466">
-        <v>-1</v>
-      </c>
-      <c r="G466">
-        <v>0.002786059621900865</v>
-      </c>
-      <c r="H466">
-        <v>0.003244046771714778</v>
-      </c>
-      <c r="I466">
-        <v>-0.462012850186087</v>
-      </c>
-      <c r="J466">
-        <v>-0.2012850186086983</v>
-      </c>
-      <c r="K466">
-        <v>1.51</v>
-      </c>
-      <c r="L466">
-        <v>3.09</v>
-      </c>
-      <c r="M466">
-        <v>1.52</v>
-      </c>
-      <c r="N466">
-        <v>3.55</v>
-      </c>
-      <c r="O466">
-        <v>1</v>
-      </c>
-      <c r="P466" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="467" spans="1:16">
-      <c r="A467" s="1">
-        <v>0</v>
-      </c>
-      <c r="B467" t="s">
-        <v>54</v>
-      </c>
-      <c r="C467">
-        <v>3.41044845810583</v>
-      </c>
-      <c r="D467" t="s">
-        <v>127</v>
-      </c>
-      <c r="E467">
-        <v>2.851991480759747</v>
-      </c>
-      <c r="F467">
-        <v>-1</v>
-      </c>
-      <c r="G467">
-        <v>0.00288955154189417</v>
-      </c>
-      <c r="H467">
-        <v>0.002368008519240253</v>
-      </c>
-      <c r="I467">
-        <v>0.5584569773460828</v>
-      </c>
-      <c r="J467">
-        <v>-0.2050775260675825</v>
-      </c>
-      <c r="K467">
-        <v>1.27</v>
-      </c>
-      <c r="L467">
-        <v>3.15</v>
-      </c>
-      <c r="M467">
-        <v>1.18</v>
-      </c>
-      <c r="N467">
-        <v>2.61</v>
-      </c>
-      <c r="O467">
-        <v>1</v>
-      </c>
-      <c r="P467" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="468" spans="1:16">
-      <c r="A468" s="1">
-        <v>1</v>
-      </c>
-      <c r="B468" t="s">
-        <v>52</v>
-      </c>
-      <c r="C468">
-        <v>3.399667064362049</v>
-      </c>
-      <c r="D468" t="s">
-        <v>124</v>
-      </c>
-      <c r="E468">
-        <v>3.861717839622725</v>
-      </c>
-      <c r="F468">
-        <v>-1</v>
-      </c>
-      <c r="G468">
-        <v>0.00278033293563795</v>
-      </c>
-      <c r="H468">
-        <v>0.003238282160377275</v>
-      </c>
-      <c r="I468">
-        <v>-0.4620507752606757</v>
-      </c>
-      <c r="J468">
-        <v>-0.2050775260675825</v>
-      </c>
-      <c r="K468">
-        <v>1.51</v>
-      </c>
-      <c r="L468">
-        <v>3.09</v>
-      </c>
-      <c r="M468">
-        <v>1.52</v>
-      </c>
-      <c r="N468">
-        <v>3.55</v>
-      </c>
-      <c r="O468">
-        <v>1</v>
-      </c>
-      <c r="P468" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="469" spans="1:16">
-      <c r="A469" s="1">
-        <v>0</v>
-      </c>
-      <c r="B469" t="s">
-        <v>54</v>
-      </c>
-      <c r="C469">
-        <v>3.414359629198952</v>
-      </c>
-      <c r="D469" t="s">
-        <v>127</v>
-      </c>
-      <c r="E469">
-        <v>2.855625482247845</v>
-      </c>
-      <c r="F469">
-        <v>-1</v>
-      </c>
-      <c r="G469">
-        <v>0.002885640370801048</v>
-      </c>
-      <c r="H469">
-        <v>0.002364374517752155</v>
-      </c>
-      <c r="I469">
-        <v>0.5587341469511067</v>
-      </c>
-      <c r="J469">
-        <v>-0.2081571883456315</v>
-      </c>
-      <c r="K469">
-        <v>1.27</v>
-      </c>
-      <c r="L469">
-        <v>3.15</v>
-      </c>
-      <c r="M469">
-        <v>1.18</v>
-      </c>
-      <c r="N469">
-        <v>2.61</v>
-      </c>
-      <c r="O469">
-        <v>1</v>
-      </c>
-      <c r="P469" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="470" spans="1:16">
-      <c r="A470" s="1">
-        <v>1</v>
-      </c>
-      <c r="B470" t="s">
-        <v>52</v>
-      </c>
-      <c r="C470">
-        <v>3.404317354401903</v>
-      </c>
-      <c r="D470" t="s">
-        <v>124</v>
-      </c>
-      <c r="E470">
-        <v>3.86639892628536</v>
-      </c>
-      <c r="F470">
-        <v>-1</v>
-      </c>
-      <c r="G470">
-        <v>0.002775682645598096</v>
-      </c>
-      <c r="H470">
-        <v>0.00323360107371464</v>
-      </c>
-      <c r="I470">
-        <v>-0.4620815718834566</v>
-      </c>
-      <c r="J470">
-        <v>-0.2081571883456315</v>
-      </c>
-      <c r="K470">
-        <v>1.51</v>
-      </c>
-      <c r="L470">
-        <v>3.09</v>
-      </c>
-      <c r="M470">
-        <v>1.52</v>
-      </c>
-      <c r="N470">
-        <v>3.55</v>
-      </c>
-      <c r="O470">
-        <v>1</v>
-      </c>
-      <c r="P470" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="471" spans="1:16">
-      <c r="A471" s="1">
-        <v>0</v>
-      </c>
-      <c r="B471" t="s">
-        <v>54</v>
-      </c>
-      <c r="C471">
-        <v>3.397763113288954</v>
-      </c>
-      <c r="D471" t="s">
-        <v>127</v>
-      </c>
-      <c r="E471">
-        <v>2.840205097386587</v>
-      </c>
-      <c r="F471">
-        <v>-1</v>
-      </c>
-      <c r="G471">
-        <v>0.002902236886711046</v>
-      </c>
-      <c r="H471">
-        <v>0.002379794902613413</v>
-      </c>
-      <c r="I471">
-        <v>0.5575580159023672</v>
-      </c>
-      <c r="J471">
-        <v>-0.1950890655818535</v>
-      </c>
-      <c r="K471">
-        <v>1.27</v>
-      </c>
-      <c r="L471">
-        <v>3.15</v>
-      </c>
-      <c r="M471">
-        <v>1.18</v>
-      </c>
-      <c r="N471">
-        <v>2.61</v>
-      </c>
-      <c r="O471">
-        <v>1</v>
-      </c>
-      <c r="P471" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="472" spans="1:16">
-      <c r="A472" s="1">
-        <v>0</v>
-      </c>
-      <c r="B472" t="s">
-        <v>54</v>
-      </c>
-      <c r="C472">
-        <v>3.417402047821969</v>
-      </c>
-      <c r="D472" t="s">
-        <v>127</v>
-      </c>
-      <c r="E472">
-        <v>2.858452296401515</v>
-      </c>
-      <c r="F472">
-        <v>-1</v>
-      </c>
-      <c r="G472">
-        <v>0.002882597952178031</v>
-      </c>
-      <c r="H472">
-        <v>0.002361547703598485</v>
-      </c>
-      <c r="I472">
-        <v>0.5589497514204544</v>
-      </c>
-      <c r="J472">
-        <v>-0.2105527935606056</v>
-      </c>
-      <c r="K472">
-        <v>1.27</v>
-      </c>
-      <c r="L472">
-        <v>3.15</v>
-      </c>
-      <c r="M472">
-        <v>1.18</v>
-      </c>
-      <c r="N472">
-        <v>2.61</v>
-      </c>
-      <c r="O472">
-        <v>1</v>
-      </c>
-      <c r="P472" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="473" spans="1:16">
-      <c r="A473" s="1">
-        <v>0</v>
-      </c>
-      <c r="B473" t="s">
-        <v>54</v>
-      </c>
-      <c r="C473">
-        <v>3.431035380645926</v>
-      </c>
-      <c r="D473" t="s">
-        <v>127</v>
-      </c>
-      <c r="E473">
-        <v>2.871119487529286</v>
-      </c>
-      <c r="F473">
-        <v>-1</v>
-      </c>
-      <c r="G473">
-        <v>0.002868964619354074</v>
-      </c>
-      <c r="H473">
-        <v>0.002348880512470714</v>
-      </c>
-      <c r="I473">
-        <v>0.5599158931166404</v>
-      </c>
-      <c r="J473">
-        <v>-0.2212877012960047</v>
-      </c>
-      <c r="K473">
-        <v>1.27</v>
-      </c>
-      <c r="L473">
-        <v>3.15</v>
-      </c>
-      <c r="M473">
-        <v>1.18</v>
-      </c>
-      <c r="N473">
-        <v>2.61</v>
-      </c>
-      <c r="O473">
-        <v>1</v>
-      </c>
-      <c r="P473" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="474" spans="1:16">
-      <c r="A474" s="1">
-        <v>0</v>
-      </c>
-      <c r="B474" t="s">
-        <v>54</v>
-      </c>
-      <c r="C474">
-        <v>3.445724673607667</v>
-      </c>
-      <c r="D474" t="s">
-        <v>127</v>
-      </c>
-      <c r="E474">
-        <v>2.884767806974053</v>
-      </c>
-      <c r="F474">
-        <v>-1</v>
-      </c>
-      <c r="G474">
-        <v>0.002854275326392333</v>
-      </c>
-      <c r="H474">
-        <v>0.002335232193025947</v>
-      </c>
-      <c r="I474">
-        <v>0.5609568666336142</v>
-      </c>
-      <c r="J474">
-        <v>-0.2328540737068246</v>
-      </c>
-      <c r="K474">
-        <v>1.27</v>
-      </c>
-      <c r="L474">
-        <v>3.15</v>
-      </c>
-      <c r="M474">
-        <v>1.18</v>
-      </c>
-      <c r="N474">
-        <v>2.61</v>
-      </c>
-      <c r="O474">
-        <v>1</v>
-      </c>
-      <c r="P474" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="475" spans="1:16">
-      <c r="A475" s="1">
-        <v>0</v>
-      </c>
-      <c r="B475" t="s">
-        <v>52</v>
-      </c>
-      <c r="C475">
-        <v>3.498368403837766</v>
-      </c>
-      <c r="D475" t="s">
-        <v>124</v>
-      </c>
-      <c r="E475">
-        <v>3.961072830353248</v>
-      </c>
-      <c r="F475">
-        <v>-1</v>
-      </c>
-      <c r="G475">
-        <v>0.002681631596162234</v>
-      </c>
-      <c r="H475">
-        <v>0.003138927169646752</v>
-      </c>
-      <c r="I475">
-        <v>-0.4627044265154816</v>
-      </c>
-      <c r="J475">
-        <v>-0.2704426515481894</v>
-      </c>
-      <c r="K475">
-        <v>1.51</v>
-      </c>
-      <c r="L475">
-        <v>3.09</v>
-      </c>
-      <c r="M475">
-        <v>1.52</v>
-      </c>
-      <c r="N475">
-        <v>3.55</v>
-      </c>
-      <c r="O475">
-        <v>1</v>
-      </c>
-      <c r="P475" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="476" spans="1:16">
-      <c r="A476" s="1">
-        <v>0</v>
-      </c>
-      <c r="B476" t="s">
-        <v>54</v>
-      </c>
-      <c r="C476">
-        <v>3.380374413778931</v>
-      </c>
-      <c r="D476" t="s">
-        <v>128</v>
-      </c>
-      <c r="E476">
-        <v>2.845862639682621</v>
-      </c>
-      <c r="F476">
-        <v>-1</v>
-      </c>
-      <c r="G476">
-        <v>0.002919625586221069</v>
-      </c>
-      <c r="H476">
-        <v>0.002414137360317379</v>
-      </c>
-      <c r="I476">
-        <v>0.5345117740963108</v>
-      </c>
-      <c r="J476">
-        <v>-0.181397176203883</v>
-      </c>
-      <c r="K476">
-        <v>1.27</v>
-      </c>
-      <c r="L476">
-        <v>3.15</v>
-      </c>
-      <c r="M476">
-        <v>1.19</v>
-      </c>
-      <c r="N476">
-        <v>2.63</v>
-      </c>
-      <c r="O476">
-        <v>1</v>
-      </c>
-      <c r="P476" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="477" spans="1:16">
-      <c r="A477" s="1">
-        <v>0</v>
-      </c>
-      <c r="B477" t="s">
-        <v>54</v>
-      </c>
-      <c r="C477">
-        <v>3.313782027212462</v>
-      </c>
-      <c r="D477" t="s">
-        <v>128</v>
-      </c>
-      <c r="E477">
-        <v>2.783465049120339</v>
-      </c>
-      <c r="F477">
-        <v>-1</v>
-      </c>
-      <c r="G477">
-        <v>0.002986217972787538</v>
-      </c>
-      <c r="H477">
-        <v>0.002476534950879661</v>
-      </c>
-      <c r="I477">
-        <v>0.5303169780921233</v>
-      </c>
-      <c r="J477">
-        <v>-0.1289622261515449</v>
-      </c>
-      <c r="K477">
-        <v>1.27</v>
-      </c>
-      <c r="L477">
-        <v>3.15</v>
-      </c>
-      <c r="M477">
-        <v>1.19</v>
-      </c>
-      <c r="N477">
-        <v>2.63</v>
-      </c>
-      <c r="O477">
-        <v>1</v>
-      </c>
-      <c r="P477" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="478" spans="1:16">
-      <c r="A478" s="1">
-        <v>0</v>
-      </c>
-      <c r="B478" t="s">
-        <v>54</v>
-      </c>
-      <c r="C478">
-        <v>3.264322946458565</v>
-      </c>
-      <c r="D478" t="s">
-        <v>128</v>
-      </c>
-      <c r="E478">
-        <v>2.737121501012356</v>
-      </c>
-      <c r="F478">
-        <v>-1</v>
-      </c>
-      <c r="G478">
-        <v>0.003035677053541435</v>
-      </c>
-      <c r="H478">
-        <v>0.002522878498987644</v>
-      </c>
-      <c r="I478">
-        <v>0.5272014454462086</v>
-      </c>
-      <c r="J478">
-        <v>-0.09001806807761016</v>
-      </c>
-      <c r="K478">
-        <v>1.27</v>
-      </c>
-      <c r="L478">
-        <v>3.15</v>
-      </c>
-      <c r="M478">
-        <v>1.19</v>
-      </c>
-      <c r="N478">
-        <v>2.63</v>
-      </c>
-      <c r="O478">
-        <v>1</v>
-      </c>
-      <c r="P478" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="479" spans="1:16">
-      <c r="A479" s="1">
-        <v>0</v>
-      </c>
-      <c r="B479" t="s">
-        <v>54</v>
-      </c>
-      <c r="C479">
-        <v>3.138712566996877</v>
-      </c>
-      <c r="D479" t="s">
-        <v>128</v>
-      </c>
-      <c r="E479">
-        <v>2.619423586398649</v>
-      </c>
-      <c r="F479">
-        <v>-1</v>
-      </c>
-      <c r="G479">
-        <v>0.003161287433003123</v>
-      </c>
-      <c r="H479">
-        <v>0.002640576413601351</v>
-      </c>
-      <c r="I479">
-        <v>0.5192889805982288</v>
-      </c>
-      <c r="J479">
-        <v>0.008887742522143843</v>
-      </c>
-      <c r="K479">
-        <v>1.27</v>
-      </c>
-      <c r="L479">
-        <v>3.15</v>
-      </c>
-      <c r="M479">
-        <v>1.19</v>
-      </c>
-      <c r="N479">
-        <v>2.63</v>
-      </c>
-      <c r="O479">
-        <v>1</v>
-      </c>
-      <c r="P479" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="480" spans="1:16">
-      <c r="A480" s="1">
-        <v>0</v>
-      </c>
-      <c r="B480" t="s">
-        <v>54</v>
-      </c>
-      <c r="C480">
-        <v>3.089949994782248</v>
-      </c>
-      <c r="D480" t="s">
-        <v>128</v>
-      </c>
-      <c r="E480">
-        <v>2.57373267227628</v>
-      </c>
-      <c r="F480">
-        <v>-1</v>
-      </c>
-      <c r="G480">
-        <v>0.003210050005217752</v>
-      </c>
-      <c r="H480">
-        <v>0.00268626732772372</v>
-      </c>
-      <c r="I480">
-        <v>0.5162173225059683</v>
-      </c>
-      <c r="J480">
-        <v>0.04728346867539508</v>
-      </c>
-      <c r="K480">
-        <v>1.27</v>
-      </c>
-      <c r="L480">
-        <v>3.15</v>
-      </c>
-      <c r="M480">
-        <v>1.19</v>
-      </c>
-      <c r="N480">
-        <v>2.63</v>
-      </c>
-      <c r="O480">
-        <v>1</v>
-      </c>
-      <c r="P480" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="481" spans="1:16">
-      <c r="A481" s="1">
-        <v>0</v>
-      </c>
-      <c r="B481" t="s">
-        <v>54</v>
-      </c>
-      <c r="C481">
-        <v>3.063374762912356</v>
-      </c>
-      <c r="D481" t="s">
-        <v>128</v>
-      </c>
-      <c r="E481">
-        <v>2.548831470760396</v>
-      </c>
-      <c r="F481">
-        <v>-1</v>
-      </c>
-      <c r="G481">
-        <v>0.003236625237087644</v>
-      </c>
-      <c r="H481">
-        <v>0.002711168529239603</v>
-      </c>
-      <c r="I481">
-        <v>0.5145432921519593</v>
-      </c>
-      <c r="J481">
-        <v>0.06820884810050738</v>
-      </c>
-      <c r="K481">
-        <v>1.27</v>
-      </c>
-      <c r="L481">
-        <v>3.15</v>
-      </c>
-      <c r="M481">
-        <v>1.19</v>
-      </c>
-      <c r="N481">
-        <v>2.63</v>
-      </c>
-      <c r="O481">
-        <v>1</v>
-      </c>
-      <c r="P481" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="482" spans="1:16">
-      <c r="A482" s="1">
-        <v>0</v>
-      </c>
-      <c r="B482" t="s">
-        <v>54</v>
-      </c>
-      <c r="C482">
-        <v>3.055789416512437</v>
-      </c>
-      <c r="D482" t="s">
-        <v>128</v>
-      </c>
-      <c r="E482">
-        <v>2.541723941456535</v>
-      </c>
-      <c r="F482">
-        <v>-1</v>
-      </c>
-      <c r="G482">
-        <v>0.003244210583487563</v>
-      </c>
-      <c r="H482">
-        <v>0.002718276058543465</v>
-      </c>
-      <c r="I482">
-        <v>0.5140654750559017</v>
-      </c>
-      <c r="J482">
-        <v>0.07418156180123091</v>
-      </c>
-      <c r="K482">
-        <v>1.27</v>
-      </c>
-      <c r="L482">
-        <v>3.15</v>
-      </c>
-      <c r="M482">
-        <v>1.19</v>
-      </c>
-      <c r="N482">
-        <v>2.63</v>
-      </c>
-      <c r="O482">
-        <v>1</v>
-      </c>
-      <c r="P482" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="483" spans="1:16">
-      <c r="A483" s="1">
-        <v>0</v>
-      </c>
-      <c r="B483" t="s">
-        <v>54</v>
-      </c>
-      <c r="C483">
-        <v>3.104375930732028</v>
-      </c>
-      <c r="D483" t="s">
-        <v>128</v>
-      </c>
-      <c r="E483">
-        <v>2.58724988785127</v>
-      </c>
-      <c r="F483">
-        <v>-1</v>
-      </c>
-      <c r="G483">
-        <v>0.003195624069267972</v>
-      </c>
-      <c r="H483">
-        <v>0.00267275011214873</v>
-      </c>
-      <c r="I483">
-        <v>0.5171260428807578</v>
-      </c>
-      <c r="J483">
-        <v>0.03592446399052947</v>
-      </c>
-      <c r="K483">
-        <v>1.27</v>
-      </c>
-      <c r="L483">
-        <v>3.15</v>
-      </c>
-      <c r="M483">
-        <v>1.19</v>
-      </c>
-      <c r="N483">
-        <v>2.63</v>
-      </c>
-      <c r="O483">
-        <v>1</v>
-      </c>
-      <c r="P483" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="484" spans="1:16">
-      <c r="A484" s="1">
-        <v>0</v>
-      </c>
-      <c r="B484" t="s">
-        <v>54</v>
-      </c>
-      <c r="C484">
-        <v>3.091039723067857</v>
-      </c>
-      <c r="D484" t="s">
-        <v>128</v>
-      </c>
-      <c r="E484">
-        <v>2.574753756260433</v>
-      </c>
-      <c r="F484">
-        <v>-1</v>
-      </c>
-      <c r="G484">
-        <v>0.003208960276932143</v>
-      </c>
-      <c r="H484">
-        <v>0.002685246243739567</v>
-      </c>
-      <c r="I484">
-        <v>0.5162859668074238</v>
-      </c>
-      <c r="J484">
-        <v>0.04642541490719935</v>
-      </c>
-      <c r="K484">
-        <v>1.27</v>
-      </c>
-      <c r="L484">
-        <v>3.15</v>
-      </c>
-      <c r="M484">
-        <v>1.19</v>
-      </c>
-      <c r="N484">
-        <v>2.63</v>
-      </c>
-      <c r="O484">
-        <v>1</v>
-      </c>
-      <c r="P484" t="s">
         <v>313</v>
-      </c>
-    </row>
-    <row r="485" spans="1:16">
-      <c r="A485" s="1">
-        <v>0</v>
-      </c>
-      <c r="B485" t="s">
-        <v>54</v>
-      </c>
-      <c r="C485">
-        <v>3.067225510045163</v>
-      </c>
-      <c r="D485" t="s">
-        <v>128</v>
-      </c>
-      <c r="E485">
-        <v>2.552439651144681</v>
-      </c>
-      <c r="F485">
-        <v>-1</v>
-      </c>
-      <c r="G485">
-        <v>0.003232774489954837</v>
-      </c>
-      <c r="H485">
-        <v>0.002707560348855319</v>
-      </c>
-      <c r="I485">
-        <v>0.5147858589004826</v>
-      </c>
-      <c r="J485">
-        <v>0.06517676374396589</v>
-      </c>
-      <c r="K485">
-        <v>1.27</v>
-      </c>
-      <c r="L485">
-        <v>3.15</v>
-      </c>
-      <c r="M485">
-        <v>1.19</v>
-      </c>
-      <c r="N485">
-        <v>2.63</v>
-      </c>
-      <c r="O485">
-        <v>1</v>
-      </c>
-      <c r="P485" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="486" spans="1:16">
-      <c r="A486" s="1">
-        <v>0</v>
-      </c>
-      <c r="B486" t="s">
-        <v>54</v>
-      </c>
-      <c r="C486">
-        <v>3.032421580463965</v>
-      </c>
-      <c r="D486" t="s">
-        <v>128</v>
-      </c>
-      <c r="E486">
-        <v>2.519828095080408</v>
-      </c>
-      <c r="F486">
-        <v>-1</v>
-      </c>
-      <c r="G486">
-        <v>0.003267578419536035</v>
-      </c>
-      <c r="H486">
-        <v>0.002740171904919592</v>
-      </c>
-      <c r="I486">
-        <v>0.5125934853835572</v>
-      </c>
-      <c r="J486">
-        <v>0.09258143270553931</v>
-      </c>
-      <c r="K486">
-        <v>1.27</v>
-      </c>
-      <c r="L486">
-        <v>3.15</v>
-      </c>
-      <c r="M486">
-        <v>1.19</v>
-      </c>
-      <c r="N486">
-        <v>2.63</v>
-      </c>
-      <c r="O486">
-        <v>1</v>
-      </c>
-      <c r="P486" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="487" spans="1:16">
-      <c r="A487" s="1">
-        <v>0</v>
-      </c>
-      <c r="B487" t="s">
-        <v>54</v>
-      </c>
-      <c r="C487">
-        <v>3.02355949889196</v>
-      </c>
-      <c r="D487" t="s">
-        <v>128</v>
-      </c>
-      <c r="E487">
-        <v>2.51152425486727</v>
-      </c>
-      <c r="F487">
-        <v>-1</v>
-      </c>
-      <c r="G487">
-        <v>0.003276440501108039</v>
-      </c>
-      <c r="H487">
-        <v>0.00274847574513273</v>
-      </c>
-      <c r="I487">
-        <v>0.5120352440246907</v>
-      </c>
-      <c r="J487">
-        <v>0.09955944969136986</v>
-      </c>
-      <c r="K487">
-        <v>1.27</v>
-      </c>
-      <c r="L487">
-        <v>3.15</v>
-      </c>
-      <c r="M487">
-        <v>1.19</v>
-      </c>
-      <c r="N487">
-        <v>2.63</v>
-      </c>
-      <c r="O487">
-        <v>1</v>
-      </c>
-      <c r="P487" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="488" spans="1:16">
-      <c r="A488" s="1">
-        <v>0</v>
-      </c>
-      <c r="B488" t="s">
-        <v>54</v>
-      </c>
-      <c r="C488">
-        <v>3.013518087781226</v>
-      </c>
-      <c r="D488" t="s">
-        <v>128</v>
-      </c>
-      <c r="E488">
-        <v>2.502115373590282</v>
-      </c>
-      <c r="F488">
-        <v>-1</v>
-      </c>
-      <c r="G488">
-        <v>0.003286481912218774</v>
-      </c>
-      <c r="H488">
-        <v>0.002757884626409718</v>
-      </c>
-      <c r="I488">
-        <v>0.5114027141909436</v>
-      </c>
-      <c r="J488">
-        <v>0.1074660726132081</v>
-      </c>
-      <c r="K488">
-        <v>1.27</v>
-      </c>
-      <c r="L488">
-        <v>3.15</v>
-      </c>
-      <c r="M488">
-        <v>1.19</v>
-      </c>
-      <c r="N488">
-        <v>2.63</v>
-      </c>
-      <c r="O488">
-        <v>1</v>
-      </c>
-      <c r="P488" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="489" spans="1:16">
-      <c r="A489" s="1">
-        <v>0</v>
-      </c>
-      <c r="B489" t="s">
-        <v>54</v>
-      </c>
-      <c r="C489">
-        <v>3.019433914437102</v>
-      </c>
-      <c r="D489" t="s">
-        <v>128</v>
-      </c>
-      <c r="E489">
-        <v>2.507658549748151</v>
-      </c>
-      <c r="F489">
-        <v>-1</v>
-      </c>
-      <c r="G489">
-        <v>0.003280566085562898</v>
-      </c>
-      <c r="H489">
-        <v>0.002752341450251849</v>
-      </c>
-      <c r="I489">
-        <v>0.5117753646889511</v>
-      </c>
-      <c r="J489">
-        <v>0.1028079413881086</v>
-      </c>
-      <c r="K489">
-        <v>1.27</v>
-      </c>
-      <c r="L489">
-        <v>3.15</v>
-      </c>
-      <c r="M489">
-        <v>1.19</v>
-      </c>
-      <c r="N489">
-        <v>2.63</v>
-      </c>
-      <c r="O489">
-        <v>1</v>
-      </c>
-      <c r="P489" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="490" spans="1:16">
-      <c r="A490" s="1">
-        <v>0</v>
-      </c>
-      <c r="B490" t="s">
-        <v>54</v>
-      </c>
-      <c r="C490">
-        <v>3.007887241278468</v>
-      </c>
-      <c r="D490" t="s">
-        <v>128</v>
-      </c>
-      <c r="E490">
-        <v>2.496839226079824</v>
-      </c>
-      <c r="F490">
-        <v>-1</v>
-      </c>
-      <c r="G490">
-        <v>0.003292112758721532</v>
-      </c>
-      <c r="H490">
-        <v>0.002763160773920176</v>
-      </c>
-      <c r="I490">
-        <v>0.5110480151986438</v>
-      </c>
-      <c r="J490">
-        <v>0.1118998100169543</v>
-      </c>
-      <c r="K490">
-        <v>1.27</v>
-      </c>
-      <c r="L490">
-        <v>3.15</v>
-      </c>
-      <c r="M490">
-        <v>1.19</v>
-      </c>
-      <c r="N490">
-        <v>2.63</v>
-      </c>
-      <c r="O490">
-        <v>1</v>
-      </c>
-      <c r="P490" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="491" spans="1:16">
-      <c r="A491" s="1">
-        <v>0</v>
-      </c>
-      <c r="B491" t="s">
-        <v>54</v>
-      </c>
-      <c r="C491">
-        <v>2.983278990739431</v>
-      </c>
-      <c r="D491" t="s">
-        <v>128</v>
-      </c>
-      <c r="E491">
-        <v>2.473781101558994</v>
-      </c>
-      <c r="F491">
-        <v>-1</v>
-      </c>
-      <c r="G491">
-        <v>0.003316721009260569</v>
-      </c>
-      <c r="H491">
-        <v>0.002786218898441006</v>
-      </c>
-      <c r="I491">
-        <v>0.5094978891804369</v>
-      </c>
-      <c r="J491">
-        <v>0.1312763852445424</v>
-      </c>
-      <c r="K491">
-        <v>1.27</v>
-      </c>
-      <c r="L491">
-        <v>3.15</v>
-      </c>
-      <c r="M491">
-        <v>1.19</v>
-      </c>
-      <c r="N491">
-        <v>2.63</v>
-      </c>
-      <c r="O491">
-        <v>1</v>
-      </c>
-      <c r="P491" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="492" spans="1:16">
-      <c r="A492" s="1">
-        <v>0</v>
-      </c>
-      <c r="B492" t="s">
-        <v>54</v>
-      </c>
-      <c r="C492">
-        <v>2.939029445907243</v>
-      </c>
-      <c r="D492" t="s">
-        <v>128</v>
-      </c>
-      <c r="E492">
-        <v>2.432318929629621</v>
-      </c>
-      <c r="F492">
-        <v>-1</v>
-      </c>
-      <c r="G492">
-        <v>0.003360970554092757</v>
-      </c>
-      <c r="H492">
-        <v>0.002827681070370379</v>
-      </c>
-      <c r="I492">
-        <v>0.5067105162776215</v>
-      </c>
-      <c r="J492">
-        <v>0.16611854652973</v>
-      </c>
-      <c r="K492">
-        <v>1.27</v>
-      </c>
-      <c r="L492">
-        <v>3.15</v>
-      </c>
-      <c r="M492">
-        <v>1.19</v>
-      </c>
-      <c r="N492">
-        <v>2.63</v>
-      </c>
-      <c r="O492">
-        <v>1</v>
-      </c>
-      <c r="P492" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="493" spans="1:16">
-      <c r="A493" s="1">
-        <v>0</v>
-      </c>
-      <c r="B493" t="s">
-        <v>54</v>
-      </c>
-      <c r="C493">
-        <v>2.879305740765434</v>
-      </c>
-      <c r="D493" t="s">
-        <v>128</v>
-      </c>
-      <c r="E493">
-        <v>2.376357347646351</v>
-      </c>
-      <c r="F493">
-        <v>-1</v>
-      </c>
-      <c r="G493">
-        <v>0.003420694259234566</v>
-      </c>
-      <c r="H493">
-        <v>0.002883642652353649</v>
-      </c>
-      <c r="I493">
-        <v>0.5029483931190826</v>
-      </c>
-      <c r="J493">
-        <v>0.2131450860114693</v>
-      </c>
-      <c r="K493">
-        <v>1.27</v>
-      </c>
-      <c r="L493">
-        <v>3.15</v>
-      </c>
-      <c r="M493">
-        <v>1.19</v>
-      </c>
-      <c r="N493">
-        <v>2.63</v>
-      </c>
-      <c r="O493">
-        <v>1</v>
-      </c>
-      <c r="P493" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="494" spans="1:16">
-      <c r="A494" s="1">
-        <v>0</v>
-      </c>
-      <c r="B494" t="s">
-        <v>50</v>
-      </c>
-      <c r="C494">
-        <v>2.710585509297514</v>
-      </c>
-      <c r="D494" t="s">
-        <v>128</v>
-      </c>
-      <c r="E494">
-        <v>2.26641548960003</v>
-      </c>
-      <c r="F494">
-        <v>-1</v>
-      </c>
-      <c r="G494">
-        <v>0.003529414490702487</v>
-      </c>
-      <c r="H494">
-        <v>0.00299358451039997</v>
-      </c>
-      <c r="I494">
-        <v>0.4441700196974834</v>
-      </c>
-      <c r="J494">
-        <v>0.3055332020167811</v>
-      </c>
-      <c r="K494">
-        <v>1.34</v>
-      </c>
-      <c r="L494">
-        <v>3.12</v>
-      </c>
-      <c r="M494">
-        <v>1.19</v>
-      </c>
-      <c r="N494">
-        <v>2.63</v>
-      </c>
-      <c r="O494">
-        <v>1</v>
-      </c>
-      <c r="P494" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="495" spans="1:16">
-      <c r="A495" s="1">
-        <v>0</v>
-      </c>
-      <c r="B495" t="s">
-        <v>50</v>
-      </c>
-      <c r="C495">
-        <v>2.647551728558422</v>
-      </c>
-      <c r="D495" t="s">
-        <v>128</v>
-      </c>
-      <c r="E495">
-        <v>2.210437729092927</v>
-      </c>
-      <c r="F495">
-        <v>-1</v>
-      </c>
-      <c r="G495">
-        <v>0.003592448271441579</v>
-      </c>
-      <c r="H495">
-        <v>0.003049562270907073</v>
-      </c>
-      <c r="I495">
-        <v>0.4371139994654949</v>
-      </c>
-      <c r="J495">
-        <v>0.3525733368967002</v>
-      </c>
-      <c r="K495">
-        <v>1.34</v>
-      </c>
-      <c r="L495">
-        <v>3.12</v>
-      </c>
-      <c r="M495">
-        <v>1.19</v>
-      </c>
-      <c r="N495">
-        <v>2.63</v>
-      </c>
-      <c r="O495">
-        <v>1</v>
-      </c>
-      <c r="P495" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="496" spans="1:16">
-      <c r="A496" s="1">
-        <v>0</v>
-      </c>
-      <c r="B496" t="s">
-        <v>50</v>
-      </c>
-      <c r="C496">
-        <v>2.59897387935353</v>
-      </c>
-      <c r="D496" t="s">
-        <v>128</v>
-      </c>
-      <c r="E496">
-        <v>2.167297698828881</v>
-      </c>
-      <c r="F496">
-        <v>-1</v>
-      </c>
-      <c r="G496">
-        <v>0.003641026120646471</v>
-      </c>
-      <c r="H496">
-        <v>0.003092702301171119</v>
-      </c>
-      <c r="I496">
-        <v>0.431676180524649</v>
-      </c>
-      <c r="J496">
-        <v>0.3888254631690077</v>
-      </c>
-      <c r="K496">
-        <v>1.34</v>
-      </c>
-      <c r="L496">
-        <v>3.12</v>
-      </c>
-      <c r="M496">
-        <v>1.19</v>
-      </c>
-      <c r="N496">
-        <v>2.63</v>
-      </c>
-      <c r="O496">
-        <v>1</v>
-      </c>
-      <c r="P496" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="497" spans="1:16">
-      <c r="A497" s="1">
-        <v>0</v>
-      </c>
-      <c r="B497" t="s">
-        <v>50</v>
-      </c>
-      <c r="C497">
-        <v>2.575095597538799</v>
-      </c>
-      <c r="D497" t="s">
-        <v>128</v>
-      </c>
-      <c r="E497">
-        <v>2.146092359008336</v>
-      </c>
-      <c r="F497">
-        <v>-1</v>
-      </c>
-      <c r="G497">
-        <v>0.003664904402461202</v>
-      </c>
-      <c r="H497">
-        <v>0.003113907640991664</v>
-      </c>
-      <c r="I497">
-        <v>0.4290032385304627</v>
-      </c>
-      <c r="J497">
-        <v>0.4066450764635833</v>
-      </c>
-      <c r="K497">
-        <v>1.34</v>
-      </c>
-      <c r="L497">
-        <v>3.12</v>
-      </c>
-      <c r="M497">
-        <v>1.19</v>
-      </c>
-      <c r="N497">
-        <v>2.63</v>
-      </c>
-      <c r="O497">
-        <v>1</v>
-      </c>
-      <c r="P497" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="498" spans="1:16">
-      <c r="A498" s="1">
-        <v>0</v>
-      </c>
-      <c r="B498" t="s">
-        <v>50</v>
-      </c>
-      <c r="C498">
-        <v>2.513392232045375</v>
-      </c>
-      <c r="D498" t="s">
-        <v>128</v>
-      </c>
-      <c r="E498">
-        <v>2.091296086667161</v>
-      </c>
-      <c r="F498">
-        <v>-1</v>
-      </c>
-      <c r="G498">
-        <v>0.003726607767954625</v>
-      </c>
-      <c r="H498">
-        <v>0.003168703913332839</v>
-      </c>
-      <c r="I498">
-        <v>0.4220961453782142</v>
-      </c>
-      <c r="J498">
-        <v>0.4526923641452424</v>
-      </c>
-      <c r="K498">
-        <v>1.34</v>
-      </c>
-      <c r="L498">
-        <v>3.12</v>
-      </c>
-      <c r="M498">
-        <v>1.19</v>
-      </c>
-      <c r="N498">
-        <v>2.63</v>
-      </c>
-      <c r="O498">
-        <v>1</v>
-      </c>
-      <c r="P498" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="499" spans="1:16">
-      <c r="A499" s="1">
-        <v>0</v>
-      </c>
-      <c r="B499" t="s">
-        <v>50</v>
-      </c>
-      <c r="C499">
-        <v>2.46037019732591</v>
-      </c>
-      <c r="D499" t="s">
-        <v>128</v>
-      </c>
-      <c r="E499">
-        <v>2.044209354341666</v>
-      </c>
-      <c r="F499">
-        <v>-1</v>
-      </c>
-      <c r="G499">
-        <v>0.00377962980267409</v>
-      </c>
-      <c r="H499">
-        <v>0.003215790645658334</v>
-      </c>
-      <c r="I499">
-        <v>0.4161608429842438</v>
-      </c>
-      <c r="J499">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K499">
-        <v>1.34</v>
-      </c>
-      <c r="L499">
-        <v>3.12</v>
-      </c>
-      <c r="M499">
-        <v>1.19</v>
-      </c>
-      <c r="N499">
-        <v>2.63</v>
-      </c>
-      <c r="O499">
-        <v>1</v>
-      </c>
-      <c r="P499" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="331">
   <si>
     <t>trade_time</t>
   </si>
@@ -394,7 +394,7 @@
     <t>2021-04-23</t>
   </si>
   <si>
-    <t>2021-09-24</t>
+    <t>2021-09-28</t>
   </si>
   <si>
     <t>2021-04-15</t>
@@ -875,6 +875,24 @@
   </si>
   <si>
     <t>2020-12-15</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
   </si>
   <si>
     <t>2020-12-24</t>
@@ -1346,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P481"/>
+  <dimension ref="A1:P483"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -22760,7 +22778,7 @@
         <v>126</v>
       </c>
       <c r="E429">
-        <v>4.024545223359964</v>
+        <v>4.120993158546191</v>
       </c>
       <c r="F429">
         <v>-1</v>
@@ -22769,10 +22787,10 @@
         <v>0.003102510768538314</v>
       </c>
       <c r="H429">
-        <v>0.003135454776640036</v>
+        <v>0.00327900684145381</v>
       </c>
       <c r="I429">
-        <v>-0.0270559918982789</v>
+        <v>-0.1235039270845055</v>
       </c>
       <c r="J429">
         <v>-0.2944008101721614</v>
@@ -22784,10 +22802,10 @@
         <v>3.55</v>
       </c>
       <c r="M429">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N429">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O429">
         <v>1</v>
@@ -22810,7 +22828,7 @@
         <v>126</v>
       </c>
       <c r="E430">
-        <v>4.013470605461004</v>
+        <v>4.110505275370355</v>
       </c>
       <c r="F430">
         <v>-1</v>
@@ -22819,10 +22837,10 @@
         <v>0.003113658728277664</v>
       </c>
       <c r="H430">
-        <v>0.003146529394538996</v>
+        <v>0.003289494724629645</v>
       </c>
       <c r="I430">
-        <v>-0.02712933373866866</v>
+        <v>-0.1241640036480196</v>
       </c>
       <c r="J430">
         <v>-0.2870666261331153</v>
@@ -22834,10 +22852,10 @@
         <v>3.55</v>
       </c>
       <c r="M430">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N430">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O430">
         <v>1</v>
@@ -22860,7 +22878,7 @@
         <v>126</v>
       </c>
       <c r="E431">
-        <v>3.990842102418018</v>
+        <v>4.089075633415739</v>
       </c>
       <c r="F431">
         <v>-1</v>
@@ -22869,10 +22887,10 @@
         <v>0.003136437088956697</v>
       </c>
       <c r="H431">
-        <v>0.003169157897581982</v>
+        <v>0.003310924366584261</v>
       </c>
       <c r="I431">
-        <v>-0.02727919137471524</v>
+        <v>-0.1255127223724362</v>
       </c>
       <c r="J431">
         <v>-0.2720808625284886</v>
@@ -22884,10 +22902,10 @@
         <v>3.55</v>
       </c>
       <c r="M431">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N431">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O431">
         <v>1</v>
@@ -22910,7 +22928,7 @@
         <v>126</v>
       </c>
       <c r="E432">
-        <v>3.972113454143313</v>
+        <v>4.071339231407243</v>
       </c>
       <c r="F432">
         <v>-1</v>
@@ -22919,10 +22937,10 @@
         <v>0.003155289768014679</v>
       </c>
       <c r="H432">
-        <v>0.003187886545856688</v>
+        <v>0.003328660768592758</v>
       </c>
       <c r="I432">
-        <v>-0.02740322215799162</v>
+        <v>-0.1266289994219219</v>
       </c>
       <c r="J432">
         <v>-0.259677784200869</v>
@@ -22934,10 +22952,10 @@
         <v>3.55</v>
       </c>
       <c r="M432">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N432">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O432">
         <v>1</v>
@@ -22960,7 +22978,7 @@
         <v>126</v>
       </c>
       <c r="E433">
-        <v>3.952491724704075</v>
+        <v>4.052757063792601</v>
       </c>
       <c r="F433">
         <v>-1</v>
@@ -22969,10 +22987,10 @@
         <v>0.00317504144268199</v>
       </c>
       <c r="H433">
-        <v>0.003207508275295925</v>
+        <v>0.003347242936207399</v>
       </c>
       <c r="I433">
-        <v>-0.02753316738606593</v>
+        <v>-0.1277985064745919</v>
       </c>
       <c r="J433">
         <v>-0.2466832613934271</v>
@@ -22984,10 +23002,10 @@
         <v>3.55</v>
       </c>
       <c r="M433">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N433">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O433">
         <v>1</v>
@@ -23010,7 +23028,7 @@
         <v>126</v>
       </c>
       <c r="E434">
-        <v>3.931204060591023</v>
+        <v>4.032597222943817</v>
       </c>
       <c r="F434">
         <v>-1</v>
@@ -23019,10 +23037,10 @@
         <v>0.003196470084703076</v>
       </c>
       <c r="H434">
-        <v>0.003228795939408977</v>
+        <v>0.003367402777056183</v>
       </c>
       <c r="I434">
-        <v>-0.02767414529409962</v>
+        <v>-0.1290673076468933</v>
       </c>
       <c r="J434">
         <v>-0.2325854705900817</v>
@@ -23034,10 +23052,10 @@
         <v>3.55</v>
       </c>
       <c r="M434">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N434">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O434">
         <v>1</v>
@@ -23060,7 +23078,7 @@
         <v>126</v>
       </c>
       <c r="E435">
-        <v>3.914313381461833</v>
+        <v>4.016601414232067</v>
       </c>
       <c r="F435">
         <v>-1</v>
@@ -23069,10 +23087,10 @@
         <v>0.003213472622634446</v>
       </c>
       <c r="H435">
-        <v>0.003245686618538167</v>
+        <v>0.003383398585767933</v>
       </c>
       <c r="I435">
-        <v>-0.02778600409627963</v>
+        <v>-0.1300740368665134</v>
       </c>
       <c r="J435">
         <v>-0.2213995903720749</v>
@@ -23084,10 +23102,10 @@
         <v>3.55</v>
       </c>
       <c r="M435">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N435">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O435">
         <v>1</v>
@@ -23110,7 +23128,7 @@
         <v>126</v>
       </c>
       <c r="E436">
-        <v>3.901368444324518</v>
+        <v>4.004342301578848</v>
       </c>
       <c r="F436">
         <v>-1</v>
@@ -23119,10 +23137,10 @@
         <v>0.003226503287832273</v>
       </c>
       <c r="H436">
-        <v>0.003258631555675482</v>
+        <v>0.003395657698421152</v>
       </c>
       <c r="I436">
-        <v>-0.0278717321567914</v>
+        <v>-0.1308455894111216</v>
       </c>
       <c r="J436">
         <v>-0.212826784320873</v>
@@ -23134,10 +23152,10 @@
         <v>3.55</v>
       </c>
       <c r="M436">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N436">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O436">
         <v>1</v>
@@ -23160,7 +23178,7 @@
         <v>126</v>
       </c>
       <c r="E437">
-        <v>3.889599454778662</v>
+        <v>3.993196834657938</v>
       </c>
       <c r="F437">
         <v>-1</v>
@@ -23169,10 +23187,10 @@
         <v>0.003238350217706248</v>
       </c>
       <c r="H437">
-        <v>0.003270400545221338</v>
+        <v>0.003406803165342062</v>
       </c>
       <c r="I437">
-        <v>-0.02794967248490998</v>
+        <v>-0.1315470523641862</v>
       </c>
       <c r="J437">
         <v>-0.2050327515090475</v>
@@ -23184,10 +23202,10 @@
         <v>3.55</v>
       </c>
       <c r="M437">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N437">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O437">
         <v>1</v>
@@ -23204,28 +23222,28 @@
         <v>54</v>
       </c>
       <c r="C438">
-        <v>3.829553568848083</v>
+        <v>3.834878726120355</v>
       </c>
       <c r="D438" t="s">
         <v>126</v>
       </c>
       <c r="E438">
-        <v>3.857714400631977</v>
+        <v>3.968010906810598</v>
       </c>
       <c r="F438">
         <v>-1</v>
       </c>
       <c r="G438">
-        <v>0.003270446431151916</v>
+        <v>0.003265121273879644</v>
       </c>
       <c r="H438">
-        <v>0.003302285599368023</v>
+        <v>0.003431989093189403</v>
       </c>
       <c r="I438">
-        <v>-0.02816083178389439</v>
+        <v>-0.1331321806902426</v>
       </c>
       <c r="J438">
-        <v>-0.1839168216105812</v>
+        <v>-0.1874202145528653</v>
       </c>
       <c r="K438">
         <v>1.52</v>
@@ -23234,10 +23252,10 @@
         <v>3.55</v>
       </c>
       <c r="M438">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N438">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O438">
         <v>1</v>
@@ -23254,28 +23272,28 @@
         <v>54</v>
       </c>
       <c r="C439">
-        <v>3.855665816250932</v>
+        <v>3.808598117223633</v>
       </c>
       <c r="D439" t="s">
         <v>126</v>
       </c>
       <c r="E439">
-        <v>3.883654856933492</v>
+        <v>3.943286386598549</v>
       </c>
       <c r="F439">
         <v>-1</v>
       </c>
       <c r="G439">
-        <v>0.003244334183749068</v>
+        <v>0.003291401882776367</v>
       </c>
       <c r="H439">
-        <v>0.003276345143066509</v>
+        <v>0.003456713613401451</v>
       </c>
       <c r="I439">
-        <v>-0.02798904068255981</v>
+        <v>-0.1346882693749167</v>
       </c>
       <c r="J439">
-        <v>-0.2010959317440343</v>
+        <v>-0.1701303402787057</v>
       </c>
       <c r="K439">
         <v>1.52</v>
@@ -23284,10 +23302,10 @@
         <v>3.55</v>
       </c>
       <c r="M439">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N439">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O439">
         <v>1</v>
@@ -23304,28 +23322,28 @@
         <v>54</v>
       </c>
       <c r="C440">
-        <v>3.855953228285221</v>
+        <v>3.800233949670756</v>
       </c>
       <c r="D440" t="s">
         <v>126</v>
       </c>
       <c r="E440">
-        <v>3.883940378099135</v>
+        <v>3.935417465808672</v>
       </c>
       <c r="F440">
         <v>-1</v>
       </c>
       <c r="G440">
-        <v>0.003244046771714778</v>
+        <v>0.003299766050329244</v>
       </c>
       <c r="H440">
-        <v>0.003276059621900865</v>
+        <v>0.003464582534191329</v>
       </c>
       <c r="I440">
-        <v>-0.02798714981391326</v>
+        <v>-0.135183516137916</v>
       </c>
       <c r="J440">
-        <v>-0.2012850186086983</v>
+        <v>-0.1646275984676025</v>
       </c>
       <c r="K440">
         <v>1.52</v>
@@ -23334,10 +23352,10 @@
         <v>3.55</v>
       </c>
       <c r="M440">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N440">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O440">
         <v>1</v>
@@ -23354,28 +23372,28 @@
         <v>54</v>
       </c>
       <c r="C441">
-        <v>3.861717839622725</v>
+        <v>3.798188965274105</v>
       </c>
       <c r="D441" t="s">
         <v>126</v>
       </c>
       <c r="E441">
-        <v>3.88966706436205</v>
+        <v>3.933493566014454</v>
       </c>
       <c r="F441">
         <v>-1</v>
       </c>
       <c r="G441">
-        <v>0.003238282160377275</v>
+        <v>0.003301811034725895</v>
       </c>
       <c r="H441">
-        <v>0.003270332935637951</v>
+        <v>0.003466506433985547</v>
       </c>
       <c r="I441">
-        <v>-0.02794922473932449</v>
+        <v>-0.1353046007403491</v>
       </c>
       <c r="J441">
-        <v>-0.2050775260675825</v>
+        <v>-0.1632822139961216</v>
       </c>
       <c r="K441">
         <v>1.52</v>
@@ -23384,10 +23402,10 @@
         <v>3.55</v>
       </c>
       <c r="M441">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N441">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O441">
         <v>1</v>
@@ -23404,28 +23422,28 @@
         <v>54</v>
       </c>
       <c r="C442">
-        <v>3.86639892628536</v>
+        <v>3.788920893245179</v>
       </c>
       <c r="D442" t="s">
         <v>126</v>
       </c>
       <c r="E442">
-        <v>3.894317354401903</v>
+        <v>3.924774261408294</v>
       </c>
       <c r="F442">
         <v>-1</v>
       </c>
       <c r="G442">
-        <v>0.00323360107371464</v>
+        <v>0.00331107910675482</v>
       </c>
       <c r="H442">
-        <v>0.003265682645598097</v>
+        <v>0.003475225738591707</v>
       </c>
       <c r="I442">
-        <v>-0.02791842811654366</v>
+        <v>-0.1358533681631147</v>
       </c>
       <c r="J442">
-        <v>-0.2081571883456315</v>
+        <v>-0.157184798187618</v>
       </c>
       <c r="K442">
         <v>1.52</v>
@@ -23434,10 +23452,10 @@
         <v>3.55</v>
       </c>
       <c r="M442">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N442">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O442">
         <v>1</v>
@@ -23454,28 +23472,28 @@
         <v>54</v>
       </c>
       <c r="C443">
-        <v>3.846535379684417</v>
+        <v>3.79888341910942</v>
       </c>
       <c r="D443" t="s">
         <v>126</v>
       </c>
       <c r="E443">
-        <v>3.874584489028599</v>
+        <v>3.934146900872678</v>
       </c>
       <c r="F443">
         <v>-1</v>
       </c>
       <c r="G443">
-        <v>0.003253464620315583</v>
+        <v>0.00330111658089058</v>
       </c>
       <c r="H443">
-        <v>0.003285415510971401</v>
+        <v>0.003465853099127322</v>
       </c>
       <c r="I443">
-        <v>-0.02804910934418192</v>
+        <v>-0.1352634817632583</v>
       </c>
       <c r="J443">
-        <v>-0.1950890655818535</v>
+        <v>-0.1637390915193551</v>
       </c>
       <c r="K443">
         <v>1.52</v>
@@ -23484,10 +23502,10 @@
         <v>3.55</v>
       </c>
       <c r="M443">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N443">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O443">
         <v>1</v>
@@ -23504,28 +23522,28 @@
         <v>54</v>
       </c>
       <c r="C444">
-        <v>3.87004024621212</v>
+        <v>3.829553568848083</v>
       </c>
       <c r="D444" t="s">
         <v>126</v>
       </c>
       <c r="E444">
-        <v>3.897934718276514</v>
+        <v>3.963001054903131</v>
       </c>
       <c r="F444">
         <v>-1</v>
       </c>
       <c r="G444">
-        <v>0.003229959753787879</v>
+        <v>0.003270446431151916</v>
       </c>
       <c r="H444">
-        <v>0.003262065281723486</v>
+        <v>0.003436998945096869</v>
       </c>
       <c r="I444">
-        <v>-0.0278944720643941</v>
+        <v>-0.1334474860550481</v>
       </c>
       <c r="J444">
-        <v>-0.2105527935606056</v>
+        <v>-0.1839168216105812</v>
       </c>
       <c r="K444">
         <v>1.52</v>
@@ -23534,10 +23552,10 @@
         <v>3.55</v>
       </c>
       <c r="M444">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N444">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O444">
         <v>1</v>
@@ -23554,28 +23572,28 @@
         <v>54</v>
       </c>
       <c r="C445">
-        <v>3.886357305969927</v>
+        <v>3.855665816250932</v>
       </c>
       <c r="D445" t="s">
         <v>126</v>
       </c>
       <c r="E445">
-        <v>3.914144428956967</v>
+        <v>3.987567182393969</v>
       </c>
       <c r="F445">
         <v>-1</v>
       </c>
       <c r="G445">
-        <v>0.003213642694030073</v>
+        <v>0.003244334183749068</v>
       </c>
       <c r="H445">
-        <v>0.003245855571043033</v>
+        <v>0.003412432817606031</v>
       </c>
       <c r="I445">
-        <v>-0.02778712298704011</v>
+        <v>-0.1319013661430373</v>
       </c>
       <c r="J445">
-        <v>-0.2212877012960047</v>
+        <v>-0.2010959317440343</v>
       </c>
       <c r="K445">
         <v>1.52</v>
@@ -23584,10 +23602,10 @@
         <v>3.55</v>
       </c>
       <c r="M445">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N445">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O445">
         <v>1</v>
@@ -23604,28 +23622,28 @@
         <v>54</v>
       </c>
       <c r="C446">
-        <v>3.903938192034373</v>
+        <v>3.855953228285221</v>
       </c>
       <c r="D446" t="s">
         <v>126</v>
       </c>
       <c r="E446">
-        <v>3.931609651297305</v>
+        <v>3.987837576610439</v>
       </c>
       <c r="F446">
         <v>-1</v>
       </c>
       <c r="G446">
-        <v>0.003196061807965626</v>
+        <v>0.003244046771714778</v>
       </c>
       <c r="H446">
-        <v>0.003228390348702695</v>
+        <v>0.003412162423389562</v>
       </c>
       <c r="I446">
-        <v>-0.02767145926293191</v>
+        <v>-0.1318843483252174</v>
       </c>
       <c r="J446">
-        <v>-0.2328540737068246</v>
+        <v>-0.2012850186086983</v>
       </c>
       <c r="K446">
         <v>1.52</v>
@@ -23634,10 +23652,10 @@
         <v>3.55</v>
       </c>
       <c r="M446">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N446">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O446">
         <v>1</v>
@@ -23654,28 +23672,28 @@
         <v>54</v>
       </c>
       <c r="C447">
-        <v>3.961072830353248</v>
+        <v>3.861717839622725</v>
       </c>
       <c r="D447" t="s">
         <v>126</v>
       </c>
       <c r="E447">
-        <v>3.988368403837766</v>
+        <v>3.993260862276643</v>
       </c>
       <c r="F447">
         <v>-1</v>
       </c>
       <c r="G447">
-        <v>0.003138927169646752</v>
+        <v>0.003238282160377275</v>
       </c>
       <c r="H447">
-        <v>0.003171631596162234</v>
+        <v>0.003406739137723357</v>
       </c>
       <c r="I447">
-        <v>-0.02729557348451861</v>
+        <v>-0.131543022653918</v>
       </c>
       <c r="J447">
-        <v>-0.2704426515481894</v>
+        <v>-0.2050775260675825</v>
       </c>
       <c r="K447">
         <v>1.52</v>
@@ -23684,10 +23702,10 @@
         <v>3.55</v>
       </c>
       <c r="M447">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N447">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O447">
         <v>1</v>
@@ -23704,28 +23722,28 @@
         <v>54</v>
       </c>
       <c r="C448">
-        <v>3.981576852757343</v>
+        <v>3.86639892628536</v>
       </c>
       <c r="D448" t="s">
         <v>126</v>
       </c>
       <c r="E448">
-        <v>4.008737531357625</v>
+        <v>3.997664779334253</v>
       </c>
       <c r="F448">
         <v>-1</v>
       </c>
       <c r="G448">
-        <v>0.003118423147242656</v>
+        <v>0.00323360107371464</v>
       </c>
       <c r="H448">
-        <v>0.003151262468642376</v>
+        <v>0.003402335220665747</v>
       </c>
       <c r="I448">
-        <v>-0.02716067860028115</v>
+        <v>-0.1312658530488933</v>
       </c>
       <c r="J448">
-        <v>-0.2839321399719367</v>
+        <v>-0.2081571883456315</v>
       </c>
       <c r="K448">
         <v>1.52</v>
@@ -23734,10 +23752,10 @@
         <v>3.55</v>
       </c>
       <c r="M448">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N448">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O448">
         <v>1</v>
@@ -23754,28 +23772,28 @@
         <v>54</v>
       </c>
       <c r="C449">
-        <v>3.971450680589221</v>
+        <v>3.846535379684417</v>
       </c>
       <c r="D449" t="s">
         <v>126</v>
       </c>
       <c r="E449">
-        <v>3.998677978743239</v>
+        <v>3.978977363782051</v>
       </c>
       <c r="F449">
         <v>-1</v>
       </c>
       <c r="G449">
-        <v>0.003128549319410779</v>
+        <v>0.003253464620315583</v>
       </c>
       <c r="H449">
-        <v>0.003161322021256761</v>
+        <v>0.00342102263621795</v>
       </c>
       <c r="I449">
-        <v>-0.02722729815401825</v>
+        <v>-0.1324419840976336</v>
       </c>
       <c r="J449">
-        <v>-0.2772701845981717</v>
+        <v>-0.1950890655818535</v>
       </c>
       <c r="K449">
         <v>1.52</v>
@@ -23784,10 +23802,10 @@
         <v>3.55</v>
       </c>
       <c r="M449">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N449">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O449">
         <v>1</v>
@@ -23804,28 +23822,28 @@
         <v>54</v>
       </c>
       <c r="C450">
-        <v>3.968816281770093</v>
+        <v>3.87004024621212</v>
       </c>
       <c r="D450" t="s">
         <v>126</v>
       </c>
       <c r="E450">
-        <v>3.99606091149529</v>
+        <v>4.001090494791666</v>
       </c>
       <c r="F450">
         <v>-1</v>
       </c>
       <c r="G450">
-        <v>0.003131183718229907</v>
+        <v>0.003229959753787879</v>
       </c>
       <c r="H450">
-        <v>0.00316393908850471</v>
+        <v>0.003398909505208335</v>
       </c>
       <c r="I450">
-        <v>-0.02724462972519692</v>
+        <v>-0.1310502485795455</v>
       </c>
       <c r="J450">
-        <v>-0.2755370274803244</v>
+        <v>-0.2105527935606056</v>
       </c>
       <c r="K450">
         <v>1.52</v>
@@ -23834,10 +23852,10 @@
         <v>3.55</v>
       </c>
       <c r="M450">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N450">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O450">
         <v>1</v>
@@ -23854,28 +23872,28 @@
         <v>54</v>
       </c>
       <c r="C451">
-        <v>3.926789933050578</v>
+        <v>3.886357305969927</v>
       </c>
       <c r="D451" t="s">
         <v>126</v>
       </c>
       <c r="E451">
-        <v>3.954311051912088</v>
+        <v>4.016441412853287</v>
       </c>
       <c r="F451">
         <v>-1</v>
       </c>
       <c r="G451">
-        <v>0.003173210066949421</v>
+        <v>0.003213642694030073</v>
       </c>
       <c r="H451">
-        <v>0.003205688948087912</v>
+        <v>0.003383558587146713</v>
       </c>
       <c r="I451">
-        <v>-0.02752111886150965</v>
+        <v>-0.13008410688336</v>
       </c>
       <c r="J451">
-        <v>-0.2478881138490649</v>
+        <v>-0.2212877012960047</v>
       </c>
       <c r="K451">
         <v>1.52</v>
@@ -23884,10 +23902,10 @@
         <v>3.55</v>
       </c>
       <c r="M451">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N451">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O451">
         <v>1</v>
@@ -23904,28 +23922,28 @@
         <v>54</v>
       </c>
       <c r="C452">
-        <v>3.825723707829902</v>
+        <v>3.903938192034373</v>
       </c>
       <c r="D452" t="s">
         <v>126</v>
       </c>
       <c r="E452">
-        <v>3.853909736067863</v>
+        <v>4.032981325400759</v>
       </c>
       <c r="F452">
         <v>-1</v>
       </c>
       <c r="G452">
-        <v>0.003274276292170098</v>
+        <v>0.003196061807965626</v>
       </c>
       <c r="H452">
-        <v>0.003306090263932137</v>
+        <v>0.003367018674599241</v>
       </c>
       <c r="I452">
-        <v>-0.02818602823796157</v>
+        <v>-0.1290431333663857</v>
       </c>
       <c r="J452">
-        <v>-0.181397176203883</v>
+        <v>-0.2328540737068246</v>
       </c>
       <c r="K452">
         <v>1.52</v>
@@ -23934,10 +23952,10 @@
         <v>3.55</v>
       </c>
       <c r="M452">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N452">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O452">
         <v>1</v>
@@ -23954,28 +23972,28 @@
         <v>54</v>
       </c>
       <c r="C453">
-        <v>3.746022583750348</v>
+        <v>3.961072830353248</v>
       </c>
       <c r="D453" t="s">
         <v>126</v>
       </c>
       <c r="E453">
-        <v>3.774732961488833</v>
+        <v>4.086732991713911</v>
       </c>
       <c r="F453">
         <v>-1</v>
       </c>
       <c r="G453">
-        <v>0.003353977416249652</v>
+        <v>0.003138927169646752</v>
       </c>
       <c r="H453">
-        <v>0.003385267038511167</v>
+        <v>0.003313267008286089</v>
       </c>
       <c r="I453">
-        <v>-0.02871037773848473</v>
+        <v>-0.1256601613606629</v>
       </c>
       <c r="J453">
-        <v>-0.1289622261515449</v>
+        <v>-0.2704426515481894</v>
       </c>
       <c r="K453">
         <v>1.52</v>
@@ -23984,10 +24002,10 @@
         <v>3.55</v>
       </c>
       <c r="M453">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N453">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O453">
         <v>1</v>
@@ -24004,28 +24022,28 @@
         <v>54</v>
       </c>
       <c r="C454">
-        <v>3.686827463477967</v>
+        <v>3.981576852757343</v>
       </c>
       <c r="D454" t="s">
         <v>126</v>
       </c>
       <c r="E454">
-        <v>3.715927282797192</v>
+        <v>4.106022960159869</v>
       </c>
       <c r="F454">
         <v>-1</v>
       </c>
       <c r="G454">
-        <v>0.003413172536522032</v>
+        <v>0.003118423147242656</v>
       </c>
       <c r="H454">
-        <v>0.003444072717202809</v>
+        <v>0.003293977039840131</v>
       </c>
       <c r="I454">
-        <v>-0.02909981931922445</v>
+        <v>-0.1244461074025258</v>
       </c>
       <c r="J454">
-        <v>-0.09001806807761016</v>
+        <v>-0.2839321399719367</v>
       </c>
       <c r="K454">
         <v>1.52</v>
@@ -24034,10 +24052,10 @@
         <v>3.55</v>
       </c>
       <c r="M454">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N454">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O454">
         <v>1</v>
@@ -24054,28 +24072,28 @@
         <v>54</v>
       </c>
       <c r="C455">
-        <v>3.536490631366341</v>
+        <v>3.971450680589221</v>
       </c>
       <c r="D455" t="s">
         <v>126</v>
       </c>
       <c r="E455">
-        <v>3.566579508791563</v>
+        <v>4.096496363975386</v>
       </c>
       <c r="F455">
         <v>-1</v>
       </c>
       <c r="G455">
-        <v>0.003563509368633659</v>
+        <v>0.003128549319410779</v>
       </c>
       <c r="H455">
-        <v>0.003593420491208437</v>
+        <v>0.003303503636024615</v>
       </c>
       <c r="I455">
-        <v>-0.03008887742522193</v>
+        <v>-0.1250456833861651</v>
       </c>
       <c r="J455">
-        <v>0.008887742522143843</v>
+        <v>-0.2772701845981717</v>
       </c>
       <c r="K455">
         <v>1.52</v>
@@ -24084,10 +24102,10 @@
         <v>3.55</v>
       </c>
       <c r="M455">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N455">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O455">
         <v>1</v>
@@ -24104,28 +24122,28 @@
         <v>54</v>
       </c>
       <c r="C456">
-        <v>3.478129127613399</v>
+        <v>3.968816281770093</v>
       </c>
       <c r="D456" t="s">
         <v>126</v>
       </c>
       <c r="E456">
-        <v>3.508601962300153</v>
+        <v>4.094017949296864</v>
       </c>
       <c r="F456">
         <v>-1</v>
       </c>
       <c r="G456">
-        <v>0.0036218708723866</v>
+        <v>0.003131183718229907</v>
       </c>
       <c r="H456">
-        <v>0.003651398037699847</v>
+        <v>0.003305982050703136</v>
       </c>
       <c r="I456">
-        <v>-0.03047283468675399</v>
+        <v>-0.1252016675267713</v>
       </c>
       <c r="J456">
-        <v>0.04728346867539508</v>
+        <v>-0.2755370274803244</v>
       </c>
       <c r="K456">
         <v>1.52</v>
@@ -24134,10 +24152,10 @@
         <v>3.55</v>
       </c>
       <c r="M456">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N456">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O456">
         <v>1</v>
@@ -24154,28 +24172,28 @@
         <v>54</v>
       </c>
       <c r="C457">
-        <v>3.446322550887229</v>
+        <v>3.926789933050578</v>
       </c>
       <c r="D457" t="s">
         <v>126</v>
       </c>
       <c r="E457">
-        <v>3.477004639368234</v>
+        <v>4.054480002804163</v>
       </c>
       <c r="F457">
         <v>-1</v>
       </c>
       <c r="G457">
-        <v>0.003653677449112771</v>
+        <v>0.003173210066949421</v>
       </c>
       <c r="H457">
-        <v>0.003682995360631766</v>
+        <v>0.003345519997195838</v>
       </c>
       <c r="I457">
-        <v>-0.03068208848100529</v>
+        <v>-0.1276900697535845</v>
       </c>
       <c r="J457">
-        <v>0.06820884810050738</v>
+        <v>-0.2478881138490649</v>
       </c>
       <c r="K457">
         <v>1.52</v>
@@ -24184,10 +24202,10 @@
         <v>3.55</v>
       </c>
       <c r="M457">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N457">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O457">
         <v>1</v>
@@ -24204,28 +24222,28 @@
         <v>54</v>
       </c>
       <c r="C458">
-        <v>3.437244026062129</v>
+        <v>3.825723707829902</v>
       </c>
       <c r="D458" t="s">
         <v>126</v>
       </c>
       <c r="E458">
-        <v>3.467985841680141</v>
+        <v>3.959397961971553</v>
       </c>
       <c r="F458">
         <v>-1</v>
       </c>
       <c r="G458">
-        <v>0.003662755973937871</v>
+        <v>0.003274276292170098</v>
       </c>
       <c r="H458">
-        <v>0.003692014158319859</v>
+        <v>0.003440602038028448</v>
       </c>
       <c r="I458">
-        <v>-0.03074181561801259</v>
+        <v>-0.1336742541416509</v>
       </c>
       <c r="J458">
-        <v>0.07418156180123091</v>
+        <v>-0.181397176203883</v>
       </c>
       <c r="K458">
         <v>1.52</v>
@@ -24234,10 +24252,10 @@
         <v>3.55</v>
       </c>
       <c r="M458">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N458">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O458">
         <v>1</v>
@@ -24254,28 +24272,28 @@
         <v>54</v>
       </c>
       <c r="C459">
-        <v>3.495394814734395</v>
+        <v>3.746022583750348</v>
       </c>
       <c r="D459" t="s">
         <v>126</v>
       </c>
       <c r="E459">
-        <v>3.525754059374301</v>
+        <v>3.88441598339671</v>
       </c>
       <c r="F459">
         <v>-1</v>
       </c>
       <c r="G459">
-        <v>0.003604605185265604</v>
+        <v>0.003353977416249652</v>
       </c>
       <c r="H459">
-        <v>0.0036342459406257</v>
+        <v>0.003515584016603291</v>
       </c>
       <c r="I459">
-        <v>-0.03035924463990547</v>
+        <v>-0.1383933996463615</v>
       </c>
       <c r="J459">
-        <v>0.03592446399052947</v>
+        <v>-0.1289622261515449</v>
       </c>
       <c r="K459">
         <v>1.52</v>
@@ -24284,10 +24302,10 @@
         <v>3.55</v>
       </c>
       <c r="M459">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N459">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O459">
         <v>1</v>
@@ -24304,28 +24322,28 @@
         <v>54</v>
       </c>
       <c r="C460">
-        <v>3.479433369341057</v>
+        <v>3.686827463477967</v>
       </c>
       <c r="D460" t="s">
         <v>126</v>
       </c>
       <c r="E460">
-        <v>3.509897623490129</v>
+        <v>3.828725837350983</v>
       </c>
       <c r="F460">
         <v>-1</v>
       </c>
       <c r="G460">
-        <v>0.003620566630658943</v>
+        <v>0.003413172536522032</v>
       </c>
       <c r="H460">
-        <v>0.003650102376509871</v>
+        <v>0.003571274162649018</v>
       </c>
       <c r="I460">
-        <v>-0.03046425414907228</v>
+        <v>-0.1418983738730155</v>
       </c>
       <c r="J460">
-        <v>0.04642541490719935</v>
+        <v>-0.09001806807761016</v>
       </c>
       <c r="K460">
         <v>1.52</v>
@@ -24334,10 +24352,10 @@
         <v>3.55</v>
       </c>
       <c r="M460">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N460">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O460">
         <v>1</v>
@@ -24354,28 +24372,28 @@
         <v>54</v>
       </c>
       <c r="C461">
-        <v>3.450931319109172</v>
+        <v>3.536490631366341</v>
       </c>
       <c r="D461" t="s">
         <v>126</v>
       </c>
       <c r="E461">
-        <v>3.481583086746612</v>
+        <v>3.687290528193334</v>
       </c>
       <c r="F461">
         <v>-1</v>
       </c>
       <c r="G461">
-        <v>0.003649068680890828</v>
+        <v>0.003563509368633659</v>
       </c>
       <c r="H461">
-        <v>0.003678416913253389</v>
+        <v>0.003712709471806666</v>
       </c>
       <c r="I461">
-        <v>-0.03065176763744004</v>
+        <v>-0.1507998968269932</v>
       </c>
       <c r="J461">
-        <v>0.06517676374396589</v>
+        <v>0.008887742522143843</v>
       </c>
       <c r="K461">
         <v>1.52</v>
@@ -24384,10 +24402,10 @@
         <v>3.55</v>
       </c>
       <c r="M461">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N461">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O461">
         <v>1</v>
@@ -24404,28 +24422,28 @@
         <v>54</v>
       </c>
       <c r="C462">
-        <v>3.40927622228758</v>
+        <v>3.478129127613399</v>
       </c>
       <c r="D462" t="s">
         <v>126</v>
       </c>
       <c r="E462">
-        <v>3.440202036614636</v>
+        <v>3.632384639794185</v>
       </c>
       <c r="F462">
         <v>-1</v>
       </c>
       <c r="G462">
-        <v>0.00369072377771242</v>
+        <v>0.0036218708723866</v>
       </c>
       <c r="H462">
-        <v>0.003719797963385364</v>
+        <v>0.003767615360205815</v>
       </c>
       <c r="I462">
-        <v>-0.03092581432705543</v>
+        <v>-0.1542555121807858</v>
       </c>
       <c r="J462">
-        <v>0.09258143270553931</v>
+        <v>0.04728346867539508</v>
       </c>
       <c r="K462">
         <v>1.52</v>
@@ -24434,10 +24452,10 @@
         <v>3.55</v>
       </c>
       <c r="M462">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N462">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O462">
         <v>1</v>
@@ -24454,28 +24472,28 @@
         <v>54</v>
       </c>
       <c r="C463">
-        <v>3.398669636469118</v>
+        <v>3.446322550887229</v>
       </c>
       <c r="D463" t="s">
         <v>126</v>
       </c>
       <c r="E463">
-        <v>3.429665230966032</v>
+        <v>3.602461347216275</v>
       </c>
       <c r="F463">
         <v>-1</v>
       </c>
       <c r="G463">
-        <v>0.003701330363530882</v>
+        <v>0.003653677449112771</v>
       </c>
       <c r="H463">
-        <v>0.003730334769033969</v>
+        <v>0.003797538652783726</v>
       </c>
       <c r="I463">
-        <v>-0.0309955944969138</v>
+        <v>-0.1561387963290461</v>
       </c>
       <c r="J463">
-        <v>0.09955944969136986</v>
+        <v>0.06820884810050738</v>
       </c>
       <c r="K463">
         <v>1.52</v>
@@ -24484,10 +24502,10 @@
         <v>3.55</v>
       </c>
       <c r="M463">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N463">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O463">
         <v>1</v>
@@ -24504,28 +24522,28 @@
         <v>54</v>
       </c>
       <c r="C464">
-        <v>3.386651569627924</v>
+        <v>3.437244026062129</v>
       </c>
       <c r="D464" t="s">
         <v>126</v>
       </c>
       <c r="E464">
-        <v>3.417726230354056</v>
+        <v>3.59392036662424</v>
       </c>
       <c r="F464">
         <v>-1</v>
       </c>
       <c r="G464">
-        <v>0.003713348430372076</v>
+        <v>0.003662755973937871</v>
       </c>
       <c r="H464">
-        <v>0.003742273769645944</v>
+        <v>0.00380607963337576</v>
       </c>
       <c r="I464">
-        <v>-0.0310746607261323</v>
+        <v>-0.1566763405621114</v>
       </c>
       <c r="J464">
-        <v>0.1074660726132081</v>
+        <v>0.07418156180123091</v>
       </c>
       <c r="K464">
         <v>1.52</v>
@@ -24534,10 +24552,10 @@
         <v>3.55</v>
       </c>
       <c r="M464">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N464">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O464">
         <v>1</v>
@@ -24554,28 +24572,28 @@
         <v>54</v>
       </c>
       <c r="C465">
-        <v>3.393731929090075</v>
+        <v>3.495394814734395</v>
       </c>
       <c r="D465" t="s">
         <v>126</v>
       </c>
       <c r="E465">
-        <v>3.424760008503956</v>
+        <v>3.648628016493543</v>
       </c>
       <c r="F465">
         <v>-1</v>
       </c>
       <c r="G465">
-        <v>0.003706268070909925</v>
+        <v>0.003604605185265604</v>
       </c>
       <c r="H465">
-        <v>0.003735239991496044</v>
+        <v>0.003751371983506458</v>
       </c>
       <c r="I465">
-        <v>-0.0310280794138813</v>
+        <v>-0.1532332017591478</v>
       </c>
       <c r="J465">
-        <v>0.1028079413881086</v>
+        <v>0.03592446399052947</v>
       </c>
       <c r="K465">
         <v>1.52</v>
@@ -24584,10 +24602,10 @@
         <v>3.55</v>
       </c>
       <c r="M465">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N465">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O465">
         <v>1</v>
@@ -24604,28 +24622,28 @@
         <v>54</v>
       </c>
       <c r="C466">
-        <v>3.379912288774229</v>
+        <v>3.479433369341057</v>
       </c>
       <c r="D466" t="s">
         <v>126</v>
       </c>
       <c r="E466">
-        <v>3.411031286874399</v>
+        <v>3.633611656682705</v>
       </c>
       <c r="F466">
         <v>-1</v>
       </c>
       <c r="G466">
-        <v>0.00372008771122577</v>
+        <v>0.003620566630658943</v>
       </c>
       <c r="H466">
-        <v>0.003748968713125601</v>
+        <v>0.003766388343317295</v>
       </c>
       <c r="I466">
-        <v>-0.03111899810016983</v>
+        <v>-0.1541782873416486</v>
       </c>
       <c r="J466">
-        <v>0.1118998100169543</v>
+        <v>0.04642541490719935</v>
       </c>
       <c r="K466">
         <v>1.52</v>
@@ -24634,10 +24652,10 @@
         <v>3.55</v>
       </c>
       <c r="M466">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N466">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O466">
         <v>1</v>
@@ -24654,28 +24672,28 @@
         <v>54</v>
       </c>
       <c r="C467">
-        <v>3.350459894428295</v>
+        <v>3.450931319109172</v>
       </c>
       <c r="D467" t="s">
         <v>126</v>
       </c>
       <c r="E467">
-        <v>3.381772658280741</v>
+        <v>3.606797227846129</v>
       </c>
       <c r="F467">
         <v>-1</v>
       </c>
       <c r="G467">
-        <v>0.003749540105571705</v>
+        <v>0.003649068680890828</v>
       </c>
       <c r="H467">
-        <v>0.00377822734171926</v>
+        <v>0.003793202772153872</v>
       </c>
       <c r="I467">
-        <v>-0.03131276385244552</v>
+        <v>-0.1558659087369572</v>
       </c>
       <c r="J467">
-        <v>0.1312763852445424</v>
+        <v>0.06517676374396589</v>
       </c>
       <c r="K467">
         <v>1.52</v>
@@ -24684,10 +24702,10 @@
         <v>3.55</v>
       </c>
       <c r="M467">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N467">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O467">
         <v>1</v>
@@ -24704,28 +24722,28 @@
         <v>54</v>
       </c>
       <c r="C468">
-        <v>3.29749980927481</v>
+        <v>3.40927622228758</v>
       </c>
       <c r="D468" t="s">
         <v>126</v>
       </c>
       <c r="E468">
-        <v>3.329160994740108</v>
+        <v>3.567608551231079</v>
       </c>
       <c r="F468">
         <v>-1</v>
       </c>
       <c r="G468">
-        <v>0.00380250019072519</v>
+        <v>0.00369072377771242</v>
       </c>
       <c r="H468">
-        <v>0.003830839005259893</v>
+        <v>0.003832391448768921</v>
       </c>
       <c r="I468">
-        <v>-0.0316611854652975</v>
+        <v>-0.1583323289434988</v>
       </c>
       <c r="J468">
-        <v>0.16611854652973</v>
+        <v>0.09258143270553931</v>
       </c>
       <c r="K468">
         <v>1.52</v>
@@ -24734,10 +24752,10 @@
         <v>3.55</v>
       </c>
       <c r="M468">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N468">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O468">
         <v>1</v>
@@ -24754,28 +24772,28 @@
         <v>54</v>
       </c>
       <c r="C469">
-        <v>3.226019469262567</v>
+        <v>3.398669636469118</v>
       </c>
       <c r="D469" t="s">
         <v>126</v>
       </c>
       <c r="E469">
-        <v>3.258150920122682</v>
+        <v>3.557629986941341</v>
       </c>
       <c r="F469">
         <v>-1</v>
       </c>
       <c r="G469">
-        <v>0.003873980530737433</v>
+        <v>0.003701330363530882</v>
       </c>
       <c r="H469">
-        <v>0.003901849079877319</v>
+        <v>0.003842370013058659</v>
       </c>
       <c r="I469">
-        <v>-0.03213145086011515</v>
+        <v>-0.1589603504722237</v>
       </c>
       <c r="J469">
-        <v>0.2131450860114693</v>
+        <v>0.09955944969136986</v>
       </c>
       <c r="K469">
         <v>1.52</v>
@@ -24784,10 +24802,10 @@
         <v>3.55</v>
       </c>
       <c r="M469">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N469">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O469">
         <v>1</v>
@@ -24801,43 +24819,43 @@
         <v>0</v>
       </c>
       <c r="B470" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C470">
-        <v>2.761972833438688</v>
+        <v>3.386651569627924</v>
       </c>
       <c r="D470" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E470">
-        <v>2.26641548960003</v>
+        <v>3.546323516163113</v>
       </c>
       <c r="F470">
         <v>-1</v>
       </c>
       <c r="G470">
-        <v>0.003538027166561312</v>
+        <v>0.003713348430372076</v>
       </c>
       <c r="H470">
-        <v>0.00299358451039997</v>
+        <v>0.003853676483836888</v>
       </c>
       <c r="I470">
-        <v>0.4955573438386578</v>
+        <v>-0.1596719465351892</v>
       </c>
       <c r="J470">
-        <v>0.3055332020167811</v>
+        <v>0.1074660726132081</v>
       </c>
       <c r="K470">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L470">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M470">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="N470">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="O470">
         <v>1</v>
@@ -24848,34 +24866,34 @@
     </row>
     <row r="471" spans="1:16">
       <c r="A471" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B471" t="s">
         <v>54</v>
       </c>
       <c r="C471">
-        <v>3.085589532934493</v>
+        <v>3.393731929090075</v>
       </c>
       <c r="D471" t="s">
         <v>126</v>
       </c>
       <c r="E471">
-        <v>3.118644864954661</v>
+        <v>3.552984643815005</v>
       </c>
       <c r="F471">
         <v>-1</v>
       </c>
       <c r="G471">
-        <v>0.004014410467065507</v>
+        <v>0.003706268070909925</v>
       </c>
       <c r="H471">
-        <v>0.004041355135045339</v>
+        <v>0.003847015356184996</v>
       </c>
       <c r="I471">
-        <v>-0.03305533202016786</v>
+        <v>-0.1592527147249299</v>
       </c>
       <c r="J471">
-        <v>0.3055332020167811</v>
+        <v>0.1028079413881086</v>
       </c>
       <c r="K471">
         <v>1.52</v>
@@ -24884,16 +24902,16 @@
         <v>3.55</v>
       </c>
       <c r="M471">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N471">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O471">
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24901,81 +24919,81 @@
         <v>0</v>
       </c>
       <c r="B472" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C472">
-        <v>2.702231862141191</v>
+        <v>3.379912288774229</v>
       </c>
       <c r="D472" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E472">
-        <v>2.210437729092927</v>
+        <v>3.539983271675756</v>
       </c>
       <c r="F472">
         <v>-1</v>
       </c>
       <c r="G472">
-        <v>0.003597768137858809</v>
+        <v>0.00372008771122577</v>
       </c>
       <c r="H472">
-        <v>0.003049562270907073</v>
+        <v>0.003860016728324245</v>
       </c>
       <c r="I472">
-        <v>0.491794133048264</v>
+        <v>-0.1600709829015261</v>
       </c>
       <c r="J472">
-        <v>0.3525733368967002</v>
+        <v>0.1118998100169543</v>
       </c>
       <c r="K472">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L472">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M472">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="N472">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="O472">
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="473" spans="1:16">
       <c r="A473" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B473" t="s">
         <v>54</v>
       </c>
       <c r="C473">
-        <v>3.014088527917016</v>
+        <v>3.350459894428295</v>
       </c>
       <c r="D473" t="s">
         <v>126</v>
       </c>
       <c r="E473">
-        <v>3.047614261285982</v>
+        <v>3.512274769100304</v>
       </c>
       <c r="F473">
         <v>-1</v>
       </c>
       <c r="G473">
-        <v>0.004085911472082985</v>
+        <v>0.003749540105571705</v>
       </c>
       <c r="H473">
-        <v>0.004112385738714018</v>
+        <v>0.003887725230899696</v>
       </c>
       <c r="I473">
-        <v>-0.03352573336896691</v>
+        <v>-0.1618148746720092</v>
       </c>
       <c r="J473">
-        <v>0.3525733368967002</v>
+        <v>0.1312763852445424</v>
       </c>
       <c r="K473">
         <v>1.52</v>
@@ -24984,16 +25002,16 @@
         <v>3.55</v>
       </c>
       <c r="M473">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N473">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O473">
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25001,81 +25019,81 @@
         <v>0</v>
       </c>
       <c r="B474" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C474">
-        <v>2.65619166177536</v>
+        <v>3.29749980927481</v>
       </c>
       <c r="D474" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E474">
-        <v>2.167297698828881</v>
+        <v>3.462450478462486</v>
       </c>
       <c r="F474">
         <v>-1</v>
       </c>
       <c r="G474">
-        <v>0.00364380833822464</v>
+        <v>0.00380250019072519</v>
       </c>
       <c r="H474">
-        <v>0.003092702301171119</v>
+        <v>0.003937549521537514</v>
       </c>
       <c r="I474">
-        <v>0.4888939629464795</v>
+        <v>-0.1649506691876761</v>
       </c>
       <c r="J474">
-        <v>0.3888254631690077</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K474">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L474">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M474">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="N474">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="O474">
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="475" spans="1:16">
       <c r="A475" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B475" t="s">
         <v>54</v>
       </c>
       <c r="C475">
-        <v>2.958985295983108</v>
+        <v>3.226019469262567</v>
       </c>
       <c r="D475" t="s">
         <v>126</v>
       </c>
       <c r="E475">
-        <v>2.992873550614799</v>
+        <v>3.395202527003599</v>
       </c>
       <c r="F475">
         <v>-1</v>
       </c>
       <c r="G475">
-        <v>0.004141014704016891</v>
+        <v>0.003873980530737433</v>
       </c>
       <c r="H475">
-        <v>0.004167126449385202</v>
+        <v>0.004004797472996401</v>
       </c>
       <c r="I475">
-        <v>-0.03388825463169054</v>
+        <v>-0.1691830577410327</v>
       </c>
       <c r="J475">
-        <v>0.3888254631690077</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K475">
         <v>1.52</v>
@@ -25084,16 +25102,16 @@
         <v>3.55</v>
       </c>
       <c r="M475">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N475">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O475">
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25101,81 +25119,81 @@
         <v>0</v>
       </c>
       <c r="B476" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C476">
-        <v>2.633560752891249</v>
+        <v>3.085589532934493</v>
       </c>
       <c r="D476" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E476">
-        <v>2.146092359008336</v>
+        <v>3.263087521116003</v>
       </c>
       <c r="F476">
         <v>-1</v>
       </c>
       <c r="G476">
-        <v>0.003666439247108751</v>
+        <v>0.004014410467065507</v>
       </c>
       <c r="H476">
-        <v>0.003113907640991664</v>
+        <v>0.004136912478883997</v>
       </c>
       <c r="I476">
-        <v>0.4874683938829132</v>
+        <v>-0.1774979881815106</v>
       </c>
       <c r="J476">
-        <v>0.4066450764635833</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K476">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L476">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M476">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="N476">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="O476">
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="477" spans="1:16">
       <c r="A477" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B477" t="s">
         <v>54</v>
       </c>
       <c r="C477">
-        <v>2.931899483775353</v>
+        <v>3.014088527917016</v>
       </c>
       <c r="D477" t="s">
         <v>126</v>
       </c>
       <c r="E477">
-        <v>2.965965934539989</v>
+        <v>3.195820128237719</v>
       </c>
       <c r="F477">
         <v>-1</v>
       </c>
       <c r="G477">
-        <v>0.004168100516224646</v>
+        <v>0.004085911472082985</v>
       </c>
       <c r="H477">
-        <v>0.004194034065460011</v>
+        <v>0.004204179871762282</v>
       </c>
       <c r="I477">
-        <v>-0.03406645076463599</v>
+        <v>-0.1817316003207035</v>
       </c>
       <c r="J477">
-        <v>0.4066450764635833</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K477">
         <v>1.52</v>
@@ -25184,16 +25202,16 @@
         <v>3.55</v>
       </c>
       <c r="M477">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N477">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O477">
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25201,81 +25219,81 @@
         <v>0</v>
       </c>
       <c r="B478" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C478">
-        <v>2.575080697535542</v>
+        <v>2.958985295983108</v>
       </c>
       <c r="D478" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E478">
-        <v>2.091296086667161</v>
+        <v>3.143979587668319</v>
       </c>
       <c r="F478">
         <v>-1</v>
       </c>
       <c r="G478">
-        <v>0.003724919302464458</v>
+        <v>0.004141014704016891</v>
       </c>
       <c r="H478">
-        <v>0.003168703913332839</v>
+        <v>0.004256020412331681</v>
       </c>
       <c r="I478">
-        <v>0.4837846108683808</v>
+        <v>-0.1849942916852112</v>
       </c>
       <c r="J478">
-        <v>0.4526923641452424</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K478">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L478">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M478">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="N478">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="O478">
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="479" spans="1:16">
       <c r="A479" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B479" t="s">
         <v>54</v>
       </c>
       <c r="C479">
-        <v>2.861907606499231</v>
+        <v>2.931899483775353</v>
       </c>
       <c r="D479" t="s">
         <v>126</v>
       </c>
       <c r="E479">
-        <v>2.896434530140684</v>
+        <v>3.118497540657076</v>
       </c>
       <c r="F479">
         <v>-1</v>
       </c>
       <c r="G479">
-        <v>0.004238092393500768</v>
+        <v>0.004168100516224646</v>
       </c>
       <c r="H479">
-        <v>0.004263565469859316</v>
+        <v>0.004281502459342924</v>
       </c>
       <c r="I479">
-        <v>-0.03452692364145271</v>
+        <v>-0.1865980568817229</v>
       </c>
       <c r="J479">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K479">
         <v>1.52</v>
@@ -25284,16 +25302,16 @@
         <v>3.55</v>
       </c>
       <c r="M479">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N479">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O479">
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25304,28 +25322,28 @@
         <v>55</v>
       </c>
       <c r="C480">
-        <v>2.524828470599929</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D480" t="s">
         <v>127</v>
       </c>
       <c r="E480">
-        <v>2.044209354341666</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F480">
         <v>-1</v>
       </c>
       <c r="G480">
-        <v>0.003775171529400071</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H480">
-        <v>0.003215790645658334</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I480">
-        <v>0.4806191162582629</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J480">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K480">
         <v>1.27</v>
@@ -25343,7 +25361,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25354,28 +25372,28 @@
         <v>54</v>
       </c>
       <c r="C481">
-        <v>2.801763208907002</v>
+        <v>2.861907606499231</v>
       </c>
       <c r="D481" t="s">
         <v>126</v>
       </c>
       <c r="E481">
-        <v>2.836685819374719</v>
+        <v>3.052649919272303</v>
       </c>
       <c r="F481">
         <v>-1</v>
       </c>
       <c r="G481">
-        <v>0.004298236791092998</v>
+        <v>0.004238092393500768</v>
       </c>
       <c r="H481">
-        <v>0.004323314180625281</v>
+        <v>0.004347350080727697</v>
       </c>
       <c r="I481">
-        <v>-0.03492261046771716</v>
+        <v>-0.1907423127730721</v>
       </c>
       <c r="J481">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K481">
         <v>1.52</v>
@@ -25384,16 +25402,116 @@
         <v>3.55</v>
       </c>
       <c r="M481">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="N481">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O481">
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>324</v>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="482" spans="1:16">
+      <c r="A482" s="1">
+        <v>0</v>
+      </c>
+      <c r="B482" t="s">
+        <v>55</v>
+      </c>
+      <c r="C482">
+        <v>2.524828470599929</v>
+      </c>
+      <c r="D482" t="s">
+        <v>127</v>
+      </c>
+      <c r="E482">
+        <v>2.044209354341666</v>
+      </c>
+      <c r="F482">
+        <v>-1</v>
+      </c>
+      <c r="G482">
+        <v>0.003775171529400071</v>
+      </c>
+      <c r="H482">
+        <v>0.003215790645658334</v>
+      </c>
+      <c r="I482">
+        <v>0.4806191162582629</v>
+      </c>
+      <c r="J482">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K482">
+        <v>1.27</v>
+      </c>
+      <c r="L482">
+        <v>3.15</v>
+      </c>
+      <c r="M482">
+        <v>1.19</v>
+      </c>
+      <c r="N482">
+        <v>2.63</v>
+      </c>
+      <c r="O482">
+        <v>1</v>
+      </c>
+      <c r="P482" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="483" spans="1:16">
+      <c r="A483" s="1">
+        <v>1</v>
+      </c>
+      <c r="B483" t="s">
+        <v>54</v>
+      </c>
+      <c r="C483">
+        <v>2.801763208907002</v>
+      </c>
+      <c r="D483" t="s">
+        <v>126</v>
+      </c>
+      <c r="E483">
+        <v>2.996066703116456</v>
+      </c>
+      <c r="F483">
+        <v>-1</v>
+      </c>
+      <c r="G483">
+        <v>0.004298236791092998</v>
+      </c>
+      <c r="H483">
+        <v>0.004403933296883544</v>
+      </c>
+      <c r="I483">
+        <v>-0.1943034942094539</v>
+      </c>
+      <c r="J483">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K483">
+        <v>1.52</v>
+      </c>
+      <c r="L483">
+        <v>3.55</v>
+      </c>
+      <c r="M483">
+        <v>1.43</v>
+      </c>
+      <c r="N483">
+        <v>3.7</v>
+      </c>
+      <c r="O483">
+        <v>1</v>
+      </c>
+      <c r="P483" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="327">
   <si>
     <t>trade_time</t>
   </si>
@@ -181,6 +181,9 @@
     <t>2021-09-23</t>
   </si>
   <si>
+    <t>2021-03-23</t>
+  </si>
+  <si>
     <t>2017-05-09</t>
   </si>
   <si>
@@ -392,6 +395,9 @@
   </si>
   <si>
     <t>2021-09-28</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
   </si>
   <si>
     <t>2016-09-30</t>
@@ -1346,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P473"/>
+  <dimension ref="A1:P474"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1407,7 +1413,7 @@
         <v>0.1939989133597999</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>-0.4188137564277312</v>
@@ -1443,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1457,7 +1463,7 @@
         <v>0.2285614473173059</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>-0.4188137564277312</v>
@@ -1493,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1507,7 +1513,7 @@
         <v>0.1635702643140711</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>-0.4188137564277312</v>
@@ -1543,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1557,7 +1563,7 @@
         <v>0.831271862199725</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>0.2187375820559154</v>
@@ -1593,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1607,7 +1613,7 @@
         <v>0.8459196165059839</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6">
         <v>0.2187375820559154</v>
@@ -1643,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1657,7 +1663,7 @@
         <v>0.763203641762213</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7">
         <v>0.2187375820559154</v>
@@ -1693,7 +1699,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1707,7 +1713,7 @@
         <v>0.8463627094997062</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>0.2187375820559154</v>
@@ -1743,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1757,7 +1763,7 @@
         <v>0.7863627094997057</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9">
         <v>0.2187375820559154</v>
@@ -1793,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1807,7 +1813,7 @@
         <v>3.46886509305629</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10">
         <v>2.855669161372308</v>
@@ -1843,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1857,7 +1863,7 @@
         <v>3.452436406068187</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11">
         <v>2.838213681447448</v>
@@ -1893,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1907,7 +1913,7 @@
         <v>3.38636654658805</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12">
         <v>2.768014455749804</v>
@@ -1943,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1957,7 +1963,7 @@
         <v>3.3413361776263</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <v>2.720169688727944</v>
@@ -1993,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2007,7 +2013,7 @@
         <v>3.300464501418125</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14">
         <v>2.676743532756758</v>
@@ -2043,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2057,7 +2063,7 @@
         <v>3.273900806743327</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15">
         <v>2.648519607164785</v>
@@ -2093,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2107,7 +2113,7 @@
         <v>3.266088352200639</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16">
         <v>2.640218874213179</v>
@@ -2143,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2157,7 +2163,7 @@
         <v>3.262031126351886</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E17">
         <v>2.635908071748879</v>
@@ -2193,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2207,7 +2213,7 @@
         <v>3.249682018685444</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18">
         <v>2.622787144853285</v>
@@ -2243,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2257,7 +2263,7 @@
         <v>3.240416187557013</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19">
         <v>2.612942199279327</v>
@@ -2293,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2307,7 +2313,7 @@
         <v>3.224267322019204</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20">
         <v>2.595784029645404</v>
@@ -2343,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2357,7 +2363,7 @@
         <v>3.199676156013602</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21">
         <v>2.569655915764452</v>
@@ -2393,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2407,7 +2413,7 @@
         <v>3.173610926784897</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E22">
         <v>2.541961609708953</v>
@@ -2443,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2457,7 +2463,7 @@
         <v>3.150684626604055</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E23">
         <v>2.517602415766809</v>
@@ -2493,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2507,7 +2513,7 @@
         <v>3.134178515208647</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>2.500064672409188</v>
@@ -2543,7 +2549,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2557,7 +2563,7 @@
         <v>3.120022596496306</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E25">
         <v>2.485024008777326</v>
@@ -2593,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2607,7 +2613,7 @@
         <v>3.094767960086906</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E26">
         <v>2.458190957592338</v>
@@ -2643,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2657,7 +2663,7 @@
         <v>3.083329457599286</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E27">
         <v>2.446037548699242</v>
@@ -2693,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2707,7 +2713,7 @@
         <v>3.074543134313888</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E28">
         <v>2.436702080208506</v>
@@ -2743,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2757,7 +2763,7 @@
         <v>3.073229577771591</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E29">
         <v>2.435306426382315</v>
@@ -2793,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2807,7 +2813,7 @@
         <v>3.065223201825673</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E30">
         <v>2.426799651939778</v>
@@ -2843,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2857,7 +2863,7 @@
         <v>3.053370911712657</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E31">
         <v>2.414206593694698</v>
@@ -2893,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2907,7 +2913,7 @@
         <v>3.043420680449605</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E32">
         <v>2.403634472977705</v>
@@ -2943,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2957,7 +2963,7 @@
         <v>3.034138406034767</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E33">
         <v>2.39377205641194</v>
@@ -2993,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3043,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3057,7 +3063,7 @@
         <v>3.022451571690653</v>
       </c>
       <c r="D35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E35">
         <v>2.381354794921319</v>
@@ -3093,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3107,7 +3113,7 @@
         <v>1.930421456264695</v>
       </c>
       <c r="D36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E36">
         <v>2.007737588387895</v>
@@ -3143,7 +3149,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3157,7 +3163,7 @@
         <v>3.006244860280342</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E37">
         <v>2.364135164047864</v>
@@ -3193,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3207,7 +3213,7 @@
         <v>1.911108458500741</v>
       </c>
       <c r="D38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E38">
         <v>2.004869346308376</v>
@@ -3243,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3257,7 +3263,7 @@
         <v>2.997079538238938</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E39">
         <v>2.354397009378872</v>
@@ -3293,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3307,7 +3313,7 @@
         <v>1.900186449734734</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E40">
         <v>1.969405484366814</v>
@@ -3343,7 +3349,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3357,7 +3363,7 @@
         <v>2.989691832830151</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E41">
         <v>2.346547572382036</v>
@@ -3393,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3407,7 +3413,7 @@
         <v>1.89138276745593</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E42">
         <v>1.988908448053416</v>
@@ -3443,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3457,7 +3463,7 @@
         <v>2.993732811454215</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E43">
         <v>2.350841112170103</v>
@@ -3493,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3507,7 +3513,7 @@
         <v>1.896198266982939</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E44">
         <v>1.942246645980696</v>
@@ -3543,7 +3549,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3557,7 +3563,7 @@
         <v>3.004975357506775</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E45">
         <v>2.362786317350948</v>
@@ -3593,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3607,7 +3613,7 @@
         <v>1.90959563436224</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E46">
         <v>1.919910701288617</v>
@@ -3643,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3657,7 +3663,7 @@
         <v>3.012551559807466</v>
       </c>
       <c r="D47" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E47">
         <v>2.370836032295433</v>
@@ -3693,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3743,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3757,7 +3763,7 @@
         <v>3.011994006588589</v>
       </c>
       <c r="D49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E49">
         <v>2.370243632000376</v>
@@ -3793,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3807,7 +3813,7 @@
         <v>1.917959524518068</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E50">
         <v>1.906326840470971</v>
@@ -3843,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3857,7 +3863,7 @@
         <v>1.876326840470971</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E51">
         <v>1.906326840470971</v>
@@ -3893,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3907,7 +3913,7 @@
         <v>3.00769821087698</v>
       </c>
       <c r="D52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E52">
         <v>2.365679349056791</v>
@@ -3943,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3957,7 +3963,7 @@
         <v>1.912840367961734</v>
       </c>
       <c r="D53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E53">
         <v>1.955679349056791</v>
@@ -3993,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4007,7 +4013,7 @@
         <v>1.871673061783394</v>
       </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E54">
         <v>1.955679349056791</v>
@@ -4043,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4057,7 +4063,7 @@
         <v>3.004690327553521</v>
       </c>
       <c r="D55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E55">
         <v>2.362483473025616</v>
@@ -4093,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4107,7 +4113,7 @@
         <v>1.909255973667945</v>
       </c>
       <c r="D56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E56">
         <v>1.931297263327476</v>
@@ -4143,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4157,7 +4163,7 @@
         <v>1.868414521516314</v>
       </c>
       <c r="D57" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E57">
         <v>1.931297263327476</v>
@@ -4193,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4207,7 +4213,7 @@
         <v>3.007935044171493</v>
       </c>
       <c r="D58" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E58">
         <v>2.365930984432211</v>
@@ -4243,7 +4249,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4257,7 +4263,7 @@
         <v>1.891922864953648</v>
       </c>
       <c r="D59" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E59">
         <v>1.938330443133641</v>
@@ -4293,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4307,7 +4313,7 @@
         <v>1.871929631185784</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E60">
         <v>1.938330443133641</v>
@@ -4343,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4357,7 +4363,7 @@
         <v>3.014769348869088</v>
       </c>
       <c r="D61" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E61">
         <v>2.373192433173406</v>
@@ -4393,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4407,7 +4413,7 @@
         <v>1.900038601782042</v>
       </c>
       <c r="D62" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E62">
         <v>1.938105255654558</v>
@@ -4443,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4457,7 +4463,7 @@
         <v>1.879333461274845</v>
       </c>
       <c r="D63" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E63">
         <v>1.938105255654558</v>
@@ -4493,7 +4499,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4507,7 +4513,7 @@
         <v>3.020057315470159</v>
       </c>
       <c r="D64" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E64">
         <v>2.378810897687044</v>
@@ -4543,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4557,7 +4563,7 @@
         <v>1.906318062120814</v>
       </c>
       <c r="D65" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E65">
         <v>1.950061136501503</v>
@@ -4593,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4607,7 +4613,7 @@
         <v>1.885062091759339</v>
       </c>
       <c r="D66" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E66">
         <v>1.950061136501503</v>
@@ -4643,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4657,7 +4663,7 @@
         <v>3.026470251012646</v>
       </c>
       <c r="D67" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E67">
         <v>2.385624641700937</v>
@@ -4693,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4707,7 +4713,7 @@
         <v>1.913933423077517</v>
       </c>
       <c r="D68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E68">
         <v>2.07796288542562</v>
@@ -4743,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4757,7 +4763,7 @@
         <v>1.892009438597033</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E69">
         <v>2.07796288542562</v>
@@ -4793,7 +4799,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4807,7 +4813,7 @@
         <v>3.052162558207098</v>
       </c>
       <c r="D70" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E70">
         <v>2.412922718095043</v>
@@ -4843,7 +4849,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4857,7 +4863,7 @@
         <v>1.94444303787093</v>
       </c>
       <c r="D71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E71">
         <v>2.351714323704782</v>
@@ -4893,7 +4899,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4907,7 +4913,7 @@
         <v>1.919842771391023</v>
       </c>
       <c r="D72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E72">
         <v>2.351714323704782</v>
@@ -4943,7 +4949,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4957,7 +4963,7 @@
         <v>3.139870507647556</v>
       </c>
       <c r="D73" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E73">
         <v>2.506112414375529</v>
@@ -4993,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5007,7 +5013,7 @@
         <v>2.048596227831473</v>
       </c>
       <c r="D74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E74">
         <v>2.439632917331332</v>
@@ -5043,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5057,7 +5063,7 @@
         <v>2.014859716618186</v>
       </c>
       <c r="D75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E75">
         <v>2.439632917331332</v>
@@ -5093,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5107,7 +5113,7 @@
         <v>3.067734589357061</v>
       </c>
       <c r="D76" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E76">
         <v>2.429468001191877</v>
@@ -5143,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5157,7 +5163,7 @@
         <v>1.96293482486151</v>
       </c>
       <c r="D77" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E77">
         <v>2.317307812788318</v>
@@ -5193,7 +5199,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5207,7 +5213,7 @@
         <v>1.936712471803482</v>
       </c>
       <c r="D78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E78">
         <v>2.317307812788318</v>
@@ -5243,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5257,7 +5263,7 @@
         <v>3.023857588718067</v>
       </c>
       <c r="D79" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E79">
         <v>2.382848688012947</v>
@@ -5293,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5307,7 +5313,7 @@
         <v>1.910830886602705</v>
       </c>
       <c r="D80" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E80">
         <v>2.232334342850537</v>
@@ -5343,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5357,7 +5363,7 @@
         <v>1.889179054444573</v>
       </c>
       <c r="D81" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E81">
         <v>2.232334342850537</v>
@@ -5393,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5407,7 +5413,7 @@
         <v>2.96438641260543</v>
       </c>
       <c r="D82" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E82">
         <v>2.319660563393269</v>
@@ -5443,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5457,7 +5463,7 @@
         <v>1.840208864968948</v>
       </c>
       <c r="D83" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E83">
         <v>2.1280939850984</v>
@@ -5493,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5507,7 +5513,7 @@
         <v>1.824751946989215</v>
       </c>
       <c r="D84" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E84">
         <v>2.1280939850984</v>
@@ -5543,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5557,7 +5563,7 @@
         <v>2.89858481633162</v>
       </c>
       <c r="D85" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E85">
         <v>2.249746367352347</v>
@@ -5593,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5607,7 +5613,7 @@
         <v>1.782813572795181</v>
       </c>
       <c r="D86" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E86">
         <v>2.087423265310894</v>
@@ -5643,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5657,7 +5663,7 @@
         <v>1.753466884359255</v>
       </c>
       <c r="D87" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E87">
         <v>2.087423265310894</v>
@@ -5693,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5707,7 +5713,7 @@
         <v>2.863380544404418</v>
       </c>
       <c r="D88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E88">
         <v>2.212341828429695</v>
@@ -5743,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5757,7 +5763,7 @@
         <v>1.740861815415264</v>
       </c>
       <c r="D89" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E89">
         <v>2.074419260379142</v>
@@ -5793,7 +5799,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5807,7 +5813,7 @@
         <v>1.715328923104786</v>
       </c>
       <c r="D90" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E90">
         <v>2.074419260379142</v>
@@ -5843,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5857,7 +5863,7 @@
         <v>2.860232758796729</v>
       </c>
       <c r="D91" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E91">
         <v>2.208997306221525</v>
@@ -5893,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5907,7 +5913,7 @@
         <v>1.737110704232769</v>
       </c>
       <c r="D92" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E92">
         <v>2.081468211371934</v>
@@ -5943,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5957,7 +5963,7 @@
         <v>1.71191882202979</v>
       </c>
       <c r="D93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E93">
         <v>2.081468211371934</v>
@@ -5993,7 +5999,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6007,7 +6013,7 @@
         <v>2.844214660630511</v>
       </c>
       <c r="D94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E94">
         <v>2.191978076919919</v>
@@ -6043,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6057,7 +6063,7 @@
         <v>1.718022470584692</v>
       </c>
       <c r="D95" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E95">
         <v>2.066451244341104</v>
@@ -6093,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6107,7 +6113,7 @@
         <v>1.69456588234972</v>
       </c>
       <c r="D96" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E96">
         <v>2.066451244341104</v>
@@ -6143,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6157,7 +6163,7 @@
         <v>2.802243669794394</v>
       </c>
       <c r="D97" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E97">
         <v>2.147383899156544</v>
@@ -6193,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6207,7 +6213,7 @@
         <v>1.668007039838319</v>
       </c>
       <c r="D98" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E98">
         <v>2.026760758474768</v>
@@ -6243,7 +6249,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6257,7 +6263,7 @@
         <v>1.649097308943927</v>
       </c>
       <c r="D99" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E99">
         <v>2.026760758474768</v>
@@ -6293,7 +6299,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6307,7 +6313,7 @@
         <v>2.60784162529713</v>
       </c>
       <c r="D100" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E100">
         <v>2.069343992760599</v>
@@ -6343,7 +6349,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6357,7 +6363,7 @@
         <v>2.728794346127623</v>
       </c>
       <c r="D101" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E101">
         <v>2.069343992760599</v>
@@ -6393,7 +6399,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6443,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6493,7 +6499,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6507,7 +6513,7 @@
         <v>2.545370448575698</v>
       </c>
       <c r="D104" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E104">
         <v>1.994904039190669</v>
@@ -6543,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6557,7 +6563,7 @@
         <v>2.658733213355923</v>
       </c>
       <c r="D105" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E105">
         <v>1.994904039190669</v>
@@ -6593,7 +6599,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6643,7 +6649,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6693,7 +6699,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6707,7 +6713,7 @@
         <v>2.481313246131303</v>
       </c>
       <c r="D108" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E108">
         <v>1.918574195156459</v>
@@ -6743,7 +6749,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6757,7 +6763,7 @@
         <v>2.586893360147255</v>
       </c>
       <c r="D109" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E109">
         <v>1.918574195156459</v>
@@ -6793,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6843,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6893,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6907,7 +6913,7 @@
         <v>2.40667480096654</v>
       </c>
       <c r="D112" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E112">
         <v>1.855244363890487</v>
@@ -6943,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6957,7 +6963,7 @@
         <v>2.503186692672755</v>
       </c>
       <c r="D113" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E113">
         <v>1.855244363890487</v>
@@ -6993,7 +6999,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7043,7 +7049,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7093,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7107,7 +7113,7 @@
         <v>2.261174748318485</v>
       </c>
       <c r="D116" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E116">
         <v>1.708621781365236</v>
@@ -7143,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7157,7 +7163,7 @@
         <v>2.295408018482838</v>
       </c>
       <c r="D117" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E117">
         <v>1.708621781365236</v>
@@ -7193,7 +7199,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7207,7 +7213,7 @@
         <v>2.256941478154132</v>
       </c>
       <c r="D118" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E118">
         <v>1.708621781365236</v>
@@ -7243,7 +7249,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7257,7 +7263,7 @@
         <v>2.37840151605552</v>
       </c>
       <c r="D119" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E119">
         <v>1.708621781365236</v>
@@ -7293,7 +7299,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7307,7 +7313,7 @@
         <v>1.162928473299494</v>
       </c>
       <c r="D120" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E120">
         <v>1.739714710417097</v>
@@ -7343,7 +7349,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7357,7 +7363,7 @@
         <v>2.16369956491871</v>
       </c>
       <c r="D121" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E121">
         <v>1.585907487978019</v>
@@ -7393,7 +7399,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7407,7 +7413,7 @@
         <v>2.202284405770554</v>
       </c>
       <c r="D122" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E122">
         <v>1.585907487978019</v>
@@ -7443,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7457,7 +7463,7 @@
         <v>2.155114724066867</v>
       </c>
       <c r="D123" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E123">
         <v>1.585907487978019</v>
@@ -7493,7 +7499,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7507,7 +7513,7 @@
         <v>2.273963819555761</v>
       </c>
       <c r="D124" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E124">
         <v>1.585907487978019</v>
@@ -7543,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7557,7 +7563,7 @@
         <v>1.038473551637282</v>
       </c>
       <c r="D125" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E125">
         <v>1.644850469429817</v>
@@ -7593,7 +7599,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7607,7 +7613,7 @@
         <v>2.003396115050518</v>
       </c>
       <c r="D126" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E126">
         <v>1.44524374557326</v>
@@ -7657,7 +7663,7 @@
         <v>2.011358022681203</v>
       </c>
       <c r="D127" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E127">
         <v>1.44524374557326</v>
@@ -7707,7 +7713,7 @@
         <v>2.126521048903798</v>
       </c>
       <c r="D128" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E128">
         <v>1.44524374557326</v>
@@ -7757,7 +7763,7 @@
         <v>0.862770916610359</v>
       </c>
       <c r="D129" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E129">
         <v>1.510923286087617</v>
@@ -7807,7 +7813,7 @@
         <v>1.874602728130037</v>
       </c>
       <c r="D130" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E130">
         <v>1.276091140631614</v>
@@ -7843,7 +7849,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7857,7 +7863,7 @@
         <v>1.872474831255431</v>
       </c>
       <c r="D131" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E131">
         <v>1.276091140631614</v>
@@ -7893,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7907,7 +7913,7 @@
         <v>1.98407675000557</v>
       </c>
       <c r="D132" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E132">
         <v>1.276091140631614</v>
@@ -7943,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7957,7 +7963,7 @@
         <v>0.7399584468816611</v>
       </c>
       <c r="D133" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E133">
         <v>1.38153638125506</v>
@@ -7993,7 +7999,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8007,7 +8013,7 @@
         <v>1.730522677364715</v>
       </c>
       <c r="D134" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E134">
         <v>1.086861580870708</v>
@@ -8043,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8057,7 +8063,7 @@
         <v>1.717107403241213</v>
       </c>
       <c r="D135" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E135">
         <v>1.086861580870708</v>
@@ -8093,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8107,7 +8113,7 @@
         <v>1.82472554178586</v>
       </c>
       <c r="D136" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E136">
         <v>1.086861580870708</v>
@@ -8143,7 +8149,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8157,7 +8163,7 @@
         <v>0.5494009603855905</v>
       </c>
       <c r="D137" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E137">
         <v>1.236792367122156</v>
@@ -8193,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8207,7 +8213,7 @@
         <v>1.560267149716914</v>
       </c>
       <c r="D138" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E138">
         <v>0.8632540906420294</v>
@@ -8243,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8257,7 +8263,7 @@
         <v>1.533513884948193</v>
       </c>
       <c r="D139" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E139">
         <v>0.8632540906420294</v>
@@ -8293,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8307,7 +8313,7 @@
         <v>1.636424497382762</v>
       </c>
       <c r="D140" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E140">
         <v>0.8632540906420294</v>
@@ -8343,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8357,7 +8363,7 @@
         <v>0.3242242947868856</v>
       </c>
       <c r="D141" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E141">
         <v>1.065752251789342</v>
@@ -8393,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8407,7 +8413,7 @@
         <v>1.451788381289887</v>
       </c>
       <c r="D142" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E142">
         <v>0.7958855760303623</v>
@@ -8443,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8457,7 +8463,7 @@
         <v>1.416536779824118</v>
       </c>
       <c r="D143" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E143">
         <v>0.7958855760303623</v>
@@ -8493,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8507,7 +8513,7 @@
         <v>1.516447979306788</v>
       </c>
       <c r="D144" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E144">
         <v>0.7958855760303623</v>
@@ -8543,7 +8549,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8557,7 +8563,7 @@
         <v>0.1807523752543663</v>
       </c>
       <c r="D145" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E145">
         <v>0.9567735812036653</v>
@@ -8593,7 +8599,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8607,7 +8613,7 @@
         <v>1.341632314098553</v>
       </c>
       <c r="D146" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E146">
         <v>0.6547639784304042</v>
@@ -8643,7 +8649,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8657,7 +8663,7 @@
         <v>1.297750974650053</v>
       </c>
       <c r="D147" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E147">
         <v>0.6547639784304042</v>
@@ -8693,7 +8699,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8707,7 +8713,7 @@
         <v>1.394616384256465</v>
       </c>
       <c r="D148" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E148">
         <v>0.6547639784304042</v>
@@ -8743,7 +8749,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8757,7 +8763,7 @@
         <v>0.03506209284002182</v>
       </c>
       <c r="D149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E149">
         <v>0.8461098823662887</v>
@@ -8793,7 +8799,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8807,7 +8813,7 @@
         <v>1.256461817624148</v>
       </c>
       <c r="D150" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E150">
         <v>0.5456515451590462</v>
@@ -8843,7 +8849,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8857,7 +8863,7 @@
         <v>1.205908135133873</v>
       </c>
       <c r="D151" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E151">
         <v>0.5456515451590462</v>
@@ -8893,7 +8899,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8907,7 +8913,7 @@
         <v>1.300418600137307</v>
       </c>
       <c r="D152" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E152">
         <v>0.5456515451590462</v>
@@ -8943,7 +8949,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8957,7 +8963,7 @@
         <v>-0.07758275733580433</v>
       </c>
       <c r="D153" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E153">
         <v>0.7605468951247198</v>
@@ -8993,7 +8999,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9007,7 +9013,7 @@
         <v>1.07997323323726</v>
       </c>
       <c r="D154" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E154">
         <v>0.4493358506304439</v>
@@ -9043,7 +9049,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9057,7 +9063,7 @@
         <v>1.124836651250086</v>
       </c>
       <c r="D155" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E155">
         <v>0.4493358506304439</v>
@@ -9093,7 +9099,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9107,7 +9113,7 @@
         <v>-0.1770165858599375</v>
       </c>
       <c r="D156" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E156">
         <v>0.6850187605663192</v>
@@ -9143,7 +9149,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9157,7 +9163,7 @@
         <v>0.9919465651648807</v>
       </c>
       <c r="D157" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E157">
         <v>0.3474042381876092</v>
@@ -9193,7 +9199,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9207,7 +9213,7 @@
         <v>1.039038099769426</v>
       </c>
       <c r="D158" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E158">
         <v>0.3474042381876092</v>
@@ -9243,7 +9249,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9257,7 +9263,7 @@
         <v>-0.2822481425904906</v>
       </c>
       <c r="D159" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E159">
         <v>0.6050867767082688</v>
@@ -9293,7 +9299,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9307,7 +9313,7 @@
         <v>0.9183156432255819</v>
       </c>
       <c r="D160" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E160">
         <v>0.2325423301237928</v>
@@ -9357,7 +9363,7 @@
         <v>-0.3774576698762075</v>
       </c>
       <c r="D161" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E161">
         <v>0.4926188471075936</v>
@@ -9407,7 +9413,7 @@
         <v>-0.4303137196335811</v>
       </c>
       <c r="D162" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E162">
         <v>0.4926188471075936</v>
@@ -9457,7 +9463,7 @@
         <v>0.8418793262205044</v>
       </c>
       <c r="D163" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E163">
         <v>0.1384668630406214</v>
@@ -9507,7 +9513,7 @@
         <v>0.7767029332404918</v>
       </c>
       <c r="D164" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E164">
         <v>0.1384668630406214</v>
@@ -9557,7 +9563,7 @@
         <v>-0.4715331369593789</v>
       </c>
       <c r="D165" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E165">
         <v>0.4214089449404703</v>
@@ -9607,7 +9613,7 @@
         <v>-0.5240625357893807</v>
       </c>
       <c r="D166" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E166">
         <v>0.4214089449404703</v>
@@ -9657,7 +9663,7 @@
         <v>0.7712878926560949</v>
       </c>
       <c r="D167" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E167">
         <v>0.05158509865365524</v>
@@ -9707,7 +9713,7 @@
         <v>0.707921536434144</v>
       </c>
       <c r="D168" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E168">
         <v>0.05158509865365524</v>
@@ -9757,7 +9763,7 @@
         <v>-0.5584149013463451</v>
       </c>
       <c r="D169" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E169">
         <v>0.3556442760642256</v>
@@ -9807,7 +9813,7 @@
         <v>-0.6106426273833367</v>
       </c>
       <c r="D170" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E170">
         <v>0.3556442760642256</v>
@@ -9857,7 +9863,7 @@
         <v>0.7170193735272363</v>
       </c>
       <c r="D171" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E171">
         <v>-0.01520692488955522</v>
@@ -9907,7 +9913,7 @@
         <v>0.6550445177957691</v>
       </c>
       <c r="D172" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E172">
         <v>-0.01520692488955522</v>
@@ -9957,7 +9963,7 @@
         <v>-0.6252069248895555</v>
       </c>
       <c r="D173" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E173">
         <v>0.3050864249099901</v>
@@ -10007,7 +10013,7 @@
         <v>-0.6772027341781328</v>
       </c>
       <c r="D174" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E174">
         <v>0.3050864249099901</v>
@@ -10057,7 +10063,7 @@
         <v>0.6624776741967331</v>
       </c>
       <c r="D175" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E175">
         <v>-0.08233517021940617</v>
@@ -10093,7 +10099,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10107,7 +10113,7 @@
         <v>0.6019013235763042</v>
       </c>
       <c r="D176" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E176">
         <v>-0.08233517021940617</v>
@@ -10143,7 +10149,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10157,7 +10163,7 @@
         <v>-0.6923351702194065</v>
       </c>
       <c r="D177" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E177">
         <v>0.2542740725422554</v>
@@ -10193,7 +10199,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10207,7 +10213,7 @@
         <v>-0.7440978953228106</v>
       </c>
       <c r="D178" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E178">
         <v>0.2542740725422554</v>
@@ -10243,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10257,7 +10263,7 @@
         <v>0.6552913511059879</v>
       </c>
       <c r="D179" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E179">
         <v>-0.09117987556186069</v>
@@ -10293,7 +10299,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10307,7 +10313,7 @@
         <v>0.5948992651801932</v>
       </c>
       <c r="D180" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E180">
         <v>-0.09117987556186069</v>
@@ -10343,7 +10349,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10357,7 +10363,7 @@
         <v>0.543167250859228</v>
       </c>
       <c r="D181" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E181">
         <v>-0.09117987556186069</v>
@@ -10393,7 +10399,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10407,7 +10413,7 @@
         <v>0.5418273224640568</v>
       </c>
       <c r="D182" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E182">
         <v>-0.09117987556186069</v>
@@ -10443,7 +10449,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10457,7 +10463,7 @@
         <v>-0.701179875561861</v>
       </c>
       <c r="D183" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E183">
         <v>0.2475791219705359</v>
@@ -10493,7 +10499,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10507,7 +10513,7 @@
         <v>-0.7529118898828271</v>
       </c>
       <c r="D184" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E184">
         <v>0.2475791219705359</v>
@@ -10543,7 +10549,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10557,7 +10563,7 @@
         <v>0.6454205590474551</v>
       </c>
       <c r="D185" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E185">
         <v>-0.103328542710825</v>
@@ -10593,7 +10599,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10607,7 +10613,7 @@
         <v>0.5852815703539305</v>
       </c>
       <c r="D186" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E186">
         <v>-0.103328542710825</v>
@@ -10643,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10657,7 +10663,7 @@
         <v>0.5335917389050095</v>
       </c>
       <c r="D187" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E187">
         <v>-0.103328542710825</v>
@@ -10693,7 +10699,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10707,7 +10713,7 @@
         <v>0.5320408961496135</v>
       </c>
       <c r="D188" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E188">
         <v>-0.103328542710825</v>
@@ -10743,7 +10749,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10757,7 +10763,7 @@
         <v>-0.7133285427108254</v>
       </c>
       <c r="D189" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E189">
         <v>0.238383255864723</v>
@@ -10793,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10807,7 +10813,7 @@
         <v>-0.7650183741597454</v>
       </c>
       <c r="D190" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E190">
         <v>0.238383255864723</v>
@@ -10843,7 +10849,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10857,7 +10863,7 @@
         <v>0.5083726106019757</v>
       </c>
       <c r="D191" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E191">
         <v>-0.2004767023975047</v>
@@ -10907,7 +10913,7 @@
         <v>0.4570200991519675</v>
       </c>
       <c r="D192" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E192">
         <v>-0.2004767023975047</v>
@@ -10957,7 +10963,7 @@
         <v>0.4537826564020104</v>
       </c>
       <c r="D193" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E193">
         <v>-0.2004767023975047</v>
@@ -11007,7 +11013,7 @@
         <v>-0.810476702397505</v>
       </c>
       <c r="D194" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E194">
         <v>0.1648474961018893</v>
@@ -11057,7 +11063,7 @@
         <v>-0.8618292138475132</v>
       </c>
       <c r="D195" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E195">
         <v>0.1648474961018893</v>
@@ -11107,7 +11113,7 @@
         <v>0.3793436997319031</v>
       </c>
       <c r="D196" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E196">
         <v>-0.3634605898123331</v>
@@ -11143,7 +11149,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11157,7 +11163,7 @@
         <v>0.3285571045576408</v>
       </c>
       <c r="D197" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E197">
         <v>-0.3634605898123331</v>
@@ -11193,7 +11199,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11207,7 +11213,7 @@
         <v>0.3224900804289543</v>
       </c>
       <c r="D198" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E198">
         <v>-0.3634605898123331</v>
@@ -11243,7 +11249,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11257,7 +11263,7 @@
         <v>-0.9734605898123334</v>
       </c>
       <c r="D199" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E199">
         <v>0.04147774798927539</v>
@@ -11293,7 +11299,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11307,7 +11313,7 @@
         <v>-1.024247184986596</v>
       </c>
       <c r="D200" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E200">
         <v>0.04147774798927539</v>
@@ -11343,7 +11349,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11357,7 +11363,7 @@
         <v>0.1872203926773688</v>
       </c>
       <c r="D201" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E201">
         <v>-0.486627682752748</v>
@@ -11407,7 +11413,7 @@
         <v>0.2818364178207418</v>
       </c>
       <c r="D202" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E202">
         <v>-0.486627682752748</v>
@@ -11457,7 +11463,7 @@
         <v>0.2314774861636328</v>
       </c>
       <c r="D203" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E203">
         <v>-0.486627682752748</v>
@@ -11507,7 +11513,7 @@
         <v>0.2232721444491759</v>
       </c>
       <c r="D204" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E204">
         <v>-0.486627682752748</v>
@@ -11557,7 +11563,7 @@
         <v>-1.096627682752748</v>
       </c>
       <c r="D205" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E205">
         <v>-0.05175289875034395</v>
@@ -11607,7 +11613,7 @@
         <v>-1.146986614409856</v>
       </c>
       <c r="D206" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E206">
         <v>-0.05175289875034395</v>
@@ -11657,7 +11663,7 @@
         <v>0.01252453965430966</v>
       </c>
       <c r="D207" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E207">
         <v>-0.6936746196689665</v>
@@ -11693,7 +11699,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11707,7 +11713,7 @@
         <v>0.1179242594287349</v>
       </c>
       <c r="D208" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E208">
         <v>-0.6936746196689665</v>
@@ -11743,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11757,7 +11763,7 @@
         <v>0.06828424074703054</v>
       </c>
       <c r="D209" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E209">
         <v>-0.6936746196689665</v>
@@ -11793,7 +11799,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11807,7 +11813,7 @@
         <v>0.01720429679214597</v>
       </c>
       <c r="D210" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E210">
         <v>-0.6936746196689665</v>
@@ -11843,7 +11849,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11857,7 +11863,7 @@
         <v>-1.303674619668967</v>
       </c>
       <c r="D211" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E211">
         <v>-0.2084759273883146</v>
@@ -11893,7 +11899,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11907,7 +11913,7 @@
         <v>-1.353314638350671</v>
       </c>
       <c r="D212" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E212">
         <v>-0.2084759273883146</v>
@@ -11943,7 +11949,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11957,7 +11963,7 @@
         <v>-0.1245779691705016</v>
       </c>
       <c r="D213" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E213">
         <v>-0.8561664819798533</v>
@@ -11993,7 +11999,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12007,7 +12013,7 @@
         <v>-0.01071513156738391</v>
       </c>
       <c r="D214" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E214">
         <v>-0.8561664819798533</v>
@@ -12043,7 +12049,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12057,7 +12063,7 @@
         <v>-0.05979094239384253</v>
       </c>
       <c r="D215" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E215">
         <v>-0.8561664819798533</v>
@@ -12093,7 +12099,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12107,7 +12113,7 @@
         <v>-0.1125635099144651</v>
       </c>
       <c r="D216" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E216">
         <v>-0.8561664819798533</v>
@@ -12143,7 +12149,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12157,7 +12163,7 @@
         <v>-1.466166481979854</v>
       </c>
       <c r="D217" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E217">
         <v>-0.331473239831972</v>
@@ -12193,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12207,7 +12213,7 @@
         <v>-1.515242292806312</v>
       </c>
       <c r="D218" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E218">
         <v>-0.331473239831972</v>
@@ -12243,7 +12249,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12257,7 +12263,7 @@
         <v>-1.470289185120701</v>
       </c>
       <c r="D219" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E219">
         <v>-1.461213374294242</v>
@@ -12293,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12307,7 +12313,7 @@
         <v>-0.2405124524062172</v>
       </c>
       <c r="D220" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E220">
         <v>-0.9935703139629233</v>
@@ -12357,7 +12363,7 @@
         <v>-0.1194931652206472</v>
       </c>
       <c r="D221" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E221">
         <v>-0.9935703139629233</v>
@@ -12407,7 +12413,7 @@
         <v>-0.2508944510330187</v>
       </c>
       <c r="D222" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E222">
         <v>-0.9935703139629233</v>
@@ -12457,7 +12463,7 @@
         <v>-0.1680918794082764</v>
       </c>
       <c r="D223" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E223">
         <v>-0.9935703139629233</v>
@@ -12507,7 +12513,7 @@
         <v>-0.2222957368453899</v>
       </c>
       <c r="D224" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E224">
         <v>-0.9935703139629233</v>
@@ -12557,7 +12563,7 @@
         <v>-1.603570313962924</v>
       </c>
       <c r="D225" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E225">
         <v>-0.4354803070969355</v>
@@ -12607,7 +12613,7 @@
         <v>-1.652169028150552</v>
       </c>
       <c r="D226" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E226">
         <v>-0.4354803070969355</v>
@@ -12657,7 +12663,7 @@
         <v>-1.594334311216528</v>
       </c>
       <c r="D227" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E227">
         <v>-1.478729167967043</v>
@@ -12707,7 +12713,7 @@
         <v>-0.35263208243365</v>
       </c>
       <c r="D228" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E228">
         <v>-1.126452838439881</v>
@@ -12743,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12757,7 +12763,7 @@
         <v>-0.2246918304315724</v>
       </c>
       <c r="D229" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E229">
         <v>-1.126452838439881</v>
@@ -12793,7 +12799,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12807,7 +12813,7 @@
         <v>-0.3565545138983772</v>
       </c>
       <c r="D230" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E230">
         <v>-1.126452838439881</v>
@@ -12843,7 +12849,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12857,7 +12863,7 @@
         <v>-0.2728291469647672</v>
       </c>
       <c r="D231" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E231">
         <v>-1.126452838439881</v>
@@ -12893,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12907,7 +12913,7 @@
         <v>-1.736452838439881</v>
       </c>
       <c r="D232" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E232">
         <v>-0.5360649957635211</v>
@@ -12943,7 +12949,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12957,7 +12963,7 @@
         <v>-1.784590154973076</v>
       </c>
       <c r="D233" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E233">
         <v>-0.5360649957635211</v>
@@ -12993,7 +12999,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13007,7 +13013,7 @@
         <v>-1.714297701369337</v>
       </c>
       <c r="D234" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E234">
         <v>-1.46263208243365</v>
@@ -13043,7 +13049,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13057,7 +13063,7 @@
         <v>-0.2590860480244892</v>
       </c>
       <c r="D235" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E235">
         <v>-1.16989816592567</v>
@@ -13107,7 +13113,7 @@
         <v>-0.3910995833228421</v>
       </c>
       <c r="D236" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E236">
         <v>-1.16989816592567</v>
@@ -13157,7 +13163,7 @@
         <v>-0.307072512726136</v>
       </c>
       <c r="D237" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E237">
         <v>-1.16989816592567</v>
@@ -13207,7 +13213,7 @@
         <v>-1.779898165925671</v>
       </c>
       <c r="D238" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E238">
         <v>-0.5689506950409591</v>
@@ -13257,7 +13263,7 @@
         <v>-1.827884630627318</v>
       </c>
       <c r="D239" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E239">
         <v>-0.5689506950409591</v>
@@ -13307,7 +13313,7 @@
         <v>-1.753519177571786</v>
       </c>
       <c r="D240" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E240">
         <v>-1.495262006903079</v>
@@ -13357,7 +13363,7 @@
         <v>-0.3066333113890707</v>
       </c>
       <c r="D241" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E241">
         <v>-1.229957867017773</v>
@@ -13393,7 +13399,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13407,7 +13413,7 @@
         <v>-0.4388553873162158</v>
       </c>
       <c r="D242" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E242">
         <v>-1.229957867017773</v>
@@ -13443,7 +13449,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13457,7 +13463,7 @@
         <v>-0.3544112354619253</v>
       </c>
       <c r="D243" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E243">
         <v>-1.229957867017773</v>
@@ -13493,7 +13499,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13507,7 +13513,7 @@
         <v>-0.4788553873162158</v>
       </c>
       <c r="D244" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E244">
         <v>-1.229957867017773</v>
@@ -13543,7 +13549,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13557,7 +13563,7 @@
         <v>-1.839957867017773</v>
       </c>
       <c r="D245" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E245">
         <v>-0.6144125521176198</v>
@@ -13593,7 +13599,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13607,7 +13613,7 @@
         <v>-1.887735791090629</v>
       </c>
       <c r="D246" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E246">
         <v>-0.6144125521176198</v>
@@ -13643,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13657,7 +13663,7 @@
         <v>-1.807739741057712</v>
       </c>
       <c r="D247" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E247">
         <v>-1.641074829931972</v>
@@ -13693,7 +13699,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13707,7 +13713,7 @@
         <v>-0.4492665299910312</v>
       </c>
       <c r="D248" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E248">
         <v>-1.24305135649527</v>
@@ -13757,7 +13763,7 @@
         <v>-0.3647314511264801</v>
       </c>
       <c r="D249" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E249">
         <v>-1.24305135649527</v>
@@ -13807,7 +13813,7 @@
         <v>-0.4892665299910313</v>
       </c>
       <c r="D250" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E250">
         <v>-1.24305135649527</v>
@@ -13857,7 +13863,7 @@
         <v>-1.85305135649527</v>
       </c>
       <c r="D251" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E251">
         <v>-0.6243235962360032</v>
@@ -13907,7 +13913,7 @@
         <v>-1.900783817062996</v>
       </c>
       <c r="D252" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E252">
         <v>-0.6243235962360032</v>
@@ -13957,7 +13963,7 @@
         <v>-1.819560252391564</v>
       </c>
       <c r="D253" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E253">
         <v>-1.515139306016957</v>
@@ -14007,7 +14013,7 @@
         <v>-0.4959723755022063</v>
       </c>
       <c r="D254" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E254">
         <v>-1.301790585784434</v>
@@ -14043,7 +14049,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14057,7 +14063,7 @@
         <v>-0.4110293853231477</v>
       </c>
       <c r="D255" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E255">
         <v>-1.301790585784434</v>
@@ -14093,7 +14099,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14107,7 +14113,7 @@
         <v>-0.5359723755022063</v>
       </c>
       <c r="D256" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E256">
         <v>-1.301790585784434</v>
@@ -14143,7 +14149,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14157,7 +14163,7 @@
         <v>-1.911790585784434</v>
       </c>
       <c r="D257" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E257">
         <v>-0.6687859295173837</v>
@@ -14193,7 +14199,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14207,7 +14213,7 @@
         <v>-1.959319090694905</v>
       </c>
       <c r="D258" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E258">
         <v>-0.6687859295173837</v>
@@ -14243,7 +14249,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14257,7 +14263,7 @@
         <v>-1.872588723277615</v>
       </c>
       <c r="D259" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E259">
         <v>-1.283614900054561</v>
@@ -14293,7 +14299,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14307,7 +14313,7 @@
         <v>-0.4288211453050677</v>
       </c>
       <c r="D260" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E260">
         <v>-1.324363391400262</v>
@@ -14357,7 +14363,7 @@
         <v>-0.5539208910786808</v>
       </c>
       <c r="D261" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E261">
         <v>-1.324363391400262</v>
@@ -14407,7 +14413,7 @@
         <v>-1.934363391400263</v>
       </c>
       <c r="D262" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E262">
         <v>-0.6858722893238101</v>
@@ -14457,7 +14463,7 @@
         <v>-1.981813518513456</v>
       </c>
       <c r="D263" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E263">
         <v>-0.6858722893238101</v>
@@ -14507,7 +14513,7 @@
         <v>-1.892966950569682</v>
       </c>
       <c r="D264" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E264">
         <v>-1.353721399531455</v>
@@ -14557,7 +14563,7 @@
         <v>-0.46714221579668</v>
       </c>
       <c r="D265" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E265">
         <v>-1.372982194490942</v>
@@ -14593,7 +14599,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14607,7 +14613,7 @@
         <v>-0.5925795921473114</v>
       </c>
       <c r="D266" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E266">
         <v>-1.372982194490942</v>
@@ -14643,7 +14649,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14657,7 +14663,7 @@
         <v>-1.982982194490942</v>
       </c>
       <c r="D267" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E267">
         <v>-0.7226740222188379</v>
@@ -14693,7 +14699,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14707,7 +14713,7 @@
         <v>-2.030263506315626</v>
       </c>
       <c r="D268" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E268">
         <v>-0.7226740222188379</v>
@@ -14743,7 +14749,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14757,7 +14763,7 @@
         <v>-1.9368589255821</v>
       </c>
       <c r="D269" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E269">
         <v>-1.45714221579668</v>
@@ -14793,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14807,7 +14813,7 @@
         <v>-0.5866700905677851</v>
       </c>
       <c r="D270" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E270">
         <v>-1.365550157569966</v>
@@ -14857,7 +14863,7 @@
         <v>-1.975550157569966</v>
       </c>
       <c r="D271" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E271">
         <v>-0.7170483831605994</v>
@@ -14907,7 +14913,7 @@
         <v>-2.022857275078404</v>
       </c>
       <c r="D272" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E272">
         <v>-0.7170483831605994</v>
@@ -14957,7 +14963,7 @@
         <v>-1.930149447806219</v>
       </c>
       <c r="D273" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E273">
         <v>-1.537441620534035</v>
@@ -15007,7 +15013,7 @@
         <v>-0.6162550847681185</v>
       </c>
       <c r="D274" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E274">
         <v>-1.402757486520604</v>
@@ -15043,7 +15049,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15057,7 +15063,7 @@
         <v>-2.012757486520604</v>
       </c>
       <c r="D275" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E275">
         <v>-0.7452122641024017</v>
@@ -15093,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15107,7 +15113,7 @@
         <v>-2.05993541191463</v>
       </c>
       <c r="D276" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E276">
         <v>-0.7452122641024017</v>
@@ -15143,7 +15149,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15157,7 +15163,7 @@
         <v>-1.963739397553323</v>
       </c>
       <c r="D277" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E277">
         <v>-1.707297905433836</v>
@@ -15193,7 +15199,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15207,7 +15213,7 @@
         <v>-0.634446447405705</v>
       </c>
       <c r="D278" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E278">
         <v>-1.425635706780974</v>
@@ -15257,7 +15263,7 @@
         <v>-2.035635706780974</v>
       </c>
       <c r="D279" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E279">
         <v>-0.7625298058272652</v>
@@ -15307,7 +15313,7 @@
         <v>-2.082734193910206</v>
       </c>
       <c r="D280" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E280">
         <v>-0.7625298058272652</v>
@@ -15357,7 +15363,7 @@
         <v>-1.984393346399491</v>
       </c>
       <c r="D281" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E281">
         <v>-1.800870653337982</v>
@@ -15407,7 +15413,7 @@
         <v>-0.657597094999522</v>
       </c>
       <c r="D282" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E282">
         <v>-1.454750931702455</v>
@@ -15457,7 +15463,7 @@
         <v>-2.064750931702456</v>
       </c>
       <c r="D283" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E283">
         <v>-0.784568413580331</v>
@@ -15507,7 +15513,7 @@
         <v>-2.111748324300711</v>
       </c>
       <c r="D284" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E284">
         <v>-0.784568413580331</v>
@@ -15557,7 +15563,7 @@
         <v>-0.7445684135803319</v>
       </c>
       <c r="D285" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E285">
         <v>-1.372636206025691</v>
@@ -15607,7 +15613,7 @@
         <v>-2.010677924453606</v>
       </c>
       <c r="D286" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E286">
         <v>-1.818641420829181</v>
@@ -15657,7 +15663,7 @@
         <v>-0.6891909916418824</v>
       </c>
       <c r="D287" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E287">
         <v>-1.494484740580184</v>
@@ -15693,7 +15699,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15707,7 +15713,7 @@
         <v>-2.104484740580184</v>
       </c>
       <c r="D288" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E288">
         <v>-0.8146446994669452</v>
@@ -15743,7 +15749,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15757,7 +15763,7 @@
         <v>-2.151344168564281</v>
       </c>
       <c r="D289" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E289">
         <v>-0.8146446994669452</v>
@@ -15793,7 +15799,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15807,7 +15813,7 @@
         <v>-0.774644699466946</v>
       </c>
       <c r="D290" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E290">
         <v>-1.426299571880434</v>
@@ -15843,7 +15849,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15857,7 +15863,7 @@
         <v>-2.046548724134889</v>
       </c>
       <c r="D291" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E291">
         <v>-1.975143003975854</v>
@@ -15893,7 +15899,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15907,7 +15913,7 @@
         <v>-0.7107964213114482</v>
       </c>
       <c r="D292" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E292">
         <v>-1.521656634662433</v>
@@ -15943,7 +15949,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -15957,7 +15963,7 @@
         <v>-2.131656634662433</v>
       </c>
       <c r="D293" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E293">
         <v>-0.8352123137375358</v>
@@ -15993,7 +15999,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16007,7 +16013,7 @@
         <v>-2.178421715792077</v>
       </c>
       <c r="D294" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E294">
         <v>-0.8352123137375358</v>
@@ -16043,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16057,7 +16063,7 @@
         <v>-0.83197739486718</v>
       </c>
       <c r="D295" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E295">
         <v>-1.449320204366783</v>
@@ -16093,7 +16099,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16107,7 +16113,7 @@
         <v>-2.071078906292474</v>
       </c>
       <c r="D296" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E296">
         <v>-2.025199555329629</v>
@@ -16143,7 +16149,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16157,7 +16163,7 @@
         <v>-2.134267548868247</v>
       </c>
       <c r="D297" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E297">
         <v>-0.8371886307405481</v>
@@ -16207,7 +16213,7 @@
         <v>-2.181023564323565</v>
       </c>
       <c r="D298" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E298">
         <v>-0.8371886307405481</v>
@@ -16257,7 +16263,7 @@
         <v>-2.073435981617167</v>
       </c>
       <c r="D299" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E299">
         <v>-1.89126418253631</v>
@@ -16307,7 +16313,7 @@
         <v>-2.159710406445646</v>
       </c>
       <c r="D300" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E300">
         <v>-0.856447460434552</v>
@@ -16343,7 +16349,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16357,7 +16363,7 @@
         <v>-2.206378078645488</v>
       </c>
       <c r="D301" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E301">
         <v>-0.856447460434552</v>
@@ -16393,7 +16399,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16407,7 +16413,7 @@
         <v>-2.096405228041208</v>
       </c>
       <c r="D302" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E302">
         <v>-1.476441427235503</v>
@@ -16443,7 +16449,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16457,7 +16463,7 @@
         <v>-2.15897721946909</v>
       </c>
       <c r="D303" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E303">
         <v>-0.8558924786259086</v>
@@ -16493,7 +16499,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16507,7 +16513,7 @@
         <v>-2.205647437457045</v>
       </c>
       <c r="D304" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E304">
         <v>-0.8558924786259086</v>
@@ -16543,7 +16549,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16557,7 +16563,7 @@
         <v>-2.095743323131817</v>
       </c>
       <c r="D305" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E305">
         <v>-1.475871170698182</v>
@@ -16593,7 +16599,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16607,7 +16613,7 @@
         <v>-0.1977199794301434</v>
       </c>
       <c r="D306" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E306">
         <v>0.5315870882768845</v>
@@ -16643,7 +16649,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16657,7 +16663,7 @@
         <v>-0.1653191551969262</v>
       </c>
       <c r="D307" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E307">
         <v>0.5568424835917494</v>
@@ -16693,7 +16699,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16707,7 +16713,7 @@
         <v>-0.1418631150528316</v>
       </c>
       <c r="D308" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E308">
         <v>0.5751257087991237</v>
@@ -16743,7 +16749,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16757,7 +16763,7 @@
         <v>-0.1263472268305499</v>
       </c>
       <c r="D309" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E309">
         <v>0.5872198422043242</v>
@@ -16793,7 +16799,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16807,7 +16813,7 @@
         <v>-0.08054411478897006</v>
       </c>
       <c r="D310" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E310">
         <v>0.6229218877120197</v>
@@ -16843,7 +16849,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -16857,7 +16863,7 @@
         <v>-0.0483732078109167</v>
       </c>
       <c r="D311" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E311">
         <v>0.6479980699572705</v>
@@ -16893,7 +16899,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -16907,7 +16913,7 @@
         <v>-0.0426775957224228</v>
       </c>
       <c r="D312" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E312">
         <v>0.6524376155015337</v>
@@ -16943,7 +16949,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -16957,7 +16963,7 @@
         <v>-0.002260839261968961</v>
       </c>
       <c r="D313" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E313">
         <v>0.6839411709174765</v>
@@ -16993,7 +16999,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17007,7 +17013,7 @@
         <v>0.03943267924280081</v>
       </c>
       <c r="D314" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E314">
         <v>0.6803878223669297</v>
@@ -17043,7 +17049,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17057,7 +17063,7 @@
         <v>0.05500064350064493</v>
       </c>
       <c r="D315" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E315">
         <v>0.6927001287001295</v>
@@ -17093,7 +17099,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17107,7 +17113,7 @@
         <v>0.07574238655207255</v>
       </c>
       <c r="D316" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E316">
         <v>0.7091042448776848</v>
@@ -17143,7 +17149,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17157,7 +17163,7 @@
         <v>0.08618633115302332</v>
       </c>
       <c r="D317" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E317">
         <v>0.7173640946001099</v>
@@ -17193,7 +17199,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17207,7 +17213,7 @@
         <v>0.07952257316260702</v>
       </c>
       <c r="D318" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E318">
         <v>0.7120938981666245</v>
@@ -17243,7 +17249,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17257,7 +17263,7 @@
         <v>0.081678859116463</v>
       </c>
       <c r="D319" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E319">
         <v>0.7137992497955294</v>
@@ -17293,7 +17299,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17307,7 +17313,7 @@
         <v>0.06474641494014977</v>
       </c>
       <c r="D320" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E320">
         <v>0.7004078110553276</v>
@@ -17343,7 +17349,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17393,7 +17399,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17407,7 +17413,7 @@
         <v>1.960909376633722</v>
       </c>
       <c r="D322" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E322">
         <v>2.138929585003361</v>
@@ -17443,7 +17449,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17457,7 +17463,7 @@
         <v>1.947964403173783</v>
       </c>
       <c r="D323" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E323">
         <v>2.147208583938033</v>
@@ -17493,7 +17499,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17507,7 +17513,7 @@
         <v>1.932043342863845</v>
       </c>
       <c r="D324" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E324">
         <v>2.122917095879669</v>
@@ -17543,7 +17549,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17557,7 +17563,7 @@
         <v>0.2594780143743354</v>
       </c>
       <c r="D325" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E325">
         <v>0.7830777081829752</v>
@@ -17593,7 +17599,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17607,7 +17613,7 @@
         <v>1.278216256083103</v>
       </c>
       <c r="D326" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E326">
         <v>1.062585376937486</v>
@@ -17643,7 +17649,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17657,7 +17663,7 @@
         <v>0.2571117245679739</v>
       </c>
       <c r="D327" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E327">
         <v>0.7813753414158087</v>
@@ -17693,7 +17699,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17707,7 +17713,7 @@
         <v>1.276326628971548</v>
       </c>
       <c r="D328" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E328">
         <v>1.021375341415808</v>
@@ -17743,7 +17749,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17757,7 +17763,7 @@
         <v>0.2547431471759269</v>
       </c>
       <c r="D329" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E329">
         <v>0.7796713289035446</v>
@@ -17793,7 +17799,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17807,7 +17813,7 @@
         <v>1.274435175082935</v>
       </c>
       <c r="D330" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E330">
         <v>1.052874615614509</v>
@@ -17843,7 +17849,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17857,7 +17863,7 @@
         <v>0.2470149029115583</v>
       </c>
       <c r="D331" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E331">
         <v>0.7741114409435672</v>
@@ -17893,7 +17899,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17907,7 +17913,7 @@
         <v>1.26826369944736</v>
       </c>
       <c r="D332" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E332">
         <v>1.034111440943567</v>
@@ -17943,7 +17949,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -17957,7 +17963,7 @@
         <v>0.2526232548771112</v>
       </c>
       <c r="D333" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E333">
         <v>0.7686098184274901</v>
@@ -17993,7 +17999,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18007,7 +18013,7 @@
         <v>0.239367647614211</v>
       </c>
       <c r="D334" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E334">
         <v>0.7686098184274901</v>
@@ -18043,7 +18049,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18057,7 +18063,7 @@
         <v>1.262156898454514</v>
       </c>
       <c r="D335" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E335">
         <v>1.031923720243215</v>
@@ -18093,7 +18099,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18107,7 +18113,7 @@
         <v>0.2409427190185853</v>
       </c>
       <c r="D336" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E336">
         <v>0.7599575696433969</v>
@@ -18143,7 +18149,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18157,7 +18163,7 @@
         <v>0.2273410218043215</v>
       </c>
       <c r="D337" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E337">
         <v>0.7599575696433969</v>
@@ -18193,7 +18199,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18207,7 +18213,7 @@
         <v>1.252552902304171</v>
       </c>
       <c r="D338" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E338">
         <v>0.9967584182505289</v>
@@ -18243,7 +18249,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18257,7 +18263,7 @@
         <v>0.2269256946216702</v>
       </c>
       <c r="D339" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E339">
         <v>0.7495745886086449</v>
@@ -18293,7 +18299,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18307,7 +18313,7 @@
         <v>0.2129086781660163</v>
       </c>
       <c r="D340" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E340">
         <v>0.7495745886086449</v>
@@ -18343,7 +18349,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18357,7 +18363,7 @@
         <v>0.2121775147285025</v>
       </c>
       <c r="D341" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E341">
         <v>0.7386500109100023</v>
@@ -18393,7 +18399,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18407,7 +18413,7 @@
         <v>0.1977235151649031</v>
       </c>
       <c r="D342" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E342">
         <v>0.7386500109100023</v>
@@ -18443,7 +18449,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18457,7 +18463,7 @@
         <v>0.199326851658896</v>
       </c>
       <c r="D343" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E343">
         <v>0.7291310012288121</v>
@@ -18493,7 +18499,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18507,7 +18513,7 @@
         <v>0.1844920917080488</v>
       </c>
       <c r="D344" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E344">
         <v>0.7291310012288121</v>
@@ -18543,7 +18549,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18557,7 +18563,7 @@
         <v>0.1896647385133041</v>
       </c>
       <c r="D345" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E345">
         <v>0.7219738803802256</v>
@@ -18593,7 +18599,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18607,7 +18613,7 @@
         <v>0.1745436937285134</v>
       </c>
       <c r="D346" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E346">
         <v>0.7219738803802256</v>
@@ -18643,7 +18649,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18657,7 +18663,7 @@
         <v>0.1786481289410795</v>
       </c>
       <c r="D347" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E347">
         <v>0.7138134288452445</v>
@@ -18693,7 +18699,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18707,7 +18713,7 @@
         <v>0.1666907242521811</v>
       </c>
       <c r="D348" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E348">
         <v>0.7049560920386531</v>
@@ -18743,7 +18749,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18757,7 +18763,7 @@
         <v>0.1508900298653248</v>
       </c>
       <c r="D349" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E349">
         <v>0.693251873974315</v>
@@ -18793,7 +18799,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18807,7 +18813,7 @@
         <v>0.1352367892059676</v>
       </c>
       <c r="D350" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E350">
         <v>0.6816568808933097</v>
@@ -18843,7 +18849,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18857,7 +18863,7 @@
         <v>0.1201773280539471</v>
       </c>
       <c r="D351" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E351">
         <v>0.6933866727498734</v>
@@ -18893,7 +18899,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18907,7 +18913,7 @@
         <v>0.1037985724993549</v>
       </c>
       <c r="D352" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E352">
         <v>0.681618233573611</v>
@@ -18943,7 +18949,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -18957,7 +18963,7 @@
         <v>0.09387182781882397</v>
       </c>
       <c r="D353" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E353">
         <v>0.6744856836920441</v>
@@ -18993,7 +18999,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19007,7 +19013,7 @@
         <v>0.0865999587373627</v>
       </c>
       <c r="D354" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E354">
         <v>0.669260711092772</v>
@@ -19043,7 +19049,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19057,7 +19063,7 @@
         <v>0.07648563427817057</v>
       </c>
       <c r="D355" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E355">
         <v>0.6619933816665378</v>
@@ -19093,7 +19099,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19107,7 +19113,7 @@
         <v>0.1318670093468981</v>
       </c>
       <c r="D356" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E356">
         <v>0.6619933816665378</v>
@@ -19143,7 +19149,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19157,7 +19163,7 @@
         <v>0.05684614970067581</v>
       </c>
       <c r="D357" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E357">
         <v>0.6478820483034489</v>
@@ -19193,7 +19199,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19207,7 +19213,7 @@
         <v>0.1120820471058663</v>
       </c>
       <c r="D358" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E358">
         <v>0.6478820483034489</v>
@@ -19243,7 +19249,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19257,7 +19263,7 @@
         <v>0.104345747039986</v>
       </c>
       <c r="D359" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E359">
         <v>0.6353846079319303</v>
@@ -19293,7 +19299,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19307,7 +19313,7 @@
         <v>0.09455986266744842</v>
       </c>
       <c r="D360" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E360">
         <v>0.6353846079319303</v>
@@ -19343,7 +19349,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19357,7 +19363,7 @@
         <v>0.09223443486348204</v>
       </c>
       <c r="D361" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E361">
         <v>0.6266174640429685</v>
@@ -19393,7 +19399,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19407,7 +19413,7 @@
         <v>0.08226778463756368</v>
       </c>
       <c r="D362" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E362">
         <v>0.6266174640429685</v>
@@ -19443,7 +19449,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19457,7 +19463,7 @@
         <v>0.08340490038981674</v>
       </c>
       <c r="D363" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E363">
         <v>0.6202259353568076</v>
@@ -19493,7 +19499,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19507,7 +19513,7 @@
         <v>0.07330646606727642</v>
       </c>
       <c r="D364" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E364">
         <v>0.6202259353568076</v>
@@ -19543,7 +19549,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19557,7 +19563,7 @@
         <v>0.07295411923666117</v>
       </c>
       <c r="D365" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E365">
         <v>0.612660817656389</v>
@@ -19593,7 +19599,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19607,7 +19613,7 @@
         <v>0.08535626663036044</v>
       </c>
       <c r="D366" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E366">
         <v>0.6088483639401687</v>
@@ -19643,7 +19649,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19657,7 +19663,7 @@
         <v>0.08337683007148078</v>
       </c>
       <c r="D367" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E367">
         <v>0.6075510305198217</v>
@@ -19693,7 +19699,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19707,7 +19713,7 @@
         <v>0.07990431184045077</v>
       </c>
       <c r="D368" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E368">
         <v>0.6052751233008362</v>
@@ -19743,7 +19749,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19757,7 +19763,7 @@
         <v>0.07628301150993844</v>
       </c>
       <c r="D369" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E369">
         <v>0.602901703489622</v>
@@ -19793,7 +19799,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19807,7 +19813,7 @@
         <v>0.07542641148821705</v>
       </c>
       <c r="D370" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E370">
         <v>0.6023402832051152</v>
@@ -19843,7 +19849,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19857,7 +19863,7 @@
         <v>0.1032857601349302</v>
       </c>
       <c r="D371" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E371">
         <v>0.6912581248872549</v>
@@ -19893,7 +19899,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19907,7 +19913,7 @@
         <v>0.1032494207491959</v>
       </c>
       <c r="D372" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E372">
         <v>0.6912346254178132</v>
@@ -19943,7 +19949,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -19957,7 +19963,7 @@
         <v>0.1066794748126041</v>
       </c>
       <c r="D373" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E373">
         <v>0.6912346254178132</v>
@@ -19993,7 +19999,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20007,7 +20013,7 @@
         <v>0.1027485095490785</v>
       </c>
       <c r="D374" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E374">
         <v>0.6909107028417374</v>
@@ -20043,7 +20049,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20057,7 +20063,7 @@
         <v>0.2672388330248614</v>
       </c>
       <c r="D375" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E375">
         <v>0.6512870381223137</v>
@@ -20093,7 +20099,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20107,7 +20113,7 @@
         <v>1.002091352902854</v>
       </c>
       <c r="D376" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E376">
         <v>0.6273460301711169</v>
@@ -20143,7 +20149,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20157,7 +20163,7 @@
         <v>0.2741430547802919</v>
       </c>
       <c r="D377" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E377">
         <v>0.6566021929657799</v>
@@ -20193,7 +20199,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20207,7 +20213,7 @@
         <v>1.008173643496924</v>
       </c>
       <c r="D378" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E378">
         <v>0.6385919967269027</v>
@@ -20243,7 +20249,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20257,7 +20263,7 @@
         <v>1.008413016850501</v>
       </c>
       <c r="D379" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E379">
         <v>0.6476121959680365</v>
@@ -20293,7 +20299,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20307,7 +20313,7 @@
         <v>1.0141677914568</v>
       </c>
       <c r="D380" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E380">
         <v>0.6530040568604247</v>
@@ -20343,7 +20349,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20357,7 +20363,7 @@
         <v>1.021395485086037</v>
       </c>
       <c r="D381" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E381">
         <v>0.6597759499905214</v>
@@ -20393,7 +20399,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20407,7 +20413,7 @@
         <v>0.337619285136195</v>
       </c>
       <c r="D382" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E382">
         <v>0.6834894621989671</v>
@@ -20457,7 +20463,7 @@
         <v>1.028457881859448</v>
       </c>
       <c r="D383" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E383">
         <v>0.6663929703908342</v>
@@ -20507,7 +20513,7 @@
         <v>0.3407332921319595</v>
       </c>
       <c r="D384" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E384">
         <v>0.686217663018265</v>
@@ -20543,7 +20549,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20557,7 +20563,7 @@
         <v>1.031516773687146</v>
       </c>
       <c r="D385" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E385">
         <v>0.6692589591302986</v>
@@ -20593,7 +20599,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20607,7 +20613,7 @@
         <v>0.3675382538855252</v>
       </c>
       <c r="D386" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E386">
         <v>0.6963061351309554</v>
@@ -20643,7 +20649,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20657,7 +20663,7 @@
         <v>0.3522484168666464</v>
       </c>
       <c r="D387" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E387">
         <v>0.6963061351309554</v>
@@ -20693,7 +20699,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20707,7 +20713,7 @@
         <v>1.042828090904405</v>
       </c>
       <c r="D388" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E388">
         <v>0.6798569500365592</v>
@@ -20743,7 +20749,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20757,7 +20763,7 @@
         <v>0.3762667112083611</v>
       </c>
       <c r="D389" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E389">
         <v>0.7040214679431049</v>
@@ -20793,7 +20799,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20807,7 +20813,7 @@
         <v>0.3610548068441501</v>
       </c>
       <c r="D390" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E390">
         <v>0.7040214679431049</v>
@@ -20843,7 +20849,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20857,7 +20863,7 @@
         <v>1.051478615572572</v>
       </c>
       <c r="D391" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E391">
         <v>0.6879619461220496</v>
@@ -20893,7 +20899,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20907,7 +20913,7 @@
         <v>0.38797225747824</v>
       </c>
       <c r="D392" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E392">
         <v>0.7586166008276201</v>
@@ -20943,7 +20949,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -20957,7 +20963,7 @@
         <v>0.3728648669200105</v>
       </c>
       <c r="D393" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E393">
         <v>0.7586166008276201</v>
@@ -20993,7 +20999,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21007,7 +21013,7 @@
         <v>1.06307964803647</v>
       </c>
       <c r="D394" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E394">
         <v>0.6988313819440801</v>
@@ -21043,7 +21049,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21057,7 +21063,7 @@
         <v>0.4038111409481839</v>
       </c>
       <c r="D395" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E395">
         <v>0.7736069726831025</v>
@@ -21093,7 +21099,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21107,7 +21113,7 @@
         <v>0.3888451689923644</v>
       </c>
       <c r="D396" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E396">
         <v>0.7736069726831025</v>
@@ -21143,7 +21149,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21157,7 +21163,7 @@
         <v>1.078777112904004</v>
       </c>
       <c r="D397" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E397">
         <v>0.7135389165947423</v>
@@ -21193,7 +21199,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21207,7 +21213,7 @@
         <v>0.421605003019891</v>
       </c>
       <c r="D398" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E398">
         <v>0.7904475921438254</v>
@@ -21243,7 +21249,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21257,7 +21263,7 @@
         <v>0.4067979048325689</v>
       </c>
       <c r="D399" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E399">
         <v>0.7904475921438254</v>
@@ -21293,7 +21299,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21307,7 +21313,7 @@
         <v>1.096412101207214</v>
       </c>
       <c r="D400" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E400">
         <v>0.7300617885184704</v>
@@ -21343,7 +21349,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21357,7 +21363,7 @@
         <v>0.4388301519378184</v>
       </c>
       <c r="D401" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E401">
         <v>0.8067499652268637</v>
@@ -21393,7 +21399,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21407,7 +21413,7 @@
         <v>0.4241768497229779</v>
       </c>
       <c r="D402" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E402">
         <v>0.8067499652268637</v>
@@ -21443,7 +21449,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21457,7 +21463,7 @@
         <v>1.113483454152659</v>
       </c>
       <c r="D403" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E403">
         <v>0.7460565696565458</v>
@@ -21493,7 +21499,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21507,7 +21513,7 @@
         <v>3.151956422625536</v>
       </c>
       <c r="D404" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E404">
         <v>2.557425288074153</v>
@@ -21543,7 +21549,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21557,7 +21563,7 @@
         <v>3.0302870572645</v>
       </c>
       <c r="D405" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E405">
         <v>2.557425288074153</v>
@@ -21593,7 +21599,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21607,7 +21613,7 @@
         <v>3.126010595645193</v>
       </c>
       <c r="D406" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E406">
         <v>2.97243338415726</v>
@@ -21643,7 +21649,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21657,7 +21663,7 @@
         <v>3.095533634113468</v>
       </c>
       <c r="D407" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E407">
         <v>2.97243338415726</v>
@@ -21693,7 +21699,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21707,7 +21713,7 @@
         <v>3.185945174511515</v>
       </c>
       <c r="D408" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E408">
         <v>2.586594739319583</v>
@@ -21743,7 +21749,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21793,7 +21799,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21843,7 +21849,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -21857,7 +21863,7 @@
         <v>3.22654267572782</v>
       </c>
       <c r="D411" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E411">
         <v>2.621435878423129</v>
@@ -21893,7 +21899,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -21943,7 +21949,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -21993,7 +21999,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22007,7 +22013,7 @@
         <v>3.259685052120739</v>
       </c>
       <c r="D414" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E414">
         <v>2.649878962640932</v>
@@ -22043,7 +22049,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22093,7 +22099,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22143,7 +22149,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22157,7 +22163,7 @@
         <v>3.290901329475496</v>
       </c>
       <c r="D417" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E417">
         <v>2.729219817527112</v>
@@ -22193,7 +22199,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22243,7 +22249,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22257,7 +22263,7 @@
         <v>3.324668655156648</v>
       </c>
       <c r="D419" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E419">
         <v>2.758703228756178</v>
@@ -22293,7 +22299,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22343,7 +22349,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22357,7 +22363,7 @@
         <v>3.997489231461685</v>
       </c>
       <c r="D421" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E421">
         <v>4.120993158546191</v>
@@ -22393,7 +22399,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22407,7 +22413,7 @@
         <v>3.986341271722335</v>
       </c>
       <c r="D422" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E422">
         <v>4.110505275370355</v>
@@ -22443,7 +22449,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22457,7 +22463,7 @@
         <v>3.963562911043303</v>
       </c>
       <c r="D423" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E423">
         <v>4.089075633415739</v>
@@ -22493,7 +22499,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22507,7 +22513,7 @@
         <v>3.944710231985321</v>
       </c>
       <c r="D424" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E424">
         <v>4.071339231407243</v>
@@ -22543,7 +22549,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22557,7 +22563,7 @@
         <v>3.924958557318009</v>
       </c>
       <c r="D425" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E425">
         <v>4.052757063792601</v>
@@ -22593,7 +22599,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22607,7 +22613,7 @@
         <v>3.903529915296924</v>
       </c>
       <c r="D426" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E426">
         <v>4.032597222943817</v>
@@ -22643,7 +22649,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22657,7 +22663,7 @@
         <v>3.886527377365554</v>
       </c>
       <c r="D427" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E427">
         <v>4.016601414232067</v>
@@ -22693,7 +22699,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22707,7 +22713,7 @@
         <v>3.873496712167727</v>
       </c>
       <c r="D428" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E428">
         <v>4.004342301578848</v>
@@ -22743,7 +22749,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22757,7 +22763,7 @@
         <v>3.861649782293752</v>
       </c>
       <c r="D429" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E429">
         <v>3.993196834657938</v>
@@ -22793,7 +22799,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22807,7 +22813,7 @@
         <v>3.834878726120355</v>
       </c>
       <c r="D430" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E430">
         <v>3.968010906810598</v>
@@ -22843,7 +22849,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -22857,7 +22863,7 @@
         <v>3.808598117223633</v>
       </c>
       <c r="D431" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E431">
         <v>3.943286386598549</v>
@@ -22893,7 +22899,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22907,7 +22913,7 @@
         <v>3.800233949670756</v>
       </c>
       <c r="D432" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E432">
         <v>3.935417465808672</v>
@@ -22943,7 +22949,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -22957,7 +22963,7 @@
         <v>3.798188965274105</v>
       </c>
       <c r="D433" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E433">
         <v>3.933493566014454</v>
@@ -22993,7 +22999,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23007,7 +23013,7 @@
         <v>3.788920893245179</v>
       </c>
       <c r="D434" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E434">
         <v>3.924774261408294</v>
@@ -23043,7 +23049,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23057,7 +23063,7 @@
         <v>3.79888341910942</v>
       </c>
       <c r="D435" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E435">
         <v>3.934146900872678</v>
@@ -23093,7 +23099,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23107,7 +23113,7 @@
         <v>3.829553568848083</v>
       </c>
       <c r="D436" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E436">
         <v>3.963001054903131</v>
@@ -23143,7 +23149,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23157,7 +23163,7 @@
         <v>3.855665816250932</v>
       </c>
       <c r="D437" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E437">
         <v>3.987567182393969</v>
@@ -23193,7 +23199,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23207,7 +23213,7 @@
         <v>3.855953228285221</v>
       </c>
       <c r="D438" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E438">
         <v>3.987837576610439</v>
@@ -23243,7 +23249,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23257,7 +23263,7 @@
         <v>3.861717839622725</v>
       </c>
       <c r="D439" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E439">
         <v>3.993260862276643</v>
@@ -23293,7 +23299,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23307,7 +23313,7 @@
         <v>3.86639892628536</v>
       </c>
       <c r="D440" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E440">
         <v>3.997664779334253</v>
@@ -23343,7 +23349,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23357,7 +23363,7 @@
         <v>3.846535379684417</v>
       </c>
       <c r="D441" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E441">
         <v>3.978977363782051</v>
@@ -23393,7 +23399,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23407,7 +23413,7 @@
         <v>3.87004024621212</v>
       </c>
       <c r="D442" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E442">
         <v>4.001090494791666</v>
@@ -23443,7 +23449,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23457,7 +23463,7 @@
         <v>3.886357305969927</v>
       </c>
       <c r="D443" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E443">
         <v>4.016441412853287</v>
@@ -23493,7 +23499,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23507,7 +23513,7 @@
         <v>3.903938192034373</v>
       </c>
       <c r="D444" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E444">
         <v>4.032981325400759</v>
@@ -23543,7 +23549,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23557,7 +23563,7 @@
         <v>3.961072830353248</v>
       </c>
       <c r="D445" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E445">
         <v>4.086732991713911</v>
@@ -23593,7 +23599,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23607,7 +23613,7 @@
         <v>3.981576852757343</v>
       </c>
       <c r="D446" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E446">
         <v>4.106022960159869</v>
@@ -23643,7 +23649,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23657,7 +23663,7 @@
         <v>3.971450680589221</v>
       </c>
       <c r="D447" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E447">
         <v>4.096496363975386</v>
@@ -23693,7 +23699,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23707,7 +23713,7 @@
         <v>3.968816281770093</v>
       </c>
       <c r="D448" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E448">
         <v>4.094017949296864</v>
@@ -23743,7 +23749,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23757,7 +23763,7 @@
         <v>3.926789933050578</v>
       </c>
       <c r="D449" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E449">
         <v>4.054480002804163</v>
@@ -23793,7 +23799,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23807,7 +23813,7 @@
         <v>3.825723707829902</v>
       </c>
       <c r="D450" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E450">
         <v>3.959397961971553</v>
@@ -23843,7 +23849,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23857,7 +23863,7 @@
         <v>3.746022583750348</v>
       </c>
       <c r="D451" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E451">
         <v>3.88441598339671</v>
@@ -23893,7 +23899,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23907,7 +23913,7 @@
         <v>3.686827463477967</v>
       </c>
       <c r="D452" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E452">
         <v>3.828725837350983</v>
@@ -23943,7 +23949,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -23957,7 +23963,7 @@
         <v>3.536490631366341</v>
       </c>
       <c r="D453" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E453">
         <v>3.687290528193334</v>
@@ -23993,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24007,7 +24013,7 @@
         <v>3.478129127613399</v>
       </c>
       <c r="D454" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E454">
         <v>3.632384639794185</v>
@@ -24043,7 +24049,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24057,7 +24063,7 @@
         <v>3.446322550887229</v>
       </c>
       <c r="D455" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E455">
         <v>3.602461347216275</v>
@@ -24093,7 +24099,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24107,7 +24113,7 @@
         <v>3.437244026062129</v>
       </c>
       <c r="D456" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E456">
         <v>3.59392036662424</v>
@@ -24143,7 +24149,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24157,7 +24163,7 @@
         <v>3.495394814734395</v>
       </c>
       <c r="D457" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E457">
         <v>3.648628016493543</v>
@@ -24193,7 +24199,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24207,7 +24213,7 @@
         <v>3.479433369341057</v>
       </c>
       <c r="D458" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E458">
         <v>3.633611656682705</v>
@@ -24243,7 +24249,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24257,7 +24263,7 @@
         <v>3.450931319109172</v>
       </c>
       <c r="D459" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E459">
         <v>3.606797227846129</v>
@@ -24293,7 +24299,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24307,7 +24313,7 @@
         <v>3.40927622228758</v>
       </c>
       <c r="D460" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E460">
         <v>3.567608551231079</v>
@@ -24343,7 +24349,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24357,7 +24363,7 @@
         <v>3.398669636469118</v>
       </c>
       <c r="D461" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E461">
         <v>3.557629986941341</v>
@@ -24393,7 +24399,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24407,7 +24413,7 @@
         <v>3.386651569627924</v>
       </c>
       <c r="D462" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E462">
         <v>3.546323516163113</v>
@@ -24443,7 +24449,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24457,7 +24463,7 @@
         <v>3.393731929090075</v>
       </c>
       <c r="D463" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E463">
         <v>3.552984643815005</v>
@@ -24493,7 +24499,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24507,7 +24513,7 @@
         <v>3.379912288774229</v>
       </c>
       <c r="D464" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E464">
         <v>3.539983271675756</v>
@@ -24543,7 +24549,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24557,7 +24563,7 @@
         <v>3.350459894428295</v>
       </c>
       <c r="D465" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E465">
         <v>3.512274769100304</v>
@@ -24593,7 +24599,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24607,7 +24613,7 @@
         <v>3.29749980927481</v>
       </c>
       <c r="D466" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E466">
         <v>3.462450478462486</v>
@@ -24643,7 +24649,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24657,7 +24663,7 @@
         <v>3.226019469262567</v>
       </c>
       <c r="D467" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E467">
         <v>3.395202527003599</v>
@@ -24693,7 +24699,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24707,7 +24713,7 @@
         <v>3.085589532934493</v>
       </c>
       <c r="D468" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E468">
         <v>3.263087521116003</v>
@@ -24743,7 +24749,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24757,7 +24763,7 @@
         <v>3.014088527917016</v>
       </c>
       <c r="D469" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E469">
         <v>3.195820128237719</v>
@@ -24793,7 +24799,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24807,7 +24813,7 @@
         <v>2.958985295983108</v>
       </c>
       <c r="D470" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E470">
         <v>3.143979587668319</v>
@@ -24843,7 +24849,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24857,7 +24863,7 @@
         <v>2.931899483775353</v>
       </c>
       <c r="D471" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E471">
         <v>3.118497540657076</v>
@@ -24893,7 +24899,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24907,7 +24913,7 @@
         <v>2.861907606499231</v>
       </c>
       <c r="D472" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E472">
         <v>3.052649919272303</v>
@@ -24943,7 +24949,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -24951,49 +24957,99 @@
         <v>0</v>
       </c>
       <c r="B473" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C473">
-        <v>2.801763208907002</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D473" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E473">
-        <v>2.996066703116456</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F473">
         <v>-1</v>
       </c>
       <c r="G473">
-        <v>0.004298236791092998</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H473">
-        <v>0.004403933296883544</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I473">
-        <v>-0.1943034942094539</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J473">
         <v>0.4922610467717091</v>
       </c>
       <c r="K473">
+        <v>1.27</v>
+      </c>
+      <c r="L473">
+        <v>3.15</v>
+      </c>
+      <c r="M473">
+        <v>1.19</v>
+      </c>
+      <c r="N473">
+        <v>2.63</v>
+      </c>
+      <c r="O473">
+        <v>1</v>
+      </c>
+      <c r="P473" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="474" spans="1:16">
+      <c r="A474" s="1">
+        <v>1</v>
+      </c>
+      <c r="B474" t="s">
+        <v>54</v>
+      </c>
+      <c r="C474">
+        <v>2.801763208907002</v>
+      </c>
+      <c r="D474" t="s">
+        <v>126</v>
+      </c>
+      <c r="E474">
+        <v>2.996066703116456</v>
+      </c>
+      <c r="F474">
+        <v>-1</v>
+      </c>
+      <c r="G474">
+        <v>0.004298236791092998</v>
+      </c>
+      <c r="H474">
+        <v>0.004403933296883544</v>
+      </c>
+      <c r="I474">
+        <v>-0.1943034942094539</v>
+      </c>
+      <c r="J474">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K474">
         <v>1.52</v>
       </c>
-      <c r="L473">
+      <c r="L474">
         <v>3.55</v>
       </c>
-      <c r="M473">
+      <c r="M474">
         <v>1.43</v>
       </c>
-      <c r="N473">
+      <c r="N474">
         <v>3.7</v>
       </c>
-      <c r="O473">
-        <v>1</v>
-      </c>
-      <c r="P473" t="s">
-        <v>324</v>
+      <c r="O474">
+        <v>1</v>
+      </c>
+      <c r="P474" t="s">
+        <v>326</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="326">
   <si>
     <t>trade_time</t>
   </si>
@@ -1349,7 +1349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P471"/>
+  <dimension ref="A1:P472"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24754,43 +24754,43 @@
         <v>0</v>
       </c>
       <c r="B469" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C469">
-        <v>2.861907606499231</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D469" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E469">
-        <v>3.052649919272303</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F469">
         <v>-1</v>
       </c>
       <c r="G469">
-        <v>0.004238092393500768</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H469">
-        <v>0.004347350080727697</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I469">
-        <v>-0.1907423127730721</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J469">
         <v>0.4526923641452424</v>
       </c>
       <c r="K469">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L469">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M469">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="N469">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="O469">
         <v>1</v>
@@ -24801,101 +24801,151 @@
     </row>
     <row r="470" spans="1:16">
       <c r="A470" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B470" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C470">
-        <v>2.524828470599929</v>
+        <v>2.861907606499231</v>
       </c>
       <c r="D470" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E470">
-        <v>2.044209354341666</v>
+        <v>3.052649919272303</v>
       </c>
       <c r="F470">
         <v>-1</v>
       </c>
       <c r="G470">
-        <v>0.003775171529400071</v>
+        <v>0.004238092393500768</v>
       </c>
       <c r="H470">
-        <v>0.003215790645658334</v>
+        <v>0.004347350080727697</v>
       </c>
       <c r="I470">
-        <v>0.4806191162582629</v>
+        <v>-0.1907423127730721</v>
       </c>
       <c r="J470">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K470">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L470">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M470">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="N470">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="O470">
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="471" spans="1:16">
       <c r="A471" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B471" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C471">
-        <v>2.801763208907002</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D471" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E471">
-        <v>2.996066703116456</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F471">
         <v>-1</v>
       </c>
       <c r="G471">
-        <v>0.004298236791092998</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H471">
-        <v>0.004403933296883544</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I471">
-        <v>-0.1943034942094539</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J471">
         <v>0.4922610467717091</v>
       </c>
       <c r="K471">
+        <v>1.27</v>
+      </c>
+      <c r="L471">
+        <v>3.15</v>
+      </c>
+      <c r="M471">
+        <v>1.19</v>
+      </c>
+      <c r="N471">
+        <v>2.63</v>
+      </c>
+      <c r="O471">
+        <v>1</v>
+      </c>
+      <c r="P471" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="472" spans="1:16">
+      <c r="A472" s="1">
+        <v>1</v>
+      </c>
+      <c r="B472" t="s">
+        <v>54</v>
+      </c>
+      <c r="C472">
+        <v>2.801763208907002</v>
+      </c>
+      <c r="D472" t="s">
+        <v>125</v>
+      </c>
+      <c r="E472">
+        <v>2.996066703116456</v>
+      </c>
+      <c r="F472">
+        <v>-1</v>
+      </c>
+      <c r="G472">
+        <v>0.004298236791092998</v>
+      </c>
+      <c r="H472">
+        <v>0.004403933296883544</v>
+      </c>
+      <c r="I472">
+        <v>-0.1943034942094539</v>
+      </c>
+      <c r="J472">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K472">
         <v>1.52</v>
       </c>
-      <c r="L471">
+      <c r="L472">
         <v>3.55</v>
       </c>
-      <c r="M471">
+      <c r="M472">
         <v>1.43</v>
       </c>
-      <c r="N471">
+      <c r="N472">
         <v>3.7</v>
       </c>
-      <c r="O471">
-        <v>1</v>
-      </c>
-      <c r="P471" t="s">
+      <c r="O472">
+        <v>1</v>
+      </c>
+      <c r="P472" t="s">
         <v>325</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="327">
   <si>
     <t>trade_time</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>2021-09-28</t>
+  </si>
+  <si>
+    <t>2021-09-24</t>
   </si>
   <si>
     <t>2021-04-15</t>
@@ -1446,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1496,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1546,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1596,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1646,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1696,7 +1699,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1746,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1796,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1846,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1896,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1946,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1996,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2046,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2096,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2146,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2196,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2246,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2296,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2346,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2396,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2446,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2496,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2546,7 +2549,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2596,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2646,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2696,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2746,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2796,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2846,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2896,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2946,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2996,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3046,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3096,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3146,7 +3149,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3196,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3246,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3296,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3346,7 +3349,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3396,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3446,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3496,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3546,7 +3549,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3596,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3646,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3696,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3746,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3796,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3846,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3896,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3946,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3996,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4046,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4096,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4146,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4196,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4246,7 +4249,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4296,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4346,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4396,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4446,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4496,7 +4499,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4546,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4596,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4646,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4696,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4746,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4796,7 +4799,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4846,7 +4849,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4896,7 +4899,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4946,7 +4949,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4996,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5046,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5096,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5146,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5196,7 +5199,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5246,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5296,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5346,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5396,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5446,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5496,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5546,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5596,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5646,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5696,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5746,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5796,7 +5799,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5846,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5896,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5946,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5996,7 +5999,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6046,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6096,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6146,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6196,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6246,7 +6249,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6296,7 +6299,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6346,7 +6349,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6396,7 +6399,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6446,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6496,7 +6499,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6546,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6596,7 +6599,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6646,7 +6649,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6696,7 +6699,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6746,7 +6749,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6796,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6846,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6896,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6946,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6996,7 +6999,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7046,7 +7049,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7096,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7146,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7196,7 +7199,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7246,7 +7249,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7296,7 +7299,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7346,7 +7349,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7396,7 +7399,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7446,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7696,7 +7699,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7746,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7796,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7846,7 +7849,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7896,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7946,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7996,7 +7999,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8046,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8096,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8146,7 +8149,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8196,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8246,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8296,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8346,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8396,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8446,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8496,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8546,7 +8549,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8596,7 +8599,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8646,7 +8649,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8696,7 +8699,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8746,7 +8749,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8796,7 +8799,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8846,7 +8849,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8896,7 +8899,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8946,7 +8949,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8996,7 +8999,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9046,7 +9049,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9096,7 +9099,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9146,7 +9149,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9946,7 +9949,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9996,7 +9999,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10046,7 +10049,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10096,7 +10099,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10146,7 +10149,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10196,7 +10199,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10246,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10296,7 +10299,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10346,7 +10349,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10396,7 +10399,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10446,7 +10449,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10496,7 +10499,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10546,7 +10549,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10596,7 +10599,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10646,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10696,7 +10699,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10996,7 +10999,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11046,7 +11049,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11096,7 +11099,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11146,7 +11149,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11196,7 +11199,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11546,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11596,7 +11599,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11646,7 +11649,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11696,7 +11699,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11746,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11796,7 +11799,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11846,7 +11849,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11896,7 +11899,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11946,7 +11949,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11996,7 +11999,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12046,7 +12049,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12096,7 +12099,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12146,7 +12149,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12596,7 +12599,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12646,7 +12649,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12696,7 +12699,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12746,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12796,7 +12799,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12846,7 +12849,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12896,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13246,7 +13249,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13296,7 +13299,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13346,7 +13349,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13396,7 +13399,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13446,7 +13449,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13496,7 +13499,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13546,7 +13549,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13896,7 +13899,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13946,7 +13949,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13996,7 +13999,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14046,7 +14049,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14096,7 +14099,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14146,7 +14149,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14446,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14496,7 +14499,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14546,7 +14549,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14596,7 +14599,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14646,7 +14649,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14896,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14946,7 +14949,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14996,7 +14999,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15046,7 +15049,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15546,7 +15549,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15596,7 +15599,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15646,7 +15649,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15696,7 +15699,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15746,7 +15749,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15796,7 +15799,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15846,7 +15849,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15896,7 +15899,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15946,7 +15949,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -15996,7 +15999,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16196,7 +16199,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16246,7 +16249,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16296,7 +16299,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16346,7 +16349,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16396,7 +16399,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16446,7 +16449,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16496,7 +16499,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16546,7 +16549,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16596,7 +16599,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16646,7 +16649,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16696,7 +16699,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16746,7 +16749,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16796,7 +16799,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16846,7 +16849,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -16896,7 +16899,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -16946,7 +16949,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -16996,7 +16999,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17046,7 +17049,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17096,7 +17099,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17146,7 +17149,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17196,7 +17199,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17246,7 +17249,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17296,7 +17299,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17346,7 +17349,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17396,7 +17399,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17446,7 +17449,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17496,7 +17499,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17546,7 +17549,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17596,7 +17599,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17646,7 +17649,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17696,7 +17699,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17746,7 +17749,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17796,7 +17799,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17846,7 +17849,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17896,7 +17899,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17946,7 +17949,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -17996,7 +17999,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18046,7 +18049,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18096,7 +18099,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18146,7 +18149,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18196,7 +18199,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18246,7 +18249,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18296,7 +18299,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18346,7 +18349,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18396,7 +18399,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18446,7 +18449,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18496,7 +18499,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18546,7 +18549,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18596,7 +18599,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18646,7 +18649,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18696,7 +18699,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18746,7 +18749,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18796,7 +18799,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18846,7 +18849,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18896,7 +18899,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18946,7 +18949,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -18996,7 +18999,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19046,7 +19049,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19096,7 +19099,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19146,7 +19149,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19196,7 +19199,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19246,7 +19249,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19296,7 +19299,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19346,7 +19349,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19396,7 +19399,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19446,7 +19449,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19496,7 +19499,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19546,7 +19549,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19596,7 +19599,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19646,7 +19649,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19696,7 +19699,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19746,7 +19749,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19796,7 +19799,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19846,7 +19849,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19896,7 +19899,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20046,7 +20049,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20096,7 +20099,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20146,7 +20149,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20196,7 +20199,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20246,7 +20249,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20396,7 +20399,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20446,7 +20449,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20496,7 +20499,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20546,7 +20549,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20596,7 +20599,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20646,7 +20649,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20696,7 +20699,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20746,7 +20749,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20796,7 +20799,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20846,7 +20849,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20896,7 +20899,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20946,7 +20949,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -20996,7 +20999,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21046,7 +21049,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21096,7 +21099,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21146,7 +21149,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21196,7 +21199,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21246,7 +21249,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21296,7 +21299,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21346,7 +21349,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21396,7 +21399,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21446,7 +21449,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21496,7 +21499,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21546,7 +21549,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21596,7 +21599,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21646,7 +21649,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21696,7 +21699,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21746,7 +21749,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21796,7 +21799,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21846,7 +21849,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -21896,7 +21899,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -21946,7 +21949,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -21996,7 +21999,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22046,7 +22049,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22096,7 +22099,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22146,7 +22149,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22196,7 +22199,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22246,7 +22249,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22296,7 +22299,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22346,7 +22349,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22396,7 +22399,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22446,7 +22449,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22496,7 +22499,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22546,7 +22549,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22596,7 +22599,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22646,7 +22649,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22696,7 +22699,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22746,7 +22749,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22796,7 +22799,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22846,7 +22849,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -22896,7 +22899,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22946,7 +22949,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -22996,7 +22999,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23046,7 +23049,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23096,7 +23099,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23146,7 +23149,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23196,7 +23199,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23246,7 +23249,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23296,7 +23299,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23346,7 +23349,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23396,7 +23399,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23446,7 +23449,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23496,7 +23499,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23546,7 +23549,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23596,7 +23599,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23646,7 +23649,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23696,7 +23699,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23746,7 +23749,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23796,7 +23799,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23846,7 +23849,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23896,7 +23899,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23946,7 +23949,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -23996,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24046,7 +24049,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24096,7 +24099,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24146,7 +24149,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24196,7 +24199,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24246,7 +24249,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24296,7 +24299,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24346,7 +24349,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24396,7 +24399,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24446,7 +24449,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24496,7 +24499,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24546,7 +24549,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24596,7 +24599,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24646,7 +24649,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24696,7 +24699,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24710,10 +24713,10 @@
         <v>2.931899483775353</v>
       </c>
       <c r="D468" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E468">
-        <v>3.118497540657076</v>
+        <v>2.965965934539989</v>
       </c>
       <c r="F468">
         <v>-1</v>
@@ -24722,10 +24725,10 @@
         <v>0.004168100516224646</v>
       </c>
       <c r="H468">
-        <v>0.004281502459342924</v>
+        <v>0.004194034065460011</v>
       </c>
       <c r="I468">
-        <v>-0.1865980568817229</v>
+        <v>-0.03406645076463599</v>
       </c>
       <c r="J468">
         <v>0.4066450764635833</v>
@@ -24737,16 +24740,16 @@
         <v>3.55</v>
       </c>
       <c r="M468">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N468">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O468">
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24760,7 +24763,7 @@
         <v>2.575080697535542</v>
       </c>
       <c r="D469" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E469">
         <v>2.091296086667161</v>
@@ -24796,7 +24799,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24810,10 +24813,10 @@
         <v>2.861907606499231</v>
       </c>
       <c r="D470" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E470">
-        <v>3.052649919272303</v>
+        <v>2.896434530140684</v>
       </c>
       <c r="F470">
         <v>-1</v>
@@ -24822,10 +24825,10 @@
         <v>0.004238092393500768</v>
       </c>
       <c r="H470">
-        <v>0.004347350080727697</v>
+        <v>0.004263565469859316</v>
       </c>
       <c r="I470">
-        <v>-0.1907423127730721</v>
+        <v>-0.03452692364145271</v>
       </c>
       <c r="J470">
         <v>0.4526923641452424</v>
@@ -24837,16 +24840,16 @@
         <v>3.55</v>
       </c>
       <c r="M470">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N470">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O470">
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24860,7 +24863,7 @@
         <v>2.524828470599929</v>
       </c>
       <c r="D471" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E471">
         <v>2.044209354341666</v>
@@ -24896,7 +24899,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24910,10 +24913,10 @@
         <v>2.801763208907002</v>
       </c>
       <c r="D472" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E472">
-        <v>2.996066703116456</v>
+        <v>2.836685819374719</v>
       </c>
       <c r="F472">
         <v>-1</v>
@@ -24922,10 +24925,10 @@
         <v>0.004298236791092998</v>
       </c>
       <c r="H472">
-        <v>0.004403933296883544</v>
+        <v>0.004323314180625281</v>
       </c>
       <c r="I472">
-        <v>-0.1943034942094539</v>
+        <v>-0.03492261046771716</v>
       </c>
       <c r="J472">
         <v>0.4922610467717091</v>
@@ -24937,16 +24940,16 @@
         <v>3.55</v>
       </c>
       <c r="M472">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N472">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O472">
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="327">
   <si>
     <t>trade_time</t>
   </si>
@@ -1352,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P472"/>
+  <dimension ref="A1:P473"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24613,10 +24613,10 @@
         <v>3.014088527917016</v>
       </c>
       <c r="D466" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E466">
-        <v>3.195820128237719</v>
+        <v>3.047614261285982</v>
       </c>
       <c r="F466">
         <v>-1</v>
@@ -24625,10 +24625,10 @@
         <v>0.004085911472082985</v>
       </c>
       <c r="H466">
-        <v>0.004204179871762282</v>
+        <v>0.004112385738714018</v>
       </c>
       <c r="I466">
-        <v>-0.1817316003207035</v>
+        <v>-0.03352573336896691</v>
       </c>
       <c r="J466">
         <v>0.3525733368967002</v>
@@ -24640,10 +24640,10 @@
         <v>3.55</v>
       </c>
       <c r="M466">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N466">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O466">
         <v>1</v>
@@ -24663,10 +24663,10 @@
         <v>2.958985295983108</v>
       </c>
       <c r="D467" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E467">
-        <v>3.143979587668319</v>
+        <v>2.992873550614799</v>
       </c>
       <c r="F467">
         <v>-1</v>
@@ -24675,10 +24675,10 @@
         <v>0.004141014704016891</v>
       </c>
       <c r="H467">
-        <v>0.004256020412331681</v>
+        <v>0.004167126449385202</v>
       </c>
       <c r="I467">
-        <v>-0.1849942916852112</v>
+        <v>-0.03388825463169054</v>
       </c>
       <c r="J467">
         <v>0.3888254631690077</v>
@@ -24690,10 +24690,10 @@
         <v>3.55</v>
       </c>
       <c r="M467">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N467">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O467">
         <v>1</v>
@@ -24707,43 +24707,43 @@
         <v>0</v>
       </c>
       <c r="B468" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C468">
-        <v>2.931899483775353</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D468" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E468">
-        <v>2.965965934539989</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F468">
         <v>-1</v>
       </c>
       <c r="G468">
-        <v>0.004168100516224646</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H468">
-        <v>0.004194034065460011</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I468">
-        <v>-0.03406645076463599</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J468">
         <v>0.4066450764635833</v>
       </c>
       <c r="K468">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L468">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M468">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N468">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O468">
         <v>1</v>
@@ -24754,96 +24754,96 @@
     </row>
     <row r="469" spans="1:16">
       <c r="A469" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B469" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C469">
-        <v>2.575080697535542</v>
+        <v>2.931899483775353</v>
       </c>
       <c r="D469" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E469">
-        <v>2.091296086667161</v>
+        <v>2.965965934539989</v>
       </c>
       <c r="F469">
         <v>-1</v>
       </c>
       <c r="G469">
-        <v>0.003724919302464458</v>
+        <v>0.004168100516224646</v>
       </c>
       <c r="H469">
-        <v>0.003168703913332839</v>
+        <v>0.004194034065460011</v>
       </c>
       <c r="I469">
-        <v>0.4837846108683808</v>
+        <v>-0.03406645076463599</v>
       </c>
       <c r="J469">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K469">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L469">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M469">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N469">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O469">
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="470" spans="1:16">
       <c r="A470" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B470" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C470">
-        <v>2.861907606499231</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D470" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E470">
-        <v>2.896434530140684</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F470">
         <v>-1</v>
       </c>
       <c r="G470">
-        <v>0.004238092393500768</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H470">
-        <v>0.004263565469859316</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I470">
-        <v>-0.03452692364145271</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J470">
         <v>0.4526923641452424</v>
       </c>
       <c r="K470">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L470">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M470">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N470">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O470">
         <v>1</v>
@@ -24854,101 +24854,151 @@
     </row>
     <row r="471" spans="1:16">
       <c r="A471" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B471" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C471">
-        <v>2.524828470599929</v>
+        <v>2.861907606499231</v>
       </c>
       <c r="D471" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E471">
-        <v>2.044209354341666</v>
+        <v>2.896434530140684</v>
       </c>
       <c r="F471">
         <v>-1</v>
       </c>
       <c r="G471">
-        <v>0.003775171529400071</v>
+        <v>0.004238092393500768</v>
       </c>
       <c r="H471">
-        <v>0.003215790645658334</v>
+        <v>0.004263565469859316</v>
       </c>
       <c r="I471">
-        <v>0.4806191162582629</v>
+        <v>-0.03452692364145271</v>
       </c>
       <c r="J471">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K471">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L471">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M471">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N471">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O471">
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="472" spans="1:16">
       <c r="A472" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B472" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C472">
-        <v>2.801763208907002</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D472" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E472">
-        <v>2.836685819374719</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F472">
         <v>-1</v>
       </c>
       <c r="G472">
-        <v>0.004298236791092998</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H472">
-        <v>0.004323314180625281</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I472">
-        <v>-0.03492261046771716</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J472">
         <v>0.4922610467717091</v>
       </c>
       <c r="K472">
+        <v>1.27</v>
+      </c>
+      <c r="L472">
+        <v>3.15</v>
+      </c>
+      <c r="M472">
+        <v>1.19</v>
+      </c>
+      <c r="N472">
+        <v>2.63</v>
+      </c>
+      <c r="O472">
+        <v>1</v>
+      </c>
+      <c r="P472" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="473" spans="1:16">
+      <c r="A473" s="1">
+        <v>1</v>
+      </c>
+      <c r="B473" t="s">
+        <v>54</v>
+      </c>
+      <c r="C473">
+        <v>2.801763208907002</v>
+      </c>
+      <c r="D473" t="s">
+        <v>126</v>
+      </c>
+      <c r="E473">
+        <v>2.836685819374719</v>
+      </c>
+      <c r="F473">
+        <v>-1</v>
+      </c>
+      <c r="G473">
+        <v>0.004298236791092998</v>
+      </c>
+      <c r="H473">
+        <v>0.004323314180625281</v>
+      </c>
+      <c r="I473">
+        <v>-0.03492261046771716</v>
+      </c>
+      <c r="J473">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K473">
         <v>1.52</v>
       </c>
-      <c r="L472">
+      <c r="L473">
         <v>3.55</v>
       </c>
-      <c r="M472">
+      <c r="M473">
         <v>1.51</v>
       </c>
-      <c r="N472">
+      <c r="N473">
         <v>3.58</v>
       </c>
-      <c r="O472">
-        <v>1</v>
-      </c>
-      <c r="P472" t="s">
+      <c r="O473">
+        <v>1</v>
+      </c>
+      <c r="P473" t="s">
         <v>326</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="327">
   <si>
     <t>trade_time</t>
   </si>
@@ -1352,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P473"/>
+  <dimension ref="A1:P474"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24563,10 +24563,10 @@
         <v>3.085589532934493</v>
       </c>
       <c r="D465" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E465">
-        <v>3.263087521116003</v>
+        <v>3.118644864954661</v>
       </c>
       <c r="F465">
         <v>-1</v>
@@ -24575,10 +24575,10 @@
         <v>0.004014410467065507</v>
       </c>
       <c r="H465">
-        <v>0.004136912478883997</v>
+        <v>0.004041355135045339</v>
       </c>
       <c r="I465">
-        <v>-0.1774979881815106</v>
+        <v>-0.03305533202016786</v>
       </c>
       <c r="J465">
         <v>0.3055332020167811</v>
@@ -24590,10 +24590,10 @@
         <v>3.55</v>
       </c>
       <c r="M465">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N465">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O465">
         <v>1</v>
@@ -24657,43 +24657,43 @@
         <v>0</v>
       </c>
       <c r="B467" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C467">
-        <v>2.958985295983108</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D467" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E467">
-        <v>2.992873550614799</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F467">
         <v>-1</v>
       </c>
       <c r="G467">
-        <v>0.004141014704016891</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H467">
-        <v>0.004167126449385202</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I467">
-        <v>-0.03388825463169054</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J467">
         <v>0.3888254631690077</v>
       </c>
       <c r="K467">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L467">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M467">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N467">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O467">
         <v>1</v>
@@ -24704,96 +24704,96 @@
     </row>
     <row r="468" spans="1:16">
       <c r="A468" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B468" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C468">
-        <v>2.633560752891249</v>
+        <v>2.958985295983108</v>
       </c>
       <c r="D468" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E468">
-        <v>2.146092359008336</v>
+        <v>2.992873550614799</v>
       </c>
       <c r="F468">
         <v>-1</v>
       </c>
       <c r="G468">
-        <v>0.003666439247108751</v>
+        <v>0.004141014704016891</v>
       </c>
       <c r="H468">
-        <v>0.003113907640991664</v>
+        <v>0.004167126449385202</v>
       </c>
       <c r="I468">
-        <v>0.4874683938829132</v>
+        <v>-0.03388825463169054</v>
       </c>
       <c r="J468">
-        <v>0.4066450764635833</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K468">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L468">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M468">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N468">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O468">
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="469" spans="1:16">
       <c r="A469" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B469" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C469">
-        <v>2.931899483775353</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D469" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E469">
-        <v>2.965965934539989</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F469">
         <v>-1</v>
       </c>
       <c r="G469">
-        <v>0.004168100516224646</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H469">
-        <v>0.004194034065460011</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I469">
-        <v>-0.03406645076463599</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J469">
         <v>0.4066450764635833</v>
       </c>
       <c r="K469">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L469">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M469">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N469">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O469">
         <v>1</v>
@@ -24804,96 +24804,96 @@
     </row>
     <row r="470" spans="1:16">
       <c r="A470" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B470" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C470">
-        <v>2.575080697535542</v>
+        <v>2.931899483775353</v>
       </c>
       <c r="D470" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E470">
-        <v>2.091296086667161</v>
+        <v>2.965965934539989</v>
       </c>
       <c r="F470">
         <v>-1</v>
       </c>
       <c r="G470">
-        <v>0.003724919302464458</v>
+        <v>0.004168100516224646</v>
       </c>
       <c r="H470">
-        <v>0.003168703913332839</v>
+        <v>0.004194034065460011</v>
       </c>
       <c r="I470">
-        <v>0.4837846108683808</v>
+        <v>-0.03406645076463599</v>
       </c>
       <c r="J470">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K470">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L470">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M470">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N470">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O470">
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="471" spans="1:16">
       <c r="A471" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B471" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C471">
-        <v>2.861907606499231</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D471" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E471">
-        <v>2.896434530140684</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F471">
         <v>-1</v>
       </c>
       <c r="G471">
-        <v>0.004238092393500768</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H471">
-        <v>0.004263565469859316</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I471">
-        <v>-0.03452692364145271</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J471">
         <v>0.4526923641452424</v>
       </c>
       <c r="K471">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L471">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M471">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N471">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O471">
         <v>1</v>
@@ -24904,101 +24904,151 @@
     </row>
     <row r="472" spans="1:16">
       <c r="A472" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B472" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C472">
-        <v>2.524828470599929</v>
+        <v>2.861907606499231</v>
       </c>
       <c r="D472" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E472">
-        <v>2.044209354341666</v>
+        <v>2.896434530140684</v>
       </c>
       <c r="F472">
         <v>-1</v>
       </c>
       <c r="G472">
-        <v>0.003775171529400071</v>
+        <v>0.004238092393500768</v>
       </c>
       <c r="H472">
-        <v>0.003215790645658334</v>
+        <v>0.004263565469859316</v>
       </c>
       <c r="I472">
-        <v>0.4806191162582629</v>
+        <v>-0.03452692364145271</v>
       </c>
       <c r="J472">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K472">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L472">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M472">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N472">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O472">
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="473" spans="1:16">
       <c r="A473" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B473" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C473">
-        <v>2.801763208907002</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D473" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E473">
-        <v>2.836685819374719</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F473">
         <v>-1</v>
       </c>
       <c r="G473">
-        <v>0.004298236791092998</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H473">
-        <v>0.004323314180625281</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I473">
-        <v>-0.03492261046771716</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J473">
         <v>0.4922610467717091</v>
       </c>
       <c r="K473">
+        <v>1.27</v>
+      </c>
+      <c r="L473">
+        <v>3.15</v>
+      </c>
+      <c r="M473">
+        <v>1.19</v>
+      </c>
+      <c r="N473">
+        <v>2.63</v>
+      </c>
+      <c r="O473">
+        <v>1</v>
+      </c>
+      <c r="P473" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="474" spans="1:16">
+      <c r="A474" s="1">
+        <v>1</v>
+      </c>
+      <c r="B474" t="s">
+        <v>54</v>
+      </c>
+      <c r="C474">
+        <v>2.801763208907002</v>
+      </c>
+      <c r="D474" t="s">
+        <v>126</v>
+      </c>
+      <c r="E474">
+        <v>2.836685819374719</v>
+      </c>
+      <c r="F474">
+        <v>-1</v>
+      </c>
+      <c r="G474">
+        <v>0.004298236791092998</v>
+      </c>
+      <c r="H474">
+        <v>0.004323314180625281</v>
+      </c>
+      <c r="I474">
+        <v>-0.03492261046771716</v>
+      </c>
+      <c r="J474">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K474">
         <v>1.52</v>
       </c>
-      <c r="L473">
+      <c r="L474">
         <v>3.55</v>
       </c>
-      <c r="M473">
+      <c r="M474">
         <v>1.51</v>
       </c>
-      <c r="N473">
+      <c r="N474">
         <v>3.58</v>
       </c>
-      <c r="O473">
-        <v>1</v>
-      </c>
-      <c r="P473" t="s">
+      <c r="O474">
+        <v>1</v>
+      </c>
+      <c r="P474" t="s">
         <v>326</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -24513,10 +24513,10 @@
         <v>3.226019469262567</v>
       </c>
       <c r="D464" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E464">
-        <v>3.395202527003599</v>
+        <v>3.258150920122682</v>
       </c>
       <c r="F464">
         <v>-1</v>
@@ -24525,10 +24525,10 @@
         <v>0.003873980530737433</v>
       </c>
       <c r="H464">
-        <v>0.004004797472996401</v>
+        <v>0.003901849079877319</v>
       </c>
       <c r="I464">
-        <v>-0.1691830577410327</v>
+        <v>-0.03213145086011515</v>
       </c>
       <c r="J464">
         <v>0.2131450860114693</v>
@@ -24540,10 +24540,10 @@
         <v>3.55</v>
       </c>
       <c r="M464">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N464">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O464">
         <v>1</v>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="327">
   <si>
     <t>trade_time</t>
   </si>
@@ -1352,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P474"/>
+  <dimension ref="A1:P475"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24463,10 +24463,10 @@
         <v>3.29749980927481</v>
       </c>
       <c r="D463" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E463">
-        <v>3.462450478462486</v>
+        <v>3.329160994740108</v>
       </c>
       <c r="F463">
         <v>-1</v>
@@ -24475,10 +24475,10 @@
         <v>0.00380250019072519</v>
       </c>
       <c r="H463">
-        <v>0.003937549521537514</v>
+        <v>0.003830839005259893</v>
       </c>
       <c r="I463">
-        <v>-0.1649506691876761</v>
+        <v>-0.0316611854652975</v>
       </c>
       <c r="J463">
         <v>0.16611854652973</v>
@@ -24490,10 +24490,10 @@
         <v>3.55</v>
       </c>
       <c r="M463">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N463">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O463">
         <v>1</v>
@@ -24607,43 +24607,43 @@
         <v>0</v>
       </c>
       <c r="B466" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C466">
-        <v>3.014088527917016</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D466" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E466">
-        <v>3.047614261285982</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F466">
         <v>-1</v>
       </c>
       <c r="G466">
-        <v>0.004085911472082985</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H466">
-        <v>0.004112385738714018</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I466">
-        <v>-0.03352573336896691</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J466">
         <v>0.3525733368967002</v>
       </c>
       <c r="K466">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L466">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M466">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N466">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O466">
         <v>1</v>
@@ -24654,96 +24654,96 @@
     </row>
     <row r="467" spans="1:16">
       <c r="A467" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B467" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C467">
-        <v>2.65619166177536</v>
+        <v>3.014088527917016</v>
       </c>
       <c r="D467" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E467">
-        <v>2.167297698828881</v>
+        <v>3.047614261285982</v>
       </c>
       <c r="F467">
         <v>-1</v>
       </c>
       <c r="G467">
-        <v>0.00364380833822464</v>
+        <v>0.004085911472082985</v>
       </c>
       <c r="H467">
-        <v>0.003092702301171119</v>
+        <v>0.004112385738714018</v>
       </c>
       <c r="I467">
-        <v>0.4888939629464795</v>
+        <v>-0.03352573336896691</v>
       </c>
       <c r="J467">
-        <v>0.3888254631690077</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K467">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L467">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M467">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N467">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O467">
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="468" spans="1:16">
       <c r="A468" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B468" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C468">
-        <v>2.958985295983108</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D468" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E468">
-        <v>2.992873550614799</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F468">
         <v>-1</v>
       </c>
       <c r="G468">
-        <v>0.004141014704016891</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H468">
-        <v>0.004167126449385202</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I468">
-        <v>-0.03388825463169054</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J468">
         <v>0.3888254631690077</v>
       </c>
       <c r="K468">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L468">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M468">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N468">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O468">
         <v>1</v>
@@ -24754,96 +24754,96 @@
     </row>
     <row r="469" spans="1:16">
       <c r="A469" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B469" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C469">
-        <v>2.633560752891249</v>
+        <v>2.958985295983108</v>
       </c>
       <c r="D469" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E469">
-        <v>2.146092359008336</v>
+        <v>2.992873550614799</v>
       </c>
       <c r="F469">
         <v>-1</v>
       </c>
       <c r="G469">
-        <v>0.003666439247108751</v>
+        <v>0.004141014704016891</v>
       </c>
       <c r="H469">
-        <v>0.003113907640991664</v>
+        <v>0.004167126449385202</v>
       </c>
       <c r="I469">
-        <v>0.4874683938829132</v>
+        <v>-0.03388825463169054</v>
       </c>
       <c r="J469">
-        <v>0.4066450764635833</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K469">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L469">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M469">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N469">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O469">
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="470" spans="1:16">
       <c r="A470" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B470" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C470">
-        <v>2.931899483775353</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D470" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E470">
-        <v>2.965965934539989</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F470">
         <v>-1</v>
       </c>
       <c r="G470">
-        <v>0.004168100516224646</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H470">
-        <v>0.004194034065460011</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I470">
-        <v>-0.03406645076463599</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J470">
         <v>0.4066450764635833</v>
       </c>
       <c r="K470">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L470">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M470">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N470">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O470">
         <v>1</v>
@@ -24854,96 +24854,96 @@
     </row>
     <row r="471" spans="1:16">
       <c r="A471" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B471" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C471">
-        <v>2.575080697535542</v>
+        <v>2.931899483775353</v>
       </c>
       <c r="D471" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E471">
-        <v>2.091296086667161</v>
+        <v>2.965965934539989</v>
       </c>
       <c r="F471">
         <v>-1</v>
       </c>
       <c r="G471">
-        <v>0.003724919302464458</v>
+        <v>0.004168100516224646</v>
       </c>
       <c r="H471">
-        <v>0.003168703913332839</v>
+        <v>0.004194034065460011</v>
       </c>
       <c r="I471">
-        <v>0.4837846108683808</v>
+        <v>-0.03406645076463599</v>
       </c>
       <c r="J471">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K471">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L471">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M471">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N471">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O471">
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="472" spans="1:16">
       <c r="A472" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B472" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C472">
-        <v>2.861907606499231</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D472" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E472">
-        <v>2.896434530140684</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F472">
         <v>-1</v>
       </c>
       <c r="G472">
-        <v>0.004238092393500768</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H472">
-        <v>0.004263565469859316</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I472">
-        <v>-0.03452692364145271</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J472">
         <v>0.4526923641452424</v>
       </c>
       <c r="K472">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L472">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M472">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N472">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O472">
         <v>1</v>
@@ -24954,101 +24954,151 @@
     </row>
     <row r="473" spans="1:16">
       <c r="A473" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B473" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C473">
-        <v>2.524828470599929</v>
+        <v>2.861907606499231</v>
       </c>
       <c r="D473" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E473">
-        <v>2.044209354341666</v>
+        <v>2.896434530140684</v>
       </c>
       <c r="F473">
         <v>-1</v>
       </c>
       <c r="G473">
-        <v>0.003775171529400071</v>
+        <v>0.004238092393500768</v>
       </c>
       <c r="H473">
-        <v>0.003215790645658334</v>
+        <v>0.004263565469859316</v>
       </c>
       <c r="I473">
-        <v>0.4806191162582629</v>
+        <v>-0.03452692364145271</v>
       </c>
       <c r="J473">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K473">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L473">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M473">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N473">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O473">
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="474" spans="1:16">
       <c r="A474" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B474" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C474">
-        <v>2.801763208907002</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D474" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E474">
-        <v>2.836685819374719</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F474">
         <v>-1</v>
       </c>
       <c r="G474">
-        <v>0.004298236791092998</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H474">
-        <v>0.004323314180625281</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I474">
-        <v>-0.03492261046771716</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J474">
         <v>0.4922610467717091</v>
       </c>
       <c r="K474">
+        <v>1.27</v>
+      </c>
+      <c r="L474">
+        <v>3.15</v>
+      </c>
+      <c r="M474">
+        <v>1.19</v>
+      </c>
+      <c r="N474">
+        <v>2.63</v>
+      </c>
+      <c r="O474">
+        <v>1</v>
+      </c>
+      <c r="P474" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="475" spans="1:16">
+      <c r="A475" s="1">
+        <v>1</v>
+      </c>
+      <c r="B475" t="s">
+        <v>54</v>
+      </c>
+      <c r="C475">
+        <v>2.801763208907002</v>
+      </c>
+      <c r="D475" t="s">
+        <v>126</v>
+      </c>
+      <c r="E475">
+        <v>2.836685819374719</v>
+      </c>
+      <c r="F475">
+        <v>-1</v>
+      </c>
+      <c r="G475">
+        <v>0.004298236791092998</v>
+      </c>
+      <c r="H475">
+        <v>0.004323314180625281</v>
+      </c>
+      <c r="I475">
+        <v>-0.03492261046771716</v>
+      </c>
+      <c r="J475">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K475">
         <v>1.52</v>
       </c>
-      <c r="L474">
+      <c r="L475">
         <v>3.55</v>
       </c>
-      <c r="M474">
+      <c r="M475">
         <v>1.51</v>
       </c>
-      <c r="N474">
+      <c r="N475">
         <v>3.58</v>
       </c>
-      <c r="O474">
-        <v>1</v>
-      </c>
-      <c r="P474" t="s">
+      <c r="O475">
+        <v>1</v>
+      </c>
+      <c r="P475" t="s">
         <v>326</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -24413,10 +24413,10 @@
         <v>3.350459894428295</v>
       </c>
       <c r="D462" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E462">
-        <v>3.512274769100304</v>
+        <v>3.381772658280741</v>
       </c>
       <c r="F462">
         <v>-1</v>
@@ -24425,10 +24425,10 @@
         <v>0.003749540105571705</v>
       </c>
       <c r="H462">
-        <v>0.003887725230899696</v>
+        <v>0.00377822734171926</v>
       </c>
       <c r="I462">
-        <v>-0.1618148746720092</v>
+        <v>-0.03131276385244552</v>
       </c>
       <c r="J462">
         <v>0.1312763852445424</v>
@@ -24440,10 +24440,10 @@
         <v>3.55</v>
       </c>
       <c r="M462">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N462">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O462">
         <v>1</v>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="325">
   <si>
     <t>trade_time</t>
   </si>
@@ -1346,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P470"/>
+  <dimension ref="A1:P471"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -23557,10 +23557,10 @@
         <v>3.536490631366341</v>
       </c>
       <c r="D445" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E445">
-        <v>3.687290528193334</v>
+        <v>3.566579508791563</v>
       </c>
       <c r="F445">
         <v>-1</v>
@@ -23569,10 +23569,10 @@
         <v>0.003563509368633659</v>
       </c>
       <c r="H445">
-        <v>0.003712709471806666</v>
+        <v>0.003593420491208437</v>
       </c>
       <c r="I445">
-        <v>-0.1507998968269932</v>
+        <v>-0.03008887742522193</v>
       </c>
       <c r="J445">
         <v>0.008887742522143843</v>
@@ -23584,10 +23584,10 @@
         <v>3.55</v>
       </c>
       <c r="M445">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N445">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O445">
         <v>1</v>
@@ -23607,10 +23607,10 @@
         <v>3.478129127613399</v>
       </c>
       <c r="D446" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E446">
-        <v>3.632384639794185</v>
+        <v>3.508601962300153</v>
       </c>
       <c r="F446">
         <v>-1</v>
@@ -23619,10 +23619,10 @@
         <v>0.0036218708723866</v>
       </c>
       <c r="H446">
-        <v>0.003767615360205815</v>
+        <v>0.003651398037699847</v>
       </c>
       <c r="I446">
-        <v>-0.1542555121807858</v>
+        <v>-0.03047283468675399</v>
       </c>
       <c r="J446">
         <v>0.04728346867539508</v>
@@ -23634,10 +23634,10 @@
         <v>3.55</v>
       </c>
       <c r="M446">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N446">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O446">
         <v>1</v>
@@ -23657,10 +23657,10 @@
         <v>3.446322550887229</v>
       </c>
       <c r="D447" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E447">
-        <v>3.602461347216275</v>
+        <v>3.477004639368234</v>
       </c>
       <c r="F447">
         <v>-1</v>
@@ -23669,10 +23669,10 @@
         <v>0.003653677449112771</v>
       </c>
       <c r="H447">
-        <v>0.003797538652783726</v>
+        <v>0.003682995360631766</v>
       </c>
       <c r="I447">
-        <v>-0.1561387963290461</v>
+        <v>-0.03068208848100529</v>
       </c>
       <c r="J447">
         <v>0.06820884810050738</v>
@@ -23684,10 +23684,10 @@
         <v>3.55</v>
       </c>
       <c r="M447">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N447">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O447">
         <v>1</v>
@@ -23707,10 +23707,10 @@
         <v>3.437244026062129</v>
       </c>
       <c r="D448" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E448">
-        <v>3.59392036662424</v>
+        <v>3.467985841680141</v>
       </c>
       <c r="F448">
         <v>-1</v>
@@ -23719,10 +23719,10 @@
         <v>0.003662755973937871</v>
       </c>
       <c r="H448">
-        <v>0.00380607963337576</v>
+        <v>0.003692014158319859</v>
       </c>
       <c r="I448">
-        <v>-0.1566763405621114</v>
+        <v>-0.03074181561801259</v>
       </c>
       <c r="J448">
         <v>0.07418156180123091</v>
@@ -23734,10 +23734,10 @@
         <v>3.55</v>
       </c>
       <c r="M448">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N448">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O448">
         <v>1</v>
@@ -23907,10 +23907,10 @@
         <v>3.40927622228758</v>
       </c>
       <c r="D452" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E452">
-        <v>3.567608551231079</v>
+        <v>3.440202036614636</v>
       </c>
       <c r="F452">
         <v>-1</v>
@@ -23919,10 +23919,10 @@
         <v>0.00369072377771242</v>
       </c>
       <c r="H452">
-        <v>0.003832391448768921</v>
+        <v>0.003719797963385364</v>
       </c>
       <c r="I452">
-        <v>-0.1583323289434988</v>
+        <v>-0.03092581432705543</v>
       </c>
       <c r="J452">
         <v>0.09258143270553931</v>
@@ -23934,10 +23934,10 @@
         <v>3.55</v>
       </c>
       <c r="M452">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N452">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O452">
         <v>1</v>
@@ -23957,10 +23957,10 @@
         <v>3.398669636469118</v>
       </c>
       <c r="D453" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E453">
-        <v>3.557629986941341</v>
+        <v>3.429665230966032</v>
       </c>
       <c r="F453">
         <v>-1</v>
@@ -23969,10 +23969,10 @@
         <v>0.003701330363530882</v>
       </c>
       <c r="H453">
-        <v>0.003842370013058659</v>
+        <v>0.003730334769033969</v>
       </c>
       <c r="I453">
-        <v>-0.1589603504722237</v>
+        <v>-0.0309955944969138</v>
       </c>
       <c r="J453">
         <v>0.09955944969136986</v>
@@ -23984,10 +23984,10 @@
         <v>3.55</v>
       </c>
       <c r="M453">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N453">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O453">
         <v>1</v>
@@ -24007,10 +24007,10 @@
         <v>3.386651569627924</v>
       </c>
       <c r="D454" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E454">
-        <v>3.546323516163113</v>
+        <v>3.417726230354056</v>
       </c>
       <c r="F454">
         <v>-1</v>
@@ -24019,10 +24019,10 @@
         <v>0.003713348430372076</v>
       </c>
       <c r="H454">
-        <v>0.003853676483836888</v>
+        <v>0.003742273769645944</v>
       </c>
       <c r="I454">
-        <v>-0.1596719465351892</v>
+        <v>-0.0310746607261323</v>
       </c>
       <c r="J454">
         <v>0.1074660726132081</v>
@@ -24034,10 +24034,10 @@
         <v>3.55</v>
       </c>
       <c r="M454">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N454">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O454">
         <v>1</v>
@@ -24057,10 +24057,10 @@
         <v>3.393731929090075</v>
       </c>
       <c r="D455" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E455">
-        <v>3.552984643815005</v>
+        <v>3.424760008503956</v>
       </c>
       <c r="F455">
         <v>-1</v>
@@ -24069,10 +24069,10 @@
         <v>0.003706268070909925</v>
       </c>
       <c r="H455">
-        <v>0.003847015356184996</v>
+        <v>0.003735239991496044</v>
       </c>
       <c r="I455">
-        <v>-0.1592527147249299</v>
+        <v>-0.0310280794138813</v>
       </c>
       <c r="J455">
         <v>0.1028079413881086</v>
@@ -24084,10 +24084,10 @@
         <v>3.55</v>
       </c>
       <c r="M455">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N455">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O455">
         <v>1</v>
@@ -24107,10 +24107,10 @@
         <v>3.379912288774229</v>
       </c>
       <c r="D456" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E456">
-        <v>3.539983271675756</v>
+        <v>3.411031286874399</v>
       </c>
       <c r="F456">
         <v>-1</v>
@@ -24119,10 +24119,10 @@
         <v>0.00372008771122577</v>
       </c>
       <c r="H456">
-        <v>0.003860016728324245</v>
+        <v>0.003748968713125601</v>
       </c>
       <c r="I456">
-        <v>-0.1600709829015261</v>
+        <v>-0.03111899810016983</v>
       </c>
       <c r="J456">
         <v>0.1118998100169543</v>
@@ -24134,10 +24134,10 @@
         <v>3.55</v>
       </c>
       <c r="M456">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N456">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O456">
         <v>1</v>
@@ -24301,43 +24301,43 @@
         <v>0</v>
       </c>
       <c r="B460" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C460">
-        <v>3.085589532934493</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="D460" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E460">
-        <v>3.118644864954661</v>
+        <v>2.26641548960003</v>
       </c>
       <c r="F460">
         <v>-1</v>
       </c>
       <c r="G460">
-        <v>0.004014410467065507</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="H460">
-        <v>0.004041355135045339</v>
+        <v>0.00299358451039997</v>
       </c>
       <c r="I460">
-        <v>-0.03305533202016786</v>
+        <v>0.4955573438386578</v>
       </c>
       <c r="J460">
         <v>0.3055332020167811</v>
       </c>
       <c r="K460">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L460">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M460">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N460">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O460">
         <v>1</v>
@@ -24348,96 +24348,96 @@
     </row>
     <row r="461" spans="1:16">
       <c r="A461" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B461" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C461">
-        <v>2.702231862141191</v>
+        <v>3.085589532934493</v>
       </c>
       <c r="D461" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E461">
-        <v>2.210437729092927</v>
+        <v>3.118644864954661</v>
       </c>
       <c r="F461">
         <v>-1</v>
       </c>
       <c r="G461">
-        <v>0.003597768137858809</v>
+        <v>0.004014410467065507</v>
       </c>
       <c r="H461">
-        <v>0.003049562270907073</v>
+        <v>0.004041355135045339</v>
       </c>
       <c r="I461">
-        <v>0.491794133048264</v>
+        <v>-0.03305533202016786</v>
       </c>
       <c r="J461">
-        <v>0.3525733368967002</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K461">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L461">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M461">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N461">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O461">
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="462" spans="1:16">
       <c r="A462" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B462" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C462">
-        <v>3.014088527917016</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D462" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E462">
-        <v>3.047614261285982</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F462">
         <v>-1</v>
       </c>
       <c r="G462">
-        <v>0.004085911472082985</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H462">
-        <v>0.004112385738714018</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I462">
-        <v>-0.03352573336896691</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J462">
         <v>0.3525733368967002</v>
       </c>
       <c r="K462">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L462">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M462">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N462">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O462">
         <v>1</v>
@@ -24448,96 +24448,96 @@
     </row>
     <row r="463" spans="1:16">
       <c r="A463" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B463" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C463">
-        <v>2.65619166177536</v>
+        <v>3.014088527917016</v>
       </c>
       <c r="D463" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E463">
-        <v>2.167297698828881</v>
+        <v>3.047614261285982</v>
       </c>
       <c r="F463">
         <v>-1</v>
       </c>
       <c r="G463">
-        <v>0.00364380833822464</v>
+        <v>0.004085911472082985</v>
       </c>
       <c r="H463">
-        <v>0.003092702301171119</v>
+        <v>0.004112385738714018</v>
       </c>
       <c r="I463">
-        <v>0.4888939629464795</v>
+        <v>-0.03352573336896691</v>
       </c>
       <c r="J463">
-        <v>0.3888254631690077</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K463">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L463">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M463">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N463">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O463">
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="464" spans="1:16">
       <c r="A464" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B464" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C464">
-        <v>2.958985295983108</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D464" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E464">
-        <v>2.992873550614799</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F464">
         <v>-1</v>
       </c>
       <c r="G464">
-        <v>0.004141014704016891</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H464">
-        <v>0.004167126449385202</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I464">
-        <v>-0.03388825463169054</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J464">
         <v>0.3888254631690077</v>
       </c>
       <c r="K464">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L464">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M464">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N464">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O464">
         <v>1</v>
@@ -24548,96 +24548,96 @@
     </row>
     <row r="465" spans="1:16">
       <c r="A465" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B465" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C465">
-        <v>2.633560752891249</v>
+        <v>2.958985295983108</v>
       </c>
       <c r="D465" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E465">
-        <v>2.146092359008336</v>
+        <v>2.992873550614799</v>
       </c>
       <c r="F465">
         <v>-1</v>
       </c>
       <c r="G465">
-        <v>0.003666439247108751</v>
+        <v>0.004141014704016891</v>
       </c>
       <c r="H465">
-        <v>0.003113907640991664</v>
+        <v>0.004167126449385202</v>
       </c>
       <c r="I465">
-        <v>0.4874683938829132</v>
+        <v>-0.03388825463169054</v>
       </c>
       <c r="J465">
-        <v>0.4066450764635833</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K465">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L465">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M465">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N465">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O465">
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="466" spans="1:16">
       <c r="A466" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B466" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C466">
-        <v>2.931899483775353</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D466" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E466">
-        <v>2.965965934539989</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F466">
         <v>-1</v>
       </c>
       <c r="G466">
-        <v>0.004168100516224646</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H466">
-        <v>0.004194034065460011</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I466">
-        <v>-0.03406645076463599</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J466">
         <v>0.4066450764635833</v>
       </c>
       <c r="K466">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L466">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M466">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N466">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O466">
         <v>1</v>
@@ -24648,96 +24648,96 @@
     </row>
     <row r="467" spans="1:16">
       <c r="A467" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B467" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C467">
-        <v>2.575080697535542</v>
+        <v>2.931899483775353</v>
       </c>
       <c r="D467" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E467">
-        <v>2.091296086667161</v>
+        <v>2.965965934539989</v>
       </c>
       <c r="F467">
         <v>-1</v>
       </c>
       <c r="G467">
-        <v>0.003724919302464458</v>
+        <v>0.004168100516224646</v>
       </c>
       <c r="H467">
-        <v>0.003168703913332839</v>
+        <v>0.004194034065460011</v>
       </c>
       <c r="I467">
-        <v>0.4837846108683808</v>
+        <v>-0.03406645076463599</v>
       </c>
       <c r="J467">
-        <v>0.4526923641452424</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K467">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L467">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M467">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N467">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O467">
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="468" spans="1:16">
       <c r="A468" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B468" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C468">
-        <v>2.861907606499231</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D468" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E468">
-        <v>2.896434530140684</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F468">
         <v>-1</v>
       </c>
       <c r="G468">
-        <v>0.004238092393500768</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H468">
-        <v>0.004263565469859316</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I468">
-        <v>-0.03452692364145271</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J468">
         <v>0.4526923641452424</v>
       </c>
       <c r="K468">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L468">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M468">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N468">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O468">
         <v>1</v>
@@ -24748,101 +24748,151 @@
     </row>
     <row r="469" spans="1:16">
       <c r="A469" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B469" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C469">
-        <v>2.524828470599929</v>
+        <v>2.861907606499231</v>
       </c>
       <c r="D469" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E469">
-        <v>2.044209354341666</v>
+        <v>2.896434530140684</v>
       </c>
       <c r="F469">
         <v>-1</v>
       </c>
       <c r="G469">
-        <v>0.003775171529400071</v>
+        <v>0.004238092393500768</v>
       </c>
       <c r="H469">
-        <v>0.003215790645658334</v>
+        <v>0.004263565469859316</v>
       </c>
       <c r="I469">
-        <v>0.4806191162582629</v>
+        <v>-0.03452692364145271</v>
       </c>
       <c r="J469">
-        <v>0.4922610467717091</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K469">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L469">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M469">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N469">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O469">
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="470" spans="1:16">
       <c r="A470" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B470" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C470">
-        <v>2.801763208907002</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D470" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E470">
-        <v>2.836685819374719</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F470">
         <v>-1</v>
       </c>
       <c r="G470">
-        <v>0.004298236791092998</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H470">
-        <v>0.004323314180625281</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I470">
-        <v>-0.03492261046771716</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J470">
         <v>0.4922610467717091</v>
       </c>
       <c r="K470">
+        <v>1.27</v>
+      </c>
+      <c r="L470">
+        <v>3.15</v>
+      </c>
+      <c r="M470">
+        <v>1.19</v>
+      </c>
+      <c r="N470">
+        <v>2.63</v>
+      </c>
+      <c r="O470">
+        <v>1</v>
+      </c>
+      <c r="P470" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="471" spans="1:16">
+      <c r="A471" s="1">
+        <v>1</v>
+      </c>
+      <c r="B471" t="s">
+        <v>53</v>
+      </c>
+      <c r="C471">
+        <v>2.801763208907002</v>
+      </c>
+      <c r="D471" t="s">
+        <v>124</v>
+      </c>
+      <c r="E471">
+        <v>2.836685819374719</v>
+      </c>
+      <c r="F471">
+        <v>-1</v>
+      </c>
+      <c r="G471">
+        <v>0.004298236791092998</v>
+      </c>
+      <c r="H471">
+        <v>0.004323314180625281</v>
+      </c>
+      <c r="I471">
+        <v>-0.03492261046771716</v>
+      </c>
+      <c r="J471">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K471">
         <v>1.52</v>
       </c>
-      <c r="L470">
+      <c r="L471">
         <v>3.55</v>
       </c>
-      <c r="M470">
+      <c r="M471">
         <v>1.51</v>
       </c>
-      <c r="N470">
+      <c r="N471">
         <v>3.58</v>
       </c>
-      <c r="O470">
-        <v>1</v>
-      </c>
-      <c r="P470" t="s">
+      <c r="O471">
+        <v>1</v>
+      </c>
+      <c r="P471" t="s">
         <v>324</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -23457,10 +23457,10 @@
         <v>3.746022583750348</v>
       </c>
       <c r="D443" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E443">
-        <v>3.88441598339671</v>
+        <v>3.774732961488833</v>
       </c>
       <c r="F443">
         <v>-1</v>
@@ -23469,10 +23469,10 @@
         <v>0.003353977416249652</v>
       </c>
       <c r="H443">
-        <v>0.003515584016603291</v>
+        <v>0.003385267038511167</v>
       </c>
       <c r="I443">
-        <v>-0.1383933996463615</v>
+        <v>-0.02871037773848473</v>
       </c>
       <c r="J443">
         <v>-0.1289622261515449</v>
@@ -23484,10 +23484,10 @@
         <v>3.55</v>
       </c>
       <c r="M443">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N443">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O443">
         <v>1</v>
@@ -23507,10 +23507,10 @@
         <v>3.686827463477967</v>
       </c>
       <c r="D444" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E444">
-        <v>3.828725837350983</v>
+        <v>3.715927282797192</v>
       </c>
       <c r="F444">
         <v>-1</v>
@@ -23519,10 +23519,10 @@
         <v>0.003413172536522032</v>
       </c>
       <c r="H444">
-        <v>0.003571274162649018</v>
+        <v>0.003444072717202809</v>
       </c>
       <c r="I444">
-        <v>-0.1418983738730155</v>
+        <v>-0.02909981931922445</v>
       </c>
       <c r="J444">
         <v>-0.09001806807761016</v>
@@ -23534,10 +23534,10 @@
         <v>3.55</v>
       </c>
       <c r="M444">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N444">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O444">
         <v>1</v>
@@ -23857,10 +23857,10 @@
         <v>3.450931319109172</v>
       </c>
       <c r="D451" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E451">
-        <v>3.606797227846129</v>
+        <v>3.481583086746612</v>
       </c>
       <c r="F451">
         <v>-1</v>
@@ -23869,10 +23869,10 @@
         <v>0.003649068680890828</v>
       </c>
       <c r="H451">
-        <v>0.003793202772153872</v>
+        <v>0.003678416913253389</v>
       </c>
       <c r="I451">
-        <v>-0.1558659087369572</v>
+        <v>-0.03065176763744004</v>
       </c>
       <c r="J451">
         <v>0.06517676374396589</v>
@@ -23884,10 +23884,10 @@
         <v>3.55</v>
       </c>
       <c r="M451">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N451">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O451">
         <v>1</v>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -23757,10 +23757,10 @@
         <v>3.495394814734395</v>
       </c>
       <c r="D449" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E449">
-        <v>3.648628016493543</v>
+        <v>3.525754059374301</v>
       </c>
       <c r="F449">
         <v>-1</v>
@@ -23769,10 +23769,10 @@
         <v>0.003604605185265604</v>
       </c>
       <c r="H449">
-        <v>0.003751371983506458</v>
+        <v>0.0036342459406257</v>
       </c>
       <c r="I449">
-        <v>-0.1532332017591478</v>
+        <v>-0.03035924463990547</v>
       </c>
       <c r="J449">
         <v>0.03592446399052947</v>
@@ -23784,10 +23784,10 @@
         <v>3.55</v>
       </c>
       <c r="M449">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N449">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O449">
         <v>1</v>
@@ -23807,10 +23807,10 @@
         <v>3.479433369341057</v>
       </c>
       <c r="D450" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E450">
-        <v>3.633611656682705</v>
+        <v>3.509897623490129</v>
       </c>
       <c r="F450">
         <v>-1</v>
@@ -23819,10 +23819,10 @@
         <v>0.003620566630658943</v>
       </c>
       <c r="H450">
-        <v>0.003766388343317295</v>
+        <v>0.003650102376509871</v>
       </c>
       <c r="I450">
-        <v>-0.1541782873416486</v>
+        <v>-0.03046425414907228</v>
       </c>
       <c r="J450">
         <v>0.04642541490719935</v>
@@ -23834,10 +23834,10 @@
         <v>3.55</v>
       </c>
       <c r="M450">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="N450">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O450">
         <v>1</v>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="325">
   <si>
     <t>trade_time</t>
   </si>
@@ -1346,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P471"/>
+  <dimension ref="A1:P468"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24448,52 +24448,52 @@
     </row>
     <row r="463" spans="1:16">
       <c r="A463" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B463" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C463">
-        <v>3.014088527917016</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D463" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E463">
-        <v>3.047614261285982</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F463">
         <v>-1</v>
       </c>
       <c r="G463">
-        <v>0.004085911472082985</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H463">
-        <v>0.004112385738714018</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I463">
-        <v>-0.03352573336896691</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J463">
-        <v>0.3525733368967002</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K463">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L463">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M463">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N463">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O463">
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24504,28 +24504,28 @@
         <v>54</v>
       </c>
       <c r="C464">
-        <v>2.65619166177536</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D464" t="s">
         <v>125</v>
       </c>
       <c r="E464">
-        <v>2.167297698828881</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F464">
         <v>-1</v>
       </c>
       <c r="G464">
-        <v>0.00364380833822464</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H464">
-        <v>0.003092702301171119</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I464">
-        <v>0.4888939629464795</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J464">
-        <v>0.3888254631690077</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K464">
         <v>1.27</v>
@@ -24543,356 +24543,206 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="465" spans="1:16">
       <c r="A465" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B465" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C465">
-        <v>2.958985295983108</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D465" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E465">
-        <v>2.992873550614799</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F465">
         <v>-1</v>
       </c>
       <c r="G465">
-        <v>0.004141014704016891</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H465">
-        <v>0.004167126449385202</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I465">
-        <v>-0.03388825463169054</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J465">
-        <v>0.3888254631690077</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K465">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L465">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M465">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N465">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O465">
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="466" spans="1:16">
       <c r="A466" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B466" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C466">
-        <v>2.633560752891249</v>
+        <v>2.861907606499231</v>
       </c>
       <c r="D466" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E466">
-        <v>2.146092359008336</v>
+        <v>2.896434530140684</v>
       </c>
       <c r="F466">
         <v>-1</v>
       </c>
       <c r="G466">
-        <v>0.003666439247108751</v>
+        <v>0.004238092393500768</v>
       </c>
       <c r="H466">
-        <v>0.003113907640991664</v>
+        <v>0.004263565469859316</v>
       </c>
       <c r="I466">
-        <v>0.4874683938829132</v>
+        <v>-0.03452692364145271</v>
       </c>
       <c r="J466">
-        <v>0.4066450764635833</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K466">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L466">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M466">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N466">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O466">
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="467" spans="1:16">
       <c r="A467" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B467" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C467">
-        <v>2.931899483775353</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D467" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E467">
-        <v>2.965965934539989</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F467">
         <v>-1</v>
       </c>
       <c r="G467">
-        <v>0.004168100516224646</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H467">
-        <v>0.004194034065460011</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I467">
-        <v>-0.03406645076463599</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J467">
-        <v>0.4066450764635833</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K467">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L467">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M467">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N467">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O467">
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="468" spans="1:16">
       <c r="A468" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B468" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C468">
-        <v>2.575080697535542</v>
+        <v>2.801763208907002</v>
       </c>
       <c r="D468" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E468">
-        <v>2.091296086667161</v>
+        <v>2.836685819374719</v>
       </c>
       <c r="F468">
         <v>-1</v>
       </c>
       <c r="G468">
-        <v>0.003724919302464458</v>
+        <v>0.004298236791092998</v>
       </c>
       <c r="H468">
-        <v>0.003168703913332839</v>
+        <v>0.004323314180625281</v>
       </c>
       <c r="I468">
-        <v>0.4837846108683808</v>
+        <v>-0.03492261046771716</v>
       </c>
       <c r="J468">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K468">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L468">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M468">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N468">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O468">
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="469" spans="1:16">
-      <c r="A469" s="1">
-        <v>1</v>
-      </c>
-      <c r="B469" t="s">
-        <v>53</v>
-      </c>
-      <c r="C469">
-        <v>2.861907606499231</v>
-      </c>
-      <c r="D469" t="s">
-        <v>124</v>
-      </c>
-      <c r="E469">
-        <v>2.896434530140684</v>
-      </c>
-      <c r="F469">
-        <v>-1</v>
-      </c>
-      <c r="G469">
-        <v>0.004238092393500768</v>
-      </c>
-      <c r="H469">
-        <v>0.004263565469859316</v>
-      </c>
-      <c r="I469">
-        <v>-0.03452692364145271</v>
-      </c>
-      <c r="J469">
-        <v>0.4526923641452424</v>
-      </c>
-      <c r="K469">
-        <v>1.52</v>
-      </c>
-      <c r="L469">
-        <v>3.55</v>
-      </c>
-      <c r="M469">
-        <v>1.51</v>
-      </c>
-      <c r="N469">
-        <v>3.58</v>
-      </c>
-      <c r="O469">
-        <v>1</v>
-      </c>
-      <c r="P469" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="470" spans="1:16">
-      <c r="A470" s="1">
-        <v>0</v>
-      </c>
-      <c r="B470" t="s">
-        <v>54</v>
-      </c>
-      <c r="C470">
-        <v>2.524828470599929</v>
-      </c>
-      <c r="D470" t="s">
-        <v>125</v>
-      </c>
-      <c r="E470">
-        <v>2.044209354341666</v>
-      </c>
-      <c r="F470">
-        <v>-1</v>
-      </c>
-      <c r="G470">
-        <v>0.003775171529400071</v>
-      </c>
-      <c r="H470">
-        <v>0.003215790645658334</v>
-      </c>
-      <c r="I470">
-        <v>0.4806191162582629</v>
-      </c>
-      <c r="J470">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K470">
-        <v>1.27</v>
-      </c>
-      <c r="L470">
-        <v>3.15</v>
-      </c>
-      <c r="M470">
-        <v>1.19</v>
-      </c>
-      <c r="N470">
-        <v>2.63</v>
-      </c>
-      <c r="O470">
-        <v>1</v>
-      </c>
-      <c r="P470" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="471" spans="1:16">
-      <c r="A471" s="1">
-        <v>1</v>
-      </c>
-      <c r="B471" t="s">
-        <v>53</v>
-      </c>
-      <c r="C471">
-        <v>2.801763208907002</v>
-      </c>
-      <c r="D471" t="s">
-        <v>124</v>
-      </c>
-      <c r="E471">
-        <v>2.836685819374719</v>
-      </c>
-      <c r="F471">
-        <v>-1</v>
-      </c>
-      <c r="G471">
-        <v>0.004298236791092998</v>
-      </c>
-      <c r="H471">
-        <v>0.004323314180625281</v>
-      </c>
-      <c r="I471">
-        <v>-0.03492261046771716</v>
-      </c>
-      <c r="J471">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K471">
-        <v>1.52</v>
-      </c>
-      <c r="L471">
-        <v>3.55</v>
-      </c>
-      <c r="M471">
-        <v>1.51</v>
-      </c>
-      <c r="N471">
-        <v>3.58</v>
-      </c>
-      <c r="O471">
-        <v>1</v>
-      </c>
-      <c r="P471" t="s">
         <v>324</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="325">
   <si>
     <t>trade_time</t>
   </si>
@@ -1346,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P468"/>
+  <dimension ref="A1:P466"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24251,43 +24251,43 @@
         <v>0</v>
       </c>
       <c r="B459" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C459">
-        <v>3.226019469262567</v>
+        <v>2.879305740765434</v>
       </c>
       <c r="D459" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E459">
-        <v>3.258150920122682</v>
+        <v>2.376357347646351</v>
       </c>
       <c r="F459">
         <v>-1</v>
       </c>
       <c r="G459">
-        <v>0.003873980530737433</v>
+        <v>0.003420694259234566</v>
       </c>
       <c r="H459">
-        <v>0.003901849079877319</v>
+        <v>0.002883642652353649</v>
       </c>
       <c r="I459">
-        <v>-0.03213145086011515</v>
+        <v>0.5029483931190826</v>
       </c>
       <c r="J459">
         <v>0.2131450860114693</v>
       </c>
       <c r="K459">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L459">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M459">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N459">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O459">
         <v>1</v>
@@ -24348,52 +24348,52 @@
     </row>
     <row r="461" spans="1:16">
       <c r="A461" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B461" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C461">
-        <v>3.085589532934493</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D461" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E461">
-        <v>3.118644864954661</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F461">
         <v>-1</v>
       </c>
       <c r="G461">
-        <v>0.004014410467065507</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H461">
-        <v>0.004041355135045339</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I461">
-        <v>-0.03305533202016786</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J461">
-        <v>0.3055332020167811</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K461">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L461">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M461">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N461">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O461">
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24404,28 +24404,28 @@
         <v>54</v>
       </c>
       <c r="C462">
-        <v>2.702231862141191</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D462" t="s">
         <v>125</v>
       </c>
       <c r="E462">
-        <v>2.210437729092927</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F462">
         <v>-1</v>
       </c>
       <c r="G462">
-        <v>0.003597768137858809</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H462">
-        <v>0.003049562270907073</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I462">
-        <v>0.491794133048264</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J462">
-        <v>0.3525733368967002</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K462">
         <v>1.27</v>
@@ -24443,7 +24443,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24454,28 +24454,28 @@
         <v>54</v>
       </c>
       <c r="C463">
-        <v>2.65619166177536</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D463" t="s">
         <v>125</v>
       </c>
       <c r="E463">
-        <v>2.167297698828881</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F463">
         <v>-1</v>
       </c>
       <c r="G463">
-        <v>0.00364380833822464</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H463">
-        <v>0.003092702301171119</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I463">
-        <v>0.4888939629464795</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J463">
-        <v>0.3888254631690077</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K463">
         <v>1.27</v>
@@ -24493,7 +24493,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24504,28 +24504,28 @@
         <v>54</v>
       </c>
       <c r="C464">
-        <v>2.633560752891249</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D464" t="s">
         <v>125</v>
       </c>
       <c r="E464">
-        <v>2.146092359008336</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F464">
         <v>-1</v>
       </c>
       <c r="G464">
-        <v>0.003666439247108751</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H464">
-        <v>0.003113907640991664</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I464">
-        <v>0.4874683938829132</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J464">
-        <v>0.4066450764635833</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K464">
         <v>1.27</v>
@@ -24543,7 +24543,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24554,28 +24554,28 @@
         <v>54</v>
       </c>
       <c r="C465">
-        <v>2.575080697535542</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D465" t="s">
         <v>125</v>
       </c>
       <c r="E465">
-        <v>2.091296086667161</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F465">
         <v>-1</v>
       </c>
       <c r="G465">
-        <v>0.003724919302464458</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H465">
-        <v>0.003168703913332839</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I465">
-        <v>0.4837846108683808</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J465">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K465">
         <v>1.27</v>
@@ -24593,7 +24593,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24604,28 +24604,28 @@
         <v>53</v>
       </c>
       <c r="C466">
-        <v>2.861907606499231</v>
+        <v>2.801763208907002</v>
       </c>
       <c r="D466" t="s">
         <v>124</v>
       </c>
       <c r="E466">
-        <v>2.896434530140684</v>
+        <v>2.836685819374719</v>
       </c>
       <c r="F466">
         <v>-1</v>
       </c>
       <c r="G466">
-        <v>0.004238092393500768</v>
+        <v>0.004298236791092998</v>
       </c>
       <c r="H466">
-        <v>0.004263565469859316</v>
+        <v>0.004323314180625281</v>
       </c>
       <c r="I466">
-        <v>-0.03452692364145271</v>
+        <v>-0.03492261046771716</v>
       </c>
       <c r="J466">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K466">
         <v>1.52</v>
@@ -24643,106 +24643,6 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="467" spans="1:16">
-      <c r="A467" s="1">
-        <v>0</v>
-      </c>
-      <c r="B467" t="s">
-        <v>54</v>
-      </c>
-      <c r="C467">
-        <v>2.524828470599929</v>
-      </c>
-      <c r="D467" t="s">
-        <v>125</v>
-      </c>
-      <c r="E467">
-        <v>2.044209354341666</v>
-      </c>
-      <c r="F467">
-        <v>-1</v>
-      </c>
-      <c r="G467">
-        <v>0.003775171529400071</v>
-      </c>
-      <c r="H467">
-        <v>0.003215790645658334</v>
-      </c>
-      <c r="I467">
-        <v>0.4806191162582629</v>
-      </c>
-      <c r="J467">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K467">
-        <v>1.27</v>
-      </c>
-      <c r="L467">
-        <v>3.15</v>
-      </c>
-      <c r="M467">
-        <v>1.19</v>
-      </c>
-      <c r="N467">
-        <v>2.63</v>
-      </c>
-      <c r="O467">
-        <v>1</v>
-      </c>
-      <c r="P467" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="468" spans="1:16">
-      <c r="A468" s="1">
-        <v>1</v>
-      </c>
-      <c r="B468" t="s">
-        <v>53</v>
-      </c>
-      <c r="C468">
-        <v>2.801763208907002</v>
-      </c>
-      <c r="D468" t="s">
-        <v>124</v>
-      </c>
-      <c r="E468">
-        <v>2.836685819374719</v>
-      </c>
-      <c r="F468">
-        <v>-1</v>
-      </c>
-      <c r="G468">
-        <v>0.004298236791092998</v>
-      </c>
-      <c r="H468">
-        <v>0.004323314180625281</v>
-      </c>
-      <c r="I468">
-        <v>-0.03492261046771716</v>
-      </c>
-      <c r="J468">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K468">
-        <v>1.52</v>
-      </c>
-      <c r="L468">
-        <v>3.55</v>
-      </c>
-      <c r="M468">
-        <v>1.51</v>
-      </c>
-      <c r="N468">
-        <v>3.58</v>
-      </c>
-      <c r="O468">
-        <v>1</v>
-      </c>
-      <c r="P468" t="s">
         <v>324</v>
       </c>
     </row>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="324">
   <si>
     <t>trade_time</t>
   </si>
@@ -965,9 +965,6 @@
   </si>
   <si>
     <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>2021-02-09</t>
   </si>
   <si>
     <t>2021-02-10</t>
@@ -1346,7 +1343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P466"/>
+  <dimension ref="A1:P464"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24201,43 +24198,43 @@
         <v>0</v>
       </c>
       <c r="B458" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C458">
-        <v>3.29749980927481</v>
+        <v>2.879305740765434</v>
       </c>
       <c r="D458" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E458">
-        <v>3.329160994740108</v>
+        <v>2.376357347646351</v>
       </c>
       <c r="F458">
         <v>-1</v>
       </c>
       <c r="G458">
-        <v>0.00380250019072519</v>
+        <v>0.003420694259234566</v>
       </c>
       <c r="H458">
-        <v>0.003830839005259893</v>
+        <v>0.002883642652353649</v>
       </c>
       <c r="I458">
-        <v>-0.0316611854652975</v>
+        <v>0.5029483931190826</v>
       </c>
       <c r="J458">
-        <v>0.16611854652973</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K458">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L458">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M458">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N458">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O458">
         <v>1</v>
@@ -24254,28 +24251,28 @@
         <v>54</v>
       </c>
       <c r="C459">
-        <v>2.879305740765434</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="D459" t="s">
         <v>125</v>
       </c>
       <c r="E459">
-        <v>2.376357347646351</v>
+        <v>2.26641548960003</v>
       </c>
       <c r="F459">
         <v>-1</v>
       </c>
       <c r="G459">
-        <v>0.003420694259234566</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="H459">
-        <v>0.002883642652353649</v>
+        <v>0.00299358451039997</v>
       </c>
       <c r="I459">
-        <v>0.5029483931190826</v>
+        <v>0.4955573438386578</v>
       </c>
       <c r="J459">
-        <v>0.2131450860114693</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K459">
         <v>1.27</v>
@@ -24304,28 +24301,28 @@
         <v>54</v>
       </c>
       <c r="C460">
-        <v>2.761972833438688</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D460" t="s">
         <v>125</v>
       </c>
       <c r="E460">
-        <v>2.26641548960003</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F460">
         <v>-1</v>
       </c>
       <c r="G460">
-        <v>0.003538027166561312</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H460">
-        <v>0.00299358451039997</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I460">
-        <v>0.4955573438386578</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J460">
-        <v>0.3055332020167811</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K460">
         <v>1.27</v>
@@ -24354,28 +24351,28 @@
         <v>54</v>
       </c>
       <c r="C461">
-        <v>2.702231862141191</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D461" t="s">
         <v>125</v>
       </c>
       <c r="E461">
-        <v>2.210437729092927</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F461">
         <v>-1</v>
       </c>
       <c r="G461">
-        <v>0.003597768137858809</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H461">
-        <v>0.003049562270907073</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I461">
-        <v>0.491794133048264</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J461">
-        <v>0.3525733368967002</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K461">
         <v>1.27</v>
@@ -24404,28 +24401,28 @@
         <v>54</v>
       </c>
       <c r="C462">
-        <v>2.65619166177536</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D462" t="s">
         <v>125</v>
       </c>
       <c r="E462">
-        <v>2.167297698828881</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F462">
         <v>-1</v>
       </c>
       <c r="G462">
-        <v>0.00364380833822464</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H462">
-        <v>0.003092702301171119</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I462">
-        <v>0.4888939629464795</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J462">
-        <v>0.3888254631690077</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K462">
         <v>1.27</v>
@@ -24454,28 +24451,28 @@
         <v>54</v>
       </c>
       <c r="C463">
-        <v>2.633560752891249</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D463" t="s">
         <v>125</v>
       </c>
       <c r="E463">
-        <v>2.146092359008336</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F463">
         <v>-1</v>
       </c>
       <c r="G463">
-        <v>0.003666439247108751</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H463">
-        <v>0.003113907640991664</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I463">
-        <v>0.4874683938829132</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J463">
-        <v>0.4066450764635833</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K463">
         <v>1.27</v>
@@ -24504,28 +24501,28 @@
         <v>54</v>
       </c>
       <c r="C464">
-        <v>2.575080697535542</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D464" t="s">
         <v>125</v>
       </c>
       <c r="E464">
-        <v>2.091296086667161</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F464">
         <v>-1</v>
       </c>
       <c r="G464">
-        <v>0.003724919302464458</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H464">
-        <v>0.003168703913332839</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I464">
-        <v>0.4837846108683808</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J464">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K464">
         <v>1.27</v>
@@ -24544,106 +24541,6 @@
       </c>
       <c r="P464" t="s">
         <v>323</v>
-      </c>
-    </row>
-    <row r="465" spans="1:16">
-      <c r="A465" s="1">
-        <v>0</v>
-      </c>
-      <c r="B465" t="s">
-        <v>54</v>
-      </c>
-      <c r="C465">
-        <v>2.524828470599929</v>
-      </c>
-      <c r="D465" t="s">
-        <v>125</v>
-      </c>
-      <c r="E465">
-        <v>2.044209354341666</v>
-      </c>
-      <c r="F465">
-        <v>-1</v>
-      </c>
-      <c r="G465">
-        <v>0.003775171529400071</v>
-      </c>
-      <c r="H465">
-        <v>0.003215790645658334</v>
-      </c>
-      <c r="I465">
-        <v>0.4806191162582629</v>
-      </c>
-      <c r="J465">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K465">
-        <v>1.27</v>
-      </c>
-      <c r="L465">
-        <v>3.15</v>
-      </c>
-      <c r="M465">
-        <v>1.19</v>
-      </c>
-      <c r="N465">
-        <v>2.63</v>
-      </c>
-      <c r="O465">
-        <v>1</v>
-      </c>
-      <c r="P465" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="466" spans="1:16">
-      <c r="A466" s="1">
-        <v>1</v>
-      </c>
-      <c r="B466" t="s">
-        <v>53</v>
-      </c>
-      <c r="C466">
-        <v>2.801763208907002</v>
-      </c>
-      <c r="D466" t="s">
-        <v>124</v>
-      </c>
-      <c r="E466">
-        <v>2.836685819374719</v>
-      </c>
-      <c r="F466">
-        <v>-1</v>
-      </c>
-      <c r="G466">
-        <v>0.004298236791092998</v>
-      </c>
-      <c r="H466">
-        <v>0.004323314180625281</v>
-      </c>
-      <c r="I466">
-        <v>-0.03492261046771716</v>
-      </c>
-      <c r="J466">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K466">
-        <v>1.52</v>
-      </c>
-      <c r="L466">
-        <v>3.55</v>
-      </c>
-      <c r="M466">
-        <v>1.51</v>
-      </c>
-      <c r="N466">
-        <v>3.58</v>
-      </c>
-      <c r="O466">
-        <v>1</v>
-      </c>
-      <c r="P466" t="s">
-        <v>324</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="323">
   <si>
     <t>trade_time</t>
   </si>
@@ -962,9 +962,6 @@
   </si>
   <si>
     <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
   </si>
   <si>
     <t>2021-02-10</t>
@@ -1343,7 +1340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P464"/>
+  <dimension ref="A1:P463"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24148,43 +24145,43 @@
         <v>0</v>
       </c>
       <c r="B457" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C457">
-        <v>3.350459894428295</v>
+        <v>2.879305740765434</v>
       </c>
       <c r="D457" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E457">
-        <v>3.381772658280741</v>
+        <v>2.376357347646351</v>
       </c>
       <c r="F457">
         <v>-1</v>
       </c>
       <c r="G457">
-        <v>0.003749540105571705</v>
+        <v>0.003420694259234566</v>
       </c>
       <c r="H457">
-        <v>0.00377822734171926</v>
+        <v>0.002883642652353649</v>
       </c>
       <c r="I457">
-        <v>-0.03131276385244552</v>
+        <v>0.5029483931190826</v>
       </c>
       <c r="J457">
-        <v>0.1312763852445424</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K457">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L457">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M457">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N457">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O457">
         <v>1</v>
@@ -24201,28 +24198,28 @@
         <v>54</v>
       </c>
       <c r="C458">
-        <v>2.879305740765434</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="D458" t="s">
         <v>125</v>
       </c>
       <c r="E458">
-        <v>2.376357347646351</v>
+        <v>2.26641548960003</v>
       </c>
       <c r="F458">
         <v>-1</v>
       </c>
       <c r="G458">
-        <v>0.003420694259234566</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="H458">
-        <v>0.002883642652353649</v>
+        <v>0.00299358451039997</v>
       </c>
       <c r="I458">
-        <v>0.5029483931190826</v>
+        <v>0.4955573438386578</v>
       </c>
       <c r="J458">
-        <v>0.2131450860114693</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K458">
         <v>1.27</v>
@@ -24251,28 +24248,28 @@
         <v>54</v>
       </c>
       <c r="C459">
-        <v>2.761972833438688</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D459" t="s">
         <v>125</v>
       </c>
       <c r="E459">
-        <v>2.26641548960003</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F459">
         <v>-1</v>
       </c>
       <c r="G459">
-        <v>0.003538027166561312</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H459">
-        <v>0.00299358451039997</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I459">
-        <v>0.4955573438386578</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J459">
-        <v>0.3055332020167811</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K459">
         <v>1.27</v>
@@ -24301,28 +24298,28 @@
         <v>54</v>
       </c>
       <c r="C460">
-        <v>2.702231862141191</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D460" t="s">
         <v>125</v>
       </c>
       <c r="E460">
-        <v>2.210437729092927</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F460">
         <v>-1</v>
       </c>
       <c r="G460">
-        <v>0.003597768137858809</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H460">
-        <v>0.003049562270907073</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I460">
-        <v>0.491794133048264</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J460">
-        <v>0.3525733368967002</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K460">
         <v>1.27</v>
@@ -24351,28 +24348,28 @@
         <v>54</v>
       </c>
       <c r="C461">
-        <v>2.65619166177536</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D461" t="s">
         <v>125</v>
       </c>
       <c r="E461">
-        <v>2.167297698828881</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F461">
         <v>-1</v>
       </c>
       <c r="G461">
-        <v>0.00364380833822464</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H461">
-        <v>0.003092702301171119</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I461">
-        <v>0.4888939629464795</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J461">
-        <v>0.3888254631690077</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K461">
         <v>1.27</v>
@@ -24401,28 +24398,28 @@
         <v>54</v>
       </c>
       <c r="C462">
-        <v>2.633560752891249</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D462" t="s">
         <v>125</v>
       </c>
       <c r="E462">
-        <v>2.146092359008336</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F462">
         <v>-1</v>
       </c>
       <c r="G462">
-        <v>0.003666439247108751</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H462">
-        <v>0.003113907640991664</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I462">
-        <v>0.4874683938829132</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J462">
-        <v>0.4066450764635833</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K462">
         <v>1.27</v>
@@ -24451,28 +24448,28 @@
         <v>54</v>
       </c>
       <c r="C463">
-        <v>2.575080697535542</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D463" t="s">
         <v>125</v>
       </c>
       <c r="E463">
-        <v>2.091296086667161</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F463">
         <v>-1</v>
       </c>
       <c r="G463">
-        <v>0.003724919302464458</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H463">
-        <v>0.003168703913332839</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I463">
-        <v>0.4837846108683808</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J463">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K463">
         <v>1.27</v>
@@ -24491,56 +24488,6 @@
       </c>
       <c r="P463" t="s">
         <v>322</v>
-      </c>
-    </row>
-    <row r="464" spans="1:16">
-      <c r="A464" s="1">
-        <v>0</v>
-      </c>
-      <c r="B464" t="s">
-        <v>54</v>
-      </c>
-      <c r="C464">
-        <v>2.524828470599929</v>
-      </c>
-      <c r="D464" t="s">
-        <v>125</v>
-      </c>
-      <c r="E464">
-        <v>2.044209354341666</v>
-      </c>
-      <c r="F464">
-        <v>-1</v>
-      </c>
-      <c r="G464">
-        <v>0.003775171529400071</v>
-      </c>
-      <c r="H464">
-        <v>0.003215790645658334</v>
-      </c>
-      <c r="I464">
-        <v>0.4806191162582629</v>
-      </c>
-      <c r="J464">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K464">
-        <v>1.27</v>
-      </c>
-      <c r="L464">
-        <v>3.15</v>
-      </c>
-      <c r="M464">
-        <v>1.19</v>
-      </c>
-      <c r="N464">
-        <v>2.63</v>
-      </c>
-      <c r="O464">
-        <v>1</v>
-      </c>
-      <c r="P464" t="s">
-        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="322">
   <si>
     <t>trade_time</t>
   </si>
@@ -959,9 +959,6 @@
   </si>
   <si>
     <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
   </si>
   <si>
     <t>2021-02-10</t>
@@ -1340,7 +1337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P463"/>
+  <dimension ref="A1:P462"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24095,43 +24092,43 @@
         <v>0</v>
       </c>
       <c r="B456" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C456">
-        <v>3.379912288774229</v>
+        <v>2.879305740765434</v>
       </c>
       <c r="D456" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E456">
-        <v>3.411031286874399</v>
+        <v>2.376357347646351</v>
       </c>
       <c r="F456">
         <v>-1</v>
       </c>
       <c r="G456">
-        <v>0.00372008771122577</v>
+        <v>0.003420694259234566</v>
       </c>
       <c r="H456">
-        <v>0.003748968713125601</v>
+        <v>0.002883642652353649</v>
       </c>
       <c r="I456">
-        <v>-0.03111899810016983</v>
+        <v>0.5029483931190826</v>
       </c>
       <c r="J456">
-        <v>0.1118998100169543</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K456">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L456">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M456">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N456">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O456">
         <v>1</v>
@@ -24148,28 +24145,28 @@
         <v>54</v>
       </c>
       <c r="C457">
-        <v>2.879305740765434</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="D457" t="s">
         <v>125</v>
       </c>
       <c r="E457">
-        <v>2.376357347646351</v>
+        <v>2.26641548960003</v>
       </c>
       <c r="F457">
         <v>-1</v>
       </c>
       <c r="G457">
-        <v>0.003420694259234566</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="H457">
-        <v>0.002883642652353649</v>
+        <v>0.00299358451039997</v>
       </c>
       <c r="I457">
-        <v>0.5029483931190826</v>
+        <v>0.4955573438386578</v>
       </c>
       <c r="J457">
-        <v>0.2131450860114693</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K457">
         <v>1.27</v>
@@ -24198,28 +24195,28 @@
         <v>54</v>
       </c>
       <c r="C458">
-        <v>2.761972833438688</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D458" t="s">
         <v>125</v>
       </c>
       <c r="E458">
-        <v>2.26641548960003</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F458">
         <v>-1</v>
       </c>
       <c r="G458">
-        <v>0.003538027166561312</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H458">
-        <v>0.00299358451039997</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I458">
-        <v>0.4955573438386578</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J458">
-        <v>0.3055332020167811</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K458">
         <v>1.27</v>
@@ -24248,28 +24245,28 @@
         <v>54</v>
       </c>
       <c r="C459">
-        <v>2.702231862141191</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D459" t="s">
         <v>125</v>
       </c>
       <c r="E459">
-        <v>2.210437729092927</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F459">
         <v>-1</v>
       </c>
       <c r="G459">
-        <v>0.003597768137858809</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H459">
-        <v>0.003049562270907073</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I459">
-        <v>0.491794133048264</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J459">
-        <v>0.3525733368967002</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K459">
         <v>1.27</v>
@@ -24298,28 +24295,28 @@
         <v>54</v>
       </c>
       <c r="C460">
-        <v>2.65619166177536</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D460" t="s">
         <v>125</v>
       </c>
       <c r="E460">
-        <v>2.167297698828881</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F460">
         <v>-1</v>
       </c>
       <c r="G460">
-        <v>0.00364380833822464</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H460">
-        <v>0.003092702301171119</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I460">
-        <v>0.4888939629464795</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J460">
-        <v>0.3888254631690077</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K460">
         <v>1.27</v>
@@ -24348,28 +24345,28 @@
         <v>54</v>
       </c>
       <c r="C461">
-        <v>2.633560752891249</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D461" t="s">
         <v>125</v>
       </c>
       <c r="E461">
-        <v>2.146092359008336</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F461">
         <v>-1</v>
       </c>
       <c r="G461">
-        <v>0.003666439247108751</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H461">
-        <v>0.003113907640991664</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I461">
-        <v>0.4874683938829132</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J461">
-        <v>0.4066450764635833</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K461">
         <v>1.27</v>
@@ -24398,28 +24395,28 @@
         <v>54</v>
       </c>
       <c r="C462">
-        <v>2.575080697535542</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D462" t="s">
         <v>125</v>
       </c>
       <c r="E462">
-        <v>2.091296086667161</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F462">
         <v>-1</v>
       </c>
       <c r="G462">
-        <v>0.003724919302464458</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H462">
-        <v>0.003168703913332839</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I462">
-        <v>0.4837846108683808</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J462">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K462">
         <v>1.27</v>
@@ -24438,56 +24435,6 @@
       </c>
       <c r="P462" t="s">
         <v>321</v>
-      </c>
-    </row>
-    <row r="463" spans="1:16">
-      <c r="A463" s="1">
-        <v>0</v>
-      </c>
-      <c r="B463" t="s">
-        <v>54</v>
-      </c>
-      <c r="C463">
-        <v>2.524828470599929</v>
-      </c>
-      <c r="D463" t="s">
-        <v>125</v>
-      </c>
-      <c r="E463">
-        <v>2.044209354341666</v>
-      </c>
-      <c r="F463">
-        <v>-1</v>
-      </c>
-      <c r="G463">
-        <v>0.003775171529400071</v>
-      </c>
-      <c r="H463">
-        <v>0.003215790645658334</v>
-      </c>
-      <c r="I463">
-        <v>0.4806191162582629</v>
-      </c>
-      <c r="J463">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K463">
-        <v>1.27</v>
-      </c>
-      <c r="L463">
-        <v>3.15</v>
-      </c>
-      <c r="M463">
-        <v>1.19</v>
-      </c>
-      <c r="N463">
-        <v>2.63</v>
-      </c>
-      <c r="O463">
-        <v>1</v>
-      </c>
-      <c r="P463" t="s">
-        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -958,7 +958,7 @@
     <t>2021-02-03</t>
   </si>
   <si>
-    <t>2021-02-04</t>
+    <t>2021-02-09</t>
   </si>
   <si>
     <t>2021-02-10</t>
@@ -24042,43 +24042,43 @@
         <v>0</v>
       </c>
       <c r="B455" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C455">
-        <v>3.393731929090075</v>
+        <v>2.939029445907243</v>
       </c>
       <c r="D455" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E455">
-        <v>3.424760008503956</v>
+        <v>2.432318929629621</v>
       </c>
       <c r="F455">
         <v>-1</v>
       </c>
       <c r="G455">
-        <v>0.003706268070909925</v>
+        <v>0.003360970554092757</v>
       </c>
       <c r="H455">
-        <v>0.003735239991496044</v>
+        <v>0.002827681070370379</v>
       </c>
       <c r="I455">
-        <v>-0.0310280794138813</v>
+        <v>0.5067105162776215</v>
       </c>
       <c r="J455">
-        <v>0.1028079413881086</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K455">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L455">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M455">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N455">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O455">
         <v>1</v>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="321">
   <si>
     <t>trade_time</t>
   </si>
@@ -953,9 +953,6 @@
   </si>
   <si>
     <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
   </si>
   <si>
     <t>2021-02-09</t>
@@ -1337,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P462"/>
+  <dimension ref="A1:P461"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -23992,43 +23989,43 @@
         <v>0</v>
       </c>
       <c r="B454" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C454">
-        <v>3.386651569627924</v>
+        <v>2.939029445907243</v>
       </c>
       <c r="D454" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E454">
-        <v>3.417726230354056</v>
+        <v>2.432318929629621</v>
       </c>
       <c r="F454">
         <v>-1</v>
       </c>
       <c r="G454">
-        <v>0.003713348430372076</v>
+        <v>0.003360970554092757</v>
       </c>
       <c r="H454">
-        <v>0.003742273769645944</v>
+        <v>0.002827681070370379</v>
       </c>
       <c r="I454">
-        <v>-0.0310746607261323</v>
+        <v>0.5067105162776215</v>
       </c>
       <c r="J454">
-        <v>0.1074660726132081</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K454">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L454">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M454">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N454">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O454">
         <v>1</v>
@@ -24045,28 +24042,28 @@
         <v>54</v>
       </c>
       <c r="C455">
-        <v>2.939029445907243</v>
+        <v>2.879305740765434</v>
       </c>
       <c r="D455" t="s">
         <v>125</v>
       </c>
       <c r="E455">
-        <v>2.432318929629621</v>
+        <v>2.376357347646351</v>
       </c>
       <c r="F455">
         <v>-1</v>
       </c>
       <c r="G455">
-        <v>0.003360970554092757</v>
+        <v>0.003420694259234566</v>
       </c>
       <c r="H455">
-        <v>0.002827681070370379</v>
+        <v>0.002883642652353649</v>
       </c>
       <c r="I455">
-        <v>0.5067105162776215</v>
+        <v>0.5029483931190826</v>
       </c>
       <c r="J455">
-        <v>0.16611854652973</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K455">
         <v>1.27</v>
@@ -24095,28 +24092,28 @@
         <v>54</v>
       </c>
       <c r="C456">
-        <v>2.879305740765434</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="D456" t="s">
         <v>125</v>
       </c>
       <c r="E456">
-        <v>2.376357347646351</v>
+        <v>2.26641548960003</v>
       </c>
       <c r="F456">
         <v>-1</v>
       </c>
       <c r="G456">
-        <v>0.003420694259234566</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="H456">
-        <v>0.002883642652353649</v>
+        <v>0.00299358451039997</v>
       </c>
       <c r="I456">
-        <v>0.5029483931190826</v>
+        <v>0.4955573438386578</v>
       </c>
       <c r="J456">
-        <v>0.2131450860114693</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K456">
         <v>1.27</v>
@@ -24145,28 +24142,28 @@
         <v>54</v>
       </c>
       <c r="C457">
-        <v>2.761972833438688</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D457" t="s">
         <v>125</v>
       </c>
       <c r="E457">
-        <v>2.26641548960003</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F457">
         <v>-1</v>
       </c>
       <c r="G457">
-        <v>0.003538027166561312</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H457">
-        <v>0.00299358451039997</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I457">
-        <v>0.4955573438386578</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J457">
-        <v>0.3055332020167811</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K457">
         <v>1.27</v>
@@ -24195,28 +24192,28 @@
         <v>54</v>
       </c>
       <c r="C458">
-        <v>2.702231862141191</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D458" t="s">
         <v>125</v>
       </c>
       <c r="E458">
-        <v>2.210437729092927</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F458">
         <v>-1</v>
       </c>
       <c r="G458">
-        <v>0.003597768137858809</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H458">
-        <v>0.003049562270907073</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I458">
-        <v>0.491794133048264</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J458">
-        <v>0.3525733368967002</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K458">
         <v>1.27</v>
@@ -24245,28 +24242,28 @@
         <v>54</v>
       </c>
       <c r="C459">
-        <v>2.65619166177536</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D459" t="s">
         <v>125</v>
       </c>
       <c r="E459">
-        <v>2.167297698828881</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F459">
         <v>-1</v>
       </c>
       <c r="G459">
-        <v>0.00364380833822464</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H459">
-        <v>0.003092702301171119</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I459">
-        <v>0.4888939629464795</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J459">
-        <v>0.3888254631690077</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K459">
         <v>1.27</v>
@@ -24295,28 +24292,28 @@
         <v>54</v>
       </c>
       <c r="C460">
-        <v>2.633560752891249</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D460" t="s">
         <v>125</v>
       </c>
       <c r="E460">
-        <v>2.146092359008336</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F460">
         <v>-1</v>
       </c>
       <c r="G460">
-        <v>0.003666439247108751</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H460">
-        <v>0.003113907640991664</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I460">
-        <v>0.4874683938829132</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J460">
-        <v>0.4066450764635833</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K460">
         <v>1.27</v>
@@ -24345,28 +24342,28 @@
         <v>54</v>
       </c>
       <c r="C461">
-        <v>2.575080697535542</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D461" t="s">
         <v>125</v>
       </c>
       <c r="E461">
-        <v>2.091296086667161</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F461">
         <v>-1</v>
       </c>
       <c r="G461">
-        <v>0.003724919302464458</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H461">
-        <v>0.003168703913332839</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I461">
-        <v>0.4837846108683808</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J461">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K461">
         <v>1.27</v>
@@ -24385,56 +24382,6 @@
       </c>
       <c r="P461" t="s">
         <v>320</v>
-      </c>
-    </row>
-    <row r="462" spans="1:16">
-      <c r="A462" s="1">
-        <v>0</v>
-      </c>
-      <c r="B462" t="s">
-        <v>54</v>
-      </c>
-      <c r="C462">
-        <v>2.524828470599929</v>
-      </c>
-      <c r="D462" t="s">
-        <v>125</v>
-      </c>
-      <c r="E462">
-        <v>2.044209354341666</v>
-      </c>
-      <c r="F462">
-        <v>-1</v>
-      </c>
-      <c r="G462">
-        <v>0.003775171529400071</v>
-      </c>
-      <c r="H462">
-        <v>0.003215790645658334</v>
-      </c>
-      <c r="I462">
-        <v>0.4806191162582629</v>
-      </c>
-      <c r="J462">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K462">
-        <v>1.27</v>
-      </c>
-      <c r="L462">
-        <v>3.15</v>
-      </c>
-      <c r="M462">
-        <v>1.19</v>
-      </c>
-      <c r="N462">
-        <v>2.63</v>
-      </c>
-      <c r="O462">
-        <v>1</v>
-      </c>
-      <c r="P462" t="s">
-        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="320">
   <si>
     <t>trade_time</t>
   </si>
@@ -950,9 +950,6 @@
   </si>
   <si>
     <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
   </si>
   <si>
     <t>2021-02-09</t>
@@ -1334,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P461"/>
+  <dimension ref="A1:P460"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -23939,43 +23936,43 @@
         <v>0</v>
       </c>
       <c r="B453" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C453">
-        <v>3.398669636469118</v>
+        <v>2.939029445907243</v>
       </c>
       <c r="D453" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E453">
-        <v>3.429665230966032</v>
+        <v>2.432318929629621</v>
       </c>
       <c r="F453">
         <v>-1</v>
       </c>
       <c r="G453">
-        <v>0.003701330363530882</v>
+        <v>0.003360970554092757</v>
       </c>
       <c r="H453">
-        <v>0.003730334769033969</v>
+        <v>0.002827681070370379</v>
       </c>
       <c r="I453">
-        <v>-0.0309955944969138</v>
+        <v>0.5067105162776215</v>
       </c>
       <c r="J453">
-        <v>0.09955944969136986</v>
+        <v>0.16611854652973</v>
       </c>
       <c r="K453">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="L453">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M453">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="N453">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="O453">
         <v>1</v>
@@ -23992,28 +23989,28 @@
         <v>54</v>
       </c>
       <c r="C454">
-        <v>2.939029445907243</v>
+        <v>2.879305740765434</v>
       </c>
       <c r="D454" t="s">
         <v>125</v>
       </c>
       <c r="E454">
-        <v>2.432318929629621</v>
+        <v>2.376357347646351</v>
       </c>
       <c r="F454">
         <v>-1</v>
       </c>
       <c r="G454">
-        <v>0.003360970554092757</v>
+        <v>0.003420694259234566</v>
       </c>
       <c r="H454">
-        <v>0.002827681070370379</v>
+        <v>0.002883642652353649</v>
       </c>
       <c r="I454">
-        <v>0.5067105162776215</v>
+        <v>0.5029483931190826</v>
       </c>
       <c r="J454">
-        <v>0.16611854652973</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K454">
         <v>1.27</v>
@@ -24042,28 +24039,28 @@
         <v>54</v>
       </c>
       <c r="C455">
-        <v>2.879305740765434</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="D455" t="s">
         <v>125</v>
       </c>
       <c r="E455">
-        <v>2.376357347646351</v>
+        <v>2.26641548960003</v>
       </c>
       <c r="F455">
         <v>-1</v>
       </c>
       <c r="G455">
-        <v>0.003420694259234566</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="H455">
-        <v>0.002883642652353649</v>
+        <v>0.00299358451039997</v>
       </c>
       <c r="I455">
-        <v>0.5029483931190826</v>
+        <v>0.4955573438386578</v>
       </c>
       <c r="J455">
-        <v>0.2131450860114693</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K455">
         <v>1.27</v>
@@ -24092,28 +24089,28 @@
         <v>54</v>
       </c>
       <c r="C456">
-        <v>2.761972833438688</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D456" t="s">
         <v>125</v>
       </c>
       <c r="E456">
-        <v>2.26641548960003</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F456">
         <v>-1</v>
       </c>
       <c r="G456">
-        <v>0.003538027166561312</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H456">
-        <v>0.00299358451039997</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I456">
-        <v>0.4955573438386578</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J456">
-        <v>0.3055332020167811</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K456">
         <v>1.27</v>
@@ -24142,28 +24139,28 @@
         <v>54</v>
       </c>
       <c r="C457">
-        <v>2.702231862141191</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D457" t="s">
         <v>125</v>
       </c>
       <c r="E457">
-        <v>2.210437729092927</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F457">
         <v>-1</v>
       </c>
       <c r="G457">
-        <v>0.003597768137858809</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H457">
-        <v>0.003049562270907073</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I457">
-        <v>0.491794133048264</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J457">
-        <v>0.3525733368967002</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K457">
         <v>1.27</v>
@@ -24192,28 +24189,28 @@
         <v>54</v>
       </c>
       <c r="C458">
-        <v>2.65619166177536</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D458" t="s">
         <v>125</v>
       </c>
       <c r="E458">
-        <v>2.167297698828881</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F458">
         <v>-1</v>
       </c>
       <c r="G458">
-        <v>0.00364380833822464</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H458">
-        <v>0.003092702301171119</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I458">
-        <v>0.4888939629464795</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J458">
-        <v>0.3888254631690077</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K458">
         <v>1.27</v>
@@ -24242,28 +24239,28 @@
         <v>54</v>
       </c>
       <c r="C459">
-        <v>2.633560752891249</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D459" t="s">
         <v>125</v>
       </c>
       <c r="E459">
-        <v>2.146092359008336</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F459">
         <v>-1</v>
       </c>
       <c r="G459">
-        <v>0.003666439247108751</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H459">
-        <v>0.003113907640991664</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I459">
-        <v>0.4874683938829132</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J459">
-        <v>0.4066450764635833</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K459">
         <v>1.27</v>
@@ -24292,28 +24289,28 @@
         <v>54</v>
       </c>
       <c r="C460">
-        <v>2.575080697535542</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D460" t="s">
         <v>125</v>
       </c>
       <c r="E460">
-        <v>2.091296086667161</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F460">
         <v>-1</v>
       </c>
       <c r="G460">
-        <v>0.003724919302464458</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H460">
-        <v>0.003168703913332839</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I460">
-        <v>0.4837846108683808</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J460">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K460">
         <v>1.27</v>
@@ -24332,56 +24329,6 @@
       </c>
       <c r="P460" t="s">
         <v>319</v>
-      </c>
-    </row>
-    <row r="461" spans="1:16">
-      <c r="A461" s="1">
-        <v>0</v>
-      </c>
-      <c r="B461" t="s">
-        <v>54</v>
-      </c>
-      <c r="C461">
-        <v>2.524828470599929</v>
-      </c>
-      <c r="D461" t="s">
-        <v>125</v>
-      </c>
-      <c r="E461">
-        <v>2.044209354341666</v>
-      </c>
-      <c r="F461">
-        <v>-1</v>
-      </c>
-      <c r="G461">
-        <v>0.003775171529400071</v>
-      </c>
-      <c r="H461">
-        <v>0.003215790645658334</v>
-      </c>
-      <c r="I461">
-        <v>0.4806191162582629</v>
-      </c>
-      <c r="J461">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K461">
-        <v>1.27</v>
-      </c>
-      <c r="L461">
-        <v>3.15</v>
-      </c>
-      <c r="M461">
-        <v>1.19</v>
-      </c>
-      <c r="N461">
-        <v>2.63</v>
-      </c>
-      <c r="O461">
-        <v>1</v>
-      </c>
-      <c r="P461" t="s">
-        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="319">
   <si>
     <t>trade_time</t>
   </si>
@@ -950,9 +950,6 @@
   </si>
   <si>
     <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-09</t>
   </si>
   <si>
     <t>2021-02-10</t>
@@ -1331,7 +1328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P460"/>
+  <dimension ref="A1:P459"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -23939,28 +23936,28 @@
         <v>54</v>
       </c>
       <c r="C453">
-        <v>2.939029445907243</v>
+        <v>2.879305740765434</v>
       </c>
       <c r="D453" t="s">
         <v>125</v>
       </c>
       <c r="E453">
-        <v>2.432318929629621</v>
+        <v>2.376357347646351</v>
       </c>
       <c r="F453">
         <v>-1</v>
       </c>
       <c r="G453">
-        <v>0.003360970554092757</v>
+        <v>0.003420694259234566</v>
       </c>
       <c r="H453">
-        <v>0.002827681070370379</v>
+        <v>0.002883642652353649</v>
       </c>
       <c r="I453">
-        <v>0.5067105162776215</v>
+        <v>0.5029483931190826</v>
       </c>
       <c r="J453">
-        <v>0.16611854652973</v>
+        <v>0.2131450860114693</v>
       </c>
       <c r="K453">
         <v>1.27</v>
@@ -23989,28 +23986,28 @@
         <v>54</v>
       </c>
       <c r="C454">
-        <v>2.879305740765434</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="D454" t="s">
         <v>125</v>
       </c>
       <c r="E454">
-        <v>2.376357347646351</v>
+        <v>2.26641548960003</v>
       </c>
       <c r="F454">
         <v>-1</v>
       </c>
       <c r="G454">
-        <v>0.003420694259234566</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="H454">
-        <v>0.002883642652353649</v>
+        <v>0.00299358451039997</v>
       </c>
       <c r="I454">
-        <v>0.5029483931190826</v>
+        <v>0.4955573438386578</v>
       </c>
       <c r="J454">
-        <v>0.2131450860114693</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K454">
         <v>1.27</v>
@@ -24039,28 +24036,28 @@
         <v>54</v>
       </c>
       <c r="C455">
-        <v>2.761972833438688</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D455" t="s">
         <v>125</v>
       </c>
       <c r="E455">
-        <v>2.26641548960003</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F455">
         <v>-1</v>
       </c>
       <c r="G455">
-        <v>0.003538027166561312</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H455">
-        <v>0.00299358451039997</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I455">
-        <v>0.4955573438386578</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J455">
-        <v>0.3055332020167811</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K455">
         <v>1.27</v>
@@ -24089,28 +24086,28 @@
         <v>54</v>
       </c>
       <c r="C456">
-        <v>2.702231862141191</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D456" t="s">
         <v>125</v>
       </c>
       <c r="E456">
-        <v>2.210437729092927</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F456">
         <v>-1</v>
       </c>
       <c r="G456">
-        <v>0.003597768137858809</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H456">
-        <v>0.003049562270907073</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I456">
-        <v>0.491794133048264</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J456">
-        <v>0.3525733368967002</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K456">
         <v>1.27</v>
@@ -24139,28 +24136,28 @@
         <v>54</v>
       </c>
       <c r="C457">
-        <v>2.65619166177536</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D457" t="s">
         <v>125</v>
       </c>
       <c r="E457">
-        <v>2.167297698828881</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F457">
         <v>-1</v>
       </c>
       <c r="G457">
-        <v>0.00364380833822464</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H457">
-        <v>0.003092702301171119</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I457">
-        <v>0.4888939629464795</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J457">
-        <v>0.3888254631690077</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K457">
         <v>1.27</v>
@@ -24189,28 +24186,28 @@
         <v>54</v>
       </c>
       <c r="C458">
-        <v>2.633560752891249</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D458" t="s">
         <v>125</v>
       </c>
       <c r="E458">
-        <v>2.146092359008336</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F458">
         <v>-1</v>
       </c>
       <c r="G458">
-        <v>0.003666439247108751</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H458">
-        <v>0.003113907640991664</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I458">
-        <v>0.4874683938829132</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J458">
-        <v>0.4066450764635833</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K458">
         <v>1.27</v>
@@ -24239,28 +24236,28 @@
         <v>54</v>
       </c>
       <c r="C459">
-        <v>2.575080697535542</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D459" t="s">
         <v>125</v>
       </c>
       <c r="E459">
-        <v>2.091296086667161</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F459">
         <v>-1</v>
       </c>
       <c r="G459">
-        <v>0.003724919302464458</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H459">
-        <v>0.003168703913332839</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I459">
-        <v>0.4837846108683808</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J459">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K459">
         <v>1.27</v>
@@ -24279,56 +24276,6 @@
       </c>
       <c r="P459" t="s">
         <v>318</v>
-      </c>
-    </row>
-    <row r="460" spans="1:16">
-      <c r="A460" s="1">
-        <v>0</v>
-      </c>
-      <c r="B460" t="s">
-        <v>54</v>
-      </c>
-      <c r="C460">
-        <v>2.524828470599929</v>
-      </c>
-      <c r="D460" t="s">
-        <v>125</v>
-      </c>
-      <c r="E460">
-        <v>2.044209354341666</v>
-      </c>
-      <c r="F460">
-        <v>-1</v>
-      </c>
-      <c r="G460">
-        <v>0.003775171529400071</v>
-      </c>
-      <c r="H460">
-        <v>0.003215790645658334</v>
-      </c>
-      <c r="I460">
-        <v>0.4806191162582629</v>
-      </c>
-      <c r="J460">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K460">
-        <v>1.27</v>
-      </c>
-      <c r="L460">
-        <v>3.15</v>
-      </c>
-      <c r="M460">
-        <v>1.19</v>
-      </c>
-      <c r="N460">
-        <v>2.63</v>
-      </c>
-      <c r="O460">
-        <v>1</v>
-      </c>
-      <c r="P460" t="s">
-        <v>319</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="318">
   <si>
     <t>trade_time</t>
   </si>
@@ -950,9 +950,6 @@
   </si>
   <si>
     <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
   </si>
   <si>
     <t>2021-02-18</t>
@@ -1328,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P459"/>
+  <dimension ref="A1:P458"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -23936,28 +23933,28 @@
         <v>54</v>
       </c>
       <c r="C453">
-        <v>2.879305740765434</v>
+        <v>2.761972833438688</v>
       </c>
       <c r="D453" t="s">
         <v>125</v>
       </c>
       <c r="E453">
-        <v>2.376357347646351</v>
+        <v>2.26641548960003</v>
       </c>
       <c r="F453">
         <v>-1</v>
       </c>
       <c r="G453">
-        <v>0.003420694259234566</v>
+        <v>0.003538027166561312</v>
       </c>
       <c r="H453">
-        <v>0.002883642652353649</v>
+        <v>0.00299358451039997</v>
       </c>
       <c r="I453">
-        <v>0.5029483931190826</v>
+        <v>0.4955573438386578</v>
       </c>
       <c r="J453">
-        <v>0.2131450860114693</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K453">
         <v>1.27</v>
@@ -23986,28 +23983,28 @@
         <v>54</v>
       </c>
       <c r="C454">
-        <v>2.761972833438688</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D454" t="s">
         <v>125</v>
       </c>
       <c r="E454">
-        <v>2.26641548960003</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F454">
         <v>-1</v>
       </c>
       <c r="G454">
-        <v>0.003538027166561312</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H454">
-        <v>0.00299358451039997</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I454">
-        <v>0.4955573438386578</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J454">
-        <v>0.3055332020167811</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K454">
         <v>1.27</v>
@@ -24036,28 +24033,28 @@
         <v>54</v>
       </c>
       <c r="C455">
-        <v>2.702231862141191</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D455" t="s">
         <v>125</v>
       </c>
       <c r="E455">
-        <v>2.210437729092927</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F455">
         <v>-1</v>
       </c>
       <c r="G455">
-        <v>0.003597768137858809</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H455">
-        <v>0.003049562270907073</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I455">
-        <v>0.491794133048264</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J455">
-        <v>0.3525733368967002</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K455">
         <v>1.27</v>
@@ -24086,28 +24083,28 @@
         <v>54</v>
       </c>
       <c r="C456">
-        <v>2.65619166177536</v>
+        <v>2.633560752891249</v>
       </c>
       <c r="D456" t="s">
         <v>125</v>
       </c>
       <c r="E456">
-        <v>2.167297698828881</v>
+        <v>2.146092359008336</v>
       </c>
       <c r="F456">
         <v>-1</v>
       </c>
       <c r="G456">
-        <v>0.00364380833822464</v>
+        <v>0.003666439247108751</v>
       </c>
       <c r="H456">
-        <v>0.003092702301171119</v>
+        <v>0.003113907640991664</v>
       </c>
       <c r="I456">
-        <v>0.4888939629464795</v>
+        <v>0.4874683938829132</v>
       </c>
       <c r="J456">
-        <v>0.3888254631690077</v>
+        <v>0.4066450764635833</v>
       </c>
       <c r="K456">
         <v>1.27</v>
@@ -24136,28 +24133,28 @@
         <v>54</v>
       </c>
       <c r="C457">
-        <v>2.633560752891249</v>
+        <v>2.575080697535542</v>
       </c>
       <c r="D457" t="s">
         <v>125</v>
       </c>
       <c r="E457">
-        <v>2.146092359008336</v>
+        <v>2.091296086667161</v>
       </c>
       <c r="F457">
         <v>-1</v>
       </c>
       <c r="G457">
-        <v>0.003666439247108751</v>
+        <v>0.003724919302464458</v>
       </c>
       <c r="H457">
-        <v>0.003113907640991664</v>
+        <v>0.003168703913332839</v>
       </c>
       <c r="I457">
-        <v>0.4874683938829132</v>
+        <v>0.4837846108683808</v>
       </c>
       <c r="J457">
-        <v>0.4066450764635833</v>
+        <v>0.4526923641452424</v>
       </c>
       <c r="K457">
         <v>1.27</v>
@@ -24186,28 +24183,28 @@
         <v>54</v>
       </c>
       <c r="C458">
-        <v>2.575080697535542</v>
+        <v>2.524828470599929</v>
       </c>
       <c r="D458" t="s">
         <v>125</v>
       </c>
       <c r="E458">
-        <v>2.091296086667161</v>
+        <v>2.044209354341666</v>
       </c>
       <c r="F458">
         <v>-1</v>
       </c>
       <c r="G458">
-        <v>0.003724919302464458</v>
+        <v>0.003775171529400071</v>
       </c>
       <c r="H458">
-        <v>0.003168703913332839</v>
+        <v>0.003215790645658334</v>
       </c>
       <c r="I458">
-        <v>0.4837846108683808</v>
+        <v>0.4806191162582629</v>
       </c>
       <c r="J458">
-        <v>0.4526923641452424</v>
+        <v>0.4922610467717091</v>
       </c>
       <c r="K458">
         <v>1.27</v>
@@ -24226,56 +24223,6 @@
       </c>
       <c r="P458" t="s">
         <v>317</v>
-      </c>
-    </row>
-    <row r="459" spans="1:16">
-      <c r="A459" s="1">
-        <v>0</v>
-      </c>
-      <c r="B459" t="s">
-        <v>54</v>
-      </c>
-      <c r="C459">
-        <v>2.524828470599929</v>
-      </c>
-      <c r="D459" t="s">
-        <v>125</v>
-      </c>
-      <c r="E459">
-        <v>2.044209354341666</v>
-      </c>
-      <c r="F459">
-        <v>-1</v>
-      </c>
-      <c r="G459">
-        <v>0.003775171529400071</v>
-      </c>
-      <c r="H459">
-        <v>0.003215790645658334</v>
-      </c>
-      <c r="I459">
-        <v>0.4806191162582629</v>
-      </c>
-      <c r="J459">
-        <v>0.4922610467717091</v>
-      </c>
-      <c r="K459">
-        <v>1.27</v>
-      </c>
-      <c r="L459">
-        <v>3.15</v>
-      </c>
-      <c r="M459">
-        <v>1.19</v>
-      </c>
-      <c r="N459">
-        <v>2.63</v>
-      </c>
-      <c r="O459">
-        <v>1</v>
-      </c>
-      <c r="P459" t="s">
-        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00991-601991.xlsx
+++ b/s60_signal/position-00991-601991.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="322">
   <si>
     <t>trade_time</t>
   </si>
@@ -181,6 +181,12 @@
     <t>2021-03-23</t>
   </si>
   <si>
+    <t>2021-12-23</t>
+  </si>
+  <si>
+    <t>2021-12-24</t>
+  </si>
+  <si>
     <t>2017-06-12</t>
   </si>
   <si>
@@ -392,6 +398,12 @@
   </si>
   <si>
     <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>2021-12-28</t>
+  </si>
+  <si>
+    <t>2021-12-29</t>
   </si>
   <si>
     <t>2016-12-09</t>
@@ -1325,7 +1337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P458"/>
+  <dimension ref="A1:P467"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1386,7 +1398,7 @@
         <v>3.46886509305629</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2">
         <v>2.855669161372308</v>
@@ -1422,7 +1434,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1436,7 +1448,7 @@
         <v>3.452436406068187</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>2.838213681447448</v>
@@ -1472,7 +1484,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1486,7 +1498,7 @@
         <v>3.38636654658805</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>2.768014455749804</v>
@@ -1522,7 +1534,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1536,7 +1548,7 @@
         <v>3.3413361776263</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>2.720169688727944</v>
@@ -1572,7 +1584,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1586,7 +1598,7 @@
         <v>3.300464501418125</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E6">
         <v>2.676743532756758</v>
@@ -1622,7 +1634,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1636,7 +1648,7 @@
         <v>3.273900806743327</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7">
         <v>2.648519607164785</v>
@@ -1672,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1686,7 +1698,7 @@
         <v>3.266088352200639</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>2.640218874213179</v>
@@ -1722,7 +1734,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1736,7 +1748,7 @@
         <v>3.262031126351886</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9">
         <v>2.635908071748879</v>
@@ -1772,7 +1784,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1786,7 +1798,7 @@
         <v>3.249682018685444</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>2.622787144853285</v>
@@ -1822,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1836,7 +1848,7 @@
         <v>3.240416187557013</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E11">
         <v>2.612942199279327</v>
@@ -1872,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1886,7 +1898,7 @@
         <v>3.224267322019204</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E12">
         <v>2.595784029645404</v>
@@ -1922,7 +1934,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1936,7 +1948,7 @@
         <v>3.199676156013602</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E13">
         <v>2.569655915764452</v>
@@ -1972,7 +1984,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1986,7 +1998,7 @@
         <v>3.173610926784897</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14">
         <v>2.541961609708953</v>
@@ -2022,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2036,7 +2048,7 @@
         <v>3.150684626604055</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E15">
         <v>2.517602415766809</v>
@@ -2072,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2086,7 +2098,7 @@
         <v>3.134178515208647</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E16">
         <v>2.500064672409188</v>
@@ -2122,7 +2134,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2136,7 +2148,7 @@
         <v>3.120022596496306</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E17">
         <v>2.485024008777326</v>
@@ -2172,7 +2184,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2186,7 +2198,7 @@
         <v>3.094767960086906</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E18">
         <v>2.458190957592338</v>
@@ -2222,7 +2234,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2236,7 +2248,7 @@
         <v>3.083329457599286</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E19">
         <v>2.446037548699242</v>
@@ -2272,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2286,7 +2298,7 @@
         <v>3.074543134313888</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E20">
         <v>2.436702080208506</v>
@@ -2322,7 +2334,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2336,7 +2348,7 @@
         <v>3.073229577771591</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E21">
         <v>2.435306426382315</v>
@@ -2372,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2386,7 +2398,7 @@
         <v>3.065223201825673</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E22">
         <v>2.426799651939778</v>
@@ -2422,7 +2434,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2436,7 +2448,7 @@
         <v>3.053370911712657</v>
       </c>
       <c r="D23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E23">
         <v>2.414206593694698</v>
@@ -2472,7 +2484,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2486,7 +2498,7 @@
         <v>3.043420680449605</v>
       </c>
       <c r="D24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E24">
         <v>2.403634472977705</v>
@@ -2522,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2536,7 +2548,7 @@
         <v>3.034138406034767</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E25">
         <v>2.39377205641194</v>
@@ -2572,7 +2584,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2622,7 +2634,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2636,7 +2648,7 @@
         <v>3.022451571690653</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E27">
         <v>2.381354794921319</v>
@@ -2672,7 +2684,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2686,7 +2698,7 @@
         <v>1.930421456264695</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E28">
         <v>2.007737588387895</v>
@@ -2722,7 +2734,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2736,7 +2748,7 @@
         <v>3.006244860280342</v>
       </c>
       <c r="D29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E29">
         <v>2.364135164047864</v>
@@ -2772,7 +2784,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2786,7 +2798,7 @@
         <v>1.911108458500741</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E30">
         <v>2.004869346308376</v>
@@ -2822,7 +2834,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2836,7 +2848,7 @@
         <v>2.997079538238938</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E31">
         <v>2.354397009378872</v>
@@ -2872,7 +2884,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2886,7 +2898,7 @@
         <v>1.900186449734734</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32">
         <v>1.969405484366814</v>
@@ -2922,7 +2934,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2936,7 +2948,7 @@
         <v>2.989691832830151</v>
       </c>
       <c r="D33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E33">
         <v>2.346547572382036</v>
@@ -2972,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2986,7 +2998,7 @@
         <v>1.89138276745593</v>
       </c>
       <c r="D34" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E34">
         <v>1.988908448053416</v>
@@ -3022,7 +3034,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3036,7 +3048,7 @@
         <v>2.993732811454215</v>
       </c>
       <c r="D35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E35">
         <v>2.350841112170103</v>
@@ -3072,7 +3084,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3086,7 +3098,7 @@
         <v>1.896198266982939</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E36">
         <v>1.942246645980696</v>
@@ -3122,7 +3134,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3136,7 +3148,7 @@
         <v>3.004975357506775</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E37">
         <v>2.362786317350948</v>
@@ -3172,7 +3184,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3186,7 +3198,7 @@
         <v>1.90959563436224</v>
       </c>
       <c r="D38" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E38">
         <v>1.919910701288617</v>
@@ -3222,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3236,7 +3248,7 @@
         <v>3.012551559807466</v>
       </c>
       <c r="D39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E39">
         <v>2.370836032295433</v>
@@ -3272,7 +3284,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3322,7 +3334,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3336,7 +3348,7 @@
         <v>3.011994006588589</v>
       </c>
       <c r="D41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E41">
         <v>2.370243632000376</v>
@@ -3372,7 +3384,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3386,7 +3398,7 @@
         <v>1.917959524518068</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E42">
         <v>1.906326840470971</v>
@@ -3422,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3436,7 +3448,7 @@
         <v>1.876326840470971</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E43">
         <v>1.906326840470971</v>
@@ -3472,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3486,7 +3498,7 @@
         <v>3.00769821087698</v>
       </c>
       <c r="D44" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E44">
         <v>2.365679349056791</v>
@@ -3522,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3536,7 +3548,7 @@
         <v>1.912840367961734</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E45">
         <v>1.955679349056791</v>
@@ -3572,7 +3584,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3586,7 +3598,7 @@
         <v>1.871673061783394</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E46">
         <v>1.955679349056791</v>
@@ -3622,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3636,7 +3648,7 @@
         <v>3.004690327553521</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E47">
         <v>2.362483473025616</v>
@@ -3672,7 +3684,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3686,7 +3698,7 @@
         <v>1.909255973667945</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E48">
         <v>1.931297263327476</v>
@@ -3722,7 +3734,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3736,7 +3748,7 @@
         <v>1.868414521516314</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E49">
         <v>1.931297263327476</v>
@@ -3772,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3786,7 +3798,7 @@
         <v>3.007935044171493</v>
       </c>
       <c r="D50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E50">
         <v>2.365930984432211</v>
@@ -3822,7 +3834,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3836,7 +3848,7 @@
         <v>1.891922864953648</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E51">
         <v>1.938330443133641</v>
@@ -3872,7 +3884,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3886,7 +3898,7 @@
         <v>1.871929631185784</v>
       </c>
       <c r="D52" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E52">
         <v>1.938330443133641</v>
@@ -3922,7 +3934,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3936,7 +3948,7 @@
         <v>3.014769348869088</v>
       </c>
       <c r="D53" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E53">
         <v>2.373192433173406</v>
@@ -3972,7 +3984,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3986,7 +3998,7 @@
         <v>1.900038601782042</v>
       </c>
       <c r="D54" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E54">
         <v>1.938105255654558</v>
@@ -4022,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4036,7 +4048,7 @@
         <v>1.879333461274845</v>
       </c>
       <c r="D55" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E55">
         <v>1.938105255654558</v>
@@ -4072,7 +4084,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4086,7 +4098,7 @@
         <v>3.020057315470159</v>
       </c>
       <c r="D56" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E56">
         <v>2.378810897687044</v>
@@ -4122,7 +4134,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4136,7 +4148,7 @@
         <v>1.906318062120814</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E57">
         <v>1.950061136501503</v>
@@ -4172,7 +4184,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4186,7 +4198,7 @@
         <v>1.885062091759339</v>
       </c>
       <c r="D58" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E58">
         <v>1.950061136501503</v>
@@ -4222,7 +4234,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4236,7 +4248,7 @@
         <v>3.026470251012646</v>
       </c>
       <c r="D59" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E59">
         <v>2.385624641700937</v>
@@ -4272,7 +4284,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4286,7 +4298,7 @@
         <v>1.913933423077517</v>
       </c>
       <c r="D60" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E60">
         <v>2.07796288542562</v>
@@ -4322,7 +4334,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4336,7 +4348,7 @@
         <v>1.892009438597033</v>
       </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E61">
         <v>2.07796288542562</v>
@@ -4372,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4386,7 +4398,7 @@
         <v>3.052162558207098</v>
       </c>
       <c r="D62" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E62">
         <v>2.412922718095043</v>
@@ -4422,7 +4434,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4436,7 +4448,7 @@
         <v>1.94444303787093</v>
       </c>
       <c r="D63" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E63">
         <v>2.351714323704782</v>
@@ -4472,7 +4484,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4486,7 +4498,7 @@
         <v>1.919842771391023</v>
       </c>
       <c r="D64" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E64">
         <v>2.351714323704782</v>
@@ -4522,7 +4534,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4536,7 +4548,7 @@
         <v>3.139870507647556</v>
       </c>
       <c r="D65" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E65">
         <v>2.506112414375529</v>
@@ -4572,7 +4584,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4586,7 +4598,7 @@
         <v>2.048596227831473</v>
       </c>
       <c r="D66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E66">
         <v>2.439632917331332</v>
@@ -4622,7 +4634,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4636,7 +4648,7 @@
         <v>2.014859716618186</v>
       </c>
       <c r="D67" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E67">
         <v>2.439632917331332</v>
@@ -4672,7 +4684,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4686,7 +4698,7 @@
         <v>3.067734589357061</v>
       </c>
       <c r="D68" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E68">
         <v>2.429468001191877</v>
@@ -4722,7 +4734,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4736,7 +4748,7 @@
         <v>1.96293482486151</v>
       </c>
       <c r="D69" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E69">
         <v>2.317307812788318</v>
@@ -4772,7 +4784,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4786,7 +4798,7 @@
         <v>1.936712471803482</v>
       </c>
       <c r="D70" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E70">
         <v>2.317307812788318</v>
@@ -4822,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4836,7 +4848,7 @@
         <v>3.023857588718067</v>
       </c>
       <c r="D71" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E71">
         <v>2.382848688012947</v>
@@ -4872,7 +4884,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4886,7 +4898,7 @@
         <v>1.910830886602705</v>
       </c>
       <c r="D72" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E72">
         <v>2.232334342850537</v>
@@ -4922,7 +4934,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4936,7 +4948,7 @@
         <v>1.889179054444573</v>
       </c>
       <c r="D73" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E73">
         <v>2.232334342850537</v>
@@ -4972,7 +4984,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4986,7 +4998,7 @@
         <v>2.96438641260543</v>
       </c>
       <c r="D74" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E74">
         <v>2.319660563393269</v>
@@ -5022,7 +5034,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5036,7 +5048,7 @@
         <v>1.840208864968948</v>
       </c>
       <c r="D75" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E75">
         <v>2.1280939850984</v>
@@ -5072,7 +5084,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5086,7 +5098,7 @@
         <v>1.824751946989215</v>
       </c>
       <c r="D76" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E76">
         <v>2.1280939850984</v>
@@ -5122,7 +5134,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5136,7 +5148,7 @@
         <v>2.89858481633162</v>
       </c>
       <c r="D77" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E77">
         <v>2.249746367352347</v>
@@ -5172,7 +5184,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5186,7 +5198,7 @@
         <v>1.782813572795181</v>
       </c>
       <c r="D78" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E78">
         <v>2.087423265310894</v>
@@ -5222,7 +5234,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5236,7 +5248,7 @@
         <v>1.753466884359255</v>
       </c>
       <c r="D79" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E79">
         <v>2.087423265310894</v>
@@ -5272,7 +5284,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5286,7 +5298,7 @@
         <v>2.863380544404418</v>
       </c>
       <c r="D80" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E80">
         <v>2.212341828429695</v>
@@ -5322,7 +5334,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5336,7 +5348,7 @@
         <v>1.740861815415264</v>
       </c>
       <c r="D81" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E81">
         <v>2.074419260379142</v>
@@ -5372,7 +5384,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5386,7 +5398,7 @@
         <v>1.715328923104786</v>
       </c>
       <c r="D82" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E82">
         <v>2.074419260379142</v>
@@ -5422,7 +5434,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5436,7 +5448,7 @@
         <v>2.860232758796729</v>
       </c>
       <c r="D83" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E83">
         <v>2.208997306221525</v>
@@ -5472,7 +5484,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5486,7 +5498,7 @@
         <v>1.737110704232769</v>
       </c>
       <c r="D84" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E84">
         <v>2.081468211371934</v>
@@ -5522,7 +5534,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5536,7 +5548,7 @@
         <v>1.71191882202979</v>
       </c>
       <c r="D85" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E85">
         <v>2.081468211371934</v>
@@ -5572,7 +5584,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5586,7 +5598,7 @@
         <v>2.844214660630511</v>
       </c>
       <c r="D86" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E86">
         <v>2.191978076919919</v>
@@ -5622,7 +5634,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5636,7 +5648,7 @@
         <v>1.718022470584692</v>
       </c>
       <c r="D87" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E87">
         <v>2.066451244341104</v>
@@ -5672,7 +5684,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5686,7 +5698,7 @@
         <v>1.69456588234972</v>
       </c>
       <c r="D88" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E88">
         <v>2.066451244341104</v>
@@ -5722,7 +5734,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5736,7 +5748,7 @@
         <v>2.802243669794394</v>
       </c>
       <c r="D89" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E89">
         <v>2.147383899156544</v>
@@ -5772,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5786,7 +5798,7 @@
         <v>1.668007039838319</v>
       </c>
       <c r="D90" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E90">
         <v>2.026760758474768</v>
@@ -5822,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5836,7 +5848,7 @@
         <v>1.649097308943927</v>
       </c>
       <c r="D91" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E91">
         <v>2.026760758474768</v>
@@ -5872,7 +5884,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5886,7 +5898,7 @@
         <v>2.60784162529713</v>
       </c>
       <c r="D92" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E92">
         <v>2.069343992760599</v>
@@ -5922,7 +5934,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5936,7 +5948,7 @@
         <v>2.728794346127623</v>
       </c>
       <c r="D93" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E93">
         <v>2.069343992760599</v>
@@ -5972,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6022,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6072,7 +6084,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6086,7 +6098,7 @@
         <v>2.545370448575698</v>
       </c>
       <c r="D96" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E96">
         <v>1.994904039190669</v>
@@ -6122,7 +6134,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6136,7 +6148,7 @@
         <v>2.658733213355923</v>
       </c>
       <c r="D97" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E97">
         <v>1.994904039190669</v>
@@ -6172,7 +6184,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6222,7 +6234,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6272,7 +6284,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6286,7 +6298,7 @@
         <v>2.481313246131303</v>
       </c>
       <c r="D100" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E100">
         <v>1.918574195156459</v>
@@ -6322,7 +6334,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6336,7 +6348,7 @@
         <v>2.586893360147255</v>
       </c>
       <c r="D101" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E101">
         <v>1.918574195156459</v>
@@ -6372,7 +6384,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6422,7 +6434,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6472,7 +6484,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6486,7 +6498,7 @@
         <v>2.40667480096654</v>
       </c>
       <c r="D104" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E104">
         <v>1.855244363890487</v>
@@ -6522,7 +6534,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6536,7 +6548,7 @@
         <v>2.503186692672755</v>
       </c>
       <c r="D105" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E105">
         <v>1.855244363890487</v>
@@ -6572,7 +6584,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6622,7 +6634,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6672,7 +6684,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6686,7 +6698,7 @@
         <v>2.261174748318485</v>
       </c>
       <c r="D108" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E108">
         <v>1.708621781365236</v>
@@ -6722,7 +6734,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6736,7 +6748,7 @@
         <v>2.295408018482838</v>
       </c>
       <c r="D109" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E109">
         <v>1.708621781365236</v>
@@ -6772,7 +6784,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6786,7 +6798,7 @@
         <v>2.256941478154132</v>
       </c>
       <c r="D110" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E110">
         <v>1.708621781365236</v>
@@ -6822,7 +6834,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6836,7 +6848,7 @@
         <v>2.37840151605552</v>
       </c>
       <c r="D111" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E111">
         <v>1.708621781365236</v>
@@ -6872,7 +6884,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6886,7 +6898,7 @@
         <v>1.162928473299494</v>
       </c>
       <c r="D112" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E112">
         <v>1.739714710417097</v>
@@ -6922,7 +6934,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6936,7 +6948,7 @@
         <v>2.16369956491871</v>
       </c>
       <c r="D113" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E113">
         <v>1.585907487978019</v>
@@ -6972,7 +6984,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6986,7 +6998,7 @@
         <v>2.202284405770554</v>
       </c>
       <c r="D114" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E114">
         <v>1.585907487978019</v>
@@ -7022,7 +7034,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7036,7 +7048,7 @@
         <v>2.155114724066867</v>
       </c>
       <c r="D115" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E115">
         <v>1.585907487978019</v>
@@ -7072,7 +7084,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7086,7 +7098,7 @@
         <v>2.273963819555761</v>
       </c>
       <c r="D116" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E116">
         <v>1.585907487978019</v>
@@ -7122,7 +7134,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7136,7 +7148,7 @@
         <v>1.038473551637282</v>
       </c>
       <c r="D117" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E117">
         <v>1.644850469429817</v>
@@ -7172,7 +7184,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7186,7 +7198,7 @@
         <v>2.003396115050518</v>
       </c>
       <c r="D118" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E118">
         <v>1.44524374557326</v>
@@ -7236,7 +7248,7 @@
         <v>2.011358022681203</v>
       </c>
       <c r="D119" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E119">
         <v>1.44524374557326</v>
@@ -7286,7 +7298,7 @@
         <v>2.126521048903798</v>
       </c>
       <c r="D120" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E120">
         <v>1.44524374557326</v>
@@ -7336,7 +7348,7 @@
         <v>0.862770916610359</v>
       </c>
       <c r="D121" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E121">
         <v>1.510923286087617</v>
@@ -7386,7 +7398,7 @@
         <v>1.874602728130037</v>
       </c>
       <c r="D122" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E122">
         <v>1.276091140631614</v>
@@ -7422,7 +7434,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7436,7 +7448,7 @@
         <v>1.872474831255431</v>
       </c>
       <c r="D123" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E123">
         <v>1.276091140631614</v>
@@ -7472,7 +7484,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7486,7 +7498,7 @@
         <v>1.98407675000557</v>
       </c>
       <c r="D124" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E124">
         <v>1.276091140631614</v>
@@ -7522,7 +7534,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7536,7 +7548,7 @@
         <v>0.7399584468816611</v>
       </c>
       <c r="D125" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E125">
         <v>1.38153638125506</v>
@@ -7572,7 +7584,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7586,7 +7598,7 @@
         <v>1.730522677364715</v>
       </c>
       <c r="D126" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E126">
         <v>1.086861580870708</v>
@@ -7622,7 +7634,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7636,7 +7648,7 @@
         <v>1.717107403241213</v>
       </c>
       <c r="D127" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E127">
         <v>1.086861580870708</v>
@@ -7672,7 +7684,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7686,7 +7698,7 @@
         <v>1.82472554178586</v>
       </c>
       <c r="D128" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E128">
         <v>1.086861580870708</v>
@@ -7722,7 +7734,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7736,7 +7748,7 @@
         <v>0.5494009603855905</v>
       </c>
       <c r="D129" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E129">
         <v>1.236792367122156</v>
@@ -7772,7 +7784,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7786,7 +7798,7 @@
         <v>1.560267149716914</v>
       </c>
       <c r="D130" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E130">
         <v>0.8632540906420294</v>
@@ -7822,7 +7834,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7836,7 +7848,7 @@
         <v>1.533513884948193</v>
       </c>
       <c r="D131" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E131">
         <v>0.8632540906420294</v>
@@ -7872,7 +7884,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7886,7 +7898,7 @@
         <v>1.636424497382762</v>
       </c>
       <c r="D132" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E132">
         <v>0.8632540906420294</v>
@@ -7922,7 +7934,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7936,7 +7948,7 @@
         <v>0.3242242947868856</v>
       </c>
       <c r="D133" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E133">
         <v>1.065752251789342</v>
@@ -7972,7 +7984,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7986,7 +7998,7 @@
         <v>1.451788381289887</v>
       </c>
       <c r="D134" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E134">
         <v>0.7958855760303623</v>
@@ -8022,7 +8034,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8036,7 +8048,7 @@
         <v>1.416536779824118</v>
       </c>
       <c r="D135" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E135">
         <v>0.7958855760303623</v>
@@ -8072,7 +8084,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8086,7 +8098,7 @@
         <v>1.516447979306788</v>
       </c>
       <c r="D136" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E136">
         <v>0.7958855760303623</v>
@@ -8122,7 +8134,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8136,7 +8148,7 @@
         <v>0.1807523752543663</v>
       </c>
       <c r="D137" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E137">
         <v>0.9567735812036653</v>
@@ -8172,7 +8184,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8186,7 +8198,7 @@
         <v>1.341632314098553</v>
       </c>
       <c r="D138" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E138">
         <v>0.6547639784304042</v>
@@ -8222,7 +8234,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8236,7 +8248,7 @@
         <v>1.297750974650053</v>
       </c>
       <c r="D139" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E139">
         <v>0.6547639784304042</v>
@@ -8272,7 +8284,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8286,7 +8298,7 @@
         <v>1.394616384256465</v>
       </c>
       <c r="D140" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E140">
         <v>0.6547639784304042</v>
@@ -8322,7 +8334,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8336,7 +8348,7 @@
         <v>0.03506209284002182</v>
       </c>
       <c r="D141" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E141">
         <v>0.8461098823662887</v>
@@ -8372,7 +8384,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8386,7 +8398,7 @@
         <v>1.256461817624148</v>
       </c>
       <c r="D142" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E142">
         <v>0.5456515451590462</v>
@@ -8422,7 +8434,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8436,7 +8448,7 @@
         <v>1.205908135133873</v>
       </c>
       <c r="D143" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E143">
         <v>0.5456515451590462</v>
@@ -8472,7 +8484,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8486,7 +8498,7 @@
         <v>1.300418600137307</v>
       </c>
       <c r="D144" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E144">
         <v>0.5456515451590462</v>
@@ -8522,7 +8534,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8536,7 +8548,7 @@
         <v>-0.07758275733580433</v>
       </c>
       <c r="D145" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E145">
         <v>0.7605468951247198</v>
@@ -8572,7 +8584,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8586,7 +8598,7 @@
         <v>1.07997323323726</v>
       </c>
       <c r="D146" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E146">
         <v>0.4493358506304439</v>
@@ -8622,7 +8634,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8636,7 +8648,7 @@
         <v>1.124836651250086</v>
       </c>
       <c r="D147" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E147">
         <v>0.4493358506304439</v>
@@ -8672,7 +8684,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8686,7 +8698,7 @@
         <v>-0.1770165858599375</v>
       </c>
       <c r="D148" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E148">
         <v>0.6850187605663192</v>
@@ -8722,7 +8734,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8736,7 +8748,7 @@
         <v>0.9919465651648807</v>
       </c>
       <c r="D149" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E149">
         <v>0.3474042381876092</v>
@@ -8772,7 +8784,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8786,7 +8798,7 @@
         <v>1.039038099769426</v>
       </c>
       <c r="D150" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E150">
         <v>0.3474042381876092</v>
@@ -8822,7 +8834,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8836,7 +8848,7 @@
         <v>-0.2822481425904906</v>
       </c>
       <c r="D151" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E151">
         <v>0.6050867767082688</v>
@@ -8872,7 +8884,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8886,7 +8898,7 @@
         <v>0.9183156432255819</v>
       </c>
       <c r="D152" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E152">
         <v>0.2325423301237928</v>
@@ -8936,7 +8948,7 @@
         <v>-0.3774576698762075</v>
       </c>
       <c r="D153" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E153">
         <v>0.4926188471075936</v>
@@ -8986,7 +8998,7 @@
         <v>-0.4303137196335811</v>
       </c>
       <c r="D154" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E154">
         <v>0.4926188471075936</v>
@@ -9036,7 +9048,7 @@
         <v>0.8418793262205044</v>
       </c>
       <c r="D155" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E155">
         <v>0.1384668630406214</v>
@@ -9086,7 +9098,7 @@
         <v>0.7767029332404918</v>
       </c>
       <c r="D156" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E156">
         <v>0.1384668630406214</v>
@@ -9136,7 +9148,7 @@
         <v>-0.4715331369593789</v>
       </c>
       <c r="D157" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E157">
         <v>0.4214089449404703</v>
@@ -9186,7 +9198,7 @@
         <v>-0.5240625357893807</v>
       </c>
       <c r="D158" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E158">
         <v>0.4214089449404703</v>
@@ -9236,7 +9248,7 @@
         <v>0.7712878926560949</v>
       </c>
       <c r="D159" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E159">
         <v>0.05158509865365524</v>
@@ -9286,7 +9298,7 @@
         <v>0.707921536434144</v>
       </c>
       <c r="D160" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E160">
         <v>0.05158509865365524</v>
@@ -9336,7 +9348,7 @@
         <v>-0.5584149013463451</v>
       </c>
       <c r="D161" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E161">
         <v>0.3556442760642256</v>
@@ -9386,7 +9398,7 @@
         <v>-0.6106426273833367</v>
       </c>
       <c r="D162" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E162">
         <v>0.3556442760642256</v>
@@ -9436,7 +9448,7 @@
         <v>0.7170193735272363</v>
       </c>
       <c r="D163" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E163">
         <v>-0.01520692488955522</v>
@@ -9486,7 +9498,7 @@
         <v>0.6550445177957691</v>
       </c>
       <c r="D164" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E164">
         <v>-0.01520692488955522</v>
@@ -9536,7 +9548,7 @@
         <v>-0.6252069248895555</v>
       </c>
       <c r="D165" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E165">
         <v>0.3050864249099901</v>
@@ -9586,7 +9598,7 @@
         <v>-0.6772027341781328</v>
       </c>
       <c r="D166" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E166">
         <v>0.3050864249099901</v>
@@ -9636,7 +9648,7 @@
         <v>0.6624776741967331</v>
       </c>
       <c r="D167" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E167">
         <v>-0.08233517021940617</v>
@@ -9672,7 +9684,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9686,7 +9698,7 @@
         <v>0.6019013235763042</v>
       </c>
       <c r="D168" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E168">
         <v>-0.08233517021940617</v>
@@ -9722,7 +9734,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9736,7 +9748,7 @@
         <v>-0.6923351702194065</v>
       </c>
       <c r="D169" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E169">
         <v>0.2542740725422554</v>
@@ -9772,7 +9784,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9786,7 +9798,7 @@
         <v>-0.7440978953228106</v>
       </c>
       <c r="D170" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E170">
         <v>0.2542740725422554</v>
@@ -9822,7 +9834,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9836,7 +9848,7 @@
         <v>0.6552913511059879</v>
       </c>
       <c r="D171" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E171">
         <v>-0.09117987556186069</v>
@@ -9872,7 +9884,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9886,7 +9898,7 @@
         <v>0.5948992651801932</v>
       </c>
       <c r="D172" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E172">
         <v>-0.09117987556186069</v>
@@ -9922,7 +9934,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9936,7 +9948,7 @@
         <v>0.543167250859228</v>
       </c>
       <c r="D173" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E173">
         <v>-0.09117987556186069</v>
@@ -9972,7 +9984,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9986,7 +9998,7 @@
         <v>0.5418273224640568</v>
       </c>
       <c r="D174" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E174">
         <v>-0.09117987556186069</v>
@@ -10022,7 +10034,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10036,7 +10048,7 @@
         <v>-0.701179875561861</v>
       </c>
       <c r="D175" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E175">
         <v>0.2475791219705359</v>
@@ -10072,7 +10084,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10086,7 +10098,7 @@
         <v>-0.7529118898828271</v>
       </c>
       <c r="D176" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E176">
         <v>0.2475791219705359</v>
@@ -10122,7 +10134,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10136,7 +10148,7 @@
         <v>0.6454205590474551</v>
       </c>
       <c r="D177" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E177">
         <v>-0.103328542710825</v>
@@ -10172,7 +10184,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10186,7 +10198,7 @@
         <v>0.5852815703539305</v>
       </c>
       <c r="D178" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E178">
         <v>-0.103328542710825</v>
@@ -10222,7 +10234,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10236,7 +10248,7 @@
         <v>0.5335917389050095</v>
       </c>
       <c r="D179" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E179">
         <v>-0.103328542710825</v>
@@ -10272,7 +10284,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10286,7 +10298,7 @@
         <v>0.5320408961496135</v>
       </c>
       <c r="D180" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E180">
         <v>-0.103328542710825</v>
@@ -10322,7 +10334,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10336,7 +10348,7 @@
         <v>-0.7133285427108254</v>
       </c>
       <c r="D181" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E181">
         <v>0.238383255864723</v>
@@ -10372,7 +10384,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10386,7 +10398,7 @@
         <v>-0.7650183741597454</v>
       </c>
       <c r="D182" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E182">
         <v>0.238383255864723</v>
@@ -10422,7 +10434,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10436,7 +10448,7 @@
         <v>0.5083726106019757</v>
       </c>
       <c r="D183" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E183">
         <v>-0.2004767023975047</v>
@@ -10486,7 +10498,7 @@
         <v>0.4570200991519675</v>
       </c>
       <c r="D184" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E184">
         <v>-0.2004767023975047</v>
@@ -10536,7 +10548,7 @@
         <v>0.4537826564020104</v>
       </c>
       <c r="D185" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E185">
         <v>-0.2004767023975047</v>
@@ -10586,7 +10598,7 @@
         <v>-0.810476702397505</v>
       </c>
       <c r="D186" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E186">
         <v>0.1648474961018893</v>
@@ -10636,7 +10648,7 @@
         <v>-0.8618292138475132</v>
       </c>
       <c r="D187" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E187">
         <v>0.1648474961018893</v>
@@ -10686,7 +10698,7 @@
         <v>0.3793436997319031</v>
       </c>
       <c r="D188" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E188">
         <v>-0.3634605898123331</v>
@@ -10722,7 +10734,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10736,7 +10748,7 @@
         <v>0.3285571045576408</v>
       </c>
       <c r="D189" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E189">
         <v>-0.3634605898123331</v>
@@ -10772,7 +10784,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10786,7 +10798,7 @@
         <v>0.3224900804289543</v>
       </c>
       <c r="D190" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E190">
         <v>-0.3634605898123331</v>
@@ -10822,7 +10834,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10836,7 +10848,7 @@
         <v>-0.9734605898123334</v>
       </c>
       <c r="D191" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E191">
         <v>0.04147774798927539</v>
@@ -10872,7 +10884,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10886,7 +10898,7 @@
         <v>-1.024247184986596</v>
       </c>
       <c r="D192" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E192">
         <v>0.04147774798927539</v>
@@ -10922,7 +10934,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10936,7 +10948,7 @@
         <v>0.1872203926773688</v>
       </c>
       <c r="D193" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E193">
         <v>-0.486627682752748</v>
@@ -10986,7 +10998,7 @@
         <v>0.2818364178207418</v>
       </c>
       <c r="D194" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E194">
         <v>-0.486627682752748</v>
@@ -11036,7 +11048,7 @@
         <v>0.2314774861636328</v>
       </c>
       <c r="D195" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E195">
         <v>-0.486627682752748</v>
@@ -11086,7 +11098,7 @@
         <v>0.2232721444491759</v>
       </c>
       <c r="D196" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E196">
         <v>-0.486627682752748</v>
@@ -11136,7 +11148,7 @@
         <v>-1.096627682752748</v>
       </c>
       <c r="D197" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E197">
         <v>-0.05175289875034395</v>
@@ -11186,7 +11198,7 @@
         <v>-1.146986614409856</v>
       </c>
       <c r="D198" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E198">
         <v>-0.05175289875034395</v>
@@ -11236,7 +11248,7 @@
         <v>0.01252453965430966</v>
       </c>
       <c r="D199" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E199">
         <v>-0.6936746196689665</v>
@@ -11272,7 +11284,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11286,7 +11298,7 @@
         <v>0.1179242594287349</v>
       </c>
       <c r="D200" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E200">
         <v>-0.6936746196689665</v>
@@ -11322,7 +11334,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11336,7 +11348,7 @@
         <v>0.06828424074703054</v>
       </c>
       <c r="D201" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E201">
         <v>-0.6936746196689665</v>
@@ -11372,7 +11384,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11386,7 +11398,7 @@
         <v>0.01720429679214597</v>
       </c>
       <c r="D202" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E202">
         <v>-0.6936746196689665</v>
@@ -11422,7 +11434,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11436,7 +11448,7 @@
         <v>-1.303674619668967</v>
       </c>
       <c r="D203" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E203">
         <v>-0.2084759273883146</v>
@@ -11472,7 +11484,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11486,7 +11498,7 @@
         <v>-1.353314638350671</v>
       </c>
       <c r="D204" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E204">
         <v>-0.2084759273883146</v>
@@ -11522,7 +11534,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11536,7 +11548,7 @@
         <v>-0.1245779691705016</v>
       </c>
       <c r="D205" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E205">
         <v>-0.8561664819798533</v>
@@ -11572,7 +11584,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11586,7 +11598,7 @@
         <v>-0.01071513156738391</v>
       </c>
       <c r="D206" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E206">
         <v>-0.8561664819798533</v>
@@ -11622,7 +11634,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11636,7 +11648,7 @@
         <v>-0.05979094239384253</v>
       </c>
       <c r="D207" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E207">
         <v>-0.8561664819798533</v>
@@ -11672,7 +11684,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11686,7 +11698,7 @@
         <v>-0.1125635099144651</v>
       </c>
       <c r="D208" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E208">
         <v>-0.8561664819798533</v>
@@ -11722,7 +11734,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11736,7 +11748,7 @@
         <v>-1.466166481979854</v>
       </c>
       <c r="D209" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E209">
         <v>-0.331473239831972</v>
@@ -11772,7 +11784,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11786,7 +11798,7 @@
         <v>-1.515242292806312</v>
       </c>
       <c r="D210" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E210">
         <v>-0.331473239831972</v>
@@ -11822,7 +11834,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11836,7 +11848,7 @@
         <v>-1.470289185120701</v>
       </c>
       <c r="D211" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E211">
         <v>-1.461213374294242</v>
@@ -11872,7 +11884,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11886,7 +11898,7 @@
         <v>-0.2405124524062172</v>
       </c>
       <c r="D212" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E212">
         <v>-0.9935703139629233</v>
@@ -11922,7 +11934,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11936,7 +11948,7 @@
         <v>-0.1194931652206472</v>
       </c>
       <c r="D213" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E213">
         <v>-0.9935703139629233</v>
@@ -11972,7 +11984,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11986,7 +11998,7 @@
         <v>-0.2508944510330187</v>
       </c>
       <c r="D214" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E214">
         <v>-0.9935703139629233</v>
@@ -12022,7 +12034,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12036,7 +12048,7 @@
         <v>-0.1680918794082764</v>
       </c>
       <c r="D215" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E215">
         <v>-0.9935703139629233</v>
@@ -12072,7 +12084,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12086,7 +12098,7 @@
         <v>-0.2222957368453899</v>
       </c>
       <c r="D216" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E216">
         <v>-0.9935703139629233</v>
@@ -12122,7 +12134,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12136,7 +12148,7 @@
         <v>-1.603570313962924</v>
       </c>
       <c r="D217" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E217">
         <v>-0.4354803070969355</v>
@@ -12172,7 +12184,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12186,7 +12198,7 @@
         <v>-1.652169028150552</v>
       </c>
       <c r="D218" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E218">
         <v>-0.4354803070969355</v>
@@ -12222,7 +12234,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12236,7 +12248,7 @@
         <v>-1.594334311216528</v>
       </c>
       <c r="D219" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E219">
         <v>-1.478729167967043</v>
@@ -12272,7 +12284,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12286,7 +12298,7 @@
         <v>-0.35263208243365</v>
       </c>
       <c r="D220" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E220">
         <v>-1.126452838439881</v>
@@ -12322,7 +12334,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12336,7 +12348,7 @@
         <v>-0.2246918304315724</v>
       </c>
       <c r="D221" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E221">
         <v>-1.126452838439881</v>
@@ -12372,7 +12384,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12386,7 +12398,7 @@
         <v>-0.3565545138983772</v>
       </c>
       <c r="D222" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E222">
         <v>-1.126452838439881</v>
@@ -12422,7 +12434,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12436,7 +12448,7 @@
         <v>-0.2728291469647672</v>
       </c>
       <c r="D223" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E223">
         <v>-1.126452838439881</v>
@@ -12472,7 +12484,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12486,7 +12498,7 @@
         <v>-1.736452838439881</v>
       </c>
       <c r="D224" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E224">
         <v>-0.5360649957635211</v>
@@ -12522,7 +12534,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12536,7 +12548,7 @@
         <v>-1.784590154973076</v>
       </c>
       <c r="D225" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E225">
         <v>-0.5360649957635211</v>
@@ -12572,7 +12584,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12586,7 +12598,7 @@
         <v>-1.714297701369337</v>
       </c>
       <c r="D226" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E226">
         <v>-1.46263208243365</v>
@@ -12622,7 +12634,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12636,7 +12648,7 @@
         <v>-0.2590860480244892</v>
       </c>
       <c r="D227" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E227">
         <v>-1.16989816592567</v>
@@ -12686,7 +12698,7 @@
         <v>-0.3910995833228421</v>
       </c>
       <c r="D228" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E228">
         <v>-1.16989816592567</v>
@@ -12736,7 +12748,7 @@
         <v>-0.307072512726136</v>
       </c>
       <c r="D229" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E229">
         <v>-1.16989816592567</v>
@@ -12786,7 +12798,7 @@
         <v>-1.779898165925671</v>
       </c>
       <c r="D230" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E230">
         <v>-0.5689506950409591</v>
@@ -12836,7 +12848,7 @@
         <v>-1.827884630627318</v>
       </c>
       <c r="D231" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E231">
         <v>-0.5689506950409591</v>
@@ -12886,7 +12898,7 @@
         <v>-1.753519177571786</v>
       </c>
       <c r="D232" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E232">
         <v>-1.495262006903079</v>
@@ -12936,7 +12948,7 @@
         <v>-0.3066333113890707</v>
       </c>
       <c r="D233" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E233">
         <v>-1.229957867017773</v>
@@ -12972,7 +12984,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12986,7 +12998,7 @@
         <v>-0.4388553873162158</v>
       </c>
       <c r="D234" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E234">
         <v>-1.229957867017773</v>
@@ -13022,7 +13034,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13036,7 +13048,7 @@
         <v>-0.3544112354619253</v>
       </c>
       <c r="D235" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E235">
         <v>-1.229957867017773</v>
@@ -13072,7 +13084,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13086,7 +13098,7 @@
         <v>-0.4788553873162158</v>
       </c>
       <c r="D236" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E236">
         <v>-1.229957867017773</v>
@@ -13122,7 +13134,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13136,7 +13148,7 @@
         <v>-1.839957867017773</v>
       </c>
       <c r="D237" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E237">
         <v>-0.6144125521176198</v>
@@ -13172,7 +13184,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13186,7 +13198,7 @@
         <v>-1.887735791090629</v>
       </c>
       <c r="D238" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E238">
         <v>-0.6144125521176198</v>
@@ -13222,7 +13234,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13236,7 +13248,7 @@
         <v>-1.807739741057712</v>
       </c>
       <c r="D239" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E239">
         <v>-1.641074829931972</v>
@@ -13272,7 +13284,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13286,7 +13298,7 @@
         <v>-0.4492665299910312</v>
       </c>
       <c r="D240" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E240">
         <v>-1.24305135649527</v>
@@ -13336,7 +13348,7 @@
         <v>-0.3647314511264801</v>
       </c>
       <c r="D241" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E241">
         <v>-1.24305135649527</v>
@@ -13386,7 +13398,7 @@
         <v>-0.4892665299910313</v>
       </c>
       <c r="D242" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E242">
         <v>-1.24305135649527</v>
@@ -13436,7 +13448,7 @@
         <v>-1.85305135649527</v>
       </c>
       <c r="D243" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E243">
         <v>-0.6243235962360032</v>
@@ -13486,7 +13498,7 @@
         <v>-1.900783817062996</v>
       </c>
       <c r="D244" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E244">
         <v>-0.6243235962360032</v>
@@ -13536,7 +13548,7 @@
         <v>-1.819560252391564</v>
       </c>
       <c r="D245" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E245">
         <v>-1.515139306016957</v>
@@ -13586,7 +13598,7 @@
         <v>-0.4959723755022063</v>
       </c>
       <c r="D246" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E246">
         <v>-1.301790585784434</v>
@@ -13622,7 +13634,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13636,7 +13648,7 @@
         <v>-0.4110293853231477</v>
       </c>
       <c r="D247" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E247">
         <v>-1.301790585784434</v>
@@ -13672,7 +13684,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13686,7 +13698,7 @@
         <v>-0.5359723755022063</v>
       </c>
       <c r="D248" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E248">
         <v>-1.301790585784434</v>
@@ -13722,7 +13734,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13736,7 +13748,7 @@
         <v>-1.911790585784434</v>
       </c>
       <c r="D249" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E249">
         <v>-0.6687859295173837</v>
@@ -13772,7 +13784,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13786,7 +13798,7 @@
         <v>-1.959319090694905</v>
       </c>
       <c r="D250" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E250">
         <v>-0.6687859295173837</v>
@@ -13822,7 +13834,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13836,7 +13848,7 @@
         <v>-1.872588723277615</v>
       </c>
       <c r="D251" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E251">
         <v>-1.283614900054561</v>
@@ -13872,7 +13884,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13886,7 +13898,7 @@
         <v>-0.4288211453050677</v>
       </c>
       <c r="D252" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E252">
         <v>-1.324363391400262</v>
@@ -13936,7 +13948,7 @@
         <v>-0.5539208910786808</v>
       </c>
       <c r="D253" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E253">
         <v>-1.324363391400262</v>
@@ -13986,7 +13998,7 @@
         <v>-1.934363391400263</v>
       </c>
       <c r="D254" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E254">
         <v>-0.6858722893238101</v>
@@ -14036,7 +14048,7 @@
         <v>-1.981813518513456</v>
       </c>
       <c r="D255" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E255">
         <v>-0.6858722893238101</v>
@@ -14086,7 +14098,7 @@
         <v>-1.892966950569682</v>
       </c>
       <c r="D256" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E256">
         <v>-1.353721399531455</v>
@@ -14136,7 +14148,7 @@
         <v>-0.46714221579668</v>
       </c>
       <c r="D257" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E257">
         <v>-1.372982194490942</v>
@@ -14172,7 +14184,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14186,7 +14198,7 @@
         <v>-0.5925795921473114</v>
       </c>
       <c r="D258" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E258">
         <v>-1.372982194490942</v>
@@ -14222,7 +14234,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14236,7 +14248,7 @@
         <v>-1.982982194490942</v>
       </c>
       <c r="D259" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E259">
         <v>-0.7226740222188379</v>
@@ -14272,7 +14284,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14286,7 +14298,7 @@
         <v>-2.030263506315626</v>
       </c>
       <c r="D260" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E260">
         <v>-0.7226740222188379</v>
@@ -14322,7 +14334,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14336,7 +14348,7 @@
         <v>-1.9368589255821</v>
       </c>
       <c r="D261" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E261">
         <v>-1.45714221579668</v>
@@ -14372,7 +14384,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14386,7 +14398,7 @@
         <v>-0.5866700905677851</v>
       </c>
       <c r="D262" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E262">
         <v>-1.365550157569966</v>
@@ -14436,7 +14448,7 @@
         <v>-1.975550157569966</v>
       </c>
       <c r="D263" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E263">
         <v>-0.7170483831605994</v>
@@ -14486,7 +14498,7 @@
         <v>-2.022857275078404</v>
       </c>
       <c r="D264" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E264">
         <v>-0.7170483831605994</v>
@@ -14536,7 +14548,7 @@
         <v>-1.930149447806219</v>
       </c>
       <c r="D265" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E265">
         <v>-1.537441620534035</v>
@@ -14586,7 +14598,7 @@
         <v>-0.6162550847681185</v>
       </c>
       <c r="D266" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E266">
         <v>-1.402757486520604</v>
@@ -14622,7 +14634,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14636,7 +14648,7 @@
         <v>-2.012757486520604</v>
       </c>
       <c r="D267" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E267">
         <v>-0.7452122641024017</v>
@@ -14672,7 +14684,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14686,7 +14698,7 @@
         <v>-2.05993541191463</v>
       </c>
       <c r="D268" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E268">
         <v>-0.7452122641024017</v>
@@ -14722,7 +14734,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14736,7 +14748,7 @@
         <v>-1.963739397553323</v>
       </c>
       <c r="D269" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E269">
         <v>-1.707297905433836</v>
@@ -14772,7 +14784,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14786,7 +14798,7 @@
         <v>-0.634446447405705</v>
       </c>
       <c r="D270" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E270">
         <v>-1.425635706780974</v>
@@ -14836,7 +14848,7 @@
         <v>-2.035635706780974</v>
       </c>
       <c r="D271" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E271">
         <v>-0.7625298058272652</v>
@@ -14886,7 +14898,7 @@
         <v>-2.082734193910206</v>
       </c>
       <c r="D272" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E272">
         <v>-0.7625298058272652</v>
@@ -14936,7 +14948,7 @@
         <v>-1.984393346399491</v>
       </c>
       <c r="D273" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E273">
         <v>-1.800870653337982</v>
@@ -14986,7 +14998,7 @@
         <v>-0.657597094999522</v>
       </c>
       <c r="D274" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E274">
         <v>-1.454750931702455</v>
@@ -15036,7 +15048,7 @@
         <v>-2.064750931702456</v>
       </c>
       <c r="D275" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E275">
         <v>-0.784568413580331</v>
@@ -15086,7 +15098,7 @@
         <v>-2.111748324300711</v>
       </c>
       <c r="D276" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E276">
         <v>-0.784568413580331</v>
@@ -15136,7 +15148,7 @@
         <v>-0.7445684135803319</v>
       </c>
       <c r="D277" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E277">
         <v>-1.372636206025691</v>
@@ -15186,7 +15198,7 @@
         <v>-2.010677924453606</v>
       </c>
       <c r="D278" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E278">
         <v>-1.818641420829181</v>
@@ -15236,7 +15248,7 @@
         <v>-0.6891909916418824</v>
       </c>
       <c r="D279" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E279">
         <v>-1.494484740580184</v>
@@ -15272,7 +15284,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15286,7 +15298,7 @@
         <v>-2.104484740580184</v>
       </c>
       <c r="D280" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E280">
         <v>-0.8146446994669452</v>
@@ -15322,7 +15334,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15336,7 +15348,7 @@
         <v>-2.151344168564281</v>
       </c>
       <c r="D281" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E281">
         <v>-0.8146446994669452</v>
@@ -15372,7 +15384,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15386,7 +15398,7 @@
         <v>-0.774644699466946</v>
       </c>
       <c r="D282" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E282">
         <v>-1.426299571880434</v>
@@ -15422,7 +15434,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15436,7 +15448,7 @@
         <v>-2.046548724134889</v>
       </c>
       <c r="D283" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E283">
         <v>-1.975143003975854</v>
@@ -15472,7 +15484,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15486,7 +15498,7 @@
         <v>-0.7107964213114482</v>
       </c>
       <c r="D284" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E284">
         <v>-1.521656634662433</v>
@@ -15522,7 +15534,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15536,7 +15548,7 @@
         <v>-2.131656634662433</v>
       </c>
       <c r="D285" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E285">
         <v>-0.8352123137375358</v>
@@ -15572,7 +15584,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15586,7 +15598,7 @@
         <v>-2.178421715792077</v>
       </c>
       <c r="D286" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E286">
         <v>-0.8352123137375358</v>
@@ -15622,7 +15634,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15636,7 +15648,7 @@
         <v>-0.83197739486718</v>
       </c>
       <c r="D287" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E287">
         <v>-1.449320204366783</v>
@@ -15672,7 +15684,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15686,7 +15698,7 @@
         <v>-2.071078906292474</v>
       </c>
       <c r="D288" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E288">
         <v>-2.025199555329629</v>
@@ -15722,7 +15734,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15736,7 +15748,7 @@
         <v>-2.134267548868247</v>
       </c>
       <c r="D289" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E289">
         <v>-0.8371886307405481</v>
@@ -15786,7 +15798,7 @@
         <v>-2.181023564323565</v>
       </c>
       <c r="D290" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E290">
         <v>-0.8371886307405481</v>
@@ -15836,7 +15848,7 @@
         <v>-2.073435981617167</v>
       </c>
       <c r="D291" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E291">
         <v>-1.89126418253631</v>
@@ -15886,7 +15898,7 @@
         <v>-2.159710406445646</v>
       </c>
       <c r="D292" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E292">
         <v>-0.856447460434552</v>
@@ -15922,7 +15934,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -15936,7 +15948,7 @@
         <v>-2.206378078645488</v>
       </c>
       <c r="D293" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E293">
         <v>-0.856447460434552</v>
@@ -15972,7 +15984,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -15986,7 +15998,7 @@
         <v>-2.096405228041208</v>
       </c>
       <c r="D294" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E294">
         <v>-1.476441427235503</v>
@@ -16022,7 +16034,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16036,7 +16048,7 @@
         <v>-2.15897721946909</v>
       </c>
       <c r="D295" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E295">
         <v>-0.8558924786259086</v>
@@ -16072,7 +16084,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16086,7 +16098,7 @@
         <v>-2.205647437457045</v>
       </c>
       <c r="D296" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E296">
         <v>-0.8558924786259086</v>
@@ -16122,7 +16134,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16136,7 +16148,7 @@
         <v>-2.095743323131817</v>
       </c>
       <c r="D297" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E297">
         <v>-1.475871170698182</v>
@@ -16172,7 +16184,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16186,7 +16198,7 @@
         <v>-0.1977199794301434</v>
       </c>
       <c r="D298" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E298">
         <v>0.5315870882768845</v>
@@ -16222,7 +16234,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16236,7 +16248,7 @@
         <v>-0.1653191551969262</v>
       </c>
       <c r="D299" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E299">
         <v>0.5568424835917494</v>
@@ -16272,7 +16284,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16286,7 +16298,7 @@
         <v>-0.1418631150528316</v>
       </c>
       <c r="D300" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E300">
         <v>0.5751257087991237</v>
@@ -16322,7 +16334,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16336,7 +16348,7 @@
         <v>-0.1263472268305499</v>
       </c>
       <c r="D301" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E301">
         <v>0.5872198422043242</v>
@@ -16372,7 +16384,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16386,7 +16398,7 @@
         <v>-0.08054411478897006</v>
       </c>
       <c r="D302" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E302">
         <v>0.6229218877120197</v>
@@ -16422,7 +16434,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16436,7 +16448,7 @@
         <v>-0.0483732078109167</v>
       </c>
       <c r="D303" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E303">
         <v>0.6479980699572705</v>
@@ -16472,7 +16484,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16486,7 +16498,7 @@
         <v>-0.0426775957224228</v>
       </c>
       <c r="D304" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E304">
         <v>0.6524376155015337</v>
@@ -16522,7 +16534,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16536,7 +16548,7 @@
         <v>-0.002260839261968961</v>
       </c>
       <c r="D305" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E305">
         <v>0.6839411709174765</v>
@@ -16572,7 +16584,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16586,7 +16598,7 @@
         <v>0.03943267924280081</v>
       </c>
       <c r="D306" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E306">
         <v>0.6803878223669297</v>
@@ -16622,7 +16634,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16636,7 +16648,7 @@
         <v>0.05500064350064493</v>
       </c>
       <c r="D307" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E307">
         <v>0.6927001287001295</v>
@@ -16672,7 +16684,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16686,7 +16698,7 @@
         <v>0.07574238655207255</v>
       </c>
       <c r="D308" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E308">
         <v>0.7091042448776848</v>
@@ -16722,7 +16734,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16736,7 +16748,7 @@
         <v>0.08618633115302332</v>
       </c>
       <c r="D309" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E309">
         <v>0.7173640946001099</v>
@@ -16772,7 +16784,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16786,7 +16798,7 @@
         <v>0.07952257316260702</v>
       </c>
       <c r="D310" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E310">
         <v>0.7120938981666245</v>
@@ -16822,7 +16834,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -16836,7 +16848,7 @@
         <v>0.081678859116463</v>
       </c>
       <c r="D311" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E311">
         <v>0.7137992497955294</v>
@@ -16872,7 +16884,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -16886,7 +16898,7 @@
         <v>0.06474641494014977</v>
       </c>
       <c r="D312" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E312">
         <v>0.7004078110553276</v>
@@ -16922,7 +16934,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -16972,7 +16984,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -16986,7 +16998,7 @@
         <v>1.960909376633722</v>
       </c>
       <c r="D314" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E314">
         <v>2.138929585003361</v>
@@ -17022,7 +17034,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17036,7 +17048,7 @@
         <v>1.947964403173783</v>
       </c>
       <c r="D315" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E315">
         <v>2.147208583938033</v>
@@ -17072,7 +17084,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17086,7 +17098,7 @@
         <v>1.932043342863845</v>
       </c>
       <c r="D316" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E316">
         <v>2.122917095879669</v>
@@ -17122,7 +17134,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17136,7 +17148,7 @@
         <v>0.2594780143743354</v>
       </c>
       <c r="D317" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E317">
         <v>0.7830777081829752</v>
@@ -17172,7 +17184,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17186,7 +17198,7 @@
         <v>1.278216256083103</v>
       </c>
       <c r="D318" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E318">
         <v>1.062585376937486</v>
@@ -17222,7 +17234,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17236,7 +17248,7 @@
         <v>0.2571117245679739</v>
       </c>
       <c r="D319" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E319">
         <v>0.7813753414158087</v>
@@ -17272,7 +17284,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17286,7 +17298,7 @@
         <v>1.276326628971548</v>
       </c>
       <c r="D320" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E320">
         <v>1.021375341415808</v>
@@ -17322,7 +17334,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17336,7 +17348,7 @@
         <v>0.2547431471759269</v>
       </c>
       <c r="D321" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E321">
         <v>0.7796713289035446</v>
@@ -17372,7 +17384,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17386,7 +17398,7 @@
         <v>1.274435175082935</v>
       </c>
       <c r="D322" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E322">
         <v>1.052874615614509</v>
@@ -17422,7 +17434,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17436,7 +17448,7 @@
         <v>0.2470149029115583</v>
       </c>
       <c r="D323" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E323">
         <v>0.7741114409435672</v>
@@ -17472,7 +17484,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17486,7 +17498,7 @@
         <v>1.26826369944736</v>
       </c>
       <c r="D324" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E324">
         <v>1.034111440943567</v>
@@ -17522,7 +17534,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17536,7 +17548,7 @@
         <v>0.2526232548771112</v>
       </c>
       <c r="D325" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E325">
         <v>0.7686098184274901</v>
@@ -17572,7 +17584,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17586,7 +17598,7 @@
         <v>0.239367647614211</v>
       </c>
       <c r="D326" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E326">
         <v>0.7686098184274901</v>
@@ -17622,7 +17634,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17636,7 +17648,7 @@
         <v>1.262156898454514</v>
       </c>
       <c r="D327" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E327">
         <v>1.031923720243215</v>
@@ -17672,7 +17684,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17686,7 +17698,7 @@
         <v>0.2409427190185853</v>
       </c>
       <c r="D328" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E328">
         <v>0.7599575696433969</v>
@@ -17722,7 +17734,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17736,7 +17748,7 @@
         <v>0.2273410218043215</v>
       </c>
       <c r="D329" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E329">
         <v>0.7599575696433969</v>
@@ -17772,7 +17784,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17786,7 +17798,7 @@
         <v>1.252552902304171</v>
       </c>
       <c r="D330" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E330">
         <v>0.9967584182505289</v>
@@ -17822,7 +17834,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17836,7 +17848,7 @@
         <v>0.2269256946216702</v>
       </c>
       <c r="D331" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E331">
         <v>0.7495745886086449</v>
@@ -17872,7 +17884,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17886,7 +17898,7 @@
         <v>0.2129086781660163</v>
       </c>
       <c r="D332" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E332">
         <v>0.7495745886086449</v>
@@ -17922,7 +17934,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -17936,7 +17948,7 @@
         <v>0.2121775147285025</v>
       </c>
       <c r="D333" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E333">
         <v>0.7386500109100023</v>
@@ -17972,7 +17984,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -17986,7 +17998,7 @@
         <v>0.1977235151649031</v>
       </c>
       <c r="D334" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E334">
         <v>0.7386500109100023</v>
@@ -18022,7 +18034,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18036,7 +18048,7 @@
         <v>0.199326851658896</v>
       </c>
       <c r="D335" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E335">
         <v>0.7291310012288121</v>
@@ -18072,7 +18084,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18086,7 +18098,7 @@
         <v>0.1844920917080488</v>
       </c>
       <c r="D336" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E336">
         <v>0.7291310012288121</v>
@@ -18122,7 +18134,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18136,7 +18148,7 @@
         <v>0.1896647385133041</v>
       </c>
       <c r="D337" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E337">
         <v>0.7219738803802256</v>
@@ -18172,7 +18184,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18186,7 +18198,7 @@
         <v>0.1745436937285134</v>
       </c>
       <c r="D338" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E338">
         <v>0.7219738803802256</v>
@@ -18222,7 +18234,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18236,7 +18248,7 @@
         <v>0.1786481289410795</v>
       </c>
       <c r="D339" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E339">
         <v>0.7138134288452445</v>
@@ -18272,7 +18284,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18286,7 +18298,7 @@
         <v>0.1666907242521811</v>
       </c>
       <c r="D340" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E340">
         <v>0.7049560920386531</v>
@@ -18322,7 +18334,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18336,7 +18348,7 @@
         <v>0.1508900298653248</v>
       </c>
       <c r="D341" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E341">
         <v>0.693251873974315</v>
@@ -18372,7 +18384,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18386,7 +18398,7 @@
         <v>0.1352367892059676</v>
       </c>
       <c r="D342" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E342">
         <v>0.6816568808933097</v>
@@ -18422,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18436,7 +18448,7 @@
         <v>0.1201773280539471</v>
       </c>
       <c r="D343" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E343">
         <v>0.6933866727498734</v>
@@ -18472,7 +18484,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18486,7 +18498,7 @@
         <v>0.1037985724993549</v>
       </c>
       <c r="D344" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E344">
         <v>0.681618233573611</v>
@@ -18522,7 +18534,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18536,7 +18548,7 @@
         <v>0.09387182781882397</v>
       </c>
       <c r="D345" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E345">
         <v>0.6744856836920441</v>
@@ -18572,7 +18584,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18586,7 +18598,7 @@
         <v>0.0865999587373627</v>
       </c>
       <c r="D346" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E346">
         <v>0.669260711092772</v>
@@ -18622,7 +18634,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18636,7 +18648,7 @@
         <v>0.07648563427817057</v>
       </c>
       <c r="D347" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E347">
         <v>0.6619933816665378</v>
@@ -18672,7 +18684,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18686,7 +18698,7 @@
         <v>0.1318670093468981</v>
       </c>
       <c r="D348" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E348">
         <v>0.6619933816665378</v>
@@ -18722,7 +18734,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18736,7 +18748,7 @@
         <v>0.05684614970067581</v>
       </c>
       <c r="D349" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E349">
         <v>0.6478820483034489</v>
@@ -18772,7 +18784,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18786,7 +18798,7 @@
         <v>0.1120820471058663</v>
       </c>
       <c r="D350" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E350">
         <v>0.6478820483034489</v>
@@ -18822,7 +18834,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18836,7 +18848,7 @@
         <v>0.104345747039986</v>
       </c>
       <c r="D351" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E351">
         <v>0.6353846079319303</v>
@@ -18872,7 +18884,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18886,7 +18898,7 @@
         <v>0.09455986266744842</v>
       </c>
       <c r="D352" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E352">
         <v>0.6353846079319303</v>
@@ -18922,7 +18934,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -18936,7 +18948,7 @@
         <v>0.09223443486348204</v>
       </c>
       <c r="D353" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E353">
         <v>0.6266174640429685</v>
@@ -18972,7 +18984,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -18986,7 +18998,7 @@
         <v>0.08226778463756368</v>
       </c>
       <c r="D354" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E354">
         <v>0.6266174640429685</v>
@@ -19022,7 +19034,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19036,7 +19048,7 @@
         <v>0.08340490038981674</v>
       </c>
       <c r="D355" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E355">
         <v>0.6202259353568076</v>
@@ -19072,7 +19084,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19086,7 +19098,7 @@
         <v>0.07330646606727642</v>
       </c>
       <c r="D356" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E356">
         <v>0.6202259353568076</v>
@@ -19122,7 +19134,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19136,7 +19148,7 @@
         <v>0.07295411923666117</v>
       </c>
       <c r="D357" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E357">
         <v>0.612660817656389</v>
@@ -19172,7 +19184,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19186,7 +19198,7 @@
         <v>0.08535626663036044</v>
       </c>
       <c r="D358" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E358">
         <v>0.6088483639401687</v>
@@ -19222,7 +19234,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19236,7 +19248,7 @@
         <v>0.08337683007148078</v>
       </c>
       <c r="D359" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E359">
         <v>0.6075510305198217</v>
@@ -19272,7 +19284,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19286,7 +19298,7 @@
         <v>0.07990431184045077</v>
       </c>
       <c r="D360" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E360">
         <v>0.6052751233008362</v>
@@ -19322,7 +19334,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19336,7 +19348,7 @@
         <v>0.07628301150993844</v>
       </c>
       <c r="D361" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E361">
         <v>0.602901703489622</v>
@@ -19372,7 +19384,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19386,7 +19398,7 @@
         <v>0.07542641148821705</v>
       </c>
       <c r="D362" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E362">
         <v>0.6023402832051152</v>
@@ -19422,7 +19434,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19436,7 +19448,7 @@
         <v>0.1032857601349302</v>
       </c>
       <c r="D363" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E363">
         <v>0.6912581248872549</v>
@@ -19472,7 +19484,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19486,7 +19498,7 @@
         <v>0.1032494207491959</v>
       </c>
       <c r="D364" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E364">
         <v>0.6912346254178132</v>
@@ -19522,7 +19534,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19536,7 +19548,7 @@
         <v>0.1066794748126041</v>
       </c>
       <c r="D365" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E365">
         <v>0.6912346254178132</v>
@@ -19572,7 +19584,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19586,7 +19598,7 @@
         <v>0.1027485095490785</v>
       </c>
       <c r="D366" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E366">
         <v>0.6909107028417374</v>
@@ -19622,7 +19634,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19636,7 +19648,7 @@
         <v>0.2672388330248614</v>
       </c>
       <c r="D367" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E367">
         <v>0.6512870381223137</v>
@@ -19672,7 +19684,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19686,7 +19698,7 @@
         <v>1.002091352902854</v>
       </c>
       <c r="D368" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E368">
         <v>0.6273460301711169</v>
@@ -19722,7 +19734,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19736,7 +19748,7 @@
         <v>0.2741430547802919</v>
       </c>
       <c r="D369" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E369">
         <v>0.6566021929657799</v>
@@ -19772,7 +19784,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19786,7 +19798,7 @@
         <v>1.008173643496924</v>
       </c>
       <c r="D370" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E370">
         <v>0.6385919967269027</v>
@@ -19822,7 +19834,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19836,7 +19848,7 @@
         <v>1.008413016850501</v>
       </c>
       <c r="D371" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E371">
         <v>0.6476121959680365</v>
@@ -19872,7 +19884,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19886,7 +19898,7 @@
         <v>1.0141677914568</v>
       </c>
       <c r="D372" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E372">
         <v>0.6530040568604247</v>
@@ -19922,7 +19934,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -19936,7 +19948,7 @@
         <v>1.021395485086037</v>
       </c>
       <c r="D373" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E373">
         <v>0.6597759499905214</v>
@@ -19972,7 +19984,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -19986,7 +19998,7 @@
         <v>0.337619285136195</v>
       </c>
       <c r="D374" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E374">
         <v>0.6834894621989671</v>
@@ -20036,7 +20048,7 @@
         <v>1.028457881859448</v>
       </c>
       <c r="D375" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E375">
         <v>0.6663929703908342</v>
@@ -20086,7 +20098,7 @@
         <v>0.3407332921319595</v>
       </c>
       <c r="D376" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E376">
         <v>0.686217663018265</v>
@@ -20122,7 +20134,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20136,7 +20148,7 @@
         <v>1.031516773687146</v>
       </c>
       <c r="D377" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E377">
         <v>0.6692589591302986</v>
@@ -20172,7 +20184,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20186,7 +20198,7 @@
         <v>0.3675382538855252</v>
       </c>
       <c r="D378" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E378">
         <v>0.6963061351309554</v>
@@ -20222,7 +20234,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20236,7 +20248,7 @@
         <v>0.3522484168666464</v>
       </c>
       <c r="D379" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E379">
         <v>0.6963061351309554</v>
@@ -20272,7 +20284,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20286,7 +20298,7 @@
         <v>1.042828090904405</v>
       </c>
       <c r="D380" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E380">
         <v>0.6798569500365592</v>
@@ -20322,7 +20334,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20336,7 +20348,7 @@
         <v>0.3762667112083611</v>
       </c>
       <c r="D381" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E381">
         <v>0.7040214679431049</v>
@@ -20372,7 +20384,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20386,7 +20398,7 @@
         <v>0.3610548068441501</v>
       </c>
       <c r="D382" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E382">
         <v>0.7040214679431049</v>
@@ -20422,7 +20434,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20436,7 +20448,7 @@
         <v>1.051478615572572</v>
       </c>
       <c r="D383" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E383">
         <v>0.6879619461220496</v>
@@ -20472,7 +20484,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20486,7 +20498,7 @@
         <v>0.38797225747824</v>
       </c>
       <c r="D384" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E384">
         <v>0.7586166008276201</v>
@@ -20522,7 +20534,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20536,7 +20548,7 @@
         <v>0.3728648669200105</v>
       </c>
       <c r="D385" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E385">
         <v>0.7586166008276201</v>
@@ -20572,7 +20584,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20586,7 +20598,7 @@
         <v>1.06307964803647</v>
       </c>
       <c r="D386" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E386">
         <v>0.6988313819440801</v>
@@ -20622,7 +20634,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20636,7 +20648,7 @@
         <v>0.4038111409481839</v>
       </c>
       <c r="D387" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E387">
         <v>0.7736069726831025</v>
@@ -20672,7 +20684,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20686,7 +20698,7 @@
         <v>0.3888451689923644</v>
       </c>
       <c r="D388" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E388">
         <v>0.7736069726831025</v>
@@ -20722,7 +20734,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20736,7 +20748,7 @@
         <v>1.078777112904004</v>
       </c>
       <c r="D389" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E389">
         <v>0.7135389165947423</v>
@@ -20772,7 +20784,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20786,7 +20798,7 @@
         <v>0.421605003019891</v>
       </c>
       <c r="D390" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E390">
         <v>0.7904475921438254</v>
@@ -20822,7 +20834,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20836,7 +20848,7 @@
         <v>0.4067979048325689</v>
       </c>
       <c r="D391" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E391">
         <v>0.7904475921438254</v>
@@ -20872,7 +20884,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20886,7 +20898,7 @@
         <v>1.096412101207214</v>
       </c>
       <c r="D392" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E392">
         <v>0.7300617885184704</v>
@@ -20922,7 +20934,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -20936,7 +20948,7 @@
         <v>0.4388301519378184</v>
       </c>
       <c r="D393" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E393">
         <v>0.8067499652268637</v>
@@ -20972,7 +20984,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -20986,7 +20998,7 @@
         <v>0.4241768497229779</v>
       </c>
       <c r="D394" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E394">
         <v>0.8067499652268637</v>
@@ -21022,7 +21034,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21036,7 +21048,7 @@
         <v>1.113483454152659</v>
       </c>
       <c r="D395" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E395">
         <v>0.7460565696565458</v>
@@ -21072,7 +21084,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21086,7 +21098,7 @@
         <v>3.151956422625536</v>
       </c>
       <c r="D396" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E396">
         <v>2.557425288074153</v>
@@ -21122,7 +21134,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21136,7 +21148,7 @@
         <v>3.0302870572645</v>
       </c>
       <c r="D397" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E397">
         <v>2.557425288074153</v>
@@ -21172,7 +21184,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21186,7 +21198,7 @@
         <v>3.126010595645193</v>
       </c>
       <c r="D398" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E398">
         <v>2.97243338415726</v>
@@ -21222,7 +21234,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21236,7 +21248,7 @@
         <v>3.095533634113468</v>
       </c>
       <c r="D399" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E399">
         <v>2.97243338415726</v>
@@ -21272,7 +21284,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21286,7 +21298,7 @@
         <v>3.185945174511515</v>
       </c>
       <c r="D400" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E400">
         <v>2.586594739319583</v>
@@ -21322,7 +21334,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21372,7 +21384,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21422,7 +21434,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21436,7 +21448,7 @@
         <v>3.22654267572782</v>
       </c>
       <c r="D403" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E403">
         <v>2.621435878423129</v>
@@ -21472,7 +21484,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21522,7 +21534,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21572,7 +21584,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21586,7 +21598,7 @@
         <v>3.259685052120739</v>
       </c>
       <c r="D406" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E406">
         <v>2.649878962640932</v>
@@ -21622,7 +21634,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21672,7 +21684,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21722,7 +21734,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21736,7 +21748,7 @@
         <v>3.290901329475496</v>
       </c>
       <c r="D409" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E409">
         <v>2.729219817527112</v>
@@ -21772,7 +21784,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21822,7 +21834,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -21836,7 +21848,7 @@
         <v>3.324668655156648</v>
       </c>
       <c r="D411" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E411">
         <v>2.758703228756178</v>
@@ -21872,7 +21884,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -21922,7 +21934,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -21936,7 +21948,7 @@
         <v>3.997489231461685</v>
       </c>
       <c r="D413" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E413">
         <v>4.120993158546191</v>
@@ -21972,7 +21984,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -21986,7 +21998,7 @@
         <v>3.986341271722335</v>
       </c>
       <c r="D414" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E414">
         <v>4.110505275370355</v>
@@ -22022,7 +22034,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22036,7 +22048,7 @@
         <v>3.963562911043303</v>
       </c>
       <c r="D415" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E415">
         <v>4.089075633415739</v>
@@ -22072,7 +22084,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22086,7 +22098,7 @@
         <v>3.944710231985321</v>
       </c>
       <c r="D416" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E416">
         <v>4.071339231407243</v>
@@ -22122,7 +22134,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22136,7 +22148,7 @@
         <v>3.924958557318009</v>
       </c>
       <c r="D417" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E417">
         <v>4.052757063792601</v>
@@ -22172,7 +22184,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22186,7 +22198,7 @@
         <v>3.903529915296924</v>
       </c>
       <c r="D418" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E418">
         <v>4.032597222943817</v>
@@ -22222,7 +22234,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22236,7 +22248,7 @@
         <v>3.886527377365554</v>
       </c>
       <c r="D419" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E419">
         <v>4.016601414232067</v>
@@ -22272,7 +22284,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22286,7 +22298,7 @@
         <v>3.873496712167727</v>
       </c>
       <c r="D420" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E420">
         <v>4.004342301578848</v>
@@ -22322,7 +22334,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22336,7 +22348,7 @@
         <v>3.861649782293752</v>
       </c>
       <c r="D421" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E421">
         <v>3.993196834657938</v>
@@ -22372,7 +22384,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22386,7 +22398,7 @@
         <v>3.834878726120355</v>
       </c>
       <c r="D422" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E422">
         <v>3.968010906810598</v>
@@ -22422,7 +22434,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22436,7 +22448,7 @@
         <v>3.808598117223633</v>
       </c>
       <c r="D423" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E423">
         <v>3.943286386598549</v>
@@ -22472,7 +22484,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22486,7 +22498,7 @@
         <v>3.800233949670756</v>
       </c>
       <c r="D424" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E424">
         <v>3.935417465808672</v>
@@ -22522,7 +22534,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22536,7 +22548,7 @@
         <v>3.798188965274105</v>
       </c>
       <c r="D425" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E425">
         <v>3.933493566014454</v>
@@ -22572,7 +22584,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22586,7 +22598,7 @@
         <v>3.788920893245179</v>
       </c>
       <c r="D426" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E426">
         <v>3.924774261408294</v>
@@ -22622,7 +22634,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22636,7 +22648,7 @@
         <v>3.79888341910942</v>
       </c>
       <c r="D427" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E427">
         <v>3.934146900872678</v>
@@ -22672,7 +22684,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22686,7 +22698,7 @@
         <v>3.829553568848083</v>
       </c>
       <c r="D428" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E428">
         <v>3.963001054903131</v>
@@ -22722,7 +22734,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22736,7 +22748,7 @@
         <v>3.855665816250932</v>
       </c>
       <c r="D429" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E429">
         <v>3.987567182393969</v>
@@ -22772,7 +22784,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22786,7 +22798,7 @@
         <v>3.855953228285221</v>
       </c>
       <c r="D430" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E430">
         <v>3.987837576610439</v>
@@ -22822,7 +22834,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -22836,7 +22848,7 @@
         <v>3.861717839622725</v>
       </c>
       <c r="D431" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E431">
         <v>3.993260862276643</v>
@@ -22872,7 +22884,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22886,7 +22898,7 @@
         <v>3.86639892628536</v>
       </c>
       <c r="D432" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E432">
         <v>3.997664779334253</v>
@@ -22922,7 +22934,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -22936,7 +22948,7 @@
         <v>3.846535379684417</v>
       </c>
       <c r="D433" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E433">
         <v>3.978977363782051</v>
@@ -22972,7 +22984,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -22986,7 +22998,7 @@
         <v>3.87004024621212</v>
       </c>
       <c r="D434" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E434">
         <v>4.001090494791666</v>
@@ -23022,7 +23034,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23036,7 +23048,7 @@
         <v>3.886357305969927</v>
       </c>
       <c r="D435" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E435">
         <v>4.016441412853287</v>
@@ -23072,7 +23084,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23086,7 +23098,7 @@
         <v>3.903938192034373</v>
       </c>
       <c r="D436" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E436">
         <v>4.032981325400759</v>
@@ -23122,7 +23134,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23136,7 +23148,7 @@
         <v>3.961072830353248</v>
       </c>
       <c r="D437" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E437">
         <v>4.086732991713911</v>
@@ -23172,7 +23184,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23186,7 +23198,7 @@
         <v>3.981576852757343</v>
       </c>
       <c r="D438" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E438">
         <v>4.106022960159869</v>
@@ -23222,7 +23234,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23236,7 +23248,7 @@
         <v>3.971450680589221</v>
       </c>
       <c r="D439" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E439">
         <v>4.096496363975386</v>
@@ -23272,7 +23284,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23286,7 +23298,7 @@
         <v>3.968816281770093</v>
       </c>
       <c r="D440" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E440">
         <v>4.094017949296864</v>
@@ -23322,7 +23334,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23336,7 +23348,7 @@
         <v>3.926789933050578</v>
       </c>
       <c r="D441" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E441">
         <v>4.054480002804163</v>
@@ -23372,7 +23384,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23386,7 +23398,7 @@
         <v>3.825723707829902</v>
       </c>
       <c r="D442" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E442">
         <v>3.959397961971553</v>
@@ -23422,7 +23434,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23436,7 +23448,7 @@
         <v>3.746022583750348</v>
       </c>
       <c r="D443" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E443">
         <v>3.774732961488833</v>
@@ -23472,7 +23484,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23486,7 +23498,7 @@
         <v>3.686827463477967</v>
       </c>
       <c r="D444" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E444">
         <v>3.715927282797192</v>
@@ -23522,7 +23534,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23536,7 +23548,7 @@
         <v>3.536490631366341</v>
       </c>
       <c r="D445" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E445">
         <v>3.566579508791563</v>
@@ -23572,7 +23584,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23586,7 +23598,7 @@
         <v>3.478129127613399</v>
       </c>
       <c r="D446" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E446">
         <v>3.508601962300153</v>
@@ -23622,7 +23634,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23636,7 +23648,7 @@
         <v>3.446322550887229</v>
       </c>
       <c r="D447" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E447">
         <v>3.477004639368234</v>
@@ -23672,7 +23684,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23686,7 +23698,7 @@
         <v>3.437244026062129</v>
       </c>
       <c r="D448" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E448">
         <v>3.467985841680141</v>
@@ -23722,7 +23734,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23736,7 +23748,7 @@
         <v>3.495394814734395</v>
       </c>
       <c r="D449" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E449">
         <v>3.525754059374301</v>
@@ -23772,7 +23784,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23786,7 +23798,7 @@
         <v>3.479433369341057</v>
       </c>
       <c r="D450" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E450">
         <v>3.509897623490129</v>
@@ -23822,7 +23834,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23836,7 +23848,7 @@
         <v>3.450931319109172</v>
       </c>
       <c r="D451" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E451">
         <v>3.481583086746612</v>
@@ -23872,7 +23884,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23886,7 +23898,7 @@
         <v>3.40927622228758</v>
       </c>
       <c r="D452" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E452">
         <v>3.440202036614636</v>
@@ -23922,7 +23934,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -23936,7 +23948,7 @@
         <v>2.761972833438688</v>
       </c>
       <c r="D453" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E453">
         <v>2.26641548960003</v>
@@ -23972,57 +23984,57 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="454" spans="1:16">
       <c r="A454" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B454" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C454">
-        <v>2.702231862141191</v>
+        <v>3.085589532934493</v>
       </c>
       <c r="D454" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E454">
-        <v>2.210437729092927</v>
+        <v>3.118644864954661</v>
       </c>
       <c r="F454">
         <v>-1</v>
       </c>
       <c r="G454">
-        <v>0.003597768137858809</v>
+        <v>0.004014410467065507</v>
       </c>
       <c r="H454">
-        <v>0.003049562270907073</v>
+        <v>0.004041355135045339</v>
       </c>
       <c r="I454">
-        <v>0.491794133048264</v>
+        <v>-0.03305533202016786</v>
       </c>
       <c r="J454">
-        <v>0.3525733368967002</v>
+        <v>0.3055332020167811</v>
       </c>
       <c r="K454">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L454">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M454">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N454">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O454">
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24033,28 +24045,28 @@
         <v>54</v>
       </c>
       <c r="C455">
-        <v>2.65619166177536</v>
+        <v>2.702231862141191</v>
       </c>
       <c r="D455" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E455">
-        <v>2.167297698828881</v>
+        <v>2.210437729092927</v>
       </c>
       <c r="F455">
         <v>-1</v>
       </c>
       <c r="G455">
-        <v>0.00364380833822464</v>
+        <v>0.003597768137858809</v>
       </c>
       <c r="H455">
-        <v>0.003092702301171119</v>
+        <v>0.003049562270907073</v>
       </c>
       <c r="I455">
-        <v>0.4888939629464795</v>
+        <v>0.491794133048264</v>
       </c>
       <c r="J455">
-        <v>0.3888254631690077</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K455">
         <v>1.27</v>
@@ -24072,57 +24084,57 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="456" spans="1:16">
       <c r="A456" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B456" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C456">
-        <v>2.633560752891249</v>
+        <v>3.014088527917016</v>
       </c>
       <c r="D456" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E456">
-        <v>2.146092359008336</v>
+        <v>3.047614261285982</v>
       </c>
       <c r="F456">
         <v>-1</v>
       </c>
       <c r="G456">
-        <v>0.003666439247108751</v>
+        <v>0.004085911472082985</v>
       </c>
       <c r="H456">
-        <v>0.003113907640991664</v>
+        <v>0.004112385738714018</v>
       </c>
       <c r="I456">
-        <v>0.4874683938829132</v>
+        <v>-0.03352573336896691</v>
       </c>
       <c r="J456">
-        <v>0.4066450764635833</v>
+        <v>0.3525733368967002</v>
       </c>
       <c r="K456">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L456">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="M456">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="N456">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="O456">
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24133,28 +24145,28 @@
         <v>54</v>
       </c>
       <c r="C457">
-        <v>2.575080697535542</v>
+        <v>2.65619166177536</v>
       </c>
       <c r="D457" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E457">
-        <v>2.091296086667161</v>
+        <v>2.167297698828881</v>
       </c>
       <c r="F457">
         <v>-1</v>
       </c>
       <c r="G457">
-        <v>0.003724919302464458</v>
+        <v>0.00364380833822464</v>
       </c>
       <c r="H457">
-        <v>0.003168703913332839</v>
+        <v>0.003092702301171119</v>
       </c>
       <c r="I457">
-        <v>0.4837846108683808</v>
+        <v>0.4888939629464795</v>
       </c>
       <c r="J457">
-        <v>0.4526923641452424</v>
+        <v>0.3888254631690077</v>
       </c>
       <c r="K457">
         <v>1.27</v>
@@ -24172,57 +24184,507 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="458" spans="1:16">
       <c r="A458" s="1">
+        <v>1</v>
+      </c>
+      <c r="B458" t="s">
+        <v>53</v>
+      </c>
+      <c r="C458">
+        <v>2.958985295983108</v>
+      </c>
+      <c r="D458" t="s">
+        <v>126</v>
+      </c>
+      <c r="E458">
+        <v>2.992873550614799</v>
+      </c>
+      <c r="F458">
+        <v>-1</v>
+      </c>
+      <c r="G458">
+        <v>0.004141014704016891</v>
+      </c>
+      <c r="H458">
+        <v>0.004167126449385202</v>
+      </c>
+      <c r="I458">
+        <v>-0.03388825463169054</v>
+      </c>
+      <c r="J458">
+        <v>0.3888254631690077</v>
+      </c>
+      <c r="K458">
+        <v>1.52</v>
+      </c>
+      <c r="L458">
+        <v>3.55</v>
+      </c>
+      <c r="M458">
+        <v>1.51</v>
+      </c>
+      <c r="N458">
+        <v>3.58</v>
+      </c>
+      <c r="O458">
+        <v>1</v>
+      </c>
+      <c r="P458" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="459" spans="1:16">
+      <c r="A459" s="1">
         <v>0</v>
       </c>
-      <c r="B458" t="s">
+      <c r="B459" t="s">
         <v>54</v>
       </c>
-      <c r="C458">
+      <c r="C459">
+        <v>2.633560752891249</v>
+      </c>
+      <c r="D459" t="s">
+        <v>127</v>
+      </c>
+      <c r="E459">
+        <v>2.146092359008336</v>
+      </c>
+      <c r="F459">
+        <v>-1</v>
+      </c>
+      <c r="G459">
+        <v>0.003666439247108751</v>
+      </c>
+      <c r="H459">
+        <v>0.003113907640991664</v>
+      </c>
+      <c r="I459">
+        <v>0.4874683938829132</v>
+      </c>
+      <c r="J459">
+        <v>0.4066450764635833</v>
+      </c>
+      <c r="K459">
+        <v>1.27</v>
+      </c>
+      <c r="L459">
+        <v>3.15</v>
+      </c>
+      <c r="M459">
+        <v>1.19</v>
+      </c>
+      <c r="N459">
+        <v>2.63</v>
+      </c>
+      <c r="O459">
+        <v>1</v>
+      </c>
+      <c r="P459" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="460" spans="1:16">
+      <c r="A460" s="1">
+        <v>1</v>
+      </c>
+      <c r="B460" t="s">
+        <v>53</v>
+      </c>
+      <c r="C460">
+        <v>2.931899483775353</v>
+      </c>
+      <c r="D460" t="s">
+        <v>126</v>
+      </c>
+      <c r="E460">
+        <v>2.965965934539989</v>
+      </c>
+      <c r="F460">
+        <v>-1</v>
+      </c>
+      <c r="G460">
+        <v>0.004168100516224646</v>
+      </c>
+      <c r="H460">
+        <v>0.004194034065460011</v>
+      </c>
+      <c r="I460">
+        <v>-0.03406645076463599</v>
+      </c>
+      <c r="J460">
+        <v>0.4066450764635833</v>
+      </c>
+      <c r="K460">
+        <v>1.52</v>
+      </c>
+      <c r="L460">
+        <v>3.55</v>
+      </c>
+      <c r="M460">
+        <v>1.51</v>
+      </c>
+      <c r="N460">
+        <v>3.58</v>
+      </c>
+      <c r="O460">
+        <v>1</v>
+      </c>
+      <c r="P460" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="461" spans="1:16">
+      <c r="A461" s="1">
+        <v>2</v>
+      </c>
+      <c r="B461" t="s">
+        <v>55</v>
+      </c>
+      <c r="C461">
+        <v>2.641440805483828</v>
+      </c>
+      <c r="D461" t="s">
+        <v>56</v>
+      </c>
+      <c r="E461">
+        <v>2.665507256248464</v>
+      </c>
+      <c r="F461">
+        <v>-1</v>
+      </c>
+      <c r="G461">
+        <v>0.004178559194516173</v>
+      </c>
+      <c r="H461">
+        <v>0.004194492743751537</v>
+      </c>
+      <c r="I461">
+        <v>-0.02406645076463576</v>
+      </c>
+      <c r="J461">
+        <v>0.4066450764635833</v>
+      </c>
+      <c r="K461">
+        <v>1.89</v>
+      </c>
+      <c r="L461">
+        <v>3.41</v>
+      </c>
+      <c r="M461">
+        <v>1.88</v>
+      </c>
+      <c r="N461">
+        <v>3.43</v>
+      </c>
+      <c r="O461">
+        <v>1</v>
+      </c>
+      <c r="P461" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="462" spans="1:16">
+      <c r="A462" s="1">
+        <v>0</v>
+      </c>
+      <c r="B462" t="s">
+        <v>54</v>
+      </c>
+      <c r="C462">
+        <v>2.575080697535542</v>
+      </c>
+      <c r="D462" t="s">
+        <v>127</v>
+      </c>
+      <c r="E462">
+        <v>2.091296086667161</v>
+      </c>
+      <c r="F462">
+        <v>-1</v>
+      </c>
+      <c r="G462">
+        <v>0.003724919302464458</v>
+      </c>
+      <c r="H462">
+        <v>0.003168703913332839</v>
+      </c>
+      <c r="I462">
+        <v>0.4837846108683808</v>
+      </c>
+      <c r="J462">
+        <v>0.4526923641452424</v>
+      </c>
+      <c r="K462">
+        <v>1.27</v>
+      </c>
+      <c r="L462">
+        <v>3.15</v>
+      </c>
+      <c r="M462">
+        <v>1.19</v>
+      </c>
+      <c r="N462">
+        <v>2.63</v>
+      </c>
+      <c r="O462">
+        <v>1</v>
+      </c>
+      <c r="P462" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="463" spans="1:16">
+      <c r="A463" s="1">
+        <v>1</v>
+      </c>
+      <c r="B463" t="s">
+        <v>53</v>
+      </c>
+      <c r="C463">
+        <v>2.861907606499231</v>
+      </c>
+      <c r="D463" t="s">
+        <v>126</v>
+      </c>
+      <c r="E463">
+        <v>2.896434530140684</v>
+      </c>
+      <c r="F463">
+        <v>-1</v>
+      </c>
+      <c r="G463">
+        <v>0.004238092393500768</v>
+      </c>
+      <c r="H463">
+        <v>0.004263565469859316</v>
+      </c>
+      <c r="I463">
+        <v>-0.03452692364145271</v>
+      </c>
+      <c r="J463">
+        <v>0.4526923641452424</v>
+      </c>
+      <c r="K463">
+        <v>1.52</v>
+      </c>
+      <c r="L463">
+        <v>3.55</v>
+      </c>
+      <c r="M463">
+        <v>1.51</v>
+      </c>
+      <c r="N463">
+        <v>3.58</v>
+      </c>
+      <c r="O463">
+        <v>1</v>
+      </c>
+      <c r="P463" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="464" spans="1:16">
+      <c r="A464" s="1">
+        <v>2</v>
+      </c>
+      <c r="B464" t="s">
+        <v>56</v>
+      </c>
+      <c r="C464">
+        <v>2.578938355406945</v>
+      </c>
+      <c r="D464" t="s">
+        <v>128</v>
+      </c>
+      <c r="E464">
+        <v>2.457788362745826</v>
+      </c>
+      <c r="F464">
+        <v>-1</v>
+      </c>
+      <c r="G464">
+        <v>0.004281061644593056</v>
+      </c>
+      <c r="H464">
+        <v>0.004042211637254174</v>
+      </c>
+      <c r="I464">
+        <v>0.121149992661119</v>
+      </c>
+      <c r="J464">
+        <v>0.4526923641452424</v>
+      </c>
+      <c r="K464">
+        <v>1.88</v>
+      </c>
+      <c r="L464">
+        <v>3.43</v>
+      </c>
+      <c r="M464">
+        <v>1.75</v>
+      </c>
+      <c r="N464">
+        <v>3.25</v>
+      </c>
+      <c r="O464">
+        <v>1</v>
+      </c>
+      <c r="P464" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="465" spans="1:16">
+      <c r="A465" s="1">
+        <v>0</v>
+      </c>
+      <c r="B465" t="s">
+        <v>54</v>
+      </c>
+      <c r="C465">
         <v>2.524828470599929</v>
       </c>
-      <c r="D458" t="s">
-        <v>125</v>
-      </c>
-      <c r="E458">
+      <c r="D465" t="s">
+        <v>127</v>
+      </c>
+      <c r="E465">
         <v>2.044209354341666</v>
       </c>
-      <c r="F458">
-        <v>-1</v>
-      </c>
-      <c r="G458">
+      <c r="F465">
+        <v>-1</v>
+      </c>
+      <c r="G465">
         <v>0.003775171529400071</v>
       </c>
-      <c r="H458">
+      <c r="H465">
         <v>0.003215790645658334</v>
       </c>
-      <c r="I458">
+      <c r="I465">
         <v>0.4806191162582629</v>
       </c>
-      <c r="J458">
+      <c r="J465">
         <v>0.4922610467717091</v>
       </c>
-      <c r="K458">
+      <c r="K465">
         <v>1.27</v>
       </c>
-      <c r="L458">
+      <c r="L465">
         <v>3.15</v>
       </c>
-      <c r="M458">
+      <c r="M465">
         <v>1.19</v>
       </c>
-      <c r="N458">
+      <c r="N465">
         <v>2.63</v>
       </c>
-      <c r="O458">
-        <v>1</v>
-      </c>
-      <c r="P458" t="s">
-        <v>317</v>
+      <c r="O465">
+        <v>1</v>
+      </c>
+      <c r="P465" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="466" spans="1:16">
+      <c r="A466" s="1">
+        <v>1</v>
+      </c>
+      <c r="B466" t="s">
+        <v>53</v>
+      </c>
+      <c r="C466">
+        <v>2.801763208907002</v>
+      </c>
+      <c r="D466" t="s">
+        <v>126</v>
+      </c>
+      <c r="E466">
+        <v>2.836685819374719</v>
+      </c>
+      <c r="F466">
+        <v>-1</v>
+      </c>
+      <c r="G466">
+        <v>0.004298236791092998</v>
+      </c>
+      <c r="H466">
+        <v>0.004323314180625281</v>
+      </c>
+      <c r="I466">
+        <v>-0.03492261046771716</v>
+      </c>
+      <c r="J466">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K466">
+        <v>1.52</v>
+      </c>
+      <c r="L466">
+        <v>3.55</v>
+      </c>
+      <c r="M466">
+        <v>1.51</v>
+      </c>
+      <c r="N466">
+        <v>3.58</v>
+      </c>
+      <c r="O466">
+        <v>1</v>
+      </c>
+      <c r="P466" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="467" spans="1:16">
+      <c r="A467" s="1">
+        <v>2</v>
+      </c>
+      <c r="B467" t="s">
+        <v>56</v>
+      </c>
+      <c r="C467">
+        <v>2.504549232069187</v>
+      </c>
+      <c r="D467" t="s">
+        <v>129</v>
+      </c>
+      <c r="E467">
+        <v>2.30331099955266</v>
+      </c>
+      <c r="F467">
+        <v>-1</v>
+      </c>
+      <c r="G467">
+        <v>0.004355450767930814</v>
+      </c>
+      <c r="H467">
+        <v>0.00399668900044734</v>
+      </c>
+      <c r="I467">
+        <v>0.2012382325165265</v>
+      </c>
+      <c r="J467">
+        <v>0.4922610467717091</v>
+      </c>
+      <c r="K467">
+        <v>1.88</v>
+      </c>
+      <c r="L467">
+        <v>3.43</v>
+      </c>
+      <c r="M467">
+        <v>1.72</v>
+      </c>
+      <c r="N467">
+        <v>3.15</v>
+      </c>
+      <c r="O467">
+        <v>1</v>
+      </c>
+      <c r="P467" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
